--- a/GPS_Formativas_2026.xlsx
+++ b/GPS_Formativas_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="GPS_Formativas_2026" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="79">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
   <si>
     <t>Player Name</t>
   </si>
@@ -173,6 +179,12 @@
     <t>Period Tags</t>
   </si>
   <si>
+    <t>18-5-26</t>
+  </si>
+  <si>
+    <t>U19</t>
+  </si>
+  <si>
     <t>Facundo Bertolotti</t>
   </si>
   <si>
@@ -200,31 +212,58 @@
     <t>Uriel Callorda</t>
   </si>
   <si>
-    <t>Danilo Fern醤dez</t>
-  </si>
-  <si>
-    <t>I馻ki Izuibejeres</t>
-  </si>
-  <si>
-    <t>Luciano L髉ez</t>
-  </si>
-  <si>
-    <t>Mateo Mart韓ez</t>
-  </si>
-  <si>
-    <t>Baltasar Nez</t>
+    <t>Danilo Fernandez</t>
+  </si>
+  <si>
+    <t>U17</t>
+  </si>
+  <si>
+    <t>Iñaki Izuibejeres</t>
+  </si>
+  <si>
+    <t>Luciano Lopez</t>
+  </si>
+  <si>
+    <t>Mateo Martinez</t>
+  </si>
+  <si>
+    <t>Baltasar Nuñez</t>
   </si>
   <si>
     <t>Franco Olivera</t>
   </si>
   <si>
-    <t>Manuel Pe馻</t>
+    <t>Manuel Peña</t>
   </si>
   <si>
     <t>Thiago Piastri</t>
   </si>
   <si>
     <t>Santiago Sosa</t>
+  </si>
+  <si>
+    <t>19-5-26</t>
+  </si>
+  <si>
+    <t>Thiago Amaro</t>
+  </si>
+  <si>
+    <t>INTENSIVO</t>
+  </si>
+  <si>
+    <t>Danilo Fernández</t>
+  </si>
+  <si>
+    <t>Johann Lamas</t>
+  </si>
+  <si>
+    <t>Mateo Martínez</t>
+  </si>
+  <si>
+    <t>Lucas Montandon</t>
+  </si>
+  <si>
+    <t>Santiago Rosa</t>
   </si>
 </sst>
 </file>
@@ -840,11 +879,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1380,10 +1425,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AV13"/>
+  <dimension ref="A1:AX25"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:48">
+    <row r="1" spans="1:50">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1528,65 +1573,71 @@
       <c r="AV1" t="s">
         <v>47</v>
       </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="2" spans="1:48">
+    <row r="2" spans="1:50">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>3.76</v>
       </c>
-      <c r="E2">
+      <c r="G2">
         <v>-4.25</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>6</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>9</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>15</v>
       </c>
-      <c r="I2">
+      <c r="K2">
         <v>0.29</v>
       </c>
-      <c r="J2" s="1">
+      <c r="L2" s="1">
         <v>0.0354166666666667</v>
       </c>
-      <c r="K2">
+      <c r="M2">
         <v>3595.54</v>
       </c>
-      <c r="L2">
+      <c r="N2">
         <v>398.38</v>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>24.696</v>
       </c>
-      <c r="N2">
+      <c r="P2">
         <v>68.62</v>
       </c>
-      <c r="O2">
+      <c r="Q2">
         <v>70.5</v>
       </c>
-      <c r="P2">
+      <c r="R2">
         <v>7.81</v>
       </c>
-      <c r="Q2">
+      <c r="S2">
         <v>0.13</v>
       </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
       <c r="T2">
         <v>0</v>
       </c>
@@ -1599,10 +1650,10 @@
       <c r="W2">
         <v>0</v>
       </c>
-      <c r="X2" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="1">
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
         <v>0</v>
       </c>
       <c r="Z2" s="1">
@@ -1617,980 +1668,1022 @@
       <c r="AC2" s="1">
         <v>0</v>
       </c>
-      <c r="AD2">
+      <c r="AD2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF2">
         <v>316.81</v>
       </c>
-      <c r="AE2">
+      <c r="AG2">
         <v>430.81</v>
       </c>
-      <c r="AF2">
+      <c r="AH2">
         <v>169.69</v>
       </c>
-      <c r="AG2">
+      <c r="AI2">
         <v>1467.47</v>
       </c>
-      <c r="AH2">
+      <c r="AJ2">
         <v>1468.27</v>
       </c>
-      <c r="AI2">
+      <c r="AK2">
         <v>425.36</v>
       </c>
-      <c r="AJ2">
+      <c r="AL2">
         <v>64.59</v>
       </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
       <c r="AM2">
         <v>0</v>
       </c>
       <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
         <v>64.59</v>
       </c>
-      <c r="AO2">
+      <c r="AQ2">
         <v>3</v>
       </c>
-      <c r="AP2">
+      <c r="AR2">
         <v>1.27</v>
       </c>
-      <c r="AQ2">
+      <c r="AS2">
         <v>25</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AT2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:50">
+      <c r="A3" t="s">
         <v>50</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="B3" t="s">
         <v>51</v>
       </c>
-      <c r="AT2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AU2" t="s">
+      <c r="C3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" t="s">
         <v>53</v>
       </c>
-      <c r="AV2" t="s">
-        <v>54</v>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>3.64</v>
+      </c>
+      <c r="G3">
+        <v>-4.3</v>
+      </c>
+      <c r="H3">
+        <v>15</v>
+      </c>
+      <c r="I3">
+        <v>11</v>
+      </c>
+      <c r="J3">
+        <v>26</v>
+      </c>
+      <c r="K3">
+        <v>0.51</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0.0354166666666667</v>
+      </c>
+      <c r="M3">
+        <v>3459.14</v>
+      </c>
+      <c r="N3">
+        <v>321.79</v>
+      </c>
+      <c r="O3">
+        <v>27.756</v>
+      </c>
+      <c r="P3">
+        <v>77.13</v>
+      </c>
+      <c r="Q3">
+        <v>67.83</v>
+      </c>
+      <c r="R3">
+        <v>6.31</v>
+      </c>
+      <c r="S3">
+        <v>0.14</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>313.28</v>
+      </c>
+      <c r="AG3">
+        <v>678.02</v>
+      </c>
+      <c r="AH3">
+        <v>178.9</v>
+      </c>
+      <c r="AI3">
+        <v>1357.11</v>
+      </c>
+      <c r="AJ3">
+        <v>1139.48</v>
+      </c>
+      <c r="AK3">
+        <v>589.85</v>
+      </c>
+      <c r="AL3">
+        <v>159.98</v>
+      </c>
+      <c r="AM3">
+        <v>33.82</v>
+      </c>
+      <c r="AN3">
+        <v>1</v>
+      </c>
+      <c r="AO3">
+        <v>0.66</v>
+      </c>
+      <c r="AP3">
+        <v>193.8</v>
+      </c>
+      <c r="AQ3">
+        <v>10</v>
+      </c>
+      <c r="AR3">
+        <v>3.8</v>
+      </c>
+      <c r="AS3">
+        <v>18</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:48">
-      <c r="A3" t="s">
+    <row r="4" spans="1:50">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>3.97</v>
+      </c>
+      <c r="G4">
+        <v>-5.5</v>
+      </c>
+      <c r="H4">
+        <v>13</v>
+      </c>
+      <c r="I4">
+        <v>17</v>
+      </c>
+      <c r="J4">
+        <v>30</v>
+      </c>
+      <c r="K4">
+        <v>0.59</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0.0354166666666667</v>
+      </c>
+      <c r="M4">
+        <v>3970.96</v>
+      </c>
+      <c r="N4">
+        <v>379.89</v>
+      </c>
+      <c r="O4">
+        <v>25.776</v>
+      </c>
+      <c r="P4">
+        <v>71.62</v>
+      </c>
+      <c r="Q4">
+        <v>77.86</v>
+      </c>
+      <c r="R4">
+        <v>7.45</v>
+      </c>
+      <c r="S4">
+        <v>0.14</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>358.24</v>
+      </c>
+      <c r="AG4">
+        <v>603.39</v>
+      </c>
+      <c r="AH4">
+        <v>168.51</v>
+      </c>
+      <c r="AI4">
+        <v>1751.28</v>
+      </c>
+      <c r="AJ4">
+        <v>1368.42</v>
+      </c>
+      <c r="AK4">
+        <v>555.1</v>
+      </c>
+      <c r="AL4">
+        <v>118.81</v>
+      </c>
+      <c r="AM4">
+        <v>8.73</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0.17</v>
+      </c>
+      <c r="AP4">
+        <v>127.54</v>
+      </c>
+      <c r="AQ4">
+        <v>10</v>
+      </c>
+      <c r="AR4">
+        <v>2.5</v>
+      </c>
+      <c r="AS4">
+        <v>20</v>
+      </c>
+      <c r="AU4" t="s">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>3.64</v>
-      </c>
-      <c r="E3">
-        <v>-4.3</v>
-      </c>
-      <c r="F3">
-        <v>15</v>
-      </c>
-      <c r="G3">
+      <c r="AV4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:50">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>5.26</v>
+      </c>
+      <c r="G5">
+        <v>-3.8</v>
+      </c>
+      <c r="H5">
         <v>11</v>
       </c>
-      <c r="H3">
-        <v>26</v>
-      </c>
-      <c r="I3">
-        <v>0.51</v>
-      </c>
-      <c r="J3" s="1">
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>18</v>
+      </c>
+      <c r="K5">
+        <v>0.35</v>
+      </c>
+      <c r="L5" s="1">
         <v>0.0354166666666667</v>
       </c>
-      <c r="K3">
-        <v>3459.14</v>
-      </c>
-      <c r="L3">
-        <v>321.79</v>
-      </c>
-      <c r="M3">
-        <v>27.756</v>
-      </c>
-      <c r="N3">
-        <v>77.13</v>
-      </c>
-      <c r="O3">
-        <v>67.83</v>
-      </c>
-      <c r="P3">
-        <v>6.31</v>
-      </c>
-      <c r="Q3">
+      <c r="M5">
+        <v>3023.36</v>
+      </c>
+      <c r="N5">
+        <v>419.49</v>
+      </c>
+      <c r="O5">
+        <v>24.624</v>
+      </c>
+      <c r="P5">
+        <v>68.37</v>
+      </c>
+      <c r="Q5">
+        <v>59.28</v>
+      </c>
+      <c r="R5">
+        <v>8.23</v>
+      </c>
+      <c r="S5">
+        <v>0.08</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>199.08</v>
+      </c>
+      <c r="AG5">
+        <v>269.02</v>
+      </c>
+      <c r="AH5">
+        <v>482.02</v>
+      </c>
+      <c r="AI5">
+        <v>1415.79</v>
+      </c>
+      <c r="AJ5">
+        <v>881.71</v>
+      </c>
+      <c r="AK5">
+        <v>194.37</v>
+      </c>
+      <c r="AL5">
+        <v>49.11</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>49.11</v>
+      </c>
+      <c r="AQ5">
+        <v>3</v>
+      </c>
+      <c r="AR5">
+        <v>0.96</v>
+      </c>
+      <c r="AS5">
+        <v>34</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:50">
+      <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>4.39</v>
+      </c>
+      <c r="G6">
+        <v>-4.82</v>
+      </c>
+      <c r="H6">
+        <v>19</v>
+      </c>
+      <c r="I6">
+        <v>18</v>
+      </c>
+      <c r="J6">
+        <v>37</v>
+      </c>
+      <c r="K6">
+        <v>0.61</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0.0423611111111111</v>
+      </c>
+      <c r="M6">
+        <v>4551.53</v>
+      </c>
+      <c r="N6">
+        <v>506.55</v>
+      </c>
+      <c r="O6">
+        <v>29.232</v>
+      </c>
+      <c r="P6">
+        <v>74.29</v>
+      </c>
+      <c r="Q6">
+        <v>78.45</v>
+      </c>
+      <c r="R6">
+        <v>8.3</v>
+      </c>
+      <c r="S6">
         <v>0.14</v>
       </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>313.28</v>
-      </c>
-      <c r="AE3">
-        <v>678.02</v>
-      </c>
-      <c r="AF3">
-        <v>178.9</v>
-      </c>
-      <c r="AG3">
-        <v>1357.11</v>
-      </c>
-      <c r="AH3">
-        <v>1139.48</v>
-      </c>
-      <c r="AI3">
-        <v>589.85</v>
-      </c>
-      <c r="AJ3">
-        <v>159.98</v>
-      </c>
-      <c r="AK3">
-        <v>33.82</v>
-      </c>
-      <c r="AL3">
-        <v>1</v>
-      </c>
-      <c r="AM3">
-        <v>0.66</v>
-      </c>
-      <c r="AN3">
-        <v>193.8</v>
-      </c>
-      <c r="AO3">
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>410</v>
+      </c>
+      <c r="AG6">
+        <v>775.21</v>
+      </c>
+      <c r="AH6">
+        <v>207.13</v>
+      </c>
+      <c r="AI6">
+        <v>2102.6</v>
+      </c>
+      <c r="AJ6">
+        <v>1485.91</v>
+      </c>
+      <c r="AK6">
+        <v>427.39</v>
+      </c>
+      <c r="AL6">
+        <v>232.05</v>
+      </c>
+      <c r="AM6">
+        <v>96.45</v>
+      </c>
+      <c r="AN6">
+        <v>5</v>
+      </c>
+      <c r="AO6">
+        <v>1.58</v>
+      </c>
+      <c r="AP6">
+        <v>328.5</v>
+      </c>
+      <c r="AQ6">
+        <v>11</v>
+      </c>
+      <c r="AR6">
+        <v>5.39</v>
+      </c>
+      <c r="AS6">
+        <v>27</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:50">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>4.05</v>
+      </c>
+      <c r="G7">
+        <v>-4.43</v>
+      </c>
+      <c r="H7">
         <v>10</v>
       </c>
-      <c r="AP3">
-        <v>3.8</v>
-      </c>
-      <c r="AQ3">
-        <v>18</v>
-      </c>
-      <c r="AS3" t="s">
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>0.39</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0.0354166666666667</v>
+      </c>
+      <c r="M7">
+        <v>3362.69</v>
+      </c>
+      <c r="N7">
+        <v>375.3</v>
+      </c>
+      <c r="O7">
+        <v>24.948</v>
+      </c>
+      <c r="P7">
+        <v>69.34</v>
+      </c>
+      <c r="Q7">
+        <v>65.94</v>
+      </c>
+      <c r="R7">
+        <v>7.36</v>
+      </c>
+      <c r="S7">
+        <v>0.11</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>301.83</v>
+      </c>
+      <c r="AG7">
+        <v>424.84</v>
+      </c>
+      <c r="AH7">
+        <v>220.32</v>
+      </c>
+      <c r="AI7">
+        <v>1366.31</v>
+      </c>
+      <c r="AJ7">
+        <v>1389.47</v>
+      </c>
+      <c r="AK7">
+        <v>302.55</v>
+      </c>
+      <c r="AL7">
+        <v>84.03</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>84.03</v>
+      </c>
+      <c r="AQ7">
+        <v>7</v>
+      </c>
+      <c r="AR7">
+        <v>1.65</v>
+      </c>
+      <c r="AS7">
+        <v>28</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:50">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
         <v>51</v>
       </c>
-      <c r="AT3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AU3" t="s">
+      <c r="C8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" t="s">
         <v>53</v>
       </c>
-      <c r="AV3" t="s">
-        <v>54</v>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>4.2</v>
+      </c>
+      <c r="G8">
+        <v>-5.44</v>
+      </c>
+      <c r="H8">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <v>11</v>
+      </c>
+      <c r="J8">
+        <v>23</v>
+      </c>
+      <c r="K8">
+        <v>0.45</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0.0354166666666667</v>
+      </c>
+      <c r="M8">
+        <v>3334.25</v>
+      </c>
+      <c r="N8">
+        <v>326.45</v>
+      </c>
+      <c r="O8">
+        <v>26.208</v>
+      </c>
+      <c r="P8">
+        <v>72.79</v>
+      </c>
+      <c r="Q8">
+        <v>65.38</v>
+      </c>
+      <c r="R8">
+        <v>6.4</v>
+      </c>
+      <c r="S8">
+        <v>0.13</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>301.02</v>
+      </c>
+      <c r="AG8">
+        <v>512.47</v>
+      </c>
+      <c r="AH8">
+        <v>153.32</v>
+      </c>
+      <c r="AI8">
+        <v>1280.12</v>
+      </c>
+      <c r="AJ8">
+        <v>1325.41</v>
+      </c>
+      <c r="AK8">
+        <v>495.54</v>
+      </c>
+      <c r="AL8">
+        <v>73.72</v>
+      </c>
+      <c r="AM8">
+        <v>6.15</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0.12</v>
+      </c>
+      <c r="AP8">
+        <v>79.87</v>
+      </c>
+      <c r="AQ8">
+        <v>6</v>
+      </c>
+      <c r="AR8">
+        <v>1.57</v>
+      </c>
+      <c r="AS8">
+        <v>4</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:48">
-      <c r="A4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>3.97</v>
-      </c>
-      <c r="E4">
-        <v>-5.5</v>
-      </c>
-      <c r="F4">
+    <row r="9" spans="1:50">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>3.67</v>
+      </c>
+      <c r="G9">
+        <v>-4.29</v>
+      </c>
+      <c r="H9">
         <v>13</v>
       </c>
-      <c r="G4">
-        <v>17</v>
-      </c>
-      <c r="H4">
-        <v>30</v>
-      </c>
-      <c r="I4">
-        <v>0.59</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0.0354166666666667</v>
-      </c>
-      <c r="K4">
-        <v>3970.96</v>
-      </c>
-      <c r="L4">
-        <v>379.89</v>
-      </c>
-      <c r="M4">
-        <v>25.776</v>
-      </c>
-      <c r="N4">
-        <v>71.62</v>
-      </c>
-      <c r="O4">
-        <v>77.86</v>
-      </c>
-      <c r="P4">
-        <v>7.45</v>
-      </c>
-      <c r="Q4">
-        <v>0.14</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>358.24</v>
-      </c>
-      <c r="AE4">
-        <v>603.39</v>
-      </c>
-      <c r="AF4">
-        <v>168.51</v>
-      </c>
-      <c r="AG4">
-        <v>1751.28</v>
-      </c>
-      <c r="AH4">
-        <v>1368.42</v>
-      </c>
-      <c r="AI4">
-        <v>555.1</v>
-      </c>
-      <c r="AJ4">
-        <v>118.81</v>
-      </c>
-      <c r="AK4">
-        <v>8.73</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0.17</v>
-      </c>
-      <c r="AN4">
-        <v>127.54</v>
-      </c>
-      <c r="AO4">
-        <v>10</v>
-      </c>
-      <c r="AP4">
-        <v>2.5</v>
-      </c>
-      <c r="AQ4">
-        <v>20</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:48">
-      <c r="A5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>5.26</v>
-      </c>
-      <c r="E5">
-        <v>-3.8</v>
-      </c>
-      <c r="F5">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>7</v>
-      </c>
-      <c r="H5">
-        <v>18</v>
-      </c>
-      <c r="I5">
-        <v>0.35</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0.0354166666666667</v>
-      </c>
-      <c r="K5">
-        <v>3023.36</v>
-      </c>
-      <c r="L5">
-        <v>419.49</v>
-      </c>
-      <c r="M5">
-        <v>24.624</v>
-      </c>
-      <c r="N5">
-        <v>68.37</v>
-      </c>
-      <c r="O5">
-        <v>59.28</v>
-      </c>
-      <c r="P5">
-        <v>8.23</v>
-      </c>
-      <c r="Q5">
-        <v>0.08</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>199.08</v>
-      </c>
-      <c r="AE5">
-        <v>269.02</v>
-      </c>
-      <c r="AF5">
-        <v>482.02</v>
-      </c>
-      <c r="AG5">
-        <v>1415.79</v>
-      </c>
-      <c r="AH5">
-        <v>881.71</v>
-      </c>
-      <c r="AI5">
-        <v>194.37</v>
-      </c>
-      <c r="AJ5">
-        <v>49.11</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>49.11</v>
-      </c>
-      <c r="AO5">
-        <v>3</v>
-      </c>
-      <c r="AP5">
-        <v>0.96</v>
-      </c>
-      <c r="AQ5">
+      <c r="I9">
+        <v>21</v>
+      </c>
+      <c r="J9">
         <v>34</v>
       </c>
-      <c r="AS5" t="s">
-        <v>51</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:48">
-      <c r="A6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>4.39</v>
-      </c>
-      <c r="E6">
-        <v>-4.82</v>
-      </c>
-      <c r="F6">
-        <v>19</v>
-      </c>
-      <c r="G6">
-        <v>18</v>
-      </c>
-      <c r="H6">
-        <v>37</v>
-      </c>
-      <c r="I6">
-        <v>0.61</v>
-      </c>
-      <c r="J6" s="1">
+      <c r="K9">
+        <v>0.56</v>
+      </c>
+      <c r="L9" s="1">
         <v>0.0423611111111111</v>
       </c>
-      <c r="K6">
-        <v>4551.53</v>
-      </c>
-      <c r="L6">
-        <v>506.55</v>
-      </c>
-      <c r="M6">
-        <v>29.232</v>
-      </c>
-      <c r="N6">
-        <v>74.29</v>
-      </c>
-      <c r="O6">
-        <v>78.45</v>
-      </c>
-      <c r="P6">
-        <v>8.3</v>
-      </c>
-      <c r="Q6">
-        <v>0.14</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>410</v>
-      </c>
-      <c r="AE6">
-        <v>775.21</v>
-      </c>
-      <c r="AF6">
-        <v>207.13</v>
-      </c>
-      <c r="AG6">
-        <v>2102.6</v>
-      </c>
-      <c r="AH6">
-        <v>1485.91</v>
-      </c>
-      <c r="AI6">
-        <v>427.39</v>
-      </c>
-      <c r="AJ6">
-        <v>232.05</v>
-      </c>
-      <c r="AK6">
-        <v>96.45</v>
-      </c>
-      <c r="AL6">
-        <v>5</v>
-      </c>
-      <c r="AM6">
-        <v>1.58</v>
-      </c>
-      <c r="AN6">
-        <v>328.5</v>
-      </c>
-      <c r="AO6">
-        <v>11</v>
-      </c>
-      <c r="AP6">
-        <v>5.39</v>
-      </c>
-      <c r="AQ6">
-        <v>27</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>51</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>53</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:48">
-      <c r="A7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>4.05</v>
-      </c>
-      <c r="E7">
-        <v>-4.43</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>20</v>
-      </c>
-      <c r="I7">
-        <v>0.39</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0.0354166666666667</v>
-      </c>
-      <c r="K7">
-        <v>3362.69</v>
-      </c>
-      <c r="L7">
-        <v>375.3</v>
-      </c>
-      <c r="M7">
-        <v>24.948</v>
-      </c>
-      <c r="N7">
-        <v>69.34</v>
-      </c>
-      <c r="O7">
-        <v>65.94</v>
-      </c>
-      <c r="P7">
+      <c r="M9">
+        <v>4582.31</v>
+      </c>
+      <c r="N9">
+        <v>448.85</v>
+      </c>
+      <c r="O9">
+        <v>26.064</v>
+      </c>
+      <c r="P9">
+        <v>72.39</v>
+      </c>
+      <c r="Q9">
+        <v>77.04</v>
+      </c>
+      <c r="R9">
         <v>7.36</v>
       </c>
-      <c r="Q7">
+      <c r="S9">
         <v>0.11</v>
       </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>301.83</v>
-      </c>
-      <c r="AE7">
-        <v>424.84</v>
-      </c>
-      <c r="AF7">
-        <v>220.32</v>
-      </c>
-      <c r="AG7">
-        <v>1366.31</v>
-      </c>
-      <c r="AH7">
-        <v>1389.47</v>
-      </c>
-      <c r="AI7">
-        <v>302.55</v>
-      </c>
-      <c r="AJ7">
-        <v>84.03</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>84.03</v>
-      </c>
-      <c r="AO7">
-        <v>7</v>
-      </c>
-      <c r="AP7">
-        <v>1.65</v>
-      </c>
-      <c r="AQ7">
-        <v>28</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>51</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>52</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>53</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:48">
-      <c r="A8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>4.2</v>
-      </c>
-      <c r="E8">
-        <v>-5.44</v>
-      </c>
-      <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>11</v>
-      </c>
-      <c r="H8">
-        <v>23</v>
-      </c>
-      <c r="I8">
-        <v>0.45</v>
-      </c>
-      <c r="J8" s="1">
-        <v>0.0354166666666667</v>
-      </c>
-      <c r="K8">
-        <v>3334.25</v>
-      </c>
-      <c r="L8">
-        <v>326.45</v>
-      </c>
-      <c r="M8">
-        <v>26.208</v>
-      </c>
-      <c r="N8">
-        <v>72.79</v>
-      </c>
-      <c r="O8">
-        <v>65.38</v>
-      </c>
-      <c r="P8">
-        <v>6.4</v>
-      </c>
-      <c r="Q8">
-        <v>0.13</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>301.02</v>
-      </c>
-      <c r="AE8">
-        <v>512.47</v>
-      </c>
-      <c r="AF8">
-        <v>153.32</v>
-      </c>
-      <c r="AG8">
-        <v>1280.12</v>
-      </c>
-      <c r="AH8">
-        <v>1325.41</v>
-      </c>
-      <c r="AI8">
-        <v>495.54</v>
-      </c>
-      <c r="AJ8">
-        <v>73.72</v>
-      </c>
-      <c r="AK8">
-        <v>6.15</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0.12</v>
-      </c>
-      <c r="AN8">
-        <v>79.87</v>
-      </c>
-      <c r="AO8">
-        <v>6</v>
-      </c>
-      <c r="AP8">
-        <v>1.57</v>
-      </c>
-      <c r="AQ8">
-        <v>4</v>
-      </c>
-      <c r="AS8" t="s">
-        <v>51</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>52</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>53</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:48">
-      <c r="A9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>3.67</v>
-      </c>
-      <c r="E9">
-        <v>-4.29</v>
-      </c>
-      <c r="F9">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>21</v>
-      </c>
-      <c r="H9">
-        <v>34</v>
-      </c>
-      <c r="I9">
-        <v>0.56</v>
-      </c>
-      <c r="J9" s="1">
-        <v>0.0423611111111111</v>
-      </c>
-      <c r="K9">
-        <v>4582.31</v>
-      </c>
-      <c r="L9">
-        <v>448.85</v>
-      </c>
-      <c r="M9">
-        <v>26.064</v>
-      </c>
-      <c r="N9">
-        <v>72.39</v>
-      </c>
-      <c r="O9">
-        <v>77.04</v>
-      </c>
-      <c r="P9">
-        <v>7.36</v>
-      </c>
-      <c r="Q9">
-        <v>0.11</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
       <c r="T9">
         <v>0</v>
       </c>
@@ -2603,10 +2696,10 @@
       <c r="W9">
         <v>0</v>
       </c>
-      <c r="X9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="1">
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
         <v>0</v>
       </c>
       <c r="Z9" s="1">
@@ -2621,119 +2714,125 @@
       <c r="AC9" s="1">
         <v>0</v>
       </c>
-      <c r="AD9">
+      <c r="AD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF9">
         <v>396.89</v>
       </c>
-      <c r="AE9">
+      <c r="AG9">
         <v>575.56</v>
       </c>
-      <c r="AF9">
+      <c r="AH9">
         <v>148.81</v>
       </c>
-      <c r="AG9">
+      <c r="AI9">
         <v>2179.69</v>
       </c>
-      <c r="AH9">
+      <c r="AJ9">
         <v>1644.68</v>
       </c>
-      <c r="AI9">
+      <c r="AK9">
         <v>311.17</v>
       </c>
-      <c r="AJ9">
+      <c r="AL9">
         <v>291.72</v>
       </c>
-      <c r="AK9">
+      <c r="AM9">
         <v>6.25</v>
       </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
         <v>0.1</v>
       </c>
-      <c r="AN9">
+      <c r="AP9">
         <v>297.97</v>
-      </c>
-      <c r="AO9">
-        <v>12</v>
-      </c>
-      <c r="AP9">
-        <v>4.88</v>
       </c>
       <c r="AQ9">
         <v>12</v>
       </c>
-      <c r="AS9" t="s">
-        <v>51</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>52</v>
+      <c r="AR9">
+        <v>4.88</v>
+      </c>
+      <c r="AS9">
+        <v>12</v>
       </c>
       <c r="AU9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:50">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
         <v>53</v>
       </c>
-      <c r="AV9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:48">
-      <c r="A10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>3.94</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>-3.93</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>16</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>8</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>24</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>0.39</v>
       </c>
-      <c r="J10" s="1">
+      <c r="L10" s="1">
         <v>0.0423611111111111</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>4515.92</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>410.63</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>25.992</v>
       </c>
-      <c r="N10">
+      <c r="P10">
         <v>72.18</v>
       </c>
-      <c r="O10">
+      <c r="Q10">
         <v>76.46</v>
       </c>
-      <c r="P10">
+      <c r="R10">
         <v>6.73</v>
       </c>
-      <c r="Q10">
+      <c r="S10">
         <v>0.13</v>
       </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
       <c r="T10">
         <v>0</v>
       </c>
@@ -2746,10 +2845,10 @@
       <c r="W10">
         <v>0</v>
       </c>
-      <c r="X10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="1">
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
         <v>0</v>
       </c>
       <c r="Z10" s="1">
@@ -2764,488 +2863,2312 @@
       <c r="AC10" s="1">
         <v>0</v>
       </c>
-      <c r="AD10">
+      <c r="AD10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF10">
         <v>396.12</v>
       </c>
-      <c r="AE10">
+      <c r="AG10">
         <v>660.57</v>
       </c>
-      <c r="AF10">
+      <c r="AH10">
         <v>139.89</v>
       </c>
-      <c r="AG10">
+      <c r="AI10">
         <v>1990.28</v>
       </c>
-      <c r="AH10">
+      <c r="AJ10">
         <v>1701.44</v>
       </c>
-      <c r="AI10">
+      <c r="AK10">
         <v>391.75</v>
       </c>
-      <c r="AJ10">
+      <c r="AL10">
         <v>275.63</v>
       </c>
-      <c r="AK10">
+      <c r="AM10">
         <v>16.94</v>
       </c>
-      <c r="AL10">
+      <c r="AN10">
         <v>1</v>
       </c>
-      <c r="AM10">
+      <c r="AO10">
         <v>0.28</v>
       </c>
-      <c r="AN10">
+      <c r="AP10">
         <v>292.57</v>
-      </c>
-      <c r="AO10">
-        <v>13</v>
-      </c>
-      <c r="AP10">
-        <v>4.8</v>
       </c>
       <c r="AQ10">
         <v>13</v>
       </c>
-      <c r="AS10" t="s">
+      <c r="AR10">
+        <v>4.8</v>
+      </c>
+      <c r="AS10">
+        <v>13</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:50">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
         <v>51</v>
       </c>
-      <c r="AT10" t="s">
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>3.94</v>
+      </c>
+      <c r="G11">
+        <v>-5.32</v>
+      </c>
+      <c r="H11">
+        <v>8</v>
+      </c>
+      <c r="I11">
+        <v>16</v>
+      </c>
+      <c r="J11">
+        <v>24</v>
+      </c>
+      <c r="K11">
+        <v>0.47</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0.0354166666666667</v>
+      </c>
+      <c r="M11">
+        <v>3343.01</v>
+      </c>
+      <c r="N11">
+        <v>374.49</v>
+      </c>
+      <c r="O11">
+        <v>25.884</v>
+      </c>
+      <c r="P11">
+        <v>71.92</v>
+      </c>
+      <c r="Q11">
+        <v>65.55</v>
+      </c>
+      <c r="R11">
+        <v>7.34</v>
+      </c>
+      <c r="S11">
+        <v>0.11</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>299.87</v>
+      </c>
+      <c r="AG11">
+        <v>503.09</v>
+      </c>
+      <c r="AH11">
+        <v>149.4</v>
+      </c>
+      <c r="AI11">
+        <v>1475.79</v>
+      </c>
+      <c r="AJ11">
+        <v>1111.62</v>
+      </c>
+      <c r="AK11">
+        <v>511.08</v>
+      </c>
+      <c r="AL11">
+        <v>82.25</v>
+      </c>
+      <c r="AM11">
+        <v>12.85</v>
+      </c>
+      <c r="AN11">
+        <v>1</v>
+      </c>
+      <c r="AO11">
+        <v>0.25</v>
+      </c>
+      <c r="AP11">
+        <v>95.1</v>
+      </c>
+      <c r="AQ11">
+        <v>5</v>
+      </c>
+      <c r="AR11">
+        <v>1.86</v>
+      </c>
+      <c r="AS11">
+        <v>41</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:50">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>3.71</v>
+      </c>
+      <c r="G12">
+        <v>-3.84</v>
+      </c>
+      <c r="H12">
+        <v>11</v>
+      </c>
+      <c r="I12">
+        <v>9</v>
+      </c>
+      <c r="J12">
+        <v>20</v>
+      </c>
+      <c r="K12">
+        <v>0.33</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0.0423611111111111</v>
+      </c>
+      <c r="M12">
+        <v>4644.3</v>
+      </c>
+      <c r="N12">
+        <v>517.66</v>
+      </c>
+      <c r="O12">
+        <v>27.072</v>
+      </c>
+      <c r="P12">
+        <v>75.17</v>
+      </c>
+      <c r="Q12">
+        <v>79.4</v>
+      </c>
+      <c r="R12">
+        <v>8.49</v>
+      </c>
+      <c r="S12">
+        <v>0.13</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>402.66</v>
+      </c>
+      <c r="AG12">
+        <v>575.12</v>
+      </c>
+      <c r="AH12">
+        <v>153.26</v>
+      </c>
+      <c r="AI12">
+        <v>1969.17</v>
+      </c>
+      <c r="AJ12">
+        <v>1893.87</v>
+      </c>
+      <c r="AK12">
+        <v>341.67</v>
+      </c>
+      <c r="AL12">
+        <v>257.22</v>
+      </c>
+      <c r="AM12">
+        <v>29.11</v>
+      </c>
+      <c r="AN12">
+        <v>2</v>
+      </c>
+      <c r="AO12">
+        <v>0.48</v>
+      </c>
+      <c r="AP12">
+        <v>286.33</v>
+      </c>
+      <c r="AQ12">
+        <v>8</v>
+      </c>
+      <c r="AR12">
+        <v>4.69</v>
+      </c>
+      <c r="AS12">
+        <v>40</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:50">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>3.36</v>
+      </c>
+      <c r="G13">
+        <v>-3.4</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="K13">
+        <v>0.06</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0.0354166666666667</v>
+      </c>
+      <c r="M13">
+        <v>1355.86</v>
+      </c>
+      <c r="N13">
+        <v>150.27</v>
+      </c>
+      <c r="O13">
+        <v>19.08</v>
+      </c>
+      <c r="P13">
+        <v>52.97</v>
+      </c>
+      <c r="Q13">
+        <v>26.59</v>
+      </c>
+      <c r="R13">
+        <v>2.95</v>
+      </c>
+      <c r="S13">
+        <v>0.01</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>110.42</v>
+      </c>
+      <c r="AG13">
+        <v>45.27</v>
+      </c>
+      <c r="AH13">
+        <v>153.14</v>
+      </c>
+      <c r="AI13">
+        <v>790.81</v>
+      </c>
+      <c r="AJ13">
+        <v>392</v>
+      </c>
+      <c r="AK13">
+        <v>19.96</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>8</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:50">
+      <c r="A14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>3.95</v>
+      </c>
+      <c r="G14" s="2">
+        <v>-4.68</v>
+      </c>
+      <c r="H14" s="2">
+        <v>23</v>
+      </c>
+      <c r="I14" s="2">
+        <v>30</v>
+      </c>
+      <c r="J14" s="2">
+        <v>53</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0.79</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0.0465277777777778</v>
+      </c>
+      <c r="M14" s="2">
+        <v>4404.9</v>
+      </c>
+      <c r="N14" s="2">
+        <v>485.73</v>
+      </c>
+      <c r="O14" s="2">
+        <v>25.596</v>
+      </c>
+      <c r="P14" s="2">
+        <v>71.06</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>65.74</v>
+      </c>
+      <c r="R14" s="2">
+        <v>7.25</v>
+      </c>
+      <c r="S14" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="T14" s="2">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2">
+        <v>0</v>
+      </c>
+      <c r="W14" s="2">
+        <v>0</v>
+      </c>
+      <c r="X14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="2">
+        <v>389.51</v>
+      </c>
+      <c r="AG14" s="2">
+        <v>836.62</v>
+      </c>
+      <c r="AH14" s="2">
+        <v>309.28</v>
+      </c>
+      <c r="AI14" s="2">
+        <v>2071.84</v>
+      </c>
+      <c r="AJ14" s="2">
+        <v>1046.6</v>
+      </c>
+      <c r="AK14" s="2">
+        <v>464.25</v>
+      </c>
+      <c r="AL14" s="2">
+        <v>487.81</v>
+      </c>
+      <c r="AM14" s="2">
+        <v>25.13</v>
+      </c>
+      <c r="AN14" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO14" s="2">
+        <v>0.38</v>
+      </c>
+      <c r="AP14" s="2">
+        <v>512.94</v>
+      </c>
+      <c r="AQ14" s="2">
+        <v>15</v>
+      </c>
+      <c r="AR14" s="2">
+        <v>7.66</v>
+      </c>
+      <c r="AS14" s="2">
+        <v>43</v>
+      </c>
+      <c r="AT14" s="2"/>
+      <c r="AU14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX14" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:50">
+      <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AU10" t="s">
+      <c r="D15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AV10" t="s">
-        <v>54</v>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>3.45</v>
+      </c>
+      <c r="G15" s="2">
+        <v>-3.47</v>
+      </c>
+      <c r="H15" s="2">
+        <v>8</v>
+      </c>
+      <c r="I15" s="2">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2">
+        <v>16</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0.26</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0.0430555555555556</v>
+      </c>
+      <c r="M15" s="2">
+        <v>4156.59</v>
+      </c>
+      <c r="N15" s="2">
+        <v>403.86</v>
+      </c>
+      <c r="O15" s="2">
+        <v>22.86</v>
+      </c>
+      <c r="P15" s="2">
+        <v>63.5</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>67.04</v>
+      </c>
+      <c r="R15" s="2">
+        <v>6.51</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2">
+        <v>0</v>
+      </c>
+      <c r="W15" s="2">
+        <v>0</v>
+      </c>
+      <c r="X15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="2">
+        <v>356.35</v>
+      </c>
+      <c r="AG15" s="2">
+        <v>422.78</v>
+      </c>
+      <c r="AH15" s="2">
+        <v>135.7</v>
+      </c>
+      <c r="AI15" s="2">
+        <v>1999.09</v>
+      </c>
+      <c r="AJ15" s="2">
+        <v>1497.73</v>
+      </c>
+      <c r="AK15" s="2">
+        <v>450.01</v>
+      </c>
+      <c r="AL15" s="2">
+        <v>73.16</v>
+      </c>
+      <c r="AM15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="2">
+        <v>73.16</v>
+      </c>
+      <c r="AQ15" s="2">
+        <v>6</v>
+      </c>
+      <c r="AR15" s="2">
+        <v>1.18</v>
+      </c>
+      <c r="AS15" s="2">
+        <v>23</v>
+      </c>
+      <c r="AT15" s="2"/>
+      <c r="AU15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX15" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:48">
-      <c r="A11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>3.94</v>
-      </c>
-      <c r="E11">
-        <v>-5.32</v>
-      </c>
-      <c r="F11">
-        <v>8</v>
-      </c>
-      <c r="G11">
+    <row r="16" spans="1:50">
+      <c r="A16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>4.23</v>
+      </c>
+      <c r="G16" s="2">
+        <v>-5.25</v>
+      </c>
+      <c r="H16" s="2">
+        <v>17</v>
+      </c>
+      <c r="I16" s="2">
+        <v>22</v>
+      </c>
+      <c r="J16" s="2">
+        <v>39</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0.63</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0.0430555555555556</v>
+      </c>
+      <c r="M16" s="2">
+        <v>5269.45</v>
+      </c>
+      <c r="N16" s="2">
+        <v>487.75</v>
+      </c>
+      <c r="O16" s="2">
+        <v>28.152</v>
+      </c>
+      <c r="P16" s="2">
+        <v>78.22</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>84.99</v>
+      </c>
+      <c r="R16" s="2">
+        <v>7.87</v>
+      </c>
+      <c r="S16" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="T16" s="2">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2">
+        <v>0</v>
+      </c>
+      <c r="W16" s="2">
+        <v>0</v>
+      </c>
+      <c r="X16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="2">
+        <v>475.74</v>
+      </c>
+      <c r="AG16" s="2">
+        <v>825.92</v>
+      </c>
+      <c r="AH16" s="2">
+        <v>198.9</v>
+      </c>
+      <c r="AI16" s="2">
+        <v>2176.82</v>
+      </c>
+      <c r="AJ16" s="2">
+        <v>1932.72</v>
+      </c>
+      <c r="AK16" s="2">
+        <v>632.68</v>
+      </c>
+      <c r="AL16" s="2">
+        <v>242.48</v>
+      </c>
+      <c r="AM16" s="2">
+        <v>85.92</v>
+      </c>
+      <c r="AN16" s="2">
+        <v>7</v>
+      </c>
+      <c r="AO16" s="2">
+        <v>1.39</v>
+      </c>
+      <c r="AP16" s="2">
+        <v>328.4</v>
+      </c>
+      <c r="AQ16" s="2">
         <v>16</v>
       </c>
-      <c r="H11">
+      <c r="AR16" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="AS16" s="2">
+        <v>23</v>
+      </c>
+      <c r="AT16" s="2"/>
+      <c r="AU16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX16" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:50">
+      <c r="A17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>4.07</v>
+      </c>
+      <c r="G17" s="2">
+        <v>-4.55</v>
+      </c>
+      <c r="H17" s="2">
+        <v>9</v>
+      </c>
+      <c r="I17" s="2">
+        <v>15</v>
+      </c>
+      <c r="J17" s="2">
         <v>24</v>
       </c>
-      <c r="I11">
-        <v>0.47</v>
-      </c>
-      <c r="J11" s="1">
-        <v>0.0354166666666667</v>
-      </c>
-      <c r="K11">
-        <v>3343.01</v>
-      </c>
-      <c r="L11">
-        <v>374.49</v>
-      </c>
-      <c r="M11">
-        <v>25.884</v>
-      </c>
-      <c r="N11">
-        <v>71.92</v>
-      </c>
-      <c r="O11">
-        <v>65.55</v>
-      </c>
-      <c r="P11">
-        <v>7.34</v>
-      </c>
-      <c r="Q11">
+      <c r="K17" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0.0430555555555556</v>
+      </c>
+      <c r="M17" s="2">
+        <v>4701.89</v>
+      </c>
+      <c r="N17" s="2">
+        <v>413.73</v>
+      </c>
+      <c r="O17" s="2">
+        <v>26.496</v>
+      </c>
+      <c r="P17" s="2">
+        <v>73.64</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>75.84</v>
+      </c>
+      <c r="R17" s="2">
+        <v>6.67</v>
+      </c>
+      <c r="S17" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="T17" s="2">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2">
+        <v>0</v>
+      </c>
+      <c r="W17" s="2">
+        <v>0</v>
+      </c>
+      <c r="X17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="2">
+        <v>412.96</v>
+      </c>
+      <c r="AG17" s="2">
+        <v>566.48</v>
+      </c>
+      <c r="AH17" s="2">
+        <v>143.22</v>
+      </c>
+      <c r="AI17" s="2">
+        <v>2088.17</v>
+      </c>
+      <c r="AJ17" s="2">
+        <v>1763.38</v>
+      </c>
+      <c r="AK17" s="2">
+        <v>530.09</v>
+      </c>
+      <c r="AL17" s="2">
+        <v>165.83</v>
+      </c>
+      <c r="AM17" s="2">
+        <v>11.2</v>
+      </c>
+      <c r="AN17" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO17" s="2">
+        <v>0.18</v>
+      </c>
+      <c r="AP17" s="2">
+        <v>177.03</v>
+      </c>
+      <c r="AQ17" s="2">
+        <v>13</v>
+      </c>
+      <c r="AR17" s="2">
+        <v>2.86</v>
+      </c>
+      <c r="AS17" s="2">
+        <v>16</v>
+      </c>
+      <c r="AT17" s="2"/>
+      <c r="AU17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX17" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:50">
+      <c r="A18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>4.59</v>
+      </c>
+      <c r="G18" s="2">
+        <v>-6.73</v>
+      </c>
+      <c r="H18" s="2">
+        <v>22</v>
+      </c>
+      <c r="I18" s="2">
+        <v>36</v>
+      </c>
+      <c r="J18" s="2">
+        <v>58</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0.0430555555555556</v>
+      </c>
+      <c r="M18" s="2">
+        <v>5467.16</v>
+      </c>
+      <c r="N18" s="2">
+        <v>561.31</v>
+      </c>
+      <c r="O18" s="2">
+        <v>29.268</v>
+      </c>
+      <c r="P18" s="2">
+        <v>81.26</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>88.18</v>
+      </c>
+      <c r="R18" s="2">
+        <v>9.05</v>
+      </c>
+      <c r="S18" s="2">
+        <v>0.17</v>
+      </c>
+      <c r="T18" s="2">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2">
+        <v>0</v>
+      </c>
+      <c r="W18" s="2">
+        <v>0</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="2">
+        <v>501.79</v>
+      </c>
+      <c r="AG18" s="2">
+        <v>839.44</v>
+      </c>
+      <c r="AH18" s="2">
+        <v>143.08</v>
+      </c>
+      <c r="AI18" s="2">
+        <v>2233.85</v>
+      </c>
+      <c r="AJ18" s="2">
+        <v>2118.68</v>
+      </c>
+      <c r="AK18" s="2">
+        <v>528.88</v>
+      </c>
+      <c r="AL18" s="2">
+        <v>324.38</v>
+      </c>
+      <c r="AM18" s="2">
+        <v>117.5</v>
+      </c>
+      <c r="AN18" s="2">
+        <v>9</v>
+      </c>
+      <c r="AO18" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="AP18" s="2">
+        <v>441.88</v>
+      </c>
+      <c r="AQ18" s="2">
+        <v>23</v>
+      </c>
+      <c r="AR18" s="2">
+        <v>7.13</v>
+      </c>
+      <c r="AS18" s="2">
+        <v>51</v>
+      </c>
+      <c r="AT18" s="2"/>
+      <c r="AU18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX18" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:50">
+      <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>3.99</v>
+      </c>
+      <c r="G19" s="2">
+        <v>-4.37</v>
+      </c>
+      <c r="H19" s="2">
+        <v>26</v>
+      </c>
+      <c r="I19" s="2">
+        <v>24</v>
+      </c>
+      <c r="J19" s="2">
+        <v>50</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0.0465277777777778</v>
+      </c>
+      <c r="M19" s="2">
+        <v>4038.89</v>
+      </c>
+      <c r="N19" s="2">
+        <v>432.46</v>
+      </c>
+      <c r="O19" s="2">
+        <v>26.892</v>
+      </c>
+      <c r="P19" s="2">
+        <v>74.73</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>60.28</v>
+      </c>
+      <c r="R19" s="2">
+        <v>6.45</v>
+      </c>
+      <c r="S19" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="T19" s="2">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2">
+        <v>0</v>
+      </c>
+      <c r="W19" s="2">
+        <v>0</v>
+      </c>
+      <c r="X19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="2">
+        <v>360.73</v>
+      </c>
+      <c r="AG19" s="2">
+        <v>828.25</v>
+      </c>
+      <c r="AH19" s="2">
+        <v>293.36</v>
+      </c>
+      <c r="AI19" s="2">
+        <v>1618.19</v>
+      </c>
+      <c r="AJ19" s="2">
+        <v>1129.74</v>
+      </c>
+      <c r="AK19" s="2">
+        <v>348.35</v>
+      </c>
+      <c r="AL19" s="2">
+        <v>556.1</v>
+      </c>
+      <c r="AM19" s="2">
+        <v>93.15</v>
+      </c>
+      <c r="AN19" s="2">
+        <v>5</v>
+      </c>
+      <c r="AO19" s="2">
+        <v>1.39</v>
+      </c>
+      <c r="AP19" s="2">
+        <v>649.25</v>
+      </c>
+      <c r="AQ19" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR19" s="2">
+        <v>9.69</v>
+      </c>
+      <c r="AS19" s="2">
+        <v>18</v>
+      </c>
+      <c r="AT19" s="2"/>
+      <c r="AU19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX19" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:50">
+      <c r="A20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>3.73</v>
+      </c>
+      <c r="G20" s="2">
+        <v>-4.58</v>
+      </c>
+      <c r="H20" s="2">
+        <v>11</v>
+      </c>
+      <c r="I20" s="2">
+        <v>16</v>
+      </c>
+      <c r="J20" s="2">
+        <v>27</v>
+      </c>
+      <c r="K20" s="2">
+        <v>0.44</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0.0430555555555556</v>
+      </c>
+      <c r="M20" s="2">
+        <v>4484.49</v>
+      </c>
+      <c r="N20" s="2">
+        <v>449.28</v>
+      </c>
+      <c r="O20" s="2">
+        <v>27.936</v>
+      </c>
+      <c r="P20" s="2">
+        <v>77.63</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>72.33</v>
+      </c>
+      <c r="R20" s="2">
+        <v>7.25</v>
+      </c>
+      <c r="S20" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="T20" s="2">
+        <v>123</v>
+      </c>
+      <c r="U20" s="2">
+        <v>90.22</v>
+      </c>
+      <c r="V20" s="2">
+        <v>61.5</v>
+      </c>
+      <c r="W20" s="2">
+        <v>45.11</v>
+      </c>
+      <c r="X20" s="2">
+        <v>53.92</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0.0312962962962963</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0.00511574074074074</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="2">
+        <v>389.95</v>
+      </c>
+      <c r="AG20" s="2">
+        <v>423.8</v>
+      </c>
+      <c r="AH20" s="2">
+        <v>143.32</v>
+      </c>
+      <c r="AI20" s="2">
+        <v>2385.91</v>
+      </c>
+      <c r="AJ20" s="2">
+        <v>1502.18</v>
+      </c>
+      <c r="AK20" s="2">
+        <v>269.01</v>
+      </c>
+      <c r="AL20" s="2">
+        <v>147.38</v>
+      </c>
+      <c r="AM20" s="2">
+        <v>36.69</v>
+      </c>
+      <c r="AN20" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO20" s="2">
+        <v>0.59</v>
+      </c>
+      <c r="AP20" s="2">
+        <v>184.07</v>
+      </c>
+      <c r="AQ20" s="2">
+        <v>12</v>
+      </c>
+      <c r="AR20" s="2">
+        <v>2.97</v>
+      </c>
+      <c r="AS20" s="2">
+        <v>76</v>
+      </c>
+      <c r="AT20" s="2"/>
+      <c r="AU20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX20" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:50">
+      <c r="A21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>3.98</v>
+      </c>
+      <c r="G21" s="2">
+        <v>-4.23</v>
+      </c>
+      <c r="H21" s="2">
+        <v>13</v>
+      </c>
+      <c r="I21" s="2">
+        <v>15</v>
+      </c>
+      <c r="J21" s="2">
+        <v>28</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0.0430555555555556</v>
+      </c>
+      <c r="M21" s="2">
+        <v>3364.05</v>
+      </c>
+      <c r="N21" s="2">
+        <v>293.72</v>
+      </c>
+      <c r="O21" s="2">
+        <v>28.296</v>
+      </c>
+      <c r="P21" s="2">
+        <v>78.58</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>54.26</v>
+      </c>
+      <c r="R21" s="2">
+        <v>4.74</v>
+      </c>
+      <c r="S21" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="T21" s="2">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2">
+        <v>0</v>
+      </c>
+      <c r="W21" s="2">
+        <v>0</v>
+      </c>
+      <c r="X21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="2">
+        <v>790.96</v>
+      </c>
+      <c r="AG21" s="2">
+        <v>474.79</v>
+      </c>
+      <c r="AH21" s="2">
+        <v>147.7</v>
+      </c>
+      <c r="AI21" s="2">
+        <v>1996.44</v>
+      </c>
+      <c r="AJ21" s="2">
+        <v>714.33</v>
+      </c>
+      <c r="AK21" s="2">
+        <v>333.13</v>
+      </c>
+      <c r="AL21" s="2">
+        <v>131.65</v>
+      </c>
+      <c r="AM21" s="2">
+        <v>40.8</v>
+      </c>
+      <c r="AN21" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO21" s="2">
+        <v>0.66</v>
+      </c>
+      <c r="AP21" s="2">
+        <v>172.45</v>
+      </c>
+      <c r="AQ21" s="2">
+        <v>9</v>
+      </c>
+      <c r="AR21" s="2">
+        <v>2.78</v>
+      </c>
+      <c r="AS21" s="2">
+        <v>18</v>
+      </c>
+      <c r="AT21" s="2"/>
+      <c r="AU21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX21" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:50">
+      <c r="A22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
+        <v>3.84</v>
+      </c>
+      <c r="G22" s="2">
+        <v>-4.91</v>
+      </c>
+      <c r="H22" s="2">
+        <v>19</v>
+      </c>
+      <c r="I22" s="2">
+        <v>21</v>
+      </c>
+      <c r="J22" s="2">
+        <v>40</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0.0430555555555556</v>
+      </c>
+      <c r="M22" s="2">
+        <v>4785.38</v>
+      </c>
+      <c r="N22" s="2">
+        <v>447.53</v>
+      </c>
+      <c r="O22" s="2">
+        <v>28.584</v>
+      </c>
+      <c r="P22" s="2">
+        <v>79.38</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>77.18</v>
+      </c>
+      <c r="R22" s="2">
+        <v>7.22</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="T22" s="2">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2">
+        <v>0</v>
+      </c>
+      <c r="W22" s="2">
+        <v>0</v>
+      </c>
+      <c r="X22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="2">
+        <v>428.23</v>
+      </c>
+      <c r="AG22" s="2">
+        <v>697.51</v>
+      </c>
+      <c r="AH22" s="2">
+        <v>173.43</v>
+      </c>
+      <c r="AI22" s="2">
+        <v>2150.71</v>
+      </c>
+      <c r="AJ22" s="2">
+        <v>1666.1</v>
+      </c>
+      <c r="AK22" s="2">
+        <v>564.89</v>
+      </c>
+      <c r="AL22" s="2">
+        <v>190.43</v>
+      </c>
+      <c r="AM22" s="2">
+        <v>39.88</v>
+      </c>
+      <c r="AN22" s="2">
+        <v>3</v>
+      </c>
+      <c r="AO22" s="2">
+        <v>0.64</v>
+      </c>
+      <c r="AP22" s="2">
+        <v>230.31</v>
+      </c>
+      <c r="AQ22" s="2">
+        <v>14</v>
+      </c>
+      <c r="AR22" s="2">
+        <v>3.71</v>
+      </c>
+      <c r="AS22" s="2">
+        <v>21</v>
+      </c>
+      <c r="AT22" s="2"/>
+      <c r="AU22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX22" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:50">
+      <c r="A23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2">
+        <v>3.81</v>
+      </c>
+      <c r="G23" s="2">
+        <v>-5.06</v>
+      </c>
+      <c r="H23" s="2">
+        <v>25</v>
+      </c>
+      <c r="I23" s="2">
+        <v>27</v>
+      </c>
+      <c r="J23" s="2">
+        <v>52</v>
+      </c>
+      <c r="K23" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0.0465277777777778</v>
+      </c>
+      <c r="M23" s="2">
+        <v>3809.03</v>
+      </c>
+      <c r="N23" s="2">
+        <v>462.87</v>
+      </c>
+      <c r="O23" s="2">
+        <v>27.9</v>
+      </c>
+      <c r="P23" s="2">
+        <v>77.54</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>56.85</v>
+      </c>
+      <c r="R23" s="2">
+        <v>6.91</v>
+      </c>
+      <c r="S23" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="T23" s="2">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2">
+        <v>0</v>
+      </c>
+      <c r="W23" s="2">
+        <v>0</v>
+      </c>
+      <c r="X23" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="2">
+        <v>344.21</v>
+      </c>
+      <c r="AG23" s="2">
+        <v>767.99</v>
+      </c>
+      <c r="AH23" s="2">
+        <v>279.64</v>
+      </c>
+      <c r="AI23" s="2">
+        <v>1759.83</v>
+      </c>
+      <c r="AJ23" s="2">
+        <v>995.82</v>
+      </c>
+      <c r="AK23" s="2">
+        <v>267.62</v>
+      </c>
+      <c r="AL23" s="2">
+        <v>333.53</v>
+      </c>
+      <c r="AM23" s="2">
+        <v>172.6</v>
+      </c>
+      <c r="AN23" s="2">
+        <v>9</v>
+      </c>
+      <c r="AO23" s="2">
+        <v>2.58</v>
+      </c>
+      <c r="AP23" s="2">
+        <v>506.13</v>
+      </c>
+      <c r="AQ23" s="2">
+        <v>12</v>
+      </c>
+      <c r="AR23" s="2">
+        <v>7.55</v>
+      </c>
+      <c r="AS23" s="2">
+        <v>50</v>
+      </c>
+      <c r="AT23" s="2"/>
+      <c r="AU23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX23" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:50">
+      <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2">
+        <v>4.11</v>
+      </c>
+      <c r="G24" s="2">
+        <v>-4.3</v>
+      </c>
+      <c r="H24" s="2">
+        <v>16</v>
+      </c>
+      <c r="I24" s="2">
+        <v>5</v>
+      </c>
+      <c r="J24" s="2">
+        <v>21</v>
+      </c>
+      <c r="K24" s="2">
+        <v>0.34</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0.0430555555555556</v>
+      </c>
+      <c r="M24" s="2">
+        <v>3600.84</v>
+      </c>
+      <c r="N24" s="2">
+        <v>467.31</v>
+      </c>
+      <c r="O24" s="2">
+        <v>26.532</v>
+      </c>
+      <c r="P24" s="2">
+        <v>73.67</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>58.08</v>
+      </c>
+      <c r="R24" s="2">
+        <v>7.54</v>
+      </c>
+      <c r="S24" s="2">
         <v>0.11</v>
       </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>299.87</v>
-      </c>
-      <c r="AE11">
-        <v>503.09</v>
-      </c>
-      <c r="AF11">
-        <v>149.4</v>
-      </c>
-      <c r="AG11">
-        <v>1475.79</v>
-      </c>
-      <c r="AH11">
-        <v>1111.62</v>
-      </c>
-      <c r="AI11">
-        <v>511.08</v>
-      </c>
-      <c r="AJ11">
-        <v>82.25</v>
-      </c>
-      <c r="AK11">
-        <v>12.85</v>
-      </c>
-      <c r="AL11">
+      <c r="T24" s="2">
+        <v>0</v>
+      </c>
+      <c r="U24" s="2">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2">
+        <v>0</v>
+      </c>
+      <c r="W24" s="2">
+        <v>0</v>
+      </c>
+      <c r="X24" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="2">
+        <v>271.34</v>
+      </c>
+      <c r="AG24" s="2">
+        <v>452.39</v>
+      </c>
+      <c r="AH24" s="2">
+        <v>360.31</v>
+      </c>
+      <c r="AI24" s="2">
+        <v>1701.79</v>
+      </c>
+      <c r="AJ24" s="2">
+        <v>1162.78</v>
+      </c>
+      <c r="AK24" s="2">
+        <v>270.55</v>
+      </c>
+      <c r="AL24" s="2">
+        <v>92.11</v>
+      </c>
+      <c r="AM24" s="2">
+        <v>13.41</v>
+      </c>
+      <c r="AN24" s="2">
         <v>1</v>
       </c>
-      <c r="AM11">
-        <v>0.25</v>
-      </c>
-      <c r="AN11">
-        <v>95.1</v>
-      </c>
-      <c r="AO11">
-        <v>5</v>
-      </c>
-      <c r="AP11">
-        <v>1.86</v>
-      </c>
-      <c r="AQ11">
-        <v>41</v>
-      </c>
-      <c r="AS11" t="s">
+      <c r="AO24" s="2">
+        <v>0.22</v>
+      </c>
+      <c r="AP24" s="2">
+        <v>105.52</v>
+      </c>
+      <c r="AQ24" s="2">
+        <v>6</v>
+      </c>
+      <c r="AR24" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="AS24" s="2">
+        <v>25</v>
+      </c>
+      <c r="AT24" s="2"/>
+      <c r="AU24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX24" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:50">
+      <c r="A25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" t="s">
         <v>51</v>
       </c>
-      <c r="AT11" t="s">
-        <v>52</v>
-      </c>
-      <c r="AU11" t="s">
+      <c r="C25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AV11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:48">
-      <c r="A12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>3.71</v>
-      </c>
-      <c r="E12">
-        <v>-3.84</v>
-      </c>
-      <c r="F12">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>9</v>
-      </c>
-      <c r="H12">
-        <v>20</v>
-      </c>
-      <c r="I12">
-        <v>0.33</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0.0423611111111111</v>
-      </c>
-      <c r="K12">
-        <v>4644.3</v>
-      </c>
-      <c r="L12">
-        <v>517.66</v>
-      </c>
-      <c r="M12">
-        <v>27.072</v>
-      </c>
-      <c r="N12">
-        <v>75.17</v>
-      </c>
-      <c r="O12">
-        <v>79.4</v>
-      </c>
-      <c r="P12">
-        <v>8.49</v>
-      </c>
-      <c r="Q12">
-        <v>0.13</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>402.66</v>
-      </c>
-      <c r="AE12">
-        <v>575.12</v>
-      </c>
-      <c r="AF12">
-        <v>153.26</v>
-      </c>
-      <c r="AG12">
-        <v>1969.17</v>
-      </c>
-      <c r="AH12">
-        <v>1893.87</v>
-      </c>
-      <c r="AI12">
-        <v>341.67</v>
-      </c>
-      <c r="AJ12">
-        <v>257.22</v>
-      </c>
-      <c r="AK12">
-        <v>29.11</v>
-      </c>
-      <c r="AL12">
-        <v>2</v>
-      </c>
-      <c r="AM12">
-        <v>0.48</v>
-      </c>
-      <c r="AN12">
-        <v>286.33</v>
-      </c>
-      <c r="AO12">
-        <v>8</v>
-      </c>
-      <c r="AP12">
-        <v>4.69</v>
-      </c>
-      <c r="AQ12">
-        <v>40</v>
-      </c>
-      <c r="AS12" t="s">
-        <v>51</v>
-      </c>
-      <c r="AT12" t="s">
-        <v>52</v>
-      </c>
-      <c r="AU12" t="s">
-        <v>53</v>
-      </c>
-      <c r="AV12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:48">
-      <c r="A13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>3.36</v>
-      </c>
-      <c r="E13">
-        <v>-3.4</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>3</v>
-      </c>
-      <c r="I13">
-        <v>0.06</v>
-      </c>
-      <c r="J13" s="1">
-        <v>0.0354166666666667</v>
-      </c>
-      <c r="K13">
-        <v>1355.86</v>
-      </c>
-      <c r="L13">
-        <v>150.27</v>
-      </c>
-      <c r="M13">
-        <v>19.08</v>
-      </c>
-      <c r="N13">
-        <v>52.97</v>
-      </c>
-      <c r="O13">
-        <v>26.59</v>
-      </c>
-      <c r="P13">
-        <v>2.95</v>
-      </c>
-      <c r="Q13">
-        <v>0.01</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>110.42</v>
-      </c>
-      <c r="AE13">
-        <v>45.27</v>
-      </c>
-      <c r="AF13">
-        <v>153.14</v>
-      </c>
-      <c r="AG13">
-        <v>790.81</v>
-      </c>
-      <c r="AH13">
-        <v>392</v>
-      </c>
-      <c r="AI13">
-        <v>19.96</v>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>8</v>
-      </c>
-      <c r="AS13" t="s">
-        <v>51</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>52</v>
-      </c>
-      <c r="AU13" t="s">
-        <v>53</v>
-      </c>
-      <c r="AV13" t="s">
-        <v>54</v>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <v>4.16</v>
+      </c>
+      <c r="G25" s="2">
+        <v>-5.06</v>
+      </c>
+      <c r="H25" s="2">
+        <v>19</v>
+      </c>
+      <c r="I25" s="2">
+        <v>19</v>
+      </c>
+      <c r="J25" s="2">
+        <v>38</v>
+      </c>
+      <c r="K25" s="2">
+        <v>0.61</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0.0430555555555556</v>
+      </c>
+      <c r="M25" s="2">
+        <v>5280.63</v>
+      </c>
+      <c r="N25" s="2">
+        <v>596.63</v>
+      </c>
+      <c r="O25" s="2">
+        <v>27.72</v>
+      </c>
+      <c r="P25" s="2">
+        <v>77.03</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>85.17</v>
+      </c>
+      <c r="R25" s="2">
+        <v>9.62</v>
+      </c>
+      <c r="S25" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="T25" s="2">
+        <v>0</v>
+      </c>
+      <c r="U25" s="2">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2">
+        <v>0</v>
+      </c>
+      <c r="W25" s="2">
+        <v>0</v>
+      </c>
+      <c r="X25" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="2">
+        <v>474.4</v>
+      </c>
+      <c r="AG25" s="2">
+        <v>852.39</v>
+      </c>
+      <c r="AH25" s="2">
+        <v>136.52</v>
+      </c>
+      <c r="AI25" s="2">
+        <v>1789.81</v>
+      </c>
+      <c r="AJ25" s="2">
+        <v>2215.38</v>
+      </c>
+      <c r="AK25" s="2">
+        <v>776.61</v>
+      </c>
+      <c r="AL25" s="2">
+        <v>292.03</v>
+      </c>
+      <c r="AM25" s="2">
+        <v>69.7</v>
+      </c>
+      <c r="AN25" s="2">
+        <v>4</v>
+      </c>
+      <c r="AO25" s="2">
+        <v>1.12</v>
+      </c>
+      <c r="AP25" s="2">
+        <v>361.73</v>
+      </c>
+      <c r="AQ25" s="2">
+        <v>21</v>
+      </c>
+      <c r="AR25" s="2">
+        <v>5.83</v>
+      </c>
+      <c r="AS25" s="2">
+        <v>111</v>
+      </c>
+      <c r="AT25" s="2"/>
+      <c r="AU25" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX25" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/GPS_Formativas_2026.xlsx
+++ b/GPS_Formativas_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="GPS_Formativas_2026" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="116">
   <si>
     <t>Date</t>
   </si>
@@ -197,7 +197,7 @@
     <t>INTENSIVA</t>
   </si>
   <si>
-    <t>MD+2</t>
+    <t>MD+3</t>
   </si>
   <si>
     <t>Full</t>
@@ -209,10 +209,16 @@
     <t>Ramiro Burgos</t>
   </si>
   <si>
+    <t>DEL</t>
+  </si>
+  <si>
     <t>Uriel Callorda</t>
   </si>
   <si>
     <t>Danilo Fernandez</t>
+  </si>
+  <si>
+    <t>EXT</t>
   </si>
   <si>
     <t>U17</t>
@@ -221,7 +227,13 @@
     <t>Iñaki Izuibejeres</t>
   </si>
   <si>
+    <t>MD+2</t>
+  </si>
+  <si>
     <t>Luciano Lopez</t>
+  </si>
+  <si>
+    <t>ZAG</t>
   </si>
   <si>
     <t>Mateo Martinez</t>
@@ -242,6 +254,9 @@
     <t>Santiago Sosa</t>
   </si>
   <si>
+    <t>LAT</t>
+  </si>
+  <si>
     <t>19-5-26</t>
   </si>
   <si>
@@ -249,6 +264,9 @@
   </si>
   <si>
     <t>INTENSIVO</t>
+  </si>
+  <si>
+    <t>MD-3</t>
   </si>
   <si>
     <t>Danilo Fernández</t>
@@ -264,6 +282,99 @@
   </si>
   <si>
     <t>Santiago Rosa</t>
+  </si>
+  <si>
+    <t>U14</t>
+  </si>
+  <si>
+    <t>Joaquin Aphesteguy</t>
+  </si>
+  <si>
+    <t>VELOCIDAD</t>
+  </si>
+  <si>
+    <t>Bautista Azambuja</t>
+  </si>
+  <si>
+    <t>Agustin Calvente</t>
+  </si>
+  <si>
+    <t>Diago Chiosoni</t>
+  </si>
+  <si>
+    <t>Bastian Libanés</t>
+  </si>
+  <si>
+    <t>Diego Luna</t>
+  </si>
+  <si>
+    <t>Alejo Mendieta</t>
+  </si>
+  <si>
+    <t>Ian Rodríguez</t>
+  </si>
+  <si>
+    <t>Thiago Silveira</t>
+  </si>
+  <si>
+    <t>Simón Sueiro</t>
+  </si>
+  <si>
+    <t>20-5-26</t>
+  </si>
+  <si>
+    <t>MD-2</t>
+  </si>
+  <si>
+    <t>Matias Martinez</t>
+  </si>
+  <si>
+    <t>Bastian Libanes</t>
+  </si>
+  <si>
+    <t>Ian Rodriguez</t>
+  </si>
+  <si>
+    <t>Thiago Santurion</t>
+  </si>
+  <si>
+    <t>21-5-26</t>
+  </si>
+  <si>
+    <t>Juan Manuel Alvarez</t>
+  </si>
+  <si>
+    <t>MD-1</t>
+  </si>
+  <si>
+    <t>INTENSIDAD</t>
+  </si>
+  <si>
+    <t>Andres Gonzalez</t>
+  </si>
+  <si>
+    <t>Hiojan Guadalupe</t>
+  </si>
+  <si>
+    <t>Walter Mendaro</t>
+  </si>
+  <si>
+    <t>Facundo Perez</t>
+  </si>
+  <si>
+    <t>Mateo Perez</t>
+  </si>
+  <si>
+    <t>READ</t>
+  </si>
+  <si>
+    <t>READAPTACION READAPTACION</t>
+  </si>
+  <si>
+    <t>READAPTACION</t>
+  </si>
+  <si>
+    <t>Rodrigo Rios</t>
   </si>
 </sst>
 </file>
@@ -879,11 +990,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1425,7 +1542,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AX25"/>
+  <dimension ref="A1:AX73"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:50">
@@ -1868,6 +1985,9 @@
       <c r="AS3">
         <v>18</v>
       </c>
+      <c r="AT3" t="s">
+        <v>60</v>
+      </c>
       <c r="AU3" t="s">
         <v>55</v>
       </c>
@@ -1889,7 +2009,7 @@
         <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
         <v>53</v>
@@ -2016,6 +2136,9 @@
       </c>
       <c r="AS4">
         <v>20</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>54</v>
       </c>
       <c r="AU4" t="s">
         <v>55</v>
@@ -2038,7 +2161,7 @@
         <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
         <v>53</v>
@@ -2165,6 +2288,9 @@
       </c>
       <c r="AS5">
         <v>34</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>63</v>
       </c>
       <c r="AU5" t="s">
         <v>55</v>
@@ -2184,10 +2310,10 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
         <v>53</v>
@@ -2315,11 +2441,14 @@
       <c r="AS6">
         <v>27</v>
       </c>
+      <c r="AT6" t="s">
+        <v>63</v>
+      </c>
       <c r="AU6" t="s">
         <v>55</v>
       </c>
       <c r="AV6" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="AW6" t="s">
         <v>57</v>
@@ -2336,7 +2465,7 @@
         <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
         <v>53</v>
@@ -2463,6 +2592,9 @@
       </c>
       <c r="AS7">
         <v>28</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>68</v>
       </c>
       <c r="AU7" t="s">
         <v>55</v>
@@ -2485,7 +2617,7 @@
         <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
         <v>53</v>
@@ -2612,6 +2744,9 @@
       </c>
       <c r="AS8">
         <v>4</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>68</v>
       </c>
       <c r="AU8" t="s">
         <v>55</v>
@@ -2631,10 +2766,10 @@
         <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
         <v>53</v>
@@ -2762,11 +2897,14 @@
       <c r="AS9">
         <v>12</v>
       </c>
+      <c r="AT9" t="s">
+        <v>68</v>
+      </c>
       <c r="AU9" t="s">
         <v>55</v>
       </c>
       <c r="AV9" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="AW9" t="s">
         <v>57</v>
@@ -2780,10 +2918,10 @@
         <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
         <v>53</v>
@@ -2911,11 +3049,14 @@
       <c r="AS10">
         <v>13</v>
       </c>
+      <c r="AT10" t="s">
+        <v>54</v>
+      </c>
       <c r="AU10" t="s">
         <v>55</v>
       </c>
       <c r="AV10" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="AW10" t="s">
         <v>57</v>
@@ -2932,7 +3073,7 @@
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
         <v>53</v>
@@ -3059,6 +3200,9 @@
       </c>
       <c r="AS11">
         <v>41</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>54</v>
       </c>
       <c r="AU11" t="s">
         <v>55</v>
@@ -3078,10 +3222,10 @@
         <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
         <v>53</v>
@@ -3209,11 +3353,14 @@
       <c r="AS12">
         <v>40</v>
       </c>
+      <c r="AT12" t="s">
+        <v>54</v>
+      </c>
       <c r="AU12" t="s">
         <v>55</v>
       </c>
       <c r="AV12" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="AW12" t="s">
         <v>57</v>
@@ -3230,7 +3377,7 @@
         <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
         <v>53</v>
@@ -3357,6 +3504,9 @@
       </c>
       <c r="AS13">
         <v>8</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>75</v>
       </c>
       <c r="AU13" t="s">
         <v>55</v>
@@ -3373,13 +3523,13 @@
     </row>
     <row r="14" spans="1:50">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>53</v>
@@ -3507,12 +3657,14 @@
       <c r="AS14" s="2">
         <v>43</v>
       </c>
-      <c r="AT14" s="2"/>
+      <c r="AT14" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="AU14" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AV14" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="AW14" s="2" t="s">
         <v>57</v>
@@ -3523,7 +3675,7 @@
     </row>
     <row r="15" spans="1:50">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s">
         <v>51</v>
@@ -3657,12 +3809,14 @@
       <c r="AS15" s="2">
         <v>23</v>
       </c>
-      <c r="AT15" s="2"/>
+      <c r="AT15" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="AU15" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AV15" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="AW15" s="2" t="s">
         <v>57</v>
@@ -3673,7 +3827,7 @@
     </row>
     <row r="16" spans="1:50">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B16" t="s">
         <v>51</v>
@@ -3807,12 +3961,14 @@
       <c r="AS16" s="2">
         <v>23</v>
       </c>
-      <c r="AT16" s="2"/>
+      <c r="AT16" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="AU16" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AV16" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="AW16" s="2" t="s">
         <v>57</v>
@@ -3823,13 +3979,13 @@
     </row>
     <row r="17" spans="1:50">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B17" t="s">
         <v>51</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>53</v>
@@ -3957,12 +4113,14 @@
       <c r="AS17" s="2">
         <v>16</v>
       </c>
-      <c r="AT17" s="2"/>
+      <c r="AT17" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="AU17" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AV17" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="AW17" s="2" t="s">
         <v>57</v>
@@ -3973,13 +4131,13 @@
     </row>
     <row r="18" spans="1:50">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>53</v>
@@ -4107,12 +4265,14 @@
       <c r="AS18" s="2">
         <v>51</v>
       </c>
-      <c r="AT18" s="2"/>
+      <c r="AT18" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="AU18" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AV18" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="AW18" s="2" t="s">
         <v>57</v>
@@ -4123,13 +4283,13 @@
     </row>
     <row r="19" spans="1:50">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>53</v>
@@ -4257,12 +4417,14 @@
       <c r="AS19" s="2">
         <v>18</v>
       </c>
-      <c r="AT19" s="2"/>
+      <c r="AT19" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="AU19" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AV19" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="AW19" s="2" t="s">
         <v>57</v>
@@ -4273,13 +4435,13 @@
     </row>
     <row r="20" spans="1:50">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>53</v>
@@ -4407,12 +4569,14 @@
       <c r="AS20" s="2">
         <v>76</v>
       </c>
-      <c r="AT20" s="2"/>
+      <c r="AT20" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="AU20" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AV20" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="AW20" s="2" t="s">
         <v>57</v>
@@ -4423,13 +4587,13 @@
     </row>
     <row r="21" spans="1:50">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s">
         <v>51</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>53</v>
@@ -4557,12 +4721,14 @@
       <c r="AS21" s="2">
         <v>18</v>
       </c>
-      <c r="AT21" s="2"/>
+      <c r="AT21" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="AU21" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AV21" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="AW21" s="2" t="s">
         <v>57</v>
@@ -4573,13 +4739,13 @@
     </row>
     <row r="22" spans="1:50">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
         <v>51</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>53</v>
@@ -4707,12 +4873,14 @@
       <c r="AS22" s="2">
         <v>21</v>
       </c>
-      <c r="AT22" s="2"/>
+      <c r="AT22" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="AU22" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AV22" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="AW22" s="2" t="s">
         <v>57</v>
@@ -4723,13 +4891,13 @@
     </row>
     <row r="23" spans="1:50">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>53</v>
@@ -4857,12 +5025,14 @@
       <c r="AS23" s="2">
         <v>50</v>
       </c>
-      <c r="AT23" s="2"/>
+      <c r="AT23" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="AU23" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AV23" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="AW23" s="2" t="s">
         <v>57</v>
@@ -4873,13 +5043,13 @@
     </row>
     <row r="24" spans="1:50">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s">
         <v>51</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>53</v>
@@ -5007,12 +5177,14 @@
       <c r="AS24" s="2">
         <v>25</v>
       </c>
-      <c r="AT24" s="2"/>
+      <c r="AT24" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="AU24" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AV24" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="AW24" s="2" t="s">
         <v>57</v>
@@ -5023,13 +5195,13 @@
     </row>
     <row r="25" spans="1:50">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
         <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>53</v>
@@ -5157,17 +5329,7315 @@
       <c r="AS25" s="2">
         <v>111</v>
       </c>
-      <c r="AT25" s="2"/>
+      <c r="AT25" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="AU25" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AV25" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="AW25" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AX25" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:50">
+      <c r="A26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="4">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4">
+        <v>3.72</v>
+      </c>
+      <c r="G26" s="4">
+        <v>-5.11</v>
+      </c>
+      <c r="H26" s="4">
+        <v>15</v>
+      </c>
+      <c r="I26" s="4">
+        <v>27</v>
+      </c>
+      <c r="J26" s="4">
+        <v>42</v>
+      </c>
+      <c r="K26" s="4">
+        <v>0.82</v>
+      </c>
+      <c r="L26" s="5">
+        <v>0.0354166666666667</v>
+      </c>
+      <c r="M26" s="4">
+        <v>3764.96</v>
+      </c>
+      <c r="N26" s="4">
+        <v>446.94</v>
+      </c>
+      <c r="O26" s="4">
+        <v>23.58</v>
+      </c>
+      <c r="P26" s="4">
+        <v>65.46</v>
+      </c>
+      <c r="Q26" s="4">
+        <v>73.82</v>
+      </c>
+      <c r="R26" s="4">
+        <v>8.76</v>
+      </c>
+      <c r="S26" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="T26" s="4">
+        <v>0</v>
+      </c>
+      <c r="U26" s="4">
+        <v>0</v>
+      </c>
+      <c r="V26" s="4">
+        <v>0</v>
+      </c>
+      <c r="W26" s="4">
+        <v>0</v>
+      </c>
+      <c r="X26" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="4">
+        <v>347.1</v>
+      </c>
+      <c r="AG26" s="4">
+        <v>531.15</v>
+      </c>
+      <c r="AH26" s="4">
+        <v>178.26</v>
+      </c>
+      <c r="AI26" s="4">
+        <v>1721.9</v>
+      </c>
+      <c r="AJ26" s="4">
+        <v>1373.13</v>
+      </c>
+      <c r="AK26" s="4">
+        <v>408.41</v>
+      </c>
+      <c r="AL26" s="4">
+        <v>83.34</v>
+      </c>
+      <c r="AM26" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN26" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP26" s="4">
+        <v>83.34</v>
+      </c>
+      <c r="AQ26" s="4">
+        <v>9</v>
+      </c>
+      <c r="AR26" s="4">
+        <v>1.63</v>
+      </c>
+      <c r="AS26" s="4">
+        <v>28</v>
+      </c>
+      <c r="AT26" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU26" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW26" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX26" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:50">
+      <c r="A27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4">
+        <v>3.67</v>
+      </c>
+      <c r="G27" s="4">
+        <v>-4.23</v>
+      </c>
+      <c r="H27" s="4">
+        <v>14</v>
+      </c>
+      <c r="I27" s="4">
+        <v>12</v>
+      </c>
+      <c r="J27" s="4">
+        <v>26</v>
+      </c>
+      <c r="K27" s="4">
+        <v>0.51</v>
+      </c>
+      <c r="L27" s="5">
+        <v>0.0354166666666667</v>
+      </c>
+      <c r="M27" s="4">
+        <v>4052.74</v>
+      </c>
+      <c r="N27" s="4">
+        <v>438.08</v>
+      </c>
+      <c r="O27" s="4">
+        <v>24.048</v>
+      </c>
+      <c r="P27" s="4">
+        <v>66.8</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>79.47</v>
+      </c>
+      <c r="R27" s="4">
+        <v>8.59</v>
+      </c>
+      <c r="S27" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="T27" s="4">
+        <v>0</v>
+      </c>
+      <c r="U27" s="4">
+        <v>0</v>
+      </c>
+      <c r="V27" s="4">
+        <v>0</v>
+      </c>
+      <c r="W27" s="4">
+        <v>0</v>
+      </c>
+      <c r="X27" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="4">
+        <v>355.68</v>
+      </c>
+      <c r="AG27" s="4">
+        <v>338.05</v>
+      </c>
+      <c r="AH27" s="4">
+        <v>169.21</v>
+      </c>
+      <c r="AI27" s="4">
+        <v>2145.98</v>
+      </c>
+      <c r="AJ27" s="4">
+        <v>1399.64</v>
+      </c>
+      <c r="AK27" s="4">
+        <v>305.71</v>
+      </c>
+      <c r="AL27" s="4">
+        <v>32.41</v>
+      </c>
+      <c r="AM27" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP27" s="4">
+        <v>32.41</v>
+      </c>
+      <c r="AQ27" s="4">
+        <v>2</v>
+      </c>
+      <c r="AR27" s="4">
+        <v>0.64</v>
+      </c>
+      <c r="AS27" s="4">
+        <v>4</v>
+      </c>
+      <c r="AT27" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU27" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW27" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX27" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:50">
+      <c r="A28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="4">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4">
+        <v>3.77</v>
+      </c>
+      <c r="G28" s="4">
+        <v>-4.04</v>
+      </c>
+      <c r="H28" s="4">
+        <v>6</v>
+      </c>
+      <c r="I28" s="4">
+        <v>14</v>
+      </c>
+      <c r="J28" s="4">
+        <v>20</v>
+      </c>
+      <c r="K28" s="4">
+        <v>0.39</v>
+      </c>
+      <c r="L28" s="5">
+        <v>0.0354166666666667</v>
+      </c>
+      <c r="M28" s="4">
+        <v>3312.87</v>
+      </c>
+      <c r="N28" s="4">
+        <v>384.87</v>
+      </c>
+      <c r="O28" s="4">
+        <v>22.14</v>
+      </c>
+      <c r="P28" s="4">
+        <v>61.51</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>64.96</v>
+      </c>
+      <c r="R28" s="4">
+        <v>7.55</v>
+      </c>
+      <c r="S28" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="T28" s="4">
+        <v>0</v>
+      </c>
+      <c r="U28" s="4">
+        <v>0</v>
+      </c>
+      <c r="V28" s="4">
+        <v>0</v>
+      </c>
+      <c r="W28" s="4">
+        <v>0</v>
+      </c>
+      <c r="X28" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="4">
+        <v>293.2</v>
+      </c>
+      <c r="AG28" s="4">
+        <v>316.47</v>
+      </c>
+      <c r="AH28" s="4">
+        <v>223.15</v>
+      </c>
+      <c r="AI28" s="4">
+        <v>1591.99</v>
+      </c>
+      <c r="AJ28" s="4">
+        <v>1294.89</v>
+      </c>
+      <c r="AK28" s="4">
+        <v>185.74</v>
+      </c>
+      <c r="AL28" s="4">
+        <v>17.08</v>
+      </c>
+      <c r="AM28" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="4">
+        <v>17.08</v>
+      </c>
+      <c r="AQ28" s="4">
+        <v>2</v>
+      </c>
+      <c r="AR28" s="4">
+        <v>0.33</v>
+      </c>
+      <c r="AS28" s="4">
+        <v>15</v>
+      </c>
+      <c r="AT28" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU28" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX28" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:50">
+      <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="4">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4">
+        <v>3.84</v>
+      </c>
+      <c r="G29" s="4">
+        <v>-4.43</v>
+      </c>
+      <c r="H29" s="4">
+        <v>10</v>
+      </c>
+      <c r="I29" s="4">
+        <v>11</v>
+      </c>
+      <c r="J29" s="4">
+        <v>21</v>
+      </c>
+      <c r="K29" s="4">
+        <v>0.41</v>
+      </c>
+      <c r="L29" s="5">
+        <v>0.0354166666666667</v>
+      </c>
+      <c r="M29" s="4">
+        <v>3490.38</v>
+      </c>
+      <c r="N29" s="4">
+        <v>467.63</v>
+      </c>
+      <c r="O29" s="4">
+        <v>20.268</v>
+      </c>
+      <c r="P29" s="4">
+        <v>56.28</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>68.44</v>
+      </c>
+      <c r="R29" s="4">
+        <v>9.17</v>
+      </c>
+      <c r="S29" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="T29" s="4">
+        <v>0</v>
+      </c>
+      <c r="U29" s="4">
+        <v>0</v>
+      </c>
+      <c r="V29" s="4">
+        <v>0</v>
+      </c>
+      <c r="W29" s="4">
+        <v>0</v>
+      </c>
+      <c r="X29" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="4">
+        <v>310.14</v>
+      </c>
+      <c r="AG29" s="4">
+        <v>393.23</v>
+      </c>
+      <c r="AH29" s="4">
+        <v>222.07</v>
+      </c>
+      <c r="AI29" s="4">
+        <v>1905.4</v>
+      </c>
+      <c r="AJ29" s="4">
+        <v>1028.31</v>
+      </c>
+      <c r="AK29" s="4">
+        <v>328.26</v>
+      </c>
+      <c r="AL29" s="4">
+        <v>6</v>
+      </c>
+      <c r="AM29" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="4">
+        <v>6</v>
+      </c>
+      <c r="AQ29" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR29" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="AS29" s="4">
+        <v>136</v>
+      </c>
+      <c r="AT29" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU29" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV29" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX29" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:50">
+      <c r="A30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4">
+        <v>3.97</v>
+      </c>
+      <c r="G30" s="4">
+        <v>-5.04</v>
+      </c>
+      <c r="H30" s="4">
+        <v>7</v>
+      </c>
+      <c r="I30" s="4">
+        <v>13</v>
+      </c>
+      <c r="J30" s="4">
+        <v>20</v>
+      </c>
+      <c r="K30" s="4">
+        <v>0.39</v>
+      </c>
+      <c r="L30" s="5">
+        <v>0.0354166666666667</v>
+      </c>
+      <c r="M30" s="4">
+        <v>3615.45</v>
+      </c>
+      <c r="N30" s="4">
+        <v>415.65</v>
+      </c>
+      <c r="O30" s="4">
+        <v>22.32</v>
+      </c>
+      <c r="P30" s="4">
+        <v>62.02</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>70.89</v>
+      </c>
+      <c r="R30" s="4">
+        <v>8.15</v>
+      </c>
+      <c r="S30" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="T30" s="4">
+        <v>0</v>
+      </c>
+      <c r="U30" s="4">
+        <v>0</v>
+      </c>
+      <c r="V30" s="4">
+        <v>0</v>
+      </c>
+      <c r="W30" s="4">
+        <v>0</v>
+      </c>
+      <c r="X30" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="4">
+        <v>325.67</v>
+      </c>
+      <c r="AG30" s="4">
+        <v>426.05</v>
+      </c>
+      <c r="AH30" s="4">
+        <v>203.57</v>
+      </c>
+      <c r="AI30" s="4">
+        <v>1677.81</v>
+      </c>
+      <c r="AJ30" s="4">
+        <v>1397.24</v>
+      </c>
+      <c r="AK30" s="4">
+        <v>310.2</v>
+      </c>
+      <c r="AL30" s="4">
+        <v>26.29</v>
+      </c>
+      <c r="AM30" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="4">
+        <v>26.29</v>
+      </c>
+      <c r="AQ30" s="4">
+        <v>2</v>
+      </c>
+      <c r="AR30" s="4">
+        <v>0.52</v>
+      </c>
+      <c r="AS30" s="4">
+        <v>17</v>
+      </c>
+      <c r="AT30" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU30" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV30" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX30" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:50">
+      <c r="A31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" s="4">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4">
+        <v>3.84</v>
+      </c>
+      <c r="G31" s="4">
+        <v>-4.58</v>
+      </c>
+      <c r="H31" s="4">
+        <v>25</v>
+      </c>
+      <c r="I31" s="4">
+        <v>25</v>
+      </c>
+      <c r="J31" s="4">
+        <v>50</v>
+      </c>
+      <c r="K31" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="L31" s="5">
+        <v>0.0354166666666667</v>
+      </c>
+      <c r="M31" s="4">
+        <v>3215.54</v>
+      </c>
+      <c r="N31" s="4">
+        <v>438.92</v>
+      </c>
+      <c r="O31" s="4">
+        <v>25.272</v>
+      </c>
+      <c r="P31" s="4">
+        <v>70.18</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>63.05</v>
+      </c>
+      <c r="R31" s="4">
+        <v>8.61</v>
+      </c>
+      <c r="S31" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="T31" s="4">
+        <v>0</v>
+      </c>
+      <c r="U31" s="4">
+        <v>0</v>
+      </c>
+      <c r="V31" s="4">
+        <v>0</v>
+      </c>
+      <c r="W31" s="4">
+        <v>0</v>
+      </c>
+      <c r="X31" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="4">
+        <v>308.36</v>
+      </c>
+      <c r="AG31" s="4">
+        <v>591.34</v>
+      </c>
+      <c r="AH31" s="4">
+        <v>221.02</v>
+      </c>
+      <c r="AI31" s="4">
+        <v>1539.86</v>
+      </c>
+      <c r="AJ31" s="4">
+        <v>997.55</v>
+      </c>
+      <c r="AK31" s="4">
+        <v>403.89</v>
+      </c>
+      <c r="AL31" s="4">
+        <v>51.28</v>
+      </c>
+      <c r="AM31" s="4">
+        <v>2.05</v>
+      </c>
+      <c r="AN31" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="AP31" s="4">
+        <v>53.33</v>
+      </c>
+      <c r="AQ31" s="4">
+        <v>4</v>
+      </c>
+      <c r="AR31" s="4">
+        <v>1.05</v>
+      </c>
+      <c r="AS31" s="4">
+        <v>53</v>
+      </c>
+      <c r="AT31" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV31" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW31" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX31" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:50">
+      <c r="A32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E32" s="4">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4">
+        <v>4.13</v>
+      </c>
+      <c r="G32" s="4">
+        <v>-4.87</v>
+      </c>
+      <c r="H32" s="4">
+        <v>10</v>
+      </c>
+      <c r="I32" s="4">
+        <v>10</v>
+      </c>
+      <c r="J32" s="4">
+        <v>20</v>
+      </c>
+      <c r="K32" s="4">
+        <v>0.39</v>
+      </c>
+      <c r="L32" s="5">
+        <v>0.0354166666666667</v>
+      </c>
+      <c r="M32" s="4">
+        <v>3298.42</v>
+      </c>
+      <c r="N32" s="4">
+        <v>413.05</v>
+      </c>
+      <c r="O32" s="4">
+        <v>21.096</v>
+      </c>
+      <c r="P32" s="4">
+        <v>58.65</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>64.67</v>
+      </c>
+      <c r="R32" s="4">
+        <v>8.1</v>
+      </c>
+      <c r="S32" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="T32" s="4">
+        <v>0</v>
+      </c>
+      <c r="U32" s="4">
+        <v>0</v>
+      </c>
+      <c r="V32" s="4">
+        <v>0</v>
+      </c>
+      <c r="W32" s="4">
+        <v>0</v>
+      </c>
+      <c r="X32" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="4">
+        <v>289.7</v>
+      </c>
+      <c r="AG32" s="4">
+        <v>374.83</v>
+      </c>
+      <c r="AH32" s="4">
+        <v>219.02</v>
+      </c>
+      <c r="AI32" s="4">
+        <v>1703.05</v>
+      </c>
+      <c r="AJ32" s="4">
+        <v>1057.54</v>
+      </c>
+      <c r="AK32" s="4">
+        <v>303.16</v>
+      </c>
+      <c r="AL32" s="4">
+        <v>16.21</v>
+      </c>
+      <c r="AM32" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP32" s="4">
+        <v>16.21</v>
+      </c>
+      <c r="AQ32" s="4">
+        <v>2</v>
+      </c>
+      <c r="AR32" s="4">
+        <v>0.32</v>
+      </c>
+      <c r="AS32" s="4">
+        <v>26</v>
+      </c>
+      <c r="AT32" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU32" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV32" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX32" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:50">
+      <c r="A33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E33" s="4">
+        <v>0</v>
+      </c>
+      <c r="F33" s="4">
+        <v>3.86</v>
+      </c>
+      <c r="G33" s="4">
+        <v>-4.23</v>
+      </c>
+      <c r="H33" s="4">
+        <v>6</v>
+      </c>
+      <c r="I33" s="4">
+        <v>9</v>
+      </c>
+      <c r="J33" s="4">
+        <v>15</v>
+      </c>
+      <c r="K33" s="4">
+        <v>0.29</v>
+      </c>
+      <c r="L33" s="5">
+        <v>0.0354166666666667</v>
+      </c>
+      <c r="M33" s="4">
+        <v>3232.01</v>
+      </c>
+      <c r="N33" s="4">
+        <v>397.01</v>
+      </c>
+      <c r="O33" s="4">
+        <v>20.844</v>
+      </c>
+      <c r="P33" s="4">
+        <v>57.88</v>
+      </c>
+      <c r="Q33" s="4">
+        <v>63.37</v>
+      </c>
+      <c r="R33" s="4">
+        <v>7.78</v>
+      </c>
+      <c r="S33" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="T33" s="4">
+        <v>0</v>
+      </c>
+      <c r="U33" s="4">
+        <v>0</v>
+      </c>
+      <c r="V33" s="4">
+        <v>0</v>
+      </c>
+      <c r="W33" s="4">
+        <v>0</v>
+      </c>
+      <c r="X33" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="4">
+        <v>289.07</v>
+      </c>
+      <c r="AG33" s="4">
+        <v>391.43</v>
+      </c>
+      <c r="AH33" s="4">
+        <v>218.47</v>
+      </c>
+      <c r="AI33" s="4">
+        <v>1584.27</v>
+      </c>
+      <c r="AJ33" s="4">
+        <v>1117.31</v>
+      </c>
+      <c r="AK33" s="4">
+        <v>296.98</v>
+      </c>
+      <c r="AL33" s="4">
+        <v>15</v>
+      </c>
+      <c r="AM33" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO33" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP33" s="4">
+        <v>15</v>
+      </c>
+      <c r="AQ33" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR33" s="4">
+        <v>0.29</v>
+      </c>
+      <c r="AS33" s="4">
+        <v>30</v>
+      </c>
+      <c r="AT33" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU33" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV33" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW33" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX33" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:50">
+      <c r="A34" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="4">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4">
+        <v>3.66</v>
+      </c>
+      <c r="G34" s="4">
+        <v>-4.35</v>
+      </c>
+      <c r="H34" s="4">
+        <v>8</v>
+      </c>
+      <c r="I34" s="4">
+        <v>17</v>
+      </c>
+      <c r="J34" s="4">
+        <v>25</v>
+      </c>
+      <c r="K34" s="4">
+        <v>0.49</v>
+      </c>
+      <c r="L34" s="5">
+        <v>0.0354166666666667</v>
+      </c>
+      <c r="M34" s="4">
+        <v>3343.46</v>
+      </c>
+      <c r="N34" s="4">
+        <v>415.57</v>
+      </c>
+      <c r="O34" s="4">
+        <v>24.228</v>
+      </c>
+      <c r="P34" s="4">
+        <v>67.35</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>65.56</v>
+      </c>
+      <c r="R34" s="4">
+        <v>8.15</v>
+      </c>
+      <c r="S34" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="T34" s="4">
+        <v>0</v>
+      </c>
+      <c r="U34" s="4">
+        <v>0</v>
+      </c>
+      <c r="V34" s="4">
+        <v>0</v>
+      </c>
+      <c r="W34" s="4">
+        <v>0</v>
+      </c>
+      <c r="X34" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="4">
+        <v>305.69</v>
+      </c>
+      <c r="AG34" s="4">
+        <v>475.07</v>
+      </c>
+      <c r="AH34" s="4">
+        <v>167.49</v>
+      </c>
+      <c r="AI34" s="4">
+        <v>1596.99</v>
+      </c>
+      <c r="AJ34" s="4">
+        <v>1161.11</v>
+      </c>
+      <c r="AK34" s="4">
+        <v>357.53</v>
+      </c>
+      <c r="AL34" s="4">
+        <v>60.26</v>
+      </c>
+      <c r="AM34" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="4">
+        <v>60.26</v>
+      </c>
+      <c r="AQ34" s="4">
+        <v>6</v>
+      </c>
+      <c r="AR34" s="4">
+        <v>1.18</v>
+      </c>
+      <c r="AS34" s="4">
+        <v>86</v>
+      </c>
+      <c r="AT34" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU34" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV34" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW34" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX34" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:50">
+      <c r="A35" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4">
+        <v>3.84</v>
+      </c>
+      <c r="G35" s="4">
+        <v>-4.87</v>
+      </c>
+      <c r="H35" s="4">
+        <v>10</v>
+      </c>
+      <c r="I35" s="4">
+        <v>22</v>
+      </c>
+      <c r="J35" s="4">
+        <v>32</v>
+      </c>
+      <c r="K35" s="4">
+        <v>0.63</v>
+      </c>
+      <c r="L35" s="5">
+        <v>0.0354166666666667</v>
+      </c>
+      <c r="M35" s="4">
+        <v>3428.47</v>
+      </c>
+      <c r="N35" s="4">
+        <v>482.79</v>
+      </c>
+      <c r="O35" s="4">
+        <v>22.608</v>
+      </c>
+      <c r="P35" s="4">
+        <v>62.81</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>67.22</v>
+      </c>
+      <c r="R35" s="4">
+        <v>9.47</v>
+      </c>
+      <c r="S35" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="T35" s="4">
+        <v>0</v>
+      </c>
+      <c r="U35" s="4">
+        <v>0</v>
+      </c>
+      <c r="V35" s="4">
+        <v>0</v>
+      </c>
+      <c r="W35" s="4">
+        <v>0</v>
+      </c>
+      <c r="X35" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="4">
+        <v>308.18</v>
+      </c>
+      <c r="AG35" s="4">
+        <v>465.67</v>
+      </c>
+      <c r="AH35" s="4">
+        <v>245.45</v>
+      </c>
+      <c r="AI35" s="4">
+        <v>1834.53</v>
+      </c>
+      <c r="AJ35" s="4">
+        <v>905.34</v>
+      </c>
+      <c r="AK35" s="4">
+        <v>408.97</v>
+      </c>
+      <c r="AL35" s="4">
+        <v>34.19</v>
+      </c>
+      <c r="AM35" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN35" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO35" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP35" s="4">
+        <v>34.19</v>
+      </c>
+      <c r="AQ35" s="4">
+        <v>2</v>
+      </c>
+      <c r="AR35" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="AS35" s="4">
+        <v>214</v>
+      </c>
+      <c r="AT35" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU35" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV35" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW35" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX35" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:50">
+      <c r="A36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36" s="4">
+        <v>0</v>
+      </c>
+      <c r="F36" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="G36" s="4">
+        <v>-5.19</v>
+      </c>
+      <c r="H36" s="4">
+        <v>18</v>
+      </c>
+      <c r="I36" s="4">
+        <v>17</v>
+      </c>
+      <c r="J36" s="4">
+        <v>35</v>
+      </c>
+      <c r="K36" s="4">
+        <v>0.64</v>
+      </c>
+      <c r="L36" s="5">
+        <v>0.0381944444444444</v>
+      </c>
+      <c r="M36" s="4">
+        <v>4786.81</v>
+      </c>
+      <c r="N36" s="4">
+        <v>424.53</v>
+      </c>
+      <c r="O36" s="4">
+        <v>29.196</v>
+      </c>
+      <c r="P36" s="4">
+        <v>81.06</v>
+      </c>
+      <c r="Q36" s="4">
+        <v>87.03</v>
+      </c>
+      <c r="R36" s="4">
+        <v>7.72</v>
+      </c>
+      <c r="S36" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="T36" s="4">
+        <v>0</v>
+      </c>
+      <c r="U36" s="4">
+        <v>0</v>
+      </c>
+      <c r="V36" s="4">
+        <v>0</v>
+      </c>
+      <c r="W36" s="4">
+        <v>0</v>
+      </c>
+      <c r="X36" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="4">
+        <v>421.08</v>
+      </c>
+      <c r="AG36" s="4">
+        <v>783.39</v>
+      </c>
+      <c r="AH36" s="4">
+        <v>131.22</v>
+      </c>
+      <c r="AI36" s="4">
+        <v>2144.54</v>
+      </c>
+      <c r="AJ36" s="4">
+        <v>1397.06</v>
+      </c>
+      <c r="AK36" s="4">
+        <v>801.42</v>
+      </c>
+      <c r="AL36" s="4">
+        <v>275.99</v>
+      </c>
+      <c r="AM36" s="4">
+        <v>36.58</v>
+      </c>
+      <c r="AN36" s="4">
+        <v>2</v>
+      </c>
+      <c r="AO36" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="AP36" s="4">
+        <v>312.57</v>
+      </c>
+      <c r="AQ36" s="4">
+        <v>22</v>
+      </c>
+      <c r="AR36" s="4">
+        <v>5.68</v>
+      </c>
+      <c r="AS36" s="4">
+        <v>11</v>
+      </c>
+      <c r="AT36" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU36" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV36" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW36" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX36" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:50">
+      <c r="A37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" s="4">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4">
+        <v>4.23</v>
+      </c>
+      <c r="G37" s="4">
+        <v>-3.85</v>
+      </c>
+      <c r="H37" s="4">
+        <v>9</v>
+      </c>
+      <c r="I37" s="4">
+        <v>9</v>
+      </c>
+      <c r="J37" s="4">
+        <v>18</v>
+      </c>
+      <c r="K37" s="4">
+        <v>0.38</v>
+      </c>
+      <c r="L37" s="5">
+        <v>0.0326388888888889</v>
+      </c>
+      <c r="M37" s="4">
+        <v>2508.84</v>
+      </c>
+      <c r="N37" s="4">
+        <v>276.41</v>
+      </c>
+      <c r="O37" s="4">
+        <v>25.776</v>
+      </c>
+      <c r="P37" s="4">
+        <v>71.6</v>
+      </c>
+      <c r="Q37" s="4">
+        <v>53.38</v>
+      </c>
+      <c r="R37" s="4">
+        <v>5.88</v>
+      </c>
+      <c r="S37" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="T37" s="4">
+        <v>0</v>
+      </c>
+      <c r="U37" s="4">
+        <v>0</v>
+      </c>
+      <c r="V37" s="4">
+        <v>0</v>
+      </c>
+      <c r="W37" s="4">
+        <v>0</v>
+      </c>
+      <c r="X37" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="4">
+        <v>220.33</v>
+      </c>
+      <c r="AG37" s="4">
+        <v>331.19</v>
+      </c>
+      <c r="AH37" s="4">
+        <v>134</v>
+      </c>
+      <c r="AI37" s="4">
+        <v>1062.02</v>
+      </c>
+      <c r="AJ37" s="4">
+        <v>863.75</v>
+      </c>
+      <c r="AK37" s="4">
+        <v>309.34</v>
+      </c>
+      <c r="AL37" s="4">
+        <v>126.93</v>
+      </c>
+      <c r="AM37" s="4">
+        <v>12.81</v>
+      </c>
+      <c r="AN37" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO37" s="4">
+        <v>0.27</v>
+      </c>
+      <c r="AP37" s="4">
+        <v>139.74</v>
+      </c>
+      <c r="AQ37" s="4">
+        <v>8</v>
+      </c>
+      <c r="AR37" s="4">
+        <v>2.97</v>
+      </c>
+      <c r="AS37" s="4">
+        <v>15</v>
+      </c>
+      <c r="AT37" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU37" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV37" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW37" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX37" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:50">
+      <c r="A38" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" s="4">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4">
+        <v>4.01</v>
+      </c>
+      <c r="G38" s="4">
+        <v>-3.98</v>
+      </c>
+      <c r="H38" s="4">
+        <v>10</v>
+      </c>
+      <c r="I38" s="4">
+        <v>9</v>
+      </c>
+      <c r="J38" s="4">
+        <v>19</v>
+      </c>
+      <c r="K38" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="L38" s="5">
+        <v>0.0326388888888889</v>
+      </c>
+      <c r="M38" s="4">
+        <v>3283.87</v>
+      </c>
+      <c r="N38" s="4">
+        <v>321.97</v>
+      </c>
+      <c r="O38" s="4">
+        <v>26.028</v>
+      </c>
+      <c r="P38" s="4">
+        <v>72.3</v>
+      </c>
+      <c r="Q38" s="4">
+        <v>69.87</v>
+      </c>
+      <c r="R38" s="4">
+        <v>6.85</v>
+      </c>
+      <c r="S38" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="T38" s="4">
+        <v>0</v>
+      </c>
+      <c r="U38" s="4">
+        <v>0</v>
+      </c>
+      <c r="V38" s="4">
+        <v>0</v>
+      </c>
+      <c r="W38" s="4">
+        <v>0</v>
+      </c>
+      <c r="X38" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="4">
+        <v>293.44</v>
+      </c>
+      <c r="AG38" s="4">
+        <v>511.08</v>
+      </c>
+      <c r="AH38" s="4">
+        <v>165.19</v>
+      </c>
+      <c r="AI38" s="4">
+        <v>1538.33</v>
+      </c>
+      <c r="AJ38" s="4">
+        <v>1022.55</v>
+      </c>
+      <c r="AK38" s="4">
+        <v>360.56</v>
+      </c>
+      <c r="AL38" s="4">
+        <v>187.02</v>
+      </c>
+      <c r="AM38" s="4">
+        <v>10.21</v>
+      </c>
+      <c r="AN38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO38" s="4">
+        <v>0.22</v>
+      </c>
+      <c r="AP38" s="4">
+        <v>197.23</v>
+      </c>
+      <c r="AQ38" s="4">
+        <v>13</v>
+      </c>
+      <c r="AR38" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="AS38" s="4">
+        <v>9</v>
+      </c>
+      <c r="AT38" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU38" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV38" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW38" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX38" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:50">
+      <c r="A39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4">
+        <v>4.57</v>
+      </c>
+      <c r="G39" s="4">
+        <v>-6.48</v>
+      </c>
+      <c r="H39" s="4">
+        <v>13</v>
+      </c>
+      <c r="I39" s="4">
+        <v>22</v>
+      </c>
+      <c r="J39" s="4">
+        <v>35</v>
+      </c>
+      <c r="K39" s="4">
+        <v>0.74</v>
+      </c>
+      <c r="L39" s="5">
+        <v>0.0326388888888889</v>
+      </c>
+      <c r="M39" s="4">
+        <v>2668.51</v>
+      </c>
+      <c r="N39" s="4">
+        <v>245.56</v>
+      </c>
+      <c r="O39" s="4">
+        <v>28.8</v>
+      </c>
+      <c r="P39" s="4">
+        <v>80</v>
+      </c>
+      <c r="Q39" s="4">
+        <v>56.78</v>
+      </c>
+      <c r="R39" s="4">
+        <v>5.22</v>
+      </c>
+      <c r="S39" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="T39" s="4">
+        <v>0</v>
+      </c>
+      <c r="U39" s="4">
+        <v>0</v>
+      </c>
+      <c r="V39" s="4">
+        <v>0</v>
+      </c>
+      <c r="W39" s="4">
+        <v>0</v>
+      </c>
+      <c r="X39" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="4">
+        <v>246.33</v>
+      </c>
+      <c r="AG39" s="4">
+        <v>510.73</v>
+      </c>
+      <c r="AH39" s="4">
+        <v>168.62</v>
+      </c>
+      <c r="AI39" s="4">
+        <v>1180.51</v>
+      </c>
+      <c r="AJ39" s="4">
+        <v>705.54</v>
+      </c>
+      <c r="AK39" s="4">
+        <v>387.58</v>
+      </c>
+      <c r="AL39" s="4">
+        <v>178.33</v>
+      </c>
+      <c r="AM39" s="4">
+        <v>47.81</v>
+      </c>
+      <c r="AN39" s="4">
+        <v>3</v>
+      </c>
+      <c r="AO39" s="4">
+        <v>1.02</v>
+      </c>
+      <c r="AP39" s="4">
+        <v>226.14</v>
+      </c>
+      <c r="AQ39" s="4">
+        <v>11</v>
+      </c>
+      <c r="AR39" s="4">
+        <v>4.81</v>
+      </c>
+      <c r="AS39" s="4">
+        <v>8</v>
+      </c>
+      <c r="AT39" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU39" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV39" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW39" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX39" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:50">
+      <c r="A40" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4">
+        <v>4.51</v>
+      </c>
+      <c r="G40" s="4">
+        <v>-5.34</v>
+      </c>
+      <c r="H40" s="4">
+        <v>12</v>
+      </c>
+      <c r="I40" s="4">
+        <v>16</v>
+      </c>
+      <c r="J40" s="4">
+        <v>28</v>
+      </c>
+      <c r="K40" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="L40" s="5">
+        <v>0.0326388888888889</v>
+      </c>
+      <c r="M40" s="4">
+        <v>2603.49</v>
+      </c>
+      <c r="N40" s="4">
+        <v>251.96</v>
+      </c>
+      <c r="O40" s="4">
+        <v>27.18</v>
+      </c>
+      <c r="P40" s="4">
+        <v>75.5</v>
+      </c>
+      <c r="Q40" s="4">
+        <v>55.39</v>
+      </c>
+      <c r="R40" s="4">
+        <v>5.36</v>
+      </c>
+      <c r="S40" s="4">
+        <v>0.07</v>
+      </c>
+      <c r="T40" s="4">
+        <v>0</v>
+      </c>
+      <c r="U40" s="4">
+        <v>0</v>
+      </c>
+      <c r="V40" s="4">
+        <v>0</v>
+      </c>
+      <c r="W40" s="4">
+        <v>0</v>
+      </c>
+      <c r="X40" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="4">
+        <v>240.71</v>
+      </c>
+      <c r="AG40" s="4">
+        <v>460.54</v>
+      </c>
+      <c r="AH40" s="4">
+        <v>148.9</v>
+      </c>
+      <c r="AI40" s="4">
+        <v>1232.71</v>
+      </c>
+      <c r="AJ40" s="4">
+        <v>751.49</v>
+      </c>
+      <c r="AK40" s="4">
+        <v>221.72</v>
+      </c>
+      <c r="AL40" s="4">
+        <v>200.33</v>
+      </c>
+      <c r="AM40" s="4">
+        <v>48.34</v>
+      </c>
+      <c r="AN40" s="4">
+        <v>4</v>
+      </c>
+      <c r="AO40" s="4">
+        <v>1.03</v>
+      </c>
+      <c r="AP40" s="4">
+        <v>248.67</v>
+      </c>
+      <c r="AQ40" s="4">
+        <v>16</v>
+      </c>
+      <c r="AR40" s="4">
+        <v>5.29</v>
+      </c>
+      <c r="AS40" s="4">
+        <v>8</v>
+      </c>
+      <c r="AT40" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU40" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV40" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW40" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX40" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:50">
+      <c r="A41" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" s="4">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4">
+        <v>3.79</v>
+      </c>
+      <c r="G41" s="4">
+        <v>-4.35</v>
+      </c>
+      <c r="H41" s="4">
+        <v>12</v>
+      </c>
+      <c r="I41" s="4">
+        <v>11</v>
+      </c>
+      <c r="J41" s="4">
+        <v>23</v>
+      </c>
+      <c r="K41" s="4">
+        <v>0.42</v>
+      </c>
+      <c r="L41" s="5">
+        <v>0.0381944444444444</v>
+      </c>
+      <c r="M41" s="4">
+        <v>4995.87</v>
+      </c>
+      <c r="N41" s="4">
+        <v>485.14</v>
+      </c>
+      <c r="O41" s="4">
+        <v>28.08</v>
+      </c>
+      <c r="P41" s="4">
+        <v>77.98</v>
+      </c>
+      <c r="Q41" s="4">
+        <v>90.83</v>
+      </c>
+      <c r="R41" s="4">
+        <v>8.82</v>
+      </c>
+      <c r="S41" s="4">
+        <v>0.19</v>
+      </c>
+      <c r="T41" s="4">
+        <v>0</v>
+      </c>
+      <c r="U41" s="4">
+        <v>0</v>
+      </c>
+      <c r="V41" s="4">
+        <v>0</v>
+      </c>
+      <c r="W41" s="4">
+        <v>0</v>
+      </c>
+      <c r="X41" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="4">
+        <v>435.52</v>
+      </c>
+      <c r="AG41" s="4">
+        <v>907.43</v>
+      </c>
+      <c r="AH41" s="4">
+        <v>120.03</v>
+      </c>
+      <c r="AI41" s="4">
+        <v>1887.04</v>
+      </c>
+      <c r="AJ41" s="4">
+        <v>1702.79</v>
+      </c>
+      <c r="AK41" s="4">
+        <v>706.82</v>
+      </c>
+      <c r="AL41" s="4">
+        <v>537.05</v>
+      </c>
+      <c r="AM41" s="4">
+        <v>42.17</v>
+      </c>
+      <c r="AN41" s="4">
+        <v>3</v>
+      </c>
+      <c r="AO41" s="4">
+        <v>0.77</v>
+      </c>
+      <c r="AP41" s="4">
+        <v>579.22</v>
+      </c>
+      <c r="AQ41" s="4">
+        <v>32</v>
+      </c>
+      <c r="AR41" s="4">
+        <v>10.53</v>
+      </c>
+      <c r="AS41" s="4">
+        <v>13</v>
+      </c>
+      <c r="AT41" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU41" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV41" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW41" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX41" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:50">
+      <c r="A42" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E42" s="4">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4">
+        <v>4.57</v>
+      </c>
+      <c r="G42" s="4">
+        <v>-5.77</v>
+      </c>
+      <c r="H42" s="4">
+        <v>20</v>
+      </c>
+      <c r="I42" s="4">
+        <v>19</v>
+      </c>
+      <c r="J42" s="4">
+        <v>39</v>
+      </c>
+      <c r="K42" s="4">
+        <v>0.83</v>
+      </c>
+      <c r="L42" s="5">
+        <v>0.0326388888888889</v>
+      </c>
+      <c r="M42" s="4">
+        <v>3276.02</v>
+      </c>
+      <c r="N42" s="4">
+        <v>348.52</v>
+      </c>
+      <c r="O42" s="4">
+        <v>27.648</v>
+      </c>
+      <c r="P42" s="4">
+        <v>69.08</v>
+      </c>
+      <c r="Q42" s="4">
+        <v>69.7</v>
+      </c>
+      <c r="R42" s="4">
+        <v>7.42</v>
+      </c>
+      <c r="S42" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="T42" s="4">
+        <v>0</v>
+      </c>
+      <c r="U42" s="4">
+        <v>0</v>
+      </c>
+      <c r="V42" s="4">
+        <v>0</v>
+      </c>
+      <c r="W42" s="4">
+        <v>0</v>
+      </c>
+      <c r="X42" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="4">
+        <v>817.29</v>
+      </c>
+      <c r="AG42" s="4">
+        <v>651.72</v>
+      </c>
+      <c r="AH42" s="4">
+        <v>152.58</v>
+      </c>
+      <c r="AI42" s="4">
+        <v>1374.65</v>
+      </c>
+      <c r="AJ42" s="4">
+        <v>1043</v>
+      </c>
+      <c r="AK42" s="4">
+        <v>483.01</v>
+      </c>
+      <c r="AL42" s="4">
+        <v>146.71</v>
+      </c>
+      <c r="AM42" s="4">
+        <v>75.92</v>
+      </c>
+      <c r="AN42" s="4">
+        <v>6</v>
+      </c>
+      <c r="AO42" s="4">
+        <v>1.62</v>
+      </c>
+      <c r="AP42" s="4">
+        <v>222.63</v>
+      </c>
+      <c r="AQ42" s="4">
+        <v>12</v>
+      </c>
+      <c r="AR42" s="4">
+        <v>4.74</v>
+      </c>
+      <c r="AS42" s="4">
+        <v>34</v>
+      </c>
+      <c r="AT42" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU42" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV42" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW42" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX42" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:50">
+      <c r="A43" t="s">
+        <v>97</v>
+      </c>
+      <c r="B43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E43" s="4">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4">
+        <v>4.17</v>
+      </c>
+      <c r="G43" s="4">
+        <v>-5.92</v>
+      </c>
+      <c r="H43" s="4">
+        <v>11</v>
+      </c>
+      <c r="I43" s="4">
+        <v>15</v>
+      </c>
+      <c r="J43" s="4">
+        <v>26</v>
+      </c>
+      <c r="K43" s="4">
+        <v>0.55</v>
+      </c>
+      <c r="L43" s="5">
+        <v>0.0326388888888889</v>
+      </c>
+      <c r="M43" s="4">
+        <v>2595.44</v>
+      </c>
+      <c r="N43" s="4">
+        <v>273.24</v>
+      </c>
+      <c r="O43" s="4">
+        <v>27.432</v>
+      </c>
+      <c r="P43" s="4">
+        <v>76.24</v>
+      </c>
+      <c r="Q43" s="4">
+        <v>55.22</v>
+      </c>
+      <c r="R43" s="4">
+        <v>5.81</v>
+      </c>
+      <c r="S43" s="4">
+        <v>0.06</v>
+      </c>
+      <c r="T43" s="4">
+        <v>134</v>
+      </c>
+      <c r="U43" s="4">
+        <v>72.05</v>
+      </c>
+      <c r="V43" s="4">
+        <v>67</v>
+      </c>
+      <c r="W43" s="4">
+        <v>36.03</v>
+      </c>
+      <c r="X43" s="4">
+        <v>25</v>
+      </c>
+      <c r="Y43" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="5">
+        <v>0.01625</v>
+      </c>
+      <c r="AA43" s="5">
+        <v>0.000636574074074074</v>
+      </c>
+      <c r="AB43" s="5">
+        <v>0.000219907407407407</v>
+      </c>
+      <c r="AC43" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="4">
+        <v>234.6</v>
+      </c>
+      <c r="AG43" s="4">
+        <v>351.07</v>
+      </c>
+      <c r="AH43" s="4">
+        <v>146.49</v>
+      </c>
+      <c r="AI43" s="4">
+        <v>1305.43</v>
+      </c>
+      <c r="AJ43" s="4">
+        <v>788.44</v>
+      </c>
+      <c r="AK43" s="4">
+        <v>195.94</v>
+      </c>
+      <c r="AL43" s="4">
+        <v>99.1</v>
+      </c>
+      <c r="AM43" s="4">
+        <v>60.05</v>
+      </c>
+      <c r="AN43" s="4">
+        <v>6</v>
+      </c>
+      <c r="AO43" s="4">
+        <v>1.28</v>
+      </c>
+      <c r="AP43" s="4">
+        <v>159.15</v>
+      </c>
+      <c r="AQ43" s="4">
+        <v>8</v>
+      </c>
+      <c r="AR43" s="4">
+        <v>3.39</v>
+      </c>
+      <c r="AS43" s="4">
+        <v>29</v>
+      </c>
+      <c r="AT43" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU43" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV43" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW43" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX43" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:50">
+      <c r="A44" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44" s="4">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4">
+        <v>4.22</v>
+      </c>
+      <c r="G44" s="4">
+        <v>-5.71</v>
+      </c>
+      <c r="H44" s="4">
+        <v>14</v>
+      </c>
+      <c r="I44" s="4">
+        <v>15</v>
+      </c>
+      <c r="J44" s="4">
+        <v>29</v>
+      </c>
+      <c r="K44" s="4">
+        <v>0.62</v>
+      </c>
+      <c r="L44" s="5">
+        <v>0.0326388888888889</v>
+      </c>
+      <c r="M44" s="4">
+        <v>2246.48</v>
+      </c>
+      <c r="N44" s="4">
+        <v>224.62</v>
+      </c>
+      <c r="O44" s="4">
+        <v>26.82</v>
+      </c>
+      <c r="P44" s="4">
+        <v>74.46</v>
+      </c>
+      <c r="Q44" s="4">
+        <v>47.8</v>
+      </c>
+      <c r="R44" s="4">
+        <v>4.78</v>
+      </c>
+      <c r="S44" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="T44" s="4">
+        <v>0</v>
+      </c>
+      <c r="U44" s="4">
+        <v>0</v>
+      </c>
+      <c r="V44" s="4">
+        <v>0</v>
+      </c>
+      <c r="W44" s="4">
+        <v>0</v>
+      </c>
+      <c r="X44" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="4">
+        <v>552.91</v>
+      </c>
+      <c r="AG44" s="4">
+        <v>395.91</v>
+      </c>
+      <c r="AH44" s="4">
+        <v>203.45</v>
+      </c>
+      <c r="AI44" s="4">
+        <v>1125.76</v>
+      </c>
+      <c r="AJ44" s="4">
+        <v>547.7</v>
+      </c>
+      <c r="AK44" s="4">
+        <v>135.55</v>
+      </c>
+      <c r="AL44" s="4">
+        <v>164.15</v>
+      </c>
+      <c r="AM44" s="4">
+        <v>69.87</v>
+      </c>
+      <c r="AN44" s="4">
+        <v>6</v>
+      </c>
+      <c r="AO44" s="4">
+        <v>1.49</v>
+      </c>
+      <c r="AP44" s="4">
+        <v>234.02</v>
+      </c>
+      <c r="AQ44" s="4">
+        <v>11</v>
+      </c>
+      <c r="AR44" s="4">
+        <v>4.98</v>
+      </c>
+      <c r="AS44" s="4">
+        <v>14</v>
+      </c>
+      <c r="AT44" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU44" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV44" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX44" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:50">
+      <c r="A45" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="4">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4">
+        <v>4.23</v>
+      </c>
+      <c r="G45" s="4">
+        <v>-6.14</v>
+      </c>
+      <c r="H45" s="4">
+        <v>16</v>
+      </c>
+      <c r="I45" s="4">
+        <v>15</v>
+      </c>
+      <c r="J45" s="4">
+        <v>31</v>
+      </c>
+      <c r="K45" s="4">
+        <v>0.66</v>
+      </c>
+      <c r="L45" s="5">
+        <v>0.0326388888888889</v>
+      </c>
+      <c r="M45" s="4">
+        <v>2873.99</v>
+      </c>
+      <c r="N45" s="4">
+        <v>292.65</v>
+      </c>
+      <c r="O45" s="4">
+        <v>28.548</v>
+      </c>
+      <c r="P45" s="4">
+        <v>79.3</v>
+      </c>
+      <c r="Q45" s="4">
+        <v>61.15</v>
+      </c>
+      <c r="R45" s="4">
+        <v>6.23</v>
+      </c>
+      <c r="S45" s="4">
+        <v>0.07</v>
+      </c>
+      <c r="T45" s="4">
+        <v>0</v>
+      </c>
+      <c r="U45" s="4">
+        <v>0</v>
+      </c>
+      <c r="V45" s="4">
+        <v>0</v>
+      </c>
+      <c r="W45" s="4">
+        <v>0</v>
+      </c>
+      <c r="X45" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="4">
+        <v>262.64</v>
+      </c>
+      <c r="AG45" s="4">
+        <v>425.81</v>
+      </c>
+      <c r="AH45" s="4">
+        <v>163.61</v>
+      </c>
+      <c r="AI45" s="4">
+        <v>1631.99</v>
+      </c>
+      <c r="AJ45" s="4">
+        <v>684.19</v>
+      </c>
+      <c r="AK45" s="4">
+        <v>210.91</v>
+      </c>
+      <c r="AL45" s="4">
+        <v>97.16</v>
+      </c>
+      <c r="AM45" s="4">
+        <v>86.12</v>
+      </c>
+      <c r="AN45" s="4">
+        <v>6</v>
+      </c>
+      <c r="AO45" s="4">
+        <v>1.83</v>
+      </c>
+      <c r="AP45" s="4">
+        <v>183.28</v>
+      </c>
+      <c r="AQ45" s="4">
+        <v>9</v>
+      </c>
+      <c r="AR45" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="AS45" s="4">
+        <v>35</v>
+      </c>
+      <c r="AT45" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU45" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV45" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW45" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX45" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:50">
+      <c r="A46" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" s="4">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4">
+        <v>3.63</v>
+      </c>
+      <c r="G46" s="4">
+        <v>-3.99</v>
+      </c>
+      <c r="H46" s="4">
+        <v>1</v>
+      </c>
+      <c r="I46" s="4">
+        <v>10</v>
+      </c>
+      <c r="J46" s="4">
+        <v>11</v>
+      </c>
+      <c r="K46" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="L46" s="5">
+        <v>0.0381944444444444</v>
+      </c>
+      <c r="M46" s="4">
+        <v>3098.22</v>
+      </c>
+      <c r="N46" s="4">
+        <v>330.83</v>
+      </c>
+      <c r="O46" s="4">
+        <v>28.116</v>
+      </c>
+      <c r="P46" s="4">
+        <v>78.12</v>
+      </c>
+      <c r="Q46" s="4">
+        <v>56.33</v>
+      </c>
+      <c r="R46" s="4">
+        <v>6.02</v>
+      </c>
+      <c r="S46" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="T46" s="4">
+        <v>0</v>
+      </c>
+      <c r="U46" s="4">
+        <v>0</v>
+      </c>
+      <c r="V46" s="4">
+        <v>0</v>
+      </c>
+      <c r="W46" s="4">
+        <v>0</v>
+      </c>
+      <c r="X46" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="4">
+        <v>265.36</v>
+      </c>
+      <c r="AG46" s="4">
+        <v>347.47</v>
+      </c>
+      <c r="AH46" s="4">
+        <v>76.96</v>
+      </c>
+      <c r="AI46" s="4">
+        <v>1189.22</v>
+      </c>
+      <c r="AJ46" s="4">
+        <v>1289.11</v>
+      </c>
+      <c r="AK46" s="4">
+        <v>448.2</v>
+      </c>
+      <c r="AL46" s="4">
+        <v>78.81</v>
+      </c>
+      <c r="AM46" s="4">
+        <v>15.92</v>
+      </c>
+      <c r="AN46" s="4">
+        <v>1</v>
+      </c>
+      <c r="AO46" s="4">
+        <v>0.29</v>
+      </c>
+      <c r="AP46" s="4">
+        <v>94.73</v>
+      </c>
+      <c r="AQ46" s="4">
+        <v>6</v>
+      </c>
+      <c r="AR46" s="4">
+        <v>1.72</v>
+      </c>
+      <c r="AS46" s="4">
+        <v>16</v>
+      </c>
+      <c r="AT46" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU46" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV46" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW46" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX46" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:50">
+      <c r="A47" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E47" s="4">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4">
+        <v>5.29</v>
+      </c>
+      <c r="G47" s="4">
+        <v>-4.5</v>
+      </c>
+      <c r="H47" s="4">
+        <v>10</v>
+      </c>
+      <c r="I47" s="4">
+        <v>6</v>
+      </c>
+      <c r="J47" s="4">
+        <v>16</v>
+      </c>
+      <c r="K47" s="4">
+        <v>0.34</v>
+      </c>
+      <c r="L47" s="5">
+        <v>0.0326388888888889</v>
+      </c>
+      <c r="M47" s="4">
+        <v>3080.62</v>
+      </c>
+      <c r="N47" s="4">
+        <v>385.92</v>
+      </c>
+      <c r="O47" s="4">
+        <v>27.396</v>
+      </c>
+      <c r="P47" s="4">
+        <v>76.13</v>
+      </c>
+      <c r="Q47" s="4">
+        <v>65.55</v>
+      </c>
+      <c r="R47" s="4">
+        <v>8.21</v>
+      </c>
+      <c r="S47" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="T47" s="4">
+        <v>0</v>
+      </c>
+      <c r="U47" s="4">
+        <v>0</v>
+      </c>
+      <c r="V47" s="4">
+        <v>0</v>
+      </c>
+      <c r="W47" s="4">
+        <v>0</v>
+      </c>
+      <c r="X47" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="4">
+        <v>232.48</v>
+      </c>
+      <c r="AG47" s="4">
+        <v>350.83</v>
+      </c>
+      <c r="AH47" s="4">
+        <v>416.84</v>
+      </c>
+      <c r="AI47" s="4">
+        <v>1434.31</v>
+      </c>
+      <c r="AJ47" s="4">
+        <v>904.43</v>
+      </c>
+      <c r="AK47" s="4">
+        <v>204.69</v>
+      </c>
+      <c r="AL47" s="4">
+        <v>99.11</v>
+      </c>
+      <c r="AM47" s="4">
+        <v>21.23</v>
+      </c>
+      <c r="AN47" s="4">
+        <v>2</v>
+      </c>
+      <c r="AO47" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="AP47" s="4">
+        <v>120.34</v>
+      </c>
+      <c r="AQ47" s="4">
+        <v>6</v>
+      </c>
+      <c r="AR47" s="4">
+        <v>2.56</v>
+      </c>
+      <c r="AS47" s="4">
+        <v>18</v>
+      </c>
+      <c r="AT47" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU47" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV47" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW47" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX47" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="1:50">
+      <c r="A48" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E48" s="4">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4">
+        <v>4.37</v>
+      </c>
+      <c r="G48" s="4">
+        <v>-4.92</v>
+      </c>
+      <c r="H48" s="4">
+        <v>10</v>
+      </c>
+      <c r="I48" s="4">
+        <v>10</v>
+      </c>
+      <c r="J48" s="4">
+        <v>20</v>
+      </c>
+      <c r="K48" s="4">
+        <v>0.43</v>
+      </c>
+      <c r="L48" s="5">
+        <v>0.0326388888888889</v>
+      </c>
+      <c r="M48" s="4">
+        <v>3092.6</v>
+      </c>
+      <c r="N48" s="4">
+        <v>341.07</v>
+      </c>
+      <c r="O48" s="4">
+        <v>29.664</v>
+      </c>
+      <c r="P48" s="4">
+        <v>82.35</v>
+      </c>
+      <c r="Q48" s="4">
+        <v>65.8</v>
+      </c>
+      <c r="R48" s="4">
+        <v>7.26</v>
+      </c>
+      <c r="S48" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="T48" s="4">
+        <v>0</v>
+      </c>
+      <c r="U48" s="4">
+        <v>0</v>
+      </c>
+      <c r="V48" s="4">
+        <v>0</v>
+      </c>
+      <c r="W48" s="4">
+        <v>0</v>
+      </c>
+      <c r="X48" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="4">
+        <v>275.07</v>
+      </c>
+      <c r="AG48" s="4">
+        <v>500.89</v>
+      </c>
+      <c r="AH48" s="4">
+        <v>125.17</v>
+      </c>
+      <c r="AI48" s="4">
+        <v>1588.32</v>
+      </c>
+      <c r="AJ48" s="4">
+        <v>754.66</v>
+      </c>
+      <c r="AK48" s="4">
+        <v>305.22</v>
+      </c>
+      <c r="AL48" s="4">
+        <v>249.15</v>
+      </c>
+      <c r="AM48" s="4">
+        <v>70.07</v>
+      </c>
+      <c r="AN48" s="4">
+        <v>4</v>
+      </c>
+      <c r="AO48" s="4">
+        <v>1.49</v>
+      </c>
+      <c r="AP48" s="4">
+        <v>319.22</v>
+      </c>
+      <c r="AQ48" s="4">
+        <v>17</v>
+      </c>
+      <c r="AR48" s="4">
+        <v>6.79</v>
+      </c>
+      <c r="AS48" s="4">
+        <v>110</v>
+      </c>
+      <c r="AT48" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU48" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV48" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW48" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX48" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="1:50">
+      <c r="A49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" t="s">
+        <v>85</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E49" s="4">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4">
+        <v>3.41</v>
+      </c>
+      <c r="G49" s="4">
+        <v>-4.36</v>
+      </c>
+      <c r="H49" s="4">
+        <v>4</v>
+      </c>
+      <c r="I49" s="4">
+        <v>4</v>
+      </c>
+      <c r="J49" s="4">
+        <v>8</v>
+      </c>
+      <c r="K49" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="L49" s="5">
+        <v>0.181689814814815</v>
+      </c>
+      <c r="M49" s="4">
+        <v>3883.31</v>
+      </c>
+      <c r="N49" s="4">
+        <v>483.04</v>
+      </c>
+      <c r="O49" s="4">
+        <v>6.93</v>
+      </c>
+      <c r="P49" s="4">
+        <v>69.27</v>
+      </c>
+      <c r="Q49" s="4">
+        <v>15.02</v>
+      </c>
+      <c r="R49" s="4">
+        <v>1.85</v>
+      </c>
+      <c r="S49" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="T49" s="4">
+        <v>0</v>
+      </c>
+      <c r="U49" s="4">
+        <v>0</v>
+      </c>
+      <c r="V49" s="4">
+        <v>0</v>
+      </c>
+      <c r="W49" s="4">
+        <v>0</v>
+      </c>
+      <c r="X49" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="4">
+        <v>321.38</v>
+      </c>
+      <c r="AG49" s="4">
+        <v>332.85</v>
+      </c>
+      <c r="AH49" s="4">
+        <v>372.44</v>
+      </c>
+      <c r="AI49" s="4">
+        <v>2176.67</v>
+      </c>
+      <c r="AJ49" s="4">
+        <v>978.56</v>
+      </c>
+      <c r="AK49" s="4">
+        <v>239.73</v>
+      </c>
+      <c r="AL49" s="4">
+        <v>115.91</v>
+      </c>
+      <c r="AM49" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN49" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO49" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP49" s="4">
+        <v>115.91</v>
+      </c>
+      <c r="AQ49" s="4">
+        <v>8</v>
+      </c>
+      <c r="AR49" s="4">
+        <v>0.44</v>
+      </c>
+      <c r="AS49" s="4">
+        <v>96</v>
+      </c>
+      <c r="AT49" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU49" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV49" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW49" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX49" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:50">
+      <c r="A50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B50" t="s">
+        <v>85</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E50" s="4">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4">
+        <v>4.01</v>
+      </c>
+      <c r="G50" s="4">
+        <v>-3.55</v>
+      </c>
+      <c r="H50" s="4">
+        <v>8</v>
+      </c>
+      <c r="I50" s="4">
+        <v>6</v>
+      </c>
+      <c r="J50" s="4">
+        <v>14</v>
+      </c>
+      <c r="K50" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="L50" s="5">
+        <v>0.226145833333333</v>
+      </c>
+      <c r="M50" s="4">
+        <v>5245.04</v>
+      </c>
+      <c r="N50" s="4">
+        <v>576.67</v>
+      </c>
+      <c r="O50" s="4">
+        <v>7.72</v>
+      </c>
+      <c r="P50" s="4">
+        <v>77.18</v>
+      </c>
+      <c r="Q50" s="4">
+        <v>16.19</v>
+      </c>
+      <c r="R50" s="4">
+        <v>1.77</v>
+      </c>
+      <c r="S50" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="T50" s="4">
+        <v>0</v>
+      </c>
+      <c r="U50" s="4">
+        <v>0</v>
+      </c>
+      <c r="V50" s="4">
+        <v>0</v>
+      </c>
+      <c r="W50" s="4">
+        <v>0</v>
+      </c>
+      <c r="X50" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="4">
+        <v>438.74</v>
+      </c>
+      <c r="AG50" s="4">
+        <v>492.72</v>
+      </c>
+      <c r="AH50" s="4">
+        <v>362.72</v>
+      </c>
+      <c r="AI50" s="4">
+        <v>2513.53</v>
+      </c>
+      <c r="AJ50" s="4">
+        <v>1764.68</v>
+      </c>
+      <c r="AK50" s="4">
+        <v>427</v>
+      </c>
+      <c r="AL50" s="4">
+        <v>155.07</v>
+      </c>
+      <c r="AM50" s="4">
+        <v>21.2</v>
+      </c>
+      <c r="AN50" s="4">
+        <v>1</v>
+      </c>
+      <c r="AO50" s="4">
+        <v>0.07</v>
+      </c>
+      <c r="AP50" s="4">
+        <v>176.27</v>
+      </c>
+      <c r="AQ50" s="4">
+        <v>11</v>
+      </c>
+      <c r="AR50" s="4">
+        <v>0.54</v>
+      </c>
+      <c r="AS50" s="4">
+        <v>20</v>
+      </c>
+      <c r="AT50" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU50" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV50" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW50" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX50" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="1:50">
+      <c r="A51" t="s">
+        <v>97</v>
+      </c>
+      <c r="B51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" s="4">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4">
+        <v>3.62</v>
+      </c>
+      <c r="G51" s="4">
+        <v>-4.26</v>
+      </c>
+      <c r="H51" s="4">
+        <v>8</v>
+      </c>
+      <c r="I51" s="4">
+        <v>20</v>
+      </c>
+      <c r="J51" s="4">
+        <v>28</v>
+      </c>
+      <c r="K51" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="L51" s="5">
+        <v>0.226018518518519</v>
+      </c>
+      <c r="M51" s="4">
+        <v>5665.25</v>
+      </c>
+      <c r="N51" s="4">
+        <v>603.06</v>
+      </c>
+      <c r="O51" s="4">
+        <v>6.58</v>
+      </c>
+      <c r="P51" s="4">
+        <v>65.79</v>
+      </c>
+      <c r="Q51" s="4">
+        <v>17.47</v>
+      </c>
+      <c r="R51" s="4">
+        <v>1.85</v>
+      </c>
+      <c r="S51" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="T51" s="4">
+        <v>0</v>
+      </c>
+      <c r="U51" s="4">
+        <v>0</v>
+      </c>
+      <c r="V51" s="4">
+        <v>0</v>
+      </c>
+      <c r="W51" s="4">
+        <v>0</v>
+      </c>
+      <c r="X51" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="4">
+        <v>482.37</v>
+      </c>
+      <c r="AG51" s="4">
+        <v>779.54</v>
+      </c>
+      <c r="AH51" s="4">
+        <v>304.61</v>
+      </c>
+      <c r="AI51" s="4">
+        <v>2932.65</v>
+      </c>
+      <c r="AJ51" s="4">
+        <v>1551.99</v>
+      </c>
+      <c r="AK51" s="4">
+        <v>522.73</v>
+      </c>
+      <c r="AL51" s="4">
+        <v>353.26</v>
+      </c>
+      <c r="AM51" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="4">
+        <v>353.26</v>
+      </c>
+      <c r="AQ51" s="4">
+        <v>18</v>
+      </c>
+      <c r="AR51" s="4">
+        <v>1.09</v>
+      </c>
+      <c r="AS51" s="4">
+        <v>63</v>
+      </c>
+      <c r="AT51" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU51" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV51" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW51" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX51" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:50">
+      <c r="A52" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" t="s">
+        <v>85</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E52" s="4">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4">
+        <v>4.09</v>
+      </c>
+      <c r="G52" s="4">
+        <v>-6.03</v>
+      </c>
+      <c r="H52" s="4">
+        <v>6</v>
+      </c>
+      <c r="I52" s="4">
+        <v>8</v>
+      </c>
+      <c r="J52" s="4">
+        <v>14</v>
+      </c>
+      <c r="K52" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="L52" s="5">
+        <v>0.226018518518519</v>
+      </c>
+      <c r="M52" s="4">
+        <v>5079.9</v>
+      </c>
+      <c r="N52" s="4">
+        <v>667.87</v>
+      </c>
+      <c r="O52" s="4">
+        <v>7.46</v>
+      </c>
+      <c r="P52" s="4">
+        <v>74.57</v>
+      </c>
+      <c r="Q52" s="4">
+        <v>15.66</v>
+      </c>
+      <c r="R52" s="4">
+        <v>2.05</v>
+      </c>
+      <c r="S52" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="T52" s="4">
+        <v>0</v>
+      </c>
+      <c r="U52" s="4">
+        <v>0</v>
+      </c>
+      <c r="V52" s="4">
+        <v>0</v>
+      </c>
+      <c r="W52" s="4">
+        <v>0</v>
+      </c>
+      <c r="X52" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="4">
+        <v>423.93</v>
+      </c>
+      <c r="AG52" s="4">
+        <v>625.2</v>
+      </c>
+      <c r="AH52" s="4">
+        <v>431.59</v>
+      </c>
+      <c r="AI52" s="4">
+        <v>2608.66</v>
+      </c>
+      <c r="AJ52" s="4">
+        <v>1248.45</v>
+      </c>
+      <c r="AK52" s="4">
+        <v>493.67</v>
+      </c>
+      <c r="AL52" s="4">
+        <v>252.17</v>
+      </c>
+      <c r="AM52" s="4">
+        <v>45.37</v>
+      </c>
+      <c r="AN52" s="4">
+        <v>3</v>
+      </c>
+      <c r="AO52" s="4">
+        <v>0.14</v>
+      </c>
+      <c r="AP52" s="4">
+        <v>297.54</v>
+      </c>
+      <c r="AQ52" s="4">
+        <v>19</v>
+      </c>
+      <c r="AR52" s="4">
+        <v>0.91</v>
+      </c>
+      <c r="AS52" s="4">
+        <v>107</v>
+      </c>
+      <c r="AT52" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU52" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV52" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW52" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX52" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:50">
+      <c r="A53" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53" t="s">
+        <v>85</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E53" s="4">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4">
+        <v>3.93</v>
+      </c>
+      <c r="G53" s="4">
+        <v>-4.11</v>
+      </c>
+      <c r="H53" s="4">
+        <v>7</v>
+      </c>
+      <c r="I53" s="4">
+        <v>8</v>
+      </c>
+      <c r="J53" s="4">
+        <v>15</v>
+      </c>
+      <c r="K53" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="L53" s="5">
+        <v>0.226018518518519</v>
+      </c>
+      <c r="M53" s="4">
+        <v>4057.08</v>
+      </c>
+      <c r="N53" s="4">
+        <v>445.51</v>
+      </c>
+      <c r="O53" s="4">
+        <v>7.08</v>
+      </c>
+      <c r="P53" s="4">
+        <v>70.8</v>
+      </c>
+      <c r="Q53" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="R53" s="4">
+        <v>1.37</v>
+      </c>
+      <c r="S53" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="T53" s="4">
+        <v>0</v>
+      </c>
+      <c r="U53" s="4">
+        <v>0</v>
+      </c>
+      <c r="V53" s="4">
+        <v>0</v>
+      </c>
+      <c r="W53" s="4">
+        <v>0</v>
+      </c>
+      <c r="X53" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="4">
+        <v>338.79</v>
+      </c>
+      <c r="AG53" s="4">
+        <v>393.36</v>
+      </c>
+      <c r="AH53" s="4">
+        <v>383.08</v>
+      </c>
+      <c r="AI53" s="4">
+        <v>2169.55</v>
+      </c>
+      <c r="AJ53" s="4">
+        <v>1061.43</v>
+      </c>
+      <c r="AK53" s="4">
+        <v>235.01</v>
+      </c>
+      <c r="AL53" s="4">
+        <v>204.14</v>
+      </c>
+      <c r="AM53" s="4">
+        <v>3.36</v>
+      </c>
+      <c r="AN53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="AP53" s="4">
+        <v>207.5</v>
+      </c>
+      <c r="AQ53" s="4">
+        <v>16</v>
+      </c>
+      <c r="AR53" s="4">
+        <v>0.64</v>
+      </c>
+      <c r="AS53" s="4">
+        <v>26</v>
+      </c>
+      <c r="AT53" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU53" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV53" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW53" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX53" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54" spans="1:50">
+      <c r="A54" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" t="s">
+        <v>85</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E54" s="4">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4">
+        <v>3.91</v>
+      </c>
+      <c r="G54" s="4">
+        <v>-4.83</v>
+      </c>
+      <c r="H54" s="4">
+        <v>12</v>
+      </c>
+      <c r="I54" s="4">
+        <v>14</v>
+      </c>
+      <c r="J54" s="4">
+        <v>26</v>
+      </c>
+      <c r="K54" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="L54" s="5">
+        <v>0.226018518518519</v>
+      </c>
+      <c r="M54" s="4">
+        <v>4441.83</v>
+      </c>
+      <c r="N54" s="4">
+        <v>570.56</v>
+      </c>
+      <c r="O54" s="4">
+        <v>7.31</v>
+      </c>
+      <c r="P54" s="4">
+        <v>73.12</v>
+      </c>
+      <c r="Q54" s="4">
+        <v>13.72</v>
+      </c>
+      <c r="R54" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="S54" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="T54" s="4">
+        <v>0</v>
+      </c>
+      <c r="U54" s="4">
+        <v>0</v>
+      </c>
+      <c r="V54" s="4">
+        <v>0</v>
+      </c>
+      <c r="W54" s="4">
+        <v>0</v>
+      </c>
+      <c r="X54" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="4">
+        <v>376.61</v>
+      </c>
+      <c r="AG54" s="4">
+        <v>531.22</v>
+      </c>
+      <c r="AH54" s="4">
+        <v>321.25</v>
+      </c>
+      <c r="AI54" s="4">
+        <v>2408.28</v>
+      </c>
+      <c r="AJ54" s="4">
+        <v>1141.68</v>
+      </c>
+      <c r="AK54" s="4">
+        <v>332.4</v>
+      </c>
+      <c r="AL54" s="4">
+        <v>216.72</v>
+      </c>
+      <c r="AM54" s="4">
+        <v>21.13</v>
+      </c>
+      <c r="AN54" s="4">
+        <v>1</v>
+      </c>
+      <c r="AO54" s="4">
+        <v>0.06</v>
+      </c>
+      <c r="AP54" s="4">
+        <v>237.85</v>
+      </c>
+      <c r="AQ54" s="4">
+        <v>14</v>
+      </c>
+      <c r="AR54" s="4">
+        <v>0.73</v>
+      </c>
+      <c r="AS54" s="4">
+        <v>95</v>
+      </c>
+      <c r="AT54" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU54" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV54" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW54" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX54" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="1:50">
+      <c r="A55" t="s">
+        <v>97</v>
+      </c>
+      <c r="B55" t="s">
+        <v>85</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E55" s="4">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4">
+        <v>3.71</v>
+      </c>
+      <c r="G55" s="4">
+        <v>-5.06</v>
+      </c>
+      <c r="H55" s="4">
+        <v>6</v>
+      </c>
+      <c r="I55" s="4">
+        <v>11</v>
+      </c>
+      <c r="J55" s="4">
+        <v>17</v>
+      </c>
+      <c r="K55" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="L55" s="5">
+        <v>0.226018518518519</v>
+      </c>
+      <c r="M55" s="4">
+        <v>4649.95</v>
+      </c>
+      <c r="N55" s="4">
+        <v>574.08</v>
+      </c>
+      <c r="O55" s="4">
+        <v>7.43</v>
+      </c>
+      <c r="P55" s="4">
+        <v>74.29</v>
+      </c>
+      <c r="Q55" s="4">
+        <v>14.36</v>
+      </c>
+      <c r="R55" s="4">
+        <v>1.76</v>
+      </c>
+      <c r="S55" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="T55" s="4">
+        <v>0</v>
+      </c>
+      <c r="U55" s="4">
+        <v>0</v>
+      </c>
+      <c r="V55" s="4">
+        <v>0</v>
+      </c>
+      <c r="W55" s="4">
+        <v>0</v>
+      </c>
+      <c r="X55" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF55" s="4">
+        <v>386.35</v>
+      </c>
+      <c r="AG55" s="4">
+        <v>525.89</v>
+      </c>
+      <c r="AH55" s="4">
+        <v>375.96</v>
+      </c>
+      <c r="AI55" s="4">
+        <v>2456.33</v>
+      </c>
+      <c r="AJ55" s="4">
+        <v>1185.91</v>
+      </c>
+      <c r="AK55" s="4">
+        <v>415.67</v>
+      </c>
+      <c r="AL55" s="4">
+        <v>201.39</v>
+      </c>
+      <c r="AM55" s="4">
+        <v>14.69</v>
+      </c>
+      <c r="AN55" s="4">
+        <v>1</v>
+      </c>
+      <c r="AO55" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="AP55" s="4">
+        <v>216.08</v>
+      </c>
+      <c r="AQ55" s="4">
+        <v>13</v>
+      </c>
+      <c r="AR55" s="4">
+        <v>0.66</v>
+      </c>
+      <c r="AS55" s="4">
+        <v>58</v>
+      </c>
+      <c r="AT55" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU55" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV55" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW55" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX55" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="56" spans="1:50">
+      <c r="A56" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" t="s">
+        <v>85</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E56" s="4">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4">
+        <v>3.65</v>
+      </c>
+      <c r="G56" s="4">
+        <v>-4.51</v>
+      </c>
+      <c r="H56" s="4">
+        <v>12</v>
+      </c>
+      <c r="I56" s="4">
+        <v>15</v>
+      </c>
+      <c r="J56" s="4">
+        <v>27</v>
+      </c>
+      <c r="K56" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="L56" s="5">
+        <v>0.226145833333333</v>
+      </c>
+      <c r="M56" s="4">
+        <v>4522.81</v>
+      </c>
+      <c r="N56" s="4">
+        <v>523.36</v>
+      </c>
+      <c r="O56" s="4">
+        <v>7.13</v>
+      </c>
+      <c r="P56" s="4">
+        <v>71.28</v>
+      </c>
+      <c r="Q56" s="4">
+        <v>13.95</v>
+      </c>
+      <c r="R56" s="4">
+        <v>1.61</v>
+      </c>
+      <c r="S56" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="T56" s="4">
+        <v>0</v>
+      </c>
+      <c r="U56" s="4">
+        <v>0</v>
+      </c>
+      <c r="V56" s="4">
+        <v>0</v>
+      </c>
+      <c r="W56" s="4">
+        <v>0</v>
+      </c>
+      <c r="X56" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="4">
+        <v>384.82</v>
+      </c>
+      <c r="AG56" s="4">
+        <v>518.89</v>
+      </c>
+      <c r="AH56" s="4">
+        <v>407.97</v>
+      </c>
+      <c r="AI56" s="4">
+        <v>2283.01</v>
+      </c>
+      <c r="AJ56" s="4">
+        <v>1289.37</v>
+      </c>
+      <c r="AK56" s="4">
+        <v>401.06</v>
+      </c>
+      <c r="AL56" s="4">
+        <v>137.38</v>
+      </c>
+      <c r="AM56" s="4">
+        <v>3.11</v>
+      </c>
+      <c r="AN56" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO56" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="AP56" s="4">
+        <v>140.49</v>
+      </c>
+      <c r="AQ56" s="4">
+        <v>12</v>
+      </c>
+      <c r="AR56" s="4">
+        <v>0.43</v>
+      </c>
+      <c r="AS56" s="4">
+        <v>21</v>
+      </c>
+      <c r="AT56" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU56" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV56" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW56" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX56" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="57" spans="1:50">
+      <c r="A57" t="s">
+        <v>97</v>
+      </c>
+      <c r="B57" t="s">
+        <v>85</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E57" s="4">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4">
+        <v>3.69</v>
+      </c>
+      <c r="G57" s="4">
+        <v>-4.72</v>
+      </c>
+      <c r="H57" s="4">
+        <v>14</v>
+      </c>
+      <c r="I57" s="4">
+        <v>17</v>
+      </c>
+      <c r="J57" s="4">
+        <v>31</v>
+      </c>
+      <c r="K57" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="L57" s="5">
+        <v>0.194849537037037</v>
+      </c>
+      <c r="M57" s="4">
+        <v>6383.57</v>
+      </c>
+      <c r="N57" s="4">
+        <v>864.77</v>
+      </c>
+      <c r="O57" s="4">
+        <v>7.7</v>
+      </c>
+      <c r="P57" s="4">
+        <v>76.97</v>
+      </c>
+      <c r="Q57" s="4">
+        <v>22.89</v>
+      </c>
+      <c r="R57" s="4">
+        <v>3.08</v>
+      </c>
+      <c r="S57" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="T57" s="4">
+        <v>0</v>
+      </c>
+      <c r="U57" s="4">
+        <v>0</v>
+      </c>
+      <c r="V57" s="4">
+        <v>0</v>
+      </c>
+      <c r="W57" s="4">
+        <v>0</v>
+      </c>
+      <c r="X57" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="4">
+        <v>548.16</v>
+      </c>
+      <c r="AG57" s="4">
+        <v>972.08</v>
+      </c>
+      <c r="AH57" s="4">
+        <v>319.35</v>
+      </c>
+      <c r="AI57" s="4">
+        <v>2743.37</v>
+      </c>
+      <c r="AJ57" s="4">
+        <v>2058.68</v>
+      </c>
+      <c r="AK57" s="4">
+        <v>773.18</v>
+      </c>
+      <c r="AL57" s="4">
+        <v>310.72</v>
+      </c>
+      <c r="AM57" s="4">
+        <v>177.92</v>
+      </c>
+      <c r="AN57" s="4">
+        <v>7</v>
+      </c>
+      <c r="AO57" s="4">
+        <v>0.63</v>
+      </c>
+      <c r="AP57" s="4">
+        <v>488.64</v>
+      </c>
+      <c r="AQ57" s="4">
+        <v>21</v>
+      </c>
+      <c r="AR57" s="4">
+        <v>1.74</v>
+      </c>
+      <c r="AS57" s="4">
+        <v>48</v>
+      </c>
+      <c r="AT57" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU57" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV57" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW57" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX57" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:50">
+      <c r="A58" t="s">
+        <v>97</v>
+      </c>
+      <c r="B58" t="s">
+        <v>85</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E58" s="4">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4">
+        <v>3.96</v>
+      </c>
+      <c r="G58" s="4">
+        <v>-4.77</v>
+      </c>
+      <c r="H58" s="4">
+        <v>11</v>
+      </c>
+      <c r="I58" s="4">
+        <v>17</v>
+      </c>
+      <c r="J58" s="4">
+        <v>28</v>
+      </c>
+      <c r="K58" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="L58" s="5">
+        <v>0.226145833333333</v>
+      </c>
+      <c r="M58" s="4">
+        <v>5661.65</v>
+      </c>
+      <c r="N58" s="4">
+        <v>646.15</v>
+      </c>
+      <c r="O58" s="4">
+        <v>7.88</v>
+      </c>
+      <c r="P58" s="4">
+        <v>78.78</v>
+      </c>
+      <c r="Q58" s="4">
+        <v>17.49</v>
+      </c>
+      <c r="R58" s="4">
+        <v>1.98</v>
+      </c>
+      <c r="S58" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="T58" s="4">
+        <v>0</v>
+      </c>
+      <c r="U58" s="4">
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <v>0</v>
+      </c>
+      <c r="W58" s="4">
+        <v>0</v>
+      </c>
+      <c r="X58" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="4">
+        <v>488.36</v>
+      </c>
+      <c r="AG58" s="4">
+        <v>855.23</v>
+      </c>
+      <c r="AH58" s="4">
+        <v>221.25</v>
+      </c>
+      <c r="AI58" s="4">
+        <v>2987.88</v>
+      </c>
+      <c r="AJ58" s="4">
+        <v>1434.12</v>
+      </c>
+      <c r="AK58" s="4">
+        <v>479.76</v>
+      </c>
+      <c r="AL58" s="4">
+        <v>350.87</v>
+      </c>
+      <c r="AM58" s="4">
+        <v>187.23</v>
+      </c>
+      <c r="AN58" s="4">
+        <v>9</v>
+      </c>
+      <c r="AO58" s="4">
+        <v>0.57</v>
+      </c>
+      <c r="AP58" s="4">
+        <v>538.1</v>
+      </c>
+      <c r="AQ58" s="4">
+        <v>26</v>
+      </c>
+      <c r="AR58" s="4">
+        <v>1.65</v>
+      </c>
+      <c r="AS58" s="4">
+        <v>72</v>
+      </c>
+      <c r="AT58" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU58" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV58" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW58" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX58" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:50">
+      <c r="A59" t="s">
+        <v>97</v>
+      </c>
+      <c r="B59" t="s">
+        <v>85</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E59" s="4">
+        <v>0</v>
+      </c>
+      <c r="F59" s="4">
+        <v>3.85</v>
+      </c>
+      <c r="G59" s="4">
+        <v>-3.72</v>
+      </c>
+      <c r="H59" s="4">
+        <v>9</v>
+      </c>
+      <c r="I59" s="4">
+        <v>20</v>
+      </c>
+      <c r="J59" s="4">
+        <v>29</v>
+      </c>
+      <c r="K59" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="L59" s="5">
+        <v>0.179421296296296</v>
+      </c>
+      <c r="M59" s="4">
+        <v>6100.25</v>
+      </c>
+      <c r="N59" s="4">
+        <v>836.39</v>
+      </c>
+      <c r="O59" s="4">
+        <v>6.94</v>
+      </c>
+      <c r="P59" s="4">
+        <v>69.45</v>
+      </c>
+      <c r="Q59" s="4">
+        <v>23.91</v>
+      </c>
+      <c r="R59" s="4">
+        <v>3.24</v>
+      </c>
+      <c r="S59" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="T59" s="4">
+        <v>0</v>
+      </c>
+      <c r="U59" s="4">
+        <v>0</v>
+      </c>
+      <c r="V59" s="4">
+        <v>0</v>
+      </c>
+      <c r="W59" s="4">
+        <v>0</v>
+      </c>
+      <c r="X59" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="4">
+        <v>522.39</v>
+      </c>
+      <c r="AG59" s="4">
+        <v>957.75</v>
+      </c>
+      <c r="AH59" s="4">
+        <v>292.41</v>
+      </c>
+      <c r="AI59" s="4">
+        <v>3158.32</v>
+      </c>
+      <c r="AJ59" s="4">
+        <v>1339.76</v>
+      </c>
+      <c r="AK59" s="4">
+        <v>856.65</v>
+      </c>
+      <c r="AL59" s="4">
+        <v>452.78</v>
+      </c>
+      <c r="AM59" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN59" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO59" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP59" s="4">
+        <v>452.78</v>
+      </c>
+      <c r="AQ59" s="4">
+        <v>21</v>
+      </c>
+      <c r="AR59" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="AS59" s="4">
+        <v>369</v>
+      </c>
+      <c r="AT59" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU59" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV59" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW59" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX59" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:50">
+      <c r="A60" t="s">
+        <v>103</v>
+      </c>
+      <c r="B60" t="s">
+        <v>51</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E60" s="4">
+        <v>0</v>
+      </c>
+      <c r="F60" s="4">
+        <v>3.48</v>
+      </c>
+      <c r="G60" s="4">
+        <v>-2.76</v>
+      </c>
+      <c r="H60" s="4">
+        <v>1</v>
+      </c>
+      <c r="I60" s="4">
+        <v>0</v>
+      </c>
+      <c r="J60" s="4">
+        <v>1</v>
+      </c>
+      <c r="K60" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="L60" s="5">
+        <v>0.0925231481481481</v>
+      </c>
+      <c r="M60" s="4">
+        <v>2555.64</v>
+      </c>
+      <c r="N60" s="4">
+        <v>300.61</v>
+      </c>
+      <c r="O60" s="4">
+        <v>26.892</v>
+      </c>
+      <c r="P60" s="4">
+        <v>74.69</v>
+      </c>
+      <c r="Q60" s="4">
+        <v>19.66</v>
+      </c>
+      <c r="R60" s="4">
+        <v>2.26</v>
+      </c>
+      <c r="S60" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="T60" s="4">
+        <v>0</v>
+      </c>
+      <c r="U60" s="4">
+        <v>0</v>
+      </c>
+      <c r="V60" s="4">
+        <v>0</v>
+      </c>
+      <c r="W60" s="4">
+        <v>0</v>
+      </c>
+      <c r="X60" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="4">
+        <v>204.98</v>
+      </c>
+      <c r="AG60" s="4">
+        <v>143.8</v>
+      </c>
+      <c r="AH60" s="4">
+        <v>386.02</v>
+      </c>
+      <c r="AI60" s="4">
+        <v>1547.4</v>
+      </c>
+      <c r="AJ60" s="4">
+        <v>481.72</v>
+      </c>
+      <c r="AK60" s="4">
+        <v>96.87</v>
+      </c>
+      <c r="AL60" s="4">
+        <v>23.91</v>
+      </c>
+      <c r="AM60" s="4">
+        <v>18.43</v>
+      </c>
+      <c r="AN60" s="4">
+        <v>1</v>
+      </c>
+      <c r="AO60" s="4">
+        <v>0.14</v>
+      </c>
+      <c r="AP60" s="4">
+        <v>42.34</v>
+      </c>
+      <c r="AQ60" s="4">
+        <v>2</v>
+      </c>
+      <c r="AR60" s="4">
+        <v>0.32</v>
+      </c>
+      <c r="AS60" s="4">
+        <v>11</v>
+      </c>
+      <c r="AT60" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU60" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV60" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AW60" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX60" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:50">
+      <c r="A61" t="s">
+        <v>103</v>
+      </c>
+      <c r="B61" t="s">
+        <v>64</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E61" s="4">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4">
+        <v>4.26</v>
+      </c>
+      <c r="G61" s="4">
+        <v>-4.66</v>
+      </c>
+      <c r="H61" s="4">
+        <v>15</v>
+      </c>
+      <c r="I61" s="4">
+        <v>22</v>
+      </c>
+      <c r="J61" s="4">
+        <v>37</v>
+      </c>
+      <c r="K61" s="4">
+        <v>0.28</v>
+      </c>
+      <c r="L61" s="5">
+        <v>0.0921527777777778</v>
+      </c>
+      <c r="M61" s="4">
+        <v>5029.25</v>
+      </c>
+      <c r="N61" s="4">
+        <v>490.07</v>
+      </c>
+      <c r="O61" s="4">
+        <v>28.764</v>
+      </c>
+      <c r="P61" s="4">
+        <v>79.89</v>
+      </c>
+      <c r="Q61" s="4">
+        <v>38.98</v>
+      </c>
+      <c r="R61" s="4">
+        <v>3.69</v>
+      </c>
+      <c r="S61" s="4">
+        <v>0.06</v>
+      </c>
+      <c r="T61" s="4">
+        <v>0</v>
+      </c>
+      <c r="U61" s="4">
+        <v>0</v>
+      </c>
+      <c r="V61" s="4">
+        <v>0</v>
+      </c>
+      <c r="W61" s="4">
+        <v>0</v>
+      </c>
+      <c r="X61" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="4">
+        <v>436.26</v>
+      </c>
+      <c r="AG61" s="4">
+        <v>729.18</v>
+      </c>
+      <c r="AH61" s="4">
+        <v>259.56</v>
+      </c>
+      <c r="AI61" s="4">
+        <v>2251.59</v>
+      </c>
+      <c r="AJ61" s="4">
+        <v>1596.83</v>
+      </c>
+      <c r="AK61" s="4">
+        <v>522.18</v>
+      </c>
+      <c r="AL61" s="4">
+        <v>297.17</v>
+      </c>
+      <c r="AM61" s="4">
+        <v>101.92</v>
+      </c>
+      <c r="AN61" s="4">
+        <v>5</v>
+      </c>
+      <c r="AO61" s="4">
+        <v>0.77</v>
+      </c>
+      <c r="AP61" s="4">
+        <v>399.09</v>
+      </c>
+      <c r="AQ61" s="4">
+        <v>21</v>
+      </c>
+      <c r="AR61" s="4">
+        <v>3.01</v>
+      </c>
+      <c r="AS61" s="4">
+        <v>11</v>
+      </c>
+      <c r="AT61" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU61" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="AV61" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW61" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX61" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:50">
+      <c r="A62" t="s">
+        <v>103</v>
+      </c>
+      <c r="B62" t="s">
+        <v>51</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E62" s="4">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="G62" s="4">
+        <v>-3.79</v>
+      </c>
+      <c r="H62" s="4">
+        <v>5</v>
+      </c>
+      <c r="I62" s="4">
+        <v>5</v>
+      </c>
+      <c r="J62" s="4">
+        <v>10</v>
+      </c>
+      <c r="K62" s="4">
+        <v>0.14</v>
+      </c>
+      <c r="L62" s="5">
+        <v>0.0488078703703704</v>
+      </c>
+      <c r="M62" s="4">
+        <v>2790.19</v>
+      </c>
+      <c r="N62" s="4">
+        <v>257.87</v>
+      </c>
+      <c r="O62" s="4">
+        <v>26.424</v>
+      </c>
+      <c r="P62" s="4">
+        <v>73.4</v>
+      </c>
+      <c r="Q62" s="4">
+        <v>40.84</v>
+      </c>
+      <c r="R62" s="4">
+        <v>3.67</v>
+      </c>
+      <c r="S62" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="T62" s="4">
+        <v>0</v>
+      </c>
+      <c r="U62" s="4">
+        <v>0</v>
+      </c>
+      <c r="V62" s="4">
+        <v>0</v>
+      </c>
+      <c r="W62" s="4">
+        <v>0</v>
+      </c>
+      <c r="X62" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="4">
+        <v>225.33</v>
+      </c>
+      <c r="AG62" s="4">
+        <v>244.77</v>
+      </c>
+      <c r="AH62" s="4">
+        <v>398.88</v>
+      </c>
+      <c r="AI62" s="4">
+        <v>1721.61</v>
+      </c>
+      <c r="AJ62" s="4">
+        <v>379.18</v>
+      </c>
+      <c r="AK62" s="4">
+        <v>169.08</v>
+      </c>
+      <c r="AL62" s="4">
+        <v>101.29</v>
+      </c>
+      <c r="AM62" s="4">
+        <v>19.79</v>
+      </c>
+      <c r="AN62" s="4">
+        <v>2</v>
+      </c>
+      <c r="AO62" s="4">
+        <v>0.28</v>
+      </c>
+      <c r="AP62" s="4">
+        <v>121.08</v>
+      </c>
+      <c r="AQ62" s="4">
+        <v>7</v>
+      </c>
+      <c r="AR62" s="4">
+        <v>1.72</v>
+      </c>
+      <c r="AS62" s="4">
+        <v>11</v>
+      </c>
+      <c r="AT62" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU62" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV62" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AW62" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX62" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="1:50">
+      <c r="A63" t="s">
+        <v>103</v>
+      </c>
+      <c r="B63" t="s">
+        <v>51</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E63" s="4">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4">
+        <v>3.25</v>
+      </c>
+      <c r="G63" s="4">
+        <v>-4.45</v>
+      </c>
+      <c r="H63" s="4">
+        <v>3</v>
+      </c>
+      <c r="I63" s="4">
+        <v>2</v>
+      </c>
+      <c r="J63" s="4">
+        <v>5</v>
+      </c>
+      <c r="K63" s="4">
+        <v>0.07</v>
+      </c>
+      <c r="L63" s="5">
+        <v>0.0489467592592593</v>
+      </c>
+      <c r="M63" s="4">
+        <v>2271.51</v>
+      </c>
+      <c r="N63" s="4">
+        <v>201.71</v>
+      </c>
+      <c r="O63" s="4">
+        <v>23.328</v>
+      </c>
+      <c r="P63" s="4">
+        <v>64.77</v>
+      </c>
+      <c r="Q63" s="4">
+        <v>33.07</v>
+      </c>
+      <c r="R63" s="4">
+        <v>2.86</v>
+      </c>
+      <c r="S63" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="T63" s="4">
+        <v>0</v>
+      </c>
+      <c r="U63" s="4">
+        <v>0</v>
+      </c>
+      <c r="V63" s="4">
+        <v>0</v>
+      </c>
+      <c r="W63" s="4">
+        <v>0</v>
+      </c>
+      <c r="X63" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="4">
+        <v>176.2</v>
+      </c>
+      <c r="AG63" s="4">
+        <v>87.73</v>
+      </c>
+      <c r="AH63" s="4">
+        <v>370.52</v>
+      </c>
+      <c r="AI63" s="4">
+        <v>1554.06</v>
+      </c>
+      <c r="AJ63" s="4">
+        <v>241.83</v>
+      </c>
+      <c r="AK63" s="4">
+        <v>86.84</v>
+      </c>
+      <c r="AL63" s="4">
+        <v>18.26</v>
+      </c>
+      <c r="AM63" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN63" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="4">
+        <v>18.26</v>
+      </c>
+      <c r="AQ63" s="4">
+        <v>1</v>
+      </c>
+      <c r="AR63" s="4">
+        <v>0.26</v>
+      </c>
+      <c r="AS63" s="4">
+        <v>1</v>
+      </c>
+      <c r="AT63" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU63" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV63" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AW63" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX63" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:50">
+      <c r="A64" t="s">
+        <v>103</v>
+      </c>
+      <c r="B64" t="s">
+        <v>51</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E64" s="4">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4">
+        <v>3.63</v>
+      </c>
+      <c r="G64" s="4">
+        <v>-4.21</v>
+      </c>
+      <c r="H64" s="4">
+        <v>16</v>
+      </c>
+      <c r="I64" s="4">
+        <v>13</v>
+      </c>
+      <c r="J64" s="4">
+        <v>29</v>
+      </c>
+      <c r="K64" s="4">
+        <v>0.22</v>
+      </c>
+      <c r="L64" s="5">
+        <v>0.0921527777777778</v>
+      </c>
+      <c r="M64" s="4">
+        <v>3316.85</v>
+      </c>
+      <c r="N64" s="4">
+        <v>352.9</v>
+      </c>
+      <c r="O64" s="4">
+        <v>23.22</v>
+      </c>
+      <c r="P64" s="4">
+        <v>64.49</v>
+      </c>
+      <c r="Q64" s="4">
+        <v>25.01</v>
+      </c>
+      <c r="R64" s="4">
+        <v>2.66</v>
+      </c>
+      <c r="S64" s="4">
+        <v>0.06</v>
+      </c>
+      <c r="T64" s="4">
+        <v>0</v>
+      </c>
+      <c r="U64" s="4">
+        <v>0</v>
+      </c>
+      <c r="V64" s="4">
+        <v>0</v>
+      </c>
+      <c r="W64" s="4">
+        <v>0</v>
+      </c>
+      <c r="X64" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="4">
+        <v>289.77</v>
+      </c>
+      <c r="AG64" s="4">
+        <v>460.95</v>
+      </c>
+      <c r="AH64" s="4">
+        <v>321.26</v>
+      </c>
+      <c r="AI64" s="4">
+        <v>1678.49</v>
+      </c>
+      <c r="AJ64" s="4">
+        <v>634.49</v>
+      </c>
+      <c r="AK64" s="4">
+        <v>531.1</v>
+      </c>
+      <c r="AL64" s="4">
+        <v>150.56</v>
+      </c>
+      <c r="AM64" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="4">
+        <v>150.56</v>
+      </c>
+      <c r="AQ64" s="4">
+        <v>7</v>
+      </c>
+      <c r="AR64" s="4">
+        <v>1.13</v>
+      </c>
+      <c r="AS64" s="4">
+        <v>7</v>
+      </c>
+      <c r="AT64" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU64" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV64" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AW64" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX64" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65" spans="1:50">
+      <c r="A65" t="s">
+        <v>103</v>
+      </c>
+      <c r="B65" t="s">
+        <v>51</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E65" s="4">
+        <v>0</v>
+      </c>
+      <c r="F65" s="4">
+        <v>3.38</v>
+      </c>
+      <c r="G65" s="4">
+        <v>-4.58</v>
+      </c>
+      <c r="H65" s="4">
+        <v>10</v>
+      </c>
+      <c r="I65" s="4">
+        <v>12</v>
+      </c>
+      <c r="J65" s="4">
+        <v>22</v>
+      </c>
+      <c r="K65" s="4">
+        <v>0.17</v>
+      </c>
+      <c r="L65" s="5">
+        <v>0.0925231481481481</v>
+      </c>
+      <c r="M65" s="4">
+        <v>3811.25</v>
+      </c>
+      <c r="N65" s="4">
+        <v>496.47</v>
+      </c>
+      <c r="O65" s="4">
+        <v>23.76</v>
+      </c>
+      <c r="P65" s="4">
+        <v>66.02</v>
+      </c>
+      <c r="Q65" s="4">
+        <v>28.7</v>
+      </c>
+      <c r="R65" s="4">
+        <v>3.73</v>
+      </c>
+      <c r="S65" s="4">
+        <v>0.07</v>
+      </c>
+      <c r="T65" s="4">
+        <v>0</v>
+      </c>
+      <c r="U65" s="4">
+        <v>0</v>
+      </c>
+      <c r="V65" s="4">
+        <v>0</v>
+      </c>
+      <c r="W65" s="4">
+        <v>0</v>
+      </c>
+      <c r="X65" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="4">
+        <v>329.92</v>
+      </c>
+      <c r="AG65" s="4">
+        <v>445.01</v>
+      </c>
+      <c r="AH65" s="4">
+        <v>335.89</v>
+      </c>
+      <c r="AI65" s="4">
+        <v>1821.66</v>
+      </c>
+      <c r="AJ65" s="4">
+        <v>972.53</v>
+      </c>
+      <c r="AK65" s="4">
+        <v>576.7</v>
+      </c>
+      <c r="AL65" s="4">
+        <v>104.35</v>
+      </c>
+      <c r="AM65" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="4">
+        <v>104.35</v>
+      </c>
+      <c r="AQ65" s="4">
+        <v>5</v>
+      </c>
+      <c r="AR65" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="AS65" s="4">
+        <v>59</v>
+      </c>
+      <c r="AT65" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU65" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV65" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AW65" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX65" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="66" spans="1:50">
+      <c r="A66" t="s">
+        <v>103</v>
+      </c>
+      <c r="B66" t="s">
+        <v>64</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E66" s="4">
+        <v>0</v>
+      </c>
+      <c r="F66" s="4">
+        <v>4.26</v>
+      </c>
+      <c r="G66" s="4">
+        <v>-4.44</v>
+      </c>
+      <c r="H66" s="4">
+        <v>14</v>
+      </c>
+      <c r="I66" s="4">
+        <v>16</v>
+      </c>
+      <c r="J66" s="4">
+        <v>30</v>
+      </c>
+      <c r="K66" s="4">
+        <v>0.23</v>
+      </c>
+      <c r="L66" s="5">
+        <v>0.0925231481481481</v>
+      </c>
+      <c r="M66" s="4">
+        <v>4721.58</v>
+      </c>
+      <c r="N66" s="4">
+        <v>474</v>
+      </c>
+      <c r="O66" s="4">
+        <v>29.124</v>
+      </c>
+      <c r="P66" s="4">
+        <v>80.9</v>
+      </c>
+      <c r="Q66" s="4">
+        <v>35.87</v>
+      </c>
+      <c r="R66" s="4">
+        <v>3.56</v>
+      </c>
+      <c r="S66" s="4">
+        <v>0.06</v>
+      </c>
+      <c r="T66" s="4">
+        <v>0</v>
+      </c>
+      <c r="U66" s="4">
+        <v>0</v>
+      </c>
+      <c r="V66" s="4">
+        <v>0</v>
+      </c>
+      <c r="W66" s="4">
+        <v>0</v>
+      </c>
+      <c r="X66" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF66" s="4">
+        <v>409.6</v>
+      </c>
+      <c r="AG66" s="4">
+        <v>721.17</v>
+      </c>
+      <c r="AH66" s="4">
+        <v>209.29</v>
+      </c>
+      <c r="AI66" s="4">
+        <v>1911.12</v>
+      </c>
+      <c r="AJ66" s="4">
+        <v>1538.02</v>
+      </c>
+      <c r="AK66" s="4">
+        <v>786.03</v>
+      </c>
+      <c r="AL66" s="4">
+        <v>227.03</v>
+      </c>
+      <c r="AM66" s="4">
+        <v>50.07</v>
+      </c>
+      <c r="AN66" s="4">
+        <v>3</v>
+      </c>
+      <c r="AO66" s="4">
+        <v>0.38</v>
+      </c>
+      <c r="AP66" s="4">
+        <v>277.1</v>
+      </c>
+      <c r="AQ66" s="4">
+        <v>18</v>
+      </c>
+      <c r="AR66" s="4">
+        <v>2.08</v>
+      </c>
+      <c r="AS66" s="4">
+        <v>17</v>
+      </c>
+      <c r="AT66" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU66" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="AV66" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW66" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX66" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="67" spans="1:50">
+      <c r="A67" t="s">
+        <v>103</v>
+      </c>
+      <c r="B67" t="s">
+        <v>51</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E67" s="4">
+        <v>0</v>
+      </c>
+      <c r="F67" s="4">
+        <v>2.3</v>
+      </c>
+      <c r="G67" s="4">
+        <v>-1.96</v>
+      </c>
+      <c r="H67" s="4">
+        <v>0</v>
+      </c>
+      <c r="I67" s="4">
+        <v>0</v>
+      </c>
+      <c r="J67" s="4">
+        <v>0</v>
+      </c>
+      <c r="K67" s="4">
+        <v>0</v>
+      </c>
+      <c r="L67" s="5">
+        <v>0.0921527777777778</v>
+      </c>
+      <c r="M67" s="4">
+        <v>1858.65</v>
+      </c>
+      <c r="N67" s="4">
+        <v>145.09</v>
+      </c>
+      <c r="O67" s="4">
+        <v>16.56</v>
+      </c>
+      <c r="P67" s="4">
+        <v>46.01</v>
+      </c>
+      <c r="Q67" s="4">
+        <v>14.13</v>
+      </c>
+      <c r="R67" s="4">
+        <v>1.09</v>
+      </c>
+      <c r="S67" s="4">
+        <v>0</v>
+      </c>
+      <c r="T67" s="4">
+        <v>0</v>
+      </c>
+      <c r="U67" s="4">
+        <v>0</v>
+      </c>
+      <c r="V67" s="4">
+        <v>0</v>
+      </c>
+      <c r="W67" s="4">
+        <v>0</v>
+      </c>
+      <c r="X67" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB67" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD67" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF67" s="4">
+        <v>113.17</v>
+      </c>
+      <c r="AG67" s="4">
+        <v>12.26</v>
+      </c>
+      <c r="AH67" s="4">
+        <v>325.21</v>
+      </c>
+      <c r="AI67" s="4">
+        <v>1360.88</v>
+      </c>
+      <c r="AJ67" s="4">
+        <v>164.74</v>
+      </c>
+      <c r="AK67" s="4">
+        <v>7.57</v>
+      </c>
+      <c r="AL67" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM67" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN67" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO67" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP67" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ67" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR67" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS67" s="4">
+        <v>2</v>
+      </c>
+      <c r="AT67" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU67" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV67" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AW67" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX67" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="68" spans="1:50">
+      <c r="A68" t="s">
+        <v>103</v>
+      </c>
+      <c r="B68" t="s">
+        <v>51</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E68" s="4">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4">
+        <v>3.94</v>
+      </c>
+      <c r="G68" s="4">
+        <v>-4.08</v>
+      </c>
+      <c r="H68" s="4">
+        <v>8</v>
+      </c>
+      <c r="I68" s="4">
+        <v>7</v>
+      </c>
+      <c r="J68" s="4">
+        <v>15</v>
+      </c>
+      <c r="K68" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="L68" s="5">
+        <v>0.0925231481481481</v>
+      </c>
+      <c r="M68" s="4">
+        <v>2990.94</v>
+      </c>
+      <c r="N68" s="4">
+        <v>252.34</v>
+      </c>
+      <c r="O68" s="4">
+        <v>23.616</v>
+      </c>
+      <c r="P68" s="4">
+        <v>65.57</v>
+      </c>
+      <c r="Q68" s="4">
+        <v>22.82</v>
+      </c>
+      <c r="R68" s="4">
+        <v>1.89</v>
+      </c>
+      <c r="S68" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="T68" s="4">
+        <v>0</v>
+      </c>
+      <c r="U68" s="4">
+        <v>0</v>
+      </c>
+      <c r="V68" s="4">
+        <v>0</v>
+      </c>
+      <c r="W68" s="4">
+        <v>0</v>
+      </c>
+      <c r="X68" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="4">
+        <v>661.01</v>
+      </c>
+      <c r="AG68" s="4">
+        <v>266.64</v>
+      </c>
+      <c r="AH68" s="4">
+        <v>321.81</v>
+      </c>
+      <c r="AI68" s="4">
+        <v>1876.7</v>
+      </c>
+      <c r="AJ68" s="4">
+        <v>449.9</v>
+      </c>
+      <c r="AK68" s="4">
+        <v>268.4</v>
+      </c>
+      <c r="AL68" s="4">
+        <v>73.01</v>
+      </c>
+      <c r="AM68" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN68" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="4">
+        <v>73.01</v>
+      </c>
+      <c r="AQ68" s="4">
+        <v>7</v>
+      </c>
+      <c r="AR68" s="4">
+        <v>0.55</v>
+      </c>
+      <c r="AS68" s="4">
+        <v>6</v>
+      </c>
+      <c r="AT68" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU68" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV68" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AW68" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX68" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="69" spans="1:50">
+      <c r="A69" t="s">
+        <v>103</v>
+      </c>
+      <c r="B69" t="s">
+        <v>51</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E69" s="4">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4">
+        <v>3.92</v>
+      </c>
+      <c r="G69" s="4">
+        <v>-3.46</v>
+      </c>
+      <c r="H69" s="4">
+        <v>7</v>
+      </c>
+      <c r="I69" s="4">
+        <v>2</v>
+      </c>
+      <c r="J69" s="4">
+        <v>9</v>
+      </c>
+      <c r="K69" s="4">
+        <v>0.07</v>
+      </c>
+      <c r="L69" s="5">
+        <v>0.0921527777777778</v>
+      </c>
+      <c r="M69" s="4">
+        <v>3036.4</v>
+      </c>
+      <c r="N69" s="4">
+        <v>394.57</v>
+      </c>
+      <c r="O69" s="4">
+        <v>21.636</v>
+      </c>
+      <c r="P69" s="4">
+        <v>60.08</v>
+      </c>
+      <c r="Q69" s="4">
+        <v>23.34</v>
+      </c>
+      <c r="R69" s="4">
+        <v>2.97</v>
+      </c>
+      <c r="S69" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="T69" s="4">
+        <v>0</v>
+      </c>
+      <c r="U69" s="4">
+        <v>0</v>
+      </c>
+      <c r="V69" s="4">
+        <v>0</v>
+      </c>
+      <c r="W69" s="4">
+        <v>0</v>
+      </c>
+      <c r="X69" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="4">
+        <v>170.46</v>
+      </c>
+      <c r="AG69" s="4">
+        <v>241.14</v>
+      </c>
+      <c r="AH69" s="4">
+        <v>754.6</v>
+      </c>
+      <c r="AI69" s="4">
+        <v>1455.98</v>
+      </c>
+      <c r="AJ69" s="4">
+        <v>559.68</v>
+      </c>
+      <c r="AK69" s="4">
+        <v>248.92</v>
+      </c>
+      <c r="AL69" s="4">
+        <v>14.89</v>
+      </c>
+      <c r="AM69" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN69" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="4">
+        <v>14.89</v>
+      </c>
+      <c r="AQ69" s="4">
+        <v>2</v>
+      </c>
+      <c r="AR69" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="AS69" s="4">
+        <v>21</v>
+      </c>
+      <c r="AT69" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU69" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV69" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AW69" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX69" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="70" spans="1:50">
+      <c r="A70" t="s">
+        <v>103</v>
+      </c>
+      <c r="B70" t="s">
+        <v>51</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E70" s="4">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4">
+        <v>3.32</v>
+      </c>
+      <c r="G70" s="4">
+        <v>-4.12</v>
+      </c>
+      <c r="H70" s="4">
+        <v>1</v>
+      </c>
+      <c r="I70" s="4">
+        <v>1</v>
+      </c>
+      <c r="J70" s="4">
+        <v>2</v>
+      </c>
+      <c r="K70" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="L70" s="5">
+        <v>0.0488078703703704</v>
+      </c>
+      <c r="M70" s="4">
+        <v>2976.68</v>
+      </c>
+      <c r="N70" s="4">
+        <v>292.86</v>
+      </c>
+      <c r="O70" s="4">
+        <v>21.06</v>
+      </c>
+      <c r="P70" s="4">
+        <v>58.53</v>
+      </c>
+      <c r="Q70" s="4">
+        <v>43.4</v>
+      </c>
+      <c r="R70" s="4">
+        <v>4.17</v>
+      </c>
+      <c r="S70" s="4">
+        <v>0.06</v>
+      </c>
+      <c r="T70" s="4">
+        <v>0</v>
+      </c>
+      <c r="U70" s="4">
+        <v>0</v>
+      </c>
+      <c r="V70" s="4">
+        <v>0</v>
+      </c>
+      <c r="W70" s="4">
+        <v>0</v>
+      </c>
+      <c r="X70" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="4">
+        <v>242.87</v>
+      </c>
+      <c r="AG70" s="4">
+        <v>232.07</v>
+      </c>
+      <c r="AH70" s="4">
+        <v>326.74</v>
+      </c>
+      <c r="AI70" s="4">
+        <v>1484.93</v>
+      </c>
+      <c r="AJ70" s="4">
+        <v>607.89</v>
+      </c>
+      <c r="AK70" s="4">
+        <v>553.03</v>
+      </c>
+      <c r="AL70" s="4">
+        <v>4.08</v>
+      </c>
+      <c r="AM70" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="4">
+        <v>4.08</v>
+      </c>
+      <c r="AQ70" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR70" s="4">
+        <v>0.06</v>
+      </c>
+      <c r="AS70" s="4">
+        <v>2</v>
+      </c>
+      <c r="AT70" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU70" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV70" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AW70" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX70" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="71" spans="1:50">
+      <c r="A71" t="s">
+        <v>103</v>
+      </c>
+      <c r="B71" t="s">
+        <v>64</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E71" s="4">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4">
+        <v>4.19</v>
+      </c>
+      <c r="G71" s="4">
+        <v>-5.38</v>
+      </c>
+      <c r="H71" s="4">
+        <v>13</v>
+      </c>
+      <c r="I71" s="4">
+        <v>20</v>
+      </c>
+      <c r="J71" s="4">
+        <v>33</v>
+      </c>
+      <c r="K71" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="L71" s="5">
+        <v>0.0925231481481481</v>
+      </c>
+      <c r="M71" s="4">
+        <v>4578.2</v>
+      </c>
+      <c r="N71" s="4">
+        <v>530.93</v>
+      </c>
+      <c r="O71" s="4">
+        <v>27.864</v>
+      </c>
+      <c r="P71" s="4">
+        <v>77.43</v>
+      </c>
+      <c r="Q71" s="4">
+        <v>34.9</v>
+      </c>
+      <c r="R71" s="4">
+        <v>3.99</v>
+      </c>
+      <c r="S71" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="T71" s="4">
+        <v>0</v>
+      </c>
+      <c r="U71" s="4">
+        <v>0</v>
+      </c>
+      <c r="V71" s="4">
+        <v>0</v>
+      </c>
+      <c r="W71" s="4">
+        <v>0</v>
+      </c>
+      <c r="X71" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="4">
+        <v>401.47</v>
+      </c>
+      <c r="AG71" s="4">
+        <v>667.68</v>
+      </c>
+      <c r="AH71" s="4">
+        <v>247.17</v>
+      </c>
+      <c r="AI71" s="4">
+        <v>1973.17</v>
+      </c>
+      <c r="AJ71" s="4">
+        <v>1567.83</v>
+      </c>
+      <c r="AK71" s="4">
+        <v>534.72</v>
+      </c>
+      <c r="AL71" s="4">
+        <v>220.51</v>
+      </c>
+      <c r="AM71" s="4">
+        <v>34.79</v>
+      </c>
+      <c r="AN71" s="4">
+        <v>3</v>
+      </c>
+      <c r="AO71" s="4">
+        <v>0.26</v>
+      </c>
+      <c r="AP71" s="4">
+        <v>255.3</v>
+      </c>
+      <c r="AQ71" s="4">
+        <v>21</v>
+      </c>
+      <c r="AR71" s="4">
+        <v>1.92</v>
+      </c>
+      <c r="AS71" s="4">
+        <v>88</v>
+      </c>
+      <c r="AT71" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU71" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="AV71" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW71" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX71" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="72" spans="1:50">
+      <c r="A72" t="s">
+        <v>103</v>
+      </c>
+      <c r="B72" t="s">
+        <v>112</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E72" s="4">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="G72" s="4">
+        <v>-2.87</v>
+      </c>
+      <c r="H72" s="4">
+        <v>3</v>
+      </c>
+      <c r="I72" s="4">
+        <v>0</v>
+      </c>
+      <c r="J72" s="4">
+        <v>3</v>
+      </c>
+      <c r="K72" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="L72" s="5">
+        <v>0.0925231481481481</v>
+      </c>
+      <c r="M72" s="4">
+        <v>3000.42</v>
+      </c>
+      <c r="N72" s="4">
+        <v>397.97</v>
+      </c>
+      <c r="O72" s="4">
+        <v>23.364</v>
+      </c>
+      <c r="P72" s="4">
+        <v>64.94</v>
+      </c>
+      <c r="Q72" s="4">
+        <v>22.75</v>
+      </c>
+      <c r="R72" s="4">
+        <v>2.99</v>
+      </c>
+      <c r="S72" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="T72" s="4">
+        <v>0</v>
+      </c>
+      <c r="U72" s="4">
+        <v>0</v>
+      </c>
+      <c r="V72" s="4">
+        <v>0</v>
+      </c>
+      <c r="W72" s="4">
+        <v>0</v>
+      </c>
+      <c r="X72" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC72" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD72" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE72" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF72" s="4">
+        <v>253.09</v>
+      </c>
+      <c r="AG72" s="4">
+        <v>456.36</v>
+      </c>
+      <c r="AH72" s="4">
+        <v>108.45</v>
+      </c>
+      <c r="AI72" s="4">
+        <v>682.06</v>
+      </c>
+      <c r="AJ72" s="4">
+        <v>977.55</v>
+      </c>
+      <c r="AK72" s="4">
+        <v>1074.02</v>
+      </c>
+      <c r="AL72" s="4">
+        <v>158.34</v>
+      </c>
+      <c r="AM72" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN72" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO72" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP72" s="4">
+        <v>158.34</v>
+      </c>
+      <c r="AQ72" s="4">
+        <v>5</v>
+      </c>
+      <c r="AR72" s="4">
+        <v>1.19</v>
+      </c>
+      <c r="AS72" s="4">
+        <v>24</v>
+      </c>
+      <c r="AT72" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AU72" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AV72" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AW72" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX72" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:50">
+      <c r="A73" t="s">
+        <v>103</v>
+      </c>
+      <c r="B73" t="s">
+        <v>51</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E73" s="4">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4">
+        <v>3.66</v>
+      </c>
+      <c r="G73" s="4">
+        <v>-3.82</v>
+      </c>
+      <c r="H73" s="4">
+        <v>5</v>
+      </c>
+      <c r="I73" s="4">
+        <v>9</v>
+      </c>
+      <c r="J73" s="4">
+        <v>14</v>
+      </c>
+      <c r="K73" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="L73" s="5">
+        <v>0.0921527777777778</v>
+      </c>
+      <c r="M73" s="4">
+        <v>3482.26</v>
+      </c>
+      <c r="N73" s="4">
+        <v>398.42</v>
+      </c>
+      <c r="O73" s="4">
+        <v>22.572</v>
+      </c>
+      <c r="P73" s="4">
+        <v>62.73</v>
+      </c>
+      <c r="Q73" s="4">
+        <v>26.43</v>
+      </c>
+      <c r="R73" s="4">
+        <v>3</v>
+      </c>
+      <c r="S73" s="4">
+        <v>0.07</v>
+      </c>
+      <c r="T73" s="4">
+        <v>176</v>
+      </c>
+      <c r="U73" s="4">
+        <v>80.53</v>
+      </c>
+      <c r="V73" s="4">
+        <v>88</v>
+      </c>
+      <c r="W73" s="4">
+        <v>40.26</v>
+      </c>
+      <c r="X73" s="4">
+        <v>33.08</v>
+      </c>
+      <c r="Y73" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="5">
+        <v>0.0186342592592593</v>
+      </c>
+      <c r="AA73" s="5">
+        <v>0.0030787037037037</v>
+      </c>
+      <c r="AB73" s="5">
+        <v>2.31481481481481e-5</v>
+      </c>
+      <c r="AC73" s="5">
+        <v>0.000266203703703704</v>
+      </c>
+      <c r="AD73" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="4">
+        <v>296.34</v>
+      </c>
+      <c r="AG73" s="4">
+        <v>412.75</v>
+      </c>
+      <c r="AH73" s="4">
+        <v>327.97</v>
+      </c>
+      <c r="AI73" s="4">
+        <v>1688.4</v>
+      </c>
+      <c r="AJ73" s="4">
+        <v>813.04</v>
+      </c>
+      <c r="AK73" s="4">
+        <v>573.51</v>
+      </c>
+      <c r="AL73" s="4">
+        <v>78.75</v>
+      </c>
+      <c r="AM73" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="4">
+        <v>78.75</v>
+      </c>
+      <c r="AQ73" s="4">
+        <v>5</v>
+      </c>
+      <c r="AR73" s="4">
+        <v>0.59</v>
+      </c>
+      <c r="AS73" s="4">
+        <v>16</v>
+      </c>
+      <c r="AT73" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU73" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV73" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AW73" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX73" s="4" t="s">
         <v>58</v>
       </c>
     </row>

--- a/GPS_Formativas_2026.xlsx
+++ b/GPS_Formativas_2026.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="122">
   <si>
     <t>Date</t>
   </si>
@@ -363,6 +363,36 @@
   </si>
   <si>
     <t>Rodrigo Rios</t>
+  </si>
+  <si>
+    <t>Simón Sueiro</t>
+  </si>
+  <si>
+    <t>22-5-26</t>
+  </si>
+  <si>
+    <t>Tezzio Acosta</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>Benjamin Azambuja</t>
+  </si>
+  <si>
+    <t>Rodrigo Cardozo</t>
+  </si>
+  <si>
+    <t>Emiliano Figueroa</t>
+  </si>
+  <si>
+    <t>Joel Sardiña</t>
+  </si>
+  <si>
+    <t>Mateo Sosa</t>
+  </si>
+  <si>
+    <t>Alexander Velazquez</t>
   </si>
 </sst>
 </file>
@@ -978,11 +1008,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1524,7 +1560,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AX73"/>
+  <dimension ref="A1:AX98"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="30.4444444444444" customWidth="1"/>
@@ -12627,6 +12663,3806 @@
         <v>58</v>
       </c>
     </row>
+    <row r="74" spans="1:50">
+      <c r="A74" t="s">
+        <v>99</v>
+      </c>
+      <c r="B74" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E74" s="4">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4">
+        <v>3.48</v>
+      </c>
+      <c r="G74" s="4">
+        <v>-4.69</v>
+      </c>
+      <c r="H74" s="4">
+        <v>5</v>
+      </c>
+      <c r="I74" s="4">
+        <v>6</v>
+      </c>
+      <c r="J74" s="4">
+        <v>11</v>
+      </c>
+      <c r="K74" s="4">
+        <v>0.22</v>
+      </c>
+      <c r="L74" s="5">
+        <v>0.0340277777777778</v>
+      </c>
+      <c r="M74" s="4">
+        <v>3306.78</v>
+      </c>
+      <c r="N74" s="4">
+        <v>363.49</v>
+      </c>
+      <c r="O74" s="4">
+        <v>24.624</v>
+      </c>
+      <c r="P74" s="4">
+        <v>68.43</v>
+      </c>
+      <c r="Q74" s="4">
+        <v>67.49</v>
+      </c>
+      <c r="R74" s="4">
+        <v>7.42</v>
+      </c>
+      <c r="S74" s="4">
+        <v>0.07</v>
+      </c>
+      <c r="T74" s="4">
+        <v>0</v>
+      </c>
+      <c r="U74" s="4">
+        <v>0</v>
+      </c>
+      <c r="V74" s="4">
+        <v>0</v>
+      </c>
+      <c r="W74" s="4">
+        <v>0</v>
+      </c>
+      <c r="X74" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="4">
+        <v>289.96</v>
+      </c>
+      <c r="AG74" s="4">
+        <v>306.62</v>
+      </c>
+      <c r="AH74" s="4">
+        <v>203.84</v>
+      </c>
+      <c r="AI74" s="4">
+        <v>1904.33</v>
+      </c>
+      <c r="AJ74" s="4">
+        <v>955.25</v>
+      </c>
+      <c r="AK74" s="4">
+        <v>187.13</v>
+      </c>
+      <c r="AL74" s="4">
+        <v>56.6</v>
+      </c>
+      <c r="AM74" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="4">
+        <v>56.6</v>
+      </c>
+      <c r="AQ74" s="4">
+        <v>3</v>
+      </c>
+      <c r="AR74" s="4">
+        <v>1.16</v>
+      </c>
+      <c r="AS74" s="4">
+        <v>9</v>
+      </c>
+      <c r="AT74" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU74" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV74" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW74" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX74" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="75" spans="1:50">
+      <c r="A75" t="s">
+        <v>99</v>
+      </c>
+      <c r="B75" t="s">
+        <v>83</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E75" s="4">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4">
+        <v>3.55</v>
+      </c>
+      <c r="G75" s="4">
+        <v>-4.64</v>
+      </c>
+      <c r="H75" s="4">
+        <v>13</v>
+      </c>
+      <c r="I75" s="4">
+        <v>17</v>
+      </c>
+      <c r="J75" s="4">
+        <v>30</v>
+      </c>
+      <c r="K75" s="4">
+        <v>0.61</v>
+      </c>
+      <c r="L75" s="5">
+        <v>0.0340277777777778</v>
+      </c>
+      <c r="M75" s="4">
+        <v>3632.66</v>
+      </c>
+      <c r="N75" s="4">
+        <v>382.59</v>
+      </c>
+      <c r="O75" s="4">
+        <v>27.936</v>
+      </c>
+      <c r="P75" s="4">
+        <v>77.55</v>
+      </c>
+      <c r="Q75" s="4">
+        <v>74.14</v>
+      </c>
+      <c r="R75" s="4">
+        <v>7.81</v>
+      </c>
+      <c r="S75" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="T75" s="4">
+        <v>0</v>
+      </c>
+      <c r="U75" s="4">
+        <v>0</v>
+      </c>
+      <c r="V75" s="4">
+        <v>0</v>
+      </c>
+      <c r="W75" s="4">
+        <v>0</v>
+      </c>
+      <c r="X75" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="4">
+        <v>323.86</v>
+      </c>
+      <c r="AG75" s="4">
+        <v>550.9</v>
+      </c>
+      <c r="AH75" s="4">
+        <v>187.18</v>
+      </c>
+      <c r="AI75" s="4">
+        <v>1887.26</v>
+      </c>
+      <c r="AJ75" s="4">
+        <v>865.78</v>
+      </c>
+      <c r="AK75" s="4">
+        <v>448.02</v>
+      </c>
+      <c r="AL75" s="4">
+        <v>203.75</v>
+      </c>
+      <c r="AM75" s="4">
+        <v>40.56</v>
+      </c>
+      <c r="AN75" s="4">
+        <v>2</v>
+      </c>
+      <c r="AO75" s="4">
+        <v>0.83</v>
+      </c>
+      <c r="AP75" s="4">
+        <v>244.31</v>
+      </c>
+      <c r="AQ75" s="4">
+        <v>13</v>
+      </c>
+      <c r="AR75" s="4">
+        <v>4.99</v>
+      </c>
+      <c r="AS75" s="4">
+        <v>18</v>
+      </c>
+      <c r="AT75" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU75" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV75" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW75" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX75" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="76" spans="1:50">
+      <c r="A76" t="s">
+        <v>99</v>
+      </c>
+      <c r="B76" t="s">
+        <v>83</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E76" s="4">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4">
+        <v>3.34</v>
+      </c>
+      <c r="G76" s="4">
+        <v>-3.91</v>
+      </c>
+      <c r="H76" s="4">
+        <v>3</v>
+      </c>
+      <c r="I76" s="4">
+        <v>6</v>
+      </c>
+      <c r="J76" s="4">
+        <v>9</v>
+      </c>
+      <c r="K76" s="4">
+        <v>0.18</v>
+      </c>
+      <c r="L76" s="5">
+        <v>0.0340277777777778</v>
+      </c>
+      <c r="M76" s="4">
+        <v>3756.41</v>
+      </c>
+      <c r="N76" s="4">
+        <v>414.89</v>
+      </c>
+      <c r="O76" s="4">
+        <v>23.4</v>
+      </c>
+      <c r="P76" s="4">
+        <v>64.96</v>
+      </c>
+      <c r="Q76" s="4">
+        <v>76.66</v>
+      </c>
+      <c r="R76" s="4">
+        <v>8.47</v>
+      </c>
+      <c r="S76" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="T76" s="4">
+        <v>0</v>
+      </c>
+      <c r="U76" s="4">
+        <v>0</v>
+      </c>
+      <c r="V76" s="4">
+        <v>0</v>
+      </c>
+      <c r="W76" s="4">
+        <v>0</v>
+      </c>
+      <c r="X76" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="4">
+        <v>327.76</v>
+      </c>
+      <c r="AG76" s="4">
+        <v>353.35</v>
+      </c>
+      <c r="AH76" s="4">
+        <v>158.74</v>
+      </c>
+      <c r="AI76" s="4">
+        <v>2053.49</v>
+      </c>
+      <c r="AJ76" s="4">
+        <v>1206.24</v>
+      </c>
+      <c r="AK76" s="4">
+        <v>307.08</v>
+      </c>
+      <c r="AL76" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="AM76" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP76" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="AQ76" s="4">
+        <v>2</v>
+      </c>
+      <c r="AR76" s="4">
+        <v>0.63</v>
+      </c>
+      <c r="AS76" s="4">
+        <v>19</v>
+      </c>
+      <c r="AT76" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU76" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV76" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW76" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX76" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="77" spans="1:50">
+      <c r="A77" t="s">
+        <v>99</v>
+      </c>
+      <c r="B77" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E77" s="4">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="G77" s="4">
+        <v>-3.54</v>
+      </c>
+      <c r="H77" s="4">
+        <v>7</v>
+      </c>
+      <c r="I77" s="4">
+        <v>7</v>
+      </c>
+      <c r="J77" s="4">
+        <v>14</v>
+      </c>
+      <c r="K77" s="4">
+        <v>0.29</v>
+      </c>
+      <c r="L77" s="5">
+        <v>0.0340277777777778</v>
+      </c>
+      <c r="M77" s="4">
+        <v>3383.36</v>
+      </c>
+      <c r="N77" s="4">
+        <v>436.65</v>
+      </c>
+      <c r="O77" s="4">
+        <v>29.664</v>
+      </c>
+      <c r="P77" s="4">
+        <v>82.42</v>
+      </c>
+      <c r="Q77" s="4">
+        <v>69.05</v>
+      </c>
+      <c r="R77" s="4">
+        <v>8.91</v>
+      </c>
+      <c r="S77" s="4">
+        <v>0.07</v>
+      </c>
+      <c r="T77" s="4">
+        <v>0</v>
+      </c>
+      <c r="U77" s="4">
+        <v>0</v>
+      </c>
+      <c r="V77" s="4">
+        <v>0</v>
+      </c>
+      <c r="W77" s="4">
+        <v>0</v>
+      </c>
+      <c r="X77" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="4">
+        <v>288.99</v>
+      </c>
+      <c r="AG77" s="4">
+        <v>342.1</v>
+      </c>
+      <c r="AH77" s="4">
+        <v>230.89</v>
+      </c>
+      <c r="AI77" s="4">
+        <v>2077.79</v>
+      </c>
+      <c r="AJ77" s="4">
+        <v>623.6</v>
+      </c>
+      <c r="AK77" s="4">
+        <v>298.57</v>
+      </c>
+      <c r="AL77" s="4">
+        <v>126.97</v>
+      </c>
+      <c r="AM77" s="4">
+        <v>25.54</v>
+      </c>
+      <c r="AN77" s="4">
+        <v>1</v>
+      </c>
+      <c r="AO77" s="4">
+        <v>0.52</v>
+      </c>
+      <c r="AP77" s="4">
+        <v>152.51</v>
+      </c>
+      <c r="AQ77" s="4">
+        <v>7</v>
+      </c>
+      <c r="AR77" s="4">
+        <v>3.11</v>
+      </c>
+      <c r="AS77" s="4">
+        <v>71</v>
+      </c>
+      <c r="AT77" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU77" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV77" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW77" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX77" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="78" spans="1:50">
+      <c r="A78" t="s">
+        <v>99</v>
+      </c>
+      <c r="B78" t="s">
+        <v>83</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E78" s="4">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4">
+        <v>3.25</v>
+      </c>
+      <c r="G78" s="4">
+        <v>-3.54</v>
+      </c>
+      <c r="H78" s="4">
+        <v>1</v>
+      </c>
+      <c r="I78" s="4">
+        <v>4</v>
+      </c>
+      <c r="J78" s="4">
+        <v>5</v>
+      </c>
+      <c r="K78" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="L78" s="5">
+        <v>0.0340277777777778</v>
+      </c>
+      <c r="M78" s="4">
+        <v>2959.97</v>
+      </c>
+      <c r="N78" s="4">
+        <v>306.69</v>
+      </c>
+      <c r="O78" s="4">
+        <v>23.616</v>
+      </c>
+      <c r="P78" s="4">
+        <v>65.6</v>
+      </c>
+      <c r="Q78" s="4">
+        <v>60.41</v>
+      </c>
+      <c r="R78" s="4">
+        <v>6.26</v>
+      </c>
+      <c r="S78" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="T78" s="4">
+        <v>0</v>
+      </c>
+      <c r="U78" s="4">
+        <v>0</v>
+      </c>
+      <c r="V78" s="4">
+        <v>0</v>
+      </c>
+      <c r="W78" s="4">
+        <v>0</v>
+      </c>
+      <c r="X78" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="4">
+        <v>250.89</v>
+      </c>
+      <c r="AG78" s="4">
+        <v>222.39</v>
+      </c>
+      <c r="AH78" s="4">
+        <v>245.63</v>
+      </c>
+      <c r="AI78" s="4">
+        <v>1827.01</v>
+      </c>
+      <c r="AJ78" s="4">
+        <v>665.12</v>
+      </c>
+      <c r="AK78" s="4">
+        <v>175.54</v>
+      </c>
+      <c r="AL78" s="4">
+        <v>47.19</v>
+      </c>
+      <c r="AM78" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN78" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO78" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP78" s="4">
+        <v>47.19</v>
+      </c>
+      <c r="AQ78" s="4">
+        <v>4</v>
+      </c>
+      <c r="AR78" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="AS78" s="4">
+        <v>4</v>
+      </c>
+      <c r="AT78" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU78" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV78" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW78" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX78" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="79" spans="1:50">
+      <c r="A79" t="s">
+        <v>99</v>
+      </c>
+      <c r="B79" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E79" s="4">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4">
+        <v>3.56</v>
+      </c>
+      <c r="G79" s="4">
+        <v>-4.24</v>
+      </c>
+      <c r="H79" s="4">
+        <v>13</v>
+      </c>
+      <c r="I79" s="4">
+        <v>9</v>
+      </c>
+      <c r="J79" s="4">
+        <v>22</v>
+      </c>
+      <c r="K79" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="L79" s="5">
+        <v>0.0340277777777778</v>
+      </c>
+      <c r="M79" s="4">
+        <v>3059.17</v>
+      </c>
+      <c r="N79" s="4">
+        <v>376.07</v>
+      </c>
+      <c r="O79" s="4">
+        <v>27.72</v>
+      </c>
+      <c r="P79" s="4">
+        <v>77.04</v>
+      </c>
+      <c r="Q79" s="4">
+        <v>62.43</v>
+      </c>
+      <c r="R79" s="4">
+        <v>7.67</v>
+      </c>
+      <c r="S79" s="4">
+        <v>0.06</v>
+      </c>
+      <c r="T79" s="4">
+        <v>0</v>
+      </c>
+      <c r="U79" s="4">
+        <v>0</v>
+      </c>
+      <c r="V79" s="4">
+        <v>0</v>
+      </c>
+      <c r="W79" s="4">
+        <v>0</v>
+      </c>
+      <c r="X79" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="4">
+        <v>269.6</v>
+      </c>
+      <c r="AG79" s="4">
+        <v>395.61</v>
+      </c>
+      <c r="AH79" s="4">
+        <v>200.85</v>
+      </c>
+      <c r="AI79" s="4">
+        <v>1728.94</v>
+      </c>
+      <c r="AJ79" s="4">
+        <v>719.75</v>
+      </c>
+      <c r="AK79" s="4">
+        <v>267.96</v>
+      </c>
+      <c r="AL79" s="4">
+        <v>107.94</v>
+      </c>
+      <c r="AM79" s="4">
+        <v>34.02</v>
+      </c>
+      <c r="AN79" s="4">
+        <v>2</v>
+      </c>
+      <c r="AO79" s="4">
+        <v>0.69</v>
+      </c>
+      <c r="AP79" s="4">
+        <v>141.96</v>
+      </c>
+      <c r="AQ79" s="4">
+        <v>5</v>
+      </c>
+      <c r="AR79" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="AS79" s="4">
+        <v>28</v>
+      </c>
+      <c r="AT79" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU79" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV79" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW79" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX79" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="80" spans="1:50">
+      <c r="A80" t="s">
+        <v>99</v>
+      </c>
+      <c r="B80" t="s">
+        <v>83</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E80" s="4">
+        <v>0</v>
+      </c>
+      <c r="F80" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="G80" s="4">
+        <v>-3.98</v>
+      </c>
+      <c r="H80" s="4">
+        <v>14</v>
+      </c>
+      <c r="I80" s="4">
+        <v>13</v>
+      </c>
+      <c r="J80" s="4">
+        <v>27</v>
+      </c>
+      <c r="K80" s="4">
+        <v>0.55</v>
+      </c>
+      <c r="L80" s="5">
+        <v>0.0340277777777778</v>
+      </c>
+      <c r="M80" s="4">
+        <v>3178.57</v>
+      </c>
+      <c r="N80" s="4">
+        <v>340.67</v>
+      </c>
+      <c r="O80" s="4">
+        <v>24.264</v>
+      </c>
+      <c r="P80" s="4">
+        <v>67.4</v>
+      </c>
+      <c r="Q80" s="4">
+        <v>64.87</v>
+      </c>
+      <c r="R80" s="4">
+        <v>6.95</v>
+      </c>
+      <c r="S80" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="T80" s="4">
+        <v>0</v>
+      </c>
+      <c r="U80" s="4">
+        <v>0</v>
+      </c>
+      <c r="V80" s="4">
+        <v>0</v>
+      </c>
+      <c r="W80" s="4">
+        <v>0</v>
+      </c>
+      <c r="X80" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="4">
+        <v>284.03</v>
+      </c>
+      <c r="AG80" s="4">
+        <v>417.69</v>
+      </c>
+      <c r="AH80" s="4">
+        <v>190.12</v>
+      </c>
+      <c r="AI80" s="4">
+        <v>1690.19</v>
+      </c>
+      <c r="AJ80" s="4">
+        <v>935.83</v>
+      </c>
+      <c r="AK80" s="4">
+        <v>264.42</v>
+      </c>
+      <c r="AL80" s="4">
+        <v>98.27</v>
+      </c>
+      <c r="AM80" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN80" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO80" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP80" s="4">
+        <v>98.27</v>
+      </c>
+      <c r="AQ80" s="4">
+        <v>5</v>
+      </c>
+      <c r="AR80" s="4">
+        <v>2.01</v>
+      </c>
+      <c r="AS80" s="4">
+        <v>15</v>
+      </c>
+      <c r="AT80" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU80" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV80" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW80" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX80" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="81" spans="1:50">
+      <c r="A81" t="s">
+        <v>99</v>
+      </c>
+      <c r="B81" t="s">
+        <v>83</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E81" s="4">
+        <v>0</v>
+      </c>
+      <c r="F81" s="4">
+        <v>3.58</v>
+      </c>
+      <c r="G81" s="4">
+        <v>-4.49</v>
+      </c>
+      <c r="H81" s="4">
+        <v>4</v>
+      </c>
+      <c r="I81" s="4">
+        <v>7</v>
+      </c>
+      <c r="J81" s="4">
+        <v>11</v>
+      </c>
+      <c r="K81" s="4">
+        <v>0.22</v>
+      </c>
+      <c r="L81" s="5">
+        <v>0.0340277777777778</v>
+      </c>
+      <c r="M81" s="4">
+        <v>3767.51</v>
+      </c>
+      <c r="N81" s="4">
+        <v>516.03</v>
+      </c>
+      <c r="O81" s="4">
+        <v>23.328</v>
+      </c>
+      <c r="P81" s="4">
+        <v>64.77</v>
+      </c>
+      <c r="Q81" s="4">
+        <v>76.89</v>
+      </c>
+      <c r="R81" s="4">
+        <v>10.53</v>
+      </c>
+      <c r="S81" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="T81" s="4">
+        <v>0</v>
+      </c>
+      <c r="U81" s="4">
+        <v>0</v>
+      </c>
+      <c r="V81" s="4">
+        <v>0</v>
+      </c>
+      <c r="W81" s="4">
+        <v>0</v>
+      </c>
+      <c r="X81" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="4">
+        <v>330.97</v>
+      </c>
+      <c r="AG81" s="4">
+        <v>445.24</v>
+      </c>
+      <c r="AH81" s="4">
+        <v>200.23</v>
+      </c>
+      <c r="AI81" s="4">
+        <v>1691.4</v>
+      </c>
+      <c r="AJ81" s="4">
+        <v>1291.52</v>
+      </c>
+      <c r="AK81" s="4">
+        <v>500.56</v>
+      </c>
+      <c r="AL81" s="4">
+        <v>83.88</v>
+      </c>
+      <c r="AM81" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN81" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO81" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP81" s="4">
+        <v>83.88</v>
+      </c>
+      <c r="AQ81" s="4">
+        <v>6</v>
+      </c>
+      <c r="AR81" s="4">
+        <v>1.71</v>
+      </c>
+      <c r="AS81" s="4">
+        <v>44</v>
+      </c>
+      <c r="AT81" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU81" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV81" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW81" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX81" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="82" spans="1:50">
+      <c r="A82" t="s">
+        <v>99</v>
+      </c>
+      <c r="B82" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E82" s="4">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="G82" s="4">
+        <v>-4.25</v>
+      </c>
+      <c r="H82" s="4">
+        <v>8</v>
+      </c>
+      <c r="I82" s="4">
+        <v>11</v>
+      </c>
+      <c r="J82" s="4">
+        <v>19</v>
+      </c>
+      <c r="K82" s="4">
+        <v>0.39</v>
+      </c>
+      <c r="L82" s="5">
+        <v>0.0340277777777778</v>
+      </c>
+      <c r="M82" s="4">
+        <v>3300.45</v>
+      </c>
+      <c r="N82" s="4">
+        <v>378.45</v>
+      </c>
+      <c r="O82" s="4">
+        <v>26.856</v>
+      </c>
+      <c r="P82" s="4">
+        <v>74.63</v>
+      </c>
+      <c r="Q82" s="4">
+        <v>67.36</v>
+      </c>
+      <c r="R82" s="4">
+        <v>7.72</v>
+      </c>
+      <c r="S82" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="T82" s="4">
+        <v>0</v>
+      </c>
+      <c r="U82" s="4">
+        <v>0</v>
+      </c>
+      <c r="V82" s="4">
+        <v>0</v>
+      </c>
+      <c r="W82" s="4">
+        <v>0</v>
+      </c>
+      <c r="X82" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB82" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD82" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="4">
+        <v>294.21</v>
+      </c>
+      <c r="AG82" s="4">
+        <v>423.02</v>
+      </c>
+      <c r="AH82" s="4">
+        <v>163.37</v>
+      </c>
+      <c r="AI82" s="4">
+        <v>1758.53</v>
+      </c>
+      <c r="AJ82" s="4">
+        <v>971.19</v>
+      </c>
+      <c r="AK82" s="4">
+        <v>258.9</v>
+      </c>
+      <c r="AL82" s="4">
+        <v>140.02</v>
+      </c>
+      <c r="AM82" s="4">
+        <v>8.37</v>
+      </c>
+      <c r="AN82" s="4">
+        <v>1</v>
+      </c>
+      <c r="AO82" s="4">
+        <v>0.17</v>
+      </c>
+      <c r="AP82" s="4">
+        <v>148.39</v>
+      </c>
+      <c r="AQ82" s="4">
+        <v>9</v>
+      </c>
+      <c r="AR82" s="4">
+        <v>3.03</v>
+      </c>
+      <c r="AS82" s="4">
+        <v>56</v>
+      </c>
+      <c r="AT82" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU82" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV82" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW82" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX82" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="83" spans="1:50">
+      <c r="A83" t="s">
+        <v>99</v>
+      </c>
+      <c r="B83" t="s">
+        <v>83</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E83" s="4">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4">
+        <v>3.78</v>
+      </c>
+      <c r="G83" s="4">
+        <v>-3.44</v>
+      </c>
+      <c r="H83" s="4">
+        <v>8</v>
+      </c>
+      <c r="I83" s="4">
+        <v>3</v>
+      </c>
+      <c r="J83" s="4">
+        <v>11</v>
+      </c>
+      <c r="K83" s="4">
+        <v>0.22</v>
+      </c>
+      <c r="L83" s="5">
+        <v>0.0340277777777778</v>
+      </c>
+      <c r="M83" s="4">
+        <v>3501.92</v>
+      </c>
+      <c r="N83" s="4">
+        <v>457.68</v>
+      </c>
+      <c r="O83" s="4">
+        <v>22.248</v>
+      </c>
+      <c r="P83" s="4">
+        <v>61.77</v>
+      </c>
+      <c r="Q83" s="4">
+        <v>71.47</v>
+      </c>
+      <c r="R83" s="4">
+        <v>9.34</v>
+      </c>
+      <c r="S83" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="T83" s="4">
+        <v>0</v>
+      </c>
+      <c r="U83" s="4">
+        <v>0</v>
+      </c>
+      <c r="V83" s="4">
+        <v>0</v>
+      </c>
+      <c r="W83" s="4">
+        <v>0</v>
+      </c>
+      <c r="X83" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="4">
+        <v>307.78</v>
+      </c>
+      <c r="AG83" s="4">
+        <v>365.72</v>
+      </c>
+      <c r="AH83" s="4">
+        <v>190.1</v>
+      </c>
+      <c r="AI83" s="4">
+        <v>1911.84</v>
+      </c>
+      <c r="AJ83" s="4">
+        <v>1076.51</v>
+      </c>
+      <c r="AK83" s="4">
+        <v>281.57</v>
+      </c>
+      <c r="AL83" s="4">
+        <v>41.71</v>
+      </c>
+      <c r="AM83" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN83" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO83" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP83" s="4">
+        <v>41.71</v>
+      </c>
+      <c r="AQ83" s="4">
+        <v>4</v>
+      </c>
+      <c r="AR83" s="4">
+        <v>0.85</v>
+      </c>
+      <c r="AS83" s="4">
+        <v>113</v>
+      </c>
+      <c r="AT83" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU83" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV83" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW83" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX83" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="84" spans="1:50">
+      <c r="A84" t="s">
+        <v>113</v>
+      </c>
+      <c r="B84" t="s">
+        <v>51</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E84" s="4">
+        <v>0</v>
+      </c>
+      <c r="F84" s="4">
+        <v>4.12</v>
+      </c>
+      <c r="G84" s="4">
+        <v>-5.18</v>
+      </c>
+      <c r="H84" s="4">
+        <v>22</v>
+      </c>
+      <c r="I84" s="4">
+        <v>44</v>
+      </c>
+      <c r="J84" s="4">
+        <v>66</v>
+      </c>
+      <c r="K84" s="4">
+        <v>0.79</v>
+      </c>
+      <c r="L84" s="5">
+        <v>0.0583333333333333</v>
+      </c>
+      <c r="M84" s="4">
+        <v>9806.75</v>
+      </c>
+      <c r="N84" s="4">
+        <v>1210.84</v>
+      </c>
+      <c r="O84" s="4">
+        <v>27.72</v>
+      </c>
+      <c r="P84" s="4">
+        <v>76.97</v>
+      </c>
+      <c r="Q84" s="4">
+        <v>116.75</v>
+      </c>
+      <c r="R84" s="4">
+        <v>14.41</v>
+      </c>
+      <c r="S84" s="4">
+        <v>0.38</v>
+      </c>
+      <c r="T84" s="4">
+        <v>0</v>
+      </c>
+      <c r="U84" s="4">
+        <v>0</v>
+      </c>
+      <c r="V84" s="4">
+        <v>0</v>
+      </c>
+      <c r="W84" s="4">
+        <v>0</v>
+      </c>
+      <c r="X84" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="4">
+        <v>877.54</v>
+      </c>
+      <c r="AG84" s="4">
+        <v>1762.57</v>
+      </c>
+      <c r="AH84" s="4">
+        <v>158.05</v>
+      </c>
+      <c r="AI84" s="4">
+        <v>2993.91</v>
+      </c>
+      <c r="AJ84" s="4">
+        <v>4144.9</v>
+      </c>
+      <c r="AK84" s="4">
+        <v>2031.68</v>
+      </c>
+      <c r="AL84" s="4">
+        <v>441.08</v>
+      </c>
+      <c r="AM84" s="4">
+        <v>37.4</v>
+      </c>
+      <c r="AN84" s="4">
+        <v>3</v>
+      </c>
+      <c r="AO84" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="AP84" s="4">
+        <v>478.48</v>
+      </c>
+      <c r="AQ84" s="4">
+        <v>24</v>
+      </c>
+      <c r="AR84" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="AS84" s="4">
+        <v>90</v>
+      </c>
+      <c r="AT84" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU84" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV84" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW84" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX84" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="85" spans="1:50">
+      <c r="A85" t="s">
+        <v>113</v>
+      </c>
+      <c r="B85" t="s">
+        <v>51</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E85" s="4">
+        <v>0</v>
+      </c>
+      <c r="F85" s="4">
+        <v>4.04</v>
+      </c>
+      <c r="G85" s="4">
+        <v>-4.24</v>
+      </c>
+      <c r="H85" s="4">
+        <v>11</v>
+      </c>
+      <c r="I85" s="4">
+        <v>15</v>
+      </c>
+      <c r="J85" s="4">
+        <v>26</v>
+      </c>
+      <c r="K85" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="L85" s="5">
+        <v>0.025</v>
+      </c>
+      <c r="M85" s="4">
+        <v>4061.11</v>
+      </c>
+      <c r="N85" s="4">
+        <v>485</v>
+      </c>
+      <c r="O85" s="4">
+        <v>25.956</v>
+      </c>
+      <c r="P85" s="4">
+        <v>72.1</v>
+      </c>
+      <c r="Q85" s="4">
+        <v>112.81</v>
+      </c>
+      <c r="R85" s="4">
+        <v>13.47</v>
+      </c>
+      <c r="S85" s="4">
+        <v>0.32</v>
+      </c>
+      <c r="T85" s="4">
+        <v>0</v>
+      </c>
+      <c r="U85" s="4">
+        <v>0</v>
+      </c>
+      <c r="V85" s="4">
+        <v>0</v>
+      </c>
+      <c r="W85" s="4">
+        <v>0</v>
+      </c>
+      <c r="X85" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="4">
+        <v>359.77</v>
+      </c>
+      <c r="AG85" s="4">
+        <v>670.2</v>
+      </c>
+      <c r="AH85" s="4">
+        <v>72.31</v>
+      </c>
+      <c r="AI85" s="4">
+        <v>1329.73</v>
+      </c>
+      <c r="AJ85" s="4">
+        <v>1726.31</v>
+      </c>
+      <c r="AK85" s="4">
+        <v>617.99</v>
+      </c>
+      <c r="AL85" s="4">
+        <v>300.78</v>
+      </c>
+      <c r="AM85" s="4">
+        <v>13.26</v>
+      </c>
+      <c r="AN85" s="4">
+        <v>1</v>
+      </c>
+      <c r="AO85" s="4">
+        <v>0.37</v>
+      </c>
+      <c r="AP85" s="4">
+        <v>314.04</v>
+      </c>
+      <c r="AQ85" s="4">
+        <v>19</v>
+      </c>
+      <c r="AR85" s="4">
+        <v>8.72</v>
+      </c>
+      <c r="AS85" s="4">
+        <v>108</v>
+      </c>
+      <c r="AT85" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU85" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV85" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW85" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX85" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="86" spans="1:50">
+      <c r="A86" t="s">
+        <v>113</v>
+      </c>
+      <c r="B86" t="s">
+        <v>51</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E86" s="4">
+        <v>0</v>
+      </c>
+      <c r="F86" s="4">
+        <v>3.94</v>
+      </c>
+      <c r="G86" s="4">
+        <v>-5.1</v>
+      </c>
+      <c r="H86" s="4">
+        <v>19</v>
+      </c>
+      <c r="I86" s="4">
+        <v>22</v>
+      </c>
+      <c r="J86" s="4">
+        <v>41</v>
+      </c>
+      <c r="K86" s="4">
+        <v>1.14</v>
+      </c>
+      <c r="L86" s="5">
+        <v>0.025</v>
+      </c>
+      <c r="M86" s="4">
+        <v>4090.11</v>
+      </c>
+      <c r="N86" s="4">
+        <v>468.44</v>
+      </c>
+      <c r="O86" s="4">
+        <v>30.888</v>
+      </c>
+      <c r="P86" s="4">
+        <v>85.85</v>
+      </c>
+      <c r="Q86" s="4">
+        <v>113.61</v>
+      </c>
+      <c r="R86" s="4">
+        <v>13.01</v>
+      </c>
+      <c r="S86" s="4">
+        <v>0.32</v>
+      </c>
+      <c r="T86" s="4">
+        <v>0</v>
+      </c>
+      <c r="U86" s="4">
+        <v>0</v>
+      </c>
+      <c r="V86" s="4">
+        <v>0</v>
+      </c>
+      <c r="W86" s="4">
+        <v>0</v>
+      </c>
+      <c r="X86" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="4">
+        <v>366.48</v>
+      </c>
+      <c r="AG86" s="4">
+        <v>733.64</v>
+      </c>
+      <c r="AH86" s="4">
+        <v>60.98</v>
+      </c>
+      <c r="AI86" s="4">
+        <v>1390.27</v>
+      </c>
+      <c r="AJ86" s="4">
+        <v>1524.6</v>
+      </c>
+      <c r="AK86" s="4">
+        <v>721.5</v>
+      </c>
+      <c r="AL86" s="4">
+        <v>313.36</v>
+      </c>
+      <c r="AM86" s="4">
+        <v>78.68</v>
+      </c>
+      <c r="AN86" s="4">
+        <v>3</v>
+      </c>
+      <c r="AO86" s="4">
+        <v>2.19</v>
+      </c>
+      <c r="AP86" s="4">
+        <v>392.04</v>
+      </c>
+      <c r="AQ86" s="4">
+        <v>18</v>
+      </c>
+      <c r="AR86" s="4">
+        <v>10.89</v>
+      </c>
+      <c r="AS86" s="4">
+        <v>58</v>
+      </c>
+      <c r="AT86" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU86" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV86" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW86" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX86" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="87" spans="1:50">
+      <c r="A87" t="s">
+        <v>113</v>
+      </c>
+      <c r="B87" t="s">
+        <v>51</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E87" s="4">
+        <v>0</v>
+      </c>
+      <c r="F87" s="4">
+        <v>4</v>
+      </c>
+      <c r="G87" s="4">
+        <v>-4.93</v>
+      </c>
+      <c r="H87" s="4">
+        <v>15</v>
+      </c>
+      <c r="I87" s="4">
+        <v>23</v>
+      </c>
+      <c r="J87" s="4">
+        <v>38</v>
+      </c>
+      <c r="K87" s="4">
+        <v>0.64</v>
+      </c>
+      <c r="L87" s="5">
+        <v>0.0409722222222222</v>
+      </c>
+      <c r="M87" s="4">
+        <v>7391.21</v>
+      </c>
+      <c r="N87" s="4">
+        <v>698</v>
+      </c>
+      <c r="O87" s="4">
+        <v>29.196</v>
+      </c>
+      <c r="P87" s="4">
+        <v>81.08</v>
+      </c>
+      <c r="Q87" s="4">
+        <v>125.27</v>
+      </c>
+      <c r="R87" s="4">
+        <v>11.83</v>
+      </c>
+      <c r="S87" s="4">
+        <v>0.39</v>
+      </c>
+      <c r="T87" s="4">
+        <v>0</v>
+      </c>
+      <c r="U87" s="4">
+        <v>0</v>
+      </c>
+      <c r="V87" s="4">
+        <v>0</v>
+      </c>
+      <c r="W87" s="4">
+        <v>0</v>
+      </c>
+      <c r="X87" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="4">
+        <v>661.13</v>
+      </c>
+      <c r="AG87" s="4">
+        <v>1448.24</v>
+      </c>
+      <c r="AH87" s="4">
+        <v>103.49</v>
+      </c>
+      <c r="AI87" s="4">
+        <v>2418.42</v>
+      </c>
+      <c r="AJ87" s="4">
+        <v>2976.42</v>
+      </c>
+      <c r="AK87" s="4">
+        <v>1303</v>
+      </c>
+      <c r="AL87" s="4">
+        <v>518.2</v>
+      </c>
+      <c r="AM87" s="4">
+        <v>70.96</v>
+      </c>
+      <c r="AN87" s="4">
+        <v>4</v>
+      </c>
+      <c r="AO87" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="AP87" s="4">
+        <v>589.16</v>
+      </c>
+      <c r="AQ87" s="4">
+        <v>31</v>
+      </c>
+      <c r="AR87" s="4">
+        <v>9.99</v>
+      </c>
+      <c r="AS87" s="4">
+        <v>39</v>
+      </c>
+      <c r="AT87" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU87" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV87" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW87" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX87" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="88" spans="1:50">
+      <c r="A88" t="s">
+        <v>113</v>
+      </c>
+      <c r="B88" t="s">
+        <v>51</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E88" s="4">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4">
+        <v>4.37</v>
+      </c>
+      <c r="G88" s="4">
+        <v>-5.99</v>
+      </c>
+      <c r="H88" s="4">
+        <v>26</v>
+      </c>
+      <c r="I88" s="4">
+        <v>26</v>
+      </c>
+      <c r="J88" s="4">
+        <v>52</v>
+      </c>
+      <c r="K88" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="L88" s="5">
+        <v>0.0409722222222222</v>
+      </c>
+      <c r="M88" s="4">
+        <v>7617.37</v>
+      </c>
+      <c r="N88" s="4">
+        <v>850.48</v>
+      </c>
+      <c r="O88" s="4">
+        <v>26.136</v>
+      </c>
+      <c r="P88" s="4">
+        <v>72.64</v>
+      </c>
+      <c r="Q88" s="4">
+        <v>129.11</v>
+      </c>
+      <c r="R88" s="4">
+        <v>14.41</v>
+      </c>
+      <c r="S88" s="4">
+        <v>0.47</v>
+      </c>
+      <c r="T88" s="4">
+        <v>0</v>
+      </c>
+      <c r="U88" s="4">
+        <v>0</v>
+      </c>
+      <c r="V88" s="4">
+        <v>0</v>
+      </c>
+      <c r="W88" s="4">
+        <v>0</v>
+      </c>
+      <c r="X88" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="4">
+        <v>649.08</v>
+      </c>
+      <c r="AG88" s="4">
+        <v>1262.46</v>
+      </c>
+      <c r="AH88" s="4">
+        <v>73.54</v>
+      </c>
+      <c r="AI88" s="4">
+        <v>2288.02</v>
+      </c>
+      <c r="AJ88" s="4">
+        <v>3273.4</v>
+      </c>
+      <c r="AK88" s="4">
+        <v>1533.42</v>
+      </c>
+      <c r="AL88" s="4">
+        <v>438.22</v>
+      </c>
+      <c r="AM88" s="4">
+        <v>11.19</v>
+      </c>
+      <c r="AN88" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="4">
+        <v>0.19</v>
+      </c>
+      <c r="AP88" s="4">
+        <v>449.41</v>
+      </c>
+      <c r="AQ88" s="4">
+        <v>29</v>
+      </c>
+      <c r="AR88" s="4">
+        <v>7.62</v>
+      </c>
+      <c r="AS88" s="4">
+        <v>90</v>
+      </c>
+      <c r="AT88" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU88" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV88" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW88" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX88" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="89" spans="1:50">
+      <c r="A89" t="s">
+        <v>113</v>
+      </c>
+      <c r="B89" t="s">
+        <v>51</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E89" s="4">
+        <v>0</v>
+      </c>
+      <c r="F89" s="4">
+        <v>5.32</v>
+      </c>
+      <c r="G89" s="4">
+        <v>-6.87</v>
+      </c>
+      <c r="H89" s="4">
+        <v>47</v>
+      </c>
+      <c r="I89" s="4">
+        <v>51</v>
+      </c>
+      <c r="J89" s="4">
+        <v>98</v>
+      </c>
+      <c r="K89" s="4">
+        <v>1.03</v>
+      </c>
+      <c r="L89" s="5">
+        <v>0.0659722222222222</v>
+      </c>
+      <c r="M89" s="4">
+        <v>11060.12</v>
+      </c>
+      <c r="N89" s="4">
+        <v>979.96</v>
+      </c>
+      <c r="O89" s="4">
+        <v>32.004</v>
+      </c>
+      <c r="P89" s="4">
+        <v>88.94</v>
+      </c>
+      <c r="Q89" s="4">
+        <v>116.42</v>
+      </c>
+      <c r="R89" s="4">
+        <v>10.32</v>
+      </c>
+      <c r="S89" s="4">
+        <v>0.34</v>
+      </c>
+      <c r="T89" s="4">
+        <v>0</v>
+      </c>
+      <c r="U89" s="4">
+        <v>0</v>
+      </c>
+      <c r="V89" s="4">
+        <v>0</v>
+      </c>
+      <c r="W89" s="4">
+        <v>0</v>
+      </c>
+      <c r="X89" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="4">
+        <v>910.75</v>
+      </c>
+      <c r="AG89" s="4">
+        <v>1974.17</v>
+      </c>
+      <c r="AH89" s="4">
+        <v>171.99</v>
+      </c>
+      <c r="AI89" s="4">
+        <v>3995.35</v>
+      </c>
+      <c r="AJ89" s="4">
+        <v>4033.67</v>
+      </c>
+      <c r="AK89" s="4">
+        <v>2065.51</v>
+      </c>
+      <c r="AL89" s="4">
+        <v>592.32</v>
+      </c>
+      <c r="AM89" s="4">
+        <v>201.41</v>
+      </c>
+      <c r="AN89" s="4">
+        <v>9</v>
+      </c>
+      <c r="AO89" s="4">
+        <v>2.12</v>
+      </c>
+      <c r="AP89" s="4">
+        <v>793.73</v>
+      </c>
+      <c r="AQ89" s="4">
+        <v>45</v>
+      </c>
+      <c r="AR89" s="4">
+        <v>8.36</v>
+      </c>
+      <c r="AS89" s="4">
+        <v>82</v>
+      </c>
+      <c r="AT89" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU89" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV89" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW89" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX89" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="90" spans="1:50">
+      <c r="A90" t="s">
+        <v>113</v>
+      </c>
+      <c r="B90" t="s">
+        <v>51</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E90" s="4">
+        <v>0</v>
+      </c>
+      <c r="F90" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="G90" s="4">
+        <v>-4.86</v>
+      </c>
+      <c r="H90" s="4">
+        <v>24</v>
+      </c>
+      <c r="I90" s="4">
+        <v>34</v>
+      </c>
+      <c r="J90" s="4">
+        <v>58</v>
+      </c>
+      <c r="K90" s="4">
+        <v>0.61</v>
+      </c>
+      <c r="L90" s="5">
+        <v>0.0659722222222222</v>
+      </c>
+      <c r="M90" s="4">
+        <v>10317.15</v>
+      </c>
+      <c r="N90" s="4">
+        <v>914.28</v>
+      </c>
+      <c r="O90" s="4">
+        <v>29.7</v>
+      </c>
+      <c r="P90" s="4">
+        <v>82.53</v>
+      </c>
+      <c r="Q90" s="4">
+        <v>108.6</v>
+      </c>
+      <c r="R90" s="4">
+        <v>9.62</v>
+      </c>
+      <c r="S90" s="4">
+        <v>0.31</v>
+      </c>
+      <c r="T90" s="4">
+        <v>0</v>
+      </c>
+      <c r="U90" s="4">
+        <v>0</v>
+      </c>
+      <c r="V90" s="4">
+        <v>0</v>
+      </c>
+      <c r="W90" s="4">
+        <v>0</v>
+      </c>
+      <c r="X90" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD90" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF90" s="4">
+        <v>910.86</v>
+      </c>
+      <c r="AG90" s="4">
+        <v>1387.94</v>
+      </c>
+      <c r="AH90" s="4">
+        <v>190.66</v>
+      </c>
+      <c r="AI90" s="4">
+        <v>3561.1</v>
+      </c>
+      <c r="AJ90" s="4">
+        <v>4762.85</v>
+      </c>
+      <c r="AK90" s="4">
+        <v>1271.56</v>
+      </c>
+      <c r="AL90" s="4">
+        <v>428.36</v>
+      </c>
+      <c r="AM90" s="4">
+        <v>103.07</v>
+      </c>
+      <c r="AN90" s="4">
+        <v>6</v>
+      </c>
+      <c r="AO90" s="4">
+        <v>1.08</v>
+      </c>
+      <c r="AP90" s="4">
+        <v>531.43</v>
+      </c>
+      <c r="AQ90" s="4">
+        <v>28</v>
+      </c>
+      <c r="AR90" s="4">
+        <v>5.59</v>
+      </c>
+      <c r="AS90" s="4">
+        <v>43</v>
+      </c>
+      <c r="AT90" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU90" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV90" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW90" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX90" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="91" spans="1:50">
+      <c r="A91" t="s">
+        <v>113</v>
+      </c>
+      <c r="B91" t="s">
+        <v>51</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E91" s="4">
+        <v>0</v>
+      </c>
+      <c r="F91" s="4">
+        <v>4.35</v>
+      </c>
+      <c r="G91" s="4">
+        <v>-4.51</v>
+      </c>
+      <c r="H91" s="4">
+        <v>29</v>
+      </c>
+      <c r="I91" s="4">
+        <v>29</v>
+      </c>
+      <c r="J91" s="4">
+        <v>58</v>
+      </c>
+      <c r="K91" s="4">
+        <v>0.61</v>
+      </c>
+      <c r="L91" s="5">
+        <v>0.0659722222222222</v>
+      </c>
+      <c r="M91" s="4">
+        <v>9023.7</v>
+      </c>
+      <c r="N91" s="4">
+        <v>872.02</v>
+      </c>
+      <c r="O91" s="4">
+        <v>31.428</v>
+      </c>
+      <c r="P91" s="4">
+        <v>87.31</v>
+      </c>
+      <c r="Q91" s="4">
+        <v>94.99</v>
+      </c>
+      <c r="R91" s="4">
+        <v>9.18</v>
+      </c>
+      <c r="S91" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="T91" s="4">
+        <v>0</v>
+      </c>
+      <c r="U91" s="4">
+        <v>0</v>
+      </c>
+      <c r="V91" s="4">
+        <v>0</v>
+      </c>
+      <c r="W91" s="4">
+        <v>0</v>
+      </c>
+      <c r="X91" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="4">
+        <v>787.52</v>
+      </c>
+      <c r="AG91" s="4">
+        <v>1060</v>
+      </c>
+      <c r="AH91" s="4">
+        <v>194.58</v>
+      </c>
+      <c r="AI91" s="4">
+        <v>3650.1</v>
+      </c>
+      <c r="AJ91" s="4">
+        <v>3742.29</v>
+      </c>
+      <c r="AK91" s="4">
+        <v>1115.93</v>
+      </c>
+      <c r="AL91" s="4">
+        <v>278.77</v>
+      </c>
+      <c r="AM91" s="4">
+        <v>41.95</v>
+      </c>
+      <c r="AN91" s="4">
+        <v>2</v>
+      </c>
+      <c r="AO91" s="4">
+        <v>0.44</v>
+      </c>
+      <c r="AP91" s="4">
+        <v>320.72</v>
+      </c>
+      <c r="AQ91" s="4">
+        <v>20</v>
+      </c>
+      <c r="AR91" s="4">
+        <v>3.38</v>
+      </c>
+      <c r="AS91" s="4">
+        <v>46</v>
+      </c>
+      <c r="AT91" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU91" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV91" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW91" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX91" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="92" spans="1:50">
+      <c r="A92" t="s">
+        <v>113</v>
+      </c>
+      <c r="B92" t="s">
+        <v>51</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E92" s="4">
+        <v>0</v>
+      </c>
+      <c r="F92" s="4">
+        <v>4.56</v>
+      </c>
+      <c r="G92" s="4">
+        <v>-3.95</v>
+      </c>
+      <c r="H92" s="4">
+        <v>4</v>
+      </c>
+      <c r="I92" s="4">
+        <v>4</v>
+      </c>
+      <c r="J92" s="4">
+        <v>8</v>
+      </c>
+      <c r="K92" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="L92" s="5">
+        <v>0.00347222222222222</v>
+      </c>
+      <c r="M92" s="4">
+        <v>769.07</v>
+      </c>
+      <c r="N92" s="4">
+        <v>87.98</v>
+      </c>
+      <c r="O92" s="4">
+        <v>28.26</v>
+      </c>
+      <c r="P92" s="4">
+        <v>78.54</v>
+      </c>
+      <c r="Q92" s="4">
+        <v>153.81</v>
+      </c>
+      <c r="R92" s="4">
+        <v>17.6</v>
+      </c>
+      <c r="S92" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="T92" s="4">
+        <v>0</v>
+      </c>
+      <c r="U92" s="4">
+        <v>0</v>
+      </c>
+      <c r="V92" s="4">
+        <v>0</v>
+      </c>
+      <c r="W92" s="4">
+        <v>0</v>
+      </c>
+      <c r="X92" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="4">
+        <v>57.88</v>
+      </c>
+      <c r="AG92" s="4">
+        <v>178.93</v>
+      </c>
+      <c r="AH92" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="AI92" s="4">
+        <v>162.25</v>
+      </c>
+      <c r="AJ92" s="4">
+        <v>361.6</v>
+      </c>
+      <c r="AK92" s="4">
+        <v>127.58</v>
+      </c>
+      <c r="AL92" s="4">
+        <v>80.18</v>
+      </c>
+      <c r="AM92" s="4">
+        <v>33.92</v>
+      </c>
+      <c r="AN92" s="4">
+        <v>3</v>
+      </c>
+      <c r="AO92" s="4">
+        <v>6.78</v>
+      </c>
+      <c r="AP92" s="4">
+        <v>114.1</v>
+      </c>
+      <c r="AQ92" s="4">
+        <v>6</v>
+      </c>
+      <c r="AR92" s="4">
+        <v>22.82</v>
+      </c>
+      <c r="AS92" s="4">
+        <v>13</v>
+      </c>
+      <c r="AT92" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU92" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV92" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW92" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX92" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="93" spans="1:50">
+      <c r="A93" t="s">
+        <v>113</v>
+      </c>
+      <c r="B93" t="s">
+        <v>51</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E93" s="4">
+        <v>0</v>
+      </c>
+      <c r="F93" s="4">
+        <v>4.13</v>
+      </c>
+      <c r="G93" s="4">
+        <v>-5.73</v>
+      </c>
+      <c r="H93" s="4">
+        <v>34</v>
+      </c>
+      <c r="I93" s="4">
+        <v>54</v>
+      </c>
+      <c r="J93" s="4">
+        <v>88</v>
+      </c>
+      <c r="K93" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="L93" s="5">
+        <v>0.0625</v>
+      </c>
+      <c r="M93" s="4">
+        <v>9658.08</v>
+      </c>
+      <c r="N93" s="4">
+        <v>1039.6</v>
+      </c>
+      <c r="O93" s="4">
+        <v>29.844</v>
+      </c>
+      <c r="P93" s="4">
+        <v>82.86</v>
+      </c>
+      <c r="Q93" s="4">
+        <v>107.31</v>
+      </c>
+      <c r="R93" s="4">
+        <v>11.55</v>
+      </c>
+      <c r="S93" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="T93" s="4">
+        <v>0</v>
+      </c>
+      <c r="U93" s="4">
+        <v>0</v>
+      </c>
+      <c r="V93" s="4">
+        <v>0</v>
+      </c>
+      <c r="W93" s="4">
+        <v>0</v>
+      </c>
+      <c r="X93" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="4">
+        <v>863.12</v>
+      </c>
+      <c r="AG93" s="4">
+        <v>1572.98</v>
+      </c>
+      <c r="AH93" s="4">
+        <v>134.46</v>
+      </c>
+      <c r="AI93" s="4">
+        <v>4022.74</v>
+      </c>
+      <c r="AJ93" s="4">
+        <v>3462.25</v>
+      </c>
+      <c r="AK93" s="4">
+        <v>1358.32</v>
+      </c>
+      <c r="AL93" s="4">
+        <v>578.74</v>
+      </c>
+      <c r="AM93" s="4">
+        <v>101.91</v>
+      </c>
+      <c r="AN93" s="4">
+        <v>5</v>
+      </c>
+      <c r="AO93" s="4">
+        <v>1.13</v>
+      </c>
+      <c r="AP93" s="4">
+        <v>680.65</v>
+      </c>
+      <c r="AQ93" s="4">
+        <v>42</v>
+      </c>
+      <c r="AR93" s="4">
+        <v>7.56</v>
+      </c>
+      <c r="AS93" s="4">
+        <v>158</v>
+      </c>
+      <c r="AT93" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU93" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV93" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW93" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX93" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="94" spans="1:50">
+      <c r="A94" t="s">
+        <v>113</v>
+      </c>
+      <c r="B94" t="s">
+        <v>51</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E94" s="4">
+        <v>0</v>
+      </c>
+      <c r="F94" s="4">
+        <v>4.36</v>
+      </c>
+      <c r="G94" s="4">
+        <v>-4.48</v>
+      </c>
+      <c r="H94" s="4">
+        <v>17</v>
+      </c>
+      <c r="I94" s="4">
+        <v>20</v>
+      </c>
+      <c r="J94" s="4">
+        <v>37</v>
+      </c>
+      <c r="K94" s="4">
+        <v>0.39</v>
+      </c>
+      <c r="L94" s="5">
+        <v>0.0659722222222222</v>
+      </c>
+      <c r="M94" s="4">
+        <v>8804.29</v>
+      </c>
+      <c r="N94" s="4">
+        <v>812.47</v>
+      </c>
+      <c r="O94" s="4">
+        <v>28.836</v>
+      </c>
+      <c r="P94" s="4">
+        <v>80.12</v>
+      </c>
+      <c r="Q94" s="4">
+        <v>92.68</v>
+      </c>
+      <c r="R94" s="4">
+        <v>8.55</v>
+      </c>
+      <c r="S94" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="T94" s="4">
+        <v>0</v>
+      </c>
+      <c r="U94" s="4">
+        <v>0</v>
+      </c>
+      <c r="V94" s="4">
+        <v>0</v>
+      </c>
+      <c r="W94" s="4">
+        <v>0</v>
+      </c>
+      <c r="X94" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="4">
+        <v>771.02</v>
+      </c>
+      <c r="AG94" s="4">
+        <v>1007.69</v>
+      </c>
+      <c r="AH94" s="4">
+        <v>146.65</v>
+      </c>
+      <c r="AI94" s="4">
+        <v>3597.96</v>
+      </c>
+      <c r="AJ94" s="4">
+        <v>3744.52</v>
+      </c>
+      <c r="AK94" s="4">
+        <v>973.32</v>
+      </c>
+      <c r="AL94" s="4">
+        <v>250.64</v>
+      </c>
+      <c r="AM94" s="4">
+        <v>89.93</v>
+      </c>
+      <c r="AN94" s="4">
+        <v>5</v>
+      </c>
+      <c r="AO94" s="4">
+        <v>0.95</v>
+      </c>
+      <c r="AP94" s="4">
+        <v>340.57</v>
+      </c>
+      <c r="AQ94" s="4">
+        <v>20</v>
+      </c>
+      <c r="AR94" s="4">
+        <v>3.58</v>
+      </c>
+      <c r="AS94" s="4">
+        <v>38</v>
+      </c>
+      <c r="AT94" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU94" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV94" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW94" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX94" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="95" spans="1:50">
+      <c r="A95" t="s">
+        <v>113</v>
+      </c>
+      <c r="B95" t="s">
+        <v>51</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E95" s="4">
+        <v>0</v>
+      </c>
+      <c r="F95" s="4">
+        <v>3.49</v>
+      </c>
+      <c r="G95" s="4">
+        <v>-4.2</v>
+      </c>
+      <c r="H95" s="4">
+        <v>2</v>
+      </c>
+      <c r="I95" s="4">
+        <v>1</v>
+      </c>
+      <c r="J95" s="4">
+        <v>3</v>
+      </c>
+      <c r="K95" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="L95" s="5">
+        <v>0.00347222222222222</v>
+      </c>
+      <c r="M95" s="4">
+        <v>627.94</v>
+      </c>
+      <c r="N95" s="4">
+        <v>65</v>
+      </c>
+      <c r="O95" s="4">
+        <v>24.372</v>
+      </c>
+      <c r="P95" s="4">
+        <v>67.75</v>
+      </c>
+      <c r="Q95" s="4">
+        <v>125.59</v>
+      </c>
+      <c r="R95" s="4">
+        <v>13</v>
+      </c>
+      <c r="S95" s="4">
+        <v>0.36</v>
+      </c>
+      <c r="T95" s="4">
+        <v>0</v>
+      </c>
+      <c r="U95" s="4">
+        <v>0</v>
+      </c>
+      <c r="V95" s="4">
+        <v>0</v>
+      </c>
+      <c r="W95" s="4">
+        <v>0</v>
+      </c>
+      <c r="X95" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA95" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB95" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC95" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD95" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE95" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF95" s="4">
+        <v>54.14</v>
+      </c>
+      <c r="AG95" s="4">
+        <v>79.1</v>
+      </c>
+      <c r="AH95" s="4">
+        <v>14.67</v>
+      </c>
+      <c r="AI95" s="4">
+        <v>220.08</v>
+      </c>
+      <c r="AJ95" s="4">
+        <v>315.82</v>
+      </c>
+      <c r="AK95" s="4">
+        <v>64.07</v>
+      </c>
+      <c r="AL95" s="4">
+        <v>13.1</v>
+      </c>
+      <c r="AM95" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN95" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO95" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP95" s="4">
+        <v>13.1</v>
+      </c>
+      <c r="AQ95" s="4">
+        <v>1</v>
+      </c>
+      <c r="AR95" s="4">
+        <v>2.62</v>
+      </c>
+      <c r="AS95" s="4">
+        <v>7</v>
+      </c>
+      <c r="AT95" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU95" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV95" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW95" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX95" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="96" spans="1:50">
+      <c r="A96" t="s">
+        <v>113</v>
+      </c>
+      <c r="B96" t="s">
+        <v>51</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E96" s="4">
+        <v>0</v>
+      </c>
+      <c r="F96" s="4">
+        <v>3.88</v>
+      </c>
+      <c r="G96" s="4">
+        <v>-5.18</v>
+      </c>
+      <c r="H96" s="4">
+        <v>24</v>
+      </c>
+      <c r="I96" s="4">
+        <v>45</v>
+      </c>
+      <c r="J96" s="4">
+        <v>69</v>
+      </c>
+      <c r="K96" s="4">
+        <v>0.73</v>
+      </c>
+      <c r="L96" s="5">
+        <v>0.0659722222222222</v>
+      </c>
+      <c r="M96" s="4">
+        <v>9811.16</v>
+      </c>
+      <c r="N96" s="4">
+        <v>950.66</v>
+      </c>
+      <c r="O96" s="4">
+        <v>30.852</v>
+      </c>
+      <c r="P96" s="4">
+        <v>85.67</v>
+      </c>
+      <c r="Q96" s="4">
+        <v>103.28</v>
+      </c>
+      <c r="R96" s="4">
+        <v>10.01</v>
+      </c>
+      <c r="S96" s="4">
+        <v>0.27</v>
+      </c>
+      <c r="T96" s="4">
+        <v>0</v>
+      </c>
+      <c r="U96" s="4">
+        <v>0</v>
+      </c>
+      <c r="V96" s="4">
+        <v>0</v>
+      </c>
+      <c r="W96" s="4">
+        <v>0</v>
+      </c>
+      <c r="X96" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="4">
+        <v>863.6</v>
+      </c>
+      <c r="AG96" s="4">
+        <v>1521.85</v>
+      </c>
+      <c r="AH96" s="4">
+        <v>221.68</v>
+      </c>
+      <c r="AI96" s="4">
+        <v>3435.21</v>
+      </c>
+      <c r="AJ96" s="4">
+        <v>4031.25</v>
+      </c>
+      <c r="AK96" s="4">
+        <v>1502.33</v>
+      </c>
+      <c r="AL96" s="4">
+        <v>498.62</v>
+      </c>
+      <c r="AM96" s="4">
+        <v>122.46</v>
+      </c>
+      <c r="AN96" s="4">
+        <v>4</v>
+      </c>
+      <c r="AO96" s="4">
+        <v>1.29</v>
+      </c>
+      <c r="AP96" s="4">
+        <v>621.08</v>
+      </c>
+      <c r="AQ96" s="4">
+        <v>37</v>
+      </c>
+      <c r="AR96" s="4">
+        <v>6.54</v>
+      </c>
+      <c r="AS96" s="4">
+        <v>73</v>
+      </c>
+      <c r="AT96" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU96" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV96" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW96" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX96" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="97" spans="1:50">
+      <c r="A97" t="s">
+        <v>113</v>
+      </c>
+      <c r="B97" t="s">
+        <v>51</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E97" s="4">
+        <v>0</v>
+      </c>
+      <c r="F97" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="G97" s="4">
+        <v>-3.58</v>
+      </c>
+      <c r="H97" s="4">
+        <v>4</v>
+      </c>
+      <c r="I97" s="4">
+        <v>3</v>
+      </c>
+      <c r="J97" s="4">
+        <v>7</v>
+      </c>
+      <c r="K97" s="4">
+        <v>0.64</v>
+      </c>
+      <c r="L97" s="5">
+        <v>0.00763888888888889</v>
+      </c>
+      <c r="M97" s="4">
+        <v>1299.15</v>
+      </c>
+      <c r="N97" s="4">
+        <v>150.26</v>
+      </c>
+      <c r="O97" s="4">
+        <v>23.076</v>
+      </c>
+      <c r="P97" s="4">
+        <v>64.14</v>
+      </c>
+      <c r="Q97" s="4">
+        <v>118.1</v>
+      </c>
+      <c r="R97" s="4">
+        <v>13.66</v>
+      </c>
+      <c r="S97" s="4">
+        <v>0.43</v>
+      </c>
+      <c r="T97" s="4">
+        <v>0</v>
+      </c>
+      <c r="U97" s="4">
+        <v>0</v>
+      </c>
+      <c r="V97" s="4">
+        <v>0</v>
+      </c>
+      <c r="W97" s="4">
+        <v>0</v>
+      </c>
+      <c r="X97" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="4">
+        <v>308.67</v>
+      </c>
+      <c r="AG97" s="4">
+        <v>260.76</v>
+      </c>
+      <c r="AH97" s="4">
+        <v>27.87</v>
+      </c>
+      <c r="AI97" s="4">
+        <v>341.6</v>
+      </c>
+      <c r="AJ97" s="4">
+        <v>532.54</v>
+      </c>
+      <c r="AK97" s="4">
+        <v>318.79</v>
+      </c>
+      <c r="AL97" s="4">
+        <v>78.35</v>
+      </c>
+      <c r="AM97" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="4">
+        <v>78.35</v>
+      </c>
+      <c r="AQ97" s="4">
+        <v>5</v>
+      </c>
+      <c r="AR97" s="4">
+        <v>7.12</v>
+      </c>
+      <c r="AS97" s="4">
+        <v>19</v>
+      </c>
+      <c r="AT97" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU97" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV97" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW97" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX97" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="98" spans="1:50">
+      <c r="A98" t="s">
+        <v>113</v>
+      </c>
+      <c r="B98" t="s">
+        <v>51</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E98" s="4">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4">
+        <v>4.18</v>
+      </c>
+      <c r="G98" s="4">
+        <v>-6.58</v>
+      </c>
+      <c r="H98" s="4">
+        <v>27</v>
+      </c>
+      <c r="I98" s="4">
+        <v>55</v>
+      </c>
+      <c r="J98" s="4">
+        <v>82</v>
+      </c>
+      <c r="K98" s="4">
+        <v>0.91</v>
+      </c>
+      <c r="L98" s="5">
+        <v>0.0625</v>
+      </c>
+      <c r="M98" s="4">
+        <v>10259.44</v>
+      </c>
+      <c r="N98" s="4">
+        <v>1081.57</v>
+      </c>
+      <c r="O98" s="4">
+        <v>32.184</v>
+      </c>
+      <c r="P98" s="4">
+        <v>89.4</v>
+      </c>
+      <c r="Q98" s="4">
+        <v>113.99</v>
+      </c>
+      <c r="R98" s="4">
+        <v>12.02</v>
+      </c>
+      <c r="S98" s="4">
+        <v>0.33</v>
+      </c>
+      <c r="T98" s="4">
+        <v>0</v>
+      </c>
+      <c r="U98" s="4">
+        <v>0</v>
+      </c>
+      <c r="V98" s="4">
+        <v>0</v>
+      </c>
+      <c r="W98" s="4">
+        <v>0</v>
+      </c>
+      <c r="X98" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="4">
+        <v>934.2</v>
+      </c>
+      <c r="AG98" s="4">
+        <v>1952.92</v>
+      </c>
+      <c r="AH98" s="4">
+        <v>162.38</v>
+      </c>
+      <c r="AI98" s="4">
+        <v>3354.7</v>
+      </c>
+      <c r="AJ98" s="4">
+        <v>4095.97</v>
+      </c>
+      <c r="AK98" s="4">
+        <v>1658.02</v>
+      </c>
+      <c r="AL98" s="4">
+        <v>710.59</v>
+      </c>
+      <c r="AM98" s="4">
+        <v>278.04</v>
+      </c>
+      <c r="AN98" s="4">
+        <v>13</v>
+      </c>
+      <c r="AO98" s="4">
+        <v>3.09</v>
+      </c>
+      <c r="AP98" s="4">
+        <v>988.63</v>
+      </c>
+      <c r="AQ98" s="4">
+        <v>48</v>
+      </c>
+      <c r="AR98" s="4">
+        <v>10.98</v>
+      </c>
+      <c r="AS98" s="4">
+        <v>163</v>
+      </c>
+      <c r="AT98" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU98" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV98" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW98" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX98" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/GPS_Formativas_2026.xlsx
+++ b/GPS_Formativas_2026.xlsx
@@ -1008,17 +1008,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -12670,148 +12664,148 @@
       <c r="B74" t="s">
         <v>83</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E74" s="4">
-        <v>0</v>
-      </c>
-      <c r="F74" s="4">
+      <c r="E74" s="2">
+        <v>0</v>
+      </c>
+      <c r="F74" s="2">
         <v>3.48</v>
       </c>
-      <c r="G74" s="4">
+      <c r="G74" s="2">
         <v>-4.69</v>
       </c>
-      <c r="H74" s="4">
+      <c r="H74" s="2">
         <v>5</v>
       </c>
-      <c r="I74" s="4">
+      <c r="I74" s="2">
         <v>6</v>
       </c>
-      <c r="J74" s="4">
+      <c r="J74" s="2">
         <v>11</v>
       </c>
-      <c r="K74" s="4">
+      <c r="K74" s="2">
         <v>0.22</v>
       </c>
-      <c r="L74" s="5">
+      <c r="L74" s="3">
         <v>0.0340277777777778</v>
       </c>
-      <c r="M74" s="4">
+      <c r="M74" s="2">
         <v>3306.78</v>
       </c>
-      <c r="N74" s="4">
+      <c r="N74" s="2">
         <v>363.49</v>
       </c>
-      <c r="O74" s="4">
+      <c r="O74" s="2">
         <v>24.624</v>
       </c>
-      <c r="P74" s="4">
+      <c r="P74" s="2">
         <v>68.43</v>
       </c>
-      <c r="Q74" s="4">
+      <c r="Q74" s="2">
         <v>67.49</v>
       </c>
-      <c r="R74" s="4">
+      <c r="R74" s="2">
         <v>7.42</v>
       </c>
-      <c r="S74" s="4">
+      <c r="S74" s="2">
         <v>0.07</v>
       </c>
-      <c r="T74" s="4">
-        <v>0</v>
-      </c>
-      <c r="U74" s="4">
-        <v>0</v>
-      </c>
-      <c r="V74" s="4">
-        <v>0</v>
-      </c>
-      <c r="W74" s="4">
-        <v>0</v>
-      </c>
-      <c r="X74" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y74" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z74" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA74" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB74" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC74" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD74" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE74" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF74" s="4">
+      <c r="T74" s="2">
+        <v>0</v>
+      </c>
+      <c r="U74" s="2">
+        <v>0</v>
+      </c>
+      <c r="V74" s="2">
+        <v>0</v>
+      </c>
+      <c r="W74" s="2">
+        <v>0</v>
+      </c>
+      <c r="X74" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="2">
         <v>289.96</v>
       </c>
-      <c r="AG74" s="4">
+      <c r="AG74" s="2">
         <v>306.62</v>
       </c>
-      <c r="AH74" s="4">
+      <c r="AH74" s="2">
         <v>203.84</v>
       </c>
-      <c r="AI74" s="4">
+      <c r="AI74" s="2">
         <v>1904.33</v>
       </c>
-      <c r="AJ74" s="4">
+      <c r="AJ74" s="2">
         <v>955.25</v>
       </c>
-      <c r="AK74" s="4">
+      <c r="AK74" s="2">
         <v>187.13</v>
       </c>
-      <c r="AL74" s="4">
+      <c r="AL74" s="2">
         <v>56.6</v>
       </c>
-      <c r="AM74" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN74" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO74" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP74" s="4">
+      <c r="AM74" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="2">
         <v>56.6</v>
       </c>
-      <c r="AQ74" s="4">
+      <c r="AQ74" s="2">
         <v>3</v>
       </c>
-      <c r="AR74" s="4">
+      <c r="AR74" s="2">
         <v>1.16</v>
       </c>
-      <c r="AS74" s="4">
+      <c r="AS74" s="2">
         <v>9</v>
       </c>
-      <c r="AT74" s="4" t="s">
+      <c r="AT74" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AU74" s="4" t="s">
+      <c r="AU74" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV74" s="4" t="s">
+      <c r="AV74" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AW74" s="4" t="s">
+      <c r="AW74" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX74" s="4" t="s">
+      <c r="AX74" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -12822,148 +12816,148 @@
       <c r="B75" t="s">
         <v>83</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E75" s="4">
-        <v>0</v>
-      </c>
-      <c r="F75" s="4">
+      <c r="E75" s="2">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2">
         <v>3.55</v>
       </c>
-      <c r="G75" s="4">
+      <c r="G75" s="2">
         <v>-4.64</v>
       </c>
-      <c r="H75" s="4">
+      <c r="H75" s="2">
         <v>13</v>
       </c>
-      <c r="I75" s="4">
+      <c r="I75" s="2">
         <v>17</v>
       </c>
-      <c r="J75" s="4">
+      <c r="J75" s="2">
         <v>30</v>
       </c>
-      <c r="K75" s="4">
+      <c r="K75" s="2">
         <v>0.61</v>
       </c>
-      <c r="L75" s="5">
+      <c r="L75" s="3">
         <v>0.0340277777777778</v>
       </c>
-      <c r="M75" s="4">
+      <c r="M75" s="2">
         <v>3632.66</v>
       </c>
-      <c r="N75" s="4">
+      <c r="N75" s="2">
         <v>382.59</v>
       </c>
-      <c r="O75" s="4">
+      <c r="O75" s="2">
         <v>27.936</v>
       </c>
-      <c r="P75" s="4">
+      <c r="P75" s="2">
         <v>77.55</v>
       </c>
-      <c r="Q75" s="4">
+      <c r="Q75" s="2">
         <v>74.14</v>
       </c>
-      <c r="R75" s="4">
+      <c r="R75" s="2">
         <v>7.81</v>
       </c>
-      <c r="S75" s="4">
+      <c r="S75" s="2">
         <v>0.1</v>
       </c>
-      <c r="T75" s="4">
-        <v>0</v>
-      </c>
-      <c r="U75" s="4">
-        <v>0</v>
-      </c>
-      <c r="V75" s="4">
-        <v>0</v>
-      </c>
-      <c r="W75" s="4">
-        <v>0</v>
-      </c>
-      <c r="X75" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y75" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z75" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA75" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB75" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC75" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD75" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE75" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF75" s="4">
+      <c r="T75" s="2">
+        <v>0</v>
+      </c>
+      <c r="U75" s="2">
+        <v>0</v>
+      </c>
+      <c r="V75" s="2">
+        <v>0</v>
+      </c>
+      <c r="W75" s="2">
+        <v>0</v>
+      </c>
+      <c r="X75" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="2">
         <v>323.86</v>
       </c>
-      <c r="AG75" s="4">
+      <c r="AG75" s="2">
         <v>550.9</v>
       </c>
-      <c r="AH75" s="4">
+      <c r="AH75" s="2">
         <v>187.18</v>
       </c>
-      <c r="AI75" s="4">
+      <c r="AI75" s="2">
         <v>1887.26</v>
       </c>
-      <c r="AJ75" s="4">
+      <c r="AJ75" s="2">
         <v>865.78</v>
       </c>
-      <c r="AK75" s="4">
+      <c r="AK75" s="2">
         <v>448.02</v>
       </c>
-      <c r="AL75" s="4">
+      <c r="AL75" s="2">
         <v>203.75</v>
       </c>
-      <c r="AM75" s="4">
+      <c r="AM75" s="2">
         <v>40.56</v>
       </c>
-      <c r="AN75" s="4">
+      <c r="AN75" s="2">
         <v>2</v>
       </c>
-      <c r="AO75" s="4">
+      <c r="AO75" s="2">
         <v>0.83</v>
       </c>
-      <c r="AP75" s="4">
+      <c r="AP75" s="2">
         <v>244.31</v>
       </c>
-      <c r="AQ75" s="4">
+      <c r="AQ75" s="2">
         <v>13</v>
       </c>
-      <c r="AR75" s="4">
+      <c r="AR75" s="2">
         <v>4.99</v>
       </c>
-      <c r="AS75" s="4">
+      <c r="AS75" s="2">
         <v>18</v>
       </c>
-      <c r="AT75" s="4" t="s">
+      <c r="AT75" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AU75" s="4" t="s">
+      <c r="AU75" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV75" s="4" t="s">
+      <c r="AV75" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AW75" s="4" t="s">
+      <c r="AW75" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX75" s="4" t="s">
+      <c r="AX75" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -12974,148 +12968,148 @@
       <c r="B76" t="s">
         <v>83</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E76" s="4">
-        <v>0</v>
-      </c>
-      <c r="F76" s="4">
+      <c r="E76" s="2">
+        <v>0</v>
+      </c>
+      <c r="F76" s="2">
         <v>3.34</v>
       </c>
-      <c r="G76" s="4">
+      <c r="G76" s="2">
         <v>-3.91</v>
       </c>
-      <c r="H76" s="4">
+      <c r="H76" s="2">
         <v>3</v>
       </c>
-      <c r="I76" s="4">
+      <c r="I76" s="2">
         <v>6</v>
       </c>
-      <c r="J76" s="4">
+      <c r="J76" s="2">
         <v>9</v>
       </c>
-      <c r="K76" s="4">
+      <c r="K76" s="2">
         <v>0.18</v>
       </c>
-      <c r="L76" s="5">
+      <c r="L76" s="3">
         <v>0.0340277777777778</v>
       </c>
-      <c r="M76" s="4">
+      <c r="M76" s="2">
         <v>3756.41</v>
       </c>
-      <c r="N76" s="4">
+      <c r="N76" s="2">
         <v>414.89</v>
       </c>
-      <c r="O76" s="4">
+      <c r="O76" s="2">
         <v>23.4</v>
       </c>
-      <c r="P76" s="4">
+      <c r="P76" s="2">
         <v>64.96</v>
       </c>
-      <c r="Q76" s="4">
+      <c r="Q76" s="2">
         <v>76.66</v>
       </c>
-      <c r="R76" s="4">
+      <c r="R76" s="2">
         <v>8.47</v>
       </c>
-      <c r="S76" s="4">
+      <c r="S76" s="2">
         <v>0.09</v>
       </c>
-      <c r="T76" s="4">
-        <v>0</v>
-      </c>
-      <c r="U76" s="4">
-        <v>0</v>
-      </c>
-      <c r="V76" s="4">
-        <v>0</v>
-      </c>
-      <c r="W76" s="4">
-        <v>0</v>
-      </c>
-      <c r="X76" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y76" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z76" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB76" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC76" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD76" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE76" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF76" s="4">
+      <c r="T76" s="2">
+        <v>0</v>
+      </c>
+      <c r="U76" s="2">
+        <v>0</v>
+      </c>
+      <c r="V76" s="2">
+        <v>0</v>
+      </c>
+      <c r="W76" s="2">
+        <v>0</v>
+      </c>
+      <c r="X76" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="2">
         <v>327.76</v>
       </c>
-      <c r="AG76" s="4">
+      <c r="AG76" s="2">
         <v>353.35</v>
       </c>
-      <c r="AH76" s="4">
+      <c r="AH76" s="2">
         <v>158.74</v>
       </c>
-      <c r="AI76" s="4">
+      <c r="AI76" s="2">
         <v>2053.49</v>
       </c>
-      <c r="AJ76" s="4">
+      <c r="AJ76" s="2">
         <v>1206.24</v>
       </c>
-      <c r="AK76" s="4">
+      <c r="AK76" s="2">
         <v>307.08</v>
       </c>
-      <c r="AL76" s="4">
+      <c r="AL76" s="2">
         <v>30.9</v>
       </c>
-      <c r="AM76" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN76" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO76" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP76" s="4">
+      <c r="AM76" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP76" s="2">
         <v>30.9</v>
       </c>
-      <c r="AQ76" s="4">
+      <c r="AQ76" s="2">
         <v>2</v>
       </c>
-      <c r="AR76" s="4">
+      <c r="AR76" s="2">
         <v>0.63</v>
       </c>
-      <c r="AS76" s="4">
+      <c r="AS76" s="2">
         <v>19</v>
       </c>
-      <c r="AT76" s="4" t="s">
+      <c r="AT76" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AU76" s="4" t="s">
+      <c r="AU76" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV76" s="4" t="s">
+      <c r="AV76" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AW76" s="4" t="s">
+      <c r="AW76" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX76" s="4" t="s">
+      <c r="AX76" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -13126,148 +13120,148 @@
       <c r="B77" t="s">
         <v>83</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D77" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E77" s="4">
-        <v>0</v>
-      </c>
-      <c r="F77" s="4">
+      <c r="E77" s="2">
+        <v>0</v>
+      </c>
+      <c r="F77" s="2">
         <v>4.2</v>
       </c>
-      <c r="G77" s="4">
+      <c r="G77" s="2">
         <v>-3.54</v>
       </c>
-      <c r="H77" s="4">
+      <c r="H77" s="2">
         <v>7</v>
       </c>
-      <c r="I77" s="4">
+      <c r="I77" s="2">
         <v>7</v>
       </c>
-      <c r="J77" s="4">
+      <c r="J77" s="2">
         <v>14</v>
       </c>
-      <c r="K77" s="4">
+      <c r="K77" s="2">
         <v>0.29</v>
       </c>
-      <c r="L77" s="5">
+      <c r="L77" s="3">
         <v>0.0340277777777778</v>
       </c>
-      <c r="M77" s="4">
+      <c r="M77" s="2">
         <v>3383.36</v>
       </c>
-      <c r="N77" s="4">
+      <c r="N77" s="2">
         <v>436.65</v>
       </c>
-      <c r="O77" s="4">
+      <c r="O77" s="2">
         <v>29.664</v>
       </c>
-      <c r="P77" s="4">
+      <c r="P77" s="2">
         <v>82.42</v>
       </c>
-      <c r="Q77" s="4">
+      <c r="Q77" s="2">
         <v>69.05</v>
       </c>
-      <c r="R77" s="4">
+      <c r="R77" s="2">
         <v>8.91</v>
       </c>
-      <c r="S77" s="4">
+      <c r="S77" s="2">
         <v>0.07</v>
       </c>
-      <c r="T77" s="4">
-        <v>0</v>
-      </c>
-      <c r="U77" s="4">
-        <v>0</v>
-      </c>
-      <c r="V77" s="4">
-        <v>0</v>
-      </c>
-      <c r="W77" s="4">
-        <v>0</v>
-      </c>
-      <c r="X77" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y77" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z77" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA77" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB77" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC77" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD77" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE77" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF77" s="4">
+      <c r="T77" s="2">
+        <v>0</v>
+      </c>
+      <c r="U77" s="2">
+        <v>0</v>
+      </c>
+      <c r="V77" s="2">
+        <v>0</v>
+      </c>
+      <c r="W77" s="2">
+        <v>0</v>
+      </c>
+      <c r="X77" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="2">
         <v>288.99</v>
       </c>
-      <c r="AG77" s="4">
+      <c r="AG77" s="2">
         <v>342.1</v>
       </c>
-      <c r="AH77" s="4">
+      <c r="AH77" s="2">
         <v>230.89</v>
       </c>
-      <c r="AI77" s="4">
+      <c r="AI77" s="2">
         <v>2077.79</v>
       </c>
-      <c r="AJ77" s="4">
+      <c r="AJ77" s="2">
         <v>623.6</v>
       </c>
-      <c r="AK77" s="4">
+      <c r="AK77" s="2">
         <v>298.57</v>
       </c>
-      <c r="AL77" s="4">
+      <c r="AL77" s="2">
         <v>126.97</v>
       </c>
-      <c r="AM77" s="4">
+      <c r="AM77" s="2">
         <v>25.54</v>
       </c>
-      <c r="AN77" s="4">
+      <c r="AN77" s="2">
         <v>1</v>
       </c>
-      <c r="AO77" s="4">
+      <c r="AO77" s="2">
         <v>0.52</v>
       </c>
-      <c r="AP77" s="4">
+      <c r="AP77" s="2">
         <v>152.51</v>
       </c>
-      <c r="AQ77" s="4">
+      <c r="AQ77" s="2">
         <v>7</v>
       </c>
-      <c r="AR77" s="4">
+      <c r="AR77" s="2">
         <v>3.11</v>
       </c>
-      <c r="AS77" s="4">
+      <c r="AS77" s="2">
         <v>71</v>
       </c>
-      <c r="AT77" s="4" t="s">
+      <c r="AT77" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AU77" s="4" t="s">
+      <c r="AU77" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV77" s="4" t="s">
+      <c r="AV77" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AW77" s="4" t="s">
+      <c r="AW77" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX77" s="4" t="s">
+      <c r="AX77" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -13278,148 +13272,148 @@
       <c r="B78" t="s">
         <v>83</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E78" s="4">
-        <v>0</v>
-      </c>
-      <c r="F78" s="4">
+      <c r="E78" s="2">
+        <v>0</v>
+      </c>
+      <c r="F78" s="2">
         <v>3.25</v>
       </c>
-      <c r="G78" s="4">
+      <c r="G78" s="2">
         <v>-3.54</v>
       </c>
-      <c r="H78" s="4">
+      <c r="H78" s="2">
         <v>1</v>
       </c>
-      <c r="I78" s="4">
+      <c r="I78" s="2">
         <v>4</v>
       </c>
-      <c r="J78" s="4">
+      <c r="J78" s="2">
         <v>5</v>
       </c>
-      <c r="K78" s="4">
+      <c r="K78" s="2">
         <v>0.1</v>
       </c>
-      <c r="L78" s="5">
+      <c r="L78" s="3">
         <v>0.0340277777777778</v>
       </c>
-      <c r="M78" s="4">
+      <c r="M78" s="2">
         <v>2959.97</v>
       </c>
-      <c r="N78" s="4">
+      <c r="N78" s="2">
         <v>306.69</v>
       </c>
-      <c r="O78" s="4">
+      <c r="O78" s="2">
         <v>23.616</v>
       </c>
-      <c r="P78" s="4">
+      <c r="P78" s="2">
         <v>65.6</v>
       </c>
-      <c r="Q78" s="4">
+      <c r="Q78" s="2">
         <v>60.41</v>
       </c>
-      <c r="R78" s="4">
+      <c r="R78" s="2">
         <v>6.26</v>
       </c>
-      <c r="S78" s="4">
+      <c r="S78" s="2">
         <v>0.05</v>
       </c>
-      <c r="T78" s="4">
-        <v>0</v>
-      </c>
-      <c r="U78" s="4">
-        <v>0</v>
-      </c>
-      <c r="V78" s="4">
-        <v>0</v>
-      </c>
-      <c r="W78" s="4">
-        <v>0</v>
-      </c>
-      <c r="X78" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y78" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z78" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB78" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC78" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD78" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE78" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF78" s="4">
+      <c r="T78" s="2">
+        <v>0</v>
+      </c>
+      <c r="U78" s="2">
+        <v>0</v>
+      </c>
+      <c r="V78" s="2">
+        <v>0</v>
+      </c>
+      <c r="W78" s="2">
+        <v>0</v>
+      </c>
+      <c r="X78" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="2">
         <v>250.89</v>
       </c>
-      <c r="AG78" s="4">
+      <c r="AG78" s="2">
         <v>222.39</v>
       </c>
-      <c r="AH78" s="4">
+      <c r="AH78" s="2">
         <v>245.63</v>
       </c>
-      <c r="AI78" s="4">
+      <c r="AI78" s="2">
         <v>1827.01</v>
       </c>
-      <c r="AJ78" s="4">
+      <c r="AJ78" s="2">
         <v>665.12</v>
       </c>
-      <c r="AK78" s="4">
+      <c r="AK78" s="2">
         <v>175.54</v>
       </c>
-      <c r="AL78" s="4">
+      <c r="AL78" s="2">
         <v>47.19</v>
       </c>
-      <c r="AM78" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN78" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO78" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP78" s="4">
+      <c r="AM78" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN78" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO78" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP78" s="2">
         <v>47.19</v>
       </c>
-      <c r="AQ78" s="4">
+      <c r="AQ78" s="2">
         <v>4</v>
       </c>
-      <c r="AR78" s="4">
+      <c r="AR78" s="2">
         <v>0.96</v>
       </c>
-      <c r="AS78" s="4">
+      <c r="AS78" s="2">
         <v>4</v>
       </c>
-      <c r="AT78" s="4" t="s">
+      <c r="AT78" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AU78" s="4" t="s">
+      <c r="AU78" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV78" s="4" t="s">
+      <c r="AV78" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AW78" s="4" t="s">
+      <c r="AW78" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX78" s="4" t="s">
+      <c r="AX78" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -13430,148 +13424,148 @@
       <c r="B79" t="s">
         <v>83</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="D79" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E79" s="4">
-        <v>0</v>
-      </c>
-      <c r="F79" s="4">
+      <c r="E79" s="2">
+        <v>0</v>
+      </c>
+      <c r="F79" s="2">
         <v>3.56</v>
       </c>
-      <c r="G79" s="4">
+      <c r="G79" s="2">
         <v>-4.24</v>
       </c>
-      <c r="H79" s="4">
+      <c r="H79" s="2">
         <v>13</v>
       </c>
-      <c r="I79" s="4">
+      <c r="I79" s="2">
         <v>9</v>
       </c>
-      <c r="J79" s="4">
+      <c r="J79" s="2">
         <v>22</v>
       </c>
-      <c r="K79" s="4">
+      <c r="K79" s="2">
         <v>0.45</v>
       </c>
-      <c r="L79" s="5">
+      <c r="L79" s="3">
         <v>0.0340277777777778</v>
       </c>
-      <c r="M79" s="4">
+      <c r="M79" s="2">
         <v>3059.17</v>
       </c>
-      <c r="N79" s="4">
+      <c r="N79" s="2">
         <v>376.07</v>
       </c>
-      <c r="O79" s="4">
+      <c r="O79" s="2">
         <v>27.72</v>
       </c>
-      <c r="P79" s="4">
+      <c r="P79" s="2">
         <v>77.04</v>
       </c>
-      <c r="Q79" s="4">
+      <c r="Q79" s="2">
         <v>62.43</v>
       </c>
-      <c r="R79" s="4">
+      <c r="R79" s="2">
         <v>7.67</v>
       </c>
-      <c r="S79" s="4">
+      <c r="S79" s="2">
         <v>0.06</v>
       </c>
-      <c r="T79" s="4">
-        <v>0</v>
-      </c>
-      <c r="U79" s="4">
-        <v>0</v>
-      </c>
-      <c r="V79" s="4">
-        <v>0</v>
-      </c>
-      <c r="W79" s="4">
-        <v>0</v>
-      </c>
-      <c r="X79" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y79" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z79" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA79" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB79" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC79" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD79" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE79" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF79" s="4">
+      <c r="T79" s="2">
+        <v>0</v>
+      </c>
+      <c r="U79" s="2">
+        <v>0</v>
+      </c>
+      <c r="V79" s="2">
+        <v>0</v>
+      </c>
+      <c r="W79" s="2">
+        <v>0</v>
+      </c>
+      <c r="X79" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="2">
         <v>269.6</v>
       </c>
-      <c r="AG79" s="4">
+      <c r="AG79" s="2">
         <v>395.61</v>
       </c>
-      <c r="AH79" s="4">
+      <c r="AH79" s="2">
         <v>200.85</v>
       </c>
-      <c r="AI79" s="4">
+      <c r="AI79" s="2">
         <v>1728.94</v>
       </c>
-      <c r="AJ79" s="4">
+      <c r="AJ79" s="2">
         <v>719.75</v>
       </c>
-      <c r="AK79" s="4">
+      <c r="AK79" s="2">
         <v>267.96</v>
       </c>
-      <c r="AL79" s="4">
+      <c r="AL79" s="2">
         <v>107.94</v>
       </c>
-      <c r="AM79" s="4">
+      <c r="AM79" s="2">
         <v>34.02</v>
       </c>
-      <c r="AN79" s="4">
+      <c r="AN79" s="2">
         <v>2</v>
       </c>
-      <c r="AO79" s="4">
+      <c r="AO79" s="2">
         <v>0.69</v>
       </c>
-      <c r="AP79" s="4">
+      <c r="AP79" s="2">
         <v>141.96</v>
       </c>
-      <c r="AQ79" s="4">
+      <c r="AQ79" s="2">
         <v>5</v>
       </c>
-      <c r="AR79" s="4">
+      <c r="AR79" s="2">
         <v>2.9</v>
       </c>
-      <c r="AS79" s="4">
+      <c r="AS79" s="2">
         <v>28</v>
       </c>
-      <c r="AT79" s="4" t="s">
+      <c r="AT79" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AU79" s="4" t="s">
+      <c r="AU79" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV79" s="4" t="s">
+      <c r="AV79" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AW79" s="4" t="s">
+      <c r="AW79" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX79" s="4" t="s">
+      <c r="AX79" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -13582,148 +13576,148 @@
       <c r="B80" t="s">
         <v>83</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="D80" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E80" s="4">
-        <v>0</v>
-      </c>
-      <c r="F80" s="4">
+      <c r="E80" s="2">
+        <v>0</v>
+      </c>
+      <c r="F80" s="2">
         <v>3.7</v>
       </c>
-      <c r="G80" s="4">
+      <c r="G80" s="2">
         <v>-3.98</v>
       </c>
-      <c r="H80" s="4">
+      <c r="H80" s="2">
         <v>14</v>
       </c>
-      <c r="I80" s="4">
+      <c r="I80" s="2">
         <v>13</v>
       </c>
-      <c r="J80" s="4">
+      <c r="J80" s="2">
         <v>27</v>
       </c>
-      <c r="K80" s="4">
+      <c r="K80" s="2">
         <v>0.55</v>
       </c>
-      <c r="L80" s="5">
+      <c r="L80" s="3">
         <v>0.0340277777777778</v>
       </c>
-      <c r="M80" s="4">
+      <c r="M80" s="2">
         <v>3178.57</v>
       </c>
-      <c r="N80" s="4">
+      <c r="N80" s="2">
         <v>340.67</v>
       </c>
-      <c r="O80" s="4">
+      <c r="O80" s="2">
         <v>24.264</v>
       </c>
-      <c r="P80" s="4">
+      <c r="P80" s="2">
         <v>67.4</v>
       </c>
-      <c r="Q80" s="4">
+      <c r="Q80" s="2">
         <v>64.87</v>
       </c>
-      <c r="R80" s="4">
+      <c r="R80" s="2">
         <v>6.95</v>
       </c>
-      <c r="S80" s="4">
+      <c r="S80" s="2">
         <v>0.08</v>
       </c>
-      <c r="T80" s="4">
-        <v>0</v>
-      </c>
-      <c r="U80" s="4">
-        <v>0</v>
-      </c>
-      <c r="V80" s="4">
-        <v>0</v>
-      </c>
-      <c r="W80" s="4">
-        <v>0</v>
-      </c>
-      <c r="X80" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y80" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z80" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB80" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC80" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD80" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE80" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF80" s="4">
+      <c r="T80" s="2">
+        <v>0</v>
+      </c>
+      <c r="U80" s="2">
+        <v>0</v>
+      </c>
+      <c r="V80" s="2">
+        <v>0</v>
+      </c>
+      <c r="W80" s="2">
+        <v>0</v>
+      </c>
+      <c r="X80" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="2">
         <v>284.03</v>
       </c>
-      <c r="AG80" s="4">
+      <c r="AG80" s="2">
         <v>417.69</v>
       </c>
-      <c r="AH80" s="4">
+      <c r="AH80" s="2">
         <v>190.12</v>
       </c>
-      <c r="AI80" s="4">
+      <c r="AI80" s="2">
         <v>1690.19</v>
       </c>
-      <c r="AJ80" s="4">
+      <c r="AJ80" s="2">
         <v>935.83</v>
       </c>
-      <c r="AK80" s="4">
+      <c r="AK80" s="2">
         <v>264.42</v>
       </c>
-      <c r="AL80" s="4">
+      <c r="AL80" s="2">
         <v>98.27</v>
       </c>
-      <c r="AM80" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN80" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO80" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP80" s="4">
+      <c r="AM80" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN80" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO80" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP80" s="2">
         <v>98.27</v>
       </c>
-      <c r="AQ80" s="4">
+      <c r="AQ80" s="2">
         <v>5</v>
       </c>
-      <c r="AR80" s="4">
+      <c r="AR80" s="2">
         <v>2.01</v>
       </c>
-      <c r="AS80" s="4">
+      <c r="AS80" s="2">
         <v>15</v>
       </c>
-      <c r="AT80" s="4" t="s">
+      <c r="AT80" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AU80" s="4" t="s">
+      <c r="AU80" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV80" s="4" t="s">
+      <c r="AV80" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AW80" s="4" t="s">
+      <c r="AW80" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX80" s="4" t="s">
+      <c r="AX80" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -13734,148 +13728,148 @@
       <c r="B81" t="s">
         <v>83</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D81" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E81" s="4">
-        <v>0</v>
-      </c>
-      <c r="F81" s="4">
+      <c r="E81" s="2">
+        <v>0</v>
+      </c>
+      <c r="F81" s="2">
         <v>3.58</v>
       </c>
-      <c r="G81" s="4">
+      <c r="G81" s="2">
         <v>-4.49</v>
       </c>
-      <c r="H81" s="4">
+      <c r="H81" s="2">
         <v>4</v>
       </c>
-      <c r="I81" s="4">
+      <c r="I81" s="2">
         <v>7</v>
       </c>
-      <c r="J81" s="4">
+      <c r="J81" s="2">
         <v>11</v>
       </c>
-      <c r="K81" s="4">
+      <c r="K81" s="2">
         <v>0.22</v>
       </c>
-      <c r="L81" s="5">
+      <c r="L81" s="3">
         <v>0.0340277777777778</v>
       </c>
-      <c r="M81" s="4">
+      <c r="M81" s="2">
         <v>3767.51</v>
       </c>
-      <c r="N81" s="4">
+      <c r="N81" s="2">
         <v>516.03</v>
       </c>
-      <c r="O81" s="4">
+      <c r="O81" s="2">
         <v>23.328</v>
       </c>
-      <c r="P81" s="4">
+      <c r="P81" s="2">
         <v>64.77</v>
       </c>
-      <c r="Q81" s="4">
+      <c r="Q81" s="2">
         <v>76.89</v>
       </c>
-      <c r="R81" s="4">
+      <c r="R81" s="2">
         <v>10.53</v>
       </c>
-      <c r="S81" s="4">
+      <c r="S81" s="2">
         <v>0.12</v>
       </c>
-      <c r="T81" s="4">
-        <v>0</v>
-      </c>
-      <c r="U81" s="4">
-        <v>0</v>
-      </c>
-      <c r="V81" s="4">
-        <v>0</v>
-      </c>
-      <c r="W81" s="4">
-        <v>0</v>
-      </c>
-      <c r="X81" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y81" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z81" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA81" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB81" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC81" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD81" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE81" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF81" s="4">
+      <c r="T81" s="2">
+        <v>0</v>
+      </c>
+      <c r="U81" s="2">
+        <v>0</v>
+      </c>
+      <c r="V81" s="2">
+        <v>0</v>
+      </c>
+      <c r="W81" s="2">
+        <v>0</v>
+      </c>
+      <c r="X81" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="2">
         <v>330.97</v>
       </c>
-      <c r="AG81" s="4">
+      <c r="AG81" s="2">
         <v>445.24</v>
       </c>
-      <c r="AH81" s="4">
+      <c r="AH81" s="2">
         <v>200.23</v>
       </c>
-      <c r="AI81" s="4">
+      <c r="AI81" s="2">
         <v>1691.4</v>
       </c>
-      <c r="AJ81" s="4">
+      <c r="AJ81" s="2">
         <v>1291.52</v>
       </c>
-      <c r="AK81" s="4">
+      <c r="AK81" s="2">
         <v>500.56</v>
       </c>
-      <c r="AL81" s="4">
+      <c r="AL81" s="2">
         <v>83.88</v>
       </c>
-      <c r="AM81" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN81" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO81" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP81" s="4">
+      <c r="AM81" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN81" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO81" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP81" s="2">
         <v>83.88</v>
       </c>
-      <c r="AQ81" s="4">
+      <c r="AQ81" s="2">
         <v>6</v>
       </c>
-      <c r="AR81" s="4">
+      <c r="AR81" s="2">
         <v>1.71</v>
       </c>
-      <c r="AS81" s="4">
+      <c r="AS81" s="2">
         <v>44</v>
       </c>
-      <c r="AT81" s="4" t="s">
+      <c r="AT81" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AU81" s="4" t="s">
+      <c r="AU81" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV81" s="4" t="s">
+      <c r="AV81" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AW81" s="4" t="s">
+      <c r="AW81" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX81" s="4" t="s">
+      <c r="AX81" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -13886,148 +13880,148 @@
       <c r="B82" t="s">
         <v>83</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="C82" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="D82" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E82" s="4">
-        <v>0</v>
-      </c>
-      <c r="F82" s="4">
+      <c r="E82" s="2">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2">
         <v>3.9</v>
       </c>
-      <c r="G82" s="4">
+      <c r="G82" s="2">
         <v>-4.25</v>
       </c>
-      <c r="H82" s="4">
+      <c r="H82" s="2">
         <v>8</v>
       </c>
-      <c r="I82" s="4">
+      <c r="I82" s="2">
         <v>11</v>
       </c>
-      <c r="J82" s="4">
+      <c r="J82" s="2">
         <v>19</v>
       </c>
-      <c r="K82" s="4">
+      <c r="K82" s="2">
         <v>0.39</v>
       </c>
-      <c r="L82" s="5">
+      <c r="L82" s="3">
         <v>0.0340277777777778</v>
       </c>
-      <c r="M82" s="4">
+      <c r="M82" s="2">
         <v>3300.45</v>
       </c>
-      <c r="N82" s="4">
+      <c r="N82" s="2">
         <v>378.45</v>
       </c>
-      <c r="O82" s="4">
+      <c r="O82" s="2">
         <v>26.856</v>
       </c>
-      <c r="P82" s="4">
+      <c r="P82" s="2">
         <v>74.63</v>
       </c>
-      <c r="Q82" s="4">
+      <c r="Q82" s="2">
         <v>67.36</v>
       </c>
-      <c r="R82" s="4">
+      <c r="R82" s="2">
         <v>7.72</v>
       </c>
-      <c r="S82" s="4">
+      <c r="S82" s="2">
         <v>0.09</v>
       </c>
-      <c r="T82" s="4">
-        <v>0</v>
-      </c>
-      <c r="U82" s="4">
-        <v>0</v>
-      </c>
-      <c r="V82" s="4">
-        <v>0</v>
-      </c>
-      <c r="W82" s="4">
-        <v>0</v>
-      </c>
-      <c r="X82" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y82" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z82" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA82" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB82" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC82" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD82" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE82" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF82" s="4">
+      <c r="T82" s="2">
+        <v>0</v>
+      </c>
+      <c r="U82" s="2">
+        <v>0</v>
+      </c>
+      <c r="V82" s="2">
+        <v>0</v>
+      </c>
+      <c r="W82" s="2">
+        <v>0</v>
+      </c>
+      <c r="X82" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB82" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD82" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="2">
         <v>294.21</v>
       </c>
-      <c r="AG82" s="4">
+      <c r="AG82" s="2">
         <v>423.02</v>
       </c>
-      <c r="AH82" s="4">
+      <c r="AH82" s="2">
         <v>163.37</v>
       </c>
-      <c r="AI82" s="4">
+      <c r="AI82" s="2">
         <v>1758.53</v>
       </c>
-      <c r="AJ82" s="4">
+      <c r="AJ82" s="2">
         <v>971.19</v>
       </c>
-      <c r="AK82" s="4">
+      <c r="AK82" s="2">
         <v>258.9</v>
       </c>
-      <c r="AL82" s="4">
+      <c r="AL82" s="2">
         <v>140.02</v>
       </c>
-      <c r="AM82" s="4">
+      <c r="AM82" s="2">
         <v>8.37</v>
       </c>
-      <c r="AN82" s="4">
+      <c r="AN82" s="2">
         <v>1</v>
       </c>
-      <c r="AO82" s="4">
+      <c r="AO82" s="2">
         <v>0.17</v>
       </c>
-      <c r="AP82" s="4">
+      <c r="AP82" s="2">
         <v>148.39</v>
       </c>
-      <c r="AQ82" s="4">
+      <c r="AQ82" s="2">
         <v>9</v>
       </c>
-      <c r="AR82" s="4">
+      <c r="AR82" s="2">
         <v>3.03</v>
       </c>
-      <c r="AS82" s="4">
+      <c r="AS82" s="2">
         <v>56</v>
       </c>
-      <c r="AT82" s="4" t="s">
+      <c r="AT82" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AU82" s="4" t="s">
+      <c r="AU82" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV82" s="4" t="s">
+      <c r="AV82" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AW82" s="4" t="s">
+      <c r="AW82" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX82" s="4" t="s">
+      <c r="AX82" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -14038,148 +14032,148 @@
       <c r="B83" t="s">
         <v>83</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D83" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E83" s="4">
-        <v>0</v>
-      </c>
-      <c r="F83" s="4">
+      <c r="E83" s="2">
+        <v>0</v>
+      </c>
+      <c r="F83" s="2">
         <v>3.78</v>
       </c>
-      <c r="G83" s="4">
+      <c r="G83" s="2">
         <v>-3.44</v>
       </c>
-      <c r="H83" s="4">
+      <c r="H83" s="2">
         <v>8</v>
       </c>
-      <c r="I83" s="4">
+      <c r="I83" s="2">
         <v>3</v>
       </c>
-      <c r="J83" s="4">
+      <c r="J83" s="2">
         <v>11</v>
       </c>
-      <c r="K83" s="4">
+      <c r="K83" s="2">
         <v>0.22</v>
       </c>
-      <c r="L83" s="5">
+      <c r="L83" s="3">
         <v>0.0340277777777778</v>
       </c>
-      <c r="M83" s="4">
+      <c r="M83" s="2">
         <v>3501.92</v>
       </c>
-      <c r="N83" s="4">
+      <c r="N83" s="2">
         <v>457.68</v>
       </c>
-      <c r="O83" s="4">
+      <c r="O83" s="2">
         <v>22.248</v>
       </c>
-      <c r="P83" s="4">
+      <c r="P83" s="2">
         <v>61.77</v>
       </c>
-      <c r="Q83" s="4">
+      <c r="Q83" s="2">
         <v>71.47</v>
       </c>
-      <c r="R83" s="4">
+      <c r="R83" s="2">
         <v>9.34</v>
       </c>
-      <c r="S83" s="4">
+      <c r="S83" s="2">
         <v>0.09</v>
       </c>
-      <c r="T83" s="4">
-        <v>0</v>
-      </c>
-      <c r="U83" s="4">
-        <v>0</v>
-      </c>
-      <c r="V83" s="4">
-        <v>0</v>
-      </c>
-      <c r="W83" s="4">
-        <v>0</v>
-      </c>
-      <c r="X83" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA83" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB83" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC83" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD83" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE83" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF83" s="4">
+      <c r="T83" s="2">
+        <v>0</v>
+      </c>
+      <c r="U83" s="2">
+        <v>0</v>
+      </c>
+      <c r="V83" s="2">
+        <v>0</v>
+      </c>
+      <c r="W83" s="2">
+        <v>0</v>
+      </c>
+      <c r="X83" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="2">
         <v>307.78</v>
       </c>
-      <c r="AG83" s="4">
+      <c r="AG83" s="2">
         <v>365.72</v>
       </c>
-      <c r="AH83" s="4">
+      <c r="AH83" s="2">
         <v>190.1</v>
       </c>
-      <c r="AI83" s="4">
+      <c r="AI83" s="2">
         <v>1911.84</v>
       </c>
-      <c r="AJ83" s="4">
+      <c r="AJ83" s="2">
         <v>1076.51</v>
       </c>
-      <c r="AK83" s="4">
+      <c r="AK83" s="2">
         <v>281.57</v>
       </c>
-      <c r="AL83" s="4">
+      <c r="AL83" s="2">
         <v>41.71</v>
       </c>
-      <c r="AM83" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN83" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO83" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP83" s="4">
+      <c r="AM83" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN83" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO83" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP83" s="2">
         <v>41.71</v>
       </c>
-      <c r="AQ83" s="4">
+      <c r="AQ83" s="2">
         <v>4</v>
       </c>
-      <c r="AR83" s="4">
+      <c r="AR83" s="2">
         <v>0.85</v>
       </c>
-      <c r="AS83" s="4">
+      <c r="AS83" s="2">
         <v>113</v>
       </c>
-      <c r="AT83" s="4" t="s">
+      <c r="AT83" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AU83" s="4" t="s">
+      <c r="AU83" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV83" s="4" t="s">
+      <c r="AV83" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AW83" s="4" t="s">
+      <c r="AW83" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX83" s="4" t="s">
+      <c r="AX83" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -14190,148 +14184,148 @@
       <c r="B84" t="s">
         <v>51</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C84" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="D84" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E84" s="4">
-        <v>0</v>
-      </c>
-      <c r="F84" s="4">
+      <c r="E84" s="2">
+        <v>0</v>
+      </c>
+      <c r="F84" s="2">
         <v>4.12</v>
       </c>
-      <c r="G84" s="4">
+      <c r="G84" s="2">
         <v>-5.18</v>
       </c>
-      <c r="H84" s="4">
+      <c r="H84" s="2">
         <v>22</v>
       </c>
-      <c r="I84" s="4">
+      <c r="I84" s="2">
         <v>44</v>
       </c>
-      <c r="J84" s="4">
+      <c r="J84" s="2">
         <v>66</v>
       </c>
-      <c r="K84" s="4">
+      <c r="K84" s="2">
         <v>0.79</v>
       </c>
-      <c r="L84" s="5">
+      <c r="L84" s="3">
         <v>0.0583333333333333</v>
       </c>
-      <c r="M84" s="4">
+      <c r="M84" s="2">
         <v>9806.75</v>
       </c>
-      <c r="N84" s="4">
+      <c r="N84" s="2">
         <v>1210.84</v>
       </c>
-      <c r="O84" s="4">
+      <c r="O84" s="2">
         <v>27.72</v>
       </c>
-      <c r="P84" s="4">
+      <c r="P84" s="2">
         <v>76.97</v>
       </c>
-      <c r="Q84" s="4">
+      <c r="Q84" s="2">
         <v>116.75</v>
       </c>
-      <c r="R84" s="4">
+      <c r="R84" s="2">
         <v>14.41</v>
       </c>
-      <c r="S84" s="4">
+      <c r="S84" s="2">
         <v>0.38</v>
       </c>
-      <c r="T84" s="4">
-        <v>0</v>
-      </c>
-      <c r="U84" s="4">
-        <v>0</v>
-      </c>
-      <c r="V84" s="4">
-        <v>0</v>
-      </c>
-      <c r="W84" s="4">
-        <v>0</v>
-      </c>
-      <c r="X84" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y84" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z84" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA84" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB84" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC84" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD84" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE84" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF84" s="4">
+      <c r="T84" s="2">
+        <v>0</v>
+      </c>
+      <c r="U84" s="2">
+        <v>0</v>
+      </c>
+      <c r="V84" s="2">
+        <v>0</v>
+      </c>
+      <c r="W84" s="2">
+        <v>0</v>
+      </c>
+      <c r="X84" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="2">
         <v>877.54</v>
       </c>
-      <c r="AG84" s="4">
+      <c r="AG84" s="2">
         <v>1762.57</v>
       </c>
-      <c r="AH84" s="4">
+      <c r="AH84" s="2">
         <v>158.05</v>
       </c>
-      <c r="AI84" s="4">
+      <c r="AI84" s="2">
         <v>2993.91</v>
       </c>
-      <c r="AJ84" s="4">
+      <c r="AJ84" s="2">
         <v>4144.9</v>
       </c>
-      <c r="AK84" s="4">
+      <c r="AK84" s="2">
         <v>2031.68</v>
       </c>
-      <c r="AL84" s="4">
+      <c r="AL84" s="2">
         <v>441.08</v>
       </c>
-      <c r="AM84" s="4">
+      <c r="AM84" s="2">
         <v>37.4</v>
       </c>
-      <c r="AN84" s="4">
+      <c r="AN84" s="2">
         <v>3</v>
       </c>
-      <c r="AO84" s="4">
+      <c r="AO84" s="2">
         <v>0.45</v>
       </c>
-      <c r="AP84" s="4">
+      <c r="AP84" s="2">
         <v>478.48</v>
       </c>
-      <c r="AQ84" s="4">
+      <c r="AQ84" s="2">
         <v>24</v>
       </c>
-      <c r="AR84" s="4">
+      <c r="AR84" s="2">
         <v>5.7</v>
       </c>
-      <c r="AS84" s="4">
+      <c r="AS84" s="2">
         <v>90</v>
       </c>
-      <c r="AT84" s="4" t="s">
+      <c r="AT84" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AU84" s="4" t="s">
+      <c r="AU84" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV84" s="4" t="s">
+      <c r="AV84" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AW84" s="4" t="s">
+      <c r="AW84" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX84" s="4" t="s">
+      <c r="AX84" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -14342,148 +14336,148 @@
       <c r="B85" t="s">
         <v>51</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E85" s="4">
-        <v>0</v>
-      </c>
-      <c r="F85" s="4">
+      <c r="E85" s="2">
+        <v>0</v>
+      </c>
+      <c r="F85" s="2">
         <v>4.04</v>
       </c>
-      <c r="G85" s="4">
+      <c r="G85" s="2">
         <v>-4.24</v>
       </c>
-      <c r="H85" s="4">
+      <c r="H85" s="2">
         <v>11</v>
       </c>
-      <c r="I85" s="4">
+      <c r="I85" s="2">
         <v>15</v>
       </c>
-      <c r="J85" s="4">
+      <c r="J85" s="2">
         <v>26</v>
       </c>
-      <c r="K85" s="4">
+      <c r="K85" s="2">
         <v>0.72</v>
       </c>
-      <c r="L85" s="5">
+      <c r="L85" s="3">
         <v>0.025</v>
       </c>
-      <c r="M85" s="4">
+      <c r="M85" s="2">
         <v>4061.11</v>
       </c>
-      <c r="N85" s="4">
+      <c r="N85" s="2">
         <v>485</v>
       </c>
-      <c r="O85" s="4">
+      <c r="O85" s="2">
         <v>25.956</v>
       </c>
-      <c r="P85" s="4">
+      <c r="P85" s="2">
         <v>72.1</v>
       </c>
-      <c r="Q85" s="4">
+      <c r="Q85" s="2">
         <v>112.81</v>
       </c>
-      <c r="R85" s="4">
+      <c r="R85" s="2">
         <v>13.47</v>
       </c>
-      <c r="S85" s="4">
+      <c r="S85" s="2">
         <v>0.32</v>
       </c>
-      <c r="T85" s="4">
-        <v>0</v>
-      </c>
-      <c r="U85" s="4">
-        <v>0</v>
-      </c>
-      <c r="V85" s="4">
-        <v>0</v>
-      </c>
-      <c r="W85" s="4">
-        <v>0</v>
-      </c>
-      <c r="X85" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y85" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z85" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA85" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB85" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC85" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD85" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE85" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF85" s="4">
+      <c r="T85" s="2">
+        <v>0</v>
+      </c>
+      <c r="U85" s="2">
+        <v>0</v>
+      </c>
+      <c r="V85" s="2">
+        <v>0</v>
+      </c>
+      <c r="W85" s="2">
+        <v>0</v>
+      </c>
+      <c r="X85" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="2">
         <v>359.77</v>
       </c>
-      <c r="AG85" s="4">
+      <c r="AG85" s="2">
         <v>670.2</v>
       </c>
-      <c r="AH85" s="4">
+      <c r="AH85" s="2">
         <v>72.31</v>
       </c>
-      <c r="AI85" s="4">
+      <c r="AI85" s="2">
         <v>1329.73</v>
       </c>
-      <c r="AJ85" s="4">
+      <c r="AJ85" s="2">
         <v>1726.31</v>
       </c>
-      <c r="AK85" s="4">
+      <c r="AK85" s="2">
         <v>617.99</v>
       </c>
-      <c r="AL85" s="4">
+      <c r="AL85" s="2">
         <v>300.78</v>
       </c>
-      <c r="AM85" s="4">
+      <c r="AM85" s="2">
         <v>13.26</v>
       </c>
-      <c r="AN85" s="4">
+      <c r="AN85" s="2">
         <v>1</v>
       </c>
-      <c r="AO85" s="4">
+      <c r="AO85" s="2">
         <v>0.37</v>
       </c>
-      <c r="AP85" s="4">
+      <c r="AP85" s="2">
         <v>314.04</v>
       </c>
-      <c r="AQ85" s="4">
+      <c r="AQ85" s="2">
         <v>19</v>
       </c>
-      <c r="AR85" s="4">
+      <c r="AR85" s="2">
         <v>8.72</v>
       </c>
-      <c r="AS85" s="4">
+      <c r="AS85" s="2">
         <v>108</v>
       </c>
-      <c r="AT85" s="4" t="s">
+      <c r="AT85" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AU85" s="4" t="s">
+      <c r="AU85" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV85" s="4" t="s">
+      <c r="AV85" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AW85" s="4" t="s">
+      <c r="AW85" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX85" s="4" t="s">
+      <c r="AX85" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -14494,148 +14488,148 @@
       <c r="B86" t="s">
         <v>51</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E86" s="4">
-        <v>0</v>
-      </c>
-      <c r="F86" s="4">
+      <c r="E86" s="2">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2">
         <v>3.94</v>
       </c>
-      <c r="G86" s="4">
+      <c r="G86" s="2">
         <v>-5.1</v>
       </c>
-      <c r="H86" s="4">
+      <c r="H86" s="2">
         <v>19</v>
       </c>
-      <c r="I86" s="4">
+      <c r="I86" s="2">
         <v>22</v>
       </c>
-      <c r="J86" s="4">
+      <c r="J86" s="2">
         <v>41</v>
       </c>
-      <c r="K86" s="4">
+      <c r="K86" s="2">
         <v>1.14</v>
       </c>
-      <c r="L86" s="5">
+      <c r="L86" s="3">
         <v>0.025</v>
       </c>
-      <c r="M86" s="4">
+      <c r="M86" s="2">
         <v>4090.11</v>
       </c>
-      <c r="N86" s="4">
+      <c r="N86" s="2">
         <v>468.44</v>
       </c>
-      <c r="O86" s="4">
+      <c r="O86" s="2">
         <v>30.888</v>
       </c>
-      <c r="P86" s="4">
+      <c r="P86" s="2">
         <v>85.85</v>
       </c>
-      <c r="Q86" s="4">
+      <c r="Q86" s="2">
         <v>113.61</v>
       </c>
-      <c r="R86" s="4">
+      <c r="R86" s="2">
         <v>13.01</v>
       </c>
-      <c r="S86" s="4">
+      <c r="S86" s="2">
         <v>0.32</v>
       </c>
-      <c r="T86" s="4">
-        <v>0</v>
-      </c>
-      <c r="U86" s="4">
-        <v>0</v>
-      </c>
-      <c r="V86" s="4">
-        <v>0</v>
-      </c>
-      <c r="W86" s="4">
-        <v>0</v>
-      </c>
-      <c r="X86" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y86" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z86" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA86" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB86" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC86" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD86" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE86" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF86" s="4">
+      <c r="T86" s="2">
+        <v>0</v>
+      </c>
+      <c r="U86" s="2">
+        <v>0</v>
+      </c>
+      <c r="V86" s="2">
+        <v>0</v>
+      </c>
+      <c r="W86" s="2">
+        <v>0</v>
+      </c>
+      <c r="X86" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="2">
         <v>366.48</v>
       </c>
-      <c r="AG86" s="4">
+      <c r="AG86" s="2">
         <v>733.64</v>
       </c>
-      <c r="AH86" s="4">
+      <c r="AH86" s="2">
         <v>60.98</v>
       </c>
-      <c r="AI86" s="4">
+      <c r="AI86" s="2">
         <v>1390.27</v>
       </c>
-      <c r="AJ86" s="4">
+      <c r="AJ86" s="2">
         <v>1524.6</v>
       </c>
-      <c r="AK86" s="4">
+      <c r="AK86" s="2">
         <v>721.5</v>
       </c>
-      <c r="AL86" s="4">
+      <c r="AL86" s="2">
         <v>313.36</v>
       </c>
-      <c r="AM86" s="4">
+      <c r="AM86" s="2">
         <v>78.68</v>
       </c>
-      <c r="AN86" s="4">
+      <c r="AN86" s="2">
         <v>3</v>
       </c>
-      <c r="AO86" s="4">
+      <c r="AO86" s="2">
         <v>2.19</v>
       </c>
-      <c r="AP86" s="4">
+      <c r="AP86" s="2">
         <v>392.04</v>
       </c>
-      <c r="AQ86" s="4">
+      <c r="AQ86" s="2">
         <v>18</v>
       </c>
-      <c r="AR86" s="4">
+      <c r="AR86" s="2">
         <v>10.89</v>
       </c>
-      <c r="AS86" s="4">
+      <c r="AS86" s="2">
         <v>58</v>
       </c>
-      <c r="AT86" s="4" t="s">
+      <c r="AT86" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AU86" s="4" t="s">
+      <c r="AU86" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV86" s="4" t="s">
+      <c r="AV86" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AW86" s="4" t="s">
+      <c r="AW86" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX86" s="4" t="s">
+      <c r="AX86" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -14646,148 +14640,148 @@
       <c r="B87" t="s">
         <v>51</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E87" s="4">
-        <v>0</v>
-      </c>
-      <c r="F87" s="4">
+      <c r="E87" s="2">
+        <v>0</v>
+      </c>
+      <c r="F87" s="2">
         <v>4</v>
       </c>
-      <c r="G87" s="4">
+      <c r="G87" s="2">
         <v>-4.93</v>
       </c>
-      <c r="H87" s="4">
+      <c r="H87" s="2">
         <v>15</v>
       </c>
-      <c r="I87" s="4">
+      <c r="I87" s="2">
         <v>23</v>
       </c>
-      <c r="J87" s="4">
+      <c r="J87" s="2">
         <v>38</v>
       </c>
-      <c r="K87" s="4">
+      <c r="K87" s="2">
         <v>0.64</v>
       </c>
-      <c r="L87" s="5">
+      <c r="L87" s="3">
         <v>0.0409722222222222</v>
       </c>
-      <c r="M87" s="4">
+      <c r="M87" s="2">
         <v>7391.21</v>
       </c>
-      <c r="N87" s="4">
+      <c r="N87" s="2">
         <v>698</v>
       </c>
-      <c r="O87" s="4">
+      <c r="O87" s="2">
         <v>29.196</v>
       </c>
-      <c r="P87" s="4">
+      <c r="P87" s="2">
         <v>81.08</v>
       </c>
-      <c r="Q87" s="4">
+      <c r="Q87" s="2">
         <v>125.27</v>
       </c>
-      <c r="R87" s="4">
+      <c r="R87" s="2">
         <v>11.83</v>
       </c>
-      <c r="S87" s="4">
+      <c r="S87" s="2">
         <v>0.39</v>
       </c>
-      <c r="T87" s="4">
-        <v>0</v>
-      </c>
-      <c r="U87" s="4">
-        <v>0</v>
-      </c>
-      <c r="V87" s="4">
-        <v>0</v>
-      </c>
-      <c r="W87" s="4">
-        <v>0</v>
-      </c>
-      <c r="X87" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y87" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z87" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA87" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB87" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC87" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD87" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE87" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF87" s="4">
+      <c r="T87" s="2">
+        <v>0</v>
+      </c>
+      <c r="U87" s="2">
+        <v>0</v>
+      </c>
+      <c r="V87" s="2">
+        <v>0</v>
+      </c>
+      <c r="W87" s="2">
+        <v>0</v>
+      </c>
+      <c r="X87" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="2">
         <v>661.13</v>
       </c>
-      <c r="AG87" s="4">
+      <c r="AG87" s="2">
         <v>1448.24</v>
       </c>
-      <c r="AH87" s="4">
+      <c r="AH87" s="2">
         <v>103.49</v>
       </c>
-      <c r="AI87" s="4">
+      <c r="AI87" s="2">
         <v>2418.42</v>
       </c>
-      <c r="AJ87" s="4">
+      <c r="AJ87" s="2">
         <v>2976.42</v>
       </c>
-      <c r="AK87" s="4">
+      <c r="AK87" s="2">
         <v>1303</v>
       </c>
-      <c r="AL87" s="4">
+      <c r="AL87" s="2">
         <v>518.2</v>
       </c>
-      <c r="AM87" s="4">
+      <c r="AM87" s="2">
         <v>70.96</v>
       </c>
-      <c r="AN87" s="4">
+      <c r="AN87" s="2">
         <v>4</v>
       </c>
-      <c r="AO87" s="4">
+      <c r="AO87" s="2">
         <v>1.2</v>
       </c>
-      <c r="AP87" s="4">
+      <c r="AP87" s="2">
         <v>589.16</v>
       </c>
-      <c r="AQ87" s="4">
+      <c r="AQ87" s="2">
         <v>31</v>
       </c>
-      <c r="AR87" s="4">
+      <c r="AR87" s="2">
         <v>9.99</v>
       </c>
-      <c r="AS87" s="4">
+      <c r="AS87" s="2">
         <v>39</v>
       </c>
-      <c r="AT87" s="4" t="s">
+      <c r="AT87" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AU87" s="4" t="s">
+      <c r="AU87" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV87" s="4" t="s">
+      <c r="AV87" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AW87" s="4" t="s">
+      <c r="AW87" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX87" s="4" t="s">
+      <c r="AX87" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -14798,148 +14792,148 @@
       <c r="B88" t="s">
         <v>51</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="D88" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E88" s="4">
-        <v>0</v>
-      </c>
-      <c r="F88" s="4">
+      <c r="E88" s="2">
+        <v>0</v>
+      </c>
+      <c r="F88" s="2">
         <v>4.37</v>
       </c>
-      <c r="G88" s="4">
+      <c r="G88" s="2">
         <v>-5.99</v>
       </c>
-      <c r="H88" s="4">
+      <c r="H88" s="2">
         <v>26</v>
       </c>
-      <c r="I88" s="4">
+      <c r="I88" s="2">
         <v>26</v>
       </c>
-      <c r="J88" s="4">
+      <c r="J88" s="2">
         <v>52</v>
       </c>
-      <c r="K88" s="4">
+      <c r="K88" s="2">
         <v>0.88</v>
       </c>
-      <c r="L88" s="5">
+      <c r="L88" s="3">
         <v>0.0409722222222222</v>
       </c>
-      <c r="M88" s="4">
+      <c r="M88" s="2">
         <v>7617.37</v>
       </c>
-      <c r="N88" s="4">
+      <c r="N88" s="2">
         <v>850.48</v>
       </c>
-      <c r="O88" s="4">
+      <c r="O88" s="2">
         <v>26.136</v>
       </c>
-      <c r="P88" s="4">
+      <c r="P88" s="2">
         <v>72.64</v>
       </c>
-      <c r="Q88" s="4">
+      <c r="Q88" s="2">
         <v>129.11</v>
       </c>
-      <c r="R88" s="4">
+      <c r="R88" s="2">
         <v>14.41</v>
       </c>
-      <c r="S88" s="4">
+      <c r="S88" s="2">
         <v>0.47</v>
       </c>
-      <c r="T88" s="4">
-        <v>0</v>
-      </c>
-      <c r="U88" s="4">
-        <v>0</v>
-      </c>
-      <c r="V88" s="4">
-        <v>0</v>
-      </c>
-      <c r="W88" s="4">
-        <v>0</v>
-      </c>
-      <c r="X88" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y88" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z88" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA88" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB88" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC88" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD88" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE88" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF88" s="4">
+      <c r="T88" s="2">
+        <v>0</v>
+      </c>
+      <c r="U88" s="2">
+        <v>0</v>
+      </c>
+      <c r="V88" s="2">
+        <v>0</v>
+      </c>
+      <c r="W88" s="2">
+        <v>0</v>
+      </c>
+      <c r="X88" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="2">
         <v>649.08</v>
       </c>
-      <c r="AG88" s="4">
+      <c r="AG88" s="2">
         <v>1262.46</v>
       </c>
-      <c r="AH88" s="4">
+      <c r="AH88" s="2">
         <v>73.54</v>
       </c>
-      <c r="AI88" s="4">
+      <c r="AI88" s="2">
         <v>2288.02</v>
       </c>
-      <c r="AJ88" s="4">
+      <c r="AJ88" s="2">
         <v>3273.4</v>
       </c>
-      <c r="AK88" s="4">
+      <c r="AK88" s="2">
         <v>1533.42</v>
       </c>
-      <c r="AL88" s="4">
+      <c r="AL88" s="2">
         <v>438.22</v>
       </c>
-      <c r="AM88" s="4">
+      <c r="AM88" s="2">
         <v>11.19</v>
       </c>
-      <c r="AN88" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO88" s="4">
+      <c r="AN88" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="2">
         <v>0.19</v>
       </c>
-      <c r="AP88" s="4">
+      <c r="AP88" s="2">
         <v>449.41</v>
       </c>
-      <c r="AQ88" s="4">
+      <c r="AQ88" s="2">
         <v>29</v>
       </c>
-      <c r="AR88" s="4">
+      <c r="AR88" s="2">
         <v>7.62</v>
       </c>
-      <c r="AS88" s="4">
+      <c r="AS88" s="2">
         <v>90</v>
       </c>
-      <c r="AT88" s="4" t="s">
+      <c r="AT88" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AU88" s="4" t="s">
+      <c r="AU88" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV88" s="4" t="s">
+      <c r="AV88" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AW88" s="4" t="s">
+      <c r="AW88" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX88" s="4" t="s">
+      <c r="AX88" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -14950,148 +14944,148 @@
       <c r="B89" t="s">
         <v>51</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="D89" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E89" s="4">
-        <v>0</v>
-      </c>
-      <c r="F89" s="4">
+      <c r="E89" s="2">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2">
         <v>5.32</v>
       </c>
-      <c r="G89" s="4">
+      <c r="G89" s="2">
         <v>-6.87</v>
       </c>
-      <c r="H89" s="4">
+      <c r="H89" s="2">
         <v>47</v>
       </c>
-      <c r="I89" s="4">
+      <c r="I89" s="2">
         <v>51</v>
       </c>
-      <c r="J89" s="4">
+      <c r="J89" s="2">
         <v>98</v>
       </c>
-      <c r="K89" s="4">
+      <c r="K89" s="2">
         <v>1.03</v>
       </c>
-      <c r="L89" s="5">
+      <c r="L89" s="3">
         <v>0.0659722222222222</v>
       </c>
-      <c r="M89" s="4">
+      <c r="M89" s="2">
         <v>11060.12</v>
       </c>
-      <c r="N89" s="4">
+      <c r="N89" s="2">
         <v>979.96</v>
       </c>
-      <c r="O89" s="4">
+      <c r="O89" s="2">
         <v>32.004</v>
       </c>
-      <c r="P89" s="4">
+      <c r="P89" s="2">
         <v>88.94</v>
       </c>
-      <c r="Q89" s="4">
+      <c r="Q89" s="2">
         <v>116.42</v>
       </c>
-      <c r="R89" s="4">
+      <c r="R89" s="2">
         <v>10.32</v>
       </c>
-      <c r="S89" s="4">
+      <c r="S89" s="2">
         <v>0.34</v>
       </c>
-      <c r="T89" s="4">
-        <v>0</v>
-      </c>
-      <c r="U89" s="4">
-        <v>0</v>
-      </c>
-      <c r="V89" s="4">
-        <v>0</v>
-      </c>
-      <c r="W89" s="4">
-        <v>0</v>
-      </c>
-      <c r="X89" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA89" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC89" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD89" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE89" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF89" s="4">
+      <c r="T89" s="2">
+        <v>0</v>
+      </c>
+      <c r="U89" s="2">
+        <v>0</v>
+      </c>
+      <c r="V89" s="2">
+        <v>0</v>
+      </c>
+      <c r="W89" s="2">
+        <v>0</v>
+      </c>
+      <c r="X89" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="2">
         <v>910.75</v>
       </c>
-      <c r="AG89" s="4">
+      <c r="AG89" s="2">
         <v>1974.17</v>
       </c>
-      <c r="AH89" s="4">
+      <c r="AH89" s="2">
         <v>171.99</v>
       </c>
-      <c r="AI89" s="4">
+      <c r="AI89" s="2">
         <v>3995.35</v>
       </c>
-      <c r="AJ89" s="4">
+      <c r="AJ89" s="2">
         <v>4033.67</v>
       </c>
-      <c r="AK89" s="4">
+      <c r="AK89" s="2">
         <v>2065.51</v>
       </c>
-      <c r="AL89" s="4">
+      <c r="AL89" s="2">
         <v>592.32</v>
       </c>
-      <c r="AM89" s="4">
+      <c r="AM89" s="2">
         <v>201.41</v>
       </c>
-      <c r="AN89" s="4">
+      <c r="AN89" s="2">
         <v>9</v>
       </c>
-      <c r="AO89" s="4">
+      <c r="AO89" s="2">
         <v>2.12</v>
       </c>
-      <c r="AP89" s="4">
+      <c r="AP89" s="2">
         <v>793.73</v>
       </c>
-      <c r="AQ89" s="4">
+      <c r="AQ89" s="2">
         <v>45</v>
       </c>
-      <c r="AR89" s="4">
+      <c r="AR89" s="2">
         <v>8.36</v>
       </c>
-      <c r="AS89" s="4">
+      <c r="AS89" s="2">
         <v>82</v>
       </c>
-      <c r="AT89" s="4" t="s">
+      <c r="AT89" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AU89" s="4" t="s">
+      <c r="AU89" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV89" s="4" t="s">
+      <c r="AV89" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AW89" s="4" t="s">
+      <c r="AW89" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX89" s="4" t="s">
+      <c r="AX89" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -15102,148 +15096,148 @@
       <c r="B90" t="s">
         <v>51</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="D90" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E90" s="4">
-        <v>0</v>
-      </c>
-      <c r="F90" s="4">
+      <c r="E90" s="2">
+        <v>0</v>
+      </c>
+      <c r="F90" s="2">
         <v>4.7</v>
       </c>
-      <c r="G90" s="4">
+      <c r="G90" s="2">
         <v>-4.86</v>
       </c>
-      <c r="H90" s="4">
+      <c r="H90" s="2">
         <v>24</v>
       </c>
-      <c r="I90" s="4">
+      <c r="I90" s="2">
         <v>34</v>
       </c>
-      <c r="J90" s="4">
+      <c r="J90" s="2">
         <v>58</v>
       </c>
-      <c r="K90" s="4">
+      <c r="K90" s="2">
         <v>0.61</v>
       </c>
-      <c r="L90" s="5">
+      <c r="L90" s="3">
         <v>0.0659722222222222</v>
       </c>
-      <c r="M90" s="4">
+      <c r="M90" s="2">
         <v>10317.15</v>
       </c>
-      <c r="N90" s="4">
+      <c r="N90" s="2">
         <v>914.28</v>
       </c>
-      <c r="O90" s="4">
+      <c r="O90" s="2">
         <v>29.7</v>
       </c>
-      <c r="P90" s="4">
+      <c r="P90" s="2">
         <v>82.53</v>
       </c>
-      <c r="Q90" s="4">
+      <c r="Q90" s="2">
         <v>108.6</v>
       </c>
-      <c r="R90" s="4">
+      <c r="R90" s="2">
         <v>9.62</v>
       </c>
-      <c r="S90" s="4">
+      <c r="S90" s="2">
         <v>0.31</v>
       </c>
-      <c r="T90" s="4">
-        <v>0</v>
-      </c>
-      <c r="U90" s="4">
-        <v>0</v>
-      </c>
-      <c r="V90" s="4">
-        <v>0</v>
-      </c>
-      <c r="W90" s="4">
-        <v>0</v>
-      </c>
-      <c r="X90" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y90" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z90" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA90" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB90" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC90" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD90" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE90" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF90" s="4">
+      <c r="T90" s="2">
+        <v>0</v>
+      </c>
+      <c r="U90" s="2">
+        <v>0</v>
+      </c>
+      <c r="V90" s="2">
+        <v>0</v>
+      </c>
+      <c r="W90" s="2">
+        <v>0</v>
+      </c>
+      <c r="X90" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD90" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF90" s="2">
         <v>910.86</v>
       </c>
-      <c r="AG90" s="4">
+      <c r="AG90" s="2">
         <v>1387.94</v>
       </c>
-      <c r="AH90" s="4">
+      <c r="AH90" s="2">
         <v>190.66</v>
       </c>
-      <c r="AI90" s="4">
+      <c r="AI90" s="2">
         <v>3561.1</v>
       </c>
-      <c r="AJ90" s="4">
+      <c r="AJ90" s="2">
         <v>4762.85</v>
       </c>
-      <c r="AK90" s="4">
+      <c r="AK90" s="2">
         <v>1271.56</v>
       </c>
-      <c r="AL90" s="4">
+      <c r="AL90" s="2">
         <v>428.36</v>
       </c>
-      <c r="AM90" s="4">
+      <c r="AM90" s="2">
         <v>103.07</v>
       </c>
-      <c r="AN90" s="4">
+      <c r="AN90" s="2">
         <v>6</v>
       </c>
-      <c r="AO90" s="4">
+      <c r="AO90" s="2">
         <v>1.08</v>
       </c>
-      <c r="AP90" s="4">
+      <c r="AP90" s="2">
         <v>531.43</v>
       </c>
-      <c r="AQ90" s="4">
+      <c r="AQ90" s="2">
         <v>28</v>
       </c>
-      <c r="AR90" s="4">
+      <c r="AR90" s="2">
         <v>5.59</v>
       </c>
-      <c r="AS90" s="4">
+      <c r="AS90" s="2">
         <v>43</v>
       </c>
-      <c r="AT90" s="4" t="s">
+      <c r="AT90" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AU90" s="4" t="s">
+      <c r="AU90" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV90" s="4" t="s">
+      <c r="AV90" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AW90" s="4" t="s">
+      <c r="AW90" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX90" s="4" t="s">
+      <c r="AX90" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -15254,148 +15248,148 @@
       <c r="B91" t="s">
         <v>51</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="D91" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E91" s="4">
-        <v>0</v>
-      </c>
-      <c r="F91" s="4">
+      <c r="E91" s="2">
+        <v>0</v>
+      </c>
+      <c r="F91" s="2">
         <v>4.35</v>
       </c>
-      <c r="G91" s="4">
+      <c r="G91" s="2">
         <v>-4.51</v>
       </c>
-      <c r="H91" s="4">
+      <c r="H91" s="2">
         <v>29</v>
       </c>
-      <c r="I91" s="4">
+      <c r="I91" s="2">
         <v>29</v>
       </c>
-      <c r="J91" s="4">
+      <c r="J91" s="2">
         <v>58</v>
       </c>
-      <c r="K91" s="4">
+      <c r="K91" s="2">
         <v>0.61</v>
       </c>
-      <c r="L91" s="5">
+      <c r="L91" s="3">
         <v>0.0659722222222222</v>
       </c>
-      <c r="M91" s="4">
+      <c r="M91" s="2">
         <v>9023.7</v>
       </c>
-      <c r="N91" s="4">
+      <c r="N91" s="2">
         <v>872.02</v>
       </c>
-      <c r="O91" s="4">
+      <c r="O91" s="2">
         <v>31.428</v>
       </c>
-      <c r="P91" s="4">
+      <c r="P91" s="2">
         <v>87.31</v>
       </c>
-      <c r="Q91" s="4">
+      <c r="Q91" s="2">
         <v>94.99</v>
       </c>
-      <c r="R91" s="4">
+      <c r="R91" s="2">
         <v>9.18</v>
       </c>
-      <c r="S91" s="4">
+      <c r="S91" s="2">
         <v>0.2</v>
       </c>
-      <c r="T91" s="4">
-        <v>0</v>
-      </c>
-      <c r="U91" s="4">
-        <v>0</v>
-      </c>
-      <c r="V91" s="4">
-        <v>0</v>
-      </c>
-      <c r="W91" s="4">
-        <v>0</v>
-      </c>
-      <c r="X91" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC91" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD91" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE91" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="4">
+      <c r="T91" s="2">
+        <v>0</v>
+      </c>
+      <c r="U91" s="2">
+        <v>0</v>
+      </c>
+      <c r="V91" s="2">
+        <v>0</v>
+      </c>
+      <c r="W91" s="2">
+        <v>0</v>
+      </c>
+      <c r="X91" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="2">
         <v>787.52</v>
       </c>
-      <c r="AG91" s="4">
+      <c r="AG91" s="2">
         <v>1060</v>
       </c>
-      <c r="AH91" s="4">
+      <c r="AH91" s="2">
         <v>194.58</v>
       </c>
-      <c r="AI91" s="4">
+      <c r="AI91" s="2">
         <v>3650.1</v>
       </c>
-      <c r="AJ91" s="4">
+      <c r="AJ91" s="2">
         <v>3742.29</v>
       </c>
-      <c r="AK91" s="4">
+      <c r="AK91" s="2">
         <v>1115.93</v>
       </c>
-      <c r="AL91" s="4">
+      <c r="AL91" s="2">
         <v>278.77</v>
       </c>
-      <c r="AM91" s="4">
+      <c r="AM91" s="2">
         <v>41.95</v>
       </c>
-      <c r="AN91" s="4">
+      <c r="AN91" s="2">
         <v>2</v>
       </c>
-      <c r="AO91" s="4">
+      <c r="AO91" s="2">
         <v>0.44</v>
       </c>
-      <c r="AP91" s="4">
+      <c r="AP91" s="2">
         <v>320.72</v>
       </c>
-      <c r="AQ91" s="4">
+      <c r="AQ91" s="2">
         <v>20</v>
       </c>
-      <c r="AR91" s="4">
+      <c r="AR91" s="2">
         <v>3.38</v>
       </c>
-      <c r="AS91" s="4">
+      <c r="AS91" s="2">
         <v>46</v>
       </c>
-      <c r="AT91" s="4" t="s">
+      <c r="AT91" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AU91" s="4" t="s">
+      <c r="AU91" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV91" s="4" t="s">
+      <c r="AV91" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AW91" s="4" t="s">
+      <c r="AW91" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX91" s="4" t="s">
+      <c r="AX91" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -15406,148 +15400,148 @@
       <c r="B92" t="s">
         <v>51</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="D92" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E92" s="4">
-        <v>0</v>
-      </c>
-      <c r="F92" s="4">
+      <c r="E92" s="2">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2">
         <v>4.56</v>
       </c>
-      <c r="G92" s="4">
+      <c r="G92" s="2">
         <v>-3.95</v>
       </c>
-      <c r="H92" s="4">
+      <c r="H92" s="2">
         <v>4</v>
       </c>
-      <c r="I92" s="4">
+      <c r="I92" s="2">
         <v>4</v>
       </c>
-      <c r="J92" s="4">
+      <c r="J92" s="2">
         <v>8</v>
       </c>
-      <c r="K92" s="4">
+      <c r="K92" s="2">
         <v>1.6</v>
       </c>
-      <c r="L92" s="5">
+      <c r="L92" s="3">
         <v>0.00347222222222222</v>
       </c>
-      <c r="M92" s="4">
+      <c r="M92" s="2">
         <v>769.07</v>
       </c>
-      <c r="N92" s="4">
+      <c r="N92" s="2">
         <v>87.98</v>
       </c>
-      <c r="O92" s="4">
+      <c r="O92" s="2">
         <v>28.26</v>
       </c>
-      <c r="P92" s="4">
+      <c r="P92" s="2">
         <v>78.54</v>
       </c>
-      <c r="Q92" s="4">
+      <c r="Q92" s="2">
         <v>153.81</v>
       </c>
-      <c r="R92" s="4">
+      <c r="R92" s="2">
         <v>17.6</v>
       </c>
-      <c r="S92" s="4">
+      <c r="S92" s="2">
         <v>0.8</v>
       </c>
-      <c r="T92" s="4">
-        <v>0</v>
-      </c>
-      <c r="U92" s="4">
-        <v>0</v>
-      </c>
-      <c r="V92" s="4">
-        <v>0</v>
-      </c>
-      <c r="W92" s="4">
-        <v>0</v>
-      </c>
-      <c r="X92" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y92" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z92" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA92" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB92" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC92" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD92" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE92" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF92" s="4">
+      <c r="T92" s="2">
+        <v>0</v>
+      </c>
+      <c r="U92" s="2">
+        <v>0</v>
+      </c>
+      <c r="V92" s="2">
+        <v>0</v>
+      </c>
+      <c r="W92" s="2">
+        <v>0</v>
+      </c>
+      <c r="X92" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="2">
         <v>57.88</v>
       </c>
-      <c r="AG92" s="4">
+      <c r="AG92" s="2">
         <v>178.93</v>
       </c>
-      <c r="AH92" s="4">
+      <c r="AH92" s="2">
         <v>3.6</v>
       </c>
-      <c r="AI92" s="4">
+      <c r="AI92" s="2">
         <v>162.25</v>
       </c>
-      <c r="AJ92" s="4">
+      <c r="AJ92" s="2">
         <v>361.6</v>
       </c>
-      <c r="AK92" s="4">
+      <c r="AK92" s="2">
         <v>127.58</v>
       </c>
-      <c r="AL92" s="4">
+      <c r="AL92" s="2">
         <v>80.18</v>
       </c>
-      <c r="AM92" s="4">
+      <c r="AM92" s="2">
         <v>33.92</v>
       </c>
-      <c r="AN92" s="4">
+      <c r="AN92" s="2">
         <v>3</v>
       </c>
-      <c r="AO92" s="4">
+      <c r="AO92" s="2">
         <v>6.78</v>
       </c>
-      <c r="AP92" s="4">
+      <c r="AP92" s="2">
         <v>114.1</v>
       </c>
-      <c r="AQ92" s="4">
+      <c r="AQ92" s="2">
         <v>6</v>
       </c>
-      <c r="AR92" s="4">
+      <c r="AR92" s="2">
         <v>22.82</v>
       </c>
-      <c r="AS92" s="4">
+      <c r="AS92" s="2">
         <v>13</v>
       </c>
-      <c r="AT92" s="4" t="s">
+      <c r="AT92" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AU92" s="4" t="s">
+      <c r="AU92" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV92" s="4" t="s">
+      <c r="AV92" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AW92" s="4" t="s">
+      <c r="AW92" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX92" s="4" t="s">
+      <c r="AX92" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -15558,148 +15552,148 @@
       <c r="B93" t="s">
         <v>51</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D93" s="4" t="s">
+      <c r="D93" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E93" s="4">
-        <v>0</v>
-      </c>
-      <c r="F93" s="4">
+      <c r="E93" s="2">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2">
         <v>4.13</v>
       </c>
-      <c r="G93" s="4">
+      <c r="G93" s="2">
         <v>-5.73</v>
       </c>
-      <c r="H93" s="4">
+      <c r="H93" s="2">
         <v>34</v>
       </c>
-      <c r="I93" s="4">
+      <c r="I93" s="2">
         <v>54</v>
       </c>
-      <c r="J93" s="4">
+      <c r="J93" s="2">
         <v>88</v>
       </c>
-      <c r="K93" s="4">
+      <c r="K93" s="2">
         <v>0.98</v>
       </c>
-      <c r="L93" s="5">
+      <c r="L93" s="3">
         <v>0.0625</v>
       </c>
-      <c r="M93" s="4">
+      <c r="M93" s="2">
         <v>9658.08</v>
       </c>
-      <c r="N93" s="4">
+      <c r="N93" s="2">
         <v>1039.6</v>
       </c>
-      <c r="O93" s="4">
+      <c r="O93" s="2">
         <v>29.844</v>
       </c>
-      <c r="P93" s="4">
+      <c r="P93" s="2">
         <v>82.86</v>
       </c>
-      <c r="Q93" s="4">
+      <c r="Q93" s="2">
         <v>107.31</v>
       </c>
-      <c r="R93" s="4">
+      <c r="R93" s="2">
         <v>11.55</v>
       </c>
-      <c r="S93" s="4">
+      <c r="S93" s="2">
         <v>0.25</v>
       </c>
-      <c r="T93" s="4">
-        <v>0</v>
-      </c>
-      <c r="U93" s="4">
-        <v>0</v>
-      </c>
-      <c r="V93" s="4">
-        <v>0</v>
-      </c>
-      <c r="W93" s="4">
-        <v>0</v>
-      </c>
-      <c r="X93" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y93" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z93" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA93" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB93" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC93" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD93" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE93" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF93" s="4">
+      <c r="T93" s="2">
+        <v>0</v>
+      </c>
+      <c r="U93" s="2">
+        <v>0</v>
+      </c>
+      <c r="V93" s="2">
+        <v>0</v>
+      </c>
+      <c r="W93" s="2">
+        <v>0</v>
+      </c>
+      <c r="X93" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="2">
         <v>863.12</v>
       </c>
-      <c r="AG93" s="4">
+      <c r="AG93" s="2">
         <v>1572.98</v>
       </c>
-      <c r="AH93" s="4">
+      <c r="AH93" s="2">
         <v>134.46</v>
       </c>
-      <c r="AI93" s="4">
+      <c r="AI93" s="2">
         <v>4022.74</v>
       </c>
-      <c r="AJ93" s="4">
+      <c r="AJ93" s="2">
         <v>3462.25</v>
       </c>
-      <c r="AK93" s="4">
+      <c r="AK93" s="2">
         <v>1358.32</v>
       </c>
-      <c r="AL93" s="4">
+      <c r="AL93" s="2">
         <v>578.74</v>
       </c>
-      <c r="AM93" s="4">
+      <c r="AM93" s="2">
         <v>101.91</v>
       </c>
-      <c r="AN93" s="4">
+      <c r="AN93" s="2">
         <v>5</v>
       </c>
-      <c r="AO93" s="4">
+      <c r="AO93" s="2">
         <v>1.13</v>
       </c>
-      <c r="AP93" s="4">
+      <c r="AP93" s="2">
         <v>680.65</v>
       </c>
-      <c r="AQ93" s="4">
+      <c r="AQ93" s="2">
         <v>42</v>
       </c>
-      <c r="AR93" s="4">
+      <c r="AR93" s="2">
         <v>7.56</v>
       </c>
-      <c r="AS93" s="4">
+      <c r="AS93" s="2">
         <v>158</v>
       </c>
-      <c r="AT93" s="4" t="s">
+      <c r="AT93" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AU93" s="4" t="s">
+      <c r="AU93" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV93" s="4" t="s">
+      <c r="AV93" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AW93" s="4" t="s">
+      <c r="AW93" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX93" s="4" t="s">
+      <c r="AX93" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -15710,148 +15704,148 @@
       <c r="B94" t="s">
         <v>51</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D94" s="4" t="s">
+      <c r="D94" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E94" s="4">
-        <v>0</v>
-      </c>
-      <c r="F94" s="4">
+      <c r="E94" s="2">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2">
         <v>4.36</v>
       </c>
-      <c r="G94" s="4">
+      <c r="G94" s="2">
         <v>-4.48</v>
       </c>
-      <c r="H94" s="4">
+      <c r="H94" s="2">
         <v>17</v>
       </c>
-      <c r="I94" s="4">
+      <c r="I94" s="2">
         <v>20</v>
       </c>
-      <c r="J94" s="4">
+      <c r="J94" s="2">
         <v>37</v>
       </c>
-      <c r="K94" s="4">
+      <c r="K94" s="2">
         <v>0.39</v>
       </c>
-      <c r="L94" s="5">
+      <c r="L94" s="3">
         <v>0.0659722222222222</v>
       </c>
-      <c r="M94" s="4">
+      <c r="M94" s="2">
         <v>8804.29</v>
       </c>
-      <c r="N94" s="4">
+      <c r="N94" s="2">
         <v>812.47</v>
       </c>
-      <c r="O94" s="4">
+      <c r="O94" s="2">
         <v>28.836</v>
       </c>
-      <c r="P94" s="4">
+      <c r="P94" s="2">
         <v>80.12</v>
       </c>
-      <c r="Q94" s="4">
+      <c r="Q94" s="2">
         <v>92.68</v>
       </c>
-      <c r="R94" s="4">
+      <c r="R94" s="2">
         <v>8.55</v>
       </c>
-      <c r="S94" s="4">
+      <c r="S94" s="2">
         <v>0.2</v>
       </c>
-      <c r="T94" s="4">
-        <v>0</v>
-      </c>
-      <c r="U94" s="4">
-        <v>0</v>
-      </c>
-      <c r="V94" s="4">
-        <v>0</v>
-      </c>
-      <c r="W94" s="4">
-        <v>0</v>
-      </c>
-      <c r="X94" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE94" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="4">
+      <c r="T94" s="2">
+        <v>0</v>
+      </c>
+      <c r="U94" s="2">
+        <v>0</v>
+      </c>
+      <c r="V94" s="2">
+        <v>0</v>
+      </c>
+      <c r="W94" s="2">
+        <v>0</v>
+      </c>
+      <c r="X94" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="2">
         <v>771.02</v>
       </c>
-      <c r="AG94" s="4">
+      <c r="AG94" s="2">
         <v>1007.69</v>
       </c>
-      <c r="AH94" s="4">
+      <c r="AH94" s="2">
         <v>146.65</v>
       </c>
-      <c r="AI94" s="4">
+      <c r="AI94" s="2">
         <v>3597.96</v>
       </c>
-      <c r="AJ94" s="4">
+      <c r="AJ94" s="2">
         <v>3744.52</v>
       </c>
-      <c r="AK94" s="4">
+      <c r="AK94" s="2">
         <v>973.32</v>
       </c>
-      <c r="AL94" s="4">
+      <c r="AL94" s="2">
         <v>250.64</v>
       </c>
-      <c r="AM94" s="4">
+      <c r="AM94" s="2">
         <v>89.93</v>
       </c>
-      <c r="AN94" s="4">
+      <c r="AN94" s="2">
         <v>5</v>
       </c>
-      <c r="AO94" s="4">
+      <c r="AO94" s="2">
         <v>0.95</v>
       </c>
-      <c r="AP94" s="4">
+      <c r="AP94" s="2">
         <v>340.57</v>
       </c>
-      <c r="AQ94" s="4">
+      <c r="AQ94" s="2">
         <v>20</v>
       </c>
-      <c r="AR94" s="4">
+      <c r="AR94" s="2">
         <v>3.58</v>
       </c>
-      <c r="AS94" s="4">
+      <c r="AS94" s="2">
         <v>38</v>
       </c>
-      <c r="AT94" s="4" t="s">
+      <c r="AT94" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AU94" s="4" t="s">
+      <c r="AU94" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV94" s="4" t="s">
+      <c r="AV94" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AW94" s="4" t="s">
+      <c r="AW94" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX94" s="4" t="s">
+      <c r="AX94" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -15862,148 +15856,148 @@
       <c r="B95" t="s">
         <v>51</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C95" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D95" s="4" t="s">
+      <c r="D95" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E95" s="4">
-        <v>0</v>
-      </c>
-      <c r="F95" s="4">
+      <c r="E95" s="2">
+        <v>0</v>
+      </c>
+      <c r="F95" s="2">
         <v>3.49</v>
       </c>
-      <c r="G95" s="4">
+      <c r="G95" s="2">
         <v>-4.2</v>
       </c>
-      <c r="H95" s="4">
+      <c r="H95" s="2">
         <v>2</v>
       </c>
-      <c r="I95" s="4">
+      <c r="I95" s="2">
         <v>1</v>
       </c>
-      <c r="J95" s="4">
+      <c r="J95" s="2">
         <v>3</v>
       </c>
-      <c r="K95" s="4">
+      <c r="K95" s="2">
         <v>0.6</v>
       </c>
-      <c r="L95" s="5">
+      <c r="L95" s="3">
         <v>0.00347222222222222</v>
       </c>
-      <c r="M95" s="4">
+      <c r="M95" s="2">
         <v>627.94</v>
       </c>
-      <c r="N95" s="4">
+      <c r="N95" s="2">
         <v>65</v>
       </c>
-      <c r="O95" s="4">
+      <c r="O95" s="2">
         <v>24.372</v>
       </c>
-      <c r="P95" s="4">
+      <c r="P95" s="2">
         <v>67.75</v>
       </c>
-      <c r="Q95" s="4">
+      <c r="Q95" s="2">
         <v>125.59</v>
       </c>
-      <c r="R95" s="4">
+      <c r="R95" s="2">
         <v>13</v>
       </c>
-      <c r="S95" s="4">
+      <c r="S95" s="2">
         <v>0.36</v>
       </c>
-      <c r="T95" s="4">
-        <v>0</v>
-      </c>
-      <c r="U95" s="4">
-        <v>0</v>
-      </c>
-      <c r="V95" s="4">
-        <v>0</v>
-      </c>
-      <c r="W95" s="4">
-        <v>0</v>
-      </c>
-      <c r="X95" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y95" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z95" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA95" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB95" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC95" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD95" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE95" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF95" s="4">
+      <c r="T95" s="2">
+        <v>0</v>
+      </c>
+      <c r="U95" s="2">
+        <v>0</v>
+      </c>
+      <c r="V95" s="2">
+        <v>0</v>
+      </c>
+      <c r="W95" s="2">
+        <v>0</v>
+      </c>
+      <c r="X95" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA95" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB95" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC95" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD95" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE95" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF95" s="2">
         <v>54.14</v>
       </c>
-      <c r="AG95" s="4">
+      <c r="AG95" s="2">
         <v>79.1</v>
       </c>
-      <c r="AH95" s="4">
+      <c r="AH95" s="2">
         <v>14.67</v>
       </c>
-      <c r="AI95" s="4">
+      <c r="AI95" s="2">
         <v>220.08</v>
       </c>
-      <c r="AJ95" s="4">
+      <c r="AJ95" s="2">
         <v>315.82</v>
       </c>
-      <c r="AK95" s="4">
+      <c r="AK95" s="2">
         <v>64.07</v>
       </c>
-      <c r="AL95" s="4">
+      <c r="AL95" s="2">
         <v>13.1</v>
       </c>
-      <c r="AM95" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN95" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO95" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP95" s="4">
+      <c r="AM95" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN95" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO95" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP95" s="2">
         <v>13.1</v>
       </c>
-      <c r="AQ95" s="4">
+      <c r="AQ95" s="2">
         <v>1</v>
       </c>
-      <c r="AR95" s="4">
+      <c r="AR95" s="2">
         <v>2.62</v>
       </c>
-      <c r="AS95" s="4">
+      <c r="AS95" s="2">
         <v>7</v>
       </c>
-      <c r="AT95" s="4" t="s">
+      <c r="AT95" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AU95" s="4" t="s">
+      <c r="AU95" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV95" s="4" t="s">
+      <c r="AV95" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AW95" s="4" t="s">
+      <c r="AW95" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX95" s="4" t="s">
+      <c r="AX95" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -16014,148 +16008,148 @@
       <c r="B96" t="s">
         <v>51</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C96" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D96" s="4" t="s">
+      <c r="D96" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E96" s="4">
-        <v>0</v>
-      </c>
-      <c r="F96" s="4">
+      <c r="E96" s="2">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2">
         <v>3.88</v>
       </c>
-      <c r="G96" s="4">
+      <c r="G96" s="2">
         <v>-5.18</v>
       </c>
-      <c r="H96" s="4">
+      <c r="H96" s="2">
         <v>24</v>
       </c>
-      <c r="I96" s="4">
+      <c r="I96" s="2">
         <v>45</v>
       </c>
-      <c r="J96" s="4">
+      <c r="J96" s="2">
         <v>69</v>
       </c>
-      <c r="K96" s="4">
+      <c r="K96" s="2">
         <v>0.73</v>
       </c>
-      <c r="L96" s="5">
+      <c r="L96" s="3">
         <v>0.0659722222222222</v>
       </c>
-      <c r="M96" s="4">
+      <c r="M96" s="2">
         <v>9811.16</v>
       </c>
-      <c r="N96" s="4">
+      <c r="N96" s="2">
         <v>950.66</v>
       </c>
-      <c r="O96" s="4">
+      <c r="O96" s="2">
         <v>30.852</v>
       </c>
-      <c r="P96" s="4">
+      <c r="P96" s="2">
         <v>85.67</v>
       </c>
-      <c r="Q96" s="4">
+      <c r="Q96" s="2">
         <v>103.28</v>
       </c>
-      <c r="R96" s="4">
+      <c r="R96" s="2">
         <v>10.01</v>
       </c>
-      <c r="S96" s="4">
+      <c r="S96" s="2">
         <v>0.27</v>
       </c>
-      <c r="T96" s="4">
-        <v>0</v>
-      </c>
-      <c r="U96" s="4">
-        <v>0</v>
-      </c>
-      <c r="V96" s="4">
-        <v>0</v>
-      </c>
-      <c r="W96" s="4">
-        <v>0</v>
-      </c>
-      <c r="X96" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA96" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB96" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC96" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE96" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF96" s="4">
+      <c r="T96" s="2">
+        <v>0</v>
+      </c>
+      <c r="U96" s="2">
+        <v>0</v>
+      </c>
+      <c r="V96" s="2">
+        <v>0</v>
+      </c>
+      <c r="W96" s="2">
+        <v>0</v>
+      </c>
+      <c r="X96" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="2">
         <v>863.6</v>
       </c>
-      <c r="AG96" s="4">
+      <c r="AG96" s="2">
         <v>1521.85</v>
       </c>
-      <c r="AH96" s="4">
+      <c r="AH96" s="2">
         <v>221.68</v>
       </c>
-      <c r="AI96" s="4">
+      <c r="AI96" s="2">
         <v>3435.21</v>
       </c>
-      <c r="AJ96" s="4">
+      <c r="AJ96" s="2">
         <v>4031.25</v>
       </c>
-      <c r="AK96" s="4">
+      <c r="AK96" s="2">
         <v>1502.33</v>
       </c>
-      <c r="AL96" s="4">
+      <c r="AL96" s="2">
         <v>498.62</v>
       </c>
-      <c r="AM96" s="4">
+      <c r="AM96" s="2">
         <v>122.46</v>
       </c>
-      <c r="AN96" s="4">
+      <c r="AN96" s="2">
         <v>4</v>
       </c>
-      <c r="AO96" s="4">
+      <c r="AO96" s="2">
         <v>1.29</v>
       </c>
-      <c r="AP96" s="4">
+      <c r="AP96" s="2">
         <v>621.08</v>
       </c>
-      <c r="AQ96" s="4">
+      <c r="AQ96" s="2">
         <v>37</v>
       </c>
-      <c r="AR96" s="4">
+      <c r="AR96" s="2">
         <v>6.54</v>
       </c>
-      <c r="AS96" s="4">
+      <c r="AS96" s="2">
         <v>73</v>
       </c>
-      <c r="AT96" s="4" t="s">
+      <c r="AT96" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AU96" s="4" t="s">
+      <c r="AU96" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV96" s="4" t="s">
+      <c r="AV96" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AW96" s="4" t="s">
+      <c r="AW96" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX96" s="4" t="s">
+      <c r="AX96" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -16166,148 +16160,148 @@
       <c r="B97" t="s">
         <v>51</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D97" s="4" t="s">
+      <c r="D97" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E97" s="4">
-        <v>0</v>
-      </c>
-      <c r="F97" s="4">
+      <c r="E97" s="2">
+        <v>0</v>
+      </c>
+      <c r="F97" s="2">
         <v>3.8</v>
       </c>
-      <c r="G97" s="4">
+      <c r="G97" s="2">
         <v>-3.58</v>
       </c>
-      <c r="H97" s="4">
+      <c r="H97" s="2">
         <v>4</v>
       </c>
-      <c r="I97" s="4">
+      <c r="I97" s="2">
         <v>3</v>
       </c>
-      <c r="J97" s="4">
+      <c r="J97" s="2">
         <v>7</v>
       </c>
-      <c r="K97" s="4">
+      <c r="K97" s="2">
         <v>0.64</v>
       </c>
-      <c r="L97" s="5">
+      <c r="L97" s="3">
         <v>0.00763888888888889</v>
       </c>
-      <c r="M97" s="4">
+      <c r="M97" s="2">
         <v>1299.15</v>
       </c>
-      <c r="N97" s="4">
+      <c r="N97" s="2">
         <v>150.26</v>
       </c>
-      <c r="O97" s="4">
+      <c r="O97" s="2">
         <v>23.076</v>
       </c>
-      <c r="P97" s="4">
+      <c r="P97" s="2">
         <v>64.14</v>
       </c>
-      <c r="Q97" s="4">
+      <c r="Q97" s="2">
         <v>118.1</v>
       </c>
-      <c r="R97" s="4">
+      <c r="R97" s="2">
         <v>13.66</v>
       </c>
-      <c r="S97" s="4">
+      <c r="S97" s="2">
         <v>0.43</v>
       </c>
-      <c r="T97" s="4">
-        <v>0</v>
-      </c>
-      <c r="U97" s="4">
-        <v>0</v>
-      </c>
-      <c r="V97" s="4">
-        <v>0</v>
-      </c>
-      <c r="W97" s="4">
-        <v>0</v>
-      </c>
-      <c r="X97" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y97" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z97" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA97" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB97" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC97" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD97" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE97" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF97" s="4">
+      <c r="T97" s="2">
+        <v>0</v>
+      </c>
+      <c r="U97" s="2">
+        <v>0</v>
+      </c>
+      <c r="V97" s="2">
+        <v>0</v>
+      </c>
+      <c r="W97" s="2">
+        <v>0</v>
+      </c>
+      <c r="X97" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="2">
         <v>308.67</v>
       </c>
-      <c r="AG97" s="4">
+      <c r="AG97" s="2">
         <v>260.76</v>
       </c>
-      <c r="AH97" s="4">
+      <c r="AH97" s="2">
         <v>27.87</v>
       </c>
-      <c r="AI97" s="4">
+      <c r="AI97" s="2">
         <v>341.6</v>
       </c>
-      <c r="AJ97" s="4">
+      <c r="AJ97" s="2">
         <v>532.54</v>
       </c>
-      <c r="AK97" s="4">
+      <c r="AK97" s="2">
         <v>318.79</v>
       </c>
-      <c r="AL97" s="4">
+      <c r="AL97" s="2">
         <v>78.35</v>
       </c>
-      <c r="AM97" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN97" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO97" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP97" s="4">
+      <c r="AM97" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="2">
         <v>78.35</v>
       </c>
-      <c r="AQ97" s="4">
+      <c r="AQ97" s="2">
         <v>5</v>
       </c>
-      <c r="AR97" s="4">
+      <c r="AR97" s="2">
         <v>7.12</v>
       </c>
-      <c r="AS97" s="4">
+      <c r="AS97" s="2">
         <v>19</v>
       </c>
-      <c r="AT97" s="4" t="s">
+      <c r="AT97" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AU97" s="4" t="s">
+      <c r="AU97" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV97" s="4" t="s">
+      <c r="AV97" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AW97" s="4" t="s">
+      <c r="AW97" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX97" s="4" t="s">
+      <c r="AX97" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -16318,148 +16312,148 @@
       <c r="B98" t="s">
         <v>51</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="D98" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E98" s="4">
-        <v>0</v>
-      </c>
-      <c r="F98" s="4">
+      <c r="E98" s="2">
+        <v>0</v>
+      </c>
+      <c r="F98" s="2">
         <v>4.18</v>
       </c>
-      <c r="G98" s="4">
+      <c r="G98" s="2">
         <v>-6.58</v>
       </c>
-      <c r="H98" s="4">
+      <c r="H98" s="2">
         <v>27</v>
       </c>
-      <c r="I98" s="4">
+      <c r="I98" s="2">
         <v>55</v>
       </c>
-      <c r="J98" s="4">
+      <c r="J98" s="2">
         <v>82</v>
       </c>
-      <c r="K98" s="4">
+      <c r="K98" s="2">
         <v>0.91</v>
       </c>
-      <c r="L98" s="5">
+      <c r="L98" s="3">
         <v>0.0625</v>
       </c>
-      <c r="M98" s="4">
+      <c r="M98" s="2">
         <v>10259.44</v>
       </c>
-      <c r="N98" s="4">
+      <c r="N98" s="2">
         <v>1081.57</v>
       </c>
-      <c r="O98" s="4">
+      <c r="O98" s="2">
         <v>32.184</v>
       </c>
-      <c r="P98" s="4">
+      <c r="P98" s="2">
         <v>89.4</v>
       </c>
-      <c r="Q98" s="4">
+      <c r="Q98" s="2">
         <v>113.99</v>
       </c>
-      <c r="R98" s="4">
+      <c r="R98" s="2">
         <v>12.02</v>
       </c>
-      <c r="S98" s="4">
+      <c r="S98" s="2">
         <v>0.33</v>
       </c>
-      <c r="T98" s="4">
-        <v>0</v>
-      </c>
-      <c r="U98" s="4">
-        <v>0</v>
-      </c>
-      <c r="V98" s="4">
-        <v>0</v>
-      </c>
-      <c r="W98" s="4">
-        <v>0</v>
-      </c>
-      <c r="X98" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y98" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z98" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA98" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB98" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC98" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD98" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE98" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF98" s="4">
+      <c r="T98" s="2">
+        <v>0</v>
+      </c>
+      <c r="U98" s="2">
+        <v>0</v>
+      </c>
+      <c r="V98" s="2">
+        <v>0</v>
+      </c>
+      <c r="W98" s="2">
+        <v>0</v>
+      </c>
+      <c r="X98" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="2">
         <v>934.2</v>
       </c>
-      <c r="AG98" s="4">
+      <c r="AG98" s="2">
         <v>1952.92</v>
       </c>
-      <c r="AH98" s="4">
+      <c r="AH98" s="2">
         <v>162.38</v>
       </c>
-      <c r="AI98" s="4">
+      <c r="AI98" s="2">
         <v>3354.7</v>
       </c>
-      <c r="AJ98" s="4">
+      <c r="AJ98" s="2">
         <v>4095.97</v>
       </c>
-      <c r="AK98" s="4">
+      <c r="AK98" s="2">
         <v>1658.02</v>
       </c>
-      <c r="AL98" s="4">
+      <c r="AL98" s="2">
         <v>710.59</v>
       </c>
-      <c r="AM98" s="4">
+      <c r="AM98" s="2">
         <v>278.04</v>
       </c>
-      <c r="AN98" s="4">
+      <c r="AN98" s="2">
         <v>13</v>
       </c>
-      <c r="AO98" s="4">
+      <c r="AO98" s="2">
         <v>3.09</v>
       </c>
-      <c r="AP98" s="4">
+      <c r="AP98" s="2">
         <v>988.63</v>
       </c>
-      <c r="AQ98" s="4">
+      <c r="AQ98" s="2">
         <v>48</v>
       </c>
-      <c r="AR98" s="4">
+      <c r="AR98" s="2">
         <v>10.98</v>
       </c>
-      <c r="AS98" s="4">
+      <c r="AS98" s="2">
         <v>163</v>
       </c>
-      <c r="AT98" s="4" t="s">
+      <c r="AT98" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AU98" s="4" t="s">
+      <c r="AU98" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AV98" s="4" t="s">
+      <c r="AV98" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AW98" s="4" t="s">
+      <c r="AW98" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX98" s="4" t="s">
+      <c r="AX98" s="2" t="s">
         <v>58</v>
       </c>
     </row>

--- a/GPS_Formativas_2026.xlsx
+++ b/GPS_Formativas_2026.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="122">
   <si>
     <t>Date</t>
   </si>
@@ -263,9 +263,6 @@
     <t>Thiago Amaro</t>
   </si>
   <si>
-    <t>INTENSIVO</t>
-  </si>
-  <si>
     <t>MD-3</t>
   </si>
   <si>
@@ -335,9 +332,6 @@
     <t>MD-1</t>
   </si>
   <si>
-    <t>INTENSIDAD</t>
-  </si>
-  <si>
     <t>Andres Gonzalez</t>
   </si>
   <si>
@@ -393,6 +387,12 @@
   </si>
   <si>
     <t>Alexander Velazquez</t>
+  </si>
+  <si>
+    <t>25-5-26</t>
+  </si>
+  <si>
+    <t>MC 20</t>
   </si>
 </sst>
 </file>
@@ -1008,11 +1008,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1554,7 +1560,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AX98"/>
+  <dimension ref="A1:AX106"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="30.4444444444444" customWidth="1"/>
@@ -3676,8 +3682,8 @@
       <c r="AT14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AU14" s="2" t="s">
-        <v>78</v>
+      <c r="AU14" t="s">
+        <v>55</v>
       </c>
       <c r="AV14" s="2" t="s">
         <v>66</v>
@@ -3828,11 +3834,11 @@
       <c r="AT15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AU15" s="2" t="s">
+      <c r="AU15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV15" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="AV15" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="AW15" s="2" t="s">
         <v>57</v>
@@ -3980,11 +3986,11 @@
       <c r="AT16" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AU16" s="2" t="s">
+      <c r="AU16" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV16" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="AV16" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="AW16" s="2" t="s">
         <v>57</v>
@@ -4132,11 +4138,11 @@
       <c r="AT17" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AU17" s="2" t="s">
+      <c r="AU17" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV17" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="AV17" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="AW17" s="2" t="s">
         <v>57</v>
@@ -4284,11 +4290,11 @@
       <c r="AT18" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AU18" s="2" t="s">
+      <c r="AU18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV18" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="AV18" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="AW18" s="2" t="s">
         <v>57</v>
@@ -4305,7 +4311,7 @@
         <v>64</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>53</v>
@@ -4436,8 +4442,8 @@
       <c r="AT19" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AU19" s="2" t="s">
-        <v>78</v>
+      <c r="AU19" t="s">
+        <v>55</v>
       </c>
       <c r="AV19" s="2" t="s">
         <v>66</v>
@@ -4588,11 +4594,11 @@
       <c r="AT20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AU20" s="2" t="s">
+      <c r="AU20" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV20" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="AV20" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="AW20" s="2" t="s">
         <v>57</v>
@@ -4609,7 +4615,7 @@
         <v>51</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>53</v>
@@ -4740,11 +4746,11 @@
       <c r="AT21" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AU21" s="2" t="s">
+      <c r="AU21" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV21" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="AV21" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="AW21" s="2" t="s">
         <v>57</v>
@@ -4892,11 +4898,11 @@
       <c r="AT22" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AU22" s="2" t="s">
+      <c r="AU22" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV22" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="AV22" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="AW22" s="2" t="s">
         <v>57</v>
@@ -5044,8 +5050,8 @@
       <c r="AT23" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AU23" s="2" t="s">
-        <v>78</v>
+      <c r="AU23" t="s">
+        <v>55</v>
       </c>
       <c r="AV23" s="2" t="s">
         <v>66</v>
@@ -5065,7 +5071,7 @@
         <v>51</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>53</v>
@@ -5196,11 +5202,11 @@
       <c r="AT24" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AU24" s="2" t="s">
+      <c r="AU24" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV24" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="AV24" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="AW24" s="2" t="s">
         <v>57</v>
@@ -5348,11 +5354,11 @@
       <c r="AT25" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AU25" s="2" t="s">
+      <c r="AU25" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV25" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="AV25" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="AW25" s="2" t="s">
         <v>57</v>
@@ -5366,10 +5372,10 @@
         <v>76</v>
       </c>
       <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>53</v>
@@ -5501,7 +5507,7 @@
         <v>68</v>
       </c>
       <c r="AU26" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV26" s="2" t="s">
         <v>56</v>
@@ -5518,10 +5524,10 @@
         <v>76</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>53</v>
@@ -5653,7 +5659,7 @@
         <v>63</v>
       </c>
       <c r="AU27" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV27" s="2" t="s">
         <v>56</v>
@@ -5670,10 +5676,10 @@
         <v>76</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>53</v>
@@ -5805,7 +5811,7 @@
         <v>60</v>
       </c>
       <c r="AU28" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV28" s="2" t="s">
         <v>56</v>
@@ -5822,10 +5828,10 @@
         <v>76</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>53</v>
@@ -5957,7 +5963,7 @@
         <v>75</v>
       </c>
       <c r="AU29" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV29" s="2" t="s">
         <v>56</v>
@@ -5974,10 +5980,10 @@
         <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>53</v>
@@ -6109,7 +6115,7 @@
         <v>68</v>
       </c>
       <c r="AU30" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV30" s="2" t="s">
         <v>56</v>
@@ -6126,10 +6132,10 @@
         <v>76</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>53</v>
@@ -6261,7 +6267,7 @@
         <v>75</v>
       </c>
       <c r="AU31" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV31" s="2" t="s">
         <v>56</v>
@@ -6278,10 +6284,10 @@
         <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>53</v>
@@ -6413,7 +6419,7 @@
         <v>63</v>
       </c>
       <c r="AU32" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV32" s="2" t="s">
         <v>56</v>
@@ -6430,10 +6436,10 @@
         <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>53</v>
@@ -6565,7 +6571,7 @@
         <v>54</v>
       </c>
       <c r="AU33" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV33" s="2" t="s">
         <v>56</v>
@@ -6582,10 +6588,10 @@
         <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>53</v>
@@ -6717,7 +6723,7 @@
         <v>63</v>
       </c>
       <c r="AU34" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV34" s="2" t="s">
         <v>56</v>
@@ -6734,10 +6740,10 @@
         <v>76</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>53</v>
@@ -6869,7 +6875,7 @@
         <v>54</v>
       </c>
       <c r="AU35" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV35" s="2" t="s">
         <v>56</v>
@@ -6883,7 +6889,7 @@
     </row>
     <row r="36" spans="1:50">
       <c r="A36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B36" t="s">
         <v>64</v>
@@ -7024,7 +7030,7 @@
         <v>55</v>
       </c>
       <c r="AV36" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW36" s="2" t="s">
         <v>57</v>
@@ -7035,7 +7041,7 @@
     </row>
     <row r="37" spans="1:50">
       <c r="A37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B37" t="s">
         <v>51</v>
@@ -7173,10 +7179,10 @@
         <v>54</v>
       </c>
       <c r="AU37" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV37" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW37" s="2" t="s">
         <v>57</v>
@@ -7187,7 +7193,7 @@
     </row>
     <row r="38" spans="1:50">
       <c r="A38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B38" t="s">
         <v>51</v>
@@ -7325,10 +7331,10 @@
         <v>60</v>
       </c>
       <c r="AU38" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV38" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW38" s="2" t="s">
         <v>57</v>
@@ -7339,7 +7345,7 @@
     </row>
     <row r="39" spans="1:50">
       <c r="A39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B39" t="s">
         <v>51</v>
@@ -7477,10 +7483,10 @@
         <v>54</v>
       </c>
       <c r="AU39" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV39" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW39" s="2" t="s">
         <v>57</v>
@@ -7491,7 +7497,7 @@
     </row>
     <row r="40" spans="1:50">
       <c r="A40" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B40" t="s">
         <v>51</v>
@@ -7629,10 +7635,10 @@
         <v>63</v>
       </c>
       <c r="AU40" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV40" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW40" s="2" t="s">
         <v>57</v>
@@ -7643,13 +7649,13 @@
     </row>
     <row r="41" spans="1:50">
       <c r="A41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B41" t="s">
         <v>64</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>53</v>
@@ -7784,7 +7790,7 @@
         <v>55</v>
       </c>
       <c r="AV41" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW41" s="2" t="s">
         <v>57</v>
@@ -7795,13 +7801,13 @@
     </row>
     <row r="42" spans="1:50">
       <c r="A42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
         <v>51</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>53</v>
@@ -7933,10 +7939,10 @@
         <v>75</v>
       </c>
       <c r="AU42" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV42" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW42" s="2" t="s">
         <v>57</v>
@@ -7947,7 +7953,7 @@
     </row>
     <row r="43" spans="1:50">
       <c r="A43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B43" t="s">
         <v>51</v>
@@ -8085,10 +8091,10 @@
         <v>68</v>
       </c>
       <c r="AU43" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV43" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW43" s="2" t="s">
         <v>57</v>
@@ -8099,13 +8105,13 @@
     </row>
     <row r="44" spans="1:50">
       <c r="A44" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B44" t="s">
         <v>51</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>53</v>
@@ -8237,10 +8243,10 @@
         <v>68</v>
       </c>
       <c r="AU44" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV44" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW44" s="2" t="s">
         <v>57</v>
@@ -8251,7 +8257,7 @@
     </row>
     <row r="45" spans="1:50">
       <c r="A45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B45" t="s">
         <v>51</v>
@@ -8389,10 +8395,10 @@
         <v>54</v>
       </c>
       <c r="AU45" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV45" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW45" s="2" t="s">
         <v>57</v>
@@ -8403,7 +8409,7 @@
     </row>
     <row r="46" spans="1:50">
       <c r="A46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B46" t="s">
         <v>64</v>
@@ -8544,7 +8550,7 @@
         <v>55</v>
       </c>
       <c r="AV46" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW46" s="2" t="s">
         <v>57</v>
@@ -8555,13 +8561,13 @@
     </row>
     <row r="47" spans="1:50">
       <c r="A47" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B47" t="s">
         <v>51</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>53</v>
@@ -8693,10 +8699,10 @@
         <v>54</v>
       </c>
       <c r="AU47" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV47" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW47" s="2" t="s">
         <v>57</v>
@@ -8707,7 +8713,7 @@
     </row>
     <row r="48" spans="1:50">
       <c r="A48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B48" t="s">
         <v>51</v>
@@ -8845,10 +8851,10 @@
         <v>75</v>
       </c>
       <c r="AU48" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV48" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW48" s="2" t="s">
         <v>57</v>
@@ -8859,13 +8865,13 @@
     </row>
     <row r="49" spans="1:50">
       <c r="A49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B49" t="s">
+        <v>82</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>53</v>
@@ -8997,10 +9003,10 @@
         <v>68</v>
       </c>
       <c r="AU49" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV49" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW49" s="2" t="s">
         <v>57</v>
@@ -9011,13 +9017,13 @@
     </row>
     <row r="50" spans="1:50">
       <c r="A50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>53</v>
@@ -9149,10 +9155,10 @@
         <v>63</v>
       </c>
       <c r="AU50" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV50" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW50" s="2" t="s">
         <v>57</v>
@@ -9163,13 +9169,13 @@
     </row>
     <row r="51" spans="1:50">
       <c r="A51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>53</v>
@@ -9301,10 +9307,10 @@
         <v>60</v>
       </c>
       <c r="AU51" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV51" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW51" s="2" t="s">
         <v>57</v>
@@ -9315,13 +9321,13 @@
     </row>
     <row r="52" spans="1:50">
       <c r="A52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B52" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>53</v>
@@ -9453,10 +9459,10 @@
         <v>75</v>
       </c>
       <c r="AU52" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV52" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW52" s="2" t="s">
         <v>57</v>
@@ -9467,13 +9473,13 @@
     </row>
     <row r="53" spans="1:50">
       <c r="A53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B53" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>53</v>
@@ -9605,10 +9611,10 @@
         <v>68</v>
       </c>
       <c r="AU53" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV53" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW53" s="2" t="s">
         <v>57</v>
@@ -9619,13 +9625,13 @@
     </row>
     <row r="54" spans="1:50">
       <c r="A54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>53</v>
@@ -9757,10 +9763,10 @@
         <v>75</v>
       </c>
       <c r="AU54" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV54" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW54" s="2" t="s">
         <v>57</v>
@@ -9771,13 +9777,13 @@
     </row>
     <row r="55" spans="1:50">
       <c r="A55" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B55" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>53</v>
@@ -9909,10 +9915,10 @@
         <v>63</v>
       </c>
       <c r="AU55" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV55" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW55" s="2" t="s">
         <v>57</v>
@@ -9923,13 +9929,13 @@
     </row>
     <row r="56" spans="1:50">
       <c r="A56" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B56" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>53</v>
@@ -10061,10 +10067,10 @@
         <v>54</v>
       </c>
       <c r="AU56" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV56" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW56" s="2" t="s">
         <v>57</v>
@@ -10075,13 +10081,13 @@
     </row>
     <row r="57" spans="1:50">
       <c r="A57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B57" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>53</v>
@@ -10213,10 +10219,10 @@
         <v>63</v>
       </c>
       <c r="AU57" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV57" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW57" s="2" t="s">
         <v>57</v>
@@ -10227,13 +10233,13 @@
     </row>
     <row r="58" spans="1:50">
       <c r="A58" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>53</v>
@@ -10365,10 +10371,10 @@
         <v>63</v>
       </c>
       <c r="AU58" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV58" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW58" s="2" t="s">
         <v>57</v>
@@ -10379,13 +10385,13 @@
     </row>
     <row r="59" spans="1:50">
       <c r="A59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B59" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>53</v>
@@ -10517,10 +10523,10 @@
         <v>54</v>
       </c>
       <c r="AU59" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV59" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW59" s="2" t="s">
         <v>57</v>
@@ -10531,13 +10537,13 @@
     </row>
     <row r="60" spans="1:50">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B60" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>53</v>
@@ -10669,10 +10675,10 @@
         <v>75</v>
       </c>
       <c r="AU60" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV60" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AW60" s="2" t="s">
         <v>57</v>
@@ -10683,7 +10689,7 @@
     </row>
     <row r="61" spans="1:50">
       <c r="A61" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B61" t="s">
         <v>64</v>
@@ -10821,10 +10827,10 @@
         <v>75</v>
       </c>
       <c r="AU61" s="2" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="AV61" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW61" s="2" t="s">
         <v>57</v>
@@ -10835,7 +10841,7 @@
     </row>
     <row r="62" spans="1:50">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B62" t="s">
         <v>51</v>
@@ -10973,10 +10979,10 @@
         <v>60</v>
       </c>
       <c r="AU62" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV62" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AW62" s="2" t="s">
         <v>57</v>
@@ -10987,7 +10993,7 @@
     </row>
     <row r="63" spans="1:50">
       <c r="A63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B63" t="s">
         <v>51</v>
@@ -11125,10 +11131,10 @@
         <v>54</v>
       </c>
       <c r="AU63" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV63" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AW63" s="2" t="s">
         <v>57</v>
@@ -11139,13 +11145,13 @@
     </row>
     <row r="64" spans="1:50">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B64" t="s">
         <v>51</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>53</v>
@@ -11277,10 +11283,10 @@
         <v>68</v>
       </c>
       <c r="AU64" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV64" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AW64" s="2" t="s">
         <v>57</v>
@@ -11291,13 +11297,13 @@
     </row>
     <row r="65" spans="1:50">
       <c r="A65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B65" t="s">
         <v>51</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>53</v>
@@ -11429,10 +11435,10 @@
         <v>75</v>
       </c>
       <c r="AU65" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV65" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AW65" s="2" t="s">
         <v>57</v>
@@ -11443,13 +11449,13 @@
     </row>
     <row r="66" spans="1:50">
       <c r="A66" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B66" t="s">
         <v>64</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>53</v>
@@ -11581,10 +11587,10 @@
         <v>63</v>
       </c>
       <c r="AU66" s="2" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="AV66" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW66" s="2" t="s">
         <v>57</v>
@@ -11595,13 +11601,13 @@
     </row>
     <row r="67" spans="1:50">
       <c r="A67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B67" t="s">
         <v>51</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>53</v>
@@ -11733,10 +11739,10 @@
         <v>63</v>
       </c>
       <c r="AU67" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV67" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AW67" s="2" t="s">
         <v>57</v>
@@ -11747,13 +11753,13 @@
     </row>
     <row r="68" spans="1:50">
       <c r="A68" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B68" t="s">
         <v>51</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>53</v>
@@ -11885,10 +11891,10 @@
         <v>68</v>
       </c>
       <c r="AU68" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV68" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AW68" s="2" t="s">
         <v>57</v>
@@ -11899,13 +11905,13 @@
     </row>
     <row r="69" spans="1:50">
       <c r="A69" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B69" t="s">
         <v>51</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>53</v>
@@ -12037,10 +12043,10 @@
         <v>54</v>
       </c>
       <c r="AU69" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV69" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AW69" s="2" t="s">
         <v>57</v>
@@ -12051,13 +12057,13 @@
     </row>
     <row r="70" spans="1:50">
       <c r="A70" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B70" t="s">
         <v>51</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>53</v>
@@ -12189,10 +12195,10 @@
         <v>60</v>
       </c>
       <c r="AU70" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV70" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AW70" s="2" t="s">
         <v>57</v>
@@ -12203,7 +12209,7 @@
     </row>
     <row r="71" spans="1:50">
       <c r="A71" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B71" t="s">
         <v>64</v>
@@ -12341,10 +12347,10 @@
         <v>54</v>
       </c>
       <c r="AU71" s="2" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="AV71" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW71" s="2" t="s">
         <v>57</v>
@@ -12355,13 +12361,13 @@
     </row>
     <row r="72" spans="1:50">
       <c r="A72" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B72" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>53</v>
@@ -12490,13 +12496,13 @@
         <v>24</v>
       </c>
       <c r="AT72" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU72" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV72" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AW72" s="2" t="s">
         <v>57</v>
@@ -12507,13 +12513,13 @@
     </row>
     <row r="73" spans="1:50">
       <c r="A73" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B73" t="s">
         <v>51</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>53</v>
@@ -12645,10 +12651,10 @@
         <v>75</v>
       </c>
       <c r="AU73" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV73" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AW73" s="2" t="s">
         <v>57</v>
@@ -12659,13 +12665,13 @@
     </row>
     <row r="74" spans="1:50">
       <c r="A74" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B74" t="s">
+        <v>82</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>53</v>
@@ -12797,10 +12803,10 @@
         <v>68</v>
       </c>
       <c r="AU74" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV74" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW74" s="2" t="s">
         <v>57</v>
@@ -12811,13 +12817,13 @@
     </row>
     <row r="75" spans="1:50">
       <c r="A75" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B75" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>53</v>
@@ -12949,10 +12955,10 @@
         <v>54</v>
       </c>
       <c r="AU75" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV75" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW75" s="2" t="s">
         <v>57</v>
@@ -12963,13 +12969,13 @@
     </row>
     <row r="76" spans="1:50">
       <c r="A76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B76" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>53</v>
@@ -13101,10 +13107,10 @@
         <v>60</v>
       </c>
       <c r="AU76" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV76" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW76" s="2" t="s">
         <v>57</v>
@@ -13115,13 +13121,13 @@
     </row>
     <row r="77" spans="1:50">
       <c r="A77" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>53</v>
@@ -13253,10 +13259,10 @@
         <v>75</v>
       </c>
       <c r="AU77" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV77" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW77" s="2" t="s">
         <v>57</v>
@@ -13267,13 +13273,13 @@
     </row>
     <row r="78" spans="1:50">
       <c r="A78" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>53</v>
@@ -13405,10 +13411,10 @@
         <v>68</v>
       </c>
       <c r="AU78" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV78" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW78" s="2" t="s">
         <v>57</v>
@@ -13419,13 +13425,13 @@
     </row>
     <row r="79" spans="1:50">
       <c r="A79" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B79" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>53</v>
@@ -13557,10 +13563,10 @@
         <v>63</v>
       </c>
       <c r="AU79" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV79" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW79" s="2" t="s">
         <v>57</v>
@@ -13571,13 +13577,13 @@
     </row>
     <row r="80" spans="1:50">
       <c r="A80" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B80" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>53</v>
@@ -13709,10 +13715,10 @@
         <v>54</v>
       </c>
       <c r="AU80" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV80" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW80" s="2" t="s">
         <v>57</v>
@@ -13723,13 +13729,13 @@
     </row>
     <row r="81" spans="1:50">
       <c r="A81" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B81" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>53</v>
@@ -13861,10 +13867,10 @@
         <v>63</v>
       </c>
       <c r="AU81" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV81" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW81" s="2" t="s">
         <v>57</v>
@@ -13875,13 +13881,13 @@
     </row>
     <row r="82" spans="1:50">
       <c r="A82" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B82" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>53</v>
@@ -14013,10 +14019,10 @@
         <v>63</v>
       </c>
       <c r="AU82" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV82" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW82" s="2" t="s">
         <v>57</v>
@@ -14027,13 +14033,13 @@
     </row>
     <row r="83" spans="1:50">
       <c r="A83" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>53</v>
@@ -14165,10 +14171,10 @@
         <v>54</v>
       </c>
       <c r="AU83" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV83" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AW83" s="2" t="s">
         <v>57</v>
@@ -14179,13 +14185,13 @@
     </row>
     <row r="84" spans="1:50">
       <c r="A84" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B84" t="s">
         <v>51</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>53</v>
@@ -14317,10 +14323,10 @@
         <v>54</v>
       </c>
       <c r="AU84" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV84" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AW84" s="2" t="s">
         <v>57</v>
@@ -14331,13 +14337,13 @@
     </row>
     <row r="85" spans="1:50">
       <c r="A85" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B85" t="s">
         <v>51</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>53</v>
@@ -14469,10 +14475,10 @@
         <v>60</v>
       </c>
       <c r="AU85" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV85" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AW85" s="2" t="s">
         <v>57</v>
@@ -14483,7 +14489,7 @@
     </row>
     <row r="86" spans="1:50">
       <c r="A86" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B86" t="s">
         <v>51</v>
@@ -14621,10 +14627,10 @@
         <v>63</v>
       </c>
       <c r="AU86" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV86" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AW86" s="2" t="s">
         <v>57</v>
@@ -14635,7 +14641,7 @@
     </row>
     <row r="87" spans="1:50">
       <c r="A87" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B87" t="s">
         <v>51</v>
@@ -14773,10 +14779,10 @@
         <v>60</v>
       </c>
       <c r="AU87" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV87" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AW87" s="2" t="s">
         <v>57</v>
@@ -14787,13 +14793,13 @@
     </row>
     <row r="88" spans="1:50">
       <c r="A88" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B88" t="s">
         <v>51</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>53</v>
@@ -14925,10 +14931,10 @@
         <v>75</v>
       </c>
       <c r="AU88" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV88" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AW88" s="2" t="s">
         <v>57</v>
@@ -14939,13 +14945,13 @@
     </row>
     <row r="89" spans="1:50">
       <c r="A89" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B89" t="s">
         <v>51</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>53</v>
@@ -15077,10 +15083,10 @@
         <v>54</v>
       </c>
       <c r="AU89" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV89" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AW89" s="2" t="s">
         <v>57</v>
@@ -15091,7 +15097,7 @@
     </row>
     <row r="90" spans="1:50">
       <c r="A90" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B90" t="s">
         <v>51</v>
@@ -15229,10 +15235,10 @@
         <v>68</v>
       </c>
       <c r="AU90" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV90" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AW90" s="2" t="s">
         <v>57</v>
@@ -15243,7 +15249,7 @@
     </row>
     <row r="91" spans="1:50">
       <c r="A91" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B91" t="s">
         <v>51</v>
@@ -15381,10 +15387,10 @@
         <v>68</v>
       </c>
       <c r="AU91" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV91" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AW91" s="2" t="s">
         <v>57</v>
@@ -15395,13 +15401,13 @@
     </row>
     <row r="92" spans="1:50">
       <c r="A92" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B92" t="s">
         <v>51</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>53</v>
@@ -15533,10 +15539,10 @@
         <v>63</v>
       </c>
       <c r="AU92" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV92" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AW92" s="2" t="s">
         <v>57</v>
@@ -15547,7 +15553,7 @@
     </row>
     <row r="93" spans="1:50">
       <c r="A93" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B93" t="s">
         <v>51</v>
@@ -15685,10 +15691,10 @@
         <v>54</v>
       </c>
       <c r="AU93" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV93" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AW93" s="2" t="s">
         <v>57</v>
@@ -15699,13 +15705,13 @@
     </row>
     <row r="94" spans="1:50">
       <c r="A94" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B94" t="s">
         <v>51</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>53</v>
@@ -15837,10 +15843,10 @@
         <v>68</v>
       </c>
       <c r="AU94" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV94" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AW94" s="2" t="s">
         <v>57</v>
@@ -15851,13 +15857,13 @@
     </row>
     <row r="95" spans="1:50">
       <c r="A95" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B95" t="s">
         <v>51</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>53</v>
@@ -15989,10 +15995,10 @@
         <v>68</v>
       </c>
       <c r="AU95" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV95" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AW95" s="2" t="s">
         <v>57</v>
@@ -16003,7 +16009,7 @@
     </row>
     <row r="96" spans="1:50">
       <c r="A96" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B96" t="s">
         <v>51</v>
@@ -16141,10 +16147,10 @@
         <v>75</v>
       </c>
       <c r="AU96" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV96" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AW96" s="2" t="s">
         <v>57</v>
@@ -16155,13 +16161,13 @@
     </row>
     <row r="97" spans="1:50">
       <c r="A97" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B97" t="s">
         <v>51</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>53</v>
@@ -16293,10 +16299,10 @@
         <v>54</v>
       </c>
       <c r="AU97" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV97" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AW97" s="2" t="s">
         <v>57</v>
@@ -16307,13 +16313,13 @@
     </row>
     <row r="98" spans="1:50">
       <c r="A98" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B98" t="s">
         <v>51</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>53</v>
@@ -16445,16 +16451,1232 @@
         <v>63</v>
       </c>
       <c r="AU98" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV98" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AW98" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AX98" s="2" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="99" spans="1:50">
+      <c r="A99" t="s">
+        <v>120</v>
+      </c>
+      <c r="B99" t="s">
+        <v>51</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E99" s="4">
+        <v>0</v>
+      </c>
+      <c r="F99" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="G99" s="4">
+        <v>-4.67</v>
+      </c>
+      <c r="H99" s="4">
+        <v>21</v>
+      </c>
+      <c r="I99" s="4">
+        <v>22</v>
+      </c>
+      <c r="J99" s="4">
+        <v>43</v>
+      </c>
+      <c r="K99" s="4">
+        <v>0.61</v>
+      </c>
+      <c r="L99" s="5">
+        <v>0.0486111111111111</v>
+      </c>
+      <c r="M99" s="4">
+        <v>5227.93</v>
+      </c>
+      <c r="N99" s="4">
+        <v>507.91</v>
+      </c>
+      <c r="O99" s="4">
+        <v>26.496</v>
+      </c>
+      <c r="P99" s="4">
+        <v>73.64</v>
+      </c>
+      <c r="Q99" s="4">
+        <v>74.68</v>
+      </c>
+      <c r="R99" s="4">
+        <v>7.26</v>
+      </c>
+      <c r="S99" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="T99" s="4">
+        <v>0</v>
+      </c>
+      <c r="U99" s="4">
+        <v>0</v>
+      </c>
+      <c r="V99" s="4">
+        <v>0</v>
+      </c>
+      <c r="W99" s="4">
+        <v>0</v>
+      </c>
+      <c r="X99" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="4">
+        <v>467.22</v>
+      </c>
+      <c r="AG99" s="4">
+        <v>742.65</v>
+      </c>
+      <c r="AH99" s="4">
+        <v>189.02</v>
+      </c>
+      <c r="AI99" s="4">
+        <v>2380.64</v>
+      </c>
+      <c r="AJ99" s="4">
+        <v>1806.8</v>
+      </c>
+      <c r="AK99" s="4">
+        <v>719.21</v>
+      </c>
+      <c r="AL99" s="4">
+        <v>118.07</v>
+      </c>
+      <c r="AM99" s="4">
+        <v>14.19</v>
+      </c>
+      <c r="AN99" s="4">
+        <v>1</v>
+      </c>
+      <c r="AO99" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AP99" s="4">
+        <v>132.26</v>
+      </c>
+      <c r="AQ99" s="4">
+        <v>10</v>
+      </c>
+      <c r="AR99" s="4">
+        <v>1.89</v>
+      </c>
+      <c r="AS99" s="4">
+        <v>25</v>
+      </c>
+      <c r="AT99" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU99" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV99" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW99" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX99" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="100" spans="1:50">
+      <c r="A100" t="s">
+        <v>120</v>
+      </c>
+      <c r="B100" t="s">
+        <v>51</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E100" s="4">
+        <v>0</v>
+      </c>
+      <c r="F100" s="4">
+        <v>4.13</v>
+      </c>
+      <c r="G100" s="4">
+        <v>-3.81</v>
+      </c>
+      <c r="H100" s="4">
+        <v>21</v>
+      </c>
+      <c r="I100" s="4">
+        <v>15</v>
+      </c>
+      <c r="J100" s="4">
+        <v>36</v>
+      </c>
+      <c r="K100" s="4">
+        <v>0.51</v>
+      </c>
+      <c r="L100" s="5">
+        <v>0.0486111111111111</v>
+      </c>
+      <c r="M100" s="4">
+        <v>5492.02</v>
+      </c>
+      <c r="N100" s="4">
+        <v>520.02</v>
+      </c>
+      <c r="O100" s="4">
+        <v>25.128</v>
+      </c>
+      <c r="P100" s="4">
+        <v>69.82</v>
+      </c>
+      <c r="Q100" s="4">
+        <v>78.46</v>
+      </c>
+      <c r="R100" s="4">
+        <v>7.43</v>
+      </c>
+      <c r="S100" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="T100" s="4">
+        <v>0</v>
+      </c>
+      <c r="U100" s="4">
+        <v>0</v>
+      </c>
+      <c r="V100" s="4">
+        <v>0</v>
+      </c>
+      <c r="W100" s="4">
+        <v>0</v>
+      </c>
+      <c r="X100" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="4">
+        <v>479.32</v>
+      </c>
+      <c r="AG100" s="4">
+        <v>526.41</v>
+      </c>
+      <c r="AH100" s="4">
+        <v>203.84</v>
+      </c>
+      <c r="AI100" s="4">
+        <v>2900.66</v>
+      </c>
+      <c r="AJ100" s="4">
+        <v>1861.78</v>
+      </c>
+      <c r="AK100" s="4">
+        <v>463.24</v>
+      </c>
+      <c r="AL100" s="4">
+        <v>62.49</v>
+      </c>
+      <c r="AM100" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN100" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO100" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP100" s="4">
+        <v>62.49</v>
+      </c>
+      <c r="AQ100" s="4">
+        <v>6</v>
+      </c>
+      <c r="AR100" s="4">
+        <v>0.89</v>
+      </c>
+      <c r="AS100" s="4">
+        <v>18</v>
+      </c>
+      <c r="AT100" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU100" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV100" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW100" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX100" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="101" spans="1:50">
+      <c r="A101" t="s">
+        <v>120</v>
+      </c>
+      <c r="B101" t="s">
+        <v>51</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E101" s="4">
+        <v>0</v>
+      </c>
+      <c r="F101" s="4">
+        <v>4.28</v>
+      </c>
+      <c r="G101" s="4">
+        <v>-5.05</v>
+      </c>
+      <c r="H101" s="4">
+        <v>22</v>
+      </c>
+      <c r="I101" s="4">
+        <v>23</v>
+      </c>
+      <c r="J101" s="4">
+        <v>45</v>
+      </c>
+      <c r="K101" s="4">
+        <v>0.64</v>
+      </c>
+      <c r="L101" s="5">
+        <v>0.0486111111111111</v>
+      </c>
+      <c r="M101" s="4">
+        <v>5362.14</v>
+      </c>
+      <c r="N101" s="4">
+        <v>539.27</v>
+      </c>
+      <c r="O101" s="4">
+        <v>26.352</v>
+      </c>
+      <c r="P101" s="4">
+        <v>73.19</v>
+      </c>
+      <c r="Q101" s="4">
+        <v>76.6</v>
+      </c>
+      <c r="R101" s="4">
+        <v>7.7</v>
+      </c>
+      <c r="S101" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="T101" s="4">
+        <v>0</v>
+      </c>
+      <c r="U101" s="4">
+        <v>0</v>
+      </c>
+      <c r="V101" s="4">
+        <v>0</v>
+      </c>
+      <c r="W101" s="4">
+        <v>0</v>
+      </c>
+      <c r="X101" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="4">
+        <v>476.42</v>
+      </c>
+      <c r="AG101" s="4">
+        <v>660.64</v>
+      </c>
+      <c r="AH101" s="4">
+        <v>167.35</v>
+      </c>
+      <c r="AI101" s="4">
+        <v>2855.15</v>
+      </c>
+      <c r="AJ101" s="4">
+        <v>1618.69</v>
+      </c>
+      <c r="AK101" s="4">
+        <v>549.09</v>
+      </c>
+      <c r="AL101" s="4">
+        <v>149.47</v>
+      </c>
+      <c r="AM101" s="4">
+        <v>22.39</v>
+      </c>
+      <c r="AN101" s="4">
+        <v>1</v>
+      </c>
+      <c r="AO101" s="4">
+        <v>0.32</v>
+      </c>
+      <c r="AP101" s="4">
+        <v>171.86</v>
+      </c>
+      <c r="AQ101" s="4">
+        <v>12</v>
+      </c>
+      <c r="AR101" s="4">
+        <v>2.46</v>
+      </c>
+      <c r="AS101" s="4">
+        <v>94</v>
+      </c>
+      <c r="AT101" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU101" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV101" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW101" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX101" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="102" spans="1:50">
+      <c r="A102" t="s">
+        <v>120</v>
+      </c>
+      <c r="B102" t="s">
+        <v>51</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E102" s="4">
+        <v>0</v>
+      </c>
+      <c r="F102" s="4">
+        <v>3.94</v>
+      </c>
+      <c r="G102" s="4">
+        <v>-4.57</v>
+      </c>
+      <c r="H102" s="4">
+        <v>11</v>
+      </c>
+      <c r="I102" s="4">
+        <v>25</v>
+      </c>
+      <c r="J102" s="4">
+        <v>36</v>
+      </c>
+      <c r="K102" s="4">
+        <v>0.51</v>
+      </c>
+      <c r="L102" s="5">
+        <v>0.0486111111111111</v>
+      </c>
+      <c r="M102" s="4">
+        <v>5109.37</v>
+      </c>
+      <c r="N102" s="4">
+        <v>569.15</v>
+      </c>
+      <c r="O102" s="4">
+        <v>24.588</v>
+      </c>
+      <c r="P102" s="4">
+        <v>68.31</v>
+      </c>
+      <c r="Q102" s="4">
+        <v>72.99</v>
+      </c>
+      <c r="R102" s="4">
+        <v>8.13</v>
+      </c>
+      <c r="S102" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="T102" s="4">
+        <v>0</v>
+      </c>
+      <c r="U102" s="4">
+        <v>0</v>
+      </c>
+      <c r="V102" s="4">
+        <v>0</v>
+      </c>
+      <c r="W102" s="4">
+        <v>0</v>
+      </c>
+      <c r="X102" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="4">
+        <v>366.39</v>
+      </c>
+      <c r="AG102" s="4">
+        <v>579.66</v>
+      </c>
+      <c r="AH102" s="4">
+        <v>250.62</v>
+      </c>
+      <c r="AI102" s="4">
+        <v>2381.33</v>
+      </c>
+      <c r="AJ102" s="4">
+        <v>1920.87</v>
+      </c>
+      <c r="AK102" s="4">
+        <v>502.3</v>
+      </c>
+      <c r="AL102" s="4">
+        <v>54.32</v>
+      </c>
+      <c r="AM102" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP102" s="4">
+        <v>54.32</v>
+      </c>
+      <c r="AQ102" s="4">
+        <v>5</v>
+      </c>
+      <c r="AR102" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="AS102" s="4">
+        <v>25</v>
+      </c>
+      <c r="AT102" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU102" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV102" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW102" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX102" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="103" spans="1:50">
+      <c r="A103" t="s">
+        <v>120</v>
+      </c>
+      <c r="B103" t="s">
+        <v>51</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E103" s="4">
+        <v>0</v>
+      </c>
+      <c r="F103" s="4">
+        <v>3.91</v>
+      </c>
+      <c r="G103" s="4">
+        <v>-4.39</v>
+      </c>
+      <c r="H103" s="4">
+        <v>19</v>
+      </c>
+      <c r="I103" s="4">
+        <v>19</v>
+      </c>
+      <c r="J103" s="4">
+        <v>38</v>
+      </c>
+      <c r="K103" s="4">
+        <v>0.54</v>
+      </c>
+      <c r="L103" s="5">
+        <v>0.0486111111111111</v>
+      </c>
+      <c r="M103" s="4">
+        <v>5242.69</v>
+      </c>
+      <c r="N103" s="4">
+        <v>473.96</v>
+      </c>
+      <c r="O103" s="4">
+        <v>25.308</v>
+      </c>
+      <c r="P103" s="4">
+        <v>70.33</v>
+      </c>
+      <c r="Q103" s="4">
+        <v>74.9</v>
+      </c>
+      <c r="R103" s="4">
+        <v>6.77</v>
+      </c>
+      <c r="S103" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="T103" s="4">
+        <v>0</v>
+      </c>
+      <c r="U103" s="4">
+        <v>0</v>
+      </c>
+      <c r="V103" s="4">
+        <v>0</v>
+      </c>
+      <c r="W103" s="4">
+        <v>0</v>
+      </c>
+      <c r="X103" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y103" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z103" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA103" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB103" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC103" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD103" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF103" s="4">
+        <v>1249.65</v>
+      </c>
+      <c r="AG103" s="4">
+        <v>620.02</v>
+      </c>
+      <c r="AH103" s="4">
+        <v>190.47</v>
+      </c>
+      <c r="AI103" s="4">
+        <v>2727.23</v>
+      </c>
+      <c r="AJ103" s="4">
+        <v>1766.23</v>
+      </c>
+      <c r="AK103" s="4">
+        <v>441.64</v>
+      </c>
+      <c r="AL103" s="4">
+        <v>112.92</v>
+      </c>
+      <c r="AM103" s="4">
+        <v>4.09</v>
+      </c>
+      <c r="AN103" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO103" s="4">
+        <v>0.06</v>
+      </c>
+      <c r="AP103" s="4">
+        <v>117.01</v>
+      </c>
+      <c r="AQ103" s="4">
+        <v>9</v>
+      </c>
+      <c r="AR103" s="4">
+        <v>1.67</v>
+      </c>
+      <c r="AS103" s="4">
+        <v>28</v>
+      </c>
+      <c r="AT103" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU103" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV103" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW103" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX103" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="104" spans="1:50">
+      <c r="A104" t="s">
+        <v>120</v>
+      </c>
+      <c r="B104" t="s">
+        <v>51</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E104" s="4">
+        <v>0</v>
+      </c>
+      <c r="F104" s="4">
+        <v>5.44</v>
+      </c>
+      <c r="G104" s="4">
+        <v>-3.11</v>
+      </c>
+      <c r="H104" s="4">
+        <v>20</v>
+      </c>
+      <c r="I104" s="4">
+        <v>2</v>
+      </c>
+      <c r="J104" s="4">
+        <v>22</v>
+      </c>
+      <c r="K104" s="4">
+        <v>0.31</v>
+      </c>
+      <c r="L104" s="5">
+        <v>0.0486111111111111</v>
+      </c>
+      <c r="M104" s="4">
+        <v>4836.68</v>
+      </c>
+      <c r="N104" s="4">
+        <v>507.6</v>
+      </c>
+      <c r="O104" s="4">
+        <v>23.544</v>
+      </c>
+      <c r="P104" s="4">
+        <v>65.38</v>
+      </c>
+      <c r="Q104" s="4">
+        <v>69.1</v>
+      </c>
+      <c r="R104" s="4">
+        <v>7.25</v>
+      </c>
+      <c r="S104" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="T104" s="4">
+        <v>0</v>
+      </c>
+      <c r="U104" s="4">
+        <v>0</v>
+      </c>
+      <c r="V104" s="4">
+        <v>0</v>
+      </c>
+      <c r="W104" s="4">
+        <v>0</v>
+      </c>
+      <c r="X104" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z104" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA104" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB104" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC104" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD104" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE104" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF104" s="4">
+        <v>376.46</v>
+      </c>
+      <c r="AG104" s="4">
+        <v>559.59</v>
+      </c>
+      <c r="AH104" s="4">
+        <v>502.59</v>
+      </c>
+      <c r="AI104" s="4">
+        <v>2290.57</v>
+      </c>
+      <c r="AJ104" s="4">
+        <v>1577.69</v>
+      </c>
+      <c r="AK104" s="4">
+        <v>384.57</v>
+      </c>
+      <c r="AL104" s="4">
+        <v>81.26</v>
+      </c>
+      <c r="AM104" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN104" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO104" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP104" s="4">
+        <v>81.26</v>
+      </c>
+      <c r="AQ104" s="4">
+        <v>6</v>
+      </c>
+      <c r="AR104" s="4">
+        <v>1.16</v>
+      </c>
+      <c r="AS104" s="4">
+        <v>17</v>
+      </c>
+      <c r="AT104" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU104" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV104" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW104" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX104" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="105" spans="1:50">
+      <c r="A105" t="s">
+        <v>120</v>
+      </c>
+      <c r="B105" t="s">
+        <v>51</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E105" s="4">
+        <v>0</v>
+      </c>
+      <c r="F105" s="4">
+        <v>4.12</v>
+      </c>
+      <c r="G105" s="4">
+        <v>-4.6</v>
+      </c>
+      <c r="H105" s="4">
+        <v>17</v>
+      </c>
+      <c r="I105" s="4">
+        <v>19</v>
+      </c>
+      <c r="J105" s="4">
+        <v>36</v>
+      </c>
+      <c r="K105" s="4">
+        <v>0.51</v>
+      </c>
+      <c r="L105" s="5">
+        <v>0.0486111111111111</v>
+      </c>
+      <c r="M105" s="4">
+        <v>5573.12</v>
+      </c>
+      <c r="N105" s="4">
+        <v>519.31</v>
+      </c>
+      <c r="O105" s="4">
+        <v>26.316</v>
+      </c>
+      <c r="P105" s="4">
+        <v>73.13</v>
+      </c>
+      <c r="Q105" s="4">
+        <v>79.62</v>
+      </c>
+      <c r="R105" s="4">
+        <v>7.42</v>
+      </c>
+      <c r="S105" s="4">
+        <v>0.18</v>
+      </c>
+      <c r="T105" s="4">
+        <v>0</v>
+      </c>
+      <c r="U105" s="4">
+        <v>0</v>
+      </c>
+      <c r="V105" s="4">
+        <v>0</v>
+      </c>
+      <c r="W105" s="4">
+        <v>0</v>
+      </c>
+      <c r="X105" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z105" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA105" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB105" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC105" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD105" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE105" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF105" s="4">
+        <v>500.5</v>
+      </c>
+      <c r="AG105" s="4">
+        <v>830.89</v>
+      </c>
+      <c r="AH105" s="4">
+        <v>153.86</v>
+      </c>
+      <c r="AI105" s="4">
+        <v>2205.75</v>
+      </c>
+      <c r="AJ105" s="4">
+        <v>2180.47</v>
+      </c>
+      <c r="AK105" s="4">
+        <v>816.07</v>
+      </c>
+      <c r="AL105" s="4">
+        <v>207.05</v>
+      </c>
+      <c r="AM105" s="4">
+        <v>9.8</v>
+      </c>
+      <c r="AN105" s="4">
+        <v>1</v>
+      </c>
+      <c r="AO105" s="4">
+        <v>0.14</v>
+      </c>
+      <c r="AP105" s="4">
+        <v>216.85</v>
+      </c>
+      <c r="AQ105" s="4">
+        <v>17</v>
+      </c>
+      <c r="AR105" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="AS105" s="4">
+        <v>14</v>
+      </c>
+      <c r="AT105" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU105" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV105" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW105" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX105" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="106" spans="1:50">
+      <c r="A106" t="s">
+        <v>120</v>
+      </c>
+      <c r="B106" t="s">
+        <v>51</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E106" s="4">
+        <v>0</v>
+      </c>
+      <c r="F106" s="4">
+        <v>4.18</v>
+      </c>
+      <c r="G106" s="4">
+        <v>-4.44</v>
+      </c>
+      <c r="H106" s="4">
+        <v>13</v>
+      </c>
+      <c r="I106" s="4">
+        <v>11</v>
+      </c>
+      <c r="J106" s="4">
+        <v>24</v>
+      </c>
+      <c r="K106" s="4">
+        <v>0.34</v>
+      </c>
+      <c r="L106" s="5">
+        <v>0.0486111111111111</v>
+      </c>
+      <c r="M106" s="4">
+        <v>4861.25</v>
+      </c>
+      <c r="N106" s="4">
+        <v>495.14</v>
+      </c>
+      <c r="O106" s="4">
+        <v>24.624</v>
+      </c>
+      <c r="P106" s="4">
+        <v>68.41</v>
+      </c>
+      <c r="Q106" s="4">
+        <v>69.45</v>
+      </c>
+      <c r="R106" s="4">
+        <v>7.07</v>
+      </c>
+      <c r="S106" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="T106" s="4">
+        <v>159</v>
+      </c>
+      <c r="U106" s="4">
+        <v>76.01</v>
+      </c>
+      <c r="V106" s="4">
+        <v>79.5</v>
+      </c>
+      <c r="W106" s="4">
+        <v>38.01</v>
+      </c>
+      <c r="X106" s="4">
+        <v>54.21</v>
+      </c>
+      <c r="Y106" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z106" s="5">
+        <v>0.0322337962962963</v>
+      </c>
+      <c r="AA106" s="5">
+        <v>0.00296296296296296</v>
+      </c>
+      <c r="AB106" s="5">
+        <v>0.00122685185185185</v>
+      </c>
+      <c r="AC106" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD106" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE106" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF106" s="4">
+        <v>425.57</v>
+      </c>
+      <c r="AG106" s="4">
+        <v>528.84</v>
+      </c>
+      <c r="AH106" s="4">
+        <v>206.47</v>
+      </c>
+      <c r="AI106" s="4">
+        <v>2483.29</v>
+      </c>
+      <c r="AJ106" s="4">
+        <v>1659.19</v>
+      </c>
+      <c r="AK106" s="4">
+        <v>434.18</v>
+      </c>
+      <c r="AL106" s="4">
+        <v>78.13</v>
+      </c>
+      <c r="AM106" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN106" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO106" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP106" s="4">
+        <v>78.13</v>
+      </c>
+      <c r="AQ106" s="4">
+        <v>5</v>
+      </c>
+      <c r="AR106" s="4">
+        <v>1.12</v>
+      </c>
+      <c r="AS106" s="4">
+        <v>60</v>
+      </c>
+      <c r="AT106" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU106" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV106" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW106" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX106" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/GPS_Formativas_2026.xlsx
+++ b/GPS_Formativas_2026.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="124">
   <si>
     <t>Date</t>
   </si>
@@ -368,6 +368,9 @@
     <t>Tezzio Acosta</t>
   </si>
   <si>
+    <t>COMPETENCIA</t>
+  </si>
+  <si>
     <t>MD</t>
   </si>
   <si>
@@ -394,6 +397,9 @@
   <si>
     <t>MC 20</t>
   </si>
+  <si>
+    <t>23-5-26</t>
+  </si>
 </sst>
 </file>
 
@@ -405,7 +411,14 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -878,16 +891,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -896,119 +906,122 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1027,6 +1040,8 @@
     <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="35" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1560,7 +1575,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AX106"/>
+  <dimension ref="A1:AX115"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="30.4444444444444" customWidth="1"/>
@@ -14323,10 +14338,10 @@
         <v>54</v>
       </c>
       <c r="AU84" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="AV84" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW84" s="2" t="s">
         <v>57</v>
@@ -14343,7 +14358,7 @@
         <v>51</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>53</v>
@@ -14475,10 +14490,10 @@
         <v>60</v>
       </c>
       <c r="AU85" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="AV85" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW85" s="2" t="s">
         <v>57</v>
@@ -14627,10 +14642,10 @@
         <v>63</v>
       </c>
       <c r="AU86" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="AV86" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW86" s="2" t="s">
         <v>57</v>
@@ -14779,10 +14794,10 @@
         <v>60</v>
       </c>
       <c r="AU87" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="AV87" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW87" s="2" t="s">
         <v>57</v>
@@ -14799,7 +14814,7 @@
         <v>51</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>53</v>
@@ -14931,10 +14946,10 @@
         <v>75</v>
       </c>
       <c r="AU88" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="AV88" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW88" s="2" t="s">
         <v>57</v>
@@ -14951,7 +14966,7 @@
         <v>51</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>53</v>
@@ -15083,10 +15098,10 @@
         <v>54</v>
       </c>
       <c r="AU89" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="AV89" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW89" s="2" t="s">
         <v>57</v>
@@ -15235,10 +15250,10 @@
         <v>68</v>
       </c>
       <c r="AU90" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="AV90" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW90" s="2" t="s">
         <v>57</v>
@@ -15387,10 +15402,10 @@
         <v>68</v>
       </c>
       <c r="AU91" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="AV91" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW91" s="2" t="s">
         <v>57</v>
@@ -15539,10 +15554,10 @@
         <v>63</v>
       </c>
       <c r="AU92" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="AV92" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW92" s="2" t="s">
         <v>57</v>
@@ -15691,10 +15706,10 @@
         <v>54</v>
       </c>
       <c r="AU93" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="AV93" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW93" s="2" t="s">
         <v>57</v>
@@ -15843,10 +15858,10 @@
         <v>68</v>
       </c>
       <c r="AU94" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="AV94" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW94" s="2" t="s">
         <v>57</v>
@@ -15863,7 +15878,7 @@
         <v>51</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>53</v>
@@ -15995,10 +16010,10 @@
         <v>68</v>
       </c>
       <c r="AU95" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="AV95" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW95" s="2" t="s">
         <v>57</v>
@@ -16147,10 +16162,10 @@
         <v>75</v>
       </c>
       <c r="AU96" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="AV96" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW96" s="2" t="s">
         <v>57</v>
@@ -16167,7 +16182,7 @@
         <v>51</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>53</v>
@@ -16299,10 +16314,10 @@
         <v>54</v>
       </c>
       <c r="AU97" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="AV97" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW97" s="2" t="s">
         <v>57</v>
@@ -16319,7 +16334,7 @@
         <v>51</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>53</v>
@@ -16451,10 +16466,10 @@
         <v>63</v>
       </c>
       <c r="AU98" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="AV98" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW98" s="2" t="s">
         <v>57</v>
@@ -16465,7 +16480,7 @@
     </row>
     <row r="99" spans="1:50">
       <c r="A99" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B99" t="s">
         <v>51</v>
@@ -16612,12 +16627,12 @@
         <v>57</v>
       </c>
       <c r="AX99" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="100" spans="1:50">
       <c r="A100" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B100" t="s">
         <v>51</v>
@@ -16764,12 +16779,12 @@
         <v>57</v>
       </c>
       <c r="AX100" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="101" spans="1:50">
       <c r="A101" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B101" t="s">
         <v>51</v>
@@ -16916,12 +16931,12 @@
         <v>57</v>
       </c>
       <c r="AX101" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="102" spans="1:50">
       <c r="A102" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B102" t="s">
         <v>51</v>
@@ -17068,12 +17083,12 @@
         <v>57</v>
       </c>
       <c r="AX102" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="103" spans="1:50">
       <c r="A103" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B103" t="s">
         <v>51</v>
@@ -17220,12 +17235,12 @@
         <v>57</v>
       </c>
       <c r="AX103" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="104" spans="1:50">
       <c r="A104" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B104" t="s">
         <v>51</v>
@@ -17372,12 +17387,12 @@
         <v>57</v>
       </c>
       <c r="AX104" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="105" spans="1:50">
       <c r="A105" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B105" t="s">
         <v>51</v>
@@ -17524,12 +17539,12 @@
         <v>57</v>
       </c>
       <c r="AX105" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="106" spans="1:50">
       <c r="A106" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B106" t="s">
         <v>51</v>
@@ -17676,7 +17691,1375 @@
         <v>57</v>
       </c>
       <c r="AX106" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="107" spans="1:50">
+      <c r="A107" t="s">
+        <v>123</v>
+      </c>
+      <c r="B107" t="s">
+        <v>82</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E107" s="6">
+        <v>0</v>
+      </c>
+      <c r="F107" s="6">
+        <v>3.75</v>
+      </c>
+      <c r="G107" s="6">
+        <v>-5.57</v>
+      </c>
+      <c r="H107" s="6">
+        <v>20</v>
+      </c>
+      <c r="I107" s="6">
+        <v>18</v>
+      </c>
+      <c r="J107" s="6">
+        <v>38</v>
+      </c>
+      <c r="K107" s="6">
+        <v>0.43</v>
+      </c>
+      <c r="L107" s="7">
+        <v>0.0617939814814815</v>
+      </c>
+      <c r="M107" s="6">
+        <v>8998.77</v>
+      </c>
+      <c r="N107" s="6">
+        <v>953.78</v>
+      </c>
+      <c r="O107" s="6">
+        <v>27.756</v>
+      </c>
+      <c r="P107" s="6">
+        <v>77.06</v>
+      </c>
+      <c r="Q107" s="6">
+        <v>101.13</v>
+      </c>
+      <c r="R107" s="6">
+        <v>10.72</v>
+      </c>
+      <c r="S107" s="6">
+        <v>0.23</v>
+      </c>
+      <c r="T107" s="6">
+        <v>0</v>
+      </c>
+      <c r="U107" s="6">
+        <v>0</v>
+      </c>
+      <c r="V107" s="6">
+        <v>0</v>
+      </c>
+      <c r="W107" s="6">
+        <v>0</v>
+      </c>
+      <c r="X107" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB107" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC107" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD107" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE107" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF107" s="6">
+        <v>785.51</v>
+      </c>
+      <c r="AG107" s="6">
+        <v>1287.4</v>
+      </c>
+      <c r="AH107" s="6">
+        <v>208.93</v>
+      </c>
+      <c r="AI107" s="6">
+        <v>3507.24</v>
+      </c>
+      <c r="AJ107" s="6">
+        <v>3418.02</v>
+      </c>
+      <c r="AK107" s="6">
+        <v>1274.01</v>
+      </c>
+      <c r="AL107" s="6">
+        <v>487.44</v>
+      </c>
+      <c r="AM107" s="6">
+        <v>99.38</v>
+      </c>
+      <c r="AN107" s="6">
+        <v>4</v>
+      </c>
+      <c r="AO107" s="6">
+        <v>1.12</v>
+      </c>
+      <c r="AP107" s="6">
+        <v>586.82</v>
+      </c>
+      <c r="AQ107" s="6">
+        <v>30</v>
+      </c>
+      <c r="AR107" s="6">
+        <v>6.59</v>
+      </c>
+      <c r="AS107" s="6">
+        <v>51</v>
+      </c>
+      <c r="AT107" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU107" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV107" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW107" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX107" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="108" spans="1:50">
+      <c r="A108" t="s">
+        <v>123</v>
+      </c>
+      <c r="B108" t="s">
+        <v>82</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E108" s="6">
+        <v>0</v>
+      </c>
+      <c r="F108" s="6">
+        <v>4.51</v>
+      </c>
+      <c r="G108" s="6">
+        <v>-5.75</v>
+      </c>
+      <c r="H108" s="6">
+        <v>30</v>
+      </c>
+      <c r="I108" s="6">
+        <v>40</v>
+      </c>
+      <c r="J108" s="6">
+        <v>70</v>
+      </c>
+      <c r="K108" s="6">
+        <v>0.69</v>
+      </c>
+      <c r="L108" s="7">
+        <v>0.0701388888888889</v>
+      </c>
+      <c r="M108" s="6">
+        <v>11148.18</v>
+      </c>
+      <c r="N108" s="6">
+        <v>1094.4</v>
+      </c>
+      <c r="O108" s="6">
+        <v>29.556</v>
+      </c>
+      <c r="P108" s="6">
+        <v>82.05</v>
+      </c>
+      <c r="Q108" s="6">
+        <v>110.38</v>
+      </c>
+      <c r="R108" s="6">
+        <v>10.84</v>
+      </c>
+      <c r="S108" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="T108" s="6">
+        <v>0</v>
+      </c>
+      <c r="U108" s="6">
+        <v>0</v>
+      </c>
+      <c r="V108" s="6">
+        <v>0</v>
+      </c>
+      <c r="W108" s="6">
+        <v>0</v>
+      </c>
+      <c r="X108" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z108" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA108" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB108" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC108" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD108" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE108" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF108" s="6">
+        <v>983.76</v>
+      </c>
+      <c r="AG108" s="6">
+        <v>1688.43</v>
+      </c>
+      <c r="AH108" s="6">
+        <v>195.04</v>
+      </c>
+      <c r="AI108" s="6">
+        <v>4208.89</v>
+      </c>
+      <c r="AJ108" s="6">
+        <v>4033.02</v>
+      </c>
+      <c r="AK108" s="6">
+        <v>1886.52</v>
+      </c>
+      <c r="AL108" s="6">
+        <v>636.29</v>
+      </c>
+      <c r="AM108" s="6">
+        <v>188.15</v>
+      </c>
+      <c r="AN108" s="6">
+        <v>12</v>
+      </c>
+      <c r="AO108" s="6">
+        <v>1.86</v>
+      </c>
+      <c r="AP108" s="6">
+        <v>824.44</v>
+      </c>
+      <c r="AQ108" s="6">
+        <v>43</v>
+      </c>
+      <c r="AR108" s="6">
+        <v>8.16</v>
+      </c>
+      <c r="AS108" s="6">
+        <v>70</v>
+      </c>
+      <c r="AT108" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU108" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV108" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW108" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX108" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="109" spans="1:50">
+      <c r="A109" t="s">
+        <v>123</v>
+      </c>
+      <c r="B109" t="s">
+        <v>82</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E109" s="6">
+        <v>0</v>
+      </c>
+      <c r="F109" s="6">
+        <v>4.22</v>
+      </c>
+      <c r="G109" s="6">
+        <v>-4.86</v>
+      </c>
+      <c r="H109" s="6">
+        <v>7</v>
+      </c>
+      <c r="I109" s="6">
+        <v>19</v>
+      </c>
+      <c r="J109" s="6">
+        <v>26</v>
+      </c>
+      <c r="K109" s="6">
+        <v>0.53</v>
+      </c>
+      <c r="L109" s="7">
+        <v>0.0340277777777778</v>
+      </c>
+      <c r="M109" s="6">
+        <v>4748.71</v>
+      </c>
+      <c r="N109" s="6">
+        <v>499.41</v>
+      </c>
+      <c r="O109" s="6">
+        <v>23.616</v>
+      </c>
+      <c r="P109" s="6">
+        <v>65.55</v>
+      </c>
+      <c r="Q109" s="6">
+        <v>96.91</v>
+      </c>
+      <c r="R109" s="6">
+        <v>10.19</v>
+      </c>
+      <c r="S109" s="6">
+        <v>0.18</v>
+      </c>
+      <c r="T109" s="6">
+        <v>0</v>
+      </c>
+      <c r="U109" s="6">
+        <v>0</v>
+      </c>
+      <c r="V109" s="6">
+        <v>0</v>
+      </c>
+      <c r="W109" s="6">
+        <v>0</v>
+      </c>
+      <c r="X109" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC109" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD109" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE109" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF109" s="6">
+        <v>412.84</v>
+      </c>
+      <c r="AG109" s="6">
+        <v>495.51</v>
+      </c>
+      <c r="AH109" s="6">
+        <v>98.92</v>
+      </c>
+      <c r="AI109" s="6">
+        <v>2173.07</v>
+      </c>
+      <c r="AJ109" s="6">
+        <v>1866.06</v>
+      </c>
+      <c r="AK109" s="6">
+        <v>529.4</v>
+      </c>
+      <c r="AL109" s="6">
+        <v>80.03</v>
+      </c>
+      <c r="AM109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP109" s="6">
+        <v>80.03</v>
+      </c>
+      <c r="AQ109" s="6">
+        <v>7</v>
+      </c>
+      <c r="AR109" s="6">
+        <v>1.63</v>
+      </c>
+      <c r="AS109" s="6">
+        <v>26</v>
+      </c>
+      <c r="AT109" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU109" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV109" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW109" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX109" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="110" spans="1:50">
+      <c r="A110" t="s">
+        <v>123</v>
+      </c>
+      <c r="B110" t="s">
+        <v>82</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E110" s="6">
+        <v>0</v>
+      </c>
+      <c r="F110" s="6">
+        <v>3.23</v>
+      </c>
+      <c r="G110" s="6">
+        <v>-7.32</v>
+      </c>
+      <c r="H110" s="6">
+        <v>3</v>
+      </c>
+      <c r="I110" s="6">
+        <v>5</v>
+      </c>
+      <c r="J110" s="6">
+        <v>8</v>
+      </c>
+      <c r="K110" s="6">
+        <v>0.45</v>
+      </c>
+      <c r="L110" s="7">
+        <v>0.0123263888888889</v>
+      </c>
+      <c r="M110" s="6">
+        <v>1819.03</v>
+      </c>
+      <c r="N110" s="6">
+        <v>193.54</v>
+      </c>
+      <c r="O110" s="6">
+        <v>29.484</v>
+      </c>
+      <c r="P110" s="6">
+        <v>81.94</v>
+      </c>
+      <c r="Q110" s="6">
+        <v>102.48</v>
+      </c>
+      <c r="R110" s="6">
+        <v>10.9</v>
+      </c>
+      <c r="S110" s="6">
+        <v>0.28</v>
+      </c>
+      <c r="T110" s="6">
+        <v>0</v>
+      </c>
+      <c r="U110" s="6">
+        <v>0</v>
+      </c>
+      <c r="V110" s="6">
+        <v>0</v>
+      </c>
+      <c r="W110" s="6">
+        <v>0</v>
+      </c>
+      <c r="X110" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y110" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z110" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA110" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB110" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC110" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD110" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE110" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF110" s="6">
+        <v>161.33</v>
+      </c>
+      <c r="AG110" s="6">
+        <v>315.33</v>
+      </c>
+      <c r="AH110" s="6">
+        <v>43.42</v>
+      </c>
+      <c r="AI110" s="6">
+        <v>629.18</v>
+      </c>
+      <c r="AJ110" s="6">
+        <v>672.99</v>
+      </c>
+      <c r="AK110" s="6">
+        <v>313.19</v>
+      </c>
+      <c r="AL110" s="6">
+        <v>129.86</v>
+      </c>
+      <c r="AM110" s="6">
+        <v>30.39</v>
+      </c>
+      <c r="AN110" s="6">
+        <v>2</v>
+      </c>
+      <c r="AO110" s="6">
+        <v>1.71</v>
+      </c>
+      <c r="AP110" s="6">
+        <v>160.25</v>
+      </c>
+      <c r="AQ110" s="6">
+        <v>10</v>
+      </c>
+      <c r="AR110" s="6">
+        <v>9.03</v>
+      </c>
+      <c r="AS110" s="6">
+        <v>37</v>
+      </c>
+      <c r="AT110" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU110" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV110" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW110" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX110" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="111" spans="1:50">
+      <c r="A111" t="s">
+        <v>123</v>
+      </c>
+      <c r="B111" t="s">
+        <v>82</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E111" s="6">
+        <v>0</v>
+      </c>
+      <c r="F111" s="6">
+        <v>4.06</v>
+      </c>
+      <c r="G111" s="6">
+        <v>-5.59</v>
+      </c>
+      <c r="H111" s="6">
+        <v>30</v>
+      </c>
+      <c r="I111" s="6">
+        <v>34</v>
+      </c>
+      <c r="J111" s="6">
+        <v>64</v>
+      </c>
+      <c r="K111" s="6">
+        <v>0.63</v>
+      </c>
+      <c r="L111" s="7">
+        <v>0.0701388888888889</v>
+      </c>
+      <c r="M111" s="6">
+        <v>9997.88</v>
+      </c>
+      <c r="N111" s="6">
+        <v>1062.8</v>
+      </c>
+      <c r="O111" s="6">
+        <v>28.044</v>
+      </c>
+      <c r="P111" s="6">
+        <v>77.95</v>
+      </c>
+      <c r="Q111" s="6">
+        <v>98.99</v>
+      </c>
+      <c r="R111" s="6">
+        <v>10.52</v>
+      </c>
+      <c r="S111" s="6">
+        <v>0.23</v>
+      </c>
+      <c r="T111" s="6">
+        <v>0</v>
+      </c>
+      <c r="U111" s="6">
+        <v>0</v>
+      </c>
+      <c r="V111" s="6">
+        <v>0</v>
+      </c>
+      <c r="W111" s="6">
+        <v>0</v>
+      </c>
+      <c r="X111" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="6">
+        <v>875.41</v>
+      </c>
+      <c r="AG111" s="6">
+        <v>1564.45</v>
+      </c>
+      <c r="AH111" s="6">
+        <v>258.08</v>
+      </c>
+      <c r="AI111" s="6">
+        <v>3955.77</v>
+      </c>
+      <c r="AJ111" s="6">
+        <v>3408.21</v>
+      </c>
+      <c r="AK111" s="6">
+        <v>1652.42</v>
+      </c>
+      <c r="AL111" s="6">
+        <v>642.83</v>
+      </c>
+      <c r="AM111" s="6">
+        <v>81.17</v>
+      </c>
+      <c r="AN111" s="6">
+        <v>5</v>
+      </c>
+      <c r="AO111" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="AP111" s="6">
+        <v>724</v>
+      </c>
+      <c r="AQ111" s="6">
+        <v>38</v>
+      </c>
+      <c r="AR111" s="6">
+        <v>7.17</v>
+      </c>
+      <c r="AS111" s="6">
+        <v>105</v>
+      </c>
+      <c r="AT111" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU111" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV111" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW111" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX111" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="112" spans="1:50">
+      <c r="A112" t="s">
+        <v>123</v>
+      </c>
+      <c r="B112" t="s">
+        <v>82</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E112" s="6">
+        <v>0</v>
+      </c>
+      <c r="F112" s="6">
+        <v>4.14</v>
+      </c>
+      <c r="G112" s="6">
+        <v>-5.36</v>
+      </c>
+      <c r="H112" s="6">
+        <v>33</v>
+      </c>
+      <c r="I112" s="6">
+        <v>32</v>
+      </c>
+      <c r="J112" s="6">
+        <v>65</v>
+      </c>
+      <c r="K112" s="6">
+        <v>0.64</v>
+      </c>
+      <c r="L112" s="7">
+        <v>0.0701388888888889</v>
+      </c>
+      <c r="M112" s="6">
+        <v>10143.07</v>
+      </c>
+      <c r="N112" s="6">
+        <v>1150.3</v>
+      </c>
+      <c r="O112" s="6">
+        <v>27.684</v>
+      </c>
+      <c r="P112" s="6">
+        <v>76.9</v>
+      </c>
+      <c r="Q112" s="6">
+        <v>100.43</v>
+      </c>
+      <c r="R112" s="6">
+        <v>11.39</v>
+      </c>
+      <c r="S112" s="6">
+        <v>0.23</v>
+      </c>
+      <c r="T112" s="6">
+        <v>0</v>
+      </c>
+      <c r="U112" s="6">
+        <v>0</v>
+      </c>
+      <c r="V112" s="6">
+        <v>0</v>
+      </c>
+      <c r="W112" s="6">
+        <v>0</v>
+      </c>
+      <c r="X112" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y112" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z112" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA112" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB112" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC112" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD112" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE112" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF112" s="6">
+        <v>899.16</v>
+      </c>
+      <c r="AG112" s="6">
+        <v>1598.64</v>
+      </c>
+      <c r="AH112" s="6">
+        <v>170.25</v>
+      </c>
+      <c r="AI112" s="6">
+        <v>4102.14</v>
+      </c>
+      <c r="AJ112" s="6">
+        <v>3670.27</v>
+      </c>
+      <c r="AK112" s="6">
+        <v>1490.87</v>
+      </c>
+      <c r="AL112" s="6">
+        <v>609.63</v>
+      </c>
+      <c r="AM112" s="6">
+        <v>100.55</v>
+      </c>
+      <c r="AN112" s="6">
+        <v>6</v>
+      </c>
+      <c r="AO112" s="6">
+        <v>1</v>
+      </c>
+      <c r="AP112" s="6">
+        <v>710.18</v>
+      </c>
+      <c r="AQ112" s="6">
+        <v>44</v>
+      </c>
+      <c r="AR112" s="6">
+        <v>7.03</v>
+      </c>
+      <c r="AS112" s="6">
+        <v>99</v>
+      </c>
+      <c r="AT112" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU112" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV112" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW112" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX112" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="113" spans="1:50">
+      <c r="A113" t="s">
+        <v>123</v>
+      </c>
+      <c r="B113" t="s">
+        <v>82</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E113" s="6">
+        <v>0</v>
+      </c>
+      <c r="F113" s="6">
+        <v>4.33</v>
+      </c>
+      <c r="G113" s="6">
+        <v>-4.57</v>
+      </c>
+      <c r="H113" s="6">
+        <v>10</v>
+      </c>
+      <c r="I113" s="6">
+        <v>8</v>
+      </c>
+      <c r="J113" s="6">
+        <v>18</v>
+      </c>
+      <c r="K113" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="L113" s="7">
+        <v>0.0361111111111111</v>
+      </c>
+      <c r="M113" s="6">
+        <v>3180</v>
+      </c>
+      <c r="N113" s="6">
+        <v>335.94</v>
+      </c>
+      <c r="O113" s="6">
+        <v>26.1</v>
+      </c>
+      <c r="P113" s="6">
+        <v>72.49</v>
+      </c>
+      <c r="Q113" s="6">
+        <v>61.15</v>
+      </c>
+      <c r="R113" s="6">
+        <v>6.46</v>
+      </c>
+      <c r="S113" s="6">
+        <v>0.23</v>
+      </c>
+      <c r="T113" s="6">
+        <v>0</v>
+      </c>
+      <c r="U113" s="6">
+        <v>0</v>
+      </c>
+      <c r="V113" s="6">
+        <v>0</v>
+      </c>
+      <c r="W113" s="6">
+        <v>0</v>
+      </c>
+      <c r="X113" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y113" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z113" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA113" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB113" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC113" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD113" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE113" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF113" s="6">
+        <v>274.23</v>
+      </c>
+      <c r="AG113" s="6">
+        <v>389.33</v>
+      </c>
+      <c r="AH113" s="6">
+        <v>46.49</v>
+      </c>
+      <c r="AI113" s="6">
+        <v>1307.9</v>
+      </c>
+      <c r="AJ113" s="6">
+        <v>1195.14</v>
+      </c>
+      <c r="AK113" s="6">
+        <v>487.9</v>
+      </c>
+      <c r="AL113" s="6">
+        <v>137.06</v>
+      </c>
+      <c r="AM113" s="6">
+        <v>5.36</v>
+      </c>
+      <c r="AN113" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO113" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AP113" s="6">
+        <v>142.42</v>
+      </c>
+      <c r="AQ113" s="6">
+        <v>9</v>
+      </c>
+      <c r="AR113" s="6">
+        <v>2.74</v>
+      </c>
+      <c r="AS113" s="6">
+        <v>33</v>
+      </c>
+      <c r="AT113" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU113" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV113" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW113" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX113" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="114" spans="1:50">
+      <c r="A114" t="s">
+        <v>123</v>
+      </c>
+      <c r="B114" t="s">
+        <v>82</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E114" s="6">
+        <v>0</v>
+      </c>
+      <c r="F114" s="6">
+        <v>4.03</v>
+      </c>
+      <c r="G114" s="6">
+        <v>-5.42</v>
+      </c>
+      <c r="H114" s="6">
+        <v>13</v>
+      </c>
+      <c r="I114" s="6">
+        <v>23</v>
+      </c>
+      <c r="J114" s="6">
+        <v>36</v>
+      </c>
+      <c r="K114" s="6">
+        <v>0.69</v>
+      </c>
+      <c r="L114" s="7">
+        <v>0.0361111111111111</v>
+      </c>
+      <c r="M114" s="6">
+        <v>5868.37</v>
+      </c>
+      <c r="N114" s="6">
+        <v>581.13</v>
+      </c>
+      <c r="O114" s="6">
+        <v>26.748</v>
+      </c>
+      <c r="P114" s="6">
+        <v>74.3</v>
+      </c>
+      <c r="Q114" s="6">
+        <v>112.85</v>
+      </c>
+      <c r="R114" s="6">
+        <v>11.18</v>
+      </c>
+      <c r="S114" s="6">
+        <v>0.34</v>
+      </c>
+      <c r="T114" s="6">
+        <v>0</v>
+      </c>
+      <c r="U114" s="6">
+        <v>0</v>
+      </c>
+      <c r="V114" s="6">
+        <v>0</v>
+      </c>
+      <c r="W114" s="6">
+        <v>0</v>
+      </c>
+      <c r="X114" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y114" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA114" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB114" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC114" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD114" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE114" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF114" s="6">
+        <v>511.54</v>
+      </c>
+      <c r="AG114" s="6">
+        <v>804.75</v>
+      </c>
+      <c r="AH114" s="6">
+        <v>83.61</v>
+      </c>
+      <c r="AI114" s="6">
+        <v>1926.39</v>
+      </c>
+      <c r="AJ114" s="6">
+        <v>2640.94</v>
+      </c>
+      <c r="AK114" s="6">
+        <v>944.18</v>
+      </c>
+      <c r="AL114" s="6">
+        <v>258.75</v>
+      </c>
+      <c r="AM114" s="6">
+        <v>12.93</v>
+      </c>
+      <c r="AN114" s="6">
+        <v>1</v>
+      </c>
+      <c r="AO114" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="AP114" s="6">
+        <v>271.68</v>
+      </c>
+      <c r="AQ114" s="6">
+        <v>18</v>
+      </c>
+      <c r="AR114" s="6">
+        <v>5.22</v>
+      </c>
+      <c r="AS114" s="6">
+        <v>37</v>
+      </c>
+      <c r="AT114" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU114" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV114" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW114" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX114" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="115" spans="1:50">
+      <c r="A115" t="s">
+        <v>123</v>
+      </c>
+      <c r="B115" t="s">
+        <v>82</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E115" s="6">
+        <v>0</v>
+      </c>
+      <c r="F115" s="6">
+        <v>4.03</v>
+      </c>
+      <c r="G115" s="6">
+        <v>-4.97</v>
+      </c>
+      <c r="H115" s="6">
+        <v>12</v>
+      </c>
+      <c r="I115" s="6">
+        <v>26</v>
+      </c>
+      <c r="J115" s="6">
+        <v>38</v>
+      </c>
+      <c r="K115" s="6">
+        <v>0.47</v>
+      </c>
+      <c r="L115" s="7">
+        <v>0.05625</v>
+      </c>
+      <c r="M115" s="6">
+        <v>8544.58</v>
+      </c>
+      <c r="N115" s="6">
+        <v>887.42</v>
+      </c>
+      <c r="O115" s="6">
+        <v>27.432</v>
+      </c>
+      <c r="P115" s="6">
+        <v>76.23</v>
+      </c>
+      <c r="Q115" s="6">
+        <v>105.49</v>
+      </c>
+      <c r="R115" s="6">
+        <v>10.96</v>
+      </c>
+      <c r="S115" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="T115" s="6">
+        <v>0</v>
+      </c>
+      <c r="U115" s="6">
+        <v>0</v>
+      </c>
+      <c r="V115" s="6">
+        <v>0</v>
+      </c>
+      <c r="W115" s="6">
+        <v>0</v>
+      </c>
+      <c r="X115" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y115" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z115" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA115" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB115" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC115" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD115" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE115" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF115" s="6">
+        <v>740.99</v>
+      </c>
+      <c r="AG115" s="6">
+        <v>1000.63</v>
+      </c>
+      <c r="AH115" s="6">
+        <v>154.01</v>
+      </c>
+      <c r="AI115" s="6">
+        <v>3944.92</v>
+      </c>
+      <c r="AJ115" s="6">
+        <v>2999.21</v>
+      </c>
+      <c r="AK115" s="6">
+        <v>1187.39</v>
+      </c>
+      <c r="AL115" s="6">
+        <v>217.3</v>
+      </c>
+      <c r="AM115" s="6">
+        <v>41.69</v>
+      </c>
+      <c r="AN115" s="6">
+        <v>3</v>
+      </c>
+      <c r="AO115" s="6">
+        <v>0.51</v>
+      </c>
+      <c r="AP115" s="6">
+        <v>258.99</v>
+      </c>
+      <c r="AQ115" s="6">
+        <v>10</v>
+      </c>
+      <c r="AR115" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="AS115" s="6">
+        <v>136</v>
+      </c>
+      <c r="AT115" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU115" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV115" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW115" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX115" s="6" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/GPS_Formativas_2026.xlsx
+++ b/GPS_Formativas_2026.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="129">
   <si>
     <t>Date</t>
   </si>
@@ -399,6 +399,21 @@
   </si>
   <si>
     <t>23-5-26</t>
+  </si>
+  <si>
+    <t>U15</t>
+  </si>
+  <si>
+    <t>Benjamin Arigon</t>
+  </si>
+  <si>
+    <t>Lucas Juarez</t>
+  </si>
+  <si>
+    <t>Ramiro Mombrum</t>
+  </si>
+  <si>
+    <t>Facundo Muniz</t>
   </si>
 </sst>
 </file>
@@ -1575,7 +1590,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AX115"/>
+  <dimension ref="A1:AX119"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="30.4444444444444" customWidth="1"/>
@@ -19062,6 +19077,614 @@
         <v>58</v>
       </c>
     </row>
+    <row r="116" spans="1:50">
+      <c r="A116" t="s">
+        <v>121</v>
+      </c>
+      <c r="B116" t="s">
+        <v>124</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E116" s="6">
+        <v>0</v>
+      </c>
+      <c r="F116" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="G116" s="6">
+        <v>-5.16</v>
+      </c>
+      <c r="H116" s="6">
+        <v>6</v>
+      </c>
+      <c r="I116" s="6">
+        <v>8</v>
+      </c>
+      <c r="J116" s="6">
+        <v>14</v>
+      </c>
+      <c r="K116" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="L116" s="6">
+        <v>0.0631944444444444</v>
+      </c>
+      <c r="M116" s="6">
+        <v>5253.2</v>
+      </c>
+      <c r="N116" s="6">
+        <v>591.38</v>
+      </c>
+      <c r="O116" s="6">
+        <v>22.212</v>
+      </c>
+      <c r="P116" s="6">
+        <v>61.69</v>
+      </c>
+      <c r="Q116" s="6">
+        <v>58.86</v>
+      </c>
+      <c r="R116" s="6">
+        <v>6.5</v>
+      </c>
+      <c r="S116" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="T116" s="6">
+        <v>151</v>
+      </c>
+      <c r="U116" s="6">
+        <v>112.25</v>
+      </c>
+      <c r="V116" s="6">
+        <v>75.5</v>
+      </c>
+      <c r="W116" s="6">
+        <v>56.12</v>
+      </c>
+      <c r="X116" s="6">
+        <v>42.82</v>
+      </c>
+      <c r="Y116" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="6">
+        <v>0.00869212962962963</v>
+      </c>
+      <c r="AA116" s="6">
+        <v>0.0110185185185185</v>
+      </c>
+      <c r="AB116" s="6">
+        <v>0.00520833333333333</v>
+      </c>
+      <c r="AC116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>447.52</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>379.8</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>345.46</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>2452.66</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>2082.08</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>341</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>31.39</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP116" s="6">
+        <v>31.39</v>
+      </c>
+      <c r="AQ116" s="6">
+        <v>3</v>
+      </c>
+      <c r="AR116" s="6">
+        <v>0.34</v>
+      </c>
+      <c r="AS116" s="6">
+        <v>25</v>
+      </c>
+      <c r="AT116" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU116" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV116" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW116" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX116" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="117" spans="1:50">
+      <c r="A117" t="s">
+        <v>121</v>
+      </c>
+      <c r="B117" t="s">
+        <v>124</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E117" s="6">
+        <v>0</v>
+      </c>
+      <c r="F117" s="6">
+        <v>3.62</v>
+      </c>
+      <c r="G117" s="6">
+        <v>-4.32</v>
+      </c>
+      <c r="H117" s="6">
+        <v>10</v>
+      </c>
+      <c r="I117" s="6">
+        <v>16</v>
+      </c>
+      <c r="J117" s="6">
+        <v>26</v>
+      </c>
+      <c r="K117" s="6">
+        <v>0.29</v>
+      </c>
+      <c r="L117" s="6">
+        <v>0.0631944444444444</v>
+      </c>
+      <c r="M117" s="6">
+        <v>6028.39</v>
+      </c>
+      <c r="N117" s="6">
+        <v>690.17</v>
+      </c>
+      <c r="O117" s="6">
+        <v>25.884</v>
+      </c>
+      <c r="P117" s="6">
+        <v>71.94</v>
+      </c>
+      <c r="Q117" s="6">
+        <v>67.85</v>
+      </c>
+      <c r="R117" s="6">
+        <v>7.58</v>
+      </c>
+      <c r="S117" s="6">
+        <v>0.14</v>
+      </c>
+      <c r="T117" s="6">
+        <v>0</v>
+      </c>
+      <c r="U117" s="6">
+        <v>0</v>
+      </c>
+      <c r="V117" s="6">
+        <v>0</v>
+      </c>
+      <c r="W117" s="6">
+        <v>0</v>
+      </c>
+      <c r="X117" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y117" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z117" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA117" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB117" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC117" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD117" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE117" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF117" s="6">
+        <v>525.19</v>
+      </c>
+      <c r="AG117" s="6">
+        <v>751.46</v>
+      </c>
+      <c r="AH117" s="6">
+        <v>306.48</v>
+      </c>
+      <c r="AI117" s="6">
+        <v>2156.64</v>
+      </c>
+      <c r="AJ117" s="6">
+        <v>2654.33</v>
+      </c>
+      <c r="AK117" s="6">
+        <v>699.48</v>
+      </c>
+      <c r="AL117" s="6">
+        <v>195.51</v>
+      </c>
+      <c r="AM117" s="6">
+        <v>15.96</v>
+      </c>
+      <c r="AN117" s="6">
+        <v>1</v>
+      </c>
+      <c r="AO117" s="6">
+        <v>0.18</v>
+      </c>
+      <c r="AP117" s="6">
+        <v>211.47</v>
+      </c>
+      <c r="AQ117" s="6">
+        <v>14</v>
+      </c>
+      <c r="AR117" s="6">
+        <v>2.32</v>
+      </c>
+      <c r="AS117" s="6">
+        <v>21</v>
+      </c>
+      <c r="AT117" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU117" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV117" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW117" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX117" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="118" spans="1:50">
+      <c r="A118" t="s">
+        <v>121</v>
+      </c>
+      <c r="B118" t="s">
+        <v>124</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E118" s="6">
+        <v>0</v>
+      </c>
+      <c r="F118" s="6">
+        <v>3.87</v>
+      </c>
+      <c r="G118" s="6">
+        <v>-4.27</v>
+      </c>
+      <c r="H118" s="6">
+        <v>10</v>
+      </c>
+      <c r="I118" s="6">
+        <v>6</v>
+      </c>
+      <c r="J118" s="6">
+        <v>16</v>
+      </c>
+      <c r="K118" s="6">
+        <v>0.18</v>
+      </c>
+      <c r="L118" s="6">
+        <v>0.0631944444444444</v>
+      </c>
+      <c r="M118" s="6">
+        <v>4855.85</v>
+      </c>
+      <c r="N118" s="6">
+        <v>583.26</v>
+      </c>
+      <c r="O118" s="6">
+        <v>24.876</v>
+      </c>
+      <c r="P118" s="6">
+        <v>69.14</v>
+      </c>
+      <c r="Q118" s="6">
+        <v>54.89</v>
+      </c>
+      <c r="R118" s="6">
+        <v>6.41</v>
+      </c>
+      <c r="S118" s="6">
+        <v>0.07</v>
+      </c>
+      <c r="T118" s="6">
+        <v>0</v>
+      </c>
+      <c r="U118" s="6">
+        <v>0</v>
+      </c>
+      <c r="V118" s="6">
+        <v>0</v>
+      </c>
+      <c r="W118" s="6">
+        <v>0</v>
+      </c>
+      <c r="X118" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y118" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z118" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA118" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB118" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC118" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD118" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE118" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF118" s="6">
+        <v>414.25</v>
+      </c>
+      <c r="AG118" s="6">
+        <v>357.25</v>
+      </c>
+      <c r="AH118" s="6">
+        <v>324.86</v>
+      </c>
+      <c r="AI118" s="6">
+        <v>2143.4</v>
+      </c>
+      <c r="AJ118" s="6">
+        <v>1981.46</v>
+      </c>
+      <c r="AK118" s="6">
+        <v>377.21</v>
+      </c>
+      <c r="AL118" s="6">
+        <v>28.58</v>
+      </c>
+      <c r="AM118" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN118" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO118" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP118" s="6">
+        <v>28.58</v>
+      </c>
+      <c r="AQ118" s="6">
+        <v>2</v>
+      </c>
+      <c r="AR118" s="6">
+        <v>0.31</v>
+      </c>
+      <c r="AS118" s="6">
+        <v>29</v>
+      </c>
+      <c r="AT118" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU118" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV118" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW118" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX118" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="119" spans="1:50">
+      <c r="A119" t="s">
+        <v>121</v>
+      </c>
+      <c r="B119" t="s">
+        <v>124</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E119" s="6">
+        <v>0</v>
+      </c>
+      <c r="F119" s="6">
+        <v>3.39</v>
+      </c>
+      <c r="G119" s="6">
+        <v>-3.73</v>
+      </c>
+      <c r="H119" s="6">
+        <v>5</v>
+      </c>
+      <c r="I119" s="6">
+        <v>8</v>
+      </c>
+      <c r="J119" s="6">
+        <v>13</v>
+      </c>
+      <c r="K119" s="6">
+        <v>0.14</v>
+      </c>
+      <c r="L119" s="6">
+        <v>0.0631944444444444</v>
+      </c>
+      <c r="M119" s="6">
+        <v>5189.43</v>
+      </c>
+      <c r="N119" s="6">
+        <v>506.03</v>
+      </c>
+      <c r="O119" s="6">
+        <v>28.548</v>
+      </c>
+      <c r="P119" s="6">
+        <v>79.34</v>
+      </c>
+      <c r="Q119" s="6">
+        <v>57.99</v>
+      </c>
+      <c r="R119" s="6">
+        <v>5.56</v>
+      </c>
+      <c r="S119" s="6">
+        <v>0.09</v>
+      </c>
+      <c r="T119" s="6">
+        <v>0</v>
+      </c>
+      <c r="U119" s="6">
+        <v>0</v>
+      </c>
+      <c r="V119" s="6">
+        <v>0</v>
+      </c>
+      <c r="W119" s="6">
+        <v>0</v>
+      </c>
+      <c r="X119" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y119" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z119" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA119" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB119" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC119" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD119" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE119" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF119" s="6">
+        <v>437.7</v>
+      </c>
+      <c r="AG119" s="6">
+        <v>527.69</v>
+      </c>
+      <c r="AH119" s="6">
+        <v>264.96</v>
+      </c>
+      <c r="AI119" s="6">
+        <v>2079.53</v>
+      </c>
+      <c r="AJ119" s="6">
+        <v>1788.27</v>
+      </c>
+      <c r="AK119" s="6">
+        <v>841.58</v>
+      </c>
+      <c r="AL119" s="6">
+        <v>194.83</v>
+      </c>
+      <c r="AM119" s="6">
+        <v>20.26</v>
+      </c>
+      <c r="AN119" s="6">
+        <v>1</v>
+      </c>
+      <c r="AO119" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="AP119" s="6">
+        <v>215.09</v>
+      </c>
+      <c r="AQ119" s="6">
+        <v>11</v>
+      </c>
+      <c r="AR119" s="6">
+        <v>2.36</v>
+      </c>
+      <c r="AS119" s="6">
+        <v>10</v>
+      </c>
+      <c r="AT119" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU119" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV119" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW119" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX119" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/GPS_Formativas_2026.xlsx
+++ b/GPS_Formativas_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="GPS_Formativas_2026" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="144">
   <si>
     <t>Date</t>
   </si>
@@ -415,6 +415,51 @@
   <si>
     <t>Facundo Muniz</t>
   </si>
+  <si>
+    <t>27-5-26</t>
+  </si>
+  <si>
+    <t>U16</t>
+  </si>
+  <si>
+    <t>Kimey Do Santo</t>
+  </si>
+  <si>
+    <t>MD-4</t>
+  </si>
+  <si>
+    <t>Lucas Ferron</t>
+  </si>
+  <si>
+    <t>Dilan Furtado</t>
+  </si>
+  <si>
+    <t>Thiago Gainza</t>
+  </si>
+  <si>
+    <t>Valentino Moreira</t>
+  </si>
+  <si>
+    <t>DEF</t>
+  </si>
+  <si>
+    <t>28-5-26</t>
+  </si>
+  <si>
+    <t>EXTENSIVA</t>
+  </si>
+  <si>
+    <t>Benjamin Silvera</t>
+  </si>
+  <si>
+    <t>25/5</t>
+  </si>
+  <si>
+    <t>INTRODUCTORIA</t>
+  </si>
+  <si>
+    <t>26/5</t>
+  </si>
 </sst>
 </file>
 
@@ -426,14 +471,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -906,13 +944,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -921,122 +962,119 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1049,14 +1087,8 @@
     <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="35" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1590,7 +1622,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AX119"/>
+  <dimension ref="A1:AX144"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="30.4444444444444" customWidth="1"/>
@@ -16500,148 +16532,148 @@
       <c r="B99" t="s">
         <v>51</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="D99" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E99" s="4">
-        <v>0</v>
-      </c>
-      <c r="F99" s="4">
+      <c r="E99" s="2">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2">
         <v>3.8</v>
       </c>
-      <c r="G99" s="4">
+      <c r="G99" s="2">
         <v>-4.67</v>
       </c>
-      <c r="H99" s="4">
+      <c r="H99" s="2">
         <v>21</v>
       </c>
-      <c r="I99" s="4">
+      <c r="I99" s="2">
         <v>22</v>
       </c>
-      <c r="J99" s="4">
+      <c r="J99" s="2">
         <v>43</v>
       </c>
-      <c r="K99" s="4">
+      <c r="K99" s="2">
         <v>0.61</v>
       </c>
-      <c r="L99" s="5">
+      <c r="L99" s="3">
         <v>0.0486111111111111</v>
       </c>
-      <c r="M99" s="4">
+      <c r="M99" s="2">
         <v>5227.93</v>
       </c>
-      <c r="N99" s="4">
+      <c r="N99" s="2">
         <v>507.91</v>
       </c>
-      <c r="O99" s="4">
+      <c r="O99" s="2">
         <v>26.496</v>
       </c>
-      <c r="P99" s="4">
+      <c r="P99" s="2">
         <v>73.64</v>
       </c>
-      <c r="Q99" s="4">
+      <c r="Q99" s="2">
         <v>74.68</v>
       </c>
-      <c r="R99" s="4">
+      <c r="R99" s="2">
         <v>7.26</v>
       </c>
-      <c r="S99" s="4">
+      <c r="S99" s="2">
         <v>0.13</v>
       </c>
-      <c r="T99" s="4">
-        <v>0</v>
-      </c>
-      <c r="U99" s="4">
-        <v>0</v>
-      </c>
-      <c r="V99" s="4">
-        <v>0</v>
-      </c>
-      <c r="W99" s="4">
-        <v>0</v>
-      </c>
-      <c r="X99" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y99" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z99" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA99" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB99" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC99" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD99" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE99" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF99" s="4">
+      <c r="T99" s="2">
+        <v>0</v>
+      </c>
+      <c r="U99" s="2">
+        <v>0</v>
+      </c>
+      <c r="V99" s="2">
+        <v>0</v>
+      </c>
+      <c r="W99" s="2">
+        <v>0</v>
+      </c>
+      <c r="X99" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="2">
         <v>467.22</v>
       </c>
-      <c r="AG99" s="4">
+      <c r="AG99" s="2">
         <v>742.65</v>
       </c>
-      <c r="AH99" s="4">
+      <c r="AH99" s="2">
         <v>189.02</v>
       </c>
-      <c r="AI99" s="4">
+      <c r="AI99" s="2">
         <v>2380.64</v>
       </c>
-      <c r="AJ99" s="4">
+      <c r="AJ99" s="2">
         <v>1806.8</v>
       </c>
-      <c r="AK99" s="4">
+      <c r="AK99" s="2">
         <v>719.21</v>
       </c>
-      <c r="AL99" s="4">
+      <c r="AL99" s="2">
         <v>118.07</v>
       </c>
-      <c r="AM99" s="4">
+      <c r="AM99" s="2">
         <v>14.19</v>
       </c>
-      <c r="AN99" s="4">
+      <c r="AN99" s="2">
         <v>1</v>
       </c>
-      <c r="AO99" s="4">
+      <c r="AO99" s="2">
         <v>0.2</v>
       </c>
-      <c r="AP99" s="4">
+      <c r="AP99" s="2">
         <v>132.26</v>
       </c>
-      <c r="AQ99" s="4">
+      <c r="AQ99" s="2">
         <v>10</v>
       </c>
-      <c r="AR99" s="4">
+      <c r="AR99" s="2">
         <v>1.89</v>
       </c>
-      <c r="AS99" s="4">
+      <c r="AS99" s="2">
         <v>25</v>
       </c>
-      <c r="AT99" s="4" t="s">
+      <c r="AT99" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AU99" s="4" t="s">
+      <c r="AU99" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AV99" s="4" t="s">
+      <c r="AV99" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AW99" s="4" t="s">
+      <c r="AW99" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX99" s="4" t="s">
+      <c r="AX99" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -16652,148 +16684,148 @@
       <c r="B100" t="s">
         <v>51</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="D100" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E100" s="4">
-        <v>0</v>
-      </c>
-      <c r="F100" s="4">
+      <c r="E100" s="2">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2">
         <v>4.13</v>
       </c>
-      <c r="G100" s="4">
+      <c r="G100" s="2">
         <v>-3.81</v>
       </c>
-      <c r="H100" s="4">
+      <c r="H100" s="2">
         <v>21</v>
       </c>
-      <c r="I100" s="4">
+      <c r="I100" s="2">
         <v>15</v>
       </c>
-      <c r="J100" s="4">
+      <c r="J100" s="2">
         <v>36</v>
       </c>
-      <c r="K100" s="4">
+      <c r="K100" s="2">
         <v>0.51</v>
       </c>
-      <c r="L100" s="5">
+      <c r="L100" s="3">
         <v>0.0486111111111111</v>
       </c>
-      <c r="M100" s="4">
+      <c r="M100" s="2">
         <v>5492.02</v>
       </c>
-      <c r="N100" s="4">
+      <c r="N100" s="2">
         <v>520.02</v>
       </c>
-      <c r="O100" s="4">
+      <c r="O100" s="2">
         <v>25.128</v>
       </c>
-      <c r="P100" s="4">
+      <c r="P100" s="2">
         <v>69.82</v>
       </c>
-      <c r="Q100" s="4">
+      <c r="Q100" s="2">
         <v>78.46</v>
       </c>
-      <c r="R100" s="4">
+      <c r="R100" s="2">
         <v>7.43</v>
       </c>
-      <c r="S100" s="4">
+      <c r="S100" s="2">
         <v>0.11</v>
       </c>
-      <c r="T100" s="4">
-        <v>0</v>
-      </c>
-      <c r="U100" s="4">
-        <v>0</v>
-      </c>
-      <c r="V100" s="4">
-        <v>0</v>
-      </c>
-      <c r="W100" s="4">
-        <v>0</v>
-      </c>
-      <c r="X100" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE100" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="4">
+      <c r="T100" s="2">
+        <v>0</v>
+      </c>
+      <c r="U100" s="2">
+        <v>0</v>
+      </c>
+      <c r="V100" s="2">
+        <v>0</v>
+      </c>
+      <c r="W100" s="2">
+        <v>0</v>
+      </c>
+      <c r="X100" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="2">
         <v>479.32</v>
       </c>
-      <c r="AG100" s="4">
+      <c r="AG100" s="2">
         <v>526.41</v>
       </c>
-      <c r="AH100" s="4">
+      <c r="AH100" s="2">
         <v>203.84</v>
       </c>
-      <c r="AI100" s="4">
+      <c r="AI100" s="2">
         <v>2900.66</v>
       </c>
-      <c r="AJ100" s="4">
+      <c r="AJ100" s="2">
         <v>1861.78</v>
       </c>
-      <c r="AK100" s="4">
+      <c r="AK100" s="2">
         <v>463.24</v>
       </c>
-      <c r="AL100" s="4">
+      <c r="AL100" s="2">
         <v>62.49</v>
       </c>
-      <c r="AM100" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN100" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO100" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP100" s="4">
+      <c r="AM100" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN100" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO100" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP100" s="2">
         <v>62.49</v>
       </c>
-      <c r="AQ100" s="4">
+      <c r="AQ100" s="2">
         <v>6</v>
       </c>
-      <c r="AR100" s="4">
+      <c r="AR100" s="2">
         <v>0.89</v>
       </c>
-      <c r="AS100" s="4">
+      <c r="AS100" s="2">
         <v>18</v>
       </c>
-      <c r="AT100" s="4" t="s">
+      <c r="AT100" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AU100" s="4" t="s">
+      <c r="AU100" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AV100" s="4" t="s">
+      <c r="AV100" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AW100" s="4" t="s">
+      <c r="AW100" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX100" s="4" t="s">
+      <c r="AX100" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -16804,148 +16836,148 @@
       <c r="B101" t="s">
         <v>51</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D101" s="4" t="s">
+      <c r="D101" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E101" s="4">
-        <v>0</v>
-      </c>
-      <c r="F101" s="4">
+      <c r="E101" s="2">
+        <v>0</v>
+      </c>
+      <c r="F101" s="2">
         <v>4.28</v>
       </c>
-      <c r="G101" s="4">
+      <c r="G101" s="2">
         <v>-5.05</v>
       </c>
-      <c r="H101" s="4">
+      <c r="H101" s="2">
         <v>22</v>
       </c>
-      <c r="I101" s="4">
+      <c r="I101" s="2">
         <v>23</v>
       </c>
-      <c r="J101" s="4">
+      <c r="J101" s="2">
         <v>45</v>
       </c>
-      <c r="K101" s="4">
+      <c r="K101" s="2">
         <v>0.64</v>
       </c>
-      <c r="L101" s="5">
+      <c r="L101" s="3">
         <v>0.0486111111111111</v>
       </c>
-      <c r="M101" s="4">
+      <c r="M101" s="2">
         <v>5362.14</v>
       </c>
-      <c r="N101" s="4">
+      <c r="N101" s="2">
         <v>539.27</v>
       </c>
-      <c r="O101" s="4">
+      <c r="O101" s="2">
         <v>26.352</v>
       </c>
-      <c r="P101" s="4">
+      <c r="P101" s="2">
         <v>73.19</v>
       </c>
-      <c r="Q101" s="4">
+      <c r="Q101" s="2">
         <v>76.6</v>
       </c>
-      <c r="R101" s="4">
+      <c r="R101" s="2">
         <v>7.7</v>
       </c>
-      <c r="S101" s="4">
+      <c r="S101" s="2">
         <v>0.11</v>
       </c>
-      <c r="T101" s="4">
-        <v>0</v>
-      </c>
-      <c r="U101" s="4">
-        <v>0</v>
-      </c>
-      <c r="V101" s="4">
-        <v>0</v>
-      </c>
-      <c r="W101" s="4">
-        <v>0</v>
-      </c>
-      <c r="X101" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD101" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF101" s="4">
+      <c r="T101" s="2">
+        <v>0</v>
+      </c>
+      <c r="U101" s="2">
+        <v>0</v>
+      </c>
+      <c r="V101" s="2">
+        <v>0</v>
+      </c>
+      <c r="W101" s="2">
+        <v>0</v>
+      </c>
+      <c r="X101" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="2">
         <v>476.42</v>
       </c>
-      <c r="AG101" s="4">
+      <c r="AG101" s="2">
         <v>660.64</v>
       </c>
-      <c r="AH101" s="4">
+      <c r="AH101" s="2">
         <v>167.35</v>
       </c>
-      <c r="AI101" s="4">
+      <c r="AI101" s="2">
         <v>2855.15</v>
       </c>
-      <c r="AJ101" s="4">
+      <c r="AJ101" s="2">
         <v>1618.69</v>
       </c>
-      <c r="AK101" s="4">
+      <c r="AK101" s="2">
         <v>549.09</v>
       </c>
-      <c r="AL101" s="4">
+      <c r="AL101" s="2">
         <v>149.47</v>
       </c>
-      <c r="AM101" s="4">
+      <c r="AM101" s="2">
         <v>22.39</v>
       </c>
-      <c r="AN101" s="4">
+      <c r="AN101" s="2">
         <v>1</v>
       </c>
-      <c r="AO101" s="4">
+      <c r="AO101" s="2">
         <v>0.32</v>
       </c>
-      <c r="AP101" s="4">
+      <c r="AP101" s="2">
         <v>171.86</v>
       </c>
-      <c r="AQ101" s="4">
+      <c r="AQ101" s="2">
         <v>12</v>
       </c>
-      <c r="AR101" s="4">
+      <c r="AR101" s="2">
         <v>2.46</v>
       </c>
-      <c r="AS101" s="4">
+      <c r="AS101" s="2">
         <v>94</v>
       </c>
-      <c r="AT101" s="4" t="s">
+      <c r="AT101" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AU101" s="4" t="s">
+      <c r="AU101" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AV101" s="4" t="s">
+      <c r="AV101" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AW101" s="4" t="s">
+      <c r="AW101" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX101" s="4" t="s">
+      <c r="AX101" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -16956,148 +16988,148 @@
       <c r="B102" t="s">
         <v>51</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="D102" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E102" s="4">
-        <v>0</v>
-      </c>
-      <c r="F102" s="4">
+      <c r="E102" s="2">
+        <v>0</v>
+      </c>
+      <c r="F102" s="2">
         <v>3.94</v>
       </c>
-      <c r="G102" s="4">
+      <c r="G102" s="2">
         <v>-4.57</v>
       </c>
-      <c r="H102" s="4">
+      <c r="H102" s="2">
         <v>11</v>
       </c>
-      <c r="I102" s="4">
+      <c r="I102" s="2">
         <v>25</v>
       </c>
-      <c r="J102" s="4">
+      <c r="J102" s="2">
         <v>36</v>
       </c>
-      <c r="K102" s="4">
+      <c r="K102" s="2">
         <v>0.51</v>
       </c>
-      <c r="L102" s="5">
+      <c r="L102" s="3">
         <v>0.0486111111111111</v>
       </c>
-      <c r="M102" s="4">
+      <c r="M102" s="2">
         <v>5109.37</v>
       </c>
-      <c r="N102" s="4">
+      <c r="N102" s="2">
         <v>569.15</v>
       </c>
-      <c r="O102" s="4">
+      <c r="O102" s="2">
         <v>24.588</v>
       </c>
-      <c r="P102" s="4">
+      <c r="P102" s="2">
         <v>68.31</v>
       </c>
-      <c r="Q102" s="4">
+      <c r="Q102" s="2">
         <v>72.99</v>
       </c>
-      <c r="R102" s="4">
+      <c r="R102" s="2">
         <v>8.13</v>
       </c>
-      <c r="S102" s="4">
+      <c r="S102" s="2">
         <v>0.12</v>
       </c>
-      <c r="T102" s="4">
-        <v>0</v>
-      </c>
-      <c r="U102" s="4">
-        <v>0</v>
-      </c>
-      <c r="V102" s="4">
-        <v>0</v>
-      </c>
-      <c r="W102" s="4">
-        <v>0</v>
-      </c>
-      <c r="X102" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC102" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE102" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF102" s="4">
+      <c r="T102" s="2">
+        <v>0</v>
+      </c>
+      <c r="U102" s="2">
+        <v>0</v>
+      </c>
+      <c r="V102" s="2">
+        <v>0</v>
+      </c>
+      <c r="W102" s="2">
+        <v>0</v>
+      </c>
+      <c r="X102" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="2">
         <v>366.39</v>
       </c>
-      <c r="AG102" s="4">
+      <c r="AG102" s="2">
         <v>579.66</v>
       </c>
-      <c r="AH102" s="4">
+      <c r="AH102" s="2">
         <v>250.62</v>
       </c>
-      <c r="AI102" s="4">
+      <c r="AI102" s="2">
         <v>2381.33</v>
       </c>
-      <c r="AJ102" s="4">
+      <c r="AJ102" s="2">
         <v>1920.87</v>
       </c>
-      <c r="AK102" s="4">
+      <c r="AK102" s="2">
         <v>502.3</v>
       </c>
-      <c r="AL102" s="4">
+      <c r="AL102" s="2">
         <v>54.32</v>
       </c>
-      <c r="AM102" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN102" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO102" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP102" s="4">
+      <c r="AM102" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP102" s="2">
         <v>54.32</v>
       </c>
-      <c r="AQ102" s="4">
+      <c r="AQ102" s="2">
         <v>5</v>
       </c>
-      <c r="AR102" s="4">
+      <c r="AR102" s="2">
         <v>0.78</v>
       </c>
-      <c r="AS102" s="4">
+      <c r="AS102" s="2">
         <v>25</v>
       </c>
-      <c r="AT102" s="4" t="s">
+      <c r="AT102" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AU102" s="4" t="s">
+      <c r="AU102" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AV102" s="4" t="s">
+      <c r="AV102" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AW102" s="4" t="s">
+      <c r="AW102" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX102" s="4" t="s">
+      <c r="AX102" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -17108,148 +17140,148 @@
       <c r="B103" t="s">
         <v>51</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C103" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D103" s="4" t="s">
+      <c r="D103" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E103" s="4">
-        <v>0</v>
-      </c>
-      <c r="F103" s="4">
+      <c r="E103" s="2">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2">
         <v>3.91</v>
       </c>
-      <c r="G103" s="4">
+      <c r="G103" s="2">
         <v>-4.39</v>
       </c>
-      <c r="H103" s="4">
+      <c r="H103" s="2">
         <v>19</v>
       </c>
-      <c r="I103" s="4">
+      <c r="I103" s="2">
         <v>19</v>
       </c>
-      <c r="J103" s="4">
+      <c r="J103" s="2">
         <v>38</v>
       </c>
-      <c r="K103" s="4">
+      <c r="K103" s="2">
         <v>0.54</v>
       </c>
-      <c r="L103" s="5">
+      <c r="L103" s="3">
         <v>0.0486111111111111</v>
       </c>
-      <c r="M103" s="4">
+      <c r="M103" s="2">
         <v>5242.69</v>
       </c>
-      <c r="N103" s="4">
+      <c r="N103" s="2">
         <v>473.96</v>
       </c>
-      <c r="O103" s="4">
+      <c r="O103" s="2">
         <v>25.308</v>
       </c>
-      <c r="P103" s="4">
+      <c r="P103" s="2">
         <v>70.33</v>
       </c>
-      <c r="Q103" s="4">
+      <c r="Q103" s="2">
         <v>74.9</v>
       </c>
-      <c r="R103" s="4">
+      <c r="R103" s="2">
         <v>6.77</v>
       </c>
-      <c r="S103" s="4">
+      <c r="S103" s="2">
         <v>0.1</v>
       </c>
-      <c r="T103" s="4">
-        <v>0</v>
-      </c>
-      <c r="U103" s="4">
-        <v>0</v>
-      </c>
-      <c r="V103" s="4">
-        <v>0</v>
-      </c>
-      <c r="W103" s="4">
-        <v>0</v>
-      </c>
-      <c r="X103" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y103" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z103" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA103" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB103" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC103" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD103" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE103" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF103" s="4">
+      <c r="T103" s="2">
+        <v>0</v>
+      </c>
+      <c r="U103" s="2">
+        <v>0</v>
+      </c>
+      <c r="V103" s="2">
+        <v>0</v>
+      </c>
+      <c r="W103" s="2">
+        <v>0</v>
+      </c>
+      <c r="X103" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y103" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z103" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA103" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB103" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC103" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD103" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF103" s="2">
         <v>1249.65</v>
       </c>
-      <c r="AG103" s="4">
+      <c r="AG103" s="2">
         <v>620.02</v>
       </c>
-      <c r="AH103" s="4">
+      <c r="AH103" s="2">
         <v>190.47</v>
       </c>
-      <c r="AI103" s="4">
+      <c r="AI103" s="2">
         <v>2727.23</v>
       </c>
-      <c r="AJ103" s="4">
+      <c r="AJ103" s="2">
         <v>1766.23</v>
       </c>
-      <c r="AK103" s="4">
+      <c r="AK103" s="2">
         <v>441.64</v>
       </c>
-      <c r="AL103" s="4">
+      <c r="AL103" s="2">
         <v>112.92</v>
       </c>
-      <c r="AM103" s="4">
+      <c r="AM103" s="2">
         <v>4.09</v>
       </c>
-      <c r="AN103" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO103" s="4">
+      <c r="AN103" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO103" s="2">
         <v>0.06</v>
       </c>
-      <c r="AP103" s="4">
+      <c r="AP103" s="2">
         <v>117.01</v>
       </c>
-      <c r="AQ103" s="4">
+      <c r="AQ103" s="2">
         <v>9</v>
       </c>
-      <c r="AR103" s="4">
+      <c r="AR103" s="2">
         <v>1.67</v>
       </c>
-      <c r="AS103" s="4">
+      <c r="AS103" s="2">
         <v>28</v>
       </c>
-      <c r="AT103" s="4" t="s">
+      <c r="AT103" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AU103" s="4" t="s">
+      <c r="AU103" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AV103" s="4" t="s">
+      <c r="AV103" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AW103" s="4" t="s">
+      <c r="AW103" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX103" s="4" t="s">
+      <c r="AX103" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -17260,148 +17292,148 @@
       <c r="B104" t="s">
         <v>51</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C104" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D104" s="4" t="s">
+      <c r="D104" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E104" s="4">
-        <v>0</v>
-      </c>
-      <c r="F104" s="4">
+      <c r="E104" s="2">
+        <v>0</v>
+      </c>
+      <c r="F104" s="2">
         <v>5.44</v>
       </c>
-      <c r="G104" s="4">
+      <c r="G104" s="2">
         <v>-3.11</v>
       </c>
-      <c r="H104" s="4">
+      <c r="H104" s="2">
         <v>20</v>
       </c>
-      <c r="I104" s="4">
+      <c r="I104" s="2">
         <v>2</v>
       </c>
-      <c r="J104" s="4">
+      <c r="J104" s="2">
         <v>22</v>
       </c>
-      <c r="K104" s="4">
+      <c r="K104" s="2">
         <v>0.31</v>
       </c>
-      <c r="L104" s="5">
+      <c r="L104" s="3">
         <v>0.0486111111111111</v>
       </c>
-      <c r="M104" s="4">
+      <c r="M104" s="2">
         <v>4836.68</v>
       </c>
-      <c r="N104" s="4">
+      <c r="N104" s="2">
         <v>507.6</v>
       </c>
-      <c r="O104" s="4">
+      <c r="O104" s="2">
         <v>23.544</v>
       </c>
-      <c r="P104" s="4">
+      <c r="P104" s="2">
         <v>65.38</v>
       </c>
-      <c r="Q104" s="4">
+      <c r="Q104" s="2">
         <v>69.1</v>
       </c>
-      <c r="R104" s="4">
+      <c r="R104" s="2">
         <v>7.25</v>
       </c>
-      <c r="S104" s="4">
+      <c r="S104" s="2">
         <v>0.11</v>
       </c>
-      <c r="T104" s="4">
-        <v>0</v>
-      </c>
-      <c r="U104" s="4">
-        <v>0</v>
-      </c>
-      <c r="V104" s="4">
-        <v>0</v>
-      </c>
-      <c r="W104" s="4">
-        <v>0</v>
-      </c>
-      <c r="X104" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y104" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z104" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA104" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB104" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC104" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD104" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE104" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF104" s="4">
+      <c r="T104" s="2">
+        <v>0</v>
+      </c>
+      <c r="U104" s="2">
+        <v>0</v>
+      </c>
+      <c r="V104" s="2">
+        <v>0</v>
+      </c>
+      <c r="W104" s="2">
+        <v>0</v>
+      </c>
+      <c r="X104" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z104" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA104" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB104" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC104" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD104" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE104" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF104" s="2">
         <v>376.46</v>
       </c>
-      <c r="AG104" s="4">
+      <c r="AG104" s="2">
         <v>559.59</v>
       </c>
-      <c r="AH104" s="4">
+      <c r="AH104" s="2">
         <v>502.59</v>
       </c>
-      <c r="AI104" s="4">
+      <c r="AI104" s="2">
         <v>2290.57</v>
       </c>
-      <c r="AJ104" s="4">
+      <c r="AJ104" s="2">
         <v>1577.69</v>
       </c>
-      <c r="AK104" s="4">
+      <c r="AK104" s="2">
         <v>384.57</v>
       </c>
-      <c r="AL104" s="4">
+      <c r="AL104" s="2">
         <v>81.26</v>
       </c>
-      <c r="AM104" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN104" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO104" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP104" s="4">
+      <c r="AM104" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN104" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO104" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP104" s="2">
         <v>81.26</v>
       </c>
-      <c r="AQ104" s="4">
+      <c r="AQ104" s="2">
         <v>6</v>
       </c>
-      <c r="AR104" s="4">
+      <c r="AR104" s="2">
         <v>1.16</v>
       </c>
-      <c r="AS104" s="4">
+      <c r="AS104" s="2">
         <v>17</v>
       </c>
-      <c r="AT104" s="4" t="s">
+      <c r="AT104" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AU104" s="4" t="s">
+      <c r="AU104" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AV104" s="4" t="s">
+      <c r="AV104" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AW104" s="4" t="s">
+      <c r="AW104" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX104" s="4" t="s">
+      <c r="AX104" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -17412,148 +17444,148 @@
       <c r="B105" t="s">
         <v>51</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C105" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D105" s="4" t="s">
+      <c r="D105" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="4">
-        <v>0</v>
-      </c>
-      <c r="F105" s="4">
+      <c r="E105" s="2">
+        <v>0</v>
+      </c>
+      <c r="F105" s="2">
         <v>4.12</v>
       </c>
-      <c r="G105" s="4">
+      <c r="G105" s="2">
         <v>-4.6</v>
       </c>
-      <c r="H105" s="4">
+      <c r="H105" s="2">
         <v>17</v>
       </c>
-      <c r="I105" s="4">
+      <c r="I105" s="2">
         <v>19</v>
       </c>
-      <c r="J105" s="4">
+      <c r="J105" s="2">
         <v>36</v>
       </c>
-      <c r="K105" s="4">
+      <c r="K105" s="2">
         <v>0.51</v>
       </c>
-      <c r="L105" s="5">
+      <c r="L105" s="3">
         <v>0.0486111111111111</v>
       </c>
-      <c r="M105" s="4">
+      <c r="M105" s="2">
         <v>5573.12</v>
       </c>
-      <c r="N105" s="4">
+      <c r="N105" s="2">
         <v>519.31</v>
       </c>
-      <c r="O105" s="4">
+      <c r="O105" s="2">
         <v>26.316</v>
       </c>
-      <c r="P105" s="4">
+      <c r="P105" s="2">
         <v>73.13</v>
       </c>
-      <c r="Q105" s="4">
+      <c r="Q105" s="2">
         <v>79.62</v>
       </c>
-      <c r="R105" s="4">
+      <c r="R105" s="2">
         <v>7.42</v>
       </c>
-      <c r="S105" s="4">
+      <c r="S105" s="2">
         <v>0.18</v>
       </c>
-      <c r="T105" s="4">
-        <v>0</v>
-      </c>
-      <c r="U105" s="4">
-        <v>0</v>
-      </c>
-      <c r="V105" s="4">
-        <v>0</v>
-      </c>
-      <c r="W105" s="4">
-        <v>0</v>
-      </c>
-      <c r="X105" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y105" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z105" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA105" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB105" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC105" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD105" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE105" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF105" s="4">
+      <c r="T105" s="2">
+        <v>0</v>
+      </c>
+      <c r="U105" s="2">
+        <v>0</v>
+      </c>
+      <c r="V105" s="2">
+        <v>0</v>
+      </c>
+      <c r="W105" s="2">
+        <v>0</v>
+      </c>
+      <c r="X105" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z105" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA105" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB105" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC105" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD105" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE105" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF105" s="2">
         <v>500.5</v>
       </c>
-      <c r="AG105" s="4">
+      <c r="AG105" s="2">
         <v>830.89</v>
       </c>
-      <c r="AH105" s="4">
+      <c r="AH105" s="2">
         <v>153.86</v>
       </c>
-      <c r="AI105" s="4">
+      <c r="AI105" s="2">
         <v>2205.75</v>
       </c>
-      <c r="AJ105" s="4">
+      <c r="AJ105" s="2">
         <v>2180.47</v>
       </c>
-      <c r="AK105" s="4">
+      <c r="AK105" s="2">
         <v>816.07</v>
       </c>
-      <c r="AL105" s="4">
+      <c r="AL105" s="2">
         <v>207.05</v>
       </c>
-      <c r="AM105" s="4">
+      <c r="AM105" s="2">
         <v>9.8</v>
       </c>
-      <c r="AN105" s="4">
+      <c r="AN105" s="2">
         <v>1</v>
       </c>
-      <c r="AO105" s="4">
+      <c r="AO105" s="2">
         <v>0.14</v>
       </c>
-      <c r="AP105" s="4">
+      <c r="AP105" s="2">
         <v>216.85</v>
       </c>
-      <c r="AQ105" s="4">
+      <c r="AQ105" s="2">
         <v>17</v>
       </c>
-      <c r="AR105" s="4">
+      <c r="AR105" s="2">
         <v>3.1</v>
       </c>
-      <c r="AS105" s="4">
+      <c r="AS105" s="2">
         <v>14</v>
       </c>
-      <c r="AT105" s="4" t="s">
+      <c r="AT105" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AU105" s="4" t="s">
+      <c r="AU105" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AV105" s="4" t="s">
+      <c r="AV105" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AW105" s="4" t="s">
+      <c r="AW105" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX105" s="4" t="s">
+      <c r="AX105" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -17564,148 +17596,148 @@
       <c r="B106" t="s">
         <v>51</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D106" s="4" t="s">
+      <c r="D106" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E106" s="4">
-        <v>0</v>
-      </c>
-      <c r="F106" s="4">
+      <c r="E106" s="2">
+        <v>0</v>
+      </c>
+      <c r="F106" s="2">
         <v>4.18</v>
       </c>
-      <c r="G106" s="4">
+      <c r="G106" s="2">
         <v>-4.44</v>
       </c>
-      <c r="H106" s="4">
+      <c r="H106" s="2">
         <v>13</v>
       </c>
-      <c r="I106" s="4">
+      <c r="I106" s="2">
         <v>11</v>
       </c>
-      <c r="J106" s="4">
+      <c r="J106" s="2">
         <v>24</v>
       </c>
-      <c r="K106" s="4">
+      <c r="K106" s="2">
         <v>0.34</v>
       </c>
-      <c r="L106" s="5">
+      <c r="L106" s="3">
         <v>0.0486111111111111</v>
       </c>
-      <c r="M106" s="4">
+      <c r="M106" s="2">
         <v>4861.25</v>
       </c>
-      <c r="N106" s="4">
+      <c r="N106" s="2">
         <v>495.14</v>
       </c>
-      <c r="O106" s="4">
+      <c r="O106" s="2">
         <v>24.624</v>
       </c>
-      <c r="P106" s="4">
+      <c r="P106" s="2">
         <v>68.41</v>
       </c>
-      <c r="Q106" s="4">
+      <c r="Q106" s="2">
         <v>69.45</v>
       </c>
-      <c r="R106" s="4">
+      <c r="R106" s="2">
         <v>7.07</v>
       </c>
-      <c r="S106" s="4">
+      <c r="S106" s="2">
         <v>0.09</v>
       </c>
-      <c r="T106" s="4">
+      <c r="T106" s="2">
         <v>159</v>
       </c>
-      <c r="U106" s="4">
+      <c r="U106" s="2">
         <v>76.01</v>
       </c>
-      <c r="V106" s="4">
+      <c r="V106" s="2">
         <v>79.5</v>
       </c>
-      <c r="W106" s="4">
+      <c r="W106" s="2">
         <v>38.01</v>
       </c>
-      <c r="X106" s="4">
+      <c r="X106" s="2">
         <v>54.21</v>
       </c>
-      <c r="Y106" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z106" s="5">
+      <c r="Y106" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z106" s="3">
         <v>0.0322337962962963</v>
       </c>
-      <c r="AA106" s="5">
+      <c r="AA106" s="3">
         <v>0.00296296296296296</v>
       </c>
-      <c r="AB106" s="5">
+      <c r="AB106" s="3">
         <v>0.00122685185185185</v>
       </c>
-      <c r="AC106" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD106" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE106" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF106" s="4">
+      <c r="AC106" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD106" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE106" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF106" s="2">
         <v>425.57</v>
       </c>
-      <c r="AG106" s="4">
+      <c r="AG106" s="2">
         <v>528.84</v>
       </c>
-      <c r="AH106" s="4">
+      <c r="AH106" s="2">
         <v>206.47</v>
       </c>
-      <c r="AI106" s="4">
+      <c r="AI106" s="2">
         <v>2483.29</v>
       </c>
-      <c r="AJ106" s="4">
+      <c r="AJ106" s="2">
         <v>1659.19</v>
       </c>
-      <c r="AK106" s="4">
+      <c r="AK106" s="2">
         <v>434.18</v>
       </c>
-      <c r="AL106" s="4">
+      <c r="AL106" s="2">
         <v>78.13</v>
       </c>
-      <c r="AM106" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN106" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO106" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP106" s="4">
+      <c r="AM106" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN106" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO106" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP106" s="2">
         <v>78.13</v>
       </c>
-      <c r="AQ106" s="4">
+      <c r="AQ106" s="2">
         <v>5</v>
       </c>
-      <c r="AR106" s="4">
+      <c r="AR106" s="2">
         <v>1.12</v>
       </c>
-      <c r="AS106" s="4">
+      <c r="AS106" s="2">
         <v>60</v>
       </c>
-      <c r="AT106" s="4" t="s">
+      <c r="AT106" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AU106" s="4" t="s">
+      <c r="AU106" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AV106" s="4" t="s">
+      <c r="AV106" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AW106" s="4" t="s">
+      <c r="AW106" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AX106" s="4" t="s">
+      <c r="AX106" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -17716,148 +17748,148 @@
       <c r="B107" t="s">
         <v>82</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="C107" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="D107" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E107" s="6">
-        <v>0</v>
-      </c>
-      <c r="F107" s="6">
+      <c r="E107" s="4">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4">
         <v>3.75</v>
       </c>
-      <c r="G107" s="6">
+      <c r="G107" s="4">
         <v>-5.57</v>
       </c>
-      <c r="H107" s="6">
+      <c r="H107" s="4">
         <v>20</v>
       </c>
-      <c r="I107" s="6">
+      <c r="I107" s="4">
         <v>18</v>
       </c>
-      <c r="J107" s="6">
+      <c r="J107" s="4">
         <v>38</v>
       </c>
-      <c r="K107" s="6">
+      <c r="K107" s="4">
         <v>0.43</v>
       </c>
-      <c r="L107" s="7">
+      <c r="L107" s="5">
         <v>0.0617939814814815</v>
       </c>
-      <c r="M107" s="6">
+      <c r="M107" s="4">
         <v>8998.77</v>
       </c>
-      <c r="N107" s="6">
+      <c r="N107" s="4">
         <v>953.78</v>
       </c>
-      <c r="O107" s="6">
+      <c r="O107" s="4">
         <v>27.756</v>
       </c>
-      <c r="P107" s="6">
+      <c r="P107" s="4">
         <v>77.06</v>
       </c>
-      <c r="Q107" s="6">
+      <c r="Q107" s="4">
         <v>101.13</v>
       </c>
-      <c r="R107" s="6">
+      <c r="R107" s="4">
         <v>10.72</v>
       </c>
-      <c r="S107" s="6">
+      <c r="S107" s="4">
         <v>0.23</v>
       </c>
-      <c r="T107" s="6">
-        <v>0</v>
-      </c>
-      <c r="U107" s="6">
-        <v>0</v>
-      </c>
-      <c r="V107" s="6">
-        <v>0</v>
-      </c>
-      <c r="W107" s="6">
-        <v>0</v>
-      </c>
-      <c r="X107" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y107" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z107" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA107" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB107" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC107" s="7">
-        <v>0</v>
-      </c>
-      <c r="AD107" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE107" s="7">
-        <v>0</v>
-      </c>
-      <c r="AF107" s="6">
+      <c r="T107" s="4">
+        <v>0</v>
+      </c>
+      <c r="U107" s="4">
+        <v>0</v>
+      </c>
+      <c r="V107" s="4">
+        <v>0</v>
+      </c>
+      <c r="W107" s="4">
+        <v>0</v>
+      </c>
+      <c r="X107" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB107" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC107" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD107" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE107" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF107" s="4">
         <v>785.51</v>
       </c>
-      <c r="AG107" s="6">
+      <c r="AG107" s="4">
         <v>1287.4</v>
       </c>
-      <c r="AH107" s="6">
+      <c r="AH107" s="4">
         <v>208.93</v>
       </c>
-      <c r="AI107" s="6">
+      <c r="AI107" s="4">
         <v>3507.24</v>
       </c>
-      <c r="AJ107" s="6">
+      <c r="AJ107" s="4">
         <v>3418.02</v>
       </c>
-      <c r="AK107" s="6">
+      <c r="AK107" s="4">
         <v>1274.01</v>
       </c>
-      <c r="AL107" s="6">
+      <c r="AL107" s="4">
         <v>487.44</v>
       </c>
-      <c r="AM107" s="6">
+      <c r="AM107" s="4">
         <v>99.38</v>
       </c>
-      <c r="AN107" s="6">
+      <c r="AN107" s="4">
         <v>4</v>
       </c>
-      <c r="AO107" s="6">
+      <c r="AO107" s="4">
         <v>1.12</v>
       </c>
-      <c r="AP107" s="6">
+      <c r="AP107" s="4">
         <v>586.82</v>
       </c>
-      <c r="AQ107" s="6">
+      <c r="AQ107" s="4">
         <v>30</v>
       </c>
-      <c r="AR107" s="6">
+      <c r="AR107" s="4">
         <v>6.59</v>
       </c>
-      <c r="AS107" s="6">
+      <c r="AS107" s="4">
         <v>51</v>
       </c>
-      <c r="AT107" s="6" t="s">
+      <c r="AT107" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="AU107" s="6" t="s">
+      <c r="AU107" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AV107" s="6" t="s">
+      <c r="AV107" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AW107" s="6" t="s">
+      <c r="AW107" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AX107" s="6" t="s">
+      <c r="AX107" s="4" t="s">
         <v>58</v>
       </c>
     </row>
@@ -17868,148 +17900,148 @@
       <c r="B108" t="s">
         <v>82</v>
       </c>
-      <c r="C108" s="6" t="s">
+      <c r="C108" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D108" s="6" t="s">
+      <c r="D108" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E108" s="6">
-        <v>0</v>
-      </c>
-      <c r="F108" s="6">
+      <c r="E108" s="4">
+        <v>0</v>
+      </c>
+      <c r="F108" s="4">
         <v>4.51</v>
       </c>
-      <c r="G108" s="6">
+      <c r="G108" s="4">
         <v>-5.75</v>
       </c>
-      <c r="H108" s="6">
+      <c r="H108" s="4">
         <v>30</v>
       </c>
-      <c r="I108" s="6">
+      <c r="I108" s="4">
         <v>40</v>
       </c>
-      <c r="J108" s="6">
+      <c r="J108" s="4">
         <v>70</v>
       </c>
-      <c r="K108" s="6">
+      <c r="K108" s="4">
         <v>0.69</v>
       </c>
-      <c r="L108" s="7">
+      <c r="L108" s="5">
         <v>0.0701388888888889</v>
       </c>
-      <c r="M108" s="6">
+      <c r="M108" s="4">
         <v>11148.18</v>
       </c>
-      <c r="N108" s="6">
+      <c r="N108" s="4">
         <v>1094.4</v>
       </c>
-      <c r="O108" s="6">
+      <c r="O108" s="4">
         <v>29.556</v>
       </c>
-      <c r="P108" s="6">
+      <c r="P108" s="4">
         <v>82.05</v>
       </c>
-      <c r="Q108" s="6">
+      <c r="Q108" s="4">
         <v>110.38</v>
       </c>
-      <c r="R108" s="6">
+      <c r="R108" s="4">
         <v>10.84</v>
       </c>
-      <c r="S108" s="6">
+      <c r="S108" s="4">
         <v>0.3</v>
       </c>
-      <c r="T108" s="6">
-        <v>0</v>
-      </c>
-      <c r="U108" s="6">
-        <v>0</v>
-      </c>
-      <c r="V108" s="6">
-        <v>0</v>
-      </c>
-      <c r="W108" s="6">
-        <v>0</v>
-      </c>
-      <c r="X108" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y108" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z108" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA108" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB108" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC108" s="7">
-        <v>0</v>
-      </c>
-      <c r="AD108" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE108" s="7">
-        <v>0</v>
-      </c>
-      <c r="AF108" s="6">
+      <c r="T108" s="4">
+        <v>0</v>
+      </c>
+      <c r="U108" s="4">
+        <v>0</v>
+      </c>
+      <c r="V108" s="4">
+        <v>0</v>
+      </c>
+      <c r="W108" s="4">
+        <v>0</v>
+      </c>
+      <c r="X108" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z108" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA108" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB108" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC108" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD108" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE108" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF108" s="4">
         <v>983.76</v>
       </c>
-      <c r="AG108" s="6">
+      <c r="AG108" s="4">
         <v>1688.43</v>
       </c>
-      <c r="AH108" s="6">
+      <c r="AH108" s="4">
         <v>195.04</v>
       </c>
-      <c r="AI108" s="6">
+      <c r="AI108" s="4">
         <v>4208.89</v>
       </c>
-      <c r="AJ108" s="6">
+      <c r="AJ108" s="4">
         <v>4033.02</v>
       </c>
-      <c r="AK108" s="6">
+      <c r="AK108" s="4">
         <v>1886.52</v>
       </c>
-      <c r="AL108" s="6">
+      <c r="AL108" s="4">
         <v>636.29</v>
       </c>
-      <c r="AM108" s="6">
+      <c r="AM108" s="4">
         <v>188.15</v>
       </c>
-      <c r="AN108" s="6">
+      <c r="AN108" s="4">
         <v>12</v>
       </c>
-      <c r="AO108" s="6">
+      <c r="AO108" s="4">
         <v>1.86</v>
       </c>
-      <c r="AP108" s="6">
+      <c r="AP108" s="4">
         <v>824.44</v>
       </c>
-      <c r="AQ108" s="6">
+      <c r="AQ108" s="4">
         <v>43</v>
       </c>
-      <c r="AR108" s="6">
+      <c r="AR108" s="4">
         <v>8.16</v>
       </c>
-      <c r="AS108" s="6">
+      <c r="AS108" s="4">
         <v>70</v>
       </c>
-      <c r="AT108" s="6" t="s">
+      <c r="AT108" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AU108" s="6" t="s">
+      <c r="AU108" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AV108" s="6" t="s">
+      <c r="AV108" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AW108" s="6" t="s">
+      <c r="AW108" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AX108" s="6" t="s">
+      <c r="AX108" s="4" t="s">
         <v>58</v>
       </c>
     </row>
@@ -18020,148 +18052,148 @@
       <c r="B109" t="s">
         <v>82</v>
       </c>
-      <c r="C109" s="6" t="s">
+      <c r="C109" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D109" s="6" t="s">
+      <c r="D109" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E109" s="6">
-        <v>0</v>
-      </c>
-      <c r="F109" s="6">
+      <c r="E109" s="4">
+        <v>0</v>
+      </c>
+      <c r="F109" s="4">
         <v>4.22</v>
       </c>
-      <c r="G109" s="6">
+      <c r="G109" s="4">
         <v>-4.86</v>
       </c>
-      <c r="H109" s="6">
+      <c r="H109" s="4">
         <v>7</v>
       </c>
-      <c r="I109" s="6">
+      <c r="I109" s="4">
         <v>19</v>
       </c>
-      <c r="J109" s="6">
+      <c r="J109" s="4">
         <v>26</v>
       </c>
-      <c r="K109" s="6">
+      <c r="K109" s="4">
         <v>0.53</v>
       </c>
-      <c r="L109" s="7">
+      <c r="L109" s="5">
         <v>0.0340277777777778</v>
       </c>
-      <c r="M109" s="6">
+      <c r="M109" s="4">
         <v>4748.71</v>
       </c>
-      <c r="N109" s="6">
+      <c r="N109" s="4">
         <v>499.41</v>
       </c>
-      <c r="O109" s="6">
+      <c r="O109" s="4">
         <v>23.616</v>
       </c>
-      <c r="P109" s="6">
+      <c r="P109" s="4">
         <v>65.55</v>
       </c>
-      <c r="Q109" s="6">
+      <c r="Q109" s="4">
         <v>96.91</v>
       </c>
-      <c r="R109" s="6">
+      <c r="R109" s="4">
         <v>10.19</v>
       </c>
-      <c r="S109" s="6">
+      <c r="S109" s="4">
         <v>0.18</v>
       </c>
-      <c r="T109" s="6">
-        <v>0</v>
-      </c>
-      <c r="U109" s="6">
-        <v>0</v>
-      </c>
-      <c r="V109" s="6">
-        <v>0</v>
-      </c>
-      <c r="W109" s="6">
-        <v>0</v>
-      </c>
-      <c r="X109" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y109" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z109" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA109" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB109" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC109" s="7">
-        <v>0</v>
-      </c>
-      <c r="AD109" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE109" s="7">
-        <v>0</v>
-      </c>
-      <c r="AF109" s="6">
+      <c r="T109" s="4">
+        <v>0</v>
+      </c>
+      <c r="U109" s="4">
+        <v>0</v>
+      </c>
+      <c r="V109" s="4">
+        <v>0</v>
+      </c>
+      <c r="W109" s="4">
+        <v>0</v>
+      </c>
+      <c r="X109" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC109" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD109" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE109" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF109" s="4">
         <v>412.84</v>
       </c>
-      <c r="AG109" s="6">
+      <c r="AG109" s="4">
         <v>495.51</v>
       </c>
-      <c r="AH109" s="6">
+      <c r="AH109" s="4">
         <v>98.92</v>
       </c>
-      <c r="AI109" s="6">
+      <c r="AI109" s="4">
         <v>2173.07</v>
       </c>
-      <c r="AJ109" s="6">
+      <c r="AJ109" s="4">
         <v>1866.06</v>
       </c>
-      <c r="AK109" s="6">
+      <c r="AK109" s="4">
         <v>529.4</v>
       </c>
-      <c r="AL109" s="6">
+      <c r="AL109" s="4">
         <v>80.03</v>
       </c>
-      <c r="AM109" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN109" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO109" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP109" s="6">
+      <c r="AM109" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN109" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO109" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP109" s="4">
         <v>80.03</v>
       </c>
-      <c r="AQ109" s="6">
+      <c r="AQ109" s="4">
         <v>7</v>
       </c>
-      <c r="AR109" s="6">
+      <c r="AR109" s="4">
         <v>1.63</v>
       </c>
-      <c r="AS109" s="6">
+      <c r="AS109" s="4">
         <v>26</v>
       </c>
-      <c r="AT109" s="6" t="s">
+      <c r="AT109" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AU109" s="6" t="s">
+      <c r="AU109" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AV109" s="6" t="s">
+      <c r="AV109" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AW109" s="6" t="s">
+      <c r="AW109" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AX109" s="6" t="s">
+      <c r="AX109" s="4" t="s">
         <v>58</v>
       </c>
     </row>
@@ -18172,148 +18204,148 @@
       <c r="B110" t="s">
         <v>82</v>
       </c>
-      <c r="C110" s="6" t="s">
+      <c r="C110" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D110" s="6" t="s">
+      <c r="D110" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E110" s="6">
-        <v>0</v>
-      </c>
-      <c r="F110" s="6">
+      <c r="E110" s="4">
+        <v>0</v>
+      </c>
+      <c r="F110" s="4">
         <v>3.23</v>
       </c>
-      <c r="G110" s="6">
+      <c r="G110" s="4">
         <v>-7.32</v>
       </c>
-      <c r="H110" s="6">
+      <c r="H110" s="4">
         <v>3</v>
       </c>
-      <c r="I110" s="6">
+      <c r="I110" s="4">
         <v>5</v>
       </c>
-      <c r="J110" s="6">
+      <c r="J110" s="4">
         <v>8</v>
       </c>
-      <c r="K110" s="6">
+      <c r="K110" s="4">
         <v>0.45</v>
       </c>
-      <c r="L110" s="7">
+      <c r="L110" s="5">
         <v>0.0123263888888889</v>
       </c>
-      <c r="M110" s="6">
+      <c r="M110" s="4">
         <v>1819.03</v>
       </c>
-      <c r="N110" s="6">
+      <c r="N110" s="4">
         <v>193.54</v>
       </c>
-      <c r="O110" s="6">
+      <c r="O110" s="4">
         <v>29.484</v>
       </c>
-      <c r="P110" s="6">
+      <c r="P110" s="4">
         <v>81.94</v>
       </c>
-      <c r="Q110" s="6">
+      <c r="Q110" s="4">
         <v>102.48</v>
       </c>
-      <c r="R110" s="6">
+      <c r="R110" s="4">
         <v>10.9</v>
       </c>
-      <c r="S110" s="6">
+      <c r="S110" s="4">
         <v>0.28</v>
       </c>
-      <c r="T110" s="6">
-        <v>0</v>
-      </c>
-      <c r="U110" s="6">
-        <v>0</v>
-      </c>
-      <c r="V110" s="6">
-        <v>0</v>
-      </c>
-      <c r="W110" s="6">
-        <v>0</v>
-      </c>
-      <c r="X110" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y110" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z110" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA110" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB110" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC110" s="7">
-        <v>0</v>
-      </c>
-      <c r="AD110" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE110" s="7">
-        <v>0</v>
-      </c>
-      <c r="AF110" s="6">
+      <c r="T110" s="4">
+        <v>0</v>
+      </c>
+      <c r="U110" s="4">
+        <v>0</v>
+      </c>
+      <c r="V110" s="4">
+        <v>0</v>
+      </c>
+      <c r="W110" s="4">
+        <v>0</v>
+      </c>
+      <c r="X110" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y110" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z110" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA110" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB110" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC110" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD110" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE110" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF110" s="4">
         <v>161.33</v>
       </c>
-      <c r="AG110" s="6">
+      <c r="AG110" s="4">
         <v>315.33</v>
       </c>
-      <c r="AH110" s="6">
+      <c r="AH110" s="4">
         <v>43.42</v>
       </c>
-      <c r="AI110" s="6">
+      <c r="AI110" s="4">
         <v>629.18</v>
       </c>
-      <c r="AJ110" s="6">
+      <c r="AJ110" s="4">
         <v>672.99</v>
       </c>
-      <c r="AK110" s="6">
+      <c r="AK110" s="4">
         <v>313.19</v>
       </c>
-      <c r="AL110" s="6">
+      <c r="AL110" s="4">
         <v>129.86</v>
       </c>
-      <c r="AM110" s="6">
+      <c r="AM110" s="4">
         <v>30.39</v>
       </c>
-      <c r="AN110" s="6">
+      <c r="AN110" s="4">
         <v>2</v>
       </c>
-      <c r="AO110" s="6">
+      <c r="AO110" s="4">
         <v>1.71</v>
       </c>
-      <c r="AP110" s="6">
+      <c r="AP110" s="4">
         <v>160.25</v>
       </c>
-      <c r="AQ110" s="6">
+      <c r="AQ110" s="4">
         <v>10</v>
       </c>
-      <c r="AR110" s="6">
+      <c r="AR110" s="4">
         <v>9.03</v>
       </c>
-      <c r="AS110" s="6">
+      <c r="AS110" s="4">
         <v>37</v>
       </c>
-      <c r="AT110" s="6" t="s">
+      <c r="AT110" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AU110" s="6" t="s">
+      <c r="AU110" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AV110" s="6" t="s">
+      <c r="AV110" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AW110" s="6" t="s">
+      <c r="AW110" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AX110" s="6" t="s">
+      <c r="AX110" s="4" t="s">
         <v>58</v>
       </c>
     </row>
@@ -18324,148 +18356,148 @@
       <c r="B111" t="s">
         <v>82</v>
       </c>
-      <c r="C111" s="6" t="s">
+      <c r="C111" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D111" s="6" t="s">
+      <c r="D111" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E111" s="6">
-        <v>0</v>
-      </c>
-      <c r="F111" s="6">
+      <c r="E111" s="4">
+        <v>0</v>
+      </c>
+      <c r="F111" s="4">
         <v>4.06</v>
       </c>
-      <c r="G111" s="6">
+      <c r="G111" s="4">
         <v>-5.59</v>
       </c>
-      <c r="H111" s="6">
+      <c r="H111" s="4">
         <v>30</v>
       </c>
-      <c r="I111" s="6">
+      <c r="I111" s="4">
         <v>34</v>
       </c>
-      <c r="J111" s="6">
+      <c r="J111" s="4">
         <v>64</v>
       </c>
-      <c r="K111" s="6">
+      <c r="K111" s="4">
         <v>0.63</v>
       </c>
-      <c r="L111" s="7">
+      <c r="L111" s="5">
         <v>0.0701388888888889</v>
       </c>
-      <c r="M111" s="6">
+      <c r="M111" s="4">
         <v>9997.88</v>
       </c>
-      <c r="N111" s="6">
+      <c r="N111" s="4">
         <v>1062.8</v>
       </c>
-      <c r="O111" s="6">
+      <c r="O111" s="4">
         <v>28.044</v>
       </c>
-      <c r="P111" s="6">
+      <c r="P111" s="4">
         <v>77.95</v>
       </c>
-      <c r="Q111" s="6">
+      <c r="Q111" s="4">
         <v>98.99</v>
       </c>
-      <c r="R111" s="6">
+      <c r="R111" s="4">
         <v>10.52</v>
       </c>
-      <c r="S111" s="6">
+      <c r="S111" s="4">
         <v>0.23</v>
       </c>
-      <c r="T111" s="6">
-        <v>0</v>
-      </c>
-      <c r="U111" s="6">
-        <v>0</v>
-      </c>
-      <c r="V111" s="6">
-        <v>0</v>
-      </c>
-      <c r="W111" s="6">
-        <v>0</v>
-      </c>
-      <c r="X111" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y111" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z111" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA111" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB111" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC111" s="7">
-        <v>0</v>
-      </c>
-      <c r="AD111" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE111" s="7">
-        <v>0</v>
-      </c>
-      <c r="AF111" s="6">
+      <c r="T111" s="4">
+        <v>0</v>
+      </c>
+      <c r="U111" s="4">
+        <v>0</v>
+      </c>
+      <c r="V111" s="4">
+        <v>0</v>
+      </c>
+      <c r="W111" s="4">
+        <v>0</v>
+      </c>
+      <c r="X111" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="4">
         <v>875.41</v>
       </c>
-      <c r="AG111" s="6">
+      <c r="AG111" s="4">
         <v>1564.45</v>
       </c>
-      <c r="AH111" s="6">
+      <c r="AH111" s="4">
         <v>258.08</v>
       </c>
-      <c r="AI111" s="6">
+      <c r="AI111" s="4">
         <v>3955.77</v>
       </c>
-      <c r="AJ111" s="6">
+      <c r="AJ111" s="4">
         <v>3408.21</v>
       </c>
-      <c r="AK111" s="6">
+      <c r="AK111" s="4">
         <v>1652.42</v>
       </c>
-      <c r="AL111" s="6">
+      <c r="AL111" s="4">
         <v>642.83</v>
       </c>
-      <c r="AM111" s="6">
+      <c r="AM111" s="4">
         <v>81.17</v>
       </c>
-      <c r="AN111" s="6">
+      <c r="AN111" s="4">
         <v>5</v>
       </c>
-      <c r="AO111" s="6">
+      <c r="AO111" s="4">
         <v>0.8</v>
       </c>
-      <c r="AP111" s="6">
+      <c r="AP111" s="4">
         <v>724</v>
       </c>
-      <c r="AQ111" s="6">
+      <c r="AQ111" s="4">
         <v>38</v>
       </c>
-      <c r="AR111" s="6">
+      <c r="AR111" s="4">
         <v>7.17</v>
       </c>
-      <c r="AS111" s="6">
+      <c r="AS111" s="4">
         <v>105</v>
       </c>
-      <c r="AT111" s="6" t="s">
+      <c r="AT111" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="AU111" s="6" t="s">
+      <c r="AU111" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AV111" s="6" t="s">
+      <c r="AV111" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AW111" s="6" t="s">
+      <c r="AW111" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AX111" s="6" t="s">
+      <c r="AX111" s="4" t="s">
         <v>58</v>
       </c>
     </row>
@@ -18476,148 +18508,148 @@
       <c r="B112" t="s">
         <v>82</v>
       </c>
-      <c r="C112" s="6" t="s">
+      <c r="C112" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D112" s="6" t="s">
+      <c r="D112" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E112" s="6">
-        <v>0</v>
-      </c>
-      <c r="F112" s="6">
+      <c r="E112" s="4">
+        <v>0</v>
+      </c>
+      <c r="F112" s="4">
         <v>4.14</v>
       </c>
-      <c r="G112" s="6">
+      <c r="G112" s="4">
         <v>-5.36</v>
       </c>
-      <c r="H112" s="6">
+      <c r="H112" s="4">
         <v>33</v>
       </c>
-      <c r="I112" s="6">
+      <c r="I112" s="4">
         <v>32</v>
       </c>
-      <c r="J112" s="6">
+      <c r="J112" s="4">
         <v>65</v>
       </c>
-      <c r="K112" s="6">
+      <c r="K112" s="4">
         <v>0.64</v>
       </c>
-      <c r="L112" s="7">
+      <c r="L112" s="5">
         <v>0.0701388888888889</v>
       </c>
-      <c r="M112" s="6">
+      <c r="M112" s="4">
         <v>10143.07</v>
       </c>
-      <c r="N112" s="6">
+      <c r="N112" s="4">
         <v>1150.3</v>
       </c>
-      <c r="O112" s="6">
+      <c r="O112" s="4">
         <v>27.684</v>
       </c>
-      <c r="P112" s="6">
+      <c r="P112" s="4">
         <v>76.9</v>
       </c>
-      <c r="Q112" s="6">
+      <c r="Q112" s="4">
         <v>100.43</v>
       </c>
-      <c r="R112" s="6">
+      <c r="R112" s="4">
         <v>11.39</v>
       </c>
-      <c r="S112" s="6">
+      <c r="S112" s="4">
         <v>0.23</v>
       </c>
-      <c r="T112" s="6">
-        <v>0</v>
-      </c>
-      <c r="U112" s="6">
-        <v>0</v>
-      </c>
-      <c r="V112" s="6">
-        <v>0</v>
-      </c>
-      <c r="W112" s="6">
-        <v>0</v>
-      </c>
-      <c r="X112" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y112" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z112" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA112" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB112" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC112" s="7">
-        <v>0</v>
-      </c>
-      <c r="AD112" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE112" s="7">
-        <v>0</v>
-      </c>
-      <c r="AF112" s="6">
+      <c r="T112" s="4">
+        <v>0</v>
+      </c>
+      <c r="U112" s="4">
+        <v>0</v>
+      </c>
+      <c r="V112" s="4">
+        <v>0</v>
+      </c>
+      <c r="W112" s="4">
+        <v>0</v>
+      </c>
+      <c r="X112" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y112" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z112" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA112" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB112" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC112" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD112" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE112" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF112" s="4">
         <v>899.16</v>
       </c>
-      <c r="AG112" s="6">
+      <c r="AG112" s="4">
         <v>1598.64</v>
       </c>
-      <c r="AH112" s="6">
+      <c r="AH112" s="4">
         <v>170.25</v>
       </c>
-      <c r="AI112" s="6">
+      <c r="AI112" s="4">
         <v>4102.14</v>
       </c>
-      <c r="AJ112" s="6">
+      <c r="AJ112" s="4">
         <v>3670.27</v>
       </c>
-      <c r="AK112" s="6">
+      <c r="AK112" s="4">
         <v>1490.87</v>
       </c>
-      <c r="AL112" s="6">
+      <c r="AL112" s="4">
         <v>609.63</v>
       </c>
-      <c r="AM112" s="6">
+      <c r="AM112" s="4">
         <v>100.55</v>
       </c>
-      <c r="AN112" s="6">
+      <c r="AN112" s="4">
         <v>6</v>
       </c>
-      <c r="AO112" s="6">
+      <c r="AO112" s="4">
         <v>1</v>
       </c>
-      <c r="AP112" s="6">
+      <c r="AP112" s="4">
         <v>710.18</v>
       </c>
-      <c r="AQ112" s="6">
+      <c r="AQ112" s="4">
         <v>44</v>
       </c>
-      <c r="AR112" s="6">
+      <c r="AR112" s="4">
         <v>7.03</v>
       </c>
-      <c r="AS112" s="6">
+      <c r="AS112" s="4">
         <v>99</v>
       </c>
-      <c r="AT112" s="6" t="s">
+      <c r="AT112" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AU112" s="6" t="s">
+      <c r="AU112" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AV112" s="6" t="s">
+      <c r="AV112" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AW112" s="6" t="s">
+      <c r="AW112" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AX112" s="6" t="s">
+      <c r="AX112" s="4" t="s">
         <v>58</v>
       </c>
     </row>
@@ -18628,148 +18660,148 @@
       <c r="B113" t="s">
         <v>82</v>
       </c>
-      <c r="C113" s="6" t="s">
+      <c r="C113" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D113" s="6" t="s">
+      <c r="D113" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E113" s="6">
-        <v>0</v>
-      </c>
-      <c r="F113" s="6">
+      <c r="E113" s="4">
+        <v>0</v>
+      </c>
+      <c r="F113" s="4">
         <v>4.33</v>
       </c>
-      <c r="G113" s="6">
+      <c r="G113" s="4">
         <v>-4.57</v>
       </c>
-      <c r="H113" s="6">
+      <c r="H113" s="4">
         <v>10</v>
       </c>
-      <c r="I113" s="6">
+      <c r="I113" s="4">
         <v>8</v>
       </c>
-      <c r="J113" s="6">
+      <c r="J113" s="4">
         <v>18</v>
       </c>
-      <c r="K113" s="6">
+      <c r="K113" s="4">
         <v>0.35</v>
       </c>
-      <c r="L113" s="7">
+      <c r="L113" s="5">
         <v>0.0361111111111111</v>
       </c>
-      <c r="M113" s="6">
+      <c r="M113" s="4">
         <v>3180</v>
       </c>
-      <c r="N113" s="6">
+      <c r="N113" s="4">
         <v>335.94</v>
       </c>
-      <c r="O113" s="6">
+      <c r="O113" s="4">
         <v>26.1</v>
       </c>
-      <c r="P113" s="6">
+      <c r="P113" s="4">
         <v>72.49</v>
       </c>
-      <c r="Q113" s="6">
+      <c r="Q113" s="4">
         <v>61.15</v>
       </c>
-      <c r="R113" s="6">
+      <c r="R113" s="4">
         <v>6.46</v>
       </c>
-      <c r="S113" s="6">
+      <c r="S113" s="4">
         <v>0.23</v>
       </c>
-      <c r="T113" s="6">
-        <v>0</v>
-      </c>
-      <c r="U113" s="6">
-        <v>0</v>
-      </c>
-      <c r="V113" s="6">
-        <v>0</v>
-      </c>
-      <c r="W113" s="6">
-        <v>0</v>
-      </c>
-      <c r="X113" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y113" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z113" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA113" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB113" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC113" s="7">
-        <v>0</v>
-      </c>
-      <c r="AD113" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE113" s="7">
-        <v>0</v>
-      </c>
-      <c r="AF113" s="6">
+      <c r="T113" s="4">
+        <v>0</v>
+      </c>
+      <c r="U113" s="4">
+        <v>0</v>
+      </c>
+      <c r="V113" s="4">
+        <v>0</v>
+      </c>
+      <c r="W113" s="4">
+        <v>0</v>
+      </c>
+      <c r="X113" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y113" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z113" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA113" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB113" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC113" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD113" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE113" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF113" s="4">
         <v>274.23</v>
       </c>
-      <c r="AG113" s="6">
+      <c r="AG113" s="4">
         <v>389.33</v>
       </c>
-      <c r="AH113" s="6">
+      <c r="AH113" s="4">
         <v>46.49</v>
       </c>
-      <c r="AI113" s="6">
+      <c r="AI113" s="4">
         <v>1307.9</v>
       </c>
-      <c r="AJ113" s="6">
+      <c r="AJ113" s="4">
         <v>1195.14</v>
       </c>
-      <c r="AK113" s="6">
+      <c r="AK113" s="4">
         <v>487.9</v>
       </c>
-      <c r="AL113" s="6">
+      <c r="AL113" s="4">
         <v>137.06</v>
       </c>
-      <c r="AM113" s="6">
+      <c r="AM113" s="4">
         <v>5.36</v>
       </c>
-      <c r="AN113" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO113" s="6">
+      <c r="AN113" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO113" s="4">
         <v>0.1</v>
       </c>
-      <c r="AP113" s="6">
+      <c r="AP113" s="4">
         <v>142.42</v>
       </c>
-      <c r="AQ113" s="6">
+      <c r="AQ113" s="4">
         <v>9</v>
       </c>
-      <c r="AR113" s="6">
+      <c r="AR113" s="4">
         <v>2.74</v>
       </c>
-      <c r="AS113" s="6">
+      <c r="AS113" s="4">
         <v>33</v>
       </c>
-      <c r="AT113" s="6" t="s">
+      <c r="AT113" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="AU113" s="6" t="s">
+      <c r="AU113" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AV113" s="6" t="s">
+      <c r="AV113" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AW113" s="6" t="s">
+      <c r="AW113" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AX113" s="6" t="s">
+      <c r="AX113" s="4" t="s">
         <v>58</v>
       </c>
     </row>
@@ -18780,148 +18812,148 @@
       <c r="B114" t="s">
         <v>82</v>
       </c>
-      <c r="C114" s="6" t="s">
+      <c r="C114" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D114" s="6" t="s">
+      <c r="D114" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E114" s="6">
-        <v>0</v>
-      </c>
-      <c r="F114" s="6">
+      <c r="E114" s="4">
+        <v>0</v>
+      </c>
+      <c r="F114" s="4">
         <v>4.03</v>
       </c>
-      <c r="G114" s="6">
+      <c r="G114" s="4">
         <v>-5.42</v>
       </c>
-      <c r="H114" s="6">
+      <c r="H114" s="4">
         <v>13</v>
       </c>
-      <c r="I114" s="6">
+      <c r="I114" s="4">
         <v>23</v>
       </c>
-      <c r="J114" s="6">
+      <c r="J114" s="4">
         <v>36</v>
       </c>
-      <c r="K114" s="6">
+      <c r="K114" s="4">
         <v>0.69</v>
       </c>
-      <c r="L114" s="7">
+      <c r="L114" s="5">
         <v>0.0361111111111111</v>
       </c>
-      <c r="M114" s="6">
+      <c r="M114" s="4">
         <v>5868.37</v>
       </c>
-      <c r="N114" s="6">
+      <c r="N114" s="4">
         <v>581.13</v>
       </c>
-      <c r="O114" s="6">
+      <c r="O114" s="4">
         <v>26.748</v>
       </c>
-      <c r="P114" s="6">
+      <c r="P114" s="4">
         <v>74.3</v>
       </c>
-      <c r="Q114" s="6">
+      <c r="Q114" s="4">
         <v>112.85</v>
       </c>
-      <c r="R114" s="6">
+      <c r="R114" s="4">
         <v>11.18</v>
       </c>
-      <c r="S114" s="6">
+      <c r="S114" s="4">
         <v>0.34</v>
       </c>
-      <c r="T114" s="6">
-        <v>0</v>
-      </c>
-      <c r="U114" s="6">
-        <v>0</v>
-      </c>
-      <c r="V114" s="6">
-        <v>0</v>
-      </c>
-      <c r="W114" s="6">
-        <v>0</v>
-      </c>
-      <c r="X114" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y114" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z114" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA114" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB114" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC114" s="7">
-        <v>0</v>
-      </c>
-      <c r="AD114" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE114" s="7">
-        <v>0</v>
-      </c>
-      <c r="AF114" s="6">
+      <c r="T114" s="4">
+        <v>0</v>
+      </c>
+      <c r="U114" s="4">
+        <v>0</v>
+      </c>
+      <c r="V114" s="4">
+        <v>0</v>
+      </c>
+      <c r="W114" s="4">
+        <v>0</v>
+      </c>
+      <c r="X114" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y114" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA114" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB114" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC114" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD114" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE114" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF114" s="4">
         <v>511.54</v>
       </c>
-      <c r="AG114" s="6">
+      <c r="AG114" s="4">
         <v>804.75</v>
       </c>
-      <c r="AH114" s="6">
+      <c r="AH114" s="4">
         <v>83.61</v>
       </c>
-      <c r="AI114" s="6">
+      <c r="AI114" s="4">
         <v>1926.39</v>
       </c>
-      <c r="AJ114" s="6">
+      <c r="AJ114" s="4">
         <v>2640.94</v>
       </c>
-      <c r="AK114" s="6">
+      <c r="AK114" s="4">
         <v>944.18</v>
       </c>
-      <c r="AL114" s="6">
+      <c r="AL114" s="4">
         <v>258.75</v>
       </c>
-      <c r="AM114" s="6">
+      <c r="AM114" s="4">
         <v>12.93</v>
       </c>
-      <c r="AN114" s="6">
+      <c r="AN114" s="4">
         <v>1</v>
       </c>
-      <c r="AO114" s="6">
+      <c r="AO114" s="4">
         <v>0.25</v>
       </c>
-      <c r="AP114" s="6">
+      <c r="AP114" s="4">
         <v>271.68</v>
       </c>
-      <c r="AQ114" s="6">
+      <c r="AQ114" s="4">
         <v>18</v>
       </c>
-      <c r="AR114" s="6">
+      <c r="AR114" s="4">
         <v>5.22</v>
       </c>
-      <c r="AS114" s="6">
+      <c r="AS114" s="4">
         <v>37</v>
       </c>
-      <c r="AT114" s="6" t="s">
+      <c r="AT114" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="AU114" s="6" t="s">
+      <c r="AU114" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AV114" s="6" t="s">
+      <c r="AV114" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AW114" s="6" t="s">
+      <c r="AW114" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AX114" s="6" t="s">
+      <c r="AX114" s="4" t="s">
         <v>58</v>
       </c>
     </row>
@@ -18932,148 +18964,148 @@
       <c r="B115" t="s">
         <v>82</v>
       </c>
-      <c r="C115" s="6" t="s">
+      <c r="C115" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D115" s="6" t="s">
+      <c r="D115" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E115" s="6">
-        <v>0</v>
-      </c>
-      <c r="F115" s="6">
+      <c r="E115" s="4">
+        <v>0</v>
+      </c>
+      <c r="F115" s="4">
         <v>4.03</v>
       </c>
-      <c r="G115" s="6">
+      <c r="G115" s="4">
         <v>-4.97</v>
       </c>
-      <c r="H115" s="6">
+      <c r="H115" s="4">
         <v>12</v>
       </c>
-      <c r="I115" s="6">
+      <c r="I115" s="4">
         <v>26</v>
       </c>
-      <c r="J115" s="6">
+      <c r="J115" s="4">
         <v>38</v>
       </c>
-      <c r="K115" s="6">
+      <c r="K115" s="4">
         <v>0.47</v>
       </c>
-      <c r="L115" s="7">
+      <c r="L115" s="5">
         <v>0.05625</v>
       </c>
-      <c r="M115" s="6">
+      <c r="M115" s="4">
         <v>8544.58</v>
       </c>
-      <c r="N115" s="6">
+      <c r="N115" s="4">
         <v>887.42</v>
       </c>
-      <c r="O115" s="6">
+      <c r="O115" s="4">
         <v>27.432</v>
       </c>
-      <c r="P115" s="6">
+      <c r="P115" s="4">
         <v>76.23</v>
       </c>
-      <c r="Q115" s="6">
+      <c r="Q115" s="4">
         <v>105.49</v>
       </c>
-      <c r="R115" s="6">
+      <c r="R115" s="4">
         <v>10.96</v>
       </c>
-      <c r="S115" s="6">
+      <c r="S115" s="4">
         <v>0.22</v>
       </c>
-      <c r="T115" s="6">
-        <v>0</v>
-      </c>
-      <c r="U115" s="6">
-        <v>0</v>
-      </c>
-      <c r="V115" s="6">
-        <v>0</v>
-      </c>
-      <c r="W115" s="6">
-        <v>0</v>
-      </c>
-      <c r="X115" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y115" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z115" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA115" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB115" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC115" s="7">
-        <v>0</v>
-      </c>
-      <c r="AD115" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE115" s="7">
-        <v>0</v>
-      </c>
-      <c r="AF115" s="6">
+      <c r="T115" s="4">
+        <v>0</v>
+      </c>
+      <c r="U115" s="4">
+        <v>0</v>
+      </c>
+      <c r="V115" s="4">
+        <v>0</v>
+      </c>
+      <c r="W115" s="4">
+        <v>0</v>
+      </c>
+      <c r="X115" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y115" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z115" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA115" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB115" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC115" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD115" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE115" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF115" s="4">
         <v>740.99</v>
       </c>
-      <c r="AG115" s="6">
+      <c r="AG115" s="4">
         <v>1000.63</v>
       </c>
-      <c r="AH115" s="6">
+      <c r="AH115" s="4">
         <v>154.01</v>
       </c>
-      <c r="AI115" s="6">
+      <c r="AI115" s="4">
         <v>3944.92</v>
       </c>
-      <c r="AJ115" s="6">
+      <c r="AJ115" s="4">
         <v>2999.21</v>
       </c>
-      <c r="AK115" s="6">
+      <c r="AK115" s="4">
         <v>1187.39</v>
       </c>
-      <c r="AL115" s="6">
+      <c r="AL115" s="4">
         <v>217.3</v>
       </c>
-      <c r="AM115" s="6">
+      <c r="AM115" s="4">
         <v>41.69</v>
       </c>
-      <c r="AN115" s="6">
+      <c r="AN115" s="4">
         <v>3</v>
       </c>
-      <c r="AO115" s="6">
+      <c r="AO115" s="4">
         <v>0.51</v>
       </c>
-      <c r="AP115" s="6">
+      <c r="AP115" s="4">
         <v>258.99</v>
       </c>
-      <c r="AQ115" s="6">
+      <c r="AQ115" s="4">
         <v>10</v>
       </c>
-      <c r="AR115" s="6">
+      <c r="AR115" s="4">
         <v>3.2</v>
       </c>
-      <c r="AS115" s="6">
+      <c r="AS115" s="4">
         <v>136</v>
       </c>
-      <c r="AT115" s="6" t="s">
+      <c r="AT115" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="AU115" s="6" t="s">
+      <c r="AU115" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AV115" s="6" t="s">
+      <c r="AV115" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AW115" s="6" t="s">
+      <c r="AW115" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AX115" s="6" t="s">
+      <c r="AX115" s="4" t="s">
         <v>58</v>
       </c>
     </row>
@@ -19084,148 +19116,148 @@
       <c r="B116" t="s">
         <v>124</v>
       </c>
-      <c r="C116" s="6" t="s">
+      <c r="C116" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D116" s="6" t="s">
+      <c r="D116" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E116" s="6">
-        <v>0</v>
-      </c>
-      <c r="F116" s="6">
+      <c r="E116" s="4">
+        <v>0</v>
+      </c>
+      <c r="F116" s="4">
         <v>3.9</v>
       </c>
-      <c r="G116" s="6">
+      <c r="G116" s="4">
         <v>-5.16</v>
       </c>
-      <c r="H116" s="6">
+      <c r="H116" s="4">
         <v>6</v>
       </c>
-      <c r="I116" s="6">
+      <c r="I116" s="4">
         <v>8</v>
       </c>
-      <c r="J116" s="6">
+      <c r="J116" s="4">
         <v>14</v>
       </c>
-      <c r="K116" s="6">
+      <c r="K116" s="4">
         <v>0.15</v>
       </c>
-      <c r="L116" s="6">
+      <c r="L116" s="5">
         <v>0.0631944444444444</v>
       </c>
-      <c r="M116" s="6">
+      <c r="M116" s="4">
         <v>5253.2</v>
       </c>
-      <c r="N116" s="6">
+      <c r="N116" s="4">
         <v>591.38</v>
       </c>
-      <c r="O116" s="6">
+      <c r="O116" s="4">
         <v>22.212</v>
       </c>
-      <c r="P116" s="6">
+      <c r="P116" s="4">
         <v>61.69</v>
       </c>
-      <c r="Q116" s="6">
+      <c r="Q116" s="4">
         <v>58.86</v>
       </c>
-      <c r="R116" s="6">
+      <c r="R116" s="4">
         <v>6.5</v>
       </c>
-      <c r="S116" s="6">
+      <c r="S116" s="4">
         <v>0.08</v>
       </c>
-      <c r="T116" s="6">
+      <c r="T116" s="4">
         <v>151</v>
       </c>
-      <c r="U116" s="6">
+      <c r="U116" s="4">
         <v>112.25</v>
       </c>
-      <c r="V116" s="6">
+      <c r="V116" s="4">
         <v>75.5</v>
       </c>
-      <c r="W116" s="6">
+      <c r="W116" s="4">
         <v>56.12</v>
       </c>
-      <c r="X116" s="6">
+      <c r="X116" s="4">
         <v>42.82</v>
       </c>
-      <c r="Y116" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z116" s="6">
+      <c r="Y116" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="4">
         <v>0.00869212962962963</v>
       </c>
-      <c r="AA116" s="6">
+      <c r="AA116" s="4">
         <v>0.0110185185185185</v>
       </c>
-      <c r="AB116" s="6">
+      <c r="AB116" s="4">
         <v>0.00520833333333333</v>
       </c>
-      <c r="AC116" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD116" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE116" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF116" s="6">
+      <c r="AC116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF116" s="4">
         <v>447.52</v>
       </c>
-      <c r="AG116" s="6">
+      <c r="AG116" s="4">
         <v>379.8</v>
       </c>
-      <c r="AH116" s="6">
+      <c r="AH116" s="4">
         <v>345.46</v>
       </c>
-      <c r="AI116" s="6">
+      <c r="AI116" s="4">
         <v>2452.66</v>
       </c>
-      <c r="AJ116" s="6">
+      <c r="AJ116" s="4">
         <v>2082.08</v>
       </c>
-      <c r="AK116" s="6">
+      <c r="AK116" s="4">
         <v>341</v>
       </c>
-      <c r="AL116" s="6">
+      <c r="AL116" s="4">
         <v>31.39</v>
       </c>
-      <c r="AM116" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN116" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO116" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP116" s="6">
+      <c r="AM116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP116" s="4">
         <v>31.39</v>
       </c>
-      <c r="AQ116" s="6">
+      <c r="AQ116" s="4">
         <v>3</v>
       </c>
-      <c r="AR116" s="6">
+      <c r="AR116" s="4">
         <v>0.34</v>
       </c>
-      <c r="AS116" s="6">
+      <c r="AS116" s="4">
         <v>25</v>
       </c>
-      <c r="AT116" s="6" t="s">
+      <c r="AT116" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="AU116" s="6" t="s">
+      <c r="AU116" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AV116" s="6" t="s">
+      <c r="AV116" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AW116" s="6" t="s">
+      <c r="AW116" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AX116" s="6" t="s">
+      <c r="AX116" s="4" t="s">
         <v>122</v>
       </c>
     </row>
@@ -19236,148 +19268,148 @@
       <c r="B117" t="s">
         <v>124</v>
       </c>
-      <c r="C117" s="6" t="s">
+      <c r="C117" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D117" s="6" t="s">
+      <c r="D117" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E117" s="6">
-        <v>0</v>
-      </c>
-      <c r="F117" s="6">
+      <c r="E117" s="4">
+        <v>0</v>
+      </c>
+      <c r="F117" s="4">
         <v>3.62</v>
       </c>
-      <c r="G117" s="6">
+      <c r="G117" s="4">
         <v>-4.32</v>
       </c>
-      <c r="H117" s="6">
+      <c r="H117" s="4">
         <v>10</v>
       </c>
-      <c r="I117" s="6">
+      <c r="I117" s="4">
         <v>16</v>
       </c>
-      <c r="J117" s="6">
+      <c r="J117" s="4">
         <v>26</v>
       </c>
-      <c r="K117" s="6">
+      <c r="K117" s="4">
         <v>0.29</v>
       </c>
-      <c r="L117" s="6">
+      <c r="L117" s="5">
         <v>0.0631944444444444</v>
       </c>
-      <c r="M117" s="6">
+      <c r="M117" s="4">
         <v>6028.39</v>
       </c>
-      <c r="N117" s="6">
+      <c r="N117" s="4">
         <v>690.17</v>
       </c>
-      <c r="O117" s="6">
+      <c r="O117" s="4">
         <v>25.884</v>
       </c>
-      <c r="P117" s="6">
+      <c r="P117" s="4">
         <v>71.94</v>
       </c>
-      <c r="Q117" s="6">
+      <c r="Q117" s="4">
         <v>67.85</v>
       </c>
-      <c r="R117" s="6">
+      <c r="R117" s="4">
         <v>7.58</v>
       </c>
-      <c r="S117" s="6">
+      <c r="S117" s="4">
         <v>0.14</v>
       </c>
-      <c r="T117" s="6">
-        <v>0</v>
-      </c>
-      <c r="U117" s="6">
-        <v>0</v>
-      </c>
-      <c r="V117" s="6">
-        <v>0</v>
-      </c>
-      <c r="W117" s="6">
-        <v>0</v>
-      </c>
-      <c r="X117" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y117" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z117" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA117" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB117" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC117" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD117" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE117" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF117" s="6">
+      <c r="T117" s="4">
+        <v>0</v>
+      </c>
+      <c r="U117" s="4">
+        <v>0</v>
+      </c>
+      <c r="V117" s="4">
+        <v>0</v>
+      </c>
+      <c r="W117" s="4">
+        <v>0</v>
+      </c>
+      <c r="X117" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y117" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF117" s="4">
         <v>525.19</v>
       </c>
-      <c r="AG117" s="6">
+      <c r="AG117" s="4">
         <v>751.46</v>
       </c>
-      <c r="AH117" s="6">
+      <c r="AH117" s="4">
         <v>306.48</v>
       </c>
-      <c r="AI117" s="6">
+      <c r="AI117" s="4">
         <v>2156.64</v>
       </c>
-      <c r="AJ117" s="6">
+      <c r="AJ117" s="4">
         <v>2654.33</v>
       </c>
-      <c r="AK117" s="6">
+      <c r="AK117" s="4">
         <v>699.48</v>
       </c>
-      <c r="AL117" s="6">
+      <c r="AL117" s="4">
         <v>195.51</v>
       </c>
-      <c r="AM117" s="6">
+      <c r="AM117" s="4">
         <v>15.96</v>
       </c>
-      <c r="AN117" s="6">
+      <c r="AN117" s="4">
         <v>1</v>
       </c>
-      <c r="AO117" s="6">
+      <c r="AO117" s="4">
         <v>0.18</v>
       </c>
-      <c r="AP117" s="6">
+      <c r="AP117" s="4">
         <v>211.47</v>
       </c>
-      <c r="AQ117" s="6">
+      <c r="AQ117" s="4">
         <v>14</v>
       </c>
-      <c r="AR117" s="6">
+      <c r="AR117" s="4">
         <v>2.32</v>
       </c>
-      <c r="AS117" s="6">
+      <c r="AS117" s="4">
         <v>21</v>
       </c>
-      <c r="AT117" s="6" t="s">
+      <c r="AT117" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="AU117" s="6" t="s">
+      <c r="AU117" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AV117" s="6" t="s">
+      <c r="AV117" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AW117" s="6" t="s">
+      <c r="AW117" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AX117" s="6" t="s">
+      <c r="AX117" s="4" t="s">
         <v>122</v>
       </c>
     </row>
@@ -19388,148 +19420,148 @@
       <c r="B118" t="s">
         <v>124</v>
       </c>
-      <c r="C118" s="6" t="s">
+      <c r="C118" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D118" s="6" t="s">
+      <c r="D118" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E118" s="6">
-        <v>0</v>
-      </c>
-      <c r="F118" s="6">
+      <c r="E118" s="4">
+        <v>0</v>
+      </c>
+      <c r="F118" s="4">
         <v>3.87</v>
       </c>
-      <c r="G118" s="6">
+      <c r="G118" s="4">
         <v>-4.27</v>
       </c>
-      <c r="H118" s="6">
+      <c r="H118" s="4">
         <v>10</v>
       </c>
-      <c r="I118" s="6">
+      <c r="I118" s="4">
         <v>6</v>
       </c>
-      <c r="J118" s="6">
+      <c r="J118" s="4">
         <v>16</v>
       </c>
-      <c r="K118" s="6">
+      <c r="K118" s="4">
         <v>0.18</v>
       </c>
-      <c r="L118" s="6">
+      <c r="L118" s="5">
         <v>0.0631944444444444</v>
       </c>
-      <c r="M118" s="6">
+      <c r="M118" s="4">
         <v>4855.85</v>
       </c>
-      <c r="N118" s="6">
+      <c r="N118" s="4">
         <v>583.26</v>
       </c>
-      <c r="O118" s="6">
+      <c r="O118" s="4">
         <v>24.876</v>
       </c>
-      <c r="P118" s="6">
+      <c r="P118" s="4">
         <v>69.14</v>
       </c>
-      <c r="Q118" s="6">
+      <c r="Q118" s="4">
         <v>54.89</v>
       </c>
-      <c r="R118" s="6">
+      <c r="R118" s="4">
         <v>6.41</v>
       </c>
-      <c r="S118" s="6">
+      <c r="S118" s="4">
         <v>0.07</v>
       </c>
-      <c r="T118" s="6">
-        <v>0</v>
-      </c>
-      <c r="U118" s="6">
-        <v>0</v>
-      </c>
-      <c r="V118" s="6">
-        <v>0</v>
-      </c>
-      <c r="W118" s="6">
-        <v>0</v>
-      </c>
-      <c r="X118" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y118" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z118" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA118" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB118" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC118" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD118" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE118" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF118" s="6">
+      <c r="T118" s="4">
+        <v>0</v>
+      </c>
+      <c r="U118" s="4">
+        <v>0</v>
+      </c>
+      <c r="V118" s="4">
+        <v>0</v>
+      </c>
+      <c r="W118" s="4">
+        <v>0</v>
+      </c>
+      <c r="X118" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y118" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF118" s="4">
         <v>414.25</v>
       </c>
-      <c r="AG118" s="6">
+      <c r="AG118" s="4">
         <v>357.25</v>
       </c>
-      <c r="AH118" s="6">
+      <c r="AH118" s="4">
         <v>324.86</v>
       </c>
-      <c r="AI118" s="6">
+      <c r="AI118" s="4">
         <v>2143.4</v>
       </c>
-      <c r="AJ118" s="6">
+      <c r="AJ118" s="4">
         <v>1981.46</v>
       </c>
-      <c r="AK118" s="6">
+      <c r="AK118" s="4">
         <v>377.21</v>
       </c>
-      <c r="AL118" s="6">
+      <c r="AL118" s="4">
         <v>28.58</v>
       </c>
-      <c r="AM118" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN118" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO118" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP118" s="6">
+      <c r="AM118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP118" s="4">
         <v>28.58</v>
       </c>
-      <c r="AQ118" s="6">
+      <c r="AQ118" s="4">
         <v>2</v>
       </c>
-      <c r="AR118" s="6">
+      <c r="AR118" s="4">
         <v>0.31</v>
       </c>
-      <c r="AS118" s="6">
+      <c r="AS118" s="4">
         <v>29</v>
       </c>
-      <c r="AT118" s="6" t="s">
+      <c r="AT118" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AU118" s="6" t="s">
+      <c r="AU118" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AV118" s="6" t="s">
+      <c r="AV118" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AW118" s="6" t="s">
+      <c r="AW118" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AX118" s="6" t="s">
+      <c r="AX118" s="4" t="s">
         <v>122</v>
       </c>
     </row>
@@ -19540,150 +19572,3056 @@
       <c r="B119" t="s">
         <v>124</v>
       </c>
-      <c r="C119" s="6" t="s">
+      <c r="C119" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D119" s="6" t="s">
+      <c r="D119" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E119" s="6">
-        <v>0</v>
-      </c>
-      <c r="F119" s="6">
+      <c r="E119" s="4">
+        <v>0</v>
+      </c>
+      <c r="F119" s="4">
         <v>3.39</v>
       </c>
-      <c r="G119" s="6">
+      <c r="G119" s="4">
         <v>-3.73</v>
       </c>
-      <c r="H119" s="6">
+      <c r="H119" s="4">
         <v>5</v>
       </c>
-      <c r="I119" s="6">
+      <c r="I119" s="4">
         <v>8</v>
       </c>
-      <c r="J119" s="6">
+      <c r="J119" s="4">
         <v>13</v>
       </c>
-      <c r="K119" s="6">
+      <c r="K119" s="4">
         <v>0.14</v>
       </c>
-      <c r="L119" s="6">
+      <c r="L119" s="5">
         <v>0.0631944444444444</v>
       </c>
-      <c r="M119" s="6">
+      <c r="M119" s="4">
         <v>5189.43</v>
       </c>
-      <c r="N119" s="6">
+      <c r="N119" s="4">
         <v>506.03</v>
       </c>
-      <c r="O119" s="6">
+      <c r="O119" s="4">
         <v>28.548</v>
       </c>
-      <c r="P119" s="6">
+      <c r="P119" s="4">
         <v>79.34</v>
       </c>
-      <c r="Q119" s="6">
+      <c r="Q119" s="4">
         <v>57.99</v>
       </c>
-      <c r="R119" s="6">
+      <c r="R119" s="4">
         <v>5.56</v>
       </c>
-      <c r="S119" s="6">
+      <c r="S119" s="4">
         <v>0.09</v>
       </c>
-      <c r="T119" s="6">
-        <v>0</v>
-      </c>
-      <c r="U119" s="6">
-        <v>0</v>
-      </c>
-      <c r="V119" s="6">
-        <v>0</v>
-      </c>
-      <c r="W119" s="6">
-        <v>0</v>
-      </c>
-      <c r="X119" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y119" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z119" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA119" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB119" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC119" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD119" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE119" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF119" s="6">
+      <c r="T119" s="4">
+        <v>0</v>
+      </c>
+      <c r="U119" s="4">
+        <v>0</v>
+      </c>
+      <c r="V119" s="4">
+        <v>0</v>
+      </c>
+      <c r="W119" s="4">
+        <v>0</v>
+      </c>
+      <c r="X119" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y119" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF119" s="4">
         <v>437.7</v>
       </c>
-      <c r="AG119" s="6">
+      <c r="AG119" s="4">
         <v>527.69</v>
       </c>
-      <c r="AH119" s="6">
+      <c r="AH119" s="4">
         <v>264.96</v>
       </c>
-      <c r="AI119" s="6">
+      <c r="AI119" s="4">
         <v>2079.53</v>
       </c>
-      <c r="AJ119" s="6">
+      <c r="AJ119" s="4">
         <v>1788.27</v>
       </c>
-      <c r="AK119" s="6">
+      <c r="AK119" s="4">
         <v>841.58</v>
       </c>
-      <c r="AL119" s="6">
+      <c r="AL119" s="4">
         <v>194.83</v>
       </c>
-      <c r="AM119" s="6">
+      <c r="AM119" s="4">
         <v>20.26</v>
       </c>
-      <c r="AN119" s="6">
+      <c r="AN119" s="4">
         <v>1</v>
       </c>
-      <c r="AO119" s="6">
+      <c r="AO119" s="4">
         <v>0.22</v>
       </c>
-      <c r="AP119" s="6">
+      <c r="AP119" s="4">
         <v>215.09</v>
       </c>
-      <c r="AQ119" s="6">
+      <c r="AQ119" s="4">
         <v>11</v>
       </c>
-      <c r="AR119" s="6">
+      <c r="AR119" s="4">
         <v>2.36</v>
       </c>
-      <c r="AS119" s="6">
+      <c r="AS119" s="4">
         <v>10</v>
       </c>
-      <c r="AT119" s="6" t="s">
+      <c r="AT119" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="AU119" s="6" t="s">
+      <c r="AU119" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AV119" s="6" t="s">
+      <c r="AV119" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AW119" s="6" t="s">
+      <c r="AW119" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AX119" s="6" t="s">
+      <c r="AX119" s="4" t="s">
         <v>122</v>
       </c>
+    </row>
+    <row r="120" spans="1:50">
+      <c r="A120" t="s">
+        <v>129</v>
+      </c>
+      <c r="B120" t="s">
+        <v>130</v>
+      </c>
+      <c r="C120" t="s">
+        <v>131</v>
+      </c>
+      <c r="D120" t="s">
+        <v>53</v>
+      </c>
+      <c r="E120">
+        <v>1</v>
+      </c>
+      <c r="F120">
+        <v>4.06</v>
+      </c>
+      <c r="G120">
+        <v>-5</v>
+      </c>
+      <c r="H120">
+        <v>25</v>
+      </c>
+      <c r="I120">
+        <v>20</v>
+      </c>
+      <c r="J120">
+        <v>45</v>
+      </c>
+      <c r="K120">
+        <v>0.64</v>
+      </c>
+      <c r="L120" s="5">
+        <v>0.0486111111111111</v>
+      </c>
+      <c r="M120">
+        <v>4861.55</v>
+      </c>
+      <c r="N120">
+        <v>490.9</v>
+      </c>
+      <c r="O120">
+        <v>27.864</v>
+      </c>
+      <c r="P120">
+        <v>77.35</v>
+      </c>
+      <c r="Q120">
+        <v>69.45</v>
+      </c>
+      <c r="R120">
+        <v>7.01</v>
+      </c>
+      <c r="S120">
+        <v>0.11</v>
+      </c>
+      <c r="T120">
+        <v>0</v>
+      </c>
+      <c r="U120">
+        <v>0</v>
+      </c>
+      <c r="V120">
+        <v>0</v>
+      </c>
+      <c r="W120">
+        <v>0</v>
+      </c>
+      <c r="X120">
+        <v>0</v>
+      </c>
+      <c r="Y120">
+        <v>0</v>
+      </c>
+      <c r="Z120">
+        <v>0</v>
+      </c>
+      <c r="AA120">
+        <v>0</v>
+      </c>
+      <c r="AB120">
+        <v>0</v>
+      </c>
+      <c r="AC120">
+        <v>0</v>
+      </c>
+      <c r="AD120">
+        <v>0</v>
+      </c>
+      <c r="AE120">
+        <v>0</v>
+      </c>
+      <c r="AF120">
+        <v>428.56</v>
+      </c>
+      <c r="AG120">
+        <v>701.76</v>
+      </c>
+      <c r="AH120">
+        <v>356.61</v>
+      </c>
+      <c r="AI120">
+        <v>2144.81</v>
+      </c>
+      <c r="AJ120">
+        <v>1494.71</v>
+      </c>
+      <c r="AK120">
+        <v>611.36</v>
+      </c>
+      <c r="AL120">
+        <v>191.19</v>
+      </c>
+      <c r="AM120">
+        <v>61.62</v>
+      </c>
+      <c r="AN120">
+        <v>4</v>
+      </c>
+      <c r="AO120">
+        <v>0.88</v>
+      </c>
+      <c r="AP120">
+        <v>252.81</v>
+      </c>
+      <c r="AQ120">
+        <v>12</v>
+      </c>
+      <c r="AR120">
+        <v>3.61</v>
+      </c>
+      <c r="AS120">
+        <v>22</v>
+      </c>
+      <c r="AT120" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU120" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV120" t="s">
+        <v>132</v>
+      </c>
+      <c r="AW120" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX120" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="121" spans="1:50">
+      <c r="A121" t="s">
+        <v>129</v>
+      </c>
+      <c r="B121" t="s">
+        <v>130</v>
+      </c>
+      <c r="C121" t="s">
+        <v>133</v>
+      </c>
+      <c r="D121" t="s">
+        <v>53</v>
+      </c>
+      <c r="E121">
+        <v>1</v>
+      </c>
+      <c r="F121">
+        <v>4.3</v>
+      </c>
+      <c r="G121">
+        <v>-5.66</v>
+      </c>
+      <c r="H121">
+        <v>34</v>
+      </c>
+      <c r="I121">
+        <v>31</v>
+      </c>
+      <c r="J121">
+        <v>65</v>
+      </c>
+      <c r="K121">
+        <v>0.93</v>
+      </c>
+      <c r="L121" s="5">
+        <v>0.0486111111111111</v>
+      </c>
+      <c r="M121">
+        <v>4558.02</v>
+      </c>
+      <c r="N121">
+        <v>529.15</v>
+      </c>
+      <c r="O121">
+        <v>29.7</v>
+      </c>
+      <c r="P121">
+        <v>82.54</v>
+      </c>
+      <c r="Q121">
+        <v>65.11</v>
+      </c>
+      <c r="R121">
+        <v>7.56</v>
+      </c>
+      <c r="S121">
+        <v>0.11</v>
+      </c>
+      <c r="T121">
+        <v>0</v>
+      </c>
+      <c r="U121">
+        <v>0</v>
+      </c>
+      <c r="V121">
+        <v>0</v>
+      </c>
+      <c r="W121">
+        <v>0</v>
+      </c>
+      <c r="X121">
+        <v>0</v>
+      </c>
+      <c r="Y121">
+        <v>0</v>
+      </c>
+      <c r="Z121">
+        <v>0</v>
+      </c>
+      <c r="AA121">
+        <v>0</v>
+      </c>
+      <c r="AB121">
+        <v>0</v>
+      </c>
+      <c r="AC121">
+        <v>0</v>
+      </c>
+      <c r="AD121">
+        <v>0</v>
+      </c>
+      <c r="AE121">
+        <v>0</v>
+      </c>
+      <c r="AF121">
+        <v>421.84</v>
+      </c>
+      <c r="AG121">
+        <v>808.41</v>
+      </c>
+      <c r="AH121">
+        <v>289.77</v>
+      </c>
+      <c r="AI121">
+        <v>1829.58</v>
+      </c>
+      <c r="AJ121">
+        <v>1460.61</v>
+      </c>
+      <c r="AK121">
+        <v>646.08</v>
+      </c>
+      <c r="AL121">
+        <v>221.02</v>
+      </c>
+      <c r="AM121">
+        <v>110.88</v>
+      </c>
+      <c r="AN121">
+        <v>5</v>
+      </c>
+      <c r="AO121">
+        <v>1.58</v>
+      </c>
+      <c r="AP121">
+        <v>331.9</v>
+      </c>
+      <c r="AQ121">
+        <v>18</v>
+      </c>
+      <c r="AR121">
+        <v>4.74</v>
+      </c>
+      <c r="AS121">
+        <v>41</v>
+      </c>
+      <c r="AT121" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU121" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV121" t="s">
+        <v>132</v>
+      </c>
+      <c r="AW121" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX121" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="122" spans="1:50">
+      <c r="A122" t="s">
+        <v>129</v>
+      </c>
+      <c r="B122" t="s">
+        <v>130</v>
+      </c>
+      <c r="C122" t="s">
+        <v>134</v>
+      </c>
+      <c r="D122" t="s">
+        <v>53</v>
+      </c>
+      <c r="E122">
+        <v>1</v>
+      </c>
+      <c r="F122">
+        <v>4.03</v>
+      </c>
+      <c r="G122">
+        <v>-4.72</v>
+      </c>
+      <c r="H122">
+        <v>26</v>
+      </c>
+      <c r="I122">
+        <v>35</v>
+      </c>
+      <c r="J122">
+        <v>61</v>
+      </c>
+      <c r="K122">
+        <v>0.87</v>
+      </c>
+      <c r="L122" s="5">
+        <v>0.0486111111111111</v>
+      </c>
+      <c r="M122">
+        <v>4122.26</v>
+      </c>
+      <c r="N122">
+        <v>437.97</v>
+      </c>
+      <c r="O122">
+        <v>30.276</v>
+      </c>
+      <c r="P122">
+        <v>84.11</v>
+      </c>
+      <c r="Q122">
+        <v>58.89</v>
+      </c>
+      <c r="R122">
+        <v>6.26</v>
+      </c>
+      <c r="S122">
+        <v>0.12</v>
+      </c>
+      <c r="T122">
+        <v>0</v>
+      </c>
+      <c r="U122">
+        <v>0</v>
+      </c>
+      <c r="V122">
+        <v>0</v>
+      </c>
+      <c r="W122">
+        <v>0</v>
+      </c>
+      <c r="X122">
+        <v>0</v>
+      </c>
+      <c r="Y122">
+        <v>0</v>
+      </c>
+      <c r="Z122">
+        <v>0</v>
+      </c>
+      <c r="AA122">
+        <v>0</v>
+      </c>
+      <c r="AB122">
+        <v>0</v>
+      </c>
+      <c r="AC122">
+        <v>0</v>
+      </c>
+      <c r="AD122">
+        <v>0</v>
+      </c>
+      <c r="AE122">
+        <v>0</v>
+      </c>
+      <c r="AF122">
+        <v>380.75</v>
+      </c>
+      <c r="AG122">
+        <v>776.56</v>
+      </c>
+      <c r="AH122">
+        <v>284.66</v>
+      </c>
+      <c r="AI122">
+        <v>1469.98</v>
+      </c>
+      <c r="AJ122">
+        <v>1387.02</v>
+      </c>
+      <c r="AK122">
+        <v>664.6</v>
+      </c>
+      <c r="AL122">
+        <v>208.64</v>
+      </c>
+      <c r="AM122">
+        <v>107.38</v>
+      </c>
+      <c r="AN122">
+        <v>5</v>
+      </c>
+      <c r="AO122">
+        <v>1.53</v>
+      </c>
+      <c r="AP122">
+        <v>316.02</v>
+      </c>
+      <c r="AQ122">
+        <v>17</v>
+      </c>
+      <c r="AR122">
+        <v>4.51</v>
+      </c>
+      <c r="AS122">
+        <v>44</v>
+      </c>
+      <c r="AT122" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU122" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV122" t="s">
+        <v>132</v>
+      </c>
+      <c r="AW122" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX122" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="123" spans="1:50">
+      <c r="A123" t="s">
+        <v>129</v>
+      </c>
+      <c r="B123" t="s">
+        <v>130</v>
+      </c>
+      <c r="C123" t="s">
+        <v>135</v>
+      </c>
+      <c r="D123" t="s">
+        <v>53</v>
+      </c>
+      <c r="E123">
+        <v>1</v>
+      </c>
+      <c r="F123">
+        <v>4.23</v>
+      </c>
+      <c r="G123">
+        <v>-4.64</v>
+      </c>
+      <c r="H123">
+        <v>35</v>
+      </c>
+      <c r="I123">
+        <v>30</v>
+      </c>
+      <c r="J123">
+        <v>65</v>
+      </c>
+      <c r="K123">
+        <v>0.93</v>
+      </c>
+      <c r="L123" s="5">
+        <v>0.0486111111111111</v>
+      </c>
+      <c r="M123">
+        <v>4458.16</v>
+      </c>
+      <c r="N123">
+        <v>522.94</v>
+      </c>
+      <c r="O123">
+        <v>29.556</v>
+      </c>
+      <c r="P123">
+        <v>82.07</v>
+      </c>
+      <c r="Q123">
+        <v>63.69</v>
+      </c>
+      <c r="R123">
+        <v>7.47</v>
+      </c>
+      <c r="S123">
+        <v>0.11</v>
+      </c>
+      <c r="T123">
+        <v>0</v>
+      </c>
+      <c r="U123">
+        <v>0</v>
+      </c>
+      <c r="V123">
+        <v>0</v>
+      </c>
+      <c r="W123">
+        <v>0</v>
+      </c>
+      <c r="X123">
+        <v>0</v>
+      </c>
+      <c r="Y123">
+        <v>0</v>
+      </c>
+      <c r="Z123">
+        <v>0</v>
+      </c>
+      <c r="AA123">
+        <v>0</v>
+      </c>
+      <c r="AB123">
+        <v>0</v>
+      </c>
+      <c r="AC123">
+        <v>0</v>
+      </c>
+      <c r="AD123">
+        <v>0</v>
+      </c>
+      <c r="AE123">
+        <v>0</v>
+      </c>
+      <c r="AF123">
+        <v>407.49</v>
+      </c>
+      <c r="AG123">
+        <v>818.15</v>
+      </c>
+      <c r="AH123">
+        <v>267.1</v>
+      </c>
+      <c r="AI123">
+        <v>1969.94</v>
+      </c>
+      <c r="AJ123">
+        <v>1209.11</v>
+      </c>
+      <c r="AK123">
+        <v>606.12</v>
+      </c>
+      <c r="AL123">
+        <v>283.48</v>
+      </c>
+      <c r="AM123">
+        <v>122.54</v>
+      </c>
+      <c r="AN123">
+        <v>7</v>
+      </c>
+      <c r="AO123">
+        <v>1.75</v>
+      </c>
+      <c r="AP123">
+        <v>406.02</v>
+      </c>
+      <c r="AQ123">
+        <v>21</v>
+      </c>
+      <c r="AR123">
+        <v>5.8</v>
+      </c>
+      <c r="AS123">
+        <v>158</v>
+      </c>
+      <c r="AT123" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU123" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV123" t="s">
+        <v>132</v>
+      </c>
+      <c r="AW123" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX123" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:50">
+      <c r="A124" t="s">
+        <v>129</v>
+      </c>
+      <c r="B124" t="s">
+        <v>130</v>
+      </c>
+      <c r="C124" t="s">
+        <v>136</v>
+      </c>
+      <c r="D124" t="s">
+        <v>53</v>
+      </c>
+      <c r="E124">
+        <v>1</v>
+      </c>
+      <c r="F124">
+        <v>4.29</v>
+      </c>
+      <c r="G124">
+        <v>-4.95</v>
+      </c>
+      <c r="H124">
+        <v>24</v>
+      </c>
+      <c r="I124">
+        <v>39</v>
+      </c>
+      <c r="J124">
+        <v>63</v>
+      </c>
+      <c r="K124">
+        <v>0.9</v>
+      </c>
+      <c r="L124" s="5">
+        <v>0.0486111111111111</v>
+      </c>
+      <c r="M124">
+        <v>4116.14</v>
+      </c>
+      <c r="N124">
+        <v>471.59</v>
+      </c>
+      <c r="O124">
+        <v>30.6</v>
+      </c>
+      <c r="P124">
+        <v>84.99</v>
+      </c>
+      <c r="Q124">
+        <v>58.8</v>
+      </c>
+      <c r="R124">
+        <v>6.74</v>
+      </c>
+      <c r="S124">
+        <v>0.09</v>
+      </c>
+      <c r="T124">
+        <v>0</v>
+      </c>
+      <c r="U124">
+        <v>0</v>
+      </c>
+      <c r="V124">
+        <v>0</v>
+      </c>
+      <c r="W124">
+        <v>0</v>
+      </c>
+      <c r="X124">
+        <v>0</v>
+      </c>
+      <c r="Y124">
+        <v>0</v>
+      </c>
+      <c r="Z124">
+        <v>0</v>
+      </c>
+      <c r="AA124">
+        <v>0</v>
+      </c>
+      <c r="AB124">
+        <v>0</v>
+      </c>
+      <c r="AC124">
+        <v>0</v>
+      </c>
+      <c r="AD124">
+        <v>0</v>
+      </c>
+      <c r="AE124">
+        <v>0</v>
+      </c>
+      <c r="AF124">
+        <v>381.46</v>
+      </c>
+      <c r="AG124">
+        <v>730.98</v>
+      </c>
+      <c r="AH124">
+        <v>389.87</v>
+      </c>
+      <c r="AI124">
+        <v>1757.64</v>
+      </c>
+      <c r="AJ124">
+        <v>1136.33</v>
+      </c>
+      <c r="AK124">
+        <v>528.3</v>
+      </c>
+      <c r="AL124">
+        <v>192.51</v>
+      </c>
+      <c r="AM124">
+        <v>111.64</v>
+      </c>
+      <c r="AN124">
+        <v>7</v>
+      </c>
+      <c r="AO124">
+        <v>1.59</v>
+      </c>
+      <c r="AP124">
+        <v>304.15</v>
+      </c>
+      <c r="AQ124">
+        <v>15</v>
+      </c>
+      <c r="AR124">
+        <v>4.34</v>
+      </c>
+      <c r="AS124">
+        <v>60</v>
+      </c>
+      <c r="AT124" t="s">
+        <v>137</v>
+      </c>
+      <c r="AU124" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV124" t="s">
+        <v>132</v>
+      </c>
+      <c r="AW124" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX124" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="125" spans="1:50">
+      <c r="A125" t="s">
+        <v>138</v>
+      </c>
+      <c r="B125" t="s">
+        <v>130</v>
+      </c>
+      <c r="C125" t="s">
+        <v>131</v>
+      </c>
+      <c r="D125" t="s">
+        <v>53</v>
+      </c>
+      <c r="E125">
+        <v>1</v>
+      </c>
+      <c r="F125">
+        <v>4.46</v>
+      </c>
+      <c r="G125">
+        <v>-4.48</v>
+      </c>
+      <c r="H125">
+        <v>12</v>
+      </c>
+      <c r="I125">
+        <v>12</v>
+      </c>
+      <c r="J125">
+        <v>24</v>
+      </c>
+      <c r="K125">
+        <v>0.33</v>
+      </c>
+      <c r="L125" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M125">
+        <v>5186.61</v>
+      </c>
+      <c r="N125">
+        <v>507.02</v>
+      </c>
+      <c r="O125">
+        <v>28.476</v>
+      </c>
+      <c r="P125">
+        <v>79.08</v>
+      </c>
+      <c r="Q125">
+        <v>72.04</v>
+      </c>
+      <c r="R125">
+        <v>7.04</v>
+      </c>
+      <c r="S125">
+        <v>0.14</v>
+      </c>
+      <c r="T125">
+        <v>0</v>
+      </c>
+      <c r="U125">
+        <v>0</v>
+      </c>
+      <c r="V125">
+        <v>0</v>
+      </c>
+      <c r="W125">
+        <v>0</v>
+      </c>
+      <c r="X125">
+        <v>0</v>
+      </c>
+      <c r="Y125">
+        <v>0</v>
+      </c>
+      <c r="Z125">
+        <v>0</v>
+      </c>
+      <c r="AA125">
+        <v>0</v>
+      </c>
+      <c r="AB125">
+        <v>0</v>
+      </c>
+      <c r="AC125">
+        <v>0</v>
+      </c>
+      <c r="AD125">
+        <v>0</v>
+      </c>
+      <c r="AE125">
+        <v>0</v>
+      </c>
+      <c r="AF125">
+        <v>445.89</v>
+      </c>
+      <c r="AG125">
+        <v>596.12</v>
+      </c>
+      <c r="AH125">
+        <v>256.58</v>
+      </c>
+      <c r="AI125">
+        <v>2050.14</v>
+      </c>
+      <c r="AJ125">
+        <v>2052.99</v>
+      </c>
+      <c r="AK125">
+        <v>592.61</v>
+      </c>
+      <c r="AL125">
+        <v>190.32</v>
+      </c>
+      <c r="AM125">
+        <v>43.87</v>
+      </c>
+      <c r="AN125">
+        <v>3</v>
+      </c>
+      <c r="AO125">
+        <v>0.61</v>
+      </c>
+      <c r="AP125">
+        <v>234.19</v>
+      </c>
+      <c r="AQ125">
+        <v>14</v>
+      </c>
+      <c r="AR125">
+        <v>3.25</v>
+      </c>
+      <c r="AS125">
+        <v>36</v>
+      </c>
+      <c r="AT125" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU125" t="s">
+        <v>139</v>
+      </c>
+      <c r="AV125" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW125" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX125" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="126" spans="1:50">
+      <c r="A126" t="s">
+        <v>138</v>
+      </c>
+      <c r="B126" t="s">
+        <v>130</v>
+      </c>
+      <c r="C126" t="s">
+        <v>133</v>
+      </c>
+      <c r="D126" t="s">
+        <v>53</v>
+      </c>
+      <c r="E126">
+        <v>1</v>
+      </c>
+      <c r="F126">
+        <v>4.2</v>
+      </c>
+      <c r="G126">
+        <v>-5.22</v>
+      </c>
+      <c r="H126">
+        <v>12</v>
+      </c>
+      <c r="I126">
+        <v>24</v>
+      </c>
+      <c r="J126">
+        <v>36</v>
+      </c>
+      <c r="K126">
+        <v>0.5</v>
+      </c>
+      <c r="L126" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M126">
+        <v>5159.68</v>
+      </c>
+      <c r="N126">
+        <v>521.57</v>
+      </c>
+      <c r="O126">
+        <v>29.592</v>
+      </c>
+      <c r="P126">
+        <v>82.16</v>
+      </c>
+      <c r="Q126">
+        <v>71.66</v>
+      </c>
+      <c r="R126">
+        <v>7.24</v>
+      </c>
+      <c r="S126">
+        <v>0.13</v>
+      </c>
+      <c r="T126">
+        <v>0</v>
+      </c>
+      <c r="U126">
+        <v>0</v>
+      </c>
+      <c r="V126">
+        <v>0</v>
+      </c>
+      <c r="W126">
+        <v>0</v>
+      </c>
+      <c r="X126">
+        <v>0</v>
+      </c>
+      <c r="Y126">
+        <v>0</v>
+      </c>
+      <c r="Z126">
+        <v>0</v>
+      </c>
+      <c r="AA126">
+        <v>0</v>
+      </c>
+      <c r="AB126">
+        <v>0</v>
+      </c>
+      <c r="AC126">
+        <v>0</v>
+      </c>
+      <c r="AD126">
+        <v>0</v>
+      </c>
+      <c r="AE126">
+        <v>0</v>
+      </c>
+      <c r="AF126">
+        <v>457.48</v>
+      </c>
+      <c r="AG126">
+        <v>703.32</v>
+      </c>
+      <c r="AH126">
+        <v>166.06</v>
+      </c>
+      <c r="AI126">
+        <v>2021.89</v>
+      </c>
+      <c r="AJ126">
+        <v>2111.49</v>
+      </c>
+      <c r="AK126">
+        <v>559.46</v>
+      </c>
+      <c r="AL126">
+        <v>238.15</v>
+      </c>
+      <c r="AM126">
+        <v>62.62</v>
+      </c>
+      <c r="AN126">
+        <v>4</v>
+      </c>
+      <c r="AO126">
+        <v>0.87</v>
+      </c>
+      <c r="AP126">
+        <v>300.77</v>
+      </c>
+      <c r="AQ126">
+        <v>21</v>
+      </c>
+      <c r="AR126">
+        <v>4.18</v>
+      </c>
+      <c r="AS126">
+        <v>75</v>
+      </c>
+      <c r="AT126" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU126" t="s">
+        <v>139</v>
+      </c>
+      <c r="AV126" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW126" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX126" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="127" spans="1:50">
+      <c r="A127" t="s">
+        <v>138</v>
+      </c>
+      <c r="B127" t="s">
+        <v>130</v>
+      </c>
+      <c r="C127" t="s">
+        <v>134</v>
+      </c>
+      <c r="D127" t="s">
+        <v>53</v>
+      </c>
+      <c r="E127">
+        <v>1</v>
+      </c>
+      <c r="F127">
+        <v>3.88</v>
+      </c>
+      <c r="G127">
+        <v>-5.21</v>
+      </c>
+      <c r="H127">
+        <v>24</v>
+      </c>
+      <c r="I127">
+        <v>28</v>
+      </c>
+      <c r="J127">
+        <v>52</v>
+      </c>
+      <c r="K127">
+        <v>0.72</v>
+      </c>
+      <c r="L127" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M127">
+        <v>5545.21</v>
+      </c>
+      <c r="N127">
+        <v>563.57</v>
+      </c>
+      <c r="O127">
+        <v>29.304</v>
+      </c>
+      <c r="P127">
+        <v>81.41</v>
+      </c>
+      <c r="Q127">
+        <v>77.02</v>
+      </c>
+      <c r="R127">
+        <v>7.83</v>
+      </c>
+      <c r="S127">
+        <v>0.2</v>
+      </c>
+      <c r="T127">
+        <v>0</v>
+      </c>
+      <c r="U127">
+        <v>0</v>
+      </c>
+      <c r="V127">
+        <v>0</v>
+      </c>
+      <c r="W127">
+        <v>0</v>
+      </c>
+      <c r="X127">
+        <v>0</v>
+      </c>
+      <c r="Y127">
+        <v>0</v>
+      </c>
+      <c r="Z127">
+        <v>0</v>
+      </c>
+      <c r="AA127">
+        <v>0</v>
+      </c>
+      <c r="AB127">
+        <v>0</v>
+      </c>
+      <c r="AC127">
+        <v>0</v>
+      </c>
+      <c r="AD127">
+        <v>0</v>
+      </c>
+      <c r="AE127">
+        <v>0</v>
+      </c>
+      <c r="AF127">
+        <v>499.67</v>
+      </c>
+      <c r="AG127">
+        <v>1126.65</v>
+      </c>
+      <c r="AH127">
+        <v>201.91</v>
+      </c>
+      <c r="AI127">
+        <v>1687.3</v>
+      </c>
+      <c r="AJ127">
+        <v>1938.27</v>
+      </c>
+      <c r="AK127">
+        <v>1170.88</v>
+      </c>
+      <c r="AL127">
+        <v>488.5</v>
+      </c>
+      <c r="AM127">
+        <v>58.6</v>
+      </c>
+      <c r="AN127">
+        <v>4</v>
+      </c>
+      <c r="AO127">
+        <v>0.81</v>
+      </c>
+      <c r="AP127">
+        <v>547.1</v>
+      </c>
+      <c r="AQ127">
+        <v>33</v>
+      </c>
+      <c r="AR127">
+        <v>7.6</v>
+      </c>
+      <c r="AS127">
+        <v>109</v>
+      </c>
+      <c r="AT127" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU127" t="s">
+        <v>139</v>
+      </c>
+      <c r="AV127" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW127" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX127" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="128" spans="1:50">
+      <c r="A128" t="s">
+        <v>138</v>
+      </c>
+      <c r="B128" t="s">
+        <v>130</v>
+      </c>
+      <c r="C128" t="s">
+        <v>136</v>
+      </c>
+      <c r="D128" t="s">
+        <v>53</v>
+      </c>
+      <c r="E128">
+        <v>1</v>
+      </c>
+      <c r="F128">
+        <v>3.86</v>
+      </c>
+      <c r="G128">
+        <v>-5.02</v>
+      </c>
+      <c r="H128">
+        <v>14</v>
+      </c>
+      <c r="I128">
+        <v>15</v>
+      </c>
+      <c r="J128">
+        <v>29</v>
+      </c>
+      <c r="K128">
+        <v>0.4</v>
+      </c>
+      <c r="L128" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M128">
+        <v>5168.45</v>
+      </c>
+      <c r="N128">
+        <v>594.48</v>
+      </c>
+      <c r="O128">
+        <v>29.556</v>
+      </c>
+      <c r="P128">
+        <v>82.07</v>
+      </c>
+      <c r="Q128">
+        <v>71.78</v>
+      </c>
+      <c r="R128">
+        <v>8.26</v>
+      </c>
+      <c r="S128">
+        <v>0.12</v>
+      </c>
+      <c r="T128">
+        <v>0</v>
+      </c>
+      <c r="U128">
+        <v>0</v>
+      </c>
+      <c r="V128">
+        <v>0</v>
+      </c>
+      <c r="W128">
+        <v>0</v>
+      </c>
+      <c r="X128">
+        <v>0</v>
+      </c>
+      <c r="Y128">
+        <v>0</v>
+      </c>
+      <c r="Z128">
+        <v>0</v>
+      </c>
+      <c r="AA128">
+        <v>0</v>
+      </c>
+      <c r="AB128">
+        <v>0</v>
+      </c>
+      <c r="AC128">
+        <v>0</v>
+      </c>
+      <c r="AD128">
+        <v>0</v>
+      </c>
+      <c r="AE128">
+        <v>0</v>
+      </c>
+      <c r="AF128">
+        <v>456.37</v>
+      </c>
+      <c r="AG128">
+        <v>800.12</v>
+      </c>
+      <c r="AH128">
+        <v>242.52</v>
+      </c>
+      <c r="AI128">
+        <v>2224.51</v>
+      </c>
+      <c r="AJ128">
+        <v>1699.04</v>
+      </c>
+      <c r="AK128">
+        <v>571.06</v>
+      </c>
+      <c r="AL128">
+        <v>290.44</v>
+      </c>
+      <c r="AM128">
+        <v>140.84</v>
+      </c>
+      <c r="AN128">
+        <v>8</v>
+      </c>
+      <c r="AO128">
+        <v>1.96</v>
+      </c>
+      <c r="AP128">
+        <v>431.28</v>
+      </c>
+      <c r="AQ128">
+        <v>21</v>
+      </c>
+      <c r="AR128">
+        <v>5.99</v>
+      </c>
+      <c r="AS128">
+        <v>156</v>
+      </c>
+      <c r="AT128" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU128" t="s">
+        <v>139</v>
+      </c>
+      <c r="AV128" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW128" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX128" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="129" spans="1:50">
+      <c r="A129" t="s">
+        <v>138</v>
+      </c>
+      <c r="B129" t="s">
+        <v>130</v>
+      </c>
+      <c r="C129" t="s">
+        <v>140</v>
+      </c>
+      <c r="D129" t="s">
+        <v>53</v>
+      </c>
+      <c r="E129">
+        <v>1</v>
+      </c>
+      <c r="F129">
+        <v>4.15</v>
+      </c>
+      <c r="G129">
+        <v>-5.11</v>
+      </c>
+      <c r="H129">
+        <v>21</v>
+      </c>
+      <c r="I129">
+        <v>16</v>
+      </c>
+      <c r="J129">
+        <v>37</v>
+      </c>
+      <c r="K129">
+        <v>0.51</v>
+      </c>
+      <c r="L129" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M129">
+        <v>4716.79</v>
+      </c>
+      <c r="N129">
+        <v>464.79</v>
+      </c>
+      <c r="O129">
+        <v>30.024</v>
+      </c>
+      <c r="P129">
+        <v>83.41</v>
+      </c>
+      <c r="Q129">
+        <v>65.51</v>
+      </c>
+      <c r="R129">
+        <v>6.46</v>
+      </c>
+      <c r="S129">
+        <v>0.11</v>
+      </c>
+      <c r="T129">
+        <v>0</v>
+      </c>
+      <c r="U129">
+        <v>0</v>
+      </c>
+      <c r="V129">
+        <v>0</v>
+      </c>
+      <c r="W129">
+        <v>0</v>
+      </c>
+      <c r="X129">
+        <v>0</v>
+      </c>
+      <c r="Y129">
+        <v>0</v>
+      </c>
+      <c r="Z129">
+        <v>0</v>
+      </c>
+      <c r="AA129">
+        <v>0</v>
+      </c>
+      <c r="AB129">
+        <v>0</v>
+      </c>
+      <c r="AC129">
+        <v>0</v>
+      </c>
+      <c r="AD129">
+        <v>0</v>
+      </c>
+      <c r="AE129">
+        <v>0</v>
+      </c>
+      <c r="AF129">
+        <v>420.75</v>
+      </c>
+      <c r="AG129">
+        <v>837.17</v>
+      </c>
+      <c r="AH129">
+        <v>196.93</v>
+      </c>
+      <c r="AI129">
+        <v>2088.32</v>
+      </c>
+      <c r="AJ129">
+        <v>1272.19</v>
+      </c>
+      <c r="AK129">
+        <v>646.35</v>
+      </c>
+      <c r="AL129">
+        <v>307.66</v>
+      </c>
+      <c r="AM129">
+        <v>205.39</v>
+      </c>
+      <c r="AN129">
+        <v>9</v>
+      </c>
+      <c r="AO129">
+        <v>2.85</v>
+      </c>
+      <c r="AP129">
+        <v>513.05</v>
+      </c>
+      <c r="AQ129">
+        <v>23</v>
+      </c>
+      <c r="AR129">
+        <v>7.13</v>
+      </c>
+      <c r="AS129">
+        <v>57</v>
+      </c>
+      <c r="AT129" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU129" t="s">
+        <v>139</v>
+      </c>
+      <c r="AV129" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW129" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX129" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="130" spans="1:50">
+      <c r="A130" t="s">
+        <v>141</v>
+      </c>
+      <c r="B130" t="s">
+        <v>64</v>
+      </c>
+      <c r="C130" t="s">
+        <v>77</v>
+      </c>
+      <c r="D130" t="s">
+        <v>53</v>
+      </c>
+      <c r="E130">
+        <v>1</v>
+      </c>
+      <c r="F130">
+        <v>4.24</v>
+      </c>
+      <c r="G130">
+        <v>-5.14</v>
+      </c>
+      <c r="H130">
+        <v>25</v>
+      </c>
+      <c r="I130">
+        <v>15</v>
+      </c>
+      <c r="J130">
+        <v>40</v>
+      </c>
+      <c r="K130">
+        <v>0.56</v>
+      </c>
+      <c r="L130" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M130">
+        <v>6609.86</v>
+      </c>
+      <c r="N130">
+        <v>611.72</v>
+      </c>
+      <c r="O130">
+        <v>28.8</v>
+      </c>
+      <c r="P130">
+        <v>79.98</v>
+      </c>
+      <c r="Q130">
+        <v>91.8</v>
+      </c>
+      <c r="R130">
+        <v>8.5</v>
+      </c>
+      <c r="S130">
+        <v>0.18</v>
+      </c>
+      <c r="T130">
+        <v>0</v>
+      </c>
+      <c r="U130">
+        <v>0</v>
+      </c>
+      <c r="V130">
+        <v>0</v>
+      </c>
+      <c r="W130">
+        <v>0</v>
+      </c>
+      <c r="X130">
+        <v>0</v>
+      </c>
+      <c r="Y130">
+        <v>0</v>
+      </c>
+      <c r="Z130">
+        <v>0</v>
+      </c>
+      <c r="AA130">
+        <v>0</v>
+      </c>
+      <c r="AB130">
+        <v>0</v>
+      </c>
+      <c r="AC130">
+        <v>0</v>
+      </c>
+      <c r="AD130">
+        <v>0</v>
+      </c>
+      <c r="AE130">
+        <v>0</v>
+      </c>
+      <c r="AF130">
+        <v>576.44</v>
+      </c>
+      <c r="AG130">
+        <v>944.6</v>
+      </c>
+      <c r="AH130">
+        <v>169.27</v>
+      </c>
+      <c r="AI130">
+        <v>2905.25</v>
+      </c>
+      <c r="AJ130">
+        <v>2193.1</v>
+      </c>
+      <c r="AK130">
+        <v>981.27</v>
+      </c>
+      <c r="AL130">
+        <v>342.02</v>
+      </c>
+      <c r="AM130">
+        <v>18.95</v>
+      </c>
+      <c r="AN130">
+        <v>1</v>
+      </c>
+      <c r="AO130">
+        <v>0.26</v>
+      </c>
+      <c r="AP130">
+        <v>360.97</v>
+      </c>
+      <c r="AQ130">
+        <v>21</v>
+      </c>
+      <c r="AR130">
+        <v>5.01</v>
+      </c>
+      <c r="AS130">
+        <v>22</v>
+      </c>
+      <c r="AT130" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU130" t="s">
+        <v>142</v>
+      </c>
+      <c r="AV130" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW130" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX130" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="131" spans="1:50">
+      <c r="A131" t="s">
+        <v>141</v>
+      </c>
+      <c r="B131" t="s">
+        <v>64</v>
+      </c>
+      <c r="C131" t="s">
+        <v>52</v>
+      </c>
+      <c r="D131" t="s">
+        <v>53</v>
+      </c>
+      <c r="E131">
+        <v>1</v>
+      </c>
+      <c r="F131">
+        <v>3.88</v>
+      </c>
+      <c r="G131">
+        <v>-3.84</v>
+      </c>
+      <c r="H131">
+        <v>11</v>
+      </c>
+      <c r="I131">
+        <v>5</v>
+      </c>
+      <c r="J131">
+        <v>16</v>
+      </c>
+      <c r="K131">
+        <v>0.22</v>
+      </c>
+      <c r="L131" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M131">
+        <v>4661.96</v>
+      </c>
+      <c r="N131">
+        <v>460.58</v>
+      </c>
+      <c r="O131">
+        <v>26.604</v>
+      </c>
+      <c r="P131">
+        <v>73.91</v>
+      </c>
+      <c r="Q131">
+        <v>64.75</v>
+      </c>
+      <c r="R131">
+        <v>6.4</v>
+      </c>
+      <c r="S131">
+        <v>0.11</v>
+      </c>
+      <c r="T131">
+        <v>0</v>
+      </c>
+      <c r="U131">
+        <v>0</v>
+      </c>
+      <c r="V131">
+        <v>0</v>
+      </c>
+      <c r="W131">
+        <v>0</v>
+      </c>
+      <c r="X131">
+        <v>0</v>
+      </c>
+      <c r="Y131">
+        <v>0</v>
+      </c>
+      <c r="Z131">
+        <v>0</v>
+      </c>
+      <c r="AA131">
+        <v>0</v>
+      </c>
+      <c r="AB131">
+        <v>0</v>
+      </c>
+      <c r="AC131">
+        <v>0</v>
+      </c>
+      <c r="AD131">
+        <v>0</v>
+      </c>
+      <c r="AE131">
+        <v>0</v>
+      </c>
+      <c r="AF131">
+        <v>401.35</v>
+      </c>
+      <c r="AG131">
+        <v>641.77</v>
+      </c>
+      <c r="AH131">
+        <v>158.75</v>
+      </c>
+      <c r="AI131">
+        <v>1982.51</v>
+      </c>
+      <c r="AJ131">
+        <v>1622.76</v>
+      </c>
+      <c r="AK131">
+        <v>459.8</v>
+      </c>
+      <c r="AL131">
+        <v>417.97</v>
+      </c>
+      <c r="AM131">
+        <v>20.18</v>
+      </c>
+      <c r="AN131">
+        <v>1</v>
+      </c>
+      <c r="AO131">
+        <v>0.28</v>
+      </c>
+      <c r="AP131">
+        <v>438.15</v>
+      </c>
+      <c r="AQ131">
+        <v>15</v>
+      </c>
+      <c r="AR131">
+        <v>6.09</v>
+      </c>
+      <c r="AS131">
+        <v>20</v>
+      </c>
+      <c r="AT131" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU131" t="s">
+        <v>142</v>
+      </c>
+      <c r="AV131" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW131" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX131" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="132" spans="1:50">
+      <c r="A132" t="s">
+        <v>141</v>
+      </c>
+      <c r="B132" t="s">
+        <v>64</v>
+      </c>
+      <c r="C132" t="s">
+        <v>59</v>
+      </c>
+      <c r="D132" t="s">
+        <v>53</v>
+      </c>
+      <c r="E132">
+        <v>1</v>
+      </c>
+      <c r="F132">
+        <v>3.45</v>
+      </c>
+      <c r="G132">
+        <v>-3.48</v>
+      </c>
+      <c r="H132">
+        <v>16</v>
+      </c>
+      <c r="I132">
+        <v>7</v>
+      </c>
+      <c r="J132">
+        <v>23</v>
+      </c>
+      <c r="K132">
+        <v>0.32</v>
+      </c>
+      <c r="L132" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M132">
+        <v>5631.46</v>
+      </c>
+      <c r="N132">
+        <v>563.03</v>
+      </c>
+      <c r="O132">
+        <v>24.66</v>
+      </c>
+      <c r="P132">
+        <v>68.53</v>
+      </c>
+      <c r="Q132">
+        <v>78.21</v>
+      </c>
+      <c r="R132">
+        <v>7.82</v>
+      </c>
+      <c r="S132">
+        <v>0.14</v>
+      </c>
+      <c r="T132">
+        <v>0</v>
+      </c>
+      <c r="U132">
+        <v>0</v>
+      </c>
+      <c r="V132">
+        <v>0</v>
+      </c>
+      <c r="W132">
+        <v>0</v>
+      </c>
+      <c r="X132">
+        <v>0</v>
+      </c>
+      <c r="Y132">
+        <v>0</v>
+      </c>
+      <c r="Z132">
+        <v>0</v>
+      </c>
+      <c r="AA132">
+        <v>0</v>
+      </c>
+      <c r="AB132">
+        <v>0</v>
+      </c>
+      <c r="AC132">
+        <v>0</v>
+      </c>
+      <c r="AD132">
+        <v>0</v>
+      </c>
+      <c r="AE132">
+        <v>0</v>
+      </c>
+      <c r="AF132">
+        <v>489.66</v>
+      </c>
+      <c r="AG132">
+        <v>784.94</v>
+      </c>
+      <c r="AH132">
+        <v>234.74</v>
+      </c>
+      <c r="AI132">
+        <v>2237.26</v>
+      </c>
+      <c r="AJ132">
+        <v>2103.42</v>
+      </c>
+      <c r="AK132">
+        <v>540.74</v>
+      </c>
+      <c r="AL132">
+        <v>515.3</v>
+      </c>
+      <c r="AM132">
+        <v>0</v>
+      </c>
+      <c r="AN132">
+        <v>0</v>
+      </c>
+      <c r="AO132">
+        <v>0</v>
+      </c>
+      <c r="AP132">
+        <v>515.3</v>
+      </c>
+      <c r="AQ132">
+        <v>21</v>
+      </c>
+      <c r="AR132">
+        <v>7.16</v>
+      </c>
+      <c r="AS132">
+        <v>18</v>
+      </c>
+      <c r="AT132" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU132" t="s">
+        <v>142</v>
+      </c>
+      <c r="AV132" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW132" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX132" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="133" spans="1:50">
+      <c r="A133" t="s">
+        <v>141</v>
+      </c>
+      <c r="B133" t="s">
+        <v>64</v>
+      </c>
+      <c r="C133" t="s">
+        <v>79</v>
+      </c>
+      <c r="D133" t="s">
+        <v>53</v>
+      </c>
+      <c r="E133">
+        <v>1</v>
+      </c>
+      <c r="F133">
+        <v>3.61</v>
+      </c>
+      <c r="G133">
+        <v>-4.03</v>
+      </c>
+      <c r="H133">
+        <v>15</v>
+      </c>
+      <c r="I133">
+        <v>3</v>
+      </c>
+      <c r="J133">
+        <v>18</v>
+      </c>
+      <c r="K133">
+        <v>0.25</v>
+      </c>
+      <c r="L133" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M133">
+        <v>5322.79</v>
+      </c>
+      <c r="N133">
+        <v>502</v>
+      </c>
+      <c r="O133">
+        <v>24.3</v>
+      </c>
+      <c r="P133">
+        <v>67.54</v>
+      </c>
+      <c r="Q133">
+        <v>73.93</v>
+      </c>
+      <c r="R133">
+        <v>6.97</v>
+      </c>
+      <c r="S133">
+        <v>0.14</v>
+      </c>
+      <c r="T133">
+        <v>0</v>
+      </c>
+      <c r="U133">
+        <v>0</v>
+      </c>
+      <c r="V133">
+        <v>0</v>
+      </c>
+      <c r="W133">
+        <v>0</v>
+      </c>
+      <c r="X133">
+        <v>0</v>
+      </c>
+      <c r="Y133">
+        <v>0</v>
+      </c>
+      <c r="Z133">
+        <v>0</v>
+      </c>
+      <c r="AA133">
+        <v>0</v>
+      </c>
+      <c r="AB133">
+        <v>0</v>
+      </c>
+      <c r="AC133">
+        <v>0</v>
+      </c>
+      <c r="AD133">
+        <v>0</v>
+      </c>
+      <c r="AE133">
+        <v>0</v>
+      </c>
+      <c r="AF133">
+        <v>456.31</v>
+      </c>
+      <c r="AG133">
+        <v>759.02</v>
+      </c>
+      <c r="AH133">
+        <v>131.96</v>
+      </c>
+      <c r="AI133">
+        <v>2153.91</v>
+      </c>
+      <c r="AJ133">
+        <v>1909.79</v>
+      </c>
+      <c r="AK133">
+        <v>648.25</v>
+      </c>
+      <c r="AL133">
+        <v>478.88</v>
+      </c>
+      <c r="AM133">
+        <v>0</v>
+      </c>
+      <c r="AN133">
+        <v>0</v>
+      </c>
+      <c r="AO133">
+        <v>0</v>
+      </c>
+      <c r="AP133">
+        <v>478.88</v>
+      </c>
+      <c r="AQ133">
+        <v>18</v>
+      </c>
+      <c r="AR133">
+        <v>6.65</v>
+      </c>
+      <c r="AS133">
+        <v>16</v>
+      </c>
+      <c r="AT133" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU133" t="s">
+        <v>142</v>
+      </c>
+      <c r="AV133" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW133" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX133" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="134" spans="1:50">
+      <c r="A134" t="s">
+        <v>141</v>
+      </c>
+      <c r="B134" t="s">
+        <v>64</v>
+      </c>
+      <c r="C134" t="s">
+        <v>73</v>
+      </c>
+      <c r="D134" t="s">
+        <v>53</v>
+      </c>
+      <c r="E134">
+        <v>1</v>
+      </c>
+      <c r="F134">
+        <v>3.52</v>
+      </c>
+      <c r="G134">
+        <v>-4.57</v>
+      </c>
+      <c r="H134">
+        <v>7</v>
+      </c>
+      <c r="I134">
+        <v>10</v>
+      </c>
+      <c r="J134">
+        <v>17</v>
+      </c>
+      <c r="K134">
+        <v>0.24</v>
+      </c>
+      <c r="L134" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M134">
+        <v>5030.88</v>
+      </c>
+      <c r="N134">
+        <v>490.98</v>
+      </c>
+      <c r="O134">
+        <v>25.452</v>
+      </c>
+      <c r="P134">
+        <v>70.65</v>
+      </c>
+      <c r="Q134">
+        <v>69.87</v>
+      </c>
+      <c r="R134">
+        <v>6.82</v>
+      </c>
+      <c r="S134">
+        <v>0.12</v>
+      </c>
+      <c r="T134">
+        <v>0</v>
+      </c>
+      <c r="U134">
+        <v>0</v>
+      </c>
+      <c r="V134">
+        <v>0</v>
+      </c>
+      <c r="W134">
+        <v>0</v>
+      </c>
+      <c r="X134">
+        <v>0</v>
+      </c>
+      <c r="Y134">
+        <v>0</v>
+      </c>
+      <c r="Z134">
+        <v>0</v>
+      </c>
+      <c r="AA134">
+        <v>0</v>
+      </c>
+      <c r="AB134">
+        <v>0</v>
+      </c>
+      <c r="AC134">
+        <v>0</v>
+      </c>
+      <c r="AD134">
+        <v>0</v>
+      </c>
+      <c r="AE134">
+        <v>0</v>
+      </c>
+      <c r="AF134">
+        <v>432.23</v>
+      </c>
+      <c r="AG134">
+        <v>736.56</v>
+      </c>
+      <c r="AH134">
+        <v>131</v>
+      </c>
+      <c r="AI134">
+        <v>2154.74</v>
+      </c>
+      <c r="AJ134">
+        <v>1810.26</v>
+      </c>
+      <c r="AK134">
+        <v>465.13</v>
+      </c>
+      <c r="AL134">
+        <v>465.61</v>
+      </c>
+      <c r="AM134">
+        <v>4.14</v>
+      </c>
+      <c r="AN134">
+        <v>0</v>
+      </c>
+      <c r="AO134">
+        <v>0.06</v>
+      </c>
+      <c r="AP134">
+        <v>469.75</v>
+      </c>
+      <c r="AQ134">
+        <v>17</v>
+      </c>
+      <c r="AR134">
+        <v>6.52</v>
+      </c>
+      <c r="AS134">
+        <v>44</v>
+      </c>
+      <c r="AT134" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU134" t="s">
+        <v>142</v>
+      </c>
+      <c r="AV134" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW134" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX134" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="135" spans="1:50">
+      <c r="A135" t="s">
+        <v>143</v>
+      </c>
+      <c r="B135" t="s">
+        <v>64</v>
+      </c>
+      <c r="C135" t="s">
+        <v>77</v>
+      </c>
+      <c r="D135" t="s">
+        <v>53</v>
+      </c>
+      <c r="E135">
+        <v>1</v>
+      </c>
+      <c r="F135">
+        <v>4.21</v>
+      </c>
+      <c r="G135">
+        <v>-4.38</v>
+      </c>
+      <c r="H135">
+        <v>14</v>
+      </c>
+      <c r="I135">
+        <v>17</v>
+      </c>
+      <c r="J135">
+        <v>31</v>
+      </c>
+      <c r="K135">
+        <v>0.43</v>
+      </c>
+      <c r="L135" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M135">
+        <v>5592.54</v>
+      </c>
+      <c r="N135">
+        <v>549.22</v>
+      </c>
+      <c r="O135">
+        <v>27.9</v>
+      </c>
+      <c r="P135">
+        <v>77.49</v>
+      </c>
+      <c r="Q135">
+        <v>77.67</v>
+      </c>
+      <c r="R135">
+        <v>7.63</v>
+      </c>
+      <c r="S135">
+        <v>0.12</v>
+      </c>
+      <c r="T135">
+        <v>0</v>
+      </c>
+      <c r="U135">
+        <v>0</v>
+      </c>
+      <c r="V135">
+        <v>0</v>
+      </c>
+      <c r="W135">
+        <v>0</v>
+      </c>
+      <c r="X135">
+        <v>0</v>
+      </c>
+      <c r="Y135">
+        <v>0</v>
+      </c>
+      <c r="Z135">
+        <v>0</v>
+      </c>
+      <c r="AA135">
+        <v>0</v>
+      </c>
+      <c r="AB135">
+        <v>0</v>
+      </c>
+      <c r="AC135">
+        <v>0</v>
+      </c>
+      <c r="AD135">
+        <v>0</v>
+      </c>
+      <c r="AE135">
+        <v>0</v>
+      </c>
+      <c r="AF135">
+        <v>492.49</v>
+      </c>
+      <c r="AG135">
+        <v>877.23</v>
+      </c>
+      <c r="AH135">
+        <v>258.11</v>
+      </c>
+      <c r="AI135">
+        <v>2700.47</v>
+      </c>
+      <c r="AJ135">
+        <v>1666.45</v>
+      </c>
+      <c r="AK135">
+        <v>575.05</v>
+      </c>
+      <c r="AL135">
+        <v>364.67</v>
+      </c>
+      <c r="AM135">
+        <v>27.79</v>
+      </c>
+      <c r="AN135">
+        <v>2</v>
+      </c>
+      <c r="AO135">
+        <v>0.39</v>
+      </c>
+      <c r="AP135">
+        <v>392.46</v>
+      </c>
+      <c r="AQ135">
+        <v>22</v>
+      </c>
+      <c r="AR135">
+        <v>5.45</v>
+      </c>
+      <c r="AS135">
+        <v>18</v>
+      </c>
+      <c r="AT135" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU135" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV135" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW135" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX135" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="136" spans="1:50">
+      <c r="A136" t="s">
+        <v>143</v>
+      </c>
+      <c r="B136" t="s">
+        <v>64</v>
+      </c>
+      <c r="C136" t="s">
+        <v>52</v>
+      </c>
+      <c r="D136" t="s">
+        <v>53</v>
+      </c>
+      <c r="E136">
+        <v>1</v>
+      </c>
+      <c r="F136">
+        <v>3.92</v>
+      </c>
+      <c r="G136">
+        <v>-4.81</v>
+      </c>
+      <c r="H136">
+        <v>16</v>
+      </c>
+      <c r="I136">
+        <v>12</v>
+      </c>
+      <c r="J136">
+        <v>28</v>
+      </c>
+      <c r="K136">
+        <v>0.39</v>
+      </c>
+      <c r="L136" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M136">
+        <v>4966.23</v>
+      </c>
+      <c r="N136">
+        <v>567.82</v>
+      </c>
+      <c r="O136">
+        <v>26.532</v>
+      </c>
+      <c r="P136">
+        <v>73.74</v>
+      </c>
+      <c r="Q136">
+        <v>68.98</v>
+      </c>
+      <c r="R136">
+        <v>7.89</v>
+      </c>
+      <c r="S136">
+        <v>0.12</v>
+      </c>
+      <c r="T136">
+        <v>0</v>
+      </c>
+      <c r="U136">
+        <v>0</v>
+      </c>
+      <c r="V136">
+        <v>0</v>
+      </c>
+      <c r="W136">
+        <v>0</v>
+      </c>
+      <c r="X136">
+        <v>0</v>
+      </c>
+      <c r="Y136">
+        <v>0</v>
+      </c>
+      <c r="Z136">
+        <v>0</v>
+      </c>
+      <c r="AA136">
+        <v>0</v>
+      </c>
+      <c r="AB136">
+        <v>0</v>
+      </c>
+      <c r="AC136">
+        <v>0</v>
+      </c>
+      <c r="AD136">
+        <v>0</v>
+      </c>
+      <c r="AE136">
+        <v>0</v>
+      </c>
+      <c r="AF136">
+        <v>439.91</v>
+      </c>
+      <c r="AG136">
+        <v>766.35</v>
+      </c>
+      <c r="AH136">
+        <v>246.85</v>
+      </c>
+      <c r="AI136">
+        <v>2056.94</v>
+      </c>
+      <c r="AJ136">
+        <v>1677.36</v>
+      </c>
+      <c r="AK136">
+        <v>526.45</v>
+      </c>
+      <c r="AL136">
+        <v>448.04</v>
+      </c>
+      <c r="AM136">
+        <v>10.27</v>
+      </c>
+      <c r="AN136">
+        <v>0</v>
+      </c>
+      <c r="AO136">
+        <v>0.14</v>
+      </c>
+      <c r="AP136">
+        <v>458.31</v>
+      </c>
+      <c r="AQ136">
+        <v>23</v>
+      </c>
+      <c r="AR136">
+        <v>6.37</v>
+      </c>
+      <c r="AS136">
+        <v>41</v>
+      </c>
+      <c r="AT136" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU136" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV136" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW136" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX136" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="137" spans="1:50">
+      <c r="A137" t="s">
+        <v>143</v>
+      </c>
+      <c r="B137" t="s">
+        <v>64</v>
+      </c>
+      <c r="C137" t="s">
+        <v>79</v>
+      </c>
+      <c r="D137" t="s">
+        <v>53</v>
+      </c>
+      <c r="E137">
+        <v>1</v>
+      </c>
+      <c r="F137">
+        <v>3.94</v>
+      </c>
+      <c r="G137">
+        <v>-3.87</v>
+      </c>
+      <c r="H137">
+        <v>16</v>
+      </c>
+      <c r="I137">
+        <v>12</v>
+      </c>
+      <c r="J137">
+        <v>28</v>
+      </c>
+      <c r="K137">
+        <v>0.39</v>
+      </c>
+      <c r="L137" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M137">
+        <v>5551.29</v>
+      </c>
+      <c r="N137">
+        <v>592.59</v>
+      </c>
+      <c r="O137">
+        <v>24.552</v>
+      </c>
+      <c r="P137">
+        <v>68.24</v>
+      </c>
+      <c r="Q137">
+        <v>77.1</v>
+      </c>
+      <c r="R137">
+        <v>8.23</v>
+      </c>
+      <c r="S137">
+        <v>0.16</v>
+      </c>
+      <c r="T137">
+        <v>0</v>
+      </c>
+      <c r="U137">
+        <v>0</v>
+      </c>
+      <c r="V137">
+        <v>0</v>
+      </c>
+      <c r="W137">
+        <v>0</v>
+      </c>
+      <c r="X137">
+        <v>0</v>
+      </c>
+      <c r="Y137">
+        <v>0</v>
+      </c>
+      <c r="Z137">
+        <v>0</v>
+      </c>
+      <c r="AA137">
+        <v>0</v>
+      </c>
+      <c r="AB137">
+        <v>0</v>
+      </c>
+      <c r="AC137">
+        <v>0</v>
+      </c>
+      <c r="AD137">
+        <v>0</v>
+      </c>
+      <c r="AE137">
+        <v>0</v>
+      </c>
+      <c r="AF137">
+        <v>492.36</v>
+      </c>
+      <c r="AG137">
+        <v>916.96</v>
+      </c>
+      <c r="AH137">
+        <v>265.82</v>
+      </c>
+      <c r="AI137">
+        <v>1997.52</v>
+      </c>
+      <c r="AJ137">
+        <v>2152.97</v>
+      </c>
+      <c r="AK137">
+        <v>776.85</v>
+      </c>
+      <c r="AL137">
+        <v>357.88</v>
+      </c>
+      <c r="AM137">
+        <v>0</v>
+      </c>
+      <c r="AN137">
+        <v>0</v>
+      </c>
+      <c r="AO137">
+        <v>0</v>
+      </c>
+      <c r="AP137">
+        <v>357.88</v>
+      </c>
+      <c r="AQ137">
+        <v>17</v>
+      </c>
+      <c r="AR137">
+        <v>4.97</v>
+      </c>
+      <c r="AS137">
+        <v>22</v>
+      </c>
+      <c r="AT137" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU137" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV137" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW137" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX137" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="138" spans="1:50">
+      <c r="A138" t="s">
+        <v>143</v>
+      </c>
+      <c r="B138" t="s">
+        <v>64</v>
+      </c>
+      <c r="C138" t="s">
+        <v>73</v>
+      </c>
+      <c r="D138" t="s">
+        <v>53</v>
+      </c>
+      <c r="E138">
+        <v>1</v>
+      </c>
+      <c r="F138">
+        <v>4.24</v>
+      </c>
+      <c r="G138">
+        <v>-5.2</v>
+      </c>
+      <c r="H138">
+        <v>11</v>
+      </c>
+      <c r="I138">
+        <v>24</v>
+      </c>
+      <c r="J138">
+        <v>35</v>
+      </c>
+      <c r="K138">
+        <v>0.49</v>
+      </c>
+      <c r="L138" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M138">
+        <v>4828.94</v>
+      </c>
+      <c r="N138">
+        <v>550.92</v>
+      </c>
+      <c r="O138">
+        <v>24.732</v>
+      </c>
+      <c r="P138">
+        <v>68.68</v>
+      </c>
+      <c r="Q138">
+        <v>67.07</v>
+      </c>
+      <c r="R138">
+        <v>7.65</v>
+      </c>
+      <c r="S138">
+        <v>0.12</v>
+      </c>
+      <c r="T138">
+        <v>0</v>
+      </c>
+      <c r="U138">
+        <v>0</v>
+      </c>
+      <c r="V138">
+        <v>0</v>
+      </c>
+      <c r="W138">
+        <v>0</v>
+      </c>
+      <c r="X138">
+        <v>0</v>
+      </c>
+      <c r="Y138">
+        <v>0</v>
+      </c>
+      <c r="Z138">
+        <v>0</v>
+      </c>
+      <c r="AA138">
+        <v>0</v>
+      </c>
+      <c r="AB138">
+        <v>0</v>
+      </c>
+      <c r="AC138">
+        <v>0</v>
+      </c>
+      <c r="AD138">
+        <v>0</v>
+      </c>
+      <c r="AE138">
+        <v>0</v>
+      </c>
+      <c r="AF138">
+        <v>435.47</v>
+      </c>
+      <c r="AG138">
+        <v>771.71</v>
+      </c>
+      <c r="AH138">
+        <v>211.14</v>
+      </c>
+      <c r="AI138">
+        <v>2013.94</v>
+      </c>
+      <c r="AJ138">
+        <v>1772.64</v>
+      </c>
+      <c r="AK138">
+        <v>592.06</v>
+      </c>
+      <c r="AL138">
+        <v>239.17</v>
+      </c>
+      <c r="AM138">
+        <v>0</v>
+      </c>
+      <c r="AN138">
+        <v>0</v>
+      </c>
+      <c r="AO138">
+        <v>0</v>
+      </c>
+      <c r="AP138">
+        <v>239.17</v>
+      </c>
+      <c r="AQ138">
+        <v>16</v>
+      </c>
+      <c r="AR138">
+        <v>3.32</v>
+      </c>
+      <c r="AS138">
+        <v>89</v>
+      </c>
+      <c r="AT138" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU138" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV138" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW138" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX138" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="139" spans="1:50">
+      <c r="L139" s="5"/>
+    </row>
+    <row r="140" spans="1:50">
+      <c r="L140" s="5"/>
+    </row>
+    <row r="141" spans="1:50">
+      <c r="L141" s="5"/>
+    </row>
+    <row r="142" spans="1:50">
+      <c r="L142" s="5"/>
+    </row>
+    <row r="143" spans="1:50">
+      <c r="L143" s="5"/>
+    </row>
+    <row r="144" spans="1:50">
+      <c r="L144" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GPS_Formativas_2026.xlsx
+++ b/GPS_Formativas_2026.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="147">
   <si>
     <t>Date</t>
   </si>
@@ -452,13 +452,22 @@
     <t>Benjamin Silvera</t>
   </si>
   <si>
-    <t>25/5</t>
-  </si>
-  <si>
     <t>INTRODUCTORIA</t>
   </si>
   <si>
-    <t>26/5</t>
+    <t>26-5-26</t>
+  </si>
+  <si>
+    <t>MD -2</t>
+  </si>
+  <si>
+    <t>Matteo Costantini</t>
+  </si>
+  <si>
+    <t>MD - 3</t>
+  </si>
+  <si>
+    <t>29-5-26</t>
   </si>
 </sst>
 </file>
@@ -471,13 +480,19 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -818,12 +833,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -944,16 +974,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -962,119 +989,122 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1089,6 +1119,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="35" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1622,7 +1661,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AX144"/>
+  <dimension ref="A1:AX164"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="30.4444444444444" customWidth="1"/>
@@ -21239,7 +21278,7 @@
     </row>
     <row r="130" spans="1:50">
       <c r="A130" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="B130" t="s">
         <v>64</v>
@@ -21377,7 +21416,7 @@
         <v>75</v>
       </c>
       <c r="AU130" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AV130" t="s">
         <v>66</v>
@@ -21391,7 +21430,7 @@
     </row>
     <row r="131" spans="1:50">
       <c r="A131" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="B131" t="s">
         <v>64</v>
@@ -21529,7 +21568,7 @@
         <v>54</v>
       </c>
       <c r="AU131" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AV131" t="s">
         <v>66</v>
@@ -21543,7 +21582,7 @@
     </row>
     <row r="132" spans="1:50">
       <c r="A132" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="B132" t="s">
         <v>64</v>
@@ -21681,7 +21720,7 @@
         <v>60</v>
       </c>
       <c r="AU132" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AV132" t="s">
         <v>66</v>
@@ -21695,7 +21734,7 @@
     </row>
     <row r="133" spans="1:50">
       <c r="A133" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="B133" t="s">
         <v>64</v>
@@ -21833,7 +21872,7 @@
         <v>63</v>
       </c>
       <c r="AU133" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AV133" t="s">
         <v>66</v>
@@ -21847,7 +21886,7 @@
     </row>
     <row r="134" spans="1:50">
       <c r="A134" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="B134" t="s">
         <v>64</v>
@@ -21985,7 +22024,7 @@
         <v>54</v>
       </c>
       <c r="AU134" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AV134" t="s">
         <v>66</v>
@@ -21999,7 +22038,7 @@
     </row>
     <row r="135" spans="1:50">
       <c r="A135" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B135" t="s">
         <v>64</v>
@@ -22151,7 +22190,7 @@
     </row>
     <row r="136" spans="1:50">
       <c r="A136" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B136" t="s">
         <v>64</v>
@@ -22303,7 +22342,7 @@
     </row>
     <row r="137" spans="1:50">
       <c r="A137" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B137" t="s">
         <v>64</v>
@@ -22455,7 +22494,7 @@
     </row>
     <row r="138" spans="1:50">
       <c r="A138" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B138" t="s">
         <v>64</v>
@@ -22606,22 +22645,3956 @@
       </c>
     </row>
     <row r="139" spans="1:50">
-      <c r="L139" s="5"/>
+      <c r="A139" t="s">
+        <v>129</v>
+      </c>
+      <c r="B139" t="s">
+        <v>64</v>
+      </c>
+      <c r="C139" t="s">
+        <v>77</v>
+      </c>
+      <c r="D139" t="s">
+        <v>53</v>
+      </c>
+      <c r="E139">
+        <v>1</v>
+      </c>
+      <c r="F139">
+        <v>4.51</v>
+      </c>
+      <c r="G139">
+        <v>-4.94</v>
+      </c>
+      <c r="H139">
+        <v>16</v>
+      </c>
+      <c r="I139">
+        <v>10</v>
+      </c>
+      <c r="J139">
+        <v>26</v>
+      </c>
+      <c r="K139">
+        <v>0.43</v>
+      </c>
+      <c r="L139" s="5">
+        <v>0.0423611111111111</v>
+      </c>
+      <c r="M139">
+        <v>3419.07</v>
+      </c>
+      <c r="N139">
+        <v>351.42</v>
+      </c>
+      <c r="O139">
+        <v>25.308</v>
+      </c>
+      <c r="P139">
+        <v>70.3</v>
+      </c>
+      <c r="Q139">
+        <v>56.69</v>
+      </c>
+      <c r="R139">
+        <v>5.76</v>
+      </c>
+      <c r="S139">
+        <v>0.06</v>
+      </c>
+      <c r="T139">
+        <v>0</v>
+      </c>
+      <c r="U139">
+        <v>0</v>
+      </c>
+      <c r="V139">
+        <v>0</v>
+      </c>
+      <c r="W139">
+        <v>0</v>
+      </c>
+      <c r="X139">
+        <v>0</v>
+      </c>
+      <c r="Y139">
+        <v>0</v>
+      </c>
+      <c r="Z139">
+        <v>0</v>
+      </c>
+      <c r="AA139">
+        <v>0</v>
+      </c>
+      <c r="AB139">
+        <v>0</v>
+      </c>
+      <c r="AC139">
+        <v>0</v>
+      </c>
+      <c r="AD139">
+        <v>0</v>
+      </c>
+      <c r="AE139">
+        <v>0</v>
+      </c>
+      <c r="AF139">
+        <v>291.47</v>
+      </c>
+      <c r="AG139">
+        <v>329.76</v>
+      </c>
+      <c r="AH139">
+        <v>295.51</v>
+      </c>
+      <c r="AI139">
+        <v>1762.03</v>
+      </c>
+      <c r="AJ139">
+        <v>1014.75</v>
+      </c>
+      <c r="AK139">
+        <v>243.88</v>
+      </c>
+      <c r="AL139">
+        <v>101.5</v>
+      </c>
+      <c r="AM139">
+        <v>1.28</v>
+      </c>
+      <c r="AN139">
+        <v>0</v>
+      </c>
+      <c r="AO139">
+        <v>0.02</v>
+      </c>
+      <c r="AP139">
+        <v>102.78</v>
+      </c>
+      <c r="AQ139">
+        <v>9</v>
+      </c>
+      <c r="AR139">
+        <v>1.68</v>
+      </c>
+      <c r="AS139">
+        <v>11</v>
+      </c>
+      <c r="AT139" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU139" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV139" t="s">
+        <v>143</v>
+      </c>
+      <c r="AW139" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX139" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="140" spans="1:50">
-      <c r="L140" s="5"/>
+      <c r="A140" t="s">
+        <v>129</v>
+      </c>
+      <c r="B140" t="s">
+        <v>64</v>
+      </c>
+      <c r="C140" t="s">
+        <v>52</v>
+      </c>
+      <c r="D140" t="s">
+        <v>53</v>
+      </c>
+      <c r="E140">
+        <v>1</v>
+      </c>
+      <c r="F140">
+        <v>4.25</v>
+      </c>
+      <c r="G140">
+        <v>-4.38</v>
+      </c>
+      <c r="H140">
+        <v>13</v>
+      </c>
+      <c r="I140">
+        <v>8</v>
+      </c>
+      <c r="J140">
+        <v>21</v>
+      </c>
+      <c r="K140">
+        <v>0.34</v>
+      </c>
+      <c r="L140" s="5">
+        <v>0.0423611111111111</v>
+      </c>
+      <c r="M140">
+        <v>3363.53</v>
+      </c>
+      <c r="N140">
+        <v>352.01</v>
+      </c>
+      <c r="O140">
+        <v>24.156</v>
+      </c>
+      <c r="P140">
+        <v>67.11</v>
+      </c>
+      <c r="Q140">
+        <v>55.14</v>
+      </c>
+      <c r="R140">
+        <v>5.77</v>
+      </c>
+      <c r="S140">
+        <v>0.08</v>
+      </c>
+      <c r="T140">
+        <v>0</v>
+      </c>
+      <c r="U140">
+        <v>0</v>
+      </c>
+      <c r="V140">
+        <v>0</v>
+      </c>
+      <c r="W140">
+        <v>0</v>
+      </c>
+      <c r="X140">
+        <v>0</v>
+      </c>
+      <c r="Y140">
+        <v>0</v>
+      </c>
+      <c r="Z140">
+        <v>0</v>
+      </c>
+      <c r="AA140">
+        <v>0</v>
+      </c>
+      <c r="AB140">
+        <v>0</v>
+      </c>
+      <c r="AC140">
+        <v>0</v>
+      </c>
+      <c r="AD140">
+        <v>0</v>
+      </c>
+      <c r="AE140">
+        <v>0</v>
+      </c>
+      <c r="AF140">
+        <v>290.17</v>
+      </c>
+      <c r="AG140">
+        <v>370.64</v>
+      </c>
+      <c r="AH140">
+        <v>220.43</v>
+      </c>
+      <c r="AI140">
+        <v>1525.19</v>
+      </c>
+      <c r="AJ140">
+        <v>1177.46</v>
+      </c>
+      <c r="AK140">
+        <v>381.79</v>
+      </c>
+      <c r="AL140">
+        <v>58.77</v>
+      </c>
+      <c r="AM140">
+        <v>0</v>
+      </c>
+      <c r="AN140">
+        <v>0</v>
+      </c>
+      <c r="AO140">
+        <v>0</v>
+      </c>
+      <c r="AP140">
+        <v>58.77</v>
+      </c>
+      <c r="AQ140">
+        <v>7</v>
+      </c>
+      <c r="AR140">
+        <v>0.96</v>
+      </c>
+      <c r="AS140">
+        <v>25</v>
+      </c>
+      <c r="AT140" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU140" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV140" t="s">
+        <v>143</v>
+      </c>
+      <c r="AW140" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX140" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="141" spans="1:50">
-      <c r="L141" s="5"/>
+      <c r="A141" t="s">
+        <v>129</v>
+      </c>
+      <c r="B141" t="s">
+        <v>64</v>
+      </c>
+      <c r="C141" t="s">
+        <v>59</v>
+      </c>
+      <c r="D141" t="s">
+        <v>53</v>
+      </c>
+      <c r="E141">
+        <v>1</v>
+      </c>
+      <c r="F141">
+        <v>4.11</v>
+      </c>
+      <c r="G141">
+        <v>-4.45</v>
+      </c>
+      <c r="H141">
+        <v>7</v>
+      </c>
+      <c r="I141">
+        <v>4</v>
+      </c>
+      <c r="J141">
+        <v>11</v>
+      </c>
+      <c r="K141">
+        <v>0.18</v>
+      </c>
+      <c r="L141" s="5">
+        <v>0.0423611111111111</v>
+      </c>
+      <c r="M141">
+        <v>3071.87</v>
+      </c>
+      <c r="N141">
+        <v>306.31</v>
+      </c>
+      <c r="O141">
+        <v>20.484</v>
+      </c>
+      <c r="P141">
+        <v>56.91</v>
+      </c>
+      <c r="Q141">
+        <v>50.96</v>
+      </c>
+      <c r="R141">
+        <v>5.02</v>
+      </c>
+      <c r="S141">
+        <v>0.07</v>
+      </c>
+      <c r="T141">
+        <v>0</v>
+      </c>
+      <c r="U141">
+        <v>0</v>
+      </c>
+      <c r="V141">
+        <v>0</v>
+      </c>
+      <c r="W141">
+        <v>0</v>
+      </c>
+      <c r="X141">
+        <v>0</v>
+      </c>
+      <c r="Y141">
+        <v>0</v>
+      </c>
+      <c r="Z141">
+        <v>0</v>
+      </c>
+      <c r="AA141">
+        <v>0</v>
+      </c>
+      <c r="AB141">
+        <v>0</v>
+      </c>
+      <c r="AC141">
+        <v>0</v>
+      </c>
+      <c r="AD141">
+        <v>0</v>
+      </c>
+      <c r="AE141">
+        <v>0</v>
+      </c>
+      <c r="AF141">
+        <v>254.89</v>
+      </c>
+      <c r="AG141">
+        <v>191.7</v>
+      </c>
+      <c r="AH141">
+        <v>238.13</v>
+      </c>
+      <c r="AI141">
+        <v>1561.16</v>
+      </c>
+      <c r="AJ141">
+        <v>952.06</v>
+      </c>
+      <c r="AK141">
+        <v>315.14</v>
+      </c>
+      <c r="AL141">
+        <v>5.38</v>
+      </c>
+      <c r="AM141">
+        <v>0</v>
+      </c>
+      <c r="AN141">
+        <v>0</v>
+      </c>
+      <c r="AO141">
+        <v>0</v>
+      </c>
+      <c r="AP141">
+        <v>5.38</v>
+      </c>
+      <c r="AQ141">
+        <v>0</v>
+      </c>
+      <c r="AR141">
+        <v>0.09</v>
+      </c>
+      <c r="AS141">
+        <v>12</v>
+      </c>
+      <c r="AT141" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU141" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV141" t="s">
+        <v>143</v>
+      </c>
+      <c r="AW141" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX141" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="142" spans="1:50">
-      <c r="L142" s="5"/>
+      <c r="A142" t="s">
+        <v>129</v>
+      </c>
+      <c r="B142" t="s">
+        <v>64</v>
+      </c>
+      <c r="C142" t="s">
+        <v>61</v>
+      </c>
+      <c r="D142" t="s">
+        <v>53</v>
+      </c>
+      <c r="E142">
+        <v>1</v>
+      </c>
+      <c r="F142">
+        <v>4</v>
+      </c>
+      <c r="G142">
+        <v>-5.64</v>
+      </c>
+      <c r="H142">
+        <v>20</v>
+      </c>
+      <c r="I142">
+        <v>12</v>
+      </c>
+      <c r="J142">
+        <v>32</v>
+      </c>
+      <c r="K142">
+        <v>0.52</v>
+      </c>
+      <c r="L142" s="5">
+        <v>0.0423611111111111</v>
+      </c>
+      <c r="M142">
+        <v>3527.59</v>
+      </c>
+      <c r="N142">
+        <v>332.04</v>
+      </c>
+      <c r="O142">
+        <v>27.324</v>
+      </c>
+      <c r="P142">
+        <v>75.94</v>
+      </c>
+      <c r="Q142">
+        <v>58.62</v>
+      </c>
+      <c r="R142">
+        <v>5.44</v>
+      </c>
+      <c r="S142">
+        <v>0.07</v>
+      </c>
+      <c r="T142">
+        <v>0</v>
+      </c>
+      <c r="U142">
+        <v>0</v>
+      </c>
+      <c r="V142">
+        <v>0</v>
+      </c>
+      <c r="W142">
+        <v>0</v>
+      </c>
+      <c r="X142">
+        <v>0</v>
+      </c>
+      <c r="Y142">
+        <v>0</v>
+      </c>
+      <c r="Z142">
+        <v>0</v>
+      </c>
+      <c r="AA142">
+        <v>0</v>
+      </c>
+      <c r="AB142">
+        <v>0</v>
+      </c>
+      <c r="AC142">
+        <v>0</v>
+      </c>
+      <c r="AD142">
+        <v>0</v>
+      </c>
+      <c r="AE142">
+        <v>0</v>
+      </c>
+      <c r="AF142">
+        <v>308.79</v>
+      </c>
+      <c r="AG142">
+        <v>406.78</v>
+      </c>
+      <c r="AH142">
+        <v>208.95</v>
+      </c>
+      <c r="AI142">
+        <v>1874.52</v>
+      </c>
+      <c r="AJ142">
+        <v>981.16</v>
+      </c>
+      <c r="AK142">
+        <v>366.93</v>
+      </c>
+      <c r="AL142">
+        <v>80.6</v>
+      </c>
+      <c r="AM142">
+        <v>15.43</v>
+      </c>
+      <c r="AN142">
+        <v>1</v>
+      </c>
+      <c r="AO142">
+        <v>0.25</v>
+      </c>
+      <c r="AP142">
+        <v>96.03</v>
+      </c>
+      <c r="AQ142">
+        <v>7</v>
+      </c>
+      <c r="AR142">
+        <v>1.57</v>
+      </c>
+      <c r="AS142">
+        <v>18</v>
+      </c>
+      <c r="AT142" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU142" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV142" t="s">
+        <v>143</v>
+      </c>
+      <c r="AW142" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX142" t="s">
+        <v>122</v>
+      </c>
     </row>
-    <row r="143" spans="1:50">
-      <c r="L143" s="5"/>
+    <row r="143" ht="15.15" spans="1:50">
+      <c r="A143" t="s">
+        <v>129</v>
+      </c>
+      <c r="B143" t="s">
+        <v>64</v>
+      </c>
+      <c r="C143" t="s">
+        <v>144</v>
+      </c>
+      <c r="D143" t="s">
+        <v>53</v>
+      </c>
+      <c r="E143">
+        <v>1</v>
+      </c>
+      <c r="F143">
+        <v>4.26</v>
+      </c>
+      <c r="G143">
+        <v>-5.3</v>
+      </c>
+      <c r="H143">
+        <v>9</v>
+      </c>
+      <c r="I143">
+        <v>13</v>
+      </c>
+      <c r="J143">
+        <v>22</v>
+      </c>
+      <c r="K143">
+        <v>0.36</v>
+      </c>
+      <c r="L143" s="5">
+        <v>0.0423611111111111</v>
+      </c>
+      <c r="M143">
+        <v>3183.24</v>
+      </c>
+      <c r="N143">
+        <v>275.51</v>
+      </c>
+      <c r="O143">
+        <v>25.164</v>
+      </c>
+      <c r="P143">
+        <v>69.9</v>
+      </c>
+      <c r="Q143">
+        <v>52.18</v>
+      </c>
+      <c r="R143">
+        <v>4.52</v>
+      </c>
+      <c r="S143">
+        <v>0.05</v>
+      </c>
+      <c r="T143">
+        <v>0</v>
+      </c>
+      <c r="U143">
+        <v>0</v>
+      </c>
+      <c r="V143">
+        <v>0</v>
+      </c>
+      <c r="W143">
+        <v>0</v>
+      </c>
+      <c r="X143">
+        <v>0</v>
+      </c>
+      <c r="Y143">
+        <v>0</v>
+      </c>
+      <c r="Z143">
+        <v>0</v>
+      </c>
+      <c r="AA143">
+        <v>0</v>
+      </c>
+      <c r="AB143">
+        <v>0</v>
+      </c>
+      <c r="AC143">
+        <v>0</v>
+      </c>
+      <c r="AD143">
+        <v>0</v>
+      </c>
+      <c r="AE143">
+        <v>0</v>
+      </c>
+      <c r="AF143">
+        <v>277.32</v>
+      </c>
+      <c r="AG143">
+        <v>337.9</v>
+      </c>
+      <c r="AH143">
+        <v>212.12</v>
+      </c>
+      <c r="AI143">
+        <v>1698.93</v>
+      </c>
+      <c r="AJ143">
+        <v>873.1</v>
+      </c>
+      <c r="AK143">
+        <v>265.68</v>
+      </c>
+      <c r="AL143">
+        <v>133.49</v>
+      </c>
+      <c r="AM143">
+        <v>0</v>
+      </c>
+      <c r="AN143">
+        <v>0</v>
+      </c>
+      <c r="AO143">
+        <v>0</v>
+      </c>
+      <c r="AP143">
+        <v>133.49</v>
+      </c>
+      <c r="AQ143">
+        <v>10</v>
+      </c>
+      <c r="AR143">
+        <v>2.19</v>
+      </c>
+      <c r="AS143">
+        <v>6</v>
+      </c>
+      <c r="AT143" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU143" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV143" t="s">
+        <v>143</v>
+      </c>
+      <c r="AW143" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX143" t="s">
+        <v>122</v>
+      </c>
     </row>
-    <row r="144" spans="1:50">
-      <c r="L144" s="5"/>
+    <row r="144" ht="15.15" spans="1:50">
+      <c r="A144" t="s">
+        <v>142</v>
+      </c>
+      <c r="B144" t="s">
+        <v>51</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E144" s="7">
+        <v>0</v>
+      </c>
+      <c r="F144" s="7">
+        <v>3.61</v>
+      </c>
+      <c r="G144" s="7">
+        <v>-3.93</v>
+      </c>
+      <c r="H144" s="7">
+        <v>11</v>
+      </c>
+      <c r="I144" s="7">
+        <v>12</v>
+      </c>
+      <c r="J144" s="7">
+        <v>23</v>
+      </c>
+      <c r="K144" s="7">
+        <v>0.48</v>
+      </c>
+      <c r="L144" s="8">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="M144" s="7">
+        <v>3431.97</v>
+      </c>
+      <c r="N144" s="7">
+        <v>431.97</v>
+      </c>
+      <c r="O144" s="7">
+        <v>21.024</v>
+      </c>
+      <c r="P144" s="7">
+        <v>58.37</v>
+      </c>
+      <c r="Q144" s="7">
+        <v>71.5</v>
+      </c>
+      <c r="R144" s="7">
+        <v>9</v>
+      </c>
+      <c r="S144" s="7">
+        <v>0.07</v>
+      </c>
+      <c r="T144" s="7">
+        <v>0</v>
+      </c>
+      <c r="U144" s="7">
+        <v>0</v>
+      </c>
+      <c r="V144" s="7">
+        <v>0</v>
+      </c>
+      <c r="W144" s="7">
+        <v>0</v>
+      </c>
+      <c r="X144" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y144" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z144" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA144" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB144" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC144" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD144" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE144" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF144" s="7">
+        <v>308.93</v>
+      </c>
+      <c r="AG144" s="7">
+        <v>366.34</v>
+      </c>
+      <c r="AH144" s="7">
+        <v>183.74</v>
+      </c>
+      <c r="AI144" s="7">
+        <v>2063.79</v>
+      </c>
+      <c r="AJ144" s="7">
+        <v>1011.25</v>
+      </c>
+      <c r="AK144" s="7">
+        <v>168.01</v>
+      </c>
+      <c r="AL144" s="7">
+        <v>5.37</v>
+      </c>
+      <c r="AM144" s="7">
+        <v>0</v>
+      </c>
+      <c r="AN144" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO144" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP144" s="7">
+        <v>5.37</v>
+      </c>
+      <c r="AQ144" s="7">
+        <v>1</v>
+      </c>
+      <c r="AR144" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="AS144" s="7">
+        <v>60</v>
+      </c>
+      <c r="AT144" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU144" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV144" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AW144" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX144" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="145" ht="15.15" spans="1:50">
+      <c r="A145" t="s">
+        <v>142</v>
+      </c>
+      <c r="B145" t="s">
+        <v>51</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E145" s="7">
+        <v>0</v>
+      </c>
+      <c r="F145" s="7">
+        <v>4.02</v>
+      </c>
+      <c r="G145" s="7">
+        <v>-4.46</v>
+      </c>
+      <c r="H145" s="7">
+        <v>12</v>
+      </c>
+      <c r="I145" s="7">
+        <v>14</v>
+      </c>
+      <c r="J145" s="7">
+        <v>26</v>
+      </c>
+      <c r="K145" s="7">
+        <v>0.54</v>
+      </c>
+      <c r="L145" s="8">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="M145" s="7">
+        <v>3247.06</v>
+      </c>
+      <c r="N145" s="7">
+        <v>395.7</v>
+      </c>
+      <c r="O145" s="7">
+        <v>24.084</v>
+      </c>
+      <c r="P145" s="7">
+        <v>66.9</v>
+      </c>
+      <c r="Q145" s="7">
+        <v>67.65</v>
+      </c>
+      <c r="R145" s="7">
+        <v>8.24</v>
+      </c>
+      <c r="S145" s="7">
+        <v>0.07</v>
+      </c>
+      <c r="T145" s="7">
+        <v>0</v>
+      </c>
+      <c r="U145" s="7">
+        <v>0</v>
+      </c>
+      <c r="V145" s="7">
+        <v>0</v>
+      </c>
+      <c r="W145" s="7">
+        <v>0</v>
+      </c>
+      <c r="X145" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y145" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z145" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA145" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB145" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC145" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD145" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE145" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF145" s="7">
+        <v>288.21</v>
+      </c>
+      <c r="AG145" s="7">
+        <v>325.05</v>
+      </c>
+      <c r="AH145" s="7">
+        <v>199.1</v>
+      </c>
+      <c r="AI145" s="7">
+        <v>1842.56</v>
+      </c>
+      <c r="AJ145" s="7">
+        <v>927.27</v>
+      </c>
+      <c r="AK145" s="7">
+        <v>225.53</v>
+      </c>
+      <c r="AL145" s="7">
+        <v>52.32</v>
+      </c>
+      <c r="AM145" s="7">
+        <v>0</v>
+      </c>
+      <c r="AN145" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO145" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP145" s="7">
+        <v>52.32</v>
+      </c>
+      <c r="AQ145" s="7">
+        <v>5</v>
+      </c>
+      <c r="AR145" s="7">
+        <v>1.09</v>
+      </c>
+      <c r="AS145" s="7">
+        <v>76</v>
+      </c>
+      <c r="AT145" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU145" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV145" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AW145" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX145" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="146" ht="15.15" spans="1:50">
+      <c r="A146" t="s">
+        <v>142</v>
+      </c>
+      <c r="B146" t="s">
+        <v>51</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E146" s="7">
+        <v>0</v>
+      </c>
+      <c r="F146" s="7">
+        <v>3.55</v>
+      </c>
+      <c r="G146" s="7">
+        <v>-5.45</v>
+      </c>
+      <c r="H146" s="7">
+        <v>9</v>
+      </c>
+      <c r="I146" s="7">
+        <v>8</v>
+      </c>
+      <c r="J146" s="7">
+        <v>17</v>
+      </c>
+      <c r="K146" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="L146" s="8">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="M146" s="7">
+        <v>2889.85</v>
+      </c>
+      <c r="N146" s="7">
+        <v>358</v>
+      </c>
+      <c r="O146" s="7">
+        <v>21.312</v>
+      </c>
+      <c r="P146" s="7">
+        <v>59.16</v>
+      </c>
+      <c r="Q146" s="7">
+        <v>60.21</v>
+      </c>
+      <c r="R146" s="7">
+        <v>7.46</v>
+      </c>
+      <c r="S146" s="7">
+        <v>0.07</v>
+      </c>
+      <c r="T146" s="7">
+        <v>0</v>
+      </c>
+      <c r="U146" s="7">
+        <v>0</v>
+      </c>
+      <c r="V146" s="7">
+        <v>0</v>
+      </c>
+      <c r="W146" s="7">
+        <v>0</v>
+      </c>
+      <c r="X146" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y146" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z146" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA146" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB146" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC146" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD146" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE146" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF146" s="7">
+        <v>255.04</v>
+      </c>
+      <c r="AG146" s="7">
+        <v>313.68</v>
+      </c>
+      <c r="AH146" s="7">
+        <v>213.63</v>
+      </c>
+      <c r="AI146" s="7">
+        <v>1542.34</v>
+      </c>
+      <c r="AJ146" s="7">
+        <v>927.76</v>
+      </c>
+      <c r="AK146" s="7">
+        <v>196.12</v>
+      </c>
+      <c r="AL146" s="7">
+        <v>10.03</v>
+      </c>
+      <c r="AM146" s="7">
+        <v>0</v>
+      </c>
+      <c r="AN146" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO146" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP146" s="7">
+        <v>10.03</v>
+      </c>
+      <c r="AQ146" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR146" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="AS146" s="7">
+        <v>40</v>
+      </c>
+      <c r="AT146" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU146" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV146" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AW146" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX146" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="147" ht="15.15" spans="1:50">
+      <c r="A147" t="s">
+        <v>142</v>
+      </c>
+      <c r="B147" t="s">
+        <v>51</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E147" s="7">
+        <v>0</v>
+      </c>
+      <c r="F147" s="7">
+        <v>4.84</v>
+      </c>
+      <c r="G147" s="7">
+        <v>-3.21</v>
+      </c>
+      <c r="H147" s="7">
+        <v>18</v>
+      </c>
+      <c r="I147" s="7">
+        <v>2</v>
+      </c>
+      <c r="J147" s="7">
+        <v>20</v>
+      </c>
+      <c r="K147" s="7">
+        <v>0.42</v>
+      </c>
+      <c r="L147" s="8">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="M147" s="7">
+        <v>2425.28</v>
+      </c>
+      <c r="N147" s="7">
+        <v>408.52</v>
+      </c>
+      <c r="O147" s="7">
+        <v>23.832</v>
+      </c>
+      <c r="P147" s="7">
+        <v>66.24</v>
+      </c>
+      <c r="Q147" s="7">
+        <v>50.53</v>
+      </c>
+      <c r="R147" s="7">
+        <v>8.51</v>
+      </c>
+      <c r="S147" s="7">
+        <v>0.13</v>
+      </c>
+      <c r="T147" s="7">
+        <v>0</v>
+      </c>
+      <c r="U147" s="7">
+        <v>0</v>
+      </c>
+      <c r="V147" s="7">
+        <v>0</v>
+      </c>
+      <c r="W147" s="7">
+        <v>0</v>
+      </c>
+      <c r="X147" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y147" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z147" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA147" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB147" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC147" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD147" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE147" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF147" s="7">
+        <v>177.96</v>
+      </c>
+      <c r="AG147" s="7">
+        <v>287.42</v>
+      </c>
+      <c r="AH147" s="7">
+        <v>521.56</v>
+      </c>
+      <c r="AI147" s="7">
+        <v>1046.67</v>
+      </c>
+      <c r="AJ147" s="7">
+        <v>691.24</v>
+      </c>
+      <c r="AK147" s="7">
+        <v>123.73</v>
+      </c>
+      <c r="AL147" s="7">
+        <v>42.09</v>
+      </c>
+      <c r="AM147" s="7">
+        <v>0</v>
+      </c>
+      <c r="AN147" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO147" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP147" s="7">
+        <v>42.09</v>
+      </c>
+      <c r="AQ147" s="7">
+        <v>2</v>
+      </c>
+      <c r="AR147" s="7">
+        <v>0.88</v>
+      </c>
+      <c r="AS147" s="7">
+        <v>29</v>
+      </c>
+      <c r="AT147" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU147" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV147" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AW147" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX147" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="148" ht="15.15" spans="1:50">
+      <c r="A148" t="s">
+        <v>142</v>
+      </c>
+      <c r="B148" t="s">
+        <v>51</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E148" s="7">
+        <v>0</v>
+      </c>
+      <c r="F148" s="7">
+        <v>3.55</v>
+      </c>
+      <c r="G148" s="7">
+        <v>-5.08</v>
+      </c>
+      <c r="H148" s="7">
+        <v>15</v>
+      </c>
+      <c r="I148" s="7">
+        <v>13</v>
+      </c>
+      <c r="J148" s="7">
+        <v>28</v>
+      </c>
+      <c r="K148" s="7">
+        <v>0.58</v>
+      </c>
+      <c r="L148" s="8">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="M148" s="7">
+        <v>3119.78</v>
+      </c>
+      <c r="N148" s="7">
+        <v>349.75</v>
+      </c>
+      <c r="O148" s="7">
+        <v>22.932</v>
+      </c>
+      <c r="P148" s="7">
+        <v>63.73</v>
+      </c>
+      <c r="Q148" s="7">
+        <v>65</v>
+      </c>
+      <c r="R148" s="7">
+        <v>7.29</v>
+      </c>
+      <c r="S148" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="T148" s="7">
+        <v>0</v>
+      </c>
+      <c r="U148" s="7">
+        <v>0</v>
+      </c>
+      <c r="V148" s="7">
+        <v>0</v>
+      </c>
+      <c r="W148" s="7">
+        <v>0</v>
+      </c>
+      <c r="X148" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y148" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z148" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA148" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB148" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC148" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD148" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE148" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF148" s="7">
+        <v>280.45</v>
+      </c>
+      <c r="AG148" s="7">
+        <v>324.39</v>
+      </c>
+      <c r="AH148" s="7">
+        <v>228.36</v>
+      </c>
+      <c r="AI148" s="7">
+        <v>1807.43</v>
+      </c>
+      <c r="AJ148" s="7">
+        <v>840.21</v>
+      </c>
+      <c r="AK148" s="7">
+        <v>207.42</v>
+      </c>
+      <c r="AL148" s="7">
+        <v>36.39</v>
+      </c>
+      <c r="AM148" s="7">
+        <v>0</v>
+      </c>
+      <c r="AN148" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO148" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP148" s="7">
+        <v>36.39</v>
+      </c>
+      <c r="AQ148" s="7">
+        <v>3</v>
+      </c>
+      <c r="AR148" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="AS148" s="7">
+        <v>18</v>
+      </c>
+      <c r="AT148" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU148" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV148" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AW148" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX148" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="149" ht="15.15" spans="1:50">
+      <c r="A149" t="s">
+        <v>142</v>
+      </c>
+      <c r="B149" t="s">
+        <v>51</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E149" s="7">
+        <v>0</v>
+      </c>
+      <c r="F149" s="7">
+        <v>4.27</v>
+      </c>
+      <c r="G149" s="7">
+        <v>-5.99</v>
+      </c>
+      <c r="H149" s="7">
+        <v>15</v>
+      </c>
+      <c r="I149" s="7">
+        <v>15</v>
+      </c>
+      <c r="J149" s="7">
+        <v>30</v>
+      </c>
+      <c r="K149" s="7">
+        <v>0.63</v>
+      </c>
+      <c r="L149" s="8">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="M149" s="7">
+        <v>3373.57</v>
+      </c>
+      <c r="N149" s="7">
+        <v>388.43</v>
+      </c>
+      <c r="O149" s="7">
+        <v>27.756</v>
+      </c>
+      <c r="P149" s="7">
+        <v>77.14</v>
+      </c>
+      <c r="Q149" s="7">
+        <v>70.28</v>
+      </c>
+      <c r="R149" s="7">
+        <v>8.09</v>
+      </c>
+      <c r="S149" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="T149" s="7">
+        <v>0</v>
+      </c>
+      <c r="U149" s="7">
+        <v>0</v>
+      </c>
+      <c r="V149" s="7">
+        <v>0</v>
+      </c>
+      <c r="W149" s="7">
+        <v>0</v>
+      </c>
+      <c r="X149" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y149" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z149" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA149" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB149" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC149" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD149" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE149" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF149" s="7">
+        <v>305.5</v>
+      </c>
+      <c r="AG149" s="7">
+        <v>400.5</v>
+      </c>
+      <c r="AH149" s="7">
+        <v>193.66</v>
+      </c>
+      <c r="AI149" s="7">
+        <v>1547.33</v>
+      </c>
+      <c r="AJ149" s="7">
+        <v>1309.66</v>
+      </c>
+      <c r="AK149" s="7">
+        <v>244.96</v>
+      </c>
+      <c r="AL149" s="7">
+        <v>69.57</v>
+      </c>
+      <c r="AM149" s="7">
+        <v>8.23</v>
+      </c>
+      <c r="AN149" s="7">
+        <v>1</v>
+      </c>
+      <c r="AO149" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="AP149" s="7">
+        <v>77.8</v>
+      </c>
+      <c r="AQ149" s="7">
+        <v>4</v>
+      </c>
+      <c r="AR149" s="7">
+        <v>1.62</v>
+      </c>
+      <c r="AS149" s="7">
+        <v>24</v>
+      </c>
+      <c r="AT149" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU149" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV149" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AW149" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX149" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="150" ht="15.15" spans="1:50">
+      <c r="A150" t="s">
+        <v>129</v>
+      </c>
+      <c r="B150" t="s">
+        <v>51</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E150" s="7">
+        <v>0</v>
+      </c>
+      <c r="F150" s="7">
+        <v>4.37</v>
+      </c>
+      <c r="G150" s="7">
+        <v>-4.95</v>
+      </c>
+      <c r="H150" s="7">
+        <v>18</v>
+      </c>
+      <c r="I150" s="7">
+        <v>17</v>
+      </c>
+      <c r="J150" s="7">
+        <v>35</v>
+      </c>
+      <c r="K150" s="7">
+        <v>0.66</v>
+      </c>
+      <c r="L150" s="8">
+        <v>0.0368055555555556</v>
+      </c>
+      <c r="M150" s="7">
+        <v>4835.05</v>
+      </c>
+      <c r="N150" s="7">
+        <v>482.65</v>
+      </c>
+      <c r="O150" s="7">
+        <v>30.672</v>
+      </c>
+      <c r="P150" s="7">
+        <v>85.2</v>
+      </c>
+      <c r="Q150" s="7">
+        <v>91.23</v>
+      </c>
+      <c r="R150" s="7">
+        <v>9.11</v>
+      </c>
+      <c r="S150" s="7">
+        <v>0.14</v>
+      </c>
+      <c r="T150" s="7">
+        <v>0</v>
+      </c>
+      <c r="U150" s="7">
+        <v>0</v>
+      </c>
+      <c r="V150" s="7">
+        <v>0</v>
+      </c>
+      <c r="W150" s="7">
+        <v>0</v>
+      </c>
+      <c r="X150" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y150" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z150" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA150" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB150" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC150" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD150" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE150" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF150" s="7">
+        <v>433.94</v>
+      </c>
+      <c r="AG150" s="7">
+        <v>646.33</v>
+      </c>
+      <c r="AH150" s="7">
+        <v>133.97</v>
+      </c>
+      <c r="AI150" s="7">
+        <v>2457.7</v>
+      </c>
+      <c r="AJ150" s="7">
+        <v>1574.12</v>
+      </c>
+      <c r="AK150" s="7">
+        <v>453.73</v>
+      </c>
+      <c r="AL150" s="7">
+        <v>116.96</v>
+      </c>
+      <c r="AM150" s="7">
+        <v>98.56</v>
+      </c>
+      <c r="AN150" s="7">
+        <v>4</v>
+      </c>
+      <c r="AO150" s="7">
+        <v>1.86</v>
+      </c>
+      <c r="AP150" s="7">
+        <v>215.52</v>
+      </c>
+      <c r="AQ150" s="7">
+        <v>12</v>
+      </c>
+      <c r="AR150" s="7">
+        <v>4.07</v>
+      </c>
+      <c r="AS150" s="7">
+        <v>43</v>
+      </c>
+      <c r="AT150" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU150" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="AV150" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AW150" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX150" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="151" ht="15.15" spans="1:50">
+      <c r="A151" t="s">
+        <v>129</v>
+      </c>
+      <c r="B151" t="s">
+        <v>51</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E151" s="7">
+        <v>0</v>
+      </c>
+      <c r="F151" s="7">
+        <v>4.12</v>
+      </c>
+      <c r="G151" s="7">
+        <v>-5.73</v>
+      </c>
+      <c r="H151" s="7">
+        <v>15</v>
+      </c>
+      <c r="I151" s="7">
+        <v>12</v>
+      </c>
+      <c r="J151" s="7">
+        <v>27</v>
+      </c>
+      <c r="K151" s="7">
+        <v>0.51</v>
+      </c>
+      <c r="L151" s="8">
+        <v>0.0368055555555556</v>
+      </c>
+      <c r="M151" s="7">
+        <v>4489.21</v>
+      </c>
+      <c r="N151" s="7">
+        <v>448.39</v>
+      </c>
+      <c r="O151" s="7">
+        <v>29.34</v>
+      </c>
+      <c r="P151" s="7">
+        <v>81.48</v>
+      </c>
+      <c r="Q151" s="7">
+        <v>84.7</v>
+      </c>
+      <c r="R151" s="7">
+        <v>8.46</v>
+      </c>
+      <c r="S151" s="7">
+        <v>0.12</v>
+      </c>
+      <c r="T151" s="7">
+        <v>0</v>
+      </c>
+      <c r="U151" s="7">
+        <v>0</v>
+      </c>
+      <c r="V151" s="7">
+        <v>0</v>
+      </c>
+      <c r="W151" s="7">
+        <v>0</v>
+      </c>
+      <c r="X151" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE151" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF151" s="7">
+        <v>397.24</v>
+      </c>
+      <c r="AG151" s="7">
+        <v>540.26</v>
+      </c>
+      <c r="AH151" s="7">
+        <v>116.85</v>
+      </c>
+      <c r="AI151" s="7">
+        <v>2347.31</v>
+      </c>
+      <c r="AJ151" s="7">
+        <v>1364.84</v>
+      </c>
+      <c r="AK151" s="7">
+        <v>443.33</v>
+      </c>
+      <c r="AL151" s="7">
+        <v>138.67</v>
+      </c>
+      <c r="AM151" s="7">
+        <v>78.2</v>
+      </c>
+      <c r="AN151" s="7">
+        <v>4</v>
+      </c>
+      <c r="AO151" s="7">
+        <v>1.48</v>
+      </c>
+      <c r="AP151" s="7">
+        <v>216.87</v>
+      </c>
+      <c r="AQ151" s="7">
+        <v>12</v>
+      </c>
+      <c r="AR151" s="7">
+        <v>4.09</v>
+      </c>
+      <c r="AS151" s="7">
+        <v>90</v>
+      </c>
+      <c r="AT151" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU151" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="AV151" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AW151" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX151" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="152" ht="15.15" spans="1:50">
+      <c r="A152" t="s">
+        <v>129</v>
+      </c>
+      <c r="B152" t="s">
+        <v>51</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E152" s="7">
+        <v>0</v>
+      </c>
+      <c r="F152" s="7">
+        <v>4.21</v>
+      </c>
+      <c r="G152" s="7">
+        <v>-6.67</v>
+      </c>
+      <c r="H152" s="7">
+        <v>14</v>
+      </c>
+      <c r="I152" s="7">
+        <v>25</v>
+      </c>
+      <c r="J152" s="7">
+        <v>39</v>
+      </c>
+      <c r="K152" s="7">
+        <v>0.74</v>
+      </c>
+      <c r="L152" s="8">
+        <v>0.0368055555555556</v>
+      </c>
+      <c r="M152" s="7">
+        <v>5138.13</v>
+      </c>
+      <c r="N152" s="7">
+        <v>495.28</v>
+      </c>
+      <c r="O152" s="7">
+        <v>31.212</v>
+      </c>
+      <c r="P152" s="7">
+        <v>86.68</v>
+      </c>
+      <c r="Q152" s="7">
+        <v>96.95</v>
+      </c>
+      <c r="R152" s="7">
+        <v>9.35</v>
+      </c>
+      <c r="S152" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="T152" s="7">
+        <v>0</v>
+      </c>
+      <c r="U152" s="7">
+        <v>0</v>
+      </c>
+      <c r="V152" s="7">
+        <v>0</v>
+      </c>
+      <c r="W152" s="7">
+        <v>0</v>
+      </c>
+      <c r="X152" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y152" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z152" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA152" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB152" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC152" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD152" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE152" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF152" s="7">
+        <v>378.25</v>
+      </c>
+      <c r="AG152" s="7">
+        <v>875.2</v>
+      </c>
+      <c r="AH152" s="7">
+        <v>119.12</v>
+      </c>
+      <c r="AI152" s="7">
+        <v>1985.48</v>
+      </c>
+      <c r="AJ152" s="7">
+        <v>1985.89</v>
+      </c>
+      <c r="AK152" s="7">
+        <v>731.73</v>
+      </c>
+      <c r="AL152" s="7">
+        <v>173.14</v>
+      </c>
+      <c r="AM152" s="7">
+        <v>142.78</v>
+      </c>
+      <c r="AN152" s="7">
+        <v>7</v>
+      </c>
+      <c r="AO152" s="7">
+        <v>2.69</v>
+      </c>
+      <c r="AP152" s="7">
+        <v>315.92</v>
+      </c>
+      <c r="AQ152" s="7">
+        <v>17</v>
+      </c>
+      <c r="AR152" s="7">
+        <v>5.96</v>
+      </c>
+      <c r="AS152" s="7">
+        <v>16</v>
+      </c>
+      <c r="AT152" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU152" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="AV152" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AW152" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX152" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="153" ht="15.15" spans="1:50">
+      <c r="A153" t="s">
+        <v>129</v>
+      </c>
+      <c r="B153" t="s">
+        <v>51</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E153" s="7">
+        <v>0</v>
+      </c>
+      <c r="F153" s="7">
+        <v>3.93</v>
+      </c>
+      <c r="G153" s="7">
+        <v>-4.76</v>
+      </c>
+      <c r="H153" s="7">
+        <v>14</v>
+      </c>
+      <c r="I153" s="7">
+        <v>17</v>
+      </c>
+      <c r="J153" s="7">
+        <v>31</v>
+      </c>
+      <c r="K153" s="7">
+        <v>0.58</v>
+      </c>
+      <c r="L153" s="8">
+        <v>0.0368055555555556</v>
+      </c>
+      <c r="M153" s="7">
+        <v>4723.01</v>
+      </c>
+      <c r="N153" s="7">
+        <v>429.99</v>
+      </c>
+      <c r="O153" s="7">
+        <v>27.936</v>
+      </c>
+      <c r="P153" s="7">
+        <v>77.56</v>
+      </c>
+      <c r="Q153" s="7">
+        <v>89.11</v>
+      </c>
+      <c r="R153" s="7">
+        <v>8.11</v>
+      </c>
+      <c r="S153" s="7">
+        <v>0.13</v>
+      </c>
+      <c r="T153" s="7">
+        <v>0</v>
+      </c>
+      <c r="U153" s="7">
+        <v>0</v>
+      </c>
+      <c r="V153" s="7">
+        <v>0</v>
+      </c>
+      <c r="W153" s="7">
+        <v>0</v>
+      </c>
+      <c r="X153" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y153" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z153" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA153" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB153" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC153" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD153" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE153" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF153" s="7">
+        <v>1118.3</v>
+      </c>
+      <c r="AG153" s="7">
+        <v>629.29</v>
+      </c>
+      <c r="AH153" s="7">
+        <v>126.3</v>
+      </c>
+      <c r="AI153" s="7">
+        <v>2574.31</v>
+      </c>
+      <c r="AJ153" s="7">
+        <v>1295.46</v>
+      </c>
+      <c r="AK153" s="7">
+        <v>522.11</v>
+      </c>
+      <c r="AL153" s="7">
+        <v>153.61</v>
+      </c>
+      <c r="AM153" s="7">
+        <v>51.1</v>
+      </c>
+      <c r="AN153" s="7">
+        <v>3</v>
+      </c>
+      <c r="AO153" s="7">
+        <v>0.96</v>
+      </c>
+      <c r="AP153" s="7">
+        <v>204.71</v>
+      </c>
+      <c r="AQ153" s="7">
+        <v>11</v>
+      </c>
+      <c r="AR153" s="7">
+        <v>3.86</v>
+      </c>
+      <c r="AS153" s="7">
+        <v>28</v>
+      </c>
+      <c r="AT153" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU153" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="AV153" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AW153" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX153" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="154" ht="15.15" spans="1:50">
+      <c r="A154" t="s">
+        <v>129</v>
+      </c>
+      <c r="B154" t="s">
+        <v>51</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E154" s="7">
+        <v>0</v>
+      </c>
+      <c r="F154" s="7">
+        <v>5.13</v>
+      </c>
+      <c r="G154" s="7">
+        <v>-5.73</v>
+      </c>
+      <c r="H154" s="7">
+        <v>18</v>
+      </c>
+      <c r="I154" s="7">
+        <v>7</v>
+      </c>
+      <c r="J154" s="7">
+        <v>25</v>
+      </c>
+      <c r="K154" s="7">
+        <v>0.47</v>
+      </c>
+      <c r="L154" s="8">
+        <v>0.0368055555555556</v>
+      </c>
+      <c r="M154" s="7">
+        <v>4133.12</v>
+      </c>
+      <c r="N154" s="7">
+        <v>473.01</v>
+      </c>
+      <c r="O154" s="7">
+        <v>28.908</v>
+      </c>
+      <c r="P154" s="7">
+        <v>80.35</v>
+      </c>
+      <c r="Q154" s="7">
+        <v>77.98</v>
+      </c>
+      <c r="R154" s="7">
+        <v>8.92</v>
+      </c>
+      <c r="S154" s="7">
+        <v>0.14</v>
+      </c>
+      <c r="T154" s="7">
+        <v>0</v>
+      </c>
+      <c r="U154" s="7">
+        <v>0</v>
+      </c>
+      <c r="V154" s="7">
+        <v>0</v>
+      </c>
+      <c r="W154" s="7">
+        <v>0</v>
+      </c>
+      <c r="X154" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y154" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z154" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA154" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB154" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC154" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD154" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE154" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF154" s="7">
+        <v>344.24</v>
+      </c>
+      <c r="AG154" s="7">
+        <v>635.95</v>
+      </c>
+      <c r="AH154" s="7">
+        <v>373.1</v>
+      </c>
+      <c r="AI154" s="7">
+        <v>1955.01</v>
+      </c>
+      <c r="AJ154" s="7">
+        <v>1199.11</v>
+      </c>
+      <c r="AK154" s="7">
+        <v>405.76</v>
+      </c>
+      <c r="AL154" s="7">
+        <v>160.12</v>
+      </c>
+      <c r="AM154" s="7">
+        <v>40.01</v>
+      </c>
+      <c r="AN154" s="7">
+        <v>2</v>
+      </c>
+      <c r="AO154" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="AP154" s="7">
+        <v>200.13</v>
+      </c>
+      <c r="AQ154" s="7">
+        <v>10</v>
+      </c>
+      <c r="AR154" s="7">
+        <v>3.78</v>
+      </c>
+      <c r="AS154" s="7">
+        <v>82</v>
+      </c>
+      <c r="AT154" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU154" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="AV154" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AW154" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX154" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="155" ht="15.15" spans="1:50">
+      <c r="A155" t="s">
+        <v>129</v>
+      </c>
+      <c r="B155" t="s">
+        <v>51</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E155" s="7">
+        <v>0</v>
+      </c>
+      <c r="F155" s="7">
+        <v>3.84</v>
+      </c>
+      <c r="G155" s="7">
+        <v>-4.24</v>
+      </c>
+      <c r="H155" s="7">
+        <v>8</v>
+      </c>
+      <c r="I155" s="7">
+        <v>6</v>
+      </c>
+      <c r="J155" s="7">
+        <v>14</v>
+      </c>
+      <c r="K155" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="L155" s="8">
+        <v>0.0368055555555556</v>
+      </c>
+      <c r="M155" s="7">
+        <v>2318.42</v>
+      </c>
+      <c r="N155" s="7">
+        <v>266.53</v>
+      </c>
+      <c r="O155" s="7">
+        <v>27.324</v>
+      </c>
+      <c r="P155" s="7">
+        <v>75.85</v>
+      </c>
+      <c r="Q155" s="7">
+        <v>43.74</v>
+      </c>
+      <c r="R155" s="7">
+        <v>5.03</v>
+      </c>
+      <c r="S155" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="T155" s="7">
+        <v>0</v>
+      </c>
+      <c r="U155" s="7">
+        <v>0</v>
+      </c>
+      <c r="V155" s="7">
+        <v>0</v>
+      </c>
+      <c r="W155" s="7">
+        <v>0</v>
+      </c>
+      <c r="X155" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y155" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z155" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA155" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB155" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC155" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD155" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE155" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF155" s="7">
+        <v>201.08</v>
+      </c>
+      <c r="AG155" s="7">
+        <v>203.72</v>
+      </c>
+      <c r="AH155" s="7">
+        <v>241.33</v>
+      </c>
+      <c r="AI155" s="7">
+        <v>1519.31</v>
+      </c>
+      <c r="AJ155" s="7">
+        <v>382.73</v>
+      </c>
+      <c r="AK155" s="7">
+        <v>73.64</v>
+      </c>
+      <c r="AL155" s="7">
+        <v>65.75</v>
+      </c>
+      <c r="AM155" s="7">
+        <v>35.65</v>
+      </c>
+      <c r="AN155" s="7">
+        <v>3</v>
+      </c>
+      <c r="AO155" s="7">
+        <v>0.67</v>
+      </c>
+      <c r="AP155" s="7">
+        <v>101.4</v>
+      </c>
+      <c r="AQ155" s="7">
+        <v>7</v>
+      </c>
+      <c r="AR155" s="7">
+        <v>1.91</v>
+      </c>
+      <c r="AS155" s="7">
+        <v>23</v>
+      </c>
+      <c r="AT155" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU155" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="AV155" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AW155" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX155" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="156" ht="15.15" spans="1:50">
+      <c r="A156" t="s">
+        <v>129</v>
+      </c>
+      <c r="B156" t="s">
+        <v>51</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E156" s="7">
+        <v>0</v>
+      </c>
+      <c r="F156" s="7">
+        <v>3.7</v>
+      </c>
+      <c r="G156" s="7">
+        <v>-4.32</v>
+      </c>
+      <c r="H156" s="7">
+        <v>13</v>
+      </c>
+      <c r="I156" s="7">
+        <v>9</v>
+      </c>
+      <c r="J156" s="7">
+        <v>22</v>
+      </c>
+      <c r="K156" s="7">
+        <v>0.42</v>
+      </c>
+      <c r="L156" s="8">
+        <v>0.0368055555555556</v>
+      </c>
+      <c r="M156" s="7">
+        <v>4645.84</v>
+      </c>
+      <c r="N156" s="7">
+        <v>472.03</v>
+      </c>
+      <c r="O156" s="7">
+        <v>29.196</v>
+      </c>
+      <c r="P156" s="7">
+        <v>81.13</v>
+      </c>
+      <c r="Q156" s="7">
+        <v>87.66</v>
+      </c>
+      <c r="R156" s="7">
+        <v>8.91</v>
+      </c>
+      <c r="S156" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="T156" s="7">
+        <v>194</v>
+      </c>
+      <c r="U156" s="7">
+        <v>144.28</v>
+      </c>
+      <c r="V156" s="7">
+        <v>97</v>
+      </c>
+      <c r="W156" s="7">
+        <v>72.14</v>
+      </c>
+      <c r="X156" s="7">
+        <v>82.12</v>
+      </c>
+      <c r="Y156" s="7">
+        <v>2.25</v>
+      </c>
+      <c r="Z156" s="8">
+        <v>0.00570601851851852</v>
+      </c>
+      <c r="AA156" s="8">
+        <v>0.0037962962962963</v>
+      </c>
+      <c r="AB156" s="8">
+        <v>0.0109490740740741</v>
+      </c>
+      <c r="AC156" s="8">
+        <v>0.0105902777777778</v>
+      </c>
+      <c r="AD156" s="8">
+        <v>0.00155092592592593</v>
+      </c>
+      <c r="AE156" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF156" s="7">
+        <v>414</v>
+      </c>
+      <c r="AG156" s="7">
+        <v>598.29</v>
+      </c>
+      <c r="AH156" s="7">
+        <v>129.01</v>
+      </c>
+      <c r="AI156" s="7">
+        <v>2186.15</v>
+      </c>
+      <c r="AJ156" s="7">
+        <v>1688.8</v>
+      </c>
+      <c r="AK156" s="7">
+        <v>449.19</v>
+      </c>
+      <c r="AL156" s="7">
+        <v>117.56</v>
+      </c>
+      <c r="AM156" s="7">
+        <v>75.14</v>
+      </c>
+      <c r="AN156" s="7">
+        <v>4</v>
+      </c>
+      <c r="AO156" s="7">
+        <v>1.42</v>
+      </c>
+      <c r="AP156" s="7">
+        <v>192.7</v>
+      </c>
+      <c r="AQ156" s="7">
+        <v>10</v>
+      </c>
+      <c r="AR156" s="7">
+        <v>3.64</v>
+      </c>
+      <c r="AS156" s="7">
+        <v>27</v>
+      </c>
+      <c r="AT156" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU156" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="AV156" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AW156" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX156" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="157" ht="15.15" spans="1:50">
+      <c r="A157" t="s">
+        <v>146</v>
+      </c>
+      <c r="B157" t="s">
+        <v>51</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E157" s="7">
+        <v>0</v>
+      </c>
+      <c r="F157" s="7">
+        <v>3.45</v>
+      </c>
+      <c r="G157" s="7">
+        <v>-4.24</v>
+      </c>
+      <c r="H157" s="7">
+        <v>4</v>
+      </c>
+      <c r="I157" s="7">
+        <v>11</v>
+      </c>
+      <c r="J157" s="7">
+        <v>15</v>
+      </c>
+      <c r="K157" s="7">
+        <v>0.38</v>
+      </c>
+      <c r="L157" s="8">
+        <v>0.0277777777777778</v>
+      </c>
+      <c r="M157" s="7">
+        <v>4798.21</v>
+      </c>
+      <c r="N157" s="7">
+        <v>442.96</v>
+      </c>
+      <c r="O157" s="7">
+        <v>25.488</v>
+      </c>
+      <c r="P157" s="7">
+        <v>70.83</v>
+      </c>
+      <c r="Q157" s="7">
+        <v>119.96</v>
+      </c>
+      <c r="R157" s="7">
+        <v>11.07</v>
+      </c>
+      <c r="S157" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="T157" s="7">
+        <v>0</v>
+      </c>
+      <c r="U157" s="7">
+        <v>0</v>
+      </c>
+      <c r="V157" s="7">
+        <v>0</v>
+      </c>
+      <c r="W157" s="7">
+        <v>0</v>
+      </c>
+      <c r="X157" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE157" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF157" s="7">
+        <v>418.48</v>
+      </c>
+      <c r="AG157" s="7">
+        <v>644.12</v>
+      </c>
+      <c r="AH157" s="7">
+        <v>72.8</v>
+      </c>
+      <c r="AI157" s="7">
+        <v>1724.79</v>
+      </c>
+      <c r="AJ157" s="7">
+        <v>2026.42</v>
+      </c>
+      <c r="AK157" s="7">
+        <v>792.17</v>
+      </c>
+      <c r="AL157" s="7">
+        <v>176.49</v>
+      </c>
+      <c r="AM157" s="7">
+        <v>5.58</v>
+      </c>
+      <c r="AN157" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="7">
+        <v>0.14</v>
+      </c>
+      <c r="AP157" s="7">
+        <v>182.07</v>
+      </c>
+      <c r="AQ157" s="7">
+        <v>10</v>
+      </c>
+      <c r="AR157" s="7">
+        <v>4.55</v>
+      </c>
+      <c r="AS157" s="7">
+        <v>13</v>
+      </c>
+      <c r="AT157" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU157" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV157" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW157" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX157" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="158" ht="15.15" spans="1:50">
+      <c r="A158" t="s">
+        <v>146</v>
+      </c>
+      <c r="B158" t="s">
+        <v>51</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E158" s="7">
+        <v>0</v>
+      </c>
+      <c r="F158" s="7">
+        <v>3.95</v>
+      </c>
+      <c r="G158" s="7">
+        <v>-4.35</v>
+      </c>
+      <c r="H158" s="7">
+        <v>10</v>
+      </c>
+      <c r="I158" s="7">
+        <v>6</v>
+      </c>
+      <c r="J158" s="7">
+        <v>16</v>
+      </c>
+      <c r="K158" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="L158" s="8">
+        <v>0.0277777777777778</v>
+      </c>
+      <c r="M158" s="7">
+        <v>4497.44</v>
+      </c>
+      <c r="N158" s="7">
+        <v>453.2</v>
+      </c>
+      <c r="O158" s="7">
+        <v>26.64</v>
+      </c>
+      <c r="P158" s="7">
+        <v>74.02</v>
+      </c>
+      <c r="Q158" s="7">
+        <v>112.44</v>
+      </c>
+      <c r="R158" s="7">
+        <v>11.33</v>
+      </c>
+      <c r="S158" s="7">
+        <v>0.28</v>
+      </c>
+      <c r="T158" s="7">
+        <v>0</v>
+      </c>
+      <c r="U158" s="7">
+        <v>0</v>
+      </c>
+      <c r="V158" s="7">
+        <v>0</v>
+      </c>
+      <c r="W158" s="7">
+        <v>0</v>
+      </c>
+      <c r="X158" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE158" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF158" s="7">
+        <v>391.98</v>
+      </c>
+      <c r="AG158" s="7">
+        <v>544.95</v>
+      </c>
+      <c r="AH158" s="7">
+        <v>57.84</v>
+      </c>
+      <c r="AI158" s="7">
+        <v>1769.82</v>
+      </c>
+      <c r="AJ158" s="7">
+        <v>1972.1</v>
+      </c>
+      <c r="AK158" s="7">
+        <v>530.27</v>
+      </c>
+      <c r="AL158" s="7">
+        <v>159.78</v>
+      </c>
+      <c r="AM158" s="7">
+        <v>7.63</v>
+      </c>
+      <c r="AN158" s="7">
+        <v>1</v>
+      </c>
+      <c r="AO158" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="AP158" s="7">
+        <v>167.41</v>
+      </c>
+      <c r="AQ158" s="7">
+        <v>12</v>
+      </c>
+      <c r="AR158" s="7">
+        <v>4.19</v>
+      </c>
+      <c r="AS158" s="7">
+        <v>36</v>
+      </c>
+      <c r="AT158" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU158" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV158" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW158" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX158" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="159" ht="15.15" spans="1:50">
+      <c r="A159" t="s">
+        <v>146</v>
+      </c>
+      <c r="B159" t="s">
+        <v>51</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E159" s="7">
+        <v>0</v>
+      </c>
+      <c r="F159" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="G159" s="7">
+        <v>-4.15</v>
+      </c>
+      <c r="H159" s="7">
+        <v>10</v>
+      </c>
+      <c r="I159" s="7">
+        <v>12</v>
+      </c>
+      <c r="J159" s="7">
+        <v>22</v>
+      </c>
+      <c r="K159" s="7">
+        <v>0.55</v>
+      </c>
+      <c r="L159" s="8">
+        <v>0.0277777777777778</v>
+      </c>
+      <c r="M159" s="7">
+        <v>4713.64</v>
+      </c>
+      <c r="N159" s="7">
+        <v>538.07</v>
+      </c>
+      <c r="O159" s="7">
+        <v>30.348</v>
+      </c>
+      <c r="P159" s="7">
+        <v>84.29</v>
+      </c>
+      <c r="Q159" s="7">
+        <v>117.84</v>
+      </c>
+      <c r="R159" s="7">
+        <v>13.45</v>
+      </c>
+      <c r="S159" s="7">
+        <v>0.31</v>
+      </c>
+      <c r="T159" s="7">
+        <v>0</v>
+      </c>
+      <c r="U159" s="7">
+        <v>0</v>
+      </c>
+      <c r="V159" s="7">
+        <v>0</v>
+      </c>
+      <c r="W159" s="7">
+        <v>0</v>
+      </c>
+      <c r="X159" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y159" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z159" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA159" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB159" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC159" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD159" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE159" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF159" s="7">
+        <v>410.25</v>
+      </c>
+      <c r="AG159" s="7">
+        <v>635.01</v>
+      </c>
+      <c r="AH159" s="7">
+        <v>50.26</v>
+      </c>
+      <c r="AI159" s="7">
+        <v>1608</v>
+      </c>
+      <c r="AJ159" s="7">
+        <v>2122.58</v>
+      </c>
+      <c r="AK159" s="7">
+        <v>674.73</v>
+      </c>
+      <c r="AL159" s="7">
+        <v>185.11</v>
+      </c>
+      <c r="AM159" s="7">
+        <v>72.97</v>
+      </c>
+      <c r="AN159" s="7">
+        <v>3</v>
+      </c>
+      <c r="AO159" s="7">
+        <v>1.82</v>
+      </c>
+      <c r="AP159" s="7">
+        <v>258.08</v>
+      </c>
+      <c r="AQ159" s="7">
+        <v>13</v>
+      </c>
+      <c r="AR159" s="7">
+        <v>6.45</v>
+      </c>
+      <c r="AS159" s="7">
+        <v>124</v>
+      </c>
+      <c r="AT159" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU159" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV159" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW159" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX159" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="160" ht="15.15" spans="1:50">
+      <c r="A160" t="s">
+        <v>146</v>
+      </c>
+      <c r="B160" t="s">
+        <v>51</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E160" s="7">
+        <v>0</v>
+      </c>
+      <c r="F160" s="7">
+        <v>2.65</v>
+      </c>
+      <c r="G160" s="7">
+        <v>-4.19</v>
+      </c>
+      <c r="H160" s="7">
+        <v>0</v>
+      </c>
+      <c r="I160" s="7">
+        <v>1</v>
+      </c>
+      <c r="J160" s="7">
+        <v>1</v>
+      </c>
+      <c r="K160" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="L160" s="8">
+        <v>0.0277777777777778</v>
+      </c>
+      <c r="M160" s="7">
+        <v>499.78</v>
+      </c>
+      <c r="N160" s="7">
+        <v>51.49</v>
+      </c>
+      <c r="O160" s="7">
+        <v>24.732</v>
+      </c>
+      <c r="P160" s="7">
+        <v>68.65</v>
+      </c>
+      <c r="Q160" s="7">
+        <v>12.49</v>
+      </c>
+      <c r="R160" s="7">
+        <v>1.29</v>
+      </c>
+      <c r="S160" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="T160" s="7">
+        <v>0</v>
+      </c>
+      <c r="U160" s="7">
+        <v>0</v>
+      </c>
+      <c r="V160" s="7">
+        <v>0</v>
+      </c>
+      <c r="W160" s="7">
+        <v>0</v>
+      </c>
+      <c r="X160" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y160" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z160" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA160" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB160" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC160" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD160" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE160" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF160" s="7">
+        <v>26.37</v>
+      </c>
+      <c r="AG160" s="7">
+        <v>34.77</v>
+      </c>
+      <c r="AH160" s="7">
+        <v>184.37</v>
+      </c>
+      <c r="AI160" s="7">
+        <v>241.76</v>
+      </c>
+      <c r="AJ160" s="7">
+        <v>13.81</v>
+      </c>
+      <c r="AK160" s="7">
+        <v>41.85</v>
+      </c>
+      <c r="AL160" s="7">
+        <v>18.09</v>
+      </c>
+      <c r="AM160" s="7">
+        <v>0</v>
+      </c>
+      <c r="AN160" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO160" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP160" s="7">
+        <v>18.09</v>
+      </c>
+      <c r="AQ160" s="7">
+        <v>1</v>
+      </c>
+      <c r="AR160" s="7">
+        <v>0.45</v>
+      </c>
+      <c r="AS160" s="7">
+        <v>1</v>
+      </c>
+      <c r="AT160" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU160" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV160" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW160" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX160" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="161" ht="15.15" spans="1:50">
+      <c r="A161" t="s">
+        <v>146</v>
+      </c>
+      <c r="B161" t="s">
+        <v>51</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E161" s="7">
+        <v>0</v>
+      </c>
+      <c r="F161" s="7">
+        <v>3.7</v>
+      </c>
+      <c r="G161" s="7">
+        <v>-4.14</v>
+      </c>
+      <c r="H161" s="7">
+        <v>4</v>
+      </c>
+      <c r="I161" s="7">
+        <v>6</v>
+      </c>
+      <c r="J161" s="7">
+        <v>10</v>
+      </c>
+      <c r="K161" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="L161" s="8">
+        <v>0.0277777777777778</v>
+      </c>
+      <c r="M161" s="7">
+        <v>2697.52</v>
+      </c>
+      <c r="N161" s="7">
+        <v>249.27</v>
+      </c>
+      <c r="O161" s="7">
+        <v>26.64</v>
+      </c>
+      <c r="P161" s="7">
+        <v>74.02</v>
+      </c>
+      <c r="Q161" s="7">
+        <v>67.44</v>
+      </c>
+      <c r="R161" s="7">
+        <v>6.23</v>
+      </c>
+      <c r="S161" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="T161" s="7">
+        <v>0</v>
+      </c>
+      <c r="U161" s="7">
+        <v>0</v>
+      </c>
+      <c r="V161" s="7">
+        <v>0</v>
+      </c>
+      <c r="W161" s="7">
+        <v>0</v>
+      </c>
+      <c r="X161" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y161" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z161" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA161" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB161" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC161" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD161" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE161" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF161" s="7">
+        <v>620.71</v>
+      </c>
+      <c r="AG161" s="7">
+        <v>261.48</v>
+      </c>
+      <c r="AH161" s="7">
+        <v>68.26</v>
+      </c>
+      <c r="AI161" s="7">
+        <v>1314.72</v>
+      </c>
+      <c r="AJ161" s="7">
+        <v>1011.72</v>
+      </c>
+      <c r="AK161" s="7">
+        <v>250.59</v>
+      </c>
+      <c r="AL161" s="7">
+        <v>38.07</v>
+      </c>
+      <c r="AM161" s="7">
+        <v>13.57</v>
+      </c>
+      <c r="AN161" s="7">
+        <v>1</v>
+      </c>
+      <c r="AO161" s="7">
+        <v>0.34</v>
+      </c>
+      <c r="AP161" s="7">
+        <v>51.64</v>
+      </c>
+      <c r="AQ161" s="7">
+        <v>2</v>
+      </c>
+      <c r="AR161" s="7">
+        <v>1.29</v>
+      </c>
+      <c r="AS161" s="7">
+        <v>17</v>
+      </c>
+      <c r="AT161" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU161" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV161" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW161" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX161" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="162" ht="15.15" spans="1:50">
+      <c r="A162" t="s">
+        <v>146</v>
+      </c>
+      <c r="B162" t="s">
+        <v>51</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E162" s="7">
+        <v>0</v>
+      </c>
+      <c r="F162" s="7">
+        <v>4.93</v>
+      </c>
+      <c r="G162" s="7">
+        <v>-3.81</v>
+      </c>
+      <c r="H162" s="7">
+        <v>16</v>
+      </c>
+      <c r="I162" s="7">
+        <v>5</v>
+      </c>
+      <c r="J162" s="7">
+        <v>21</v>
+      </c>
+      <c r="K162" s="7">
+        <v>0.53</v>
+      </c>
+      <c r="L162" s="8">
+        <v>0.0277777777777778</v>
+      </c>
+      <c r="M162" s="7">
+        <v>3850.52</v>
+      </c>
+      <c r="N162" s="7">
+        <v>486.3</v>
+      </c>
+      <c r="O162" s="7">
+        <v>26.676</v>
+      </c>
+      <c r="P162" s="7">
+        <v>74.08</v>
+      </c>
+      <c r="Q162" s="7">
+        <v>96.26</v>
+      </c>
+      <c r="R162" s="7">
+        <v>12.16</v>
+      </c>
+      <c r="S162" s="7">
+        <v>0.29</v>
+      </c>
+      <c r="T162" s="7">
+        <v>0</v>
+      </c>
+      <c r="U162" s="7">
+        <v>0</v>
+      </c>
+      <c r="V162" s="7">
+        <v>0</v>
+      </c>
+      <c r="W162" s="7">
+        <v>0</v>
+      </c>
+      <c r="X162" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y162" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z162" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB162" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC162" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD162" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE162" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF162" s="7">
+        <v>327.78</v>
+      </c>
+      <c r="AG162" s="7">
+        <v>625.56</v>
+      </c>
+      <c r="AH162" s="7">
+        <v>242.37</v>
+      </c>
+      <c r="AI162" s="7">
+        <v>1562.03</v>
+      </c>
+      <c r="AJ162" s="7">
+        <v>1444.99</v>
+      </c>
+      <c r="AK162" s="7">
+        <v>425.67</v>
+      </c>
+      <c r="AL162" s="7">
+        <v>155.7</v>
+      </c>
+      <c r="AM162" s="7">
+        <v>19.77</v>
+      </c>
+      <c r="AN162" s="7">
+        <v>2</v>
+      </c>
+      <c r="AO162" s="7">
+        <v>0.49</v>
+      </c>
+      <c r="AP162" s="7">
+        <v>175.47</v>
+      </c>
+      <c r="AQ162" s="7">
+        <v>12</v>
+      </c>
+      <c r="AR162" s="7">
+        <v>4.39</v>
+      </c>
+      <c r="AS162" s="7">
+        <v>27</v>
+      </c>
+      <c r="AT162" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU162" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV162" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW162" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX162" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="163" ht="15.15" spans="1:50">
+      <c r="A163" t="s">
+        <v>146</v>
+      </c>
+      <c r="B163" t="s">
+        <v>51</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E163" s="7">
+        <v>0</v>
+      </c>
+      <c r="F163" s="7">
+        <v>4.33</v>
+      </c>
+      <c r="G163" s="7">
+        <v>-1.82</v>
+      </c>
+      <c r="H163" s="7">
+        <v>1</v>
+      </c>
+      <c r="I163" s="7">
+        <v>0</v>
+      </c>
+      <c r="J163" s="7">
+        <v>1</v>
+      </c>
+      <c r="K163" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="L163" s="8">
+        <v>0.0277777777777778</v>
+      </c>
+      <c r="M163" s="7">
+        <v>454.01</v>
+      </c>
+      <c r="N163" s="7">
+        <v>30.81</v>
+      </c>
+      <c r="O163" s="7">
+        <v>22.32</v>
+      </c>
+      <c r="P163" s="7">
+        <v>61.96</v>
+      </c>
+      <c r="Q163" s="7">
+        <v>11.35</v>
+      </c>
+      <c r="R163" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="S163" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="T163" s="7">
+        <v>0</v>
+      </c>
+      <c r="U163" s="7">
+        <v>0</v>
+      </c>
+      <c r="V163" s="7">
+        <v>0</v>
+      </c>
+      <c r="W163" s="7">
+        <v>0</v>
+      </c>
+      <c r="X163" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y163" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z163" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA163" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB163" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC163" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD163" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE163" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF163" s="7">
+        <v>34.51</v>
+      </c>
+      <c r="AG163" s="7">
+        <v>26.99</v>
+      </c>
+      <c r="AH163" s="7">
+        <v>26.7</v>
+      </c>
+      <c r="AI163" s="7">
+        <v>352.64</v>
+      </c>
+      <c r="AJ163" s="7">
+        <v>18.68</v>
+      </c>
+      <c r="AK163" s="7">
+        <v>35.08</v>
+      </c>
+      <c r="AL163" s="7">
+        <v>21</v>
+      </c>
+      <c r="AM163" s="7">
+        <v>0</v>
+      </c>
+      <c r="AN163" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO163" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP163" s="7">
+        <v>21</v>
+      </c>
+      <c r="AQ163" s="7">
+        <v>1</v>
+      </c>
+      <c r="AR163" s="7">
+        <v>0.53</v>
+      </c>
+      <c r="AS163" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT163" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU163" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV163" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW163" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX163" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="164" ht="15.15" spans="1:50">
+      <c r="A164" t="s">
+        <v>146</v>
+      </c>
+      <c r="B164" t="s">
+        <v>51</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E164" s="7">
+        <v>0</v>
+      </c>
+      <c r="F164" s="7">
+        <v>3.46</v>
+      </c>
+      <c r="G164" s="7">
+        <v>-4.97</v>
+      </c>
+      <c r="H164" s="7">
+        <v>11</v>
+      </c>
+      <c r="I164" s="7">
+        <v>10</v>
+      </c>
+      <c r="J164" s="7">
+        <v>21</v>
+      </c>
+      <c r="K164" s="7">
+        <v>0.53</v>
+      </c>
+      <c r="L164" s="8">
+        <v>0.0277777777777778</v>
+      </c>
+      <c r="M164" s="7">
+        <v>4415.67</v>
+      </c>
+      <c r="N164" s="7">
+        <v>450.2</v>
+      </c>
+      <c r="O164" s="7">
+        <v>28.332</v>
+      </c>
+      <c r="P164" s="7">
+        <v>78.73</v>
+      </c>
+      <c r="Q164" s="7">
+        <v>110.39</v>
+      </c>
+      <c r="R164" s="7">
+        <v>11.25</v>
+      </c>
+      <c r="S164" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="T164" s="7">
+        <v>131</v>
+      </c>
+      <c r="U164" s="7">
+        <v>84.27</v>
+      </c>
+      <c r="V164" s="7">
+        <v>65.5</v>
+      </c>
+      <c r="W164" s="7">
+        <v>42.13</v>
+      </c>
+      <c r="X164" s="7">
+        <v>17.49</v>
+      </c>
+      <c r="Y164" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z164" s="8">
+        <v>0.00831018518518518</v>
+      </c>
+      <c r="AA164" s="8">
+        <v>0.00319444444444444</v>
+      </c>
+      <c r="AB164" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC164" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD164" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE164" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF164" s="7">
+        <v>388.57</v>
+      </c>
+      <c r="AG164" s="7">
+        <v>723.22</v>
+      </c>
+      <c r="AH164" s="7">
+        <v>107.8</v>
+      </c>
+      <c r="AI164" s="7">
+        <v>1576.89</v>
+      </c>
+      <c r="AJ164" s="7">
+        <v>1646.29</v>
+      </c>
+      <c r="AK164" s="7">
+        <v>743.2</v>
+      </c>
+      <c r="AL164" s="7">
+        <v>277.32</v>
+      </c>
+      <c r="AM164" s="7">
+        <v>64.18</v>
+      </c>
+      <c r="AN164" s="7">
+        <v>4</v>
+      </c>
+      <c r="AO164" s="7">
+        <v>1.6</v>
+      </c>
+      <c r="AP164" s="7">
+        <v>341.5</v>
+      </c>
+      <c r="AQ164" s="7">
+        <v>15</v>
+      </c>
+      <c r="AR164" s="7">
+        <v>8.54</v>
+      </c>
+      <c r="AS164" s="7">
+        <v>46</v>
+      </c>
+      <c r="AT164" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU164" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV164" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW164" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX164" s="6" t="s">
+        <v>122</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GPS_Formativas_2026.xlsx
+++ b/GPS_Formativas_2026.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="17028" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="GPS_Formativas_2026" sheetId="1" r:id="rId1"/>
@@ -1210,7 +1210,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1251,6 +1251,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -32344,7 +32347,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="202" ht="15.15" spans="1:50">
+    <row r="202" spans="1:50">
       <c r="A202" s="1" t="s">
         <v>140</v>
       </c>
@@ -32498,7 +32501,7 @@
     </row>
     <row r="203" ht="43.95" spans="1:50">
       <c r="A203" s="1">
-        <v>46028</v>
+        <v>46174</v>
       </c>
       <c r="B203" t="s">
         <v>51</v>
@@ -32650,7 +32653,7 @@
     </row>
     <row r="204" ht="43.95" spans="1:50">
       <c r="A204" s="1">
-        <v>46028</v>
+        <v>46174</v>
       </c>
       <c r="B204" t="s">
         <v>51</v>
@@ -32802,7 +32805,7 @@
     </row>
     <row r="205" ht="43.95" spans="1:50">
       <c r="A205" s="1">
-        <v>46028</v>
+        <v>46174</v>
       </c>
       <c r="B205" t="s">
         <v>51</v>
@@ -32954,7 +32957,7 @@
     </row>
     <row r="206" ht="43.95" spans="1:50">
       <c r="A206" s="1">
-        <v>46028</v>
+        <v>46174</v>
       </c>
       <c r="B206" t="s">
         <v>51</v>
@@ -33106,7 +33109,7 @@
     </row>
     <row r="207" ht="43.95" spans="1:50">
       <c r="A207" s="1">
-        <v>46028</v>
+        <v>46174</v>
       </c>
       <c r="B207" t="s">
         <v>51</v>
@@ -33258,7 +33261,7 @@
     </row>
     <row r="208" ht="43.95" spans="1:50">
       <c r="A208" s="1">
-        <v>46028</v>
+        <v>46174</v>
       </c>
       <c r="B208" t="s">
         <v>51</v>
@@ -33410,7 +33413,7 @@
     </row>
     <row r="209" ht="43.95" spans="1:50">
       <c r="A209" s="1">
-        <v>46028</v>
+        <v>46174</v>
       </c>
       <c r="B209" t="s">
         <v>51</v>
@@ -33562,7 +33565,7 @@
     </row>
     <row r="210" ht="43.95" spans="1:50">
       <c r="A210" s="1">
-        <v>46028</v>
+        <v>46174</v>
       </c>
       <c r="B210" t="s">
         <v>51</v>
@@ -33714,7 +33717,7 @@
     </row>
     <row r="211" ht="15.15" spans="1:50">
       <c r="A211" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B211" t="s">
         <v>51</v>
@@ -33866,7 +33869,7 @@
     </row>
     <row r="212" ht="15.15" spans="1:50">
       <c r="A212" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B212" t="s">
         <v>51</v>
@@ -34018,7 +34021,7 @@
     </row>
     <row r="213" ht="15.15" spans="1:50">
       <c r="A213" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B213" t="s">
         <v>51</v>
@@ -34170,7 +34173,7 @@
     </row>
     <row r="214" ht="15.15" spans="1:50">
       <c r="A214" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B214" t="s">
         <v>51</v>
@@ -34322,7 +34325,7 @@
     </row>
     <row r="215" ht="15.15" spans="1:50">
       <c r="A215" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B215" t="s">
         <v>51</v>
@@ -34474,7 +34477,7 @@
     </row>
     <row r="216" ht="15.15" spans="1:50">
       <c r="A216" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B216" t="s">
         <v>51</v>
@@ -34626,7 +34629,7 @@
     </row>
     <row r="217" ht="15.15" spans="1:50">
       <c r="A217" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B217" t="s">
         <v>51</v>
@@ -34778,7 +34781,7 @@
     </row>
     <row r="218" ht="15.15" spans="1:50">
       <c r="A218" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B218" t="s">
         <v>51</v>
@@ -34930,7 +34933,7 @@
     </row>
     <row r="219" ht="29.55" spans="1:50">
       <c r="A219" s="1">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B219" t="s">
         <v>51</v>
@@ -35082,7 +35085,7 @@
     </row>
     <row r="220" ht="29.55" spans="1:50">
       <c r="A220" s="1">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B220" t="s">
         <v>51</v>
@@ -35234,7 +35237,7 @@
     </row>
     <row r="221" ht="29.55" spans="1:50">
       <c r="A221" s="1">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B221" t="s">
         <v>51</v>
@@ -35386,7 +35389,7 @@
     </row>
     <row r="222" ht="29.55" spans="1:50">
       <c r="A222" s="1">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B222" t="s">
         <v>51</v>
@@ -36602,7 +36605,7 @@
     </row>
     <row r="230" ht="43.95" spans="1:50">
       <c r="A230" s="1">
-        <v>46028</v>
+        <v>46174</v>
       </c>
       <c r="B230" t="s">
         <v>64</v>
@@ -36752,7 +36755,7 @@
     </row>
     <row r="231" ht="43.95" spans="1:50">
       <c r="A231" s="1">
-        <v>46028</v>
+        <v>46174</v>
       </c>
       <c r="B231" t="s">
         <v>64</v>
@@ -36902,7 +36905,7 @@
     </row>
     <row r="232" ht="43.95" spans="1:50">
       <c r="A232" s="1">
-        <v>46028</v>
+        <v>46174</v>
       </c>
       <c r="B232" t="s">
         <v>64</v>
@@ -37052,7 +37055,7 @@
     </row>
     <row r="233" ht="43.95" spans="1:50">
       <c r="A233" s="1">
-        <v>46028</v>
+        <v>46174</v>
       </c>
       <c r="B233" t="s">
         <v>64</v>
@@ -37202,7 +37205,7 @@
     </row>
     <row r="234" ht="43.95" spans="1:50">
       <c r="A234" s="1">
-        <v>46028</v>
+        <v>46174</v>
       </c>
       <c r="B234" t="s">
         <v>64</v>
@@ -37352,7 +37355,7 @@
     </row>
     <row r="235" ht="43.95" spans="1:50">
       <c r="A235" s="1">
-        <v>46028</v>
+        <v>46174</v>
       </c>
       <c r="B235" t="s">
         <v>64</v>
@@ -37502,7 +37505,7 @@
     </row>
     <row r="236" ht="43.95" spans="1:50">
       <c r="A236" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B236" t="s">
         <v>64</v>
@@ -37652,7 +37655,7 @@
     </row>
     <row r="237" ht="43.95" spans="1:50">
       <c r="A237" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B237" t="s">
         <v>64</v>
@@ -37802,7 +37805,7 @@
     </row>
     <row r="238" ht="43.95" spans="1:50">
       <c r="A238" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B238" t="s">
         <v>64</v>
@@ -37952,7 +37955,7 @@
     </row>
     <row r="239" ht="43.95" spans="1:50">
       <c r="A239" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B239" t="s">
         <v>64</v>
@@ -38102,7 +38105,7 @@
     </row>
     <row r="240" ht="43.95" spans="1:50">
       <c r="A240" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B240" t="s">
         <v>64</v>
@@ -38252,7 +38255,7 @@
     </row>
     <row r="241" ht="43.95" spans="1:50">
       <c r="A241" s="1">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B241" t="s">
         <v>64</v>
@@ -38404,7 +38407,7 @@
     </row>
     <row r="242" ht="43.95" spans="1:50">
       <c r="A242" s="1">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B242" t="s">
         <v>64</v>
@@ -38556,7 +38559,7 @@
     </row>
     <row r="243" ht="43.95" spans="1:50">
       <c r="A243" s="1">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B243" t="s">
         <v>64</v>
@@ -38708,7 +38711,7 @@
     </row>
     <row r="244" ht="43.95" spans="1:50">
       <c r="A244" s="1">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B244" t="s">
         <v>64</v>
@@ -38860,7 +38863,7 @@
     </row>
     <row r="245" ht="43.95" spans="1:50">
       <c r="A245" s="1">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B245" t="s">
         <v>64</v>
@@ -39012,7 +39015,7 @@
     </row>
     <row r="246" ht="43.95" spans="1:50">
       <c r="A246" s="1">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B246" t="s">
         <v>64</v>
@@ -39164,7 +39167,7 @@
     </row>
     <row r="247" ht="28.35" spans="1:50">
       <c r="A247" s="1">
-        <v>46028</v>
+        <v>46174</v>
       </c>
       <c r="B247" t="s">
         <v>141</v>
@@ -39316,7 +39319,7 @@
     </row>
     <row r="248" ht="28.35" spans="1:50">
       <c r="A248" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B248" t="s">
         <v>141</v>
@@ -39468,7 +39471,7 @@
     </row>
     <row r="249" ht="28.35" spans="1:50">
       <c r="A249" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B249" t="s">
         <v>141</v>
@@ -39620,7 +39623,7 @@
     </row>
     <row r="250" ht="28.35" spans="1:50">
       <c r="A250" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B250" t="s">
         <v>141</v>
@@ -39772,7 +39775,7 @@
     </row>
     <row r="251" ht="28.35" spans="1:50">
       <c r="A251" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B251" t="s">
         <v>141</v>
@@ -39924,7 +39927,7 @@
     </row>
     <row r="252" ht="28.35" spans="1:50">
       <c r="A252" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B252" t="s">
         <v>141</v>
@@ -40076,7 +40079,7 @@
     </row>
     <row r="253" ht="28.35" spans="1:50">
       <c r="A253" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B253" t="s">
         <v>141</v>
@@ -40228,7 +40231,7 @@
     </row>
     <row r="254" ht="28.35" spans="1:50">
       <c r="A254" s="1">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B254" t="s">
         <v>141</v>
@@ -41899,7 +41902,7 @@
       </c>
     </row>
     <row r="265" ht="29.55" spans="1:50">
-      <c r="A265" s="1">
+      <c r="A265" s="15">
         <v>46059</v>
       </c>
       <c r="B265" t="s">

--- a/GPS_Formativas_2026.xlsx
+++ b/GPS_Formativas_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="17028" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="GPS_Formativas_2026" sheetId="1" r:id="rId1"/>
@@ -32347,7 +32347,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="202" spans="1:50">
+    <row r="202" ht="15.15" spans="1:50">
       <c r="A202" s="1" t="s">
         <v>140</v>
       </c>

--- a/GPS_Formativas_2026.xlsx
+++ b/GPS_Formativas_2026.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3017" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3017" uniqueCount="197">
   <si>
     <t>Date</t>
   </si>
@@ -440,13 +440,7 @@
     <t>26/5/26</t>
   </si>
   <si>
-    <t>MD -2</t>
-  </si>
-  <si>
     <t>Matteo Costantini</t>
-  </si>
-  <si>
-    <t>MD - 3</t>
   </si>
   <si>
     <t>29/5/26</t>
@@ -518,9 +512,6 @@
     <t>FÚTBOL</t>
   </si>
   <si>
-    <t>MD -1</t>
-  </si>
-  <si>
     <t>U19 Entrenamiento</t>
   </si>
   <si>
@@ -546,9 +537,6 @@
   </si>
   <si>
     <t>Ismael Torterolo</t>
-  </si>
-  <si>
-    <t>30/05</t>
   </si>
   <si>
     <t>U16 1er Tiempo</t>
@@ -636,13 +624,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="m/d/yy;@"/>
-    <numFmt numFmtId="179" formatCode="mm/dd/yy"/>
+    <numFmt numFmtId="179" formatCode="mm/dd/yy;@"/>
+    <numFmt numFmtId="180" formatCode="mm/dd/yy"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1286,7 +1275,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1319,10 +1308,13 @@
     <xf numFmtId="58" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -9221,7 +9213,7 @@
         <v>483.04</v>
       </c>
       <c r="O49" s="3">
-        <v>6.93</v>
+        <v>24.948</v>
       </c>
       <c r="P49" s="3">
         <v>69.27</v>
@@ -9373,7 +9365,7 @@
         <v>576.67</v>
       </c>
       <c r="O50" s="3">
-        <v>7.72</v>
+        <v>27.792</v>
       </c>
       <c r="P50" s="3">
         <v>77.18</v>
@@ -9525,7 +9517,7 @@
         <v>603.06</v>
       </c>
       <c r="O51" s="3">
-        <v>6.58</v>
+        <v>23.688</v>
       </c>
       <c r="P51" s="3">
         <v>65.79</v>
@@ -9677,7 +9669,7 @@
         <v>667.87</v>
       </c>
       <c r="O52" s="3">
-        <v>7.46</v>
+        <v>26.856</v>
       </c>
       <c r="P52" s="3">
         <v>74.57</v>
@@ -9829,7 +9821,7 @@
         <v>445.51</v>
       </c>
       <c r="O53" s="3">
-        <v>7.08</v>
+        <v>25.488</v>
       </c>
       <c r="P53" s="3">
         <v>70.8</v>
@@ -9981,7 +9973,7 @@
         <v>570.56</v>
       </c>
       <c r="O54" s="3">
-        <v>7.31</v>
+        <v>26.316</v>
       </c>
       <c r="P54" s="3">
         <v>73.12</v>
@@ -10133,7 +10125,7 @@
         <v>574.08</v>
       </c>
       <c r="O55" s="3">
-        <v>7.43</v>
+        <v>26.748</v>
       </c>
       <c r="P55" s="3">
         <v>74.29</v>
@@ -10285,7 +10277,7 @@
         <v>523.36</v>
       </c>
       <c r="O56" s="3">
-        <v>7.13</v>
+        <v>25.668</v>
       </c>
       <c r="P56" s="3">
         <v>71.28</v>
@@ -10437,7 +10429,7 @@
         <v>864.77</v>
       </c>
       <c r="O57" s="3">
-        <v>7.7</v>
+        <v>27.72</v>
       </c>
       <c r="P57" s="3">
         <v>76.97</v>
@@ -10589,7 +10581,7 @@
         <v>646.15</v>
       </c>
       <c r="O58" s="3">
-        <v>7.88</v>
+        <v>28.368</v>
       </c>
       <c r="P58" s="3">
         <v>78.78</v>
@@ -10741,7 +10733,7 @@
         <v>836.39</v>
       </c>
       <c r="O59" s="3">
-        <v>6.94</v>
+        <v>24.984</v>
       </c>
       <c r="P59" s="3">
         <v>69.45</v>
@@ -22392,7 +22384,7 @@
         <v>84</v>
       </c>
       <c r="AV135" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW135" t="s">
         <v>57</v>
@@ -22544,7 +22536,7 @@
         <v>84</v>
       </c>
       <c r="AV136" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW136" t="s">
         <v>57</v>
@@ -22696,7 +22688,7 @@
         <v>84</v>
       </c>
       <c r="AV137" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW137" t="s">
         <v>57</v>
@@ -22848,7 +22840,7 @@
         <v>84</v>
       </c>
       <c r="AV138" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW138" t="s">
         <v>57</v>
@@ -22865,7 +22857,7 @@
         <v>64</v>
       </c>
       <c r="C139" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D139" t="s">
         <v>53</v>
@@ -23000,7 +22992,7 @@
         <v>84</v>
       </c>
       <c r="AV139" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW139" t="s">
         <v>57</v>
@@ -23152,7 +23144,7 @@
         <v>55</v>
       </c>
       <c r="AV140" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AW140" t="s">
         <v>57</v>
@@ -23304,7 +23296,7 @@
         <v>55</v>
       </c>
       <c r="AV141" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AW141" t="s">
         <v>57</v>
@@ -23456,7 +23448,7 @@
         <v>55</v>
       </c>
       <c r="AV142" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AW142" t="s">
         <v>57</v>
@@ -23608,7 +23600,7 @@
         <v>55</v>
       </c>
       <c r="AV143" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AW143" t="s">
         <v>57</v>
@@ -23760,7 +23752,7 @@
         <v>55</v>
       </c>
       <c r="AV144" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AW144" t="s">
         <v>57</v>
@@ -23912,7 +23904,7 @@
         <v>55</v>
       </c>
       <c r="AV145" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AW145" t="s">
         <v>57</v>
@@ -24064,7 +24056,7 @@
         <v>133</v>
       </c>
       <c r="AV146" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW146" t="s">
         <v>57</v>
@@ -24216,7 +24208,7 @@
         <v>133</v>
       </c>
       <c r="AV147" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW147" t="s">
         <v>57</v>
@@ -24368,7 +24360,7 @@
         <v>133</v>
       </c>
       <c r="AV148" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW148" t="s">
         <v>57</v>
@@ -24520,7 +24512,7 @@
         <v>133</v>
       </c>
       <c r="AV149" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW149" t="s">
         <v>57</v>
@@ -24672,7 +24664,7 @@
         <v>133</v>
       </c>
       <c r="AV150" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW150" t="s">
         <v>57</v>
@@ -24824,7 +24816,7 @@
         <v>133</v>
       </c>
       <c r="AV151" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW151" t="s">
         <v>57</v>
@@ -24976,7 +24968,7 @@
         <v>133</v>
       </c>
       <c r="AV152" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW152" t="s">
         <v>57</v>
@@ -24987,7 +24979,7 @@
     </row>
     <row r="153" spans="1:50">
       <c r="A153" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B153" t="s">
         <v>51</v>
@@ -25139,7 +25131,7 @@
     </row>
     <row r="154" spans="1:50">
       <c r="A154" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B154" t="s">
         <v>51</v>
@@ -25291,7 +25283,7 @@
     </row>
     <row r="155" spans="1:50">
       <c r="A155" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B155" t="s">
         <v>51</v>
@@ -25443,7 +25435,7 @@
     </row>
     <row r="156" spans="1:50">
       <c r="A156" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B156" t="s">
         <v>51</v>
@@ -25595,7 +25587,7 @@
     </row>
     <row r="157" spans="1:50">
       <c r="A157" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B157" t="s">
         <v>51</v>
@@ -25747,7 +25739,7 @@
     </row>
     <row r="158" spans="1:50">
       <c r="A158" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B158" t="s">
         <v>51</v>
@@ -25899,7 +25891,7 @@
     </row>
     <row r="159" spans="1:50">
       <c r="A159" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B159" t="s">
         <v>51</v>
@@ -26051,7 +26043,7 @@
     </row>
     <row r="160" spans="1:50">
       <c r="A160" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B160" t="s">
         <v>51</v>
@@ -26206,10 +26198,10 @@
         <v>120</v>
       </c>
       <c r="B161" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C161" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D161" t="s">
         <v>53</v>
@@ -26338,7 +26330,7 @@
         <v>25</v>
       </c>
       <c r="AT161" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU161" t="s">
         <v>84</v>
@@ -26358,10 +26350,10 @@
         <v>120</v>
       </c>
       <c r="B162" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C162" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D162" t="s">
         <v>53</v>
@@ -26510,10 +26502,10 @@
         <v>120</v>
       </c>
       <c r="B163" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C163" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D163" t="s">
         <v>53</v>
@@ -26662,10 +26654,10 @@
         <v>120</v>
       </c>
       <c r="B164" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C164" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D164" t="s">
         <v>53</v>
@@ -26814,10 +26806,10 @@
         <v>136</v>
       </c>
       <c r="B165" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C165" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D165" t="s">
         <v>53</v>
@@ -26946,7 +26938,7 @@
         <v>34</v>
       </c>
       <c r="AT165" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU165" t="s">
         <v>55</v>
@@ -26966,10 +26958,10 @@
         <v>136</v>
       </c>
       <c r="B166" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C166" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D166" t="s">
         <v>53</v>
@@ -27098,7 +27090,7 @@
         <v>22</v>
       </c>
       <c r="AT166" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU166" t="s">
         <v>55</v>
@@ -27118,10 +27110,10 @@
         <v>136</v>
       </c>
       <c r="B167" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C167" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D167" t="s">
         <v>53</v>
@@ -27270,10 +27262,10 @@
         <v>136</v>
       </c>
       <c r="B168" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C168" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D168" t="s">
         <v>53</v>
@@ -27422,10 +27414,10 @@
         <v>136</v>
       </c>
       <c r="B169" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C169" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D169" t="s">
         <v>53</v>
@@ -27554,7 +27546,7 @@
         <v>58</v>
       </c>
       <c r="AT169" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU169" t="s">
         <v>55</v>
@@ -27574,10 +27566,10 @@
         <v>123</v>
       </c>
       <c r="B170" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C170" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D170" t="s">
         <v>53</v>
@@ -27706,7 +27698,7 @@
         <v>20</v>
       </c>
       <c r="AT170" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU170" t="s">
         <v>133</v>
@@ -27726,10 +27718,10 @@
         <v>123</v>
       </c>
       <c r="B171" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C171" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D171" t="s">
         <v>53</v>
@@ -27858,7 +27850,7 @@
         <v>59</v>
       </c>
       <c r="AT171" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU171" t="s">
         <v>133</v>
@@ -27878,10 +27870,10 @@
         <v>132</v>
       </c>
       <c r="B172" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C172" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D172" t="s">
         <v>53</v>
@@ -28010,7 +28002,7 @@
         <v>20</v>
       </c>
       <c r="AT172" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU172" t="s">
         <v>84</v>
@@ -28030,10 +28022,10 @@
         <v>132</v>
       </c>
       <c r="B173" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C173" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D173" t="s">
         <v>53</v>
@@ -28162,7 +28154,7 @@
         <v>28</v>
       </c>
       <c r="AT173" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU173" t="s">
         <v>84</v>
@@ -28182,10 +28174,10 @@
         <v>132</v>
       </c>
       <c r="B174" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C174" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D174" t="s">
         <v>53</v>
@@ -28314,7 +28306,7 @@
         <v>9</v>
       </c>
       <c r="AT174" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU174" t="s">
         <v>84</v>
@@ -28334,10 +28326,10 @@
         <v>132</v>
       </c>
       <c r="B175" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C175" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D175" t="s">
         <v>53</v>
@@ -28483,13 +28475,13 @@
     </row>
     <row r="176" spans="1:50">
       <c r="A176" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B176" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C176" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D176" t="s">
         <v>53</v>
@@ -28621,7 +28613,7 @@
         <v>68</v>
       </c>
       <c r="AU176" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AV176" t="s">
         <v>100</v>
@@ -28635,13 +28627,13 @@
     </row>
     <row r="177" spans="1:50">
       <c r="A177" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B177" t="s">
+        <v>139</v>
+      </c>
+      <c r="C177" t="s">
         <v>140</v>
-      </c>
-      <c r="B177" t="s">
-        <v>141</v>
-      </c>
-      <c r="C177" t="s">
-        <v>142</v>
       </c>
       <c r="D177" t="s">
         <v>53</v>
@@ -28770,10 +28762,10 @@
         <v>36</v>
       </c>
       <c r="AT177" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU177" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AV177" t="s">
         <v>100</v>
@@ -28787,13 +28779,13 @@
     </row>
     <row r="178" spans="1:50">
       <c r="A178" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B178" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C178" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D178" t="s">
         <v>53</v>
@@ -28925,7 +28917,7 @@
         <v>75</v>
       </c>
       <c r="AU178" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AV178" t="s">
         <v>100</v>
@@ -28939,13 +28931,13 @@
     </row>
     <row r="179" spans="1:50">
       <c r="A179" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B179" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C179" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D179" t="s">
         <v>53</v>
@@ -29074,10 +29066,10 @@
         <v>12</v>
       </c>
       <c r="AT179" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU179" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AV179" t="s">
         <v>100</v>
@@ -29091,13 +29083,13 @@
     </row>
     <row r="180" spans="1:50">
       <c r="A180" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B180" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C180" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D180" t="s">
         <v>53</v>
@@ -29229,7 +29221,7 @@
         <v>60</v>
       </c>
       <c r="AU180" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AV180" t="s">
         <v>100</v>
@@ -29243,13 +29235,13 @@
     </row>
     <row r="181" spans="1:50">
       <c r="A181" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B181" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C181" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D181" t="s">
         <v>53</v>
@@ -29381,7 +29373,7 @@
         <v>68</v>
       </c>
       <c r="AU181" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AV181" t="s">
         <v>100</v>
@@ -29395,13 +29387,13 @@
     </row>
     <row r="182" spans="1:50">
       <c r="A182" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B182" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C182" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D182" t="s">
         <v>53</v>
@@ -29530,10 +29522,10 @@
         <v>17</v>
       </c>
       <c r="AT182" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU182" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AV182" t="s">
         <v>100</v>
@@ -29547,13 +29539,13 @@
     </row>
     <row r="183" spans="1:50">
       <c r="A183" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B183" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C183" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D183" t="s">
         <v>53</v>
@@ -29685,7 +29677,7 @@
         <v>68</v>
       </c>
       <c r="AU183" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AV183" t="s">
         <v>100</v>
@@ -29699,13 +29691,13 @@
     </row>
     <row r="184" spans="1:50">
       <c r="A184" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B184" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C184" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D184" t="s">
         <v>53</v>
@@ -29837,7 +29829,7 @@
         <v>63</v>
       </c>
       <c r="AU184" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AV184" t="s">
         <v>100</v>
@@ -29851,13 +29843,13 @@
     </row>
     <row r="185" spans="1:50">
       <c r="A185" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B185" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C185" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D185" t="s">
         <v>53</v>
@@ -29989,7 +29981,7 @@
         <v>63</v>
       </c>
       <c r="AU185" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AV185" t="s">
         <v>100</v>
@@ -30003,13 +29995,13 @@
     </row>
     <row r="186" spans="1:50">
       <c r="A186" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B186" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C186" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D186" t="s">
         <v>53</v>
@@ -30141,7 +30133,7 @@
         <v>68</v>
       </c>
       <c r="AU186" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AV186" t="s">
         <v>113</v>
@@ -30155,13 +30147,13 @@
     </row>
     <row r="187" spans="1:50">
       <c r="A187" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B187" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C187" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D187" t="s">
         <v>53</v>
@@ -30290,10 +30282,10 @@
         <v>86</v>
       </c>
       <c r="AT187" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU187" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AV187" t="s">
         <v>113</v>
@@ -30307,13 +30299,13 @@
     </row>
     <row r="188" spans="1:50">
       <c r="A188" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B188" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C188" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D188" t="s">
         <v>53</v>
@@ -30442,10 +30434,10 @@
         <v>111</v>
       </c>
       <c r="AT188" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU188" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AV188" t="s">
         <v>113</v>
@@ -30459,13 +30451,13 @@
     </row>
     <row r="189" spans="1:50">
       <c r="A189" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B189" t="s">
+        <v>139</v>
+      </c>
+      <c r="C189" t="s">
         <v>156</v>
-      </c>
-      <c r="B189" t="s">
-        <v>141</v>
-      </c>
-      <c r="C189" t="s">
-        <v>158</v>
       </c>
       <c r="D189" t="s">
         <v>53</v>
@@ -30597,7 +30589,7 @@
         <v>75</v>
       </c>
       <c r="AU189" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AV189" t="s">
         <v>113</v>
@@ -30611,13 +30603,13 @@
     </row>
     <row r="190" spans="1:50">
       <c r="A190" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B190" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C190" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D190" t="s">
         <v>53</v>
@@ -30746,10 +30738,10 @@
         <v>82</v>
       </c>
       <c r="AT190" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU190" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AV190" t="s">
         <v>113</v>
@@ -30763,13 +30755,13 @@
     </row>
     <row r="191" spans="1:50">
       <c r="A191" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B191" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C191" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D191" t="s">
         <v>53</v>
@@ -30898,10 +30890,10 @@
         <v>34</v>
       </c>
       <c r="AT191" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU191" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AV191" t="s">
         <v>113</v>
@@ -30915,13 +30907,13 @@
     </row>
     <row r="192" spans="1:50">
       <c r="A192" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B192" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C192" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D192" t="s">
         <v>53</v>
@@ -31053,7 +31045,7 @@
         <v>63</v>
       </c>
       <c r="AU192" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AV192" t="s">
         <v>113</v>
@@ -31067,13 +31059,13 @@
     </row>
     <row r="193" spans="1:50">
       <c r="A193" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B193" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C193" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D193" t="s">
         <v>53</v>
@@ -31205,7 +31197,7 @@
         <v>63</v>
       </c>
       <c r="AU193" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AV193" t="s">
         <v>113</v>
@@ -31219,13 +31211,13 @@
     </row>
     <row r="194" spans="1:50">
       <c r="A194" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B194" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C194" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D194" t="s">
         <v>53</v>
@@ -31357,7 +31349,7 @@
         <v>75</v>
       </c>
       <c r="AU194" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AV194" t="s">
         <v>113</v>
@@ -31371,13 +31363,13 @@
     </row>
     <row r="195" spans="1:50">
       <c r="A195" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B195" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C195" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D195" t="s">
         <v>53</v>
@@ -31509,7 +31501,7 @@
         <v>60</v>
       </c>
       <c r="AU195" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AV195" t="s">
         <v>113</v>
@@ -31523,7 +31515,7 @@
     </row>
     <row r="196" spans="1:50">
       <c r="A196" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B196" t="s">
         <v>64</v>
@@ -31532,7 +31524,7 @@
         <v>77</v>
       </c>
       <c r="D196" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E196">
         <v>1</v>
@@ -31661,10 +31653,10 @@
         <v>75</v>
       </c>
       <c r="AU196" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AV196" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="AW196" t="s">
         <v>57</v>
@@ -31675,7 +31667,7 @@
     </row>
     <row r="197" spans="1:50">
       <c r="A197" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B197" t="s">
         <v>64</v>
@@ -31684,7 +31676,7 @@
         <v>52</v>
       </c>
       <c r="D197" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E197">
         <v>1</v>
@@ -31813,10 +31805,10 @@
         <v>54</v>
       </c>
       <c r="AU197" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AV197" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="AW197" t="s">
         <v>57</v>
@@ -31827,7 +31819,7 @@
     </row>
     <row r="198" spans="1:50">
       <c r="A198" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B198" t="s">
         <v>64</v>
@@ -31836,7 +31828,7 @@
         <v>59</v>
       </c>
       <c r="D198" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E198">
         <v>1</v>
@@ -31965,10 +31957,10 @@
         <v>60</v>
       </c>
       <c r="AU198" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AV198" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="AW198" t="s">
         <v>57</v>
@@ -31979,7 +31971,7 @@
     </row>
     <row r="199" spans="1:50">
       <c r="A199" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B199" t="s">
         <v>64</v>
@@ -31988,7 +31980,7 @@
         <v>61</v>
       </c>
       <c r="D199" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E199">
         <v>1</v>
@@ -32117,10 +32109,10 @@
         <v>54</v>
       </c>
       <c r="AU199" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AV199" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="AW199" t="s">
         <v>57</v>
@@ -32131,16 +32123,16 @@
     </row>
     <row r="200" spans="1:50">
       <c r="A200" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B200" t="s">
         <v>64</v>
       </c>
       <c r="C200" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D200" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -32269,10 +32261,10 @@
         <v>68</v>
       </c>
       <c r="AU200" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AV200" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="AW200" t="s">
         <v>57</v>
@@ -32283,7 +32275,7 @@
     </row>
     <row r="201" spans="1:50">
       <c r="A201" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B201" t="s">
         <v>64</v>
@@ -32292,7 +32284,7 @@
         <v>79</v>
       </c>
       <c r="D201" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E201">
         <v>1</v>
@@ -32421,10 +32413,10 @@
         <v>63</v>
       </c>
       <c r="AU201" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AV201" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="AW201" t="s">
         <v>57</v>
@@ -32435,7 +32427,7 @@
     </row>
     <row r="202" spans="1:50">
       <c r="A202" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B202" t="s">
         <v>64</v>
@@ -32444,7 +32436,7 @@
         <v>73</v>
       </c>
       <c r="D202" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E202">
         <v>1</v>
@@ -32573,10 +32565,10 @@
         <v>54</v>
       </c>
       <c r="AU202" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AV202" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="AW202" t="s">
         <v>57</v>
@@ -32587,7 +32579,7 @@
     </row>
     <row r="203" ht="15.15" spans="1:50">
       <c r="A203" s="1">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="B203" t="s">
         <v>51</v>
@@ -32596,7 +32588,7 @@
         <v>99</v>
       </c>
       <c r="D203" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E203">
         <v>1</v>
@@ -32629,7 +32621,7 @@
         <v>517.19</v>
       </c>
       <c r="O203">
-        <v>7.2</v>
+        <v>25.92</v>
       </c>
       <c r="P203">
         <v>71.95</v>
@@ -32734,12 +32726,12 @@
         <v>57</v>
       </c>
       <c r="AX203" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="204" ht="15.15" spans="1:50">
       <c r="A204" s="1">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="B204" t="s">
         <v>51</v>
@@ -32748,7 +32740,7 @@
         <v>59</v>
       </c>
       <c r="D204" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E204" s="8">
         <v>1</v>
@@ -32781,7 +32773,7 @@
         <v>485.98</v>
       </c>
       <c r="O204" s="8">
-        <v>7.71</v>
+        <v>27.756</v>
       </c>
       <c r="P204" s="8">
         <v>77.12</v>
@@ -32886,12 +32878,12 @@
         <v>57</v>
       </c>
       <c r="AX204" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="205" ht="15.15" spans="1:50">
       <c r="A205" s="1">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="B205" t="s">
         <v>51</v>
@@ -32900,7 +32892,7 @@
         <v>101</v>
       </c>
       <c r="D205" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E205" s="8">
         <v>1</v>
@@ -32933,7 +32925,7 @@
         <v>507.2</v>
       </c>
       <c r="O205" s="8">
-        <v>6.83</v>
+        <v>24.588</v>
       </c>
       <c r="P205" s="8">
         <v>68.28</v>
@@ -33038,12 +33030,12 @@
         <v>57</v>
       </c>
       <c r="AX205" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="206" ht="15.15" spans="1:50">
       <c r="A206" s="1">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="B206" t="s">
         <v>51</v>
@@ -33052,7 +33044,7 @@
         <v>103</v>
       </c>
       <c r="D206" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E206" s="8">
         <v>1</v>
@@ -33085,7 +33077,7 @@
         <v>483.09</v>
       </c>
       <c r="O206" s="8">
-        <v>7.9</v>
+        <v>28.44</v>
       </c>
       <c r="P206" s="8">
         <v>78.96</v>
@@ -33190,12 +33182,12 @@
         <v>57</v>
       </c>
       <c r="AX206" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="207" ht="15.15" spans="1:50">
       <c r="A207" s="1">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="B207" t="s">
         <v>51</v>
@@ -33204,7 +33196,7 @@
         <v>80</v>
       </c>
       <c r="D207" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E207" s="8">
         <v>1</v>
@@ -33237,7 +33229,7 @@
         <v>402.57</v>
       </c>
       <c r="O207" s="8">
-        <v>7.22</v>
+        <v>25.992</v>
       </c>
       <c r="P207" s="8">
         <v>72.15</v>
@@ -33342,12 +33334,12 @@
         <v>57</v>
       </c>
       <c r="AX207" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="208" ht="15.15" spans="1:50">
       <c r="A208" s="1">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="B208" t="s">
         <v>51</v>
@@ -33356,7 +33348,7 @@
         <v>104</v>
       </c>
       <c r="D208" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E208" s="8">
         <v>1</v>
@@ -33389,7 +33381,7 @@
         <v>482.37</v>
       </c>
       <c r="O208" s="8">
-        <v>6.48</v>
+        <v>23.328</v>
       </c>
       <c r="P208" s="8">
         <v>64.83</v>
@@ -33494,12 +33486,12 @@
         <v>57</v>
       </c>
       <c r="AX208" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="209" ht="15.15" spans="1:50">
       <c r="A209" s="1">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="B209" t="s">
         <v>51</v>
@@ -33508,7 +33500,7 @@
         <v>105</v>
       </c>
       <c r="D209" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E209" s="8">
         <v>1</v>
@@ -33541,7 +33533,7 @@
         <v>489.4</v>
       </c>
       <c r="O209" s="8">
-        <v>6.77</v>
+        <v>24.372</v>
       </c>
       <c r="P209" s="8">
         <v>67.71</v>
@@ -33646,12 +33638,12 @@
         <v>57</v>
       </c>
       <c r="AX209" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="210" ht="15.15" spans="1:50">
       <c r="A210" s="1">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="B210" t="s">
         <v>51</v>
@@ -33660,7 +33652,7 @@
         <v>109</v>
       </c>
       <c r="D210" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E210" s="8">
         <v>1</v>
@@ -33693,7 +33685,7 @@
         <v>487.02</v>
       </c>
       <c r="O210" s="8">
-        <v>6.98</v>
+        <v>25.128</v>
       </c>
       <c r="P210" s="8">
         <v>69.75</v>
@@ -33798,12 +33790,12 @@
         <v>57</v>
       </c>
       <c r="AX210" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="211" ht="15.15" spans="1:50">
       <c r="A211" s="1">
-        <v>46175</v>
+        <v>46059</v>
       </c>
       <c r="B211" t="s">
         <v>51</v>
@@ -33845,7 +33837,7 @@
         <v>572.15</v>
       </c>
       <c r="O211" s="8">
-        <v>8.35</v>
+        <v>30.06</v>
       </c>
       <c r="P211" s="8">
         <v>83.52</v>
@@ -33944,18 +33936,18 @@
         <v>133</v>
       </c>
       <c r="AV211" s="7" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AW211" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX211" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="212" ht="15.15" spans="1:50">
       <c r="A212" s="1">
-        <v>46175</v>
+        <v>46059</v>
       </c>
       <c r="B212" t="s">
         <v>51</v>
@@ -33997,7 +33989,7 @@
         <v>355.91</v>
       </c>
       <c r="O212" s="8">
-        <v>8.3</v>
+        <v>29.88</v>
       </c>
       <c r="P212" s="8">
         <v>83</v>
@@ -34096,18 +34088,18 @@
         <v>133</v>
       </c>
       <c r="AV212" s="7" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AW212" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX212" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="213" ht="15.15" spans="1:50">
       <c r="A213" s="1">
-        <v>46175</v>
+        <v>46059</v>
       </c>
       <c r="B213" t="s">
         <v>51</v>
@@ -34149,7 +34141,7 @@
         <v>606.38</v>
       </c>
       <c r="O213" s="8">
-        <v>8.4</v>
+        <v>30.24</v>
       </c>
       <c r="P213" s="8">
         <v>84.01</v>
@@ -34242,24 +34234,24 @@
         <v>174</v>
       </c>
       <c r="AT213" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU213" s="7" t="s">
         <v>133</v>
       </c>
       <c r="AV213" s="7" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AW213" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX213" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="214" ht="15.15" spans="1:50">
       <c r="A214" s="1">
-        <v>46175</v>
+        <v>46059</v>
       </c>
       <c r="B214" t="s">
         <v>51</v>
@@ -34301,7 +34293,7 @@
         <v>618.38</v>
       </c>
       <c r="O214" s="8">
-        <v>8.7</v>
+        <v>31.32</v>
       </c>
       <c r="P214" s="8">
         <v>86.99</v>
@@ -34400,18 +34392,18 @@
         <v>133</v>
       </c>
       <c r="AV214" s="7" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AW214" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX214" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="215" ht="15.15" spans="1:50">
       <c r="A215" s="1">
-        <v>46175</v>
+        <v>46059</v>
       </c>
       <c r="B215" t="s">
         <v>51</v>
@@ -34453,7 +34445,7 @@
         <v>475.95</v>
       </c>
       <c r="O215" s="8">
-        <v>8.16</v>
+        <v>29.376</v>
       </c>
       <c r="P215" s="8">
         <v>81.61</v>
@@ -34552,18 +34544,18 @@
         <v>133</v>
       </c>
       <c r="AV215" s="7" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AW215" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX215" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="216" ht="15.15" spans="1:50">
       <c r="A216" s="1">
-        <v>46175</v>
+        <v>46059</v>
       </c>
       <c r="B216" t="s">
         <v>51</v>
@@ -34605,7 +34597,7 @@
         <v>603.96</v>
       </c>
       <c r="O216" s="8">
-        <v>7.64</v>
+        <v>27.504</v>
       </c>
       <c r="P216" s="8">
         <v>76.37</v>
@@ -34704,18 +34696,18 @@
         <v>133</v>
       </c>
       <c r="AV216" s="7" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AW216" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX216" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="217" ht="15.15" spans="1:50">
       <c r="A217" s="1">
-        <v>46175</v>
+        <v>46059</v>
       </c>
       <c r="B217" t="s">
         <v>51</v>
@@ -34757,7 +34749,7 @@
         <v>727.82</v>
       </c>
       <c r="O217" s="8">
-        <v>7.88</v>
+        <v>28.368</v>
       </c>
       <c r="P217" s="8">
         <v>78.81</v>
@@ -34856,18 +34848,18 @@
         <v>133</v>
       </c>
       <c r="AV217" s="7" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AW217" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX217" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="218" ht="15.15" spans="1:50">
       <c r="A218" s="1">
-        <v>46175</v>
+        <v>46059</v>
       </c>
       <c r="B218" t="s">
         <v>51</v>
@@ -34909,7 +34901,7 @@
         <v>471.27</v>
       </c>
       <c r="O218" s="8">
-        <v>8.18</v>
+        <v>29.448</v>
       </c>
       <c r="P218" s="8">
         <v>81.8</v>
@@ -35008,18 +35000,18 @@
         <v>133</v>
       </c>
       <c r="AV218" s="7" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AW218" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX218" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="219" ht="29.55" spans="1:50">
       <c r="A219" s="1">
-        <v>46177</v>
+        <v>46118</v>
       </c>
       <c r="B219" t="s">
         <v>51</v>
@@ -35061,7 +35053,7 @@
         <v>116.29</v>
       </c>
       <c r="O219" s="8">
-        <v>5.4</v>
+        <v>19.44</v>
       </c>
       <c r="P219" s="8">
         <v>53.96</v>
@@ -35157,7 +35149,7 @@
         <v>63</v>
       </c>
       <c r="AU219" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AV219" s="7" t="s">
         <v>100</v>
@@ -35166,12 +35158,12 @@
         <v>57</v>
       </c>
       <c r="AX219" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="220" ht="29.55" spans="1:50">
       <c r="A220" s="1">
-        <v>46177</v>
+        <v>46118</v>
       </c>
       <c r="B220" t="s">
         <v>51</v>
@@ -35213,7 +35205,7 @@
         <v>103.16</v>
       </c>
       <c r="O220" s="8">
-        <v>6.01</v>
+        <v>21.636</v>
       </c>
       <c r="P220" s="8">
         <v>60.13</v>
@@ -35309,7 +35301,7 @@
         <v>68</v>
       </c>
       <c r="AU220" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AV220" s="7" t="s">
         <v>100</v>
@@ -35318,12 +35310,12 @@
         <v>57</v>
       </c>
       <c r="AX220" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="221" ht="29.55" spans="1:50">
       <c r="A221" s="1">
-        <v>46177</v>
+        <v>46118</v>
       </c>
       <c r="B221" t="s">
         <v>51</v>
@@ -35365,7 +35357,7 @@
         <v>104.44</v>
       </c>
       <c r="O221" s="8">
-        <v>5.56</v>
+        <v>20.016</v>
       </c>
       <c r="P221" s="8">
         <v>55.61</v>
@@ -35461,7 +35453,7 @@
         <v>63</v>
       </c>
       <c r="AU221" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AV221" s="7" t="s">
         <v>100</v>
@@ -35470,12 +35462,12 @@
         <v>57</v>
       </c>
       <c r="AX221" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="222" ht="29.55" spans="1:50">
       <c r="A222" s="1">
-        <v>46177</v>
+        <v>46118</v>
       </c>
       <c r="B222" t="s">
         <v>51</v>
@@ -35517,7 +35509,7 @@
         <v>81.94</v>
       </c>
       <c r="O222" s="8">
-        <v>4.63</v>
+        <v>16.668</v>
       </c>
       <c r="P222" s="8">
         <v>46.25</v>
@@ -35613,7 +35605,7 @@
         <v>63</v>
       </c>
       <c r="AU222" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AV222" s="7" t="s">
         <v>100</v>
@@ -35622,12 +35614,12 @@
         <v>57</v>
       </c>
       <c r="AX222" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="223" ht="15.15" spans="1:50">
       <c r="A223" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B223" t="s">
         <v>64</v>
@@ -35636,7 +35628,7 @@
         <v>77</v>
       </c>
       <c r="D223" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E223" s="8">
         <v>1</v>
@@ -35765,10 +35757,10 @@
         <v>75</v>
       </c>
       <c r="AU223" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AV223" s="7" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="AW223" s="7" t="s">
         <v>57</v>
@@ -35779,7 +35771,7 @@
     </row>
     <row r="224" ht="15.15" spans="1:50">
       <c r="A224" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B224" t="s">
         <v>64</v>
@@ -35788,7 +35780,7 @@
         <v>52</v>
       </c>
       <c r="D224" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E224" s="8">
         <v>1</v>
@@ -35917,10 +35909,10 @@
         <v>54</v>
       </c>
       <c r="AU224" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AV224" s="7" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="AW224" s="7" t="s">
         <v>57</v>
@@ -35931,7 +35923,7 @@
     </row>
     <row r="225" ht="15.15" spans="1:50">
       <c r="A225" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B225" t="s">
         <v>64</v>
@@ -35940,7 +35932,7 @@
         <v>59</v>
       </c>
       <c r="D225" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E225" s="8">
         <v>1</v>
@@ -36069,10 +36061,10 @@
         <v>60</v>
       </c>
       <c r="AU225" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AV225" s="7" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="AW225" s="7" t="s">
         <v>57</v>
@@ -36083,7 +36075,7 @@
     </row>
     <row r="226" ht="15.15" spans="1:50">
       <c r="A226" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B226" t="s">
         <v>64</v>
@@ -36092,7 +36084,7 @@
         <v>61</v>
       </c>
       <c r="D226" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E226" s="8">
         <v>1</v>
@@ -36221,10 +36213,10 @@
         <v>54</v>
       </c>
       <c r="AU226" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AV226" s="7" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="AW226" s="7" t="s">
         <v>57</v>
@@ -36235,16 +36227,16 @@
     </row>
     <row r="227" ht="15.15" spans="1:50">
       <c r="A227" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B227" t="s">
         <v>64</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D227" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E227" s="8">
         <v>1</v>
@@ -36373,10 +36365,10 @@
         <v>68</v>
       </c>
       <c r="AU227" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AV227" s="7" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="AW227" s="7" t="s">
         <v>57</v>
@@ -36387,7 +36379,7 @@
     </row>
     <row r="228" ht="15.15" spans="1:50">
       <c r="A228" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B228" t="s">
         <v>64</v>
@@ -36396,7 +36388,7 @@
         <v>79</v>
       </c>
       <c r="D228" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E228" s="8">
         <v>1</v>
@@ -36525,10 +36517,10 @@
         <v>63</v>
       </c>
       <c r="AU228" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AV228" s="7" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="AW228" s="7" t="s">
         <v>57</v>
@@ -36539,7 +36531,7 @@
     </row>
     <row r="229" ht="15.15" spans="1:50">
       <c r="A229" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B229" t="s">
         <v>64</v>
@@ -36548,7 +36540,7 @@
         <v>73</v>
       </c>
       <c r="D229" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E229" s="8">
         <v>1</v>
@@ -36677,10 +36669,10 @@
         <v>54</v>
       </c>
       <c r="AU229" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AV229" s="7" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="AW229" s="7" t="s">
         <v>57</v>
@@ -36691,7 +36683,7 @@
     </row>
     <row r="230" ht="29.55" spans="1:50">
       <c r="A230" s="1">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="B230" t="s">
         <v>64</v>
@@ -36700,7 +36692,7 @@
         <v>77</v>
       </c>
       <c r="D230" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E230" s="8">
         <v>1</v>
@@ -36836,12 +36828,12 @@
         <v>57</v>
       </c>
       <c r="AX230" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="231" ht="29.55" spans="1:50">
       <c r="A231" s="1">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="B231" t="s">
         <v>64</v>
@@ -36850,7 +36842,7 @@
         <v>52</v>
       </c>
       <c r="D231" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E231" s="8">
         <v>1</v>
@@ -36986,12 +36978,12 @@
         <v>57</v>
       </c>
       <c r="AX231" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="232" ht="29.55" spans="1:50">
       <c r="A232" s="1">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="B232" t="s">
         <v>64</v>
@@ -37000,7 +36992,7 @@
         <v>61</v>
       </c>
       <c r="D232" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E232" s="8">
         <v>1</v>
@@ -37136,21 +37128,21 @@
         <v>57</v>
       </c>
       <c r="AX232" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="233" ht="29.55" spans="1:50">
       <c r="A233" s="1">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="B233" t="s">
         <v>64</v>
       </c>
       <c r="C233" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D233" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E233" s="8">
         <v>1</v>
@@ -37286,12 +37278,12 @@
         <v>57</v>
       </c>
       <c r="AX233" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="234" ht="29.55" spans="1:50">
       <c r="A234" s="1">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="B234" t="s">
         <v>64</v>
@@ -37300,7 +37292,7 @@
         <v>79</v>
       </c>
       <c r="D234" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E234" s="8">
         <v>1</v>
@@ -37436,12 +37428,12 @@
         <v>57</v>
       </c>
       <c r="AX234" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="235" ht="29.55" spans="1:50">
       <c r="A235" s="1">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="B235" t="s">
         <v>64</v>
@@ -37450,7 +37442,7 @@
         <v>73</v>
       </c>
       <c r="D235" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E235" s="8">
         <v>1</v>
@@ -37586,12 +37578,12 @@
         <v>57</v>
       </c>
       <c r="AX235" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="236" ht="15.15" spans="1:50">
       <c r="A236" s="1">
-        <v>46175</v>
+        <v>46059</v>
       </c>
       <c r="B236" t="s">
         <v>64</v>
@@ -37600,7 +37592,7 @@
         <v>77</v>
       </c>
       <c r="D236" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E236" s="8">
         <v>1</v>
@@ -37736,12 +37728,12 @@
         <v>57</v>
       </c>
       <c r="AX236" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="237" ht="15.15" spans="1:50">
       <c r="A237" s="1">
-        <v>46175</v>
+        <v>46059</v>
       </c>
       <c r="B237" t="s">
         <v>64</v>
@@ -37750,7 +37742,7 @@
         <v>52</v>
       </c>
       <c r="D237" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E237" s="8">
         <v>1</v>
@@ -37886,12 +37878,12 @@
         <v>57</v>
       </c>
       <c r="AX237" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="238" ht="15.15" spans="1:50">
       <c r="A238" s="1">
-        <v>46175</v>
+        <v>46059</v>
       </c>
       <c r="B238" t="s">
         <v>64</v>
@@ -37900,7 +37892,7 @@
         <v>61</v>
       </c>
       <c r="D238" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E238" s="8">
         <v>1</v>
@@ -38036,12 +38028,12 @@
         <v>57</v>
       </c>
       <c r="AX238" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="239" ht="15.15" spans="1:50">
       <c r="A239" s="1">
-        <v>46175</v>
+        <v>46059</v>
       </c>
       <c r="B239" t="s">
         <v>64</v>
@@ -38050,7 +38042,7 @@
         <v>79</v>
       </c>
       <c r="D239" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E239" s="8">
         <v>1</v>
@@ -38186,12 +38178,12 @@
         <v>57</v>
       </c>
       <c r="AX239" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="240" ht="15.15" spans="1:50">
       <c r="A240" s="1">
-        <v>46175</v>
+        <v>46059</v>
       </c>
       <c r="B240" t="s">
         <v>64</v>
@@ -38200,7 +38192,7 @@
         <v>73</v>
       </c>
       <c r="D240" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E240" s="8">
         <v>1</v>
@@ -38336,12 +38328,12 @@
         <v>57</v>
       </c>
       <c r="AX240" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="241" ht="29.55" spans="1:50">
-      <c r="A241" s="1">
-        <v>46177</v>
+      <c r="A241" s="11">
+        <v>46118</v>
       </c>
       <c r="B241" t="s">
         <v>64</v>
@@ -38350,7 +38342,7 @@
         <v>77</v>
       </c>
       <c r="D241" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E241" s="8">
         <v>1</v>
@@ -38482,18 +38474,18 @@
         <v>84</v>
       </c>
       <c r="AV241" s="7" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW241" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX241" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="242" ht="29.55" spans="1:50">
-      <c r="A242" s="1">
-        <v>46177</v>
+      <c r="A242" s="11">
+        <v>46118</v>
       </c>
       <c r="B242" t="s">
         <v>64</v>
@@ -38502,7 +38494,7 @@
         <v>52</v>
       </c>
       <c r="D242" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E242" s="8">
         <v>1</v>
@@ -38634,18 +38626,18 @@
         <v>84</v>
       </c>
       <c r="AV242" s="7" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW242" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX242" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="243" ht="29.55" spans="1:50">
-      <c r="A243" s="1">
-        <v>46177</v>
+      <c r="A243" s="11">
+        <v>46118</v>
       </c>
       <c r="B243" t="s">
         <v>64</v>
@@ -38654,7 +38646,7 @@
         <v>61</v>
       </c>
       <c r="D243" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E243" s="8">
         <v>1</v>
@@ -38786,27 +38778,27 @@
         <v>84</v>
       </c>
       <c r="AV243" s="7" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW243" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX243" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="244" ht="29.55" spans="1:50">
       <c r="A244" s="11">
-        <v>46177</v>
+        <v>46118</v>
       </c>
       <c r="B244" t="s">
         <v>64</v>
       </c>
       <c r="C244" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D244" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E244" s="8">
         <v>1</v>
@@ -38938,18 +38930,18 @@
         <v>84</v>
       </c>
       <c r="AV244" s="7" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW244" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX244" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="245" ht="29.55" spans="1:50">
       <c r="A245" s="11">
-        <v>46177</v>
+        <v>46118</v>
       </c>
       <c r="B245" t="s">
         <v>64</v>
@@ -38958,7 +38950,7 @@
         <v>79</v>
       </c>
       <c r="D245" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E245" s="8">
         <v>1</v>
@@ -39090,18 +39082,18 @@
         <v>84</v>
       </c>
       <c r="AV245" s="7" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW245" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX245" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="246" ht="29.55" spans="1:50">
       <c r="A246" s="11">
-        <v>46177</v>
+        <v>46118</v>
       </c>
       <c r="B246" t="s">
         <v>64</v>
@@ -39110,7 +39102,7 @@
         <v>73</v>
       </c>
       <c r="D246" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E246" s="8">
         <v>1</v>
@@ -39242,24 +39234,24 @@
         <v>84</v>
       </c>
       <c r="AV246" s="7" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="AW246" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX246" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="247" ht="29.55" spans="1:50">
       <c r="A247" s="11">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="B247" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D247" s="7" t="s">
         <v>53</v>
@@ -39391,30 +39383,30 @@
         <v>60</v>
       </c>
       <c r="AU247" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AV247" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="AW247" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX247" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="248" spans="1:50">
+      <c r="A248" s="12">
+        <v>46059</v>
+      </c>
+      <c r="B248" t="s">
+        <v>139</v>
+      </c>
+      <c r="C248" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D248" s="7" t="s">
         <v>165</v>
-      </c>
-    </row>
-    <row r="248" ht="15.15" spans="1:50">
-      <c r="A248" s="11">
-        <v>46175</v>
-      </c>
-      <c r="B248" t="s">
-        <v>141</v>
-      </c>
-      <c r="C248" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D248" s="7" t="s">
-        <v>168</v>
       </c>
       <c r="E248" s="8">
         <v>1</v>
@@ -39540,7 +39532,7 @@
         <v>16</v>
       </c>
       <c r="AT248" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU248" s="7" t="s">
         <v>55</v>
@@ -39552,21 +39544,21 @@
         <v>57</v>
       </c>
       <c r="AX248" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="249" ht="15.15" spans="1:50">
-      <c r="A249" s="11">
-        <v>46175</v>
+      <c r="A249" s="12">
+        <v>46059</v>
       </c>
       <c r="B249" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C249" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D249" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E249" s="8">
         <v>1</v>
@@ -39704,21 +39696,21 @@
         <v>57</v>
       </c>
       <c r="AX249" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="250" ht="15.15" spans="1:50">
-      <c r="A250" s="11">
-        <v>46175</v>
+      <c r="A250" s="12">
+        <v>46059</v>
       </c>
       <c r="B250" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C250" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D250" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E250" s="8">
         <v>1</v>
@@ -39844,7 +39836,7 @@
         <v>15</v>
       </c>
       <c r="AT250" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU250" s="7" t="s">
         <v>55</v>
@@ -39856,21 +39848,21 @@
         <v>57</v>
       </c>
       <c r="AX250" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="251" ht="15.15" spans="1:50">
-      <c r="A251" s="11">
-        <v>46175</v>
+      <c r="A251" s="12">
+        <v>46059</v>
       </c>
       <c r="B251" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C251" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D251" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E251" s="8">
         <v>1</v>
@@ -40008,21 +40000,21 @@
         <v>57</v>
       </c>
       <c r="AX251" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="252" ht="15.15" spans="1:50">
-      <c r="A252" s="11">
-        <v>46175</v>
+      <c r="A252" s="12">
+        <v>46059</v>
       </c>
       <c r="B252" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C252" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D252" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E252" s="8">
         <v>1</v>
@@ -40160,21 +40152,21 @@
         <v>57</v>
       </c>
       <c r="AX252" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="253" ht="15.15" spans="1:50">
-      <c r="A253" s="11">
-        <v>46175</v>
+      <c r="A253" s="12">
+        <v>46059</v>
       </c>
       <c r="B253" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C253" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D253" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E253" s="8">
         <v>1</v>
@@ -40300,7 +40292,7 @@
         <v>11</v>
       </c>
       <c r="AT253" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU253" s="7" t="s">
         <v>55</v>
@@ -40312,21 +40304,21 @@
         <v>57</v>
       </c>
       <c r="AX253" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="254" ht="15.15" spans="1:50">
-      <c r="A254" s="11">
-        <v>46175</v>
+      <c r="A254" s="12">
+        <v>46059</v>
       </c>
       <c r="B254" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C254" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D254" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E254" s="8">
         <v>1</v>
@@ -40464,12 +40456,12 @@
         <v>57</v>
       </c>
       <c r="AX254" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="255" ht="29.55" spans="1:50">
       <c r="A255" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B255" t="s">
         <v>82</v>
@@ -40511,7 +40503,7 @@
         <v>1031.78</v>
       </c>
       <c r="O255" s="8">
-        <v>8.52</v>
+        <v>30.672</v>
       </c>
       <c r="P255" s="8">
         <v>85.19</v>
@@ -40613,7 +40605,7 @@
         <v>113</v>
       </c>
       <c r="AW255" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AX255" s="7" t="s">
         <v>121</v>
@@ -40621,7 +40613,7 @@
     </row>
     <row r="256" ht="29.55" spans="1:50">
       <c r="A256" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B256" t="s">
         <v>82</v>
@@ -40663,7 +40655,7 @@
         <v>739.49</v>
       </c>
       <c r="O256" s="8">
-        <v>7.69</v>
+        <v>27.684</v>
       </c>
       <c r="P256" s="8">
         <v>76.95</v>
@@ -40765,7 +40757,7 @@
         <v>113</v>
       </c>
       <c r="AW256" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AX256" s="7" t="s">
         <v>121</v>
@@ -40773,13 +40765,13 @@
     </row>
     <row r="257" ht="29.55" spans="1:50">
       <c r="A257" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B257" t="s">
         <v>82</v>
       </c>
       <c r="C257" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D257" s="7" t="s">
         <v>53</v>
@@ -40815,7 +40807,7 @@
         <v>1111.64</v>
       </c>
       <c r="O257" s="8">
-        <v>7.82</v>
+        <v>28.152</v>
       </c>
       <c r="P257" s="8">
         <v>78.16</v>
@@ -40917,7 +40909,7 @@
         <v>113</v>
       </c>
       <c r="AW257" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AX257" s="7" t="s">
         <v>121</v>
@@ -40925,7 +40917,7 @@
     </row>
     <row r="258" ht="29.55" spans="1:50">
       <c r="A258" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B258" t="s">
         <v>82</v>
@@ -40967,7 +40959,7 @@
         <v>906.42</v>
       </c>
       <c r="O258" s="8">
-        <v>7.93</v>
+        <v>28.548</v>
       </c>
       <c r="P258" s="8">
         <v>79.25</v>
@@ -41069,7 +41061,7 @@
         <v>113</v>
       </c>
       <c r="AW258" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AX258" s="7" t="s">
         <v>121</v>
@@ -41077,7 +41069,7 @@
     </row>
     <row r="259" ht="29.55" spans="1:50">
       <c r="A259" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B259" t="s">
         <v>82</v>
@@ -41119,7 +41111,7 @@
         <v>1054.69</v>
       </c>
       <c r="O259" s="8">
-        <v>7.6</v>
+        <v>27.36</v>
       </c>
       <c r="P259" s="8">
         <v>76.03</v>
@@ -41221,7 +41213,7 @@
         <v>113</v>
       </c>
       <c r="AW259" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AX259" s="7" t="s">
         <v>121</v>
@@ -41229,7 +41221,7 @@
     </row>
     <row r="260" ht="29.55" spans="1:50">
       <c r="A260" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B260" t="s">
         <v>82</v>
@@ -41271,7 +41263,7 @@
         <v>1039.24</v>
       </c>
       <c r="O260" s="8">
-        <v>7.45</v>
+        <v>26.82</v>
       </c>
       <c r="P260" s="8">
         <v>74.5</v>
@@ -41373,7 +41365,7 @@
         <v>113</v>
       </c>
       <c r="AW260" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AX260" s="7" t="s">
         <v>121</v>
@@ -41381,13 +41373,13 @@
     </row>
     <row r="261" ht="29.55" spans="1:50">
       <c r="A261" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B261" t="s">
         <v>82</v>
       </c>
       <c r="C261" s="7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D261" s="7" t="s">
         <v>53</v>
@@ -41423,7 +41415,7 @@
         <v>1283.41</v>
       </c>
       <c r="O261" s="8">
-        <v>7.65</v>
+        <v>27.54</v>
       </c>
       <c r="P261" s="8">
         <v>76.55</v>
@@ -41525,7 +41517,7 @@
         <v>113</v>
       </c>
       <c r="AW261" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AX261" s="7" t="s">
         <v>121</v>
@@ -41533,7 +41525,7 @@
     </row>
     <row r="262" ht="29.55" spans="1:50">
       <c r="A262" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B262" t="s">
         <v>82</v>
@@ -41575,7 +41567,7 @@
         <v>915.12</v>
       </c>
       <c r="O262" s="8">
-        <v>7.54</v>
+        <v>27.144</v>
       </c>
       <c r="P262" s="8">
         <v>75.41</v>
@@ -41677,7 +41669,7 @@
         <v>113</v>
       </c>
       <c r="AW262" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AX262" s="7" t="s">
         <v>121</v>
@@ -41685,7 +41677,7 @@
     </row>
     <row r="263" ht="29.55" spans="1:50">
       <c r="A263" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B263" t="s">
         <v>82</v>
@@ -41727,7 +41719,7 @@
         <v>1014.31</v>
       </c>
       <c r="O263" s="8">
-        <v>7.43</v>
+        <v>26.748</v>
       </c>
       <c r="P263" s="8">
         <v>74.29</v>
@@ -41829,7 +41821,7 @@
         <v>113</v>
       </c>
       <c r="AW263" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AX263" s="7" t="s">
         <v>121</v>
@@ -41837,13 +41829,13 @@
     </row>
     <row r="264" ht="29.55" spans="1:50">
       <c r="A264" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B264" t="s">
         <v>82</v>
       </c>
       <c r="C264" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D264" s="7" t="s">
         <v>53</v>
@@ -41879,7 +41871,7 @@
         <v>805.74</v>
       </c>
       <c r="O264" s="8">
-        <v>7.59</v>
+        <v>27.324</v>
       </c>
       <c r="P264" s="8">
         <v>75.9</v>
@@ -41981,7 +41973,7 @@
         <v>113</v>
       </c>
       <c r="AW264" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AX264" s="7" t="s">
         <v>121</v>
@@ -42031,7 +42023,7 @@
         <v>485.49</v>
       </c>
       <c r="O265" s="8">
-        <v>7.83</v>
+        <v>28.188</v>
       </c>
       <c r="P265" s="8">
         <v>78.34</v>
@@ -42136,7 +42128,7 @@
         <v>57</v>
       </c>
       <c r="AX265" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="266" ht="15.15" spans="1:50">
@@ -42183,7 +42175,7 @@
         <v>465.85</v>
       </c>
       <c r="O266" s="8">
-        <v>7.03</v>
+        <v>25.308</v>
       </c>
       <c r="P266" s="8">
         <v>70.26</v>
@@ -42288,7 +42280,7 @@
         <v>57</v>
       </c>
       <c r="AX266" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="267" ht="15.15" spans="1:50">
@@ -42335,7 +42327,7 @@
         <v>563.29</v>
       </c>
       <c r="O267" s="8">
-        <v>7.26</v>
+        <v>26.136</v>
       </c>
       <c r="P267" s="8">
         <v>72.63</v>
@@ -42440,7 +42432,7 @@
         <v>57</v>
       </c>
       <c r="AX267" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="268" ht="15.15" spans="1:50">
@@ -42487,7 +42479,7 @@
         <v>521.46</v>
       </c>
       <c r="O268" s="8">
-        <v>5.98</v>
+        <v>21.528</v>
       </c>
       <c r="P268" s="8">
         <v>59.76</v>
@@ -42592,7 +42584,7 @@
         <v>57</v>
       </c>
       <c r="AX268" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="269" ht="15.15" spans="1:50">
@@ -42639,7 +42631,7 @@
         <v>532.35</v>
       </c>
       <c r="O269" s="8">
-        <v>7.1</v>
+        <v>25.56</v>
       </c>
       <c r="P269" s="8">
         <v>70.97</v>
@@ -42744,7 +42736,7 @@
         <v>57</v>
       </c>
       <c r="AX269" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="270" ht="15.15" spans="1:50">
@@ -42791,7 +42783,7 @@
         <v>715.92</v>
       </c>
       <c r="O270" s="8">
-        <v>7.97</v>
+        <v>28.692</v>
       </c>
       <c r="P270" s="8">
         <v>79.66</v>
@@ -42896,7 +42888,7 @@
         <v>57</v>
       </c>
       <c r="AX270" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="271" ht="15.15" spans="1:50">
@@ -42943,7 +42935,7 @@
         <v>402.54</v>
       </c>
       <c r="O271" s="8">
-        <v>6.5</v>
+        <v>23.4</v>
       </c>
       <c r="P271" s="8">
         <v>65.05</v>
@@ -43048,7 +43040,7 @@
         <v>57</v>
       </c>
       <c r="AX271" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="272" ht="15.15" spans="1:50">
@@ -43095,7 +43087,7 @@
         <v>450.81</v>
       </c>
       <c r="O272" s="8">
-        <v>6.93</v>
+        <v>24.948</v>
       </c>
       <c r="P272" s="8">
         <v>69.32</v>
@@ -43200,7 +43192,7 @@
         <v>57</v>
       </c>
       <c r="AX272" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="273" ht="15.15" spans="1:50">
@@ -43247,7 +43239,7 @@
         <v>474.97</v>
       </c>
       <c r="O273" s="8">
-        <v>6.87</v>
+        <v>24.732</v>
       </c>
       <c r="P273" s="8">
         <v>68.72</v>
@@ -43352,12 +43344,12 @@
         <v>57</v>
       </c>
       <c r="AX273" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="274" ht="15.15" spans="1:50">
       <c r="A274" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B274" t="s">
         <v>124</v>
@@ -43366,7 +43358,7 @@
         <v>114</v>
       </c>
       <c r="D274" s="7" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E274" s="8">
         <v>1</v>
@@ -43398,7 +43390,7 @@
       <c r="N274" s="8">
         <v>710.24</v>
       </c>
-      <c r="O274" s="12">
+      <c r="O274" s="13">
         <v>28.01</v>
       </c>
       <c r="P274" s="8">
@@ -43495,7 +43487,7 @@
         <v>60</v>
       </c>
       <c r="AU274" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV274" s="7" t="s">
         <v>113</v>
@@ -43509,7 +43501,7 @@
     </row>
     <row r="275" ht="15.15" spans="1:50">
       <c r="A275" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B275" t="s">
         <v>124</v>
@@ -43518,7 +43510,7 @@
         <v>125</v>
       </c>
       <c r="D275" s="7" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E275" s="8">
         <v>1</v>
@@ -43550,7 +43542,7 @@
       <c r="N275" s="8">
         <v>542.81</v>
       </c>
-      <c r="O275" s="12">
+      <c r="O275" s="13">
         <v>28.8</v>
       </c>
       <c r="P275" s="8">
@@ -43647,7 +43639,7 @@
         <v>54</v>
       </c>
       <c r="AU275" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV275" s="7" t="s">
         <v>113</v>
@@ -43661,16 +43653,16 @@
     </row>
     <row r="276" ht="15.15" spans="1:50">
       <c r="A276" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B276" t="s">
         <v>124</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D276" s="7" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E276" s="8">
         <v>1</v>
@@ -43702,7 +43694,7 @@
       <c r="N276" s="8">
         <v>513.13</v>
       </c>
-      <c r="O276" s="12">
+      <c r="O276" s="13">
         <v>28.94</v>
       </c>
       <c r="P276" s="8">
@@ -43799,7 +43791,7 @@
         <v>131</v>
       </c>
       <c r="AU276" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV276" s="7" t="s">
         <v>113</v>
@@ -43813,7 +43805,7 @@
     </row>
     <row r="277" ht="15.15" spans="1:50">
       <c r="A277" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B277" t="s">
         <v>124</v>
@@ -43822,7 +43814,7 @@
         <v>127</v>
       </c>
       <c r="D277" s="7" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E277" s="8">
         <v>1</v>
@@ -43854,7 +43846,7 @@
       <c r="N277" s="8">
         <v>601.16</v>
       </c>
-      <c r="O277" s="12">
+      <c r="O277" s="13">
         <v>27.61</v>
       </c>
       <c r="P277" s="8">
@@ -43951,7 +43943,7 @@
         <v>54</v>
       </c>
       <c r="AU277" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV277" s="7" t="s">
         <v>113</v>
@@ -43965,7 +43957,7 @@
     </row>
     <row r="278" ht="15.15" spans="1:50">
       <c r="A278" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B278" t="s">
         <v>124</v>
@@ -43974,7 +43966,7 @@
         <v>128</v>
       </c>
       <c r="D278" s="7" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E278" s="8">
         <v>1</v>
@@ -44006,7 +43998,7 @@
       <c r="N278" s="8">
         <v>589.57</v>
       </c>
-      <c r="O278" s="12">
+      <c r="O278" s="13">
         <v>26.86</v>
       </c>
       <c r="P278" s="8">
@@ -44103,7 +44095,7 @@
         <v>54</v>
       </c>
       <c r="AU278" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV278" s="7" t="s">
         <v>113</v>
@@ -44117,7 +44109,7 @@
     </row>
     <row r="279" ht="15.15" spans="1:50">
       <c r="A279" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B279" t="s">
         <v>124</v>
@@ -44126,7 +44118,7 @@
         <v>129</v>
       </c>
       <c r="D279" s="7" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E279" s="8">
         <v>1</v>
@@ -44158,7 +44150,7 @@
       <c r="N279" s="8">
         <v>609.41</v>
       </c>
-      <c r="O279" s="12">
+      <c r="O279" s="13">
         <v>32</v>
       </c>
       <c r="P279" s="8">
@@ -44255,7 +44247,7 @@
         <v>75</v>
       </c>
       <c r="AU279" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV279" s="7" t="s">
         <v>113</v>
@@ -44269,16 +44261,16 @@
     </row>
     <row r="280" ht="15.15" spans="1:50">
       <c r="A280" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B280" t="s">
         <v>124</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D280" s="7" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E280" s="8">
         <v>1</v>
@@ -44310,7 +44302,7 @@
       <c r="N280" s="8">
         <v>647.08</v>
       </c>
-      <c r="O280" s="12">
+      <c r="O280" s="13">
         <v>27.97</v>
       </c>
       <c r="P280" s="8">
@@ -44407,7 +44399,7 @@
         <v>63</v>
       </c>
       <c r="AU280" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV280" s="7" t="s">
         <v>113</v>
@@ -44421,16 +44413,16 @@
     </row>
     <row r="281" ht="15.15" spans="1:50">
       <c r="A281" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B281" t="s">
         <v>124</v>
       </c>
       <c r="C281" s="7" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D281" s="7" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E281" s="8">
         <v>1</v>
@@ -44462,7 +44454,7 @@
       <c r="N281" s="8">
         <v>583.46</v>
       </c>
-      <c r="O281" s="12">
+      <c r="O281" s="13">
         <v>26.57</v>
       </c>
       <c r="P281" s="8">
@@ -44559,7 +44551,7 @@
         <v>131</v>
       </c>
       <c r="AU281" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV281" s="7" t="s">
         <v>113</v>
@@ -44573,16 +44565,16 @@
     </row>
     <row r="282" ht="15.15" spans="1:50">
       <c r="A282" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B282" t="s">
         <v>124</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D282" s="7" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E282" s="8">
         <v>1</v>
@@ -44614,7 +44606,7 @@
       <c r="N282" s="8">
         <v>620.32</v>
       </c>
-      <c r="O282" s="12">
+      <c r="O282" s="13">
         <v>26.35</v>
       </c>
       <c r="P282" s="8">
@@ -44711,7 +44703,7 @@
         <v>54</v>
       </c>
       <c r="AU282" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV282" s="7" t="s">
         <v>113</v>
@@ -44725,7 +44717,7 @@
     </row>
     <row r="283" ht="15.15" spans="1:50">
       <c r="A283" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B283" t="s">
         <v>124</v>
@@ -44734,7 +44726,7 @@
         <v>134</v>
       </c>
       <c r="D283" s="7" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E283" s="8">
         <v>1</v>
@@ -44766,7 +44758,7 @@
       <c r="N283" s="8">
         <v>545.14</v>
       </c>
-      <c r="O283" s="12">
+      <c r="O283" s="13">
         <v>29.63</v>
       </c>
       <c r="P283" s="8">
@@ -44863,7 +44855,7 @@
         <v>63</v>
       </c>
       <c r="AU283" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV283" s="7" t="s">
         <v>113</v>
@@ -44877,7 +44869,7 @@
     </row>
     <row r="284" ht="29.55" spans="1:50">
       <c r="A284" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B284" t="s">
         <v>124</v>
@@ -44886,7 +44878,7 @@
         <v>134</v>
       </c>
       <c r="D284" s="7" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E284" s="8">
         <v>2</v>
@@ -44918,7 +44910,7 @@
       <c r="N284" s="8">
         <v>415.81</v>
       </c>
-      <c r="O284" s="12">
+      <c r="O284" s="13">
         <v>31.21</v>
       </c>
       <c r="P284" s="8">
@@ -45015,7 +45007,7 @@
         <v>63</v>
       </c>
       <c r="AU284" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV284" s="7" t="s">
         <v>113</v>
@@ -45029,7 +45021,7 @@
     </row>
     <row r="285" ht="15.15" spans="1:50">
       <c r="A285" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B285" t="s">
         <v>124</v>
@@ -45038,7 +45030,7 @@
         <v>128</v>
       </c>
       <c r="D285" s="7" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E285" s="8">
         <v>2</v>
@@ -45070,7 +45062,7 @@
       <c r="N285" s="8">
         <v>470.48</v>
       </c>
-      <c r="O285" s="12">
+      <c r="O285" s="13">
         <v>25.27</v>
       </c>
       <c r="P285" s="8">
@@ -45167,7 +45159,7 @@
         <v>54</v>
       </c>
       <c r="AU285" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV285" s="7" t="s">
         <v>113</v>
@@ -45181,7 +45173,7 @@
     </row>
     <row r="286" ht="15.15" spans="1:50">
       <c r="A286" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B286" t="s">
         <v>124</v>
@@ -45190,7 +45182,7 @@
         <v>125</v>
       </c>
       <c r="D286" s="7" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E286" s="8">
         <v>2</v>
@@ -45222,7 +45214,7 @@
       <c r="N286" s="8">
         <v>499.44</v>
       </c>
-      <c r="O286" s="12">
+      <c r="O286" s="13">
         <v>28.87</v>
       </c>
       <c r="P286" s="8">
@@ -45319,7 +45311,7 @@
         <v>54</v>
       </c>
       <c r="AU286" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV286" s="7" t="s">
         <v>113</v>
@@ -45333,7 +45325,7 @@
     </row>
     <row r="287" ht="15.15" spans="1:50">
       <c r="A287" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B287" t="s">
         <v>124</v>
@@ -45342,7 +45334,7 @@
         <v>127</v>
       </c>
       <c r="D287" s="7" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E287" s="8">
         <v>2</v>
@@ -45374,7 +45366,7 @@
       <c r="N287" s="8">
         <v>599.21</v>
       </c>
-      <c r="O287" s="12">
+      <c r="O287" s="13">
         <v>28.04</v>
       </c>
       <c r="P287" s="8">
@@ -45471,7 +45463,7 @@
         <v>75</v>
       </c>
       <c r="AU287" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV287" s="7" t="s">
         <v>113</v>
@@ -45485,7 +45477,7 @@
     </row>
     <row r="288" ht="15.15" spans="1:50">
       <c r="A288" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B288" t="s">
         <v>124</v>
@@ -45494,7 +45486,7 @@
         <v>129</v>
       </c>
       <c r="D288" s="7" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E288" s="8">
         <v>2</v>
@@ -45526,7 +45518,7 @@
       <c r="N288" s="8">
         <v>611.44</v>
       </c>
-      <c r="O288" s="12">
+      <c r="O288" s="13">
         <v>29.56</v>
       </c>
       <c r="P288" s="8">
@@ -45623,7 +45615,7 @@
         <v>75</v>
       </c>
       <c r="AU288" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV288" s="7" t="s">
         <v>113</v>
@@ -45637,16 +45629,16 @@
     </row>
     <row r="289" ht="15.15" spans="1:50">
       <c r="A289" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B289" t="s">
         <v>124</v>
       </c>
       <c r="C289" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D289" s="7" t="s">
         <v>178</v>
-      </c>
-      <c r="D289" s="7" t="s">
-        <v>182</v>
       </c>
       <c r="E289" s="8">
         <v>2</v>
@@ -45678,7 +45670,7 @@
       <c r="N289" s="8">
         <v>625.56</v>
       </c>
-      <c r="O289" s="12">
+      <c r="O289" s="13">
         <v>25.52</v>
       </c>
       <c r="P289" s="8">
@@ -45775,7 +45767,7 @@
         <v>131</v>
       </c>
       <c r="AU289" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV289" s="7" t="s">
         <v>113</v>
@@ -45789,16 +45781,16 @@
     </row>
     <row r="290" ht="15.15" spans="1:50">
       <c r="A290" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B290" t="s">
         <v>124</v>
       </c>
       <c r="C290" s="7" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D290" s="7" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E290" s="8">
         <v>2</v>
@@ -45830,7 +45822,7 @@
       <c r="N290" s="8">
         <v>589.47</v>
       </c>
-      <c r="O290" s="12">
+      <c r="O290" s="13">
         <v>28.51</v>
       </c>
       <c r="P290" s="8">
@@ -45927,7 +45919,7 @@
         <v>54</v>
       </c>
       <c r="AU290" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV290" s="7" t="s">
         <v>113</v>
@@ -45941,7 +45933,7 @@
     </row>
     <row r="291" ht="15.15" spans="1:50">
       <c r="A291" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B291" t="s">
         <v>124</v>
@@ -45950,7 +45942,7 @@
         <v>114</v>
       </c>
       <c r="D291" s="7" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E291" s="8">
         <v>2</v>
@@ -45982,7 +45974,7 @@
       <c r="N291" s="8">
         <v>505.87</v>
       </c>
-      <c r="O291" s="12">
+      <c r="O291" s="13">
         <v>27.76</v>
       </c>
       <c r="P291" s="8">
@@ -46079,7 +46071,7 @@
         <v>75</v>
       </c>
       <c r="AU291" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV291" s="7" t="s">
         <v>113</v>
@@ -46093,16 +46085,16 @@
     </row>
     <row r="292" ht="29.55" spans="1:50">
       <c r="A292" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B292" t="s">
         <v>124</v>
       </c>
       <c r="C292" s="7" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D292" s="7" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E292" s="8">
         <v>2</v>
@@ -46134,7 +46126,7 @@
       <c r="N292" s="8">
         <v>444.99</v>
       </c>
-      <c r="O292" s="12">
+      <c r="O292" s="13">
         <v>28.84</v>
       </c>
       <c r="P292" s="8">
@@ -46231,7 +46223,7 @@
         <v>131</v>
       </c>
       <c r="AU292" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV292" s="7" t="s">
         <v>113</v>
@@ -46245,16 +46237,16 @@
     </row>
     <row r="293" ht="15.15" spans="1:50">
       <c r="A293" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B293" t="s">
         <v>124</v>
       </c>
       <c r="C293" s="7" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D293" s="7" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E293" s="8">
         <v>2</v>
@@ -46286,7 +46278,7 @@
       <c r="N293" s="8">
         <v>208.95</v>
       </c>
-      <c r="O293" s="12">
+      <c r="O293" s="13">
         <v>26.46</v>
       </c>
       <c r="P293" s="8">
@@ -46383,7 +46375,7 @@
         <v>63</v>
       </c>
       <c r="AU293" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV293" s="7" t="s">
         <v>113</v>
@@ -46397,16 +46389,16 @@
     </row>
     <row r="294" ht="29.55" spans="1:50">
       <c r="A294" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B294" t="s">
         <v>124</v>
       </c>
       <c r="C294" s="7" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D294" s="7" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E294" s="8">
         <v>1</v>
@@ -46438,7 +46430,7 @@
       <c r="N294" s="8">
         <v>420.47</v>
       </c>
-      <c r="O294" s="12">
+      <c r="O294" s="13">
         <v>30.06</v>
       </c>
       <c r="P294" s="8">
@@ -46535,7 +46527,7 @@
         <v>63</v>
       </c>
       <c r="AU294" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV294" s="7" t="s">
         <v>113</v>
@@ -46549,16 +46541,16 @@
     </row>
     <row r="295" ht="15.15" spans="1:50">
       <c r="A295" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B295" t="s">
         <v>124</v>
       </c>
       <c r="C295" s="7" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D295" s="7" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E295" s="8">
         <v>1</v>
@@ -46590,7 +46582,7 @@
       <c r="N295" s="8">
         <v>174.73</v>
       </c>
-      <c r="O295" s="12">
+      <c r="O295" s="13">
         <v>26.68</v>
       </c>
       <c r="P295" s="8">
@@ -46687,7 +46679,7 @@
         <v>60</v>
       </c>
       <c r="AU295" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV295" s="7" t="s">
         <v>113</v>
@@ -46701,16 +46693,16 @@
     </row>
     <row r="296" ht="15.15" spans="1:50">
       <c r="A296" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B296" t="s">
         <v>124</v>
       </c>
       <c r="C296" s="7" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D296" s="7" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E296" s="8">
         <v>1</v>
@@ -46742,7 +46734,7 @@
       <c r="N296" s="8">
         <v>85.2</v>
       </c>
-      <c r="O296" s="12">
+      <c r="O296" s="13">
         <v>22.14</v>
       </c>
       <c r="P296" s="8">
@@ -46839,7 +46831,7 @@
         <v>131</v>
       </c>
       <c r="AU296" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV296" s="7" t="s">
         <v>113</v>
@@ -46853,16 +46845,16 @@
     </row>
     <row r="297" ht="15.15" spans="1:50">
       <c r="A297" s="8" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B297" t="s">
         <v>124</v>
       </c>
       <c r="C297" s="7" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D297" s="7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E297" s="8">
         <v>1</v>
@@ -46894,7 +46886,7 @@
       <c r="N297" s="8">
         <v>77.57</v>
       </c>
-      <c r="O297" s="12">
+      <c r="O297" s="13">
         <v>27.47</v>
       </c>
       <c r="P297" s="8">
@@ -46991,7 +46983,7 @@
         <v>60</v>
       </c>
       <c r="AU297" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AV297" s="7" t="s">
         <v>113</v>
@@ -47004,17 +46996,17 @@
       </c>
     </row>
     <row r="298" ht="29.55" spans="1:50">
-      <c r="A298" s="13">
+      <c r="A298" s="14">
         <v>46028</v>
       </c>
       <c r="B298" t="s">
         <v>124</v>
       </c>
       <c r="C298" s="7" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D298" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E298" s="8">
         <v>1</v>
@@ -47047,7 +47039,7 @@
         <v>490.24</v>
       </c>
       <c r="O298" s="8">
-        <v>6.58</v>
+        <v>23.688</v>
       </c>
       <c r="P298" s="8">
         <v>65.83</v>
@@ -47146,27 +47138,27 @@
         <v>135</v>
       </c>
       <c r="AV298" s="7" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="AW298" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX298" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="299" ht="29.55" spans="1:50">
-      <c r="A299" s="13">
+      <c r="A299" s="14">
         <v>46028</v>
       </c>
       <c r="B299" t="s">
         <v>124</v>
       </c>
       <c r="C299" s="7" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D299" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E299" s="8">
         <v>1</v>
@@ -47199,7 +47191,7 @@
         <v>412.61</v>
       </c>
       <c r="O299" s="8">
-        <v>7.01</v>
+        <v>25.236</v>
       </c>
       <c r="P299" s="8">
         <v>70.07</v>
@@ -47298,27 +47290,27 @@
         <v>135</v>
       </c>
       <c r="AV299" s="7" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="AW299" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX299" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="300" ht="29.55" spans="1:50">
-      <c r="A300" s="13">
+      <c r="A300" s="14">
         <v>46028</v>
       </c>
       <c r="B300" t="s">
         <v>124</v>
       </c>
       <c r="C300" s="7" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D300" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E300" s="8">
         <v>1</v>
@@ -47351,7 +47343,7 @@
         <v>412.02</v>
       </c>
       <c r="O300" s="8">
-        <v>6.51</v>
+        <v>23.436</v>
       </c>
       <c r="P300" s="8">
         <v>65.06</v>
@@ -47450,17 +47442,17 @@
         <v>135</v>
       </c>
       <c r="AV300" s="7" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="AW300" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX300" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="301" ht="29.55" spans="1:50">
-      <c r="A301" s="13">
+      <c r="A301" s="14">
         <v>46028</v>
       </c>
       <c r="B301" t="s">
@@ -47470,7 +47462,7 @@
         <v>130</v>
       </c>
       <c r="D301" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E301" s="8">
         <v>1</v>
@@ -47503,7 +47495,7 @@
         <v>423.85</v>
       </c>
       <c r="O301" s="8">
-        <v>6.93</v>
+        <v>24.948</v>
       </c>
       <c r="P301" s="8">
         <v>69.32</v>
@@ -47602,27 +47594,27 @@
         <v>135</v>
       </c>
       <c r="AV301" s="7" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="AW301" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX301" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="302" ht="29.55" spans="1:50">
-      <c r="A302" s="13">
+      <c r="A302" s="14">
         <v>46028</v>
       </c>
       <c r="B302" t="s">
         <v>124</v>
       </c>
       <c r="C302" s="7" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D302" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E302" s="8">
         <v>1</v>
@@ -47655,7 +47647,7 @@
         <v>424.3</v>
       </c>
       <c r="O302" s="8">
-        <v>6.43</v>
+        <v>23.148</v>
       </c>
       <c r="P302" s="8">
         <v>64.34</v>
@@ -47754,17 +47746,17 @@
         <v>135</v>
       </c>
       <c r="AV302" s="7" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="AW302" s="7" t="s">
         <v>57</v>
       </c>
       <c r="AX302" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="303" ht="15.15" spans="1:50">
-      <c r="A303" s="13">
+      <c r="A303" s="14">
         <v>46059</v>
       </c>
       <c r="B303" t="s">
@@ -47774,7 +47766,7 @@
         <v>128</v>
       </c>
       <c r="D303" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E303" s="8">
         <v>1</v>
@@ -47807,7 +47799,7 @@
         <v>6.72</v>
       </c>
       <c r="O303" s="8">
-        <v>0.51</v>
+        <v>1.836</v>
       </c>
       <c r="P303" s="8">
         <v>5.15</v>
@@ -47912,11 +47904,11 @@
         <v>57</v>
       </c>
       <c r="AX303" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="304" ht="15.15" spans="1:50">
-      <c r="A304" s="13">
+      <c r="A304" s="14">
         <v>46059</v>
       </c>
       <c r="B304" t="s">
@@ -47926,7 +47918,7 @@
         <v>129</v>
       </c>
       <c r="D304" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E304" s="8">
         <v>1</v>
@@ -47959,7 +47951,7 @@
         <v>6.73</v>
       </c>
       <c r="O304" s="8">
-        <v>0.32</v>
+        <v>1.152</v>
       </c>
       <c r="P304" s="8">
         <v>3.17</v>
@@ -48064,11 +48056,11 @@
         <v>57</v>
       </c>
       <c r="AX304" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="305" ht="15.15" spans="1:50">
-      <c r="A305" s="13">
+      <c r="A305" s="14">
         <v>46059</v>
       </c>
       <c r="B305" t="s">
@@ -48078,7 +48070,7 @@
         <v>130</v>
       </c>
       <c r="D305" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E305" s="8">
         <v>1</v>
@@ -48111,7 +48103,7 @@
         <v>6.38</v>
       </c>
       <c r="O305" s="8">
-        <v>1.39</v>
+        <v>5.004</v>
       </c>
       <c r="P305" s="8">
         <v>13.86</v>
@@ -48216,21 +48208,21 @@
         <v>57</v>
       </c>
       <c r="AX305" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="306" ht="15.15" spans="1:50">
-      <c r="A306" s="13">
+      <c r="A306" s="14">
         <v>46059</v>
       </c>
       <c r="B306" t="s">
         <v>124</v>
       </c>
       <c r="C306" s="7" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D306" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E306" s="8">
         <v>1</v>
@@ -48368,11 +48360,11 @@
         <v>57</v>
       </c>
       <c r="AX306" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="307" ht="15.15" spans="1:50">
-      <c r="A307" s="13">
+      <c r="A307" s="14">
         <v>46059</v>
       </c>
       <c r="B307" t="s">
@@ -48382,7 +48374,7 @@
         <v>134</v>
       </c>
       <c r="D307" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E307" s="8">
         <v>1</v>
@@ -48415,7 +48407,7 @@
         <v>6.6</v>
       </c>
       <c r="O307" s="8">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="P307" s="8">
         <v>1.03</v>
@@ -48520,11 +48512,11 @@
         <v>57</v>
       </c>
       <c r="AX307" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="308" ht="29.55" spans="1:50">
-      <c r="A308" s="13">
+      <c r="A308" s="14">
         <v>46118</v>
       </c>
       <c r="B308" t="s">
@@ -48534,7 +48526,7 @@
         <v>125</v>
       </c>
       <c r="D308" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E308" s="8">
         <v>1</v>
@@ -48567,7 +48559,7 @@
         <v>555.96</v>
       </c>
       <c r="O308" s="8">
-        <v>7.05</v>
+        <v>25.38</v>
       </c>
       <c r="P308" s="8">
         <v>70.54</v>
@@ -48672,11 +48664,11 @@
         <v>57</v>
       </c>
       <c r="AX308" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="309" ht="29.55" spans="1:50">
-      <c r="A309" s="13">
+      <c r="A309" s="14">
         <v>46118</v>
       </c>
       <c r="B309" t="s">
@@ -48686,7 +48678,7 @@
         <v>127</v>
       </c>
       <c r="D309" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E309" s="8">
         <v>1</v>
@@ -48719,7 +48711,7 @@
         <v>513.16</v>
       </c>
       <c r="O309" s="8">
-        <v>7.64</v>
+        <v>27.504</v>
       </c>
       <c r="P309" s="8">
         <v>76.37</v>
@@ -48824,11 +48816,11 @@
         <v>57</v>
       </c>
       <c r="AX309" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="310" ht="29.55" spans="1:50">
-      <c r="A310" s="13">
+      <c r="A310" s="14">
         <v>46118</v>
       </c>
       <c r="B310" t="s">
@@ -48838,7 +48830,7 @@
         <v>128</v>
       </c>
       <c r="D310" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E310" s="8">
         <v>1</v>
@@ -48871,7 +48863,7 @@
         <v>523.16</v>
       </c>
       <c r="O310" s="8">
-        <v>6.64</v>
+        <v>23.904</v>
       </c>
       <c r="P310" s="8">
         <v>66.45</v>
@@ -48976,11 +48968,11 @@
         <v>57</v>
       </c>
       <c r="AX310" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="311" ht="29.55" spans="1:50">
-      <c r="A311" s="13">
+      <c r="A311" s="14">
         <v>46118</v>
       </c>
       <c r="B311" t="s">
@@ -48990,7 +48982,7 @@
         <v>129</v>
       </c>
       <c r="D311" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E311" s="8">
         <v>1</v>
@@ -49023,7 +49015,7 @@
         <v>447.89</v>
       </c>
       <c r="O311" s="8">
-        <v>8.15</v>
+        <v>29.34</v>
       </c>
       <c r="P311" s="8">
         <v>81.49</v>
@@ -49128,11 +49120,11 @@
         <v>57</v>
       </c>
       <c r="AX311" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="312" ht="29.55" spans="1:50">
-      <c r="A312" s="13">
+      <c r="A312" s="14">
         <v>46118</v>
       </c>
       <c r="B312" t="s">
@@ -49142,7 +49134,7 @@
         <v>130</v>
       </c>
       <c r="D312" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E312" s="8">
         <v>1</v>
@@ -49175,7 +49167,7 @@
         <v>474.17</v>
       </c>
       <c r="O312" s="8">
-        <v>7.91</v>
+        <v>28.476</v>
       </c>
       <c r="P312" s="8">
         <v>79.09</v>
@@ -49280,21 +49272,21 @@
         <v>57</v>
       </c>
       <c r="AX312" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="313" ht="29.55" spans="1:50">
-      <c r="A313" s="13">
+      <c r="A313" s="14">
         <v>46118</v>
       </c>
       <c r="B313" t="s">
         <v>124</v>
       </c>
       <c r="C313" s="7" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D313" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E313" s="8">
         <v>1</v>
@@ -49327,7 +49319,7 @@
         <v>585.18</v>
       </c>
       <c r="O313" s="8">
-        <v>6.8</v>
+        <v>24.48</v>
       </c>
       <c r="P313" s="8">
         <v>67.99</v>
@@ -49432,11 +49424,11 @@
         <v>57</v>
       </c>
       <c r="AX313" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="314" ht="29.55" spans="1:50">
-      <c r="A314" s="13">
+      <c r="A314" s="14">
         <v>46118</v>
       </c>
       <c r="B314" t="s">
@@ -49446,7 +49438,7 @@
         <v>134</v>
       </c>
       <c r="D314" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E314" s="8">
         <v>1</v>
@@ -49479,7 +49471,7 @@
         <v>446.66</v>
       </c>
       <c r="O314" s="8">
-        <v>7.71</v>
+        <v>27.756</v>
       </c>
       <c r="P314" s="8">
         <v>77.13</v>
@@ -49584,11 +49576,11 @@
         <v>57</v>
       </c>
       <c r="AX314" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="315" ht="29.55" spans="1:50">
-      <c r="A315" s="14">
+      <c r="A315" s="15">
         <v>46271</v>
       </c>
       <c r="B315" t="s">
@@ -49598,7 +49590,7 @@
         <v>77</v>
       </c>
       <c r="D315" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E315" s="8">
         <v>1</v>
@@ -49736,11 +49728,11 @@
         <v>57</v>
       </c>
       <c r="AX315" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="316" ht="29.55" spans="1:50">
-      <c r="A316" s="14">
+      <c r="A316" s="15">
         <v>46271</v>
       </c>
       <c r="B316" t="s">
@@ -49750,7 +49742,7 @@
         <v>52</v>
       </c>
       <c r="D316" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E316" s="8">
         <v>1</v>
@@ -49888,11 +49880,11 @@
         <v>57</v>
       </c>
       <c r="AX316" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="317" ht="29.55" spans="1:50">
-      <c r="A317" s="14">
+      <c r="A317" s="15">
         <v>46271</v>
       </c>
       <c r="B317" t="s">
@@ -49902,7 +49894,7 @@
         <v>59</v>
       </c>
       <c r="D317" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E317" s="8">
         <v>1</v>
@@ -50040,11 +50032,11 @@
         <v>57</v>
       </c>
       <c r="AX317" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="318" ht="29.55" spans="1:50">
-      <c r="A318" s="14">
+      <c r="A318" s="15">
         <v>46271</v>
       </c>
       <c r="B318" t="s">
@@ -50054,7 +50046,7 @@
         <v>61</v>
       </c>
       <c r="D318" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E318" s="8">
         <v>1</v>
@@ -50192,21 +50184,21 @@
         <v>57</v>
       </c>
       <c r="AX318" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="319" ht="29.55" spans="1:50">
-      <c r="A319" s="14">
+      <c r="A319" s="15">
         <v>46271</v>
       </c>
       <c r="B319" t="s">
         <v>64</v>
       </c>
       <c r="C319" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D319" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E319" s="8">
         <v>1</v>
@@ -50344,11 +50336,11 @@
         <v>57</v>
       </c>
       <c r="AX319" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="320" ht="29.55" spans="1:50">
-      <c r="A320" s="14">
+      <c r="A320" s="15">
         <v>46271</v>
       </c>
       <c r="B320" t="s">
@@ -50358,7 +50350,7 @@
         <v>79</v>
       </c>
       <c r="D320" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E320" s="8">
         <v>1</v>
@@ -50496,11 +50488,11 @@
         <v>57</v>
       </c>
       <c r="AX320" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="321" ht="29.55" spans="1:50">
-      <c r="A321" s="14">
+      <c r="A321" s="15">
         <v>46271</v>
       </c>
       <c r="B321" t="s">
@@ -50510,7 +50502,7 @@
         <v>73</v>
       </c>
       <c r="D321" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E321" s="8">
         <v>1</v>
@@ -50648,11 +50640,11 @@
         <v>57</v>
       </c>
       <c r="AX321" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="322" ht="15.15" spans="1:50">
-      <c r="A322" s="14">
+      <c r="A322" s="15">
         <v>46148</v>
       </c>
       <c r="B322" t="s">
@@ -50695,7 +50687,7 @@
         <v>877.1</v>
       </c>
       <c r="O322" s="8">
-        <v>7.3</v>
+        <v>26.28</v>
       </c>
       <c r="P322" s="8">
         <v>73.03</v>
@@ -50791,7 +50783,7 @@
         <v>63</v>
       </c>
       <c r="AU322" s="7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AV322" s="7" t="s">
         <v>113</v>
@@ -50800,11 +50792,11 @@
         <v>57</v>
       </c>
       <c r="AX322" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="323" ht="15.15" spans="1:50">
-      <c r="A323" s="14">
+      <c r="A323" s="15">
         <v>46148</v>
       </c>
       <c r="B323" t="s">
@@ -50847,7 +50839,7 @@
         <v>375.72</v>
       </c>
       <c r="O323" s="8">
-        <v>8.36</v>
+        <v>30.096</v>
       </c>
       <c r="P323" s="8">
         <v>83.56</v>
@@ -50943,7 +50935,7 @@
         <v>63</v>
       </c>
       <c r="AU323" s="7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AV323" s="7" t="s">
         <v>113</v>
@@ -50952,11 +50944,11 @@
         <v>57</v>
       </c>
       <c r="AX323" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="324" ht="15.15" spans="1:50">
-      <c r="A324" s="14">
+      <c r="A324" s="15">
         <v>46148</v>
       </c>
       <c r="B324" t="s">
@@ -50999,7 +50991,7 @@
         <v>799.24</v>
       </c>
       <c r="O324" s="8">
-        <v>7.9</v>
+        <v>28.44</v>
       </c>
       <c r="P324" s="8">
         <v>79.04</v>
@@ -51095,7 +51087,7 @@
         <v>68</v>
       </c>
       <c r="AU324" s="7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AV324" s="7" t="s">
         <v>113</v>
@@ -51104,11 +51096,11 @@
         <v>57</v>
       </c>
       <c r="AX324" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="325" ht="15.15" spans="1:50">
-      <c r="A325" s="14">
+      <c r="A325" s="15">
         <v>46148</v>
       </c>
       <c r="B325" t="s">
@@ -51151,7 +51143,7 @@
         <v>627.52</v>
       </c>
       <c r="O325" s="8">
-        <v>7.8</v>
+        <v>28.08</v>
       </c>
       <c r="P325" s="8">
         <v>77.96</v>
@@ -51247,7 +51239,7 @@
         <v>68</v>
       </c>
       <c r="AU325" s="7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AV325" s="7" t="s">
         <v>113</v>
@@ -51256,11 +51248,11 @@
         <v>57</v>
       </c>
       <c r="AX325" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="326" ht="15.15" spans="1:50">
-      <c r="A326" s="14">
+      <c r="A326" s="15">
         <v>46148</v>
       </c>
       <c r="B326" t="s">
@@ -51303,7 +51295,7 @@
         <v>554.27</v>
       </c>
       <c r="O326" s="8">
-        <v>8.09</v>
+        <v>29.124</v>
       </c>
       <c r="P326" s="8">
         <v>72.85</v>
@@ -51399,7 +51391,7 @@
         <v>75</v>
       </c>
       <c r="AU326" s="7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AV326" s="7" t="s">
         <v>113</v>
@@ -51408,11 +51400,11 @@
         <v>57</v>
       </c>
       <c r="AX326" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="327" ht="15.15" spans="1:50">
-      <c r="A327" s="14">
+      <c r="A327" s="15">
         <v>46148</v>
       </c>
       <c r="B327" t="s">
@@ -51455,7 +51447,7 @@
         <v>175.2</v>
       </c>
       <c r="O327" s="8">
-        <v>7.74</v>
+        <v>27.864</v>
       </c>
       <c r="P327" s="8">
         <v>77.37</v>
@@ -51551,7 +51543,7 @@
         <v>68</v>
       </c>
       <c r="AU327" s="7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AV327" s="7" t="s">
         <v>113</v>
@@ -51560,11 +51552,11 @@
         <v>57</v>
       </c>
       <c r="AX327" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="328" ht="15.15" spans="1:50">
-      <c r="A328" s="14">
+      <c r="A328" s="15">
         <v>46148</v>
       </c>
       <c r="B328" t="s">
@@ -51607,7 +51599,7 @@
         <v>652.73</v>
       </c>
       <c r="O328" s="8">
-        <v>8.05</v>
+        <v>28.98</v>
       </c>
       <c r="P328" s="8">
         <v>80.54</v>
@@ -51703,7 +51695,7 @@
         <v>63</v>
       </c>
       <c r="AU328" s="7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AV328" s="7" t="s">
         <v>113</v>
@@ -51712,11 +51704,11 @@
         <v>57</v>
       </c>
       <c r="AX328" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="329" ht="15.15" spans="1:50">
-      <c r="A329" s="14">
+      <c r="A329" s="15">
         <v>46148</v>
       </c>
       <c r="B329" t="s">
@@ -51759,7 +51751,7 @@
         <v>551.56</v>
       </c>
       <c r="O329" s="8">
-        <v>8.35</v>
+        <v>30.06</v>
       </c>
       <c r="P329" s="8">
         <v>83.52</v>
@@ -51852,10 +51844,10 @@
         <v>54</v>
       </c>
       <c r="AT329" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU329" s="7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AV329" s="7" t="s">
         <v>113</v>
@@ -51864,11 +51856,11 @@
         <v>57</v>
       </c>
       <c r="AX329" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="330" ht="15.15" spans="1:50">
-      <c r="A330" s="14">
+      <c r="A330" s="15">
         <v>46148</v>
       </c>
       <c r="B330" t="s">
@@ -51911,7 +51903,7 @@
         <v>902.39</v>
       </c>
       <c r="O330" s="8">
-        <v>8.03</v>
+        <v>28.908</v>
       </c>
       <c r="P330" s="8">
         <v>80.33</v>
@@ -52004,10 +51996,10 @@
         <v>87</v>
       </c>
       <c r="AT330" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AU330" s="7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AV330" s="7" t="s">
         <v>113</v>
@@ -52016,11 +52008,11 @@
         <v>57</v>
       </c>
       <c r="AX330" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="331" ht="15.15" spans="1:50">
-      <c r="A331" s="14">
+      <c r="A331" s="15">
         <v>46240</v>
       </c>
       <c r="B331" t="s">
@@ -52063,7 +52055,7 @@
         <v>516.75</v>
       </c>
       <c r="O331" s="8">
-        <v>7.06</v>
+        <v>25.416</v>
       </c>
       <c r="P331" s="8">
         <v>70.62</v>
@@ -52168,11 +52160,11 @@
         <v>57</v>
       </c>
       <c r="AX331" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="332" ht="15.15" spans="1:50">
-      <c r="A332" s="14">
+      <c r="A332" s="15">
         <v>46240</v>
       </c>
       <c r="B332" t="s">
@@ -52215,7 +52207,7 @@
         <v>543.94</v>
       </c>
       <c r="O332" s="8">
-        <v>7.62</v>
+        <v>27.432</v>
       </c>
       <c r="P332" s="8">
         <v>76.21</v>
@@ -52320,11 +52312,11 @@
         <v>57</v>
       </c>
       <c r="AX332" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="333" ht="15.15" spans="1:50">
-      <c r="A333" s="14">
+      <c r="A333" s="15">
         <v>46240</v>
       </c>
       <c r="B333" t="s">
@@ -52367,7 +52359,7 @@
         <v>584.01</v>
       </c>
       <c r="O333" s="8">
-        <v>8.43</v>
+        <v>30.348</v>
       </c>
       <c r="P333" s="8">
         <v>84.26</v>
@@ -52472,11 +52464,11 @@
         <v>57</v>
       </c>
       <c r="AX333" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="334" ht="15.15" spans="1:50">
-      <c r="A334" s="14">
+      <c r="A334" s="15">
         <v>46240</v>
       </c>
       <c r="B334" t="s">
@@ -52519,7 +52511,7 @@
         <v>534.65</v>
       </c>
       <c r="O334" s="8">
-        <v>8.31</v>
+        <v>29.916</v>
       </c>
       <c r="P334" s="8">
         <v>83.12</v>
@@ -52624,11 +52616,11 @@
         <v>57</v>
       </c>
       <c r="AX334" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="335" ht="15.15" spans="1:50">
-      <c r="A335" s="14">
+      <c r="A335" s="15">
         <v>46240</v>
       </c>
       <c r="B335" t="s">
@@ -52671,7 +52663,7 @@
         <v>476.1</v>
       </c>
       <c r="O335" s="8">
-        <v>7.41</v>
+        <v>26.676</v>
       </c>
       <c r="P335" s="8">
         <v>74.09</v>
@@ -52776,11 +52768,11 @@
         <v>57</v>
       </c>
       <c r="AX335" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="336" ht="15.15" spans="1:50">
-      <c r="A336" s="14">
+      <c r="A336" s="15">
         <v>46240</v>
       </c>
       <c r="B336" t="s">
@@ -52823,7 +52815,7 @@
         <v>486.28</v>
       </c>
       <c r="O336" s="8">
-        <v>6.84</v>
+        <v>24.624</v>
       </c>
       <c r="P336" s="8">
         <v>68.39</v>
@@ -52928,1071 +52920,1071 @@
         <v>57</v>
       </c>
       <c r="AX336" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="337" ht="28.35" spans="1:50">
-      <c r="A337" s="14">
+      <c r="A337" s="15">
         <v>46059</v>
       </c>
       <c r="B337" t="s">
+        <v>139</v>
+      </c>
+      <c r="C337" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D337" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="E337" s="17">
+        <v>1</v>
+      </c>
+      <c r="F337" s="17">
+        <v>3.81</v>
+      </c>
+      <c r="G337" s="17">
+        <v>-4.59</v>
+      </c>
+      <c r="H337" s="17">
+        <v>8</v>
+      </c>
+      <c r="I337" s="17">
+        <v>6</v>
+      </c>
+      <c r="J337" s="17">
+        <v>14</v>
+      </c>
+      <c r="K337" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="L337" s="18">
+        <v>0.0493055555555556</v>
+      </c>
+      <c r="M337" s="17">
+        <v>3423.46</v>
+      </c>
+      <c r="N337" s="17">
+        <v>391.23</v>
+      </c>
+      <c r="O337" s="17">
+        <v>20.772</v>
+      </c>
+      <c r="P337" s="17">
+        <v>57.66</v>
+      </c>
+      <c r="Q337" s="17">
+        <v>50.1</v>
+      </c>
+      <c r="R337" s="17">
+        <v>5.51</v>
+      </c>
+      <c r="S337" s="17">
+        <v>0.06</v>
+      </c>
+      <c r="T337" s="17">
+        <v>89</v>
+      </c>
+      <c r="U337" s="17">
+        <v>80.49</v>
+      </c>
+      <c r="V337" s="17">
+        <v>44.5</v>
+      </c>
+      <c r="W337" s="17">
+        <v>40.25</v>
+      </c>
+      <c r="X337" s="17">
+        <v>3.41</v>
+      </c>
+      <c r="Y337" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z337" s="18">
+        <v>0.00236111111111111</v>
+      </c>
+      <c r="AA337" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB337" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC337" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD337" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE337" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF337" s="17">
+        <v>297.69</v>
+      </c>
+      <c r="AG337" s="17">
+        <v>233.2</v>
+      </c>
+      <c r="AH337" s="17">
+        <v>257.51</v>
+      </c>
+      <c r="AI337" s="17">
+        <v>1852.92</v>
+      </c>
+      <c r="AJ337" s="17">
+        <v>1161.43</v>
+      </c>
+      <c r="AK337" s="17">
+        <v>145.64</v>
+      </c>
+      <c r="AL337" s="17">
+        <v>5.51</v>
+      </c>
+      <c r="AM337" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN337" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO337" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP337" s="17">
+        <v>5.51</v>
+      </c>
+      <c r="AQ337" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR337" s="17">
+        <v>0.08</v>
+      </c>
+      <c r="AS337" s="17">
+        <v>16</v>
+      </c>
+      <c r="AT337" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="C337" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="D337" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="E337" s="16">
-        <v>1</v>
-      </c>
-      <c r="F337" s="16">
-        <v>3.81</v>
-      </c>
-      <c r="G337" s="16">
-        <v>-4.59</v>
-      </c>
-      <c r="H337" s="16">
-        <v>8</v>
-      </c>
-      <c r="I337" s="16">
-        <v>6</v>
-      </c>
-      <c r="J337" s="16">
-        <v>14</v>
-      </c>
-      <c r="K337" s="16">
-        <v>0.2</v>
-      </c>
-      <c r="L337" s="17">
-        <v>0.0493055555555556</v>
-      </c>
-      <c r="M337" s="16">
-        <v>3423.46</v>
-      </c>
-      <c r="N337" s="16">
-        <v>391.23</v>
-      </c>
-      <c r="O337" s="16">
-        <v>20.772</v>
-      </c>
-      <c r="P337" s="16">
-        <v>57.66</v>
-      </c>
-      <c r="Q337" s="16">
-        <v>50.1</v>
-      </c>
-      <c r="R337" s="16">
-        <v>5.51</v>
-      </c>
-      <c r="S337" s="16">
-        <v>0.06</v>
-      </c>
-      <c r="T337" s="16">
-        <v>89</v>
-      </c>
-      <c r="U337" s="16">
-        <v>80.49</v>
-      </c>
-      <c r="V337" s="16">
-        <v>44.5</v>
-      </c>
-      <c r="W337" s="16">
-        <v>40.25</v>
-      </c>
-      <c r="X337" s="16">
-        <v>3.41</v>
-      </c>
-      <c r="Y337" s="16">
-        <v>0</v>
-      </c>
-      <c r="Z337" s="17">
-        <v>0.00236111111111111</v>
-      </c>
-      <c r="AA337" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB337" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC337" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD337" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE337" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF337" s="16">
-        <v>297.69</v>
-      </c>
-      <c r="AG337" s="16">
-        <v>233.2</v>
-      </c>
-      <c r="AH337" s="16">
-        <v>257.51</v>
-      </c>
-      <c r="AI337" s="16">
-        <v>1852.92</v>
-      </c>
-      <c r="AJ337" s="16">
-        <v>1161.43</v>
-      </c>
-      <c r="AK337" s="16">
-        <v>145.64</v>
-      </c>
-      <c r="AL337" s="16">
-        <v>5.51</v>
-      </c>
-      <c r="AM337" s="16">
-        <v>0</v>
-      </c>
-      <c r="AN337" s="16">
-        <v>0</v>
-      </c>
-      <c r="AO337" s="16">
-        <v>0</v>
-      </c>
-      <c r="AP337" s="16">
-        <v>5.51</v>
-      </c>
-      <c r="AQ337" s="16">
-        <v>0</v>
-      </c>
-      <c r="AR337" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="AS337" s="16">
-        <v>16</v>
-      </c>
-      <c r="AT337" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="AU337" s="18" t="s">
+      <c r="AU337" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AV337" s="18" t="s">
+      <c r="AV337" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="AW337" s="15" t="s">
+      <c r="AW337" s="16" t="s">
         <v>57</v>
       </c>
       <c r="AX337" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="338" ht="28.35" spans="1:50">
-      <c r="A338" s="14">
+      <c r="A338" s="15">
         <v>46059</v>
       </c>
       <c r="B338" t="s">
-        <v>141</v>
-      </c>
-      <c r="C338" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="D338" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="E338" s="16">
+        <v>139</v>
+      </c>
+      <c r="C338" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D338" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="E338" s="17">
         <v>1</v>
       </c>
-      <c r="F338" s="16">
+      <c r="F338" s="17">
         <v>4.03</v>
       </c>
-      <c r="G338" s="16">
+      <c r="G338" s="17">
         <v>-4.52</v>
       </c>
-      <c r="H338" s="16">
+      <c r="H338" s="17">
         <v>13</v>
       </c>
-      <c r="I338" s="16">
+      <c r="I338" s="17">
         <v>8</v>
       </c>
-      <c r="J338" s="16">
+      <c r="J338" s="17">
         <v>21</v>
       </c>
-      <c r="K338" s="16">
+      <c r="K338" s="17">
         <v>0.3</v>
       </c>
-      <c r="L338" s="17">
+      <c r="L338" s="18">
         <v>0.0493055555555556</v>
       </c>
-      <c r="M338" s="16">
+      <c r="M338" s="17">
         <v>3778.41</v>
       </c>
-      <c r="N338" s="16">
+      <c r="N338" s="17">
         <v>448.49</v>
       </c>
-      <c r="O338" s="16">
+      <c r="O338" s="17">
         <v>23.04</v>
       </c>
-      <c r="P338" s="16">
+      <c r="P338" s="17">
         <v>64.04</v>
       </c>
-      <c r="Q338" s="16">
+      <c r="Q338" s="17">
         <v>53.8</v>
       </c>
-      <c r="R338" s="16">
+      <c r="R338" s="17">
         <v>6.32</v>
       </c>
-      <c r="S338" s="16">
+      <c r="S338" s="17">
         <v>0.06</v>
       </c>
-      <c r="T338" s="16">
-        <v>0</v>
-      </c>
-      <c r="U338" s="16">
-        <v>0</v>
-      </c>
-      <c r="V338" s="16">
-        <v>0</v>
-      </c>
-      <c r="W338" s="16">
-        <v>0</v>
-      </c>
-      <c r="X338" s="16">
-        <v>0</v>
-      </c>
-      <c r="Y338" s="16">
-        <v>0</v>
-      </c>
-      <c r="Z338" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA338" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB338" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC338" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD338" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE338" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF338" s="16">
+      <c r="T338" s="17">
+        <v>0</v>
+      </c>
+      <c r="U338" s="17">
+        <v>0</v>
+      </c>
+      <c r="V338" s="17">
+        <v>0</v>
+      </c>
+      <c r="W338" s="17">
+        <v>0</v>
+      </c>
+      <c r="X338" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y338" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z338" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA338" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB338" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC338" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD338" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE338" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF338" s="17">
         <v>312.99</v>
       </c>
-      <c r="AG338" s="16">
+      <c r="AG338" s="17">
         <v>472.13</v>
       </c>
-      <c r="AH338" s="16">
+      <c r="AH338" s="17">
         <v>511.88</v>
       </c>
-      <c r="AI338" s="16">
+      <c r="AI338" s="17">
         <v>1781.04</v>
       </c>
-      <c r="AJ338" s="16">
+      <c r="AJ338" s="17">
         <v>880.17</v>
       </c>
-      <c r="AK338" s="16">
+      <c r="AK338" s="17">
         <v>454.16</v>
       </c>
-      <c r="AL338" s="16">
+      <c r="AL338" s="17">
         <v>150.89</v>
       </c>
-      <c r="AM338" s="16">
-        <v>0</v>
-      </c>
-      <c r="AN338" s="16">
-        <v>0</v>
-      </c>
-      <c r="AO338" s="16">
-        <v>0</v>
-      </c>
-      <c r="AP338" s="16">
+      <c r="AM338" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN338" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO338" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP338" s="17">
         <v>150.89</v>
       </c>
-      <c r="AQ338" s="16">
+      <c r="AQ338" s="17">
         <v>8</v>
       </c>
-      <c r="AR338" s="16">
+      <c r="AR338" s="17">
         <v>2.13</v>
       </c>
-      <c r="AS338" s="16">
+      <c r="AS338" s="17">
         <v>20</v>
       </c>
-      <c r="AT338" s="18" t="s">
+      <c r="AT338" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="AU338" s="18" t="s">
+      <c r="AU338" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AV338" s="18" t="s">
+      <c r="AV338" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="AW338" s="15" t="s">
+      <c r="AW338" s="16" t="s">
         <v>57</v>
       </c>
       <c r="AX338" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="339" ht="28.35" spans="1:50">
-      <c r="A339" s="14">
+      <c r="A339" s="15">
         <v>46059</v>
       </c>
       <c r="B339" t="s">
+        <v>139</v>
+      </c>
+      <c r="C339" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="D339" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="E339" s="17">
+        <v>1</v>
+      </c>
+      <c r="F339" s="17">
+        <v>3.47</v>
+      </c>
+      <c r="G339" s="17">
+        <v>-3.74</v>
+      </c>
+      <c r="H339" s="17">
+        <v>6</v>
+      </c>
+      <c r="I339" s="17">
+        <v>10</v>
+      </c>
+      <c r="J339" s="17">
+        <v>16</v>
+      </c>
+      <c r="K339" s="17">
+        <v>0.23</v>
+      </c>
+      <c r="L339" s="18">
+        <v>0.0493055555555556</v>
+      </c>
+      <c r="M339" s="17">
+        <v>3396.76</v>
+      </c>
+      <c r="N339" s="17">
+        <v>415.29</v>
+      </c>
+      <c r="O339" s="17">
+        <v>23.94</v>
+      </c>
+      <c r="P339" s="17">
+        <v>66.46</v>
+      </c>
+      <c r="Q339" s="17">
+        <v>50.06</v>
+      </c>
+      <c r="R339" s="17">
+        <v>5.85</v>
+      </c>
+      <c r="S339" s="17">
+        <v>0.09</v>
+      </c>
+      <c r="T339" s="17">
+        <v>0</v>
+      </c>
+      <c r="U339" s="17">
+        <v>0</v>
+      </c>
+      <c r="V339" s="17">
+        <v>0</v>
+      </c>
+      <c r="W339" s="17">
+        <v>0</v>
+      </c>
+      <c r="X339" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y339" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z339" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA339" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB339" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC339" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD339" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE339" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF339" s="17">
+        <v>300.44</v>
+      </c>
+      <c r="AG339" s="17">
+        <v>442.61</v>
+      </c>
+      <c r="AH339" s="17">
+        <v>219.15</v>
+      </c>
+      <c r="AI339" s="17">
+        <v>1538.14</v>
+      </c>
+      <c r="AJ339" s="17">
+        <v>1163.43</v>
+      </c>
+      <c r="AK339" s="17">
+        <v>388.19</v>
+      </c>
+      <c r="AL339" s="17">
+        <v>87.65</v>
+      </c>
+      <c r="AM339" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN339" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO339" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP339" s="17">
+        <v>87.65</v>
+      </c>
+      <c r="AQ339" s="17">
+        <v>6</v>
+      </c>
+      <c r="AR339" s="17">
+        <v>1.23</v>
+      </c>
+      <c r="AS339" s="17">
+        <v>15</v>
+      </c>
+      <c r="AT339" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="C339" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="D339" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="E339" s="16">
-        <v>1</v>
-      </c>
-      <c r="F339" s="16">
-        <v>3.47</v>
-      </c>
-      <c r="G339" s="16">
-        <v>-3.74</v>
-      </c>
-      <c r="H339" s="16">
-        <v>6</v>
-      </c>
-      <c r="I339" s="16">
-        <v>10</v>
-      </c>
-      <c r="J339" s="16">
-        <v>16</v>
-      </c>
-      <c r="K339" s="16">
-        <v>0.23</v>
-      </c>
-      <c r="L339" s="17">
-        <v>0.0493055555555556</v>
-      </c>
-      <c r="M339" s="16">
-        <v>3396.76</v>
-      </c>
-      <c r="N339" s="16">
-        <v>415.29</v>
-      </c>
-      <c r="O339" s="16">
-        <v>23.94</v>
-      </c>
-      <c r="P339" s="16">
-        <v>66.46</v>
-      </c>
-      <c r="Q339" s="16">
-        <v>50.06</v>
-      </c>
-      <c r="R339" s="16">
-        <v>5.85</v>
-      </c>
-      <c r="S339" s="16">
-        <v>0.09</v>
-      </c>
-      <c r="T339" s="16">
-        <v>0</v>
-      </c>
-      <c r="U339" s="16">
-        <v>0</v>
-      </c>
-      <c r="V339" s="16">
-        <v>0</v>
-      </c>
-      <c r="W339" s="16">
-        <v>0</v>
-      </c>
-      <c r="X339" s="16">
-        <v>0</v>
-      </c>
-      <c r="Y339" s="16">
-        <v>0</v>
-      </c>
-      <c r="Z339" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA339" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB339" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC339" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD339" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE339" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF339" s="16">
-        <v>300.44</v>
-      </c>
-      <c r="AG339" s="16">
-        <v>442.61</v>
-      </c>
-      <c r="AH339" s="16">
-        <v>219.15</v>
-      </c>
-      <c r="AI339" s="16">
-        <v>1538.14</v>
-      </c>
-      <c r="AJ339" s="16">
-        <v>1163.43</v>
-      </c>
-      <c r="AK339" s="16">
-        <v>388.19</v>
-      </c>
-      <c r="AL339" s="16">
-        <v>87.65</v>
-      </c>
-      <c r="AM339" s="16">
-        <v>0</v>
-      </c>
-      <c r="AN339" s="16">
-        <v>0</v>
-      </c>
-      <c r="AO339" s="16">
-        <v>0</v>
-      </c>
-      <c r="AP339" s="16">
-        <v>87.65</v>
-      </c>
-      <c r="AQ339" s="16">
-        <v>6</v>
-      </c>
-      <c r="AR339" s="16">
-        <v>1.23</v>
-      </c>
-      <c r="AS339" s="16">
-        <v>15</v>
-      </c>
-      <c r="AT339" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="AU339" s="18" t="s">
+      <c r="AU339" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AV339" s="18" t="s">
+      <c r="AV339" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="AW339" s="15" t="s">
+      <c r="AW339" s="16" t="s">
         <v>57</v>
       </c>
       <c r="AX339" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="340" ht="28.35" spans="1:50">
-      <c r="A340" s="14">
+      <c r="A340" s="15">
         <v>46059</v>
       </c>
       <c r="B340" t="s">
-        <v>141</v>
-      </c>
-      <c r="C340" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="D340" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="E340" s="16">
+        <v>139</v>
+      </c>
+      <c r="C340" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D340" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="E340" s="17">
         <v>1</v>
       </c>
-      <c r="F340" s="16">
+      <c r="F340" s="17">
         <v>3.58</v>
       </c>
-      <c r="G340" s="16">
+      <c r="G340" s="17">
         <v>-3.75</v>
       </c>
-      <c r="H340" s="16">
+      <c r="H340" s="17">
         <v>2</v>
       </c>
-      <c r="I340" s="16">
+      <c r="I340" s="17">
         <v>6</v>
       </c>
-      <c r="J340" s="16">
+      <c r="J340" s="17">
         <v>8</v>
       </c>
-      <c r="K340" s="16">
+      <c r="K340" s="17">
         <v>0.11</v>
       </c>
-      <c r="L340" s="17">
+      <c r="L340" s="18">
         <v>0.0493055555555556</v>
       </c>
-      <c r="M340" s="16">
+      <c r="M340" s="17">
         <v>3584.24</v>
       </c>
-      <c r="N340" s="16">
+      <c r="N340" s="17">
         <v>374.29</v>
       </c>
-      <c r="O340" s="16">
+      <c r="O340" s="17">
         <v>21.096</v>
       </c>
-      <c r="P340" s="16">
+      <c r="P340" s="17">
         <v>58.62</v>
       </c>
-      <c r="Q340" s="16">
+      <c r="Q340" s="17">
         <v>51.88</v>
       </c>
-      <c r="R340" s="16">
+      <c r="R340" s="17">
         <v>5.27</v>
       </c>
-      <c r="S340" s="16">
+      <c r="S340" s="17">
         <v>0.07</v>
       </c>
-      <c r="T340" s="16">
-        <v>0</v>
-      </c>
-      <c r="U340" s="16">
-        <v>0</v>
-      </c>
-      <c r="V340" s="16">
-        <v>0</v>
-      </c>
-      <c r="W340" s="16">
-        <v>0</v>
-      </c>
-      <c r="X340" s="16">
-        <v>0</v>
-      </c>
-      <c r="Y340" s="16">
-        <v>0</v>
-      </c>
-      <c r="Z340" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA340" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB340" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC340" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD340" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE340" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF340" s="16">
+      <c r="T340" s="17">
+        <v>0</v>
+      </c>
+      <c r="U340" s="17">
+        <v>0</v>
+      </c>
+      <c r="V340" s="17">
+        <v>0</v>
+      </c>
+      <c r="W340" s="17">
+        <v>0</v>
+      </c>
+      <c r="X340" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y340" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z340" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA340" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB340" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC340" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD340" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE340" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF340" s="17">
         <v>308.9</v>
       </c>
-      <c r="AG340" s="16">
+      <c r="AG340" s="17">
         <v>332.7</v>
       </c>
-      <c r="AH340" s="16">
+      <c r="AH340" s="17">
         <v>205.54</v>
       </c>
-      <c r="AI340" s="16">
+      <c r="AI340" s="17">
         <v>1925.71</v>
       </c>
-      <c r="AJ340" s="16">
+      <c r="AJ340" s="17">
         <v>1052.88</v>
       </c>
-      <c r="AK340" s="16">
+      <c r="AK340" s="17">
         <v>372.46</v>
       </c>
-      <c r="AL340" s="16">
+      <c r="AL340" s="17">
         <v>27.35</v>
       </c>
-      <c r="AM340" s="16">
-        <v>0</v>
-      </c>
-      <c r="AN340" s="16">
-        <v>0</v>
-      </c>
-      <c r="AO340" s="16">
-        <v>0</v>
-      </c>
-      <c r="AP340" s="16">
+      <c r="AM340" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN340" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO340" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP340" s="17">
         <v>27.35</v>
       </c>
-      <c r="AQ340" s="16">
+      <c r="AQ340" s="17">
         <v>2</v>
       </c>
-      <c r="AR340" s="16">
+      <c r="AR340" s="17">
         <v>0.39</v>
       </c>
-      <c r="AS340" s="16">
+      <c r="AS340" s="17">
         <v>15</v>
       </c>
-      <c r="AT340" s="18" t="s">
+      <c r="AT340" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="AU340" s="18" t="s">
+      <c r="AU340" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AV340" s="18" t="s">
+      <c r="AV340" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="AW340" s="15" t="s">
+      <c r="AW340" s="16" t="s">
         <v>57</v>
       </c>
       <c r="AX340" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="341" ht="28.35" spans="1:50">
-      <c r="A341" s="14">
+      <c r="A341" s="15">
         <v>46059</v>
       </c>
       <c r="B341" t="s">
-        <v>141</v>
-      </c>
-      <c r="C341" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D341" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="E341" s="16">
+        <v>139</v>
+      </c>
+      <c r="C341" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D341" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="E341" s="17">
         <v>1</v>
       </c>
-      <c r="F341" s="16">
+      <c r="F341" s="17">
         <v>4.2</v>
       </c>
-      <c r="G341" s="16">
+      <c r="G341" s="17">
         <v>-3.62</v>
       </c>
-      <c r="H341" s="16">
+      <c r="H341" s="17">
         <v>9</v>
       </c>
-      <c r="I341" s="16">
+      <c r="I341" s="17">
         <v>5</v>
       </c>
-      <c r="J341" s="16">
+      <c r="J341" s="17">
         <v>14</v>
       </c>
-      <c r="K341" s="16">
+      <c r="K341" s="17">
         <v>0.2</v>
       </c>
-      <c r="L341" s="17">
+      <c r="L341" s="18">
         <v>0.0493055555555556</v>
       </c>
-      <c r="M341" s="16">
+      <c r="M341" s="17">
         <v>2865.26</v>
       </c>
-      <c r="N341" s="16">
+      <c r="N341" s="17">
         <v>353.89</v>
       </c>
-      <c r="O341" s="16">
+      <c r="O341" s="17">
         <v>20.772</v>
       </c>
-      <c r="P341" s="16">
+      <c r="P341" s="17">
         <v>57.74</v>
       </c>
-      <c r="Q341" s="16">
+      <c r="Q341" s="17">
         <v>41.86</v>
       </c>
-      <c r="R341" s="16">
+      <c r="R341" s="17">
         <v>4.98</v>
       </c>
-      <c r="S341" s="16">
+      <c r="S341" s="17">
         <v>0.04</v>
       </c>
-      <c r="T341" s="16">
-        <v>0</v>
-      </c>
-      <c r="U341" s="16">
-        <v>0</v>
-      </c>
-      <c r="V341" s="16">
-        <v>0</v>
-      </c>
-      <c r="W341" s="16">
-        <v>0</v>
-      </c>
-      <c r="X341" s="16">
-        <v>0</v>
-      </c>
-      <c r="Y341" s="16">
-        <v>0</v>
-      </c>
-      <c r="Z341" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA341" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB341" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC341" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD341" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE341" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF341" s="16">
+      <c r="T341" s="17">
+        <v>0</v>
+      </c>
+      <c r="U341" s="17">
+        <v>0</v>
+      </c>
+      <c r="V341" s="17">
+        <v>0</v>
+      </c>
+      <c r="W341" s="17">
+        <v>0</v>
+      </c>
+      <c r="X341" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y341" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z341" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA341" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB341" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC341" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD341" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE341" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF341" s="17">
         <v>236.91</v>
       </c>
-      <c r="AG341" s="16">
+      <c r="AG341" s="17">
         <v>248.81</v>
       </c>
-      <c r="AH341" s="16">
+      <c r="AH341" s="17">
         <v>361.48</v>
       </c>
-      <c r="AI341" s="16">
+      <c r="AI341" s="17">
         <v>1508.67</v>
       </c>
-      <c r="AJ341" s="16">
+      <c r="AJ341" s="17">
         <v>731.68</v>
       </c>
-      <c r="AK341" s="16">
+      <c r="AK341" s="17">
         <v>245.98</v>
       </c>
-      <c r="AL341" s="16">
+      <c r="AL341" s="17">
         <v>17.44</v>
       </c>
-      <c r="AM341" s="16">
-        <v>0</v>
-      </c>
-      <c r="AN341" s="16">
-        <v>0</v>
-      </c>
-      <c r="AO341" s="16">
-        <v>0</v>
-      </c>
-      <c r="AP341" s="16">
+      <c r="AM341" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN341" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO341" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP341" s="17">
         <v>17.44</v>
       </c>
-      <c r="AQ341" s="16">
+      <c r="AQ341" s="17">
         <v>1</v>
       </c>
-      <c r="AR341" s="16">
+      <c r="AR341" s="17">
         <v>0.25</v>
       </c>
-      <c r="AS341" s="16">
+      <c r="AS341" s="17">
         <v>41</v>
       </c>
-      <c r="AT341" s="18" t="s">
+      <c r="AT341" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="AU341" s="18" t="s">
+      <c r="AU341" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AV341" s="18" t="s">
+      <c r="AV341" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="AW341" s="15" t="s">
+      <c r="AW341" s="16" t="s">
         <v>57</v>
       </c>
       <c r="AX341" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="342" ht="28.35" spans="1:50">
-      <c r="A342" s="14">
+      <c r="A342" s="15">
         <v>46059</v>
       </c>
       <c r="B342" t="s">
+        <v>139</v>
+      </c>
+      <c r="C342" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D342" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="E342" s="17">
+        <v>1</v>
+      </c>
+      <c r="F342" s="17">
+        <v>3.3</v>
+      </c>
+      <c r="G342" s="17">
+        <v>-4.3</v>
+      </c>
+      <c r="H342" s="17">
+        <v>5</v>
+      </c>
+      <c r="I342" s="17">
+        <v>12</v>
+      </c>
+      <c r="J342" s="17">
+        <v>17</v>
+      </c>
+      <c r="K342" s="17">
+        <v>0.24</v>
+      </c>
+      <c r="L342" s="18">
+        <v>0.0493055555555556</v>
+      </c>
+      <c r="M342" s="17">
+        <v>3359.22</v>
+      </c>
+      <c r="N342" s="17">
+        <v>353.95</v>
+      </c>
+      <c r="O342" s="17">
+        <v>21.996</v>
+      </c>
+      <c r="P342" s="17">
+        <v>61.11</v>
+      </c>
+      <c r="Q342" s="17">
+        <v>49.69</v>
+      </c>
+      <c r="R342" s="17">
+        <v>4.99</v>
+      </c>
+      <c r="S342" s="17">
+        <v>0.08</v>
+      </c>
+      <c r="T342" s="17">
+        <v>0</v>
+      </c>
+      <c r="U342" s="17">
+        <v>0</v>
+      </c>
+      <c r="V342" s="17">
+        <v>0</v>
+      </c>
+      <c r="W342" s="17">
+        <v>0</v>
+      </c>
+      <c r="X342" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y342" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z342" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA342" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB342" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC342" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD342" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE342" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF342" s="17">
+        <v>300.91</v>
+      </c>
+      <c r="AG342" s="17">
+        <v>354.59</v>
+      </c>
+      <c r="AH342" s="17">
+        <v>182.24</v>
+      </c>
+      <c r="AI342" s="17">
+        <v>1605.07</v>
+      </c>
+      <c r="AJ342" s="17">
+        <v>1324.89</v>
+      </c>
+      <c r="AK342" s="17">
+        <v>237.94</v>
+      </c>
+      <c r="AL342" s="17">
+        <v>8.81</v>
+      </c>
+      <c r="AM342" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN342" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO342" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP342" s="17">
+        <v>8.81</v>
+      </c>
+      <c r="AQ342" s="17">
+        <v>1</v>
+      </c>
+      <c r="AR342" s="17">
+        <v>0.12</v>
+      </c>
+      <c r="AS342" s="17">
+        <v>11</v>
+      </c>
+      <c r="AT342" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="C342" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="D342" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="E342" s="16">
-        <v>1</v>
-      </c>
-      <c r="F342" s="16">
-        <v>3.3</v>
-      </c>
-      <c r="G342" s="16">
-        <v>-4.3</v>
-      </c>
-      <c r="H342" s="16">
-        <v>5</v>
-      </c>
-      <c r="I342" s="16">
-        <v>12</v>
-      </c>
-      <c r="J342" s="16">
-        <v>17</v>
-      </c>
-      <c r="K342" s="16">
-        <v>0.24</v>
-      </c>
-      <c r="L342" s="17">
-        <v>0.0493055555555556</v>
-      </c>
-      <c r="M342" s="16">
-        <v>3359.22</v>
-      </c>
-      <c r="N342" s="16">
-        <v>353.95</v>
-      </c>
-      <c r="O342" s="16">
-        <v>21.996</v>
-      </c>
-      <c r="P342" s="16">
-        <v>61.11</v>
-      </c>
-      <c r="Q342" s="16">
-        <v>49.69</v>
-      </c>
-      <c r="R342" s="16">
-        <v>4.99</v>
-      </c>
-      <c r="S342" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="T342" s="16">
-        <v>0</v>
-      </c>
-      <c r="U342" s="16">
-        <v>0</v>
-      </c>
-      <c r="V342" s="16">
-        <v>0</v>
-      </c>
-      <c r="W342" s="16">
-        <v>0</v>
-      </c>
-      <c r="X342" s="16">
-        <v>0</v>
-      </c>
-      <c r="Y342" s="16">
-        <v>0</v>
-      </c>
-      <c r="Z342" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA342" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB342" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC342" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD342" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE342" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF342" s="16">
-        <v>300.91</v>
-      </c>
-      <c r="AG342" s="16">
-        <v>354.59</v>
-      </c>
-      <c r="AH342" s="16">
-        <v>182.24</v>
-      </c>
-      <c r="AI342" s="16">
-        <v>1605.07</v>
-      </c>
-      <c r="AJ342" s="16">
-        <v>1324.89</v>
-      </c>
-      <c r="AK342" s="16">
-        <v>237.94</v>
-      </c>
-      <c r="AL342" s="16">
-        <v>8.81</v>
-      </c>
-      <c r="AM342" s="16">
-        <v>0</v>
-      </c>
-      <c r="AN342" s="16">
-        <v>0</v>
-      </c>
-      <c r="AO342" s="16">
-        <v>0</v>
-      </c>
-      <c r="AP342" s="16">
-        <v>8.81</v>
-      </c>
-      <c r="AQ342" s="16">
-        <v>1</v>
-      </c>
-      <c r="AR342" s="16">
-        <v>0.12</v>
-      </c>
-      <c r="AS342" s="16">
-        <v>11</v>
-      </c>
-      <c r="AT342" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="AU342" s="18" t="s">
+      <c r="AU342" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AV342" s="18" t="s">
+      <c r="AV342" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="AW342" s="15" t="s">
+      <c r="AW342" s="16" t="s">
         <v>57</v>
       </c>
       <c r="AX342" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="343" ht="28.35" spans="1:50">
-      <c r="A343" s="14">
+      <c r="A343" s="15">
         <v>46059</v>
       </c>
       <c r="B343" t="s">
-        <v>141</v>
-      </c>
-      <c r="C343" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="D343" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="E343" s="16">
+        <v>139</v>
+      </c>
+      <c r="C343" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="D343" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="E343" s="17">
         <v>1</v>
       </c>
-      <c r="F343" s="16">
-        <v>0</v>
-      </c>
-      <c r="G343" s="16">
-        <v>0</v>
-      </c>
-      <c r="H343" s="16">
-        <v>0</v>
-      </c>
-      <c r="I343" s="16">
-        <v>0</v>
-      </c>
-      <c r="J343" s="16">
-        <v>0</v>
-      </c>
-      <c r="K343" s="16">
-        <v>0</v>
-      </c>
-      <c r="L343" s="17">
+      <c r="F343" s="17">
+        <v>0</v>
+      </c>
+      <c r="G343" s="17">
+        <v>0</v>
+      </c>
+      <c r="H343" s="17">
+        <v>0</v>
+      </c>
+      <c r="I343" s="17">
+        <v>0</v>
+      </c>
+      <c r="J343" s="17">
+        <v>0</v>
+      </c>
+      <c r="K343" s="17">
+        <v>0</v>
+      </c>
+      <c r="L343" s="18">
         <v>0.0493055555555556</v>
       </c>
-      <c r="M343" s="16">
+      <c r="M343" s="17">
         <v>2380.96</v>
       </c>
-      <c r="N343" s="16">
+      <c r="N343" s="17">
         <v>438.2</v>
       </c>
-      <c r="O343" s="16">
+      <c r="O343" s="17">
         <v>19.764</v>
       </c>
-      <c r="P343" s="16">
+      <c r="P343" s="17">
         <v>54.86</v>
       </c>
-      <c r="Q343" s="16">
+      <c r="Q343" s="17">
         <v>43.35</v>
       </c>
-      <c r="R343" s="16">
+      <c r="R343" s="17">
         <v>6.17</v>
       </c>
-      <c r="S343" s="16">
+      <c r="S343" s="17">
         <v>0.04</v>
       </c>
-      <c r="T343" s="16">
-        <v>0</v>
-      </c>
-      <c r="U343" s="16">
-        <v>0</v>
-      </c>
-      <c r="V343" s="16">
-        <v>0</v>
-      </c>
-      <c r="W343" s="16">
-        <v>0</v>
-      </c>
-      <c r="X343" s="16">
-        <v>0</v>
-      </c>
-      <c r="Y343" s="16">
-        <v>0</v>
-      </c>
-      <c r="Z343" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA343" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB343" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC343" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD343" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE343" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF343" s="16">
+      <c r="T343" s="17">
+        <v>0</v>
+      </c>
+      <c r="U343" s="17">
+        <v>0</v>
+      </c>
+      <c r="V343" s="17">
+        <v>0</v>
+      </c>
+      <c r="W343" s="17">
+        <v>0</v>
+      </c>
+      <c r="X343" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y343" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z343" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA343" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB343" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC343" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD343" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE343" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF343" s="17">
         <v>134.62</v>
       </c>
-      <c r="AG343" s="16">
+      <c r="AG343" s="17">
         <v>166.98</v>
       </c>
-      <c r="AH343" s="16">
+      <c r="AH343" s="17">
         <v>544.5</v>
       </c>
-      <c r="AI343" s="16">
+      <c r="AI343" s="17">
         <v>1218.31</v>
       </c>
-      <c r="AJ343" s="16">
+      <c r="AJ343" s="17">
         <v>551.41</v>
       </c>
-      <c r="AK343" s="16">
+      <c r="AK343" s="17">
         <v>66.74</v>
       </c>
-      <c r="AL343" s="16">
-        <v>0</v>
-      </c>
-      <c r="AM343" s="16">
-        <v>0</v>
-      </c>
-      <c r="AN343" s="16">
-        <v>0</v>
-      </c>
-      <c r="AO343" s="16">
-        <v>0</v>
-      </c>
-      <c r="AP343" s="16">
-        <v>0</v>
-      </c>
-      <c r="AQ343" s="16">
-        <v>0</v>
-      </c>
-      <c r="AR343" s="16">
-        <v>0</v>
-      </c>
-      <c r="AS343" s="16">
+      <c r="AL343" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM343" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN343" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO343" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP343" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ343" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR343" s="17">
+        <v>0</v>
+      </c>
+      <c r="AS343" s="17">
         <v>35</v>
       </c>
-      <c r="AT343" s="18" t="s">
+      <c r="AT343" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="AU343" s="18" t="s">
+      <c r="AU343" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AV343" s="18" t="s">
+      <c r="AV343" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="AW343" s="15" t="s">
+      <c r="AW343" s="16" t="s">
         <v>57</v>
       </c>
       <c r="AX343" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/GPS_Formativas_2026.xlsx
+++ b/GPS_Formativas_2026.xlsx
@@ -624,14 +624,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+  <numFmts count="5">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="m/d/yy;@"/>
-    <numFmt numFmtId="179" formatCode="mm/dd/yy;@"/>
-    <numFmt numFmtId="180" formatCode="mm/dd/yy"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1275,12 +1273,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
@@ -1305,20 +1303,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="58" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
@@ -1868,6 +1860,7 @@
   <dimension ref="A1:AX343"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
+    <col min="1" max="1" width="10" style="1"/>
     <col min="3" max="3" width="30.4444444444444" customWidth="1"/>
     <col min="4" max="4" width="18.5555555555556" customWidth="1"/>
     <col min="10" max="10" width="17.4444444444444" customWidth="1"/>
@@ -39396,7 +39389,7 @@
       </c>
     </row>
     <row r="248" spans="1:50">
-      <c r="A248" s="12">
+      <c r="A248" s="11">
         <v>46059</v>
       </c>
       <c r="B248" t="s">
@@ -39547,8 +39540,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="249" ht="15.15" spans="1:50">
-      <c r="A249" s="12">
+    <row r="249" spans="1:50">
+      <c r="A249" s="11">
         <v>46059</v>
       </c>
       <c r="B249" t="s">
@@ -39699,8 +39692,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="250" ht="15.15" spans="1:50">
-      <c r="A250" s="12">
+    <row r="250" spans="1:50">
+      <c r="A250" s="11">
         <v>46059</v>
       </c>
       <c r="B250" t="s">
@@ -39851,8 +39844,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="251" ht="15.15" spans="1:50">
-      <c r="A251" s="12">
+    <row r="251" spans="1:50">
+      <c r="A251" s="11">
         <v>46059</v>
       </c>
       <c r="B251" t="s">
@@ -40003,8 +39996,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="252" ht="15.15" spans="1:50">
-      <c r="A252" s="12">
+    <row r="252" spans="1:50">
+      <c r="A252" s="11">
         <v>46059</v>
       </c>
       <c r="B252" t="s">
@@ -40155,8 +40148,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="253" ht="15.15" spans="1:50">
-      <c r="A253" s="12">
+    <row r="253" spans="1:50">
+      <c r="A253" s="11">
         <v>46059</v>
       </c>
       <c r="B253" t="s">
@@ -40307,8 +40300,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="254" ht="15.15" spans="1:50">
-      <c r="A254" s="12">
+    <row r="254" spans="1:50">
+      <c r="A254" s="11">
         <v>46059</v>
       </c>
       <c r="B254" t="s">
@@ -41979,7 +41972,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="265" ht="15.15" spans="1:50">
+    <row r="265" spans="1:50">
       <c r="A265" s="11">
         <v>46059</v>
       </c>
@@ -43348,7 +43341,7 @@
       </c>
     </row>
     <row r="274" ht="15.15" spans="1:50">
-      <c r="A274" s="8" t="s">
+      <c r="A274" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B274" t="s">
@@ -43500,7 +43493,7 @@
       </c>
     </row>
     <row r="275" ht="15.15" spans="1:50">
-      <c r="A275" s="8" t="s">
+      <c r="A275" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B275" t="s">
@@ -43652,7 +43645,7 @@
       </c>
     </row>
     <row r="276" ht="15.15" spans="1:50">
-      <c r="A276" s="8" t="s">
+      <c r="A276" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B276" t="s">
@@ -43804,7 +43797,7 @@
       </c>
     </row>
     <row r="277" ht="15.15" spans="1:50">
-      <c r="A277" s="8" t="s">
+      <c r="A277" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B277" t="s">
@@ -43956,7 +43949,7 @@
       </c>
     </row>
     <row r="278" ht="15.15" spans="1:50">
-      <c r="A278" s="8" t="s">
+      <c r="A278" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B278" t="s">
@@ -44108,7 +44101,7 @@
       </c>
     </row>
     <row r="279" ht="15.15" spans="1:50">
-      <c r="A279" s="8" t="s">
+      <c r="A279" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B279" t="s">
@@ -44260,7 +44253,7 @@
       </c>
     </row>
     <row r="280" ht="15.15" spans="1:50">
-      <c r="A280" s="8" t="s">
+      <c r="A280" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B280" t="s">
@@ -44412,7 +44405,7 @@
       </c>
     </row>
     <row r="281" ht="15.15" spans="1:50">
-      <c r="A281" s="8" t="s">
+      <c r="A281" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B281" t="s">
@@ -44564,7 +44557,7 @@
       </c>
     </row>
     <row r="282" ht="15.15" spans="1:50">
-      <c r="A282" s="8" t="s">
+      <c r="A282" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B282" t="s">
@@ -44716,7 +44709,7 @@
       </c>
     </row>
     <row r="283" ht="15.15" spans="1:50">
-      <c r="A283" s="8" t="s">
+      <c r="A283" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B283" t="s">
@@ -44868,7 +44861,7 @@
       </c>
     </row>
     <row r="284" ht="29.55" spans="1:50">
-      <c r="A284" s="8" t="s">
+      <c r="A284" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B284" t="s">
@@ -45020,7 +45013,7 @@
       </c>
     </row>
     <row r="285" ht="15.15" spans="1:50">
-      <c r="A285" s="8" t="s">
+      <c r="A285" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B285" t="s">
@@ -45172,7 +45165,7 @@
       </c>
     </row>
     <row r="286" ht="15.15" spans="1:50">
-      <c r="A286" s="8" t="s">
+      <c r="A286" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B286" t="s">
@@ -45324,7 +45317,7 @@
       </c>
     </row>
     <row r="287" ht="15.15" spans="1:50">
-      <c r="A287" s="8" t="s">
+      <c r="A287" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B287" t="s">
@@ -45476,7 +45469,7 @@
       </c>
     </row>
     <row r="288" ht="15.15" spans="1:50">
-      <c r="A288" s="8" t="s">
+      <c r="A288" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B288" t="s">
@@ -45628,7 +45621,7 @@
       </c>
     </row>
     <row r="289" ht="15.15" spans="1:50">
-      <c r="A289" s="8" t="s">
+      <c r="A289" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B289" t="s">
@@ -45780,7 +45773,7 @@
       </c>
     </row>
     <row r="290" ht="15.15" spans="1:50">
-      <c r="A290" s="8" t="s">
+      <c r="A290" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B290" t="s">
@@ -45932,7 +45925,7 @@
       </c>
     </row>
     <row r="291" ht="15.15" spans="1:50">
-      <c r="A291" s="8" t="s">
+      <c r="A291" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B291" t="s">
@@ -46084,7 +46077,7 @@
       </c>
     </row>
     <row r="292" ht="29.55" spans="1:50">
-      <c r="A292" s="8" t="s">
+      <c r="A292" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B292" t="s">
@@ -46236,7 +46229,7 @@
       </c>
     </row>
     <row r="293" ht="15.15" spans="1:50">
-      <c r="A293" s="8" t="s">
+      <c r="A293" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B293" t="s">
@@ -46388,7 +46381,7 @@
       </c>
     </row>
     <row r="294" ht="29.55" spans="1:50">
-      <c r="A294" s="8" t="s">
+      <c r="A294" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B294" t="s">
@@ -46540,7 +46533,7 @@
       </c>
     </row>
     <row r="295" ht="15.15" spans="1:50">
-      <c r="A295" s="8" t="s">
+      <c r="A295" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B295" t="s">
@@ -46692,7 +46685,7 @@
       </c>
     </row>
     <row r="296" ht="15.15" spans="1:50">
-      <c r="A296" s="8" t="s">
+      <c r="A296" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B296" t="s">
@@ -46844,7 +46837,7 @@
       </c>
     </row>
     <row r="297" ht="15.15" spans="1:50">
-      <c r="A297" s="8" t="s">
+      <c r="A297" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B297" t="s">
@@ -46996,7 +46989,7 @@
       </c>
     </row>
     <row r="298" ht="29.55" spans="1:50">
-      <c r="A298" s="14">
+      <c r="A298" s="12">
         <v>46028</v>
       </c>
       <c r="B298" t="s">
@@ -47148,7 +47141,7 @@
       </c>
     </row>
     <row r="299" ht="29.55" spans="1:50">
-      <c r="A299" s="14">
+      <c r="A299" s="12">
         <v>46028</v>
       </c>
       <c r="B299" t="s">
@@ -47300,7 +47293,7 @@
       </c>
     </row>
     <row r="300" ht="29.55" spans="1:50">
-      <c r="A300" s="14">
+      <c r="A300" s="12">
         <v>46028</v>
       </c>
       <c r="B300" t="s">
@@ -47452,7 +47445,7 @@
       </c>
     </row>
     <row r="301" ht="29.55" spans="1:50">
-      <c r="A301" s="14">
+      <c r="A301" s="12">
         <v>46028</v>
       </c>
       <c r="B301" t="s">
@@ -47604,7 +47597,7 @@
       </c>
     </row>
     <row r="302" ht="29.55" spans="1:50">
-      <c r="A302" s="14">
+      <c r="A302" s="12">
         <v>46028</v>
       </c>
       <c r="B302" t="s">
@@ -47756,7 +47749,7 @@
       </c>
     </row>
     <row r="303" ht="15.15" spans="1:50">
-      <c r="A303" s="14">
+      <c r="A303" s="12">
         <v>46059</v>
       </c>
       <c r="B303" t="s">
@@ -47908,7 +47901,7 @@
       </c>
     </row>
     <row r="304" ht="15.15" spans="1:50">
-      <c r="A304" s="14">
+      <c r="A304" s="12">
         <v>46059</v>
       </c>
       <c r="B304" t="s">
@@ -48060,7 +48053,7 @@
       </c>
     </row>
     <row r="305" ht="15.15" spans="1:50">
-      <c r="A305" s="14">
+      <c r="A305" s="12">
         <v>46059</v>
       </c>
       <c r="B305" t="s">
@@ -48212,7 +48205,7 @@
       </c>
     </row>
     <row r="306" ht="15.15" spans="1:50">
-      <c r="A306" s="14">
+      <c r="A306" s="12">
         <v>46059</v>
       </c>
       <c r="B306" t="s">
@@ -48364,7 +48357,7 @@
       </c>
     </row>
     <row r="307" ht="15.15" spans="1:50">
-      <c r="A307" s="14">
+      <c r="A307" s="12">
         <v>46059</v>
       </c>
       <c r="B307" t="s">
@@ -48516,7 +48509,7 @@
       </c>
     </row>
     <row r="308" ht="29.55" spans="1:50">
-      <c r="A308" s="14">
+      <c r="A308" s="12">
         <v>46118</v>
       </c>
       <c r="B308" t="s">
@@ -48668,7 +48661,7 @@
       </c>
     </row>
     <row r="309" ht="29.55" spans="1:50">
-      <c r="A309" s="14">
+      <c r="A309" s="12">
         <v>46118</v>
       </c>
       <c r="B309" t="s">
@@ -48820,7 +48813,7 @@
       </c>
     </row>
     <row r="310" ht="29.55" spans="1:50">
-      <c r="A310" s="14">
+      <c r="A310" s="12">
         <v>46118</v>
       </c>
       <c r="B310" t="s">
@@ -48972,7 +48965,7 @@
       </c>
     </row>
     <row r="311" ht="29.55" spans="1:50">
-      <c r="A311" s="14">
+      <c r="A311" s="12">
         <v>46118</v>
       </c>
       <c r="B311" t="s">
@@ -49124,7 +49117,7 @@
       </c>
     </row>
     <row r="312" ht="29.55" spans="1:50">
-      <c r="A312" s="14">
+      <c r="A312" s="12">
         <v>46118</v>
       </c>
       <c r="B312" t="s">
@@ -49276,7 +49269,7 @@
       </c>
     </row>
     <row r="313" ht="29.55" spans="1:50">
-      <c r="A313" s="14">
+      <c r="A313" s="12">
         <v>46118</v>
       </c>
       <c r="B313" t="s">
@@ -49428,7 +49421,7 @@
       </c>
     </row>
     <row r="314" ht="29.55" spans="1:50">
-      <c r="A314" s="14">
+      <c r="A314" s="12">
         <v>46118</v>
       </c>
       <c r="B314" t="s">
@@ -49580,7 +49573,7 @@
       </c>
     </row>
     <row r="315" ht="29.55" spans="1:50">
-      <c r="A315" s="15">
+      <c r="A315" s="1">
         <v>46271</v>
       </c>
       <c r="B315" t="s">
@@ -49732,7 +49725,7 @@
       </c>
     </row>
     <row r="316" ht="29.55" spans="1:50">
-      <c r="A316" s="15">
+      <c r="A316" s="1">
         <v>46271</v>
       </c>
       <c r="B316" t="s">
@@ -49884,7 +49877,7 @@
       </c>
     </row>
     <row r="317" ht="29.55" spans="1:50">
-      <c r="A317" s="15">
+      <c r="A317" s="1">
         <v>46271</v>
       </c>
       <c r="B317" t="s">
@@ -50036,7 +50029,7 @@
       </c>
     </row>
     <row r="318" ht="29.55" spans="1:50">
-      <c r="A318" s="15">
+      <c r="A318" s="1">
         <v>46271</v>
       </c>
       <c r="B318" t="s">
@@ -50188,7 +50181,7 @@
       </c>
     </row>
     <row r="319" ht="29.55" spans="1:50">
-      <c r="A319" s="15">
+      <c r="A319" s="1">
         <v>46271</v>
       </c>
       <c r="B319" t="s">
@@ -50340,7 +50333,7 @@
       </c>
     </row>
     <row r="320" ht="29.55" spans="1:50">
-      <c r="A320" s="15">
+      <c r="A320" s="1">
         <v>46271</v>
       </c>
       <c r="B320" t="s">
@@ -50492,7 +50485,7 @@
       </c>
     </row>
     <row r="321" ht="29.55" spans="1:50">
-      <c r="A321" s="15">
+      <c r="A321" s="1">
         <v>46271</v>
       </c>
       <c r="B321" t="s">
@@ -50644,7 +50637,7 @@
       </c>
     </row>
     <row r="322" ht="15.15" spans="1:50">
-      <c r="A322" s="15">
+      <c r="A322" s="1">
         <v>46148</v>
       </c>
       <c r="B322" t="s">
@@ -50796,7 +50789,7 @@
       </c>
     </row>
     <row r="323" ht="15.15" spans="1:50">
-      <c r="A323" s="15">
+      <c r="A323" s="1">
         <v>46148</v>
       </c>
       <c r="B323" t="s">
@@ -50948,7 +50941,7 @@
       </c>
     </row>
     <row r="324" ht="15.15" spans="1:50">
-      <c r="A324" s="15">
+      <c r="A324" s="1">
         <v>46148</v>
       </c>
       <c r="B324" t="s">
@@ -51100,7 +51093,7 @@
       </c>
     </row>
     <row r="325" ht="15.15" spans="1:50">
-      <c r="A325" s="15">
+      <c r="A325" s="1">
         <v>46148</v>
       </c>
       <c r="B325" t="s">
@@ -51252,7 +51245,7 @@
       </c>
     </row>
     <row r="326" ht="15.15" spans="1:50">
-      <c r="A326" s="15">
+      <c r="A326" s="1">
         <v>46148</v>
       </c>
       <c r="B326" t="s">
@@ -51404,7 +51397,7 @@
       </c>
     </row>
     <row r="327" ht="15.15" spans="1:50">
-      <c r="A327" s="15">
+      <c r="A327" s="1">
         <v>46148</v>
       </c>
       <c r="B327" t="s">
@@ -51556,7 +51549,7 @@
       </c>
     </row>
     <row r="328" ht="15.15" spans="1:50">
-      <c r="A328" s="15">
+      <c r="A328" s="1">
         <v>46148</v>
       </c>
       <c r="B328" t="s">
@@ -51708,7 +51701,7 @@
       </c>
     </row>
     <row r="329" ht="15.15" spans="1:50">
-      <c r="A329" s="15">
+      <c r="A329" s="1">
         <v>46148</v>
       </c>
       <c r="B329" t="s">
@@ -51860,7 +51853,7 @@
       </c>
     </row>
     <row r="330" ht="15.15" spans="1:50">
-      <c r="A330" s="15">
+      <c r="A330" s="1">
         <v>46148</v>
       </c>
       <c r="B330" t="s">
@@ -52012,7 +52005,7 @@
       </c>
     </row>
     <row r="331" ht="15.15" spans="1:50">
-      <c r="A331" s="15">
+      <c r="A331" s="1">
         <v>46240</v>
       </c>
       <c r="B331" t="s">
@@ -52164,7 +52157,7 @@
       </c>
     </row>
     <row r="332" ht="15.15" spans="1:50">
-      <c r="A332" s="15">
+      <c r="A332" s="1">
         <v>46240</v>
       </c>
       <c r="B332" t="s">
@@ -52316,7 +52309,7 @@
       </c>
     </row>
     <row r="333" ht="15.15" spans="1:50">
-      <c r="A333" s="15">
+      <c r="A333" s="1">
         <v>46240</v>
       </c>
       <c r="B333" t="s">
@@ -52468,7 +52461,7 @@
       </c>
     </row>
     <row r="334" ht="15.15" spans="1:50">
-      <c r="A334" s="15">
+      <c r="A334" s="1">
         <v>46240</v>
       </c>
       <c r="B334" t="s">
@@ -52620,7 +52613,7 @@
       </c>
     </row>
     <row r="335" ht="15.15" spans="1:50">
-      <c r="A335" s="15">
+      <c r="A335" s="1">
         <v>46240</v>
       </c>
       <c r="B335" t="s">
@@ -52772,7 +52765,7 @@
       </c>
     </row>
     <row r="336" ht="15.15" spans="1:50">
-      <c r="A336" s="15">
+      <c r="A336" s="1">
         <v>46240</v>
       </c>
       <c r="B336" t="s">
@@ -52924,151 +52917,151 @@
       </c>
     </row>
     <row r="337" ht="28.35" spans="1:50">
-      <c r="A337" s="15">
+      <c r="A337" s="1">
         <v>46059</v>
       </c>
       <c r="B337" t="s">
         <v>139</v>
       </c>
-      <c r="C337" s="16" t="s">
+      <c r="C337" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D337" s="16" t="s">
+      <c r="D337" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E337" s="17">
+      <c r="E337" s="15">
         <v>1</v>
       </c>
-      <c r="F337" s="17">
+      <c r="F337" s="15">
         <v>3.81</v>
       </c>
-      <c r="G337" s="17">
+      <c r="G337" s="15">
         <v>-4.59</v>
       </c>
-      <c r="H337" s="17">
+      <c r="H337" s="15">
         <v>8</v>
       </c>
-      <c r="I337" s="17">
+      <c r="I337" s="15">
         <v>6</v>
       </c>
-      <c r="J337" s="17">
+      <c r="J337" s="15">
         <v>14</v>
       </c>
-      <c r="K337" s="17">
+      <c r="K337" s="15">
         <v>0.2</v>
       </c>
-      <c r="L337" s="18">
+      <c r="L337" s="16">
         <v>0.0493055555555556</v>
       </c>
-      <c r="M337" s="17">
+      <c r="M337" s="15">
         <v>3423.46</v>
       </c>
-      <c r="N337" s="17">
+      <c r="N337" s="15">
         <v>391.23</v>
       </c>
-      <c r="O337" s="17">
+      <c r="O337" s="15">
         <v>20.772</v>
       </c>
-      <c r="P337" s="17">
+      <c r="P337" s="15">
         <v>57.66</v>
       </c>
-      <c r="Q337" s="17">
+      <c r="Q337" s="15">
         <v>50.1</v>
       </c>
-      <c r="R337" s="17">
+      <c r="R337" s="15">
         <v>5.51</v>
       </c>
-      <c r="S337" s="17">
+      <c r="S337" s="15">
         <v>0.06</v>
       </c>
-      <c r="T337" s="17">
+      <c r="T337" s="15">
         <v>89</v>
       </c>
-      <c r="U337" s="17">
+      <c r="U337" s="15">
         <v>80.49</v>
       </c>
-      <c r="V337" s="17">
+      <c r="V337" s="15">
         <v>44.5</v>
       </c>
-      <c r="W337" s="17">
+      <c r="W337" s="15">
         <v>40.25</v>
       </c>
-      <c r="X337" s="17">
+      <c r="X337" s="15">
         <v>3.41</v>
       </c>
-      <c r="Y337" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z337" s="18">
+      <c r="Y337" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z337" s="16">
         <v>0.00236111111111111</v>
       </c>
-      <c r="AA337" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB337" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC337" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD337" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE337" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF337" s="17">
+      <c r="AA337" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB337" s="16">
+        <v>0</v>
+      </c>
+      <c r="AC337" s="16">
+        <v>0</v>
+      </c>
+      <c r="AD337" s="16">
+        <v>0</v>
+      </c>
+      <c r="AE337" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF337" s="15">
         <v>297.69</v>
       </c>
-      <c r="AG337" s="17">
+      <c r="AG337" s="15">
         <v>233.2</v>
       </c>
-      <c r="AH337" s="17">
+      <c r="AH337" s="15">
         <v>257.51</v>
       </c>
-      <c r="AI337" s="17">
+      <c r="AI337" s="15">
         <v>1852.92</v>
       </c>
-      <c r="AJ337" s="17">
+      <c r="AJ337" s="15">
         <v>1161.43</v>
       </c>
-      <c r="AK337" s="17">
+      <c r="AK337" s="15">
         <v>145.64</v>
       </c>
-      <c r="AL337" s="17">
+      <c r="AL337" s="15">
         <v>5.51</v>
       </c>
-      <c r="AM337" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN337" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO337" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP337" s="17">
+      <c r="AM337" s="15">
+        <v>0</v>
+      </c>
+      <c r="AN337" s="15">
+        <v>0</v>
+      </c>
+      <c r="AO337" s="15">
+        <v>0</v>
+      </c>
+      <c r="AP337" s="15">
         <v>5.51</v>
       </c>
-      <c r="AQ337" s="17">
-        <v>0</v>
-      </c>
-      <c r="AR337" s="17">
+      <c r="AQ337" s="15">
+        <v>0</v>
+      </c>
+      <c r="AR337" s="15">
         <v>0.08</v>
       </c>
-      <c r="AS337" s="17">
+      <c r="AS337" s="15">
         <v>16</v>
       </c>
-      <c r="AT337" s="19" t="s">
+      <c r="AT337" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="AU337" s="19" t="s">
+      <c r="AU337" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="AV337" s="19" t="s">
+      <c r="AV337" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="AW337" s="16" t="s">
+      <c r="AW337" s="14" t="s">
         <v>57</v>
       </c>
       <c r="AX337" s="7" t="s">
@@ -53076,151 +53069,151 @@
       </c>
     </row>
     <row r="338" ht="28.35" spans="1:50">
-      <c r="A338" s="15">
+      <c r="A338" s="1">
         <v>46059</v>
       </c>
       <c r="B338" t="s">
         <v>139</v>
       </c>
-      <c r="C338" s="16" t="s">
+      <c r="C338" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="D338" s="16" t="s">
+      <c r="D338" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E338" s="17">
+      <c r="E338" s="15">
         <v>1</v>
       </c>
-      <c r="F338" s="17">
+      <c r="F338" s="15">
         <v>4.03</v>
       </c>
-      <c r="G338" s="17">
+      <c r="G338" s="15">
         <v>-4.52</v>
       </c>
-      <c r="H338" s="17">
+      <c r="H338" s="15">
         <v>13</v>
       </c>
-      <c r="I338" s="17">
+      <c r="I338" s="15">
         <v>8</v>
       </c>
-      <c r="J338" s="17">
+      <c r="J338" s="15">
         <v>21</v>
       </c>
-      <c r="K338" s="17">
+      <c r="K338" s="15">
         <v>0.3</v>
       </c>
-      <c r="L338" s="18">
+      <c r="L338" s="16">
         <v>0.0493055555555556</v>
       </c>
-      <c r="M338" s="17">
+      <c r="M338" s="15">
         <v>3778.41</v>
       </c>
-      <c r="N338" s="17">
+      <c r="N338" s="15">
         <v>448.49</v>
       </c>
-      <c r="O338" s="17">
+      <c r="O338" s="15">
         <v>23.04</v>
       </c>
-      <c r="P338" s="17">
+      <c r="P338" s="15">
         <v>64.04</v>
       </c>
-      <c r="Q338" s="17">
+      <c r="Q338" s="15">
         <v>53.8</v>
       </c>
-      <c r="R338" s="17">
+      <c r="R338" s="15">
         <v>6.32</v>
       </c>
-      <c r="S338" s="17">
+      <c r="S338" s="15">
         <v>0.06</v>
       </c>
-      <c r="T338" s="17">
-        <v>0</v>
-      </c>
-      <c r="U338" s="17">
-        <v>0</v>
-      </c>
-      <c r="V338" s="17">
-        <v>0</v>
-      </c>
-      <c r="W338" s="17">
-        <v>0</v>
-      </c>
-      <c r="X338" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y338" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z338" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA338" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB338" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC338" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD338" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE338" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF338" s="17">
+      <c r="T338" s="15">
+        <v>0</v>
+      </c>
+      <c r="U338" s="15">
+        <v>0</v>
+      </c>
+      <c r="V338" s="15">
+        <v>0</v>
+      </c>
+      <c r="W338" s="15">
+        <v>0</v>
+      </c>
+      <c r="X338" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y338" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z338" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA338" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB338" s="16">
+        <v>0</v>
+      </c>
+      <c r="AC338" s="16">
+        <v>0</v>
+      </c>
+      <c r="AD338" s="16">
+        <v>0</v>
+      </c>
+      <c r="AE338" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF338" s="15">
         <v>312.99</v>
       </c>
-      <c r="AG338" s="17">
+      <c r="AG338" s="15">
         <v>472.13</v>
       </c>
-      <c r="AH338" s="17">
+      <c r="AH338" s="15">
         <v>511.88</v>
       </c>
-      <c r="AI338" s="17">
+      <c r="AI338" s="15">
         <v>1781.04</v>
       </c>
-      <c r="AJ338" s="17">
+      <c r="AJ338" s="15">
         <v>880.17</v>
       </c>
-      <c r="AK338" s="17">
+      <c r="AK338" s="15">
         <v>454.16</v>
       </c>
-      <c r="AL338" s="17">
+      <c r="AL338" s="15">
         <v>150.89</v>
       </c>
-      <c r="AM338" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN338" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO338" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP338" s="17">
+      <c r="AM338" s="15">
+        <v>0</v>
+      </c>
+      <c r="AN338" s="15">
+        <v>0</v>
+      </c>
+      <c r="AO338" s="15">
+        <v>0</v>
+      </c>
+      <c r="AP338" s="15">
         <v>150.89</v>
       </c>
-      <c r="AQ338" s="17">
+      <c r="AQ338" s="15">
         <v>8</v>
       </c>
-      <c r="AR338" s="17">
+      <c r="AR338" s="15">
         <v>2.13</v>
       </c>
-      <c r="AS338" s="17">
+      <c r="AS338" s="15">
         <v>20</v>
       </c>
-      <c r="AT338" s="19" t="s">
+      <c r="AT338" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="AU338" s="19" t="s">
+      <c r="AU338" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="AV338" s="19" t="s">
+      <c r="AV338" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="AW338" s="16" t="s">
+      <c r="AW338" s="14" t="s">
         <v>57</v>
       </c>
       <c r="AX338" s="7" t="s">
@@ -53228,151 +53221,151 @@
       </c>
     </row>
     <row r="339" ht="28.35" spans="1:50">
-      <c r="A339" s="15">
+      <c r="A339" s="1">
         <v>46059</v>
       </c>
       <c r="B339" t="s">
         <v>139</v>
       </c>
-      <c r="C339" s="16" t="s">
+      <c r="C339" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="D339" s="16" t="s">
+      <c r="D339" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E339" s="17">
+      <c r="E339" s="15">
         <v>1</v>
       </c>
-      <c r="F339" s="17">
+      <c r="F339" s="15">
         <v>3.47</v>
       </c>
-      <c r="G339" s="17">
+      <c r="G339" s="15">
         <v>-3.74</v>
       </c>
-      <c r="H339" s="17">
+      <c r="H339" s="15">
         <v>6</v>
       </c>
-      <c r="I339" s="17">
+      <c r="I339" s="15">
         <v>10</v>
       </c>
-      <c r="J339" s="17">
+      <c r="J339" s="15">
         <v>16</v>
       </c>
-      <c r="K339" s="17">
+      <c r="K339" s="15">
         <v>0.23</v>
       </c>
-      <c r="L339" s="18">
+      <c r="L339" s="16">
         <v>0.0493055555555556</v>
       </c>
-      <c r="M339" s="17">
+      <c r="M339" s="15">
         <v>3396.76</v>
       </c>
-      <c r="N339" s="17">
+      <c r="N339" s="15">
         <v>415.29</v>
       </c>
-      <c r="O339" s="17">
+      <c r="O339" s="15">
         <v>23.94</v>
       </c>
-      <c r="P339" s="17">
+      <c r="P339" s="15">
         <v>66.46</v>
       </c>
-      <c r="Q339" s="17">
+      <c r="Q339" s="15">
         <v>50.06</v>
       </c>
-      <c r="R339" s="17">
+      <c r="R339" s="15">
         <v>5.85</v>
       </c>
-      <c r="S339" s="17">
+      <c r="S339" s="15">
         <v>0.09</v>
       </c>
-      <c r="T339" s="17">
-        <v>0</v>
-      </c>
-      <c r="U339" s="17">
-        <v>0</v>
-      </c>
-      <c r="V339" s="17">
-        <v>0</v>
-      </c>
-      <c r="W339" s="17">
-        <v>0</v>
-      </c>
-      <c r="X339" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y339" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z339" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA339" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB339" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC339" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD339" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE339" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF339" s="17">
+      <c r="T339" s="15">
+        <v>0</v>
+      </c>
+      <c r="U339" s="15">
+        <v>0</v>
+      </c>
+      <c r="V339" s="15">
+        <v>0</v>
+      </c>
+      <c r="W339" s="15">
+        <v>0</v>
+      </c>
+      <c r="X339" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y339" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z339" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA339" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB339" s="16">
+        <v>0</v>
+      </c>
+      <c r="AC339" s="16">
+        <v>0</v>
+      </c>
+      <c r="AD339" s="16">
+        <v>0</v>
+      </c>
+      <c r="AE339" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF339" s="15">
         <v>300.44</v>
       </c>
-      <c r="AG339" s="17">
+      <c r="AG339" s="15">
         <v>442.61</v>
       </c>
-      <c r="AH339" s="17">
+      <c r="AH339" s="15">
         <v>219.15</v>
       </c>
-      <c r="AI339" s="17">
+      <c r="AI339" s="15">
         <v>1538.14</v>
       </c>
-      <c r="AJ339" s="17">
+      <c r="AJ339" s="15">
         <v>1163.43</v>
       </c>
-      <c r="AK339" s="17">
+      <c r="AK339" s="15">
         <v>388.19</v>
       </c>
-      <c r="AL339" s="17">
+      <c r="AL339" s="15">
         <v>87.65</v>
       </c>
-      <c r="AM339" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN339" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO339" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP339" s="17">
+      <c r="AM339" s="15">
+        <v>0</v>
+      </c>
+      <c r="AN339" s="15">
+        <v>0</v>
+      </c>
+      <c r="AO339" s="15">
+        <v>0</v>
+      </c>
+      <c r="AP339" s="15">
         <v>87.65</v>
       </c>
-      <c r="AQ339" s="17">
+      <c r="AQ339" s="15">
         <v>6</v>
       </c>
-      <c r="AR339" s="17">
+      <c r="AR339" s="15">
         <v>1.23</v>
       </c>
-      <c r="AS339" s="17">
+      <c r="AS339" s="15">
         <v>15</v>
       </c>
-      <c r="AT339" s="19" t="s">
+      <c r="AT339" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="AU339" s="19" t="s">
+      <c r="AU339" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="AV339" s="19" t="s">
+      <c r="AV339" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="AW339" s="16" t="s">
+      <c r="AW339" s="14" t="s">
         <v>57</v>
       </c>
       <c r="AX339" s="7" t="s">
@@ -53380,151 +53373,151 @@
       </c>
     </row>
     <row r="340" ht="28.35" spans="1:50">
-      <c r="A340" s="15">
+      <c r="A340" s="1">
         <v>46059</v>
       </c>
       <c r="B340" t="s">
         <v>139</v>
       </c>
-      <c r="C340" s="16" t="s">
+      <c r="C340" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="D340" s="16" t="s">
+      <c r="D340" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E340" s="17">
+      <c r="E340" s="15">
         <v>1</v>
       </c>
-      <c r="F340" s="17">
+      <c r="F340" s="15">
         <v>3.58</v>
       </c>
-      <c r="G340" s="17">
+      <c r="G340" s="15">
         <v>-3.75</v>
       </c>
-      <c r="H340" s="17">
+      <c r="H340" s="15">
         <v>2</v>
       </c>
-      <c r="I340" s="17">
+      <c r="I340" s="15">
         <v>6</v>
       </c>
-      <c r="J340" s="17">
+      <c r="J340" s="15">
         <v>8</v>
       </c>
-      <c r="K340" s="17">
+      <c r="K340" s="15">
         <v>0.11</v>
       </c>
-      <c r="L340" s="18">
+      <c r="L340" s="16">
         <v>0.0493055555555556</v>
       </c>
-      <c r="M340" s="17">
+      <c r="M340" s="15">
         <v>3584.24</v>
       </c>
-      <c r="N340" s="17">
+      <c r="N340" s="15">
         <v>374.29</v>
       </c>
-      <c r="O340" s="17">
+      <c r="O340" s="15">
         <v>21.096</v>
       </c>
-      <c r="P340" s="17">
+      <c r="P340" s="15">
         <v>58.62</v>
       </c>
-      <c r="Q340" s="17">
+      <c r="Q340" s="15">
         <v>51.88</v>
       </c>
-      <c r="R340" s="17">
+      <c r="R340" s="15">
         <v>5.27</v>
       </c>
-      <c r="S340" s="17">
+      <c r="S340" s="15">
         <v>0.07</v>
       </c>
-      <c r="T340" s="17">
-        <v>0</v>
-      </c>
-      <c r="U340" s="17">
-        <v>0</v>
-      </c>
-      <c r="V340" s="17">
-        <v>0</v>
-      </c>
-      <c r="W340" s="17">
-        <v>0</v>
-      </c>
-      <c r="X340" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y340" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z340" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA340" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB340" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC340" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD340" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE340" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF340" s="17">
+      <c r="T340" s="15">
+        <v>0</v>
+      </c>
+      <c r="U340" s="15">
+        <v>0</v>
+      </c>
+      <c r="V340" s="15">
+        <v>0</v>
+      </c>
+      <c r="W340" s="15">
+        <v>0</v>
+      </c>
+      <c r="X340" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y340" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z340" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA340" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB340" s="16">
+        <v>0</v>
+      </c>
+      <c r="AC340" s="16">
+        <v>0</v>
+      </c>
+      <c r="AD340" s="16">
+        <v>0</v>
+      </c>
+      <c r="AE340" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF340" s="15">
         <v>308.9</v>
       </c>
-      <c r="AG340" s="17">
+      <c r="AG340" s="15">
         <v>332.7</v>
       </c>
-      <c r="AH340" s="17">
+      <c r="AH340" s="15">
         <v>205.54</v>
       </c>
-      <c r="AI340" s="17">
+      <c r="AI340" s="15">
         <v>1925.71</v>
       </c>
-      <c r="AJ340" s="17">
+      <c r="AJ340" s="15">
         <v>1052.88</v>
       </c>
-      <c r="AK340" s="17">
+      <c r="AK340" s="15">
         <v>372.46</v>
       </c>
-      <c r="AL340" s="17">
+      <c r="AL340" s="15">
         <v>27.35</v>
       </c>
-      <c r="AM340" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN340" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO340" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP340" s="17">
+      <c r="AM340" s="15">
+        <v>0</v>
+      </c>
+      <c r="AN340" s="15">
+        <v>0</v>
+      </c>
+      <c r="AO340" s="15">
+        <v>0</v>
+      </c>
+      <c r="AP340" s="15">
         <v>27.35</v>
       </c>
-      <c r="AQ340" s="17">
+      <c r="AQ340" s="15">
         <v>2</v>
       </c>
-      <c r="AR340" s="17">
+      <c r="AR340" s="15">
         <v>0.39</v>
       </c>
-      <c r="AS340" s="17">
+      <c r="AS340" s="15">
         <v>15</v>
       </c>
-      <c r="AT340" s="19" t="s">
+      <c r="AT340" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="AU340" s="19" t="s">
+      <c r="AU340" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="AV340" s="19" t="s">
+      <c r="AV340" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="AW340" s="16" t="s">
+      <c r="AW340" s="14" t="s">
         <v>57</v>
       </c>
       <c r="AX340" s="7" t="s">
@@ -53532,151 +53525,151 @@
       </c>
     </row>
     <row r="341" ht="28.35" spans="1:50">
-      <c r="A341" s="15">
+      <c r="A341" s="1">
         <v>46059</v>
       </c>
       <c r="B341" t="s">
         <v>139</v>
       </c>
-      <c r="C341" s="16" t="s">
+      <c r="C341" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="D341" s="16" t="s">
+      <c r="D341" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E341" s="17">
+      <c r="E341" s="15">
         <v>1</v>
       </c>
-      <c r="F341" s="17">
+      <c r="F341" s="15">
         <v>4.2</v>
       </c>
-      <c r="G341" s="17">
+      <c r="G341" s="15">
         <v>-3.62</v>
       </c>
-      <c r="H341" s="17">
+      <c r="H341" s="15">
         <v>9</v>
       </c>
-      <c r="I341" s="17">
+      <c r="I341" s="15">
         <v>5</v>
       </c>
-      <c r="J341" s="17">
+      <c r="J341" s="15">
         <v>14</v>
       </c>
-      <c r="K341" s="17">
+      <c r="K341" s="15">
         <v>0.2</v>
       </c>
-      <c r="L341" s="18">
+      <c r="L341" s="16">
         <v>0.0493055555555556</v>
       </c>
-      <c r="M341" s="17">
+      <c r="M341" s="15">
         <v>2865.26</v>
       </c>
-      <c r="N341" s="17">
+      <c r="N341" s="15">
         <v>353.89</v>
       </c>
-      <c r="O341" s="17">
+      <c r="O341" s="15">
         <v>20.772</v>
       </c>
-      <c r="P341" s="17">
+      <c r="P341" s="15">
         <v>57.74</v>
       </c>
-      <c r="Q341" s="17">
+      <c r="Q341" s="15">
         <v>41.86</v>
       </c>
-      <c r="R341" s="17">
+      <c r="R341" s="15">
         <v>4.98</v>
       </c>
-      <c r="S341" s="17">
+      <c r="S341" s="15">
         <v>0.04</v>
       </c>
-      <c r="T341" s="17">
-        <v>0</v>
-      </c>
-      <c r="U341" s="17">
-        <v>0</v>
-      </c>
-      <c r="V341" s="17">
-        <v>0</v>
-      </c>
-      <c r="W341" s="17">
-        <v>0</v>
-      </c>
-      <c r="X341" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y341" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z341" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA341" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB341" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC341" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD341" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE341" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF341" s="17">
+      <c r="T341" s="15">
+        <v>0</v>
+      </c>
+      <c r="U341" s="15">
+        <v>0</v>
+      </c>
+      <c r="V341" s="15">
+        <v>0</v>
+      </c>
+      <c r="W341" s="15">
+        <v>0</v>
+      </c>
+      <c r="X341" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y341" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z341" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA341" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB341" s="16">
+        <v>0</v>
+      </c>
+      <c r="AC341" s="16">
+        <v>0</v>
+      </c>
+      <c r="AD341" s="16">
+        <v>0</v>
+      </c>
+      <c r="AE341" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF341" s="15">
         <v>236.91</v>
       </c>
-      <c r="AG341" s="17">
+      <c r="AG341" s="15">
         <v>248.81</v>
       </c>
-      <c r="AH341" s="17">
+      <c r="AH341" s="15">
         <v>361.48</v>
       </c>
-      <c r="AI341" s="17">
+      <c r="AI341" s="15">
         <v>1508.67</v>
       </c>
-      <c r="AJ341" s="17">
+      <c r="AJ341" s="15">
         <v>731.68</v>
       </c>
-      <c r="AK341" s="17">
+      <c r="AK341" s="15">
         <v>245.98</v>
       </c>
-      <c r="AL341" s="17">
+      <c r="AL341" s="15">
         <v>17.44</v>
       </c>
-      <c r="AM341" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN341" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO341" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP341" s="17">
+      <c r="AM341" s="15">
+        <v>0</v>
+      </c>
+      <c r="AN341" s="15">
+        <v>0</v>
+      </c>
+      <c r="AO341" s="15">
+        <v>0</v>
+      </c>
+      <c r="AP341" s="15">
         <v>17.44</v>
       </c>
-      <c r="AQ341" s="17">
+      <c r="AQ341" s="15">
         <v>1</v>
       </c>
-      <c r="AR341" s="17">
+      <c r="AR341" s="15">
         <v>0.25</v>
       </c>
-      <c r="AS341" s="17">
+      <c r="AS341" s="15">
         <v>41</v>
       </c>
-      <c r="AT341" s="19" t="s">
+      <c r="AT341" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="AU341" s="19" t="s">
+      <c r="AU341" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="AV341" s="19" t="s">
+      <c r="AV341" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="AW341" s="16" t="s">
+      <c r="AW341" s="14" t="s">
         <v>57</v>
       </c>
       <c r="AX341" s="7" t="s">
@@ -53684,151 +53677,151 @@
       </c>
     </row>
     <row r="342" ht="28.35" spans="1:50">
-      <c r="A342" s="15">
+      <c r="A342" s="1">
         <v>46059</v>
       </c>
       <c r="B342" t="s">
         <v>139</v>
       </c>
-      <c r="C342" s="16" t="s">
+      <c r="C342" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="D342" s="16" t="s">
+      <c r="D342" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E342" s="17">
+      <c r="E342" s="15">
         <v>1</v>
       </c>
-      <c r="F342" s="17">
+      <c r="F342" s="15">
         <v>3.3</v>
       </c>
-      <c r="G342" s="17">
+      <c r="G342" s="15">
         <v>-4.3</v>
       </c>
-      <c r="H342" s="17">
+      <c r="H342" s="15">
         <v>5</v>
       </c>
-      <c r="I342" s="17">
+      <c r="I342" s="15">
         <v>12</v>
       </c>
-      <c r="J342" s="17">
+      <c r="J342" s="15">
         <v>17</v>
       </c>
-      <c r="K342" s="17">
+      <c r="K342" s="15">
         <v>0.24</v>
       </c>
-      <c r="L342" s="18">
+      <c r="L342" s="16">
         <v>0.0493055555555556</v>
       </c>
-      <c r="M342" s="17">
+      <c r="M342" s="15">
         <v>3359.22</v>
       </c>
-      <c r="N342" s="17">
+      <c r="N342" s="15">
         <v>353.95</v>
       </c>
-      <c r="O342" s="17">
+      <c r="O342" s="15">
         <v>21.996</v>
       </c>
-      <c r="P342" s="17">
+      <c r="P342" s="15">
         <v>61.11</v>
       </c>
-      <c r="Q342" s="17">
+      <c r="Q342" s="15">
         <v>49.69</v>
       </c>
-      <c r="R342" s="17">
+      <c r="R342" s="15">
         <v>4.99</v>
       </c>
-      <c r="S342" s="17">
+      <c r="S342" s="15">
         <v>0.08</v>
       </c>
-      <c r="T342" s="17">
-        <v>0</v>
-      </c>
-      <c r="U342" s="17">
-        <v>0</v>
-      </c>
-      <c r="V342" s="17">
-        <v>0</v>
-      </c>
-      <c r="W342" s="17">
-        <v>0</v>
-      </c>
-      <c r="X342" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y342" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z342" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA342" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB342" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC342" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD342" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE342" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF342" s="17">
+      <c r="T342" s="15">
+        <v>0</v>
+      </c>
+      <c r="U342" s="15">
+        <v>0</v>
+      </c>
+      <c r="V342" s="15">
+        <v>0</v>
+      </c>
+      <c r="W342" s="15">
+        <v>0</v>
+      </c>
+      <c r="X342" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y342" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z342" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA342" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB342" s="16">
+        <v>0</v>
+      </c>
+      <c r="AC342" s="16">
+        <v>0</v>
+      </c>
+      <c r="AD342" s="16">
+        <v>0</v>
+      </c>
+      <c r="AE342" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF342" s="15">
         <v>300.91</v>
       </c>
-      <c r="AG342" s="17">
+      <c r="AG342" s="15">
         <v>354.59</v>
       </c>
-      <c r="AH342" s="17">
+      <c r="AH342" s="15">
         <v>182.24</v>
       </c>
-      <c r="AI342" s="17">
+      <c r="AI342" s="15">
         <v>1605.07</v>
       </c>
-      <c r="AJ342" s="17">
+      <c r="AJ342" s="15">
         <v>1324.89</v>
       </c>
-      <c r="AK342" s="17">
+      <c r="AK342" s="15">
         <v>237.94</v>
       </c>
-      <c r="AL342" s="17">
+      <c r="AL342" s="15">
         <v>8.81</v>
       </c>
-      <c r="AM342" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN342" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO342" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP342" s="17">
+      <c r="AM342" s="15">
+        <v>0</v>
+      </c>
+      <c r="AN342" s="15">
+        <v>0</v>
+      </c>
+      <c r="AO342" s="15">
+        <v>0</v>
+      </c>
+      <c r="AP342" s="15">
         <v>8.81</v>
       </c>
-      <c r="AQ342" s="17">
+      <c r="AQ342" s="15">
         <v>1</v>
       </c>
-      <c r="AR342" s="17">
+      <c r="AR342" s="15">
         <v>0.12</v>
       </c>
-      <c r="AS342" s="17">
+      <c r="AS342" s="15">
         <v>11</v>
       </c>
-      <c r="AT342" s="19" t="s">
+      <c r="AT342" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="AU342" s="19" t="s">
+      <c r="AU342" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="AV342" s="19" t="s">
+      <c r="AV342" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="AW342" s="16" t="s">
+      <c r="AW342" s="14" t="s">
         <v>57</v>
       </c>
       <c r="AX342" s="7" t="s">
@@ -53836,151 +53829,151 @@
       </c>
     </row>
     <row r="343" ht="28.35" spans="1:50">
-      <c r="A343" s="15">
+      <c r="A343" s="1">
         <v>46059</v>
       </c>
       <c r="B343" t="s">
         <v>139</v>
       </c>
-      <c r="C343" s="16" t="s">
+      <c r="C343" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="D343" s="16" t="s">
+      <c r="D343" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E343" s="17">
+      <c r="E343" s="15">
         <v>1</v>
       </c>
-      <c r="F343" s="17">
-        <v>0</v>
-      </c>
-      <c r="G343" s="17">
-        <v>0</v>
-      </c>
-      <c r="H343" s="17">
-        <v>0</v>
-      </c>
-      <c r="I343" s="17">
-        <v>0</v>
-      </c>
-      <c r="J343" s="17">
-        <v>0</v>
-      </c>
-      <c r="K343" s="17">
-        <v>0</v>
-      </c>
-      <c r="L343" s="18">
+      <c r="F343" s="15">
+        <v>0</v>
+      </c>
+      <c r="G343" s="15">
+        <v>0</v>
+      </c>
+      <c r="H343" s="15">
+        <v>0</v>
+      </c>
+      <c r="I343" s="15">
+        <v>0</v>
+      </c>
+      <c r="J343" s="15">
+        <v>0</v>
+      </c>
+      <c r="K343" s="15">
+        <v>0</v>
+      </c>
+      <c r="L343" s="16">
         <v>0.0493055555555556</v>
       </c>
-      <c r="M343" s="17">
+      <c r="M343" s="15">
         <v>2380.96</v>
       </c>
-      <c r="N343" s="17">
+      <c r="N343" s="15">
         <v>438.2</v>
       </c>
-      <c r="O343" s="17">
+      <c r="O343" s="15">
         <v>19.764</v>
       </c>
-      <c r="P343" s="17">
+      <c r="P343" s="15">
         <v>54.86</v>
       </c>
-      <c r="Q343" s="17">
+      <c r="Q343" s="15">
         <v>43.35</v>
       </c>
-      <c r="R343" s="17">
+      <c r="R343" s="15">
         <v>6.17</v>
       </c>
-      <c r="S343" s="17">
+      <c r="S343" s="15">
         <v>0.04</v>
       </c>
-      <c r="T343" s="17">
-        <v>0</v>
-      </c>
-      <c r="U343" s="17">
-        <v>0</v>
-      </c>
-      <c r="V343" s="17">
-        <v>0</v>
-      </c>
-      <c r="W343" s="17">
-        <v>0</v>
-      </c>
-      <c r="X343" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y343" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z343" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA343" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB343" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC343" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD343" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE343" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF343" s="17">
+      <c r="T343" s="15">
+        <v>0</v>
+      </c>
+      <c r="U343" s="15">
+        <v>0</v>
+      </c>
+      <c r="V343" s="15">
+        <v>0</v>
+      </c>
+      <c r="W343" s="15">
+        <v>0</v>
+      </c>
+      <c r="X343" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y343" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z343" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA343" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB343" s="16">
+        <v>0</v>
+      </c>
+      <c r="AC343" s="16">
+        <v>0</v>
+      </c>
+      <c r="AD343" s="16">
+        <v>0</v>
+      </c>
+      <c r="AE343" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF343" s="15">
         <v>134.62</v>
       </c>
-      <c r="AG343" s="17">
+      <c r="AG343" s="15">
         <v>166.98</v>
       </c>
-      <c r="AH343" s="17">
+      <c r="AH343" s="15">
         <v>544.5</v>
       </c>
-      <c r="AI343" s="17">
+      <c r="AI343" s="15">
         <v>1218.31</v>
       </c>
-      <c r="AJ343" s="17">
+      <c r="AJ343" s="15">
         <v>551.41</v>
       </c>
-      <c r="AK343" s="17">
+      <c r="AK343" s="15">
         <v>66.74</v>
       </c>
-      <c r="AL343" s="17">
-        <v>0</v>
-      </c>
-      <c r="AM343" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN343" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO343" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP343" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ343" s="17">
-        <v>0</v>
-      </c>
-      <c r="AR343" s="17">
-        <v>0</v>
-      </c>
-      <c r="AS343" s="17">
+      <c r="AL343" s="15">
+        <v>0</v>
+      </c>
+      <c r="AM343" s="15">
+        <v>0</v>
+      </c>
+      <c r="AN343" s="15">
+        <v>0</v>
+      </c>
+      <c r="AO343" s="15">
+        <v>0</v>
+      </c>
+      <c r="AP343" s="15">
+        <v>0</v>
+      </c>
+      <c r="AQ343" s="15">
+        <v>0</v>
+      </c>
+      <c r="AR343" s="15">
+        <v>0</v>
+      </c>
+      <c r="AS343" s="15">
         <v>35</v>
       </c>
-      <c r="AT343" s="19" t="s">
+      <c r="AT343" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AU343" s="19" t="s">
+      <c r="AU343" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="AV343" s="19" t="s">
+      <c r="AV343" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="AW343" s="16" t="s">
+      <c r="AW343" s="14" t="s">
         <v>57</v>
       </c>
       <c r="AX343" s="7" t="s">

--- a/GPS_Formativas_2026.xlsx
+++ b/GPS_Formativas_2026.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="GPS_Formativas_2026" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GPS_Formativas_2026!$A$1:$AX$343</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -629,7 +632,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="m/d/yy;@"/>
+    <numFmt numFmtId="178" formatCode="m/d/yyyy;@"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -32570,7 +32573,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="203" ht="15.15" spans="1:50">
+    <row r="203" spans="1:50">
       <c r="A203" s="1">
         <v>46028</v>
       </c>
@@ -32722,7 +32725,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="204" ht="15.15" spans="1:50">
+    <row r="204" spans="1:50">
       <c r="A204" s="1">
         <v>46028</v>
       </c>
@@ -32874,7 +32877,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="205" ht="15.15" spans="1:50">
+    <row r="205" spans="1:50">
       <c r="A205" s="1">
         <v>46028</v>
       </c>
@@ -33026,7 +33029,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="206" ht="15.15" spans="1:50">
+    <row r="206" spans="1:50">
       <c r="A206" s="1">
         <v>46028</v>
       </c>
@@ -33178,7 +33181,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="207" ht="15.15" spans="1:50">
+    <row r="207" spans="1:50">
       <c r="A207" s="1">
         <v>46028</v>
       </c>
@@ -33330,7 +33333,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="208" ht="15.15" spans="1:50">
+    <row r="208" spans="1:50">
       <c r="A208" s="1">
         <v>46028</v>
       </c>
@@ -33482,7 +33485,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="209" ht="15.15" spans="1:50">
+    <row r="209" spans="1:50">
       <c r="A209" s="1">
         <v>46028</v>
       </c>
@@ -33634,7 +33637,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="210" ht="15.15" spans="1:50">
+    <row r="210" spans="1:50">
       <c r="A210" s="1">
         <v>46028</v>
       </c>
@@ -33786,7 +33789,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="211" ht="15.15" spans="1:50">
+    <row r="211" spans="1:50">
       <c r="A211" s="1">
         <v>46059</v>
       </c>
@@ -33938,7 +33941,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="212" ht="15.15" spans="1:50">
+    <row r="212" spans="1:50">
       <c r="A212" s="1">
         <v>46059</v>
       </c>
@@ -34090,7 +34093,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="213" ht="15.15" spans="1:50">
+    <row r="213" spans="1:50">
       <c r="A213" s="1">
         <v>46059</v>
       </c>
@@ -34242,7 +34245,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="214" ht="15.15" spans="1:50">
+    <row r="214" spans="1:50">
       <c r="A214" s="1">
         <v>46059</v>
       </c>
@@ -34394,7 +34397,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="215" ht="15.15" spans="1:50">
+    <row r="215" spans="1:50">
       <c r="A215" s="1">
         <v>46059</v>
       </c>
@@ -34546,7 +34549,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="216" ht="15.15" spans="1:50">
+    <row r="216" spans="1:50">
       <c r="A216" s="1">
         <v>46059</v>
       </c>
@@ -34698,7 +34701,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="217" ht="15.15" spans="1:50">
+    <row r="217" spans="1:50">
       <c r="A217" s="1">
         <v>46059</v>
       </c>
@@ -34850,7 +34853,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="218" ht="15.15" spans="1:50">
+    <row r="218" spans="1:50">
       <c r="A218" s="1">
         <v>46059</v>
       </c>
@@ -35610,7 +35613,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="223" ht="15.15" spans="1:50">
+    <row r="223" spans="1:50">
       <c r="A223" s="1" t="s">
         <v>138</v>
       </c>
@@ -35762,7 +35765,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="224" ht="15.15" spans="1:50">
+    <row r="224" spans="1:50">
       <c r="A224" s="1" t="s">
         <v>138</v>
       </c>
@@ -35914,7 +35917,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="225" ht="15.15" spans="1:50">
+    <row r="225" spans="1:50">
       <c r="A225" s="1" t="s">
         <v>138</v>
       </c>
@@ -36066,7 +36069,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="226" ht="15.15" spans="1:50">
+    <row r="226" spans="1:50">
       <c r="A226" s="1" t="s">
         <v>138</v>
       </c>
@@ -36218,7 +36221,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="227" ht="15.15" spans="1:50">
+    <row r="227" spans="1:50">
       <c r="A227" s="1" t="s">
         <v>138</v>
       </c>
@@ -36370,7 +36373,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="228" ht="15.15" spans="1:50">
+    <row r="228" spans="1:50">
       <c r="A228" s="1" t="s">
         <v>138</v>
       </c>
@@ -36522,7 +36525,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="229" ht="15.15" spans="1:50">
+    <row r="229" spans="1:50">
       <c r="A229" s="1" t="s">
         <v>138</v>
       </c>
@@ -37574,7 +37577,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="236" ht="15.15" spans="1:50">
+    <row r="236" spans="1:50">
       <c r="A236" s="1">
         <v>46059</v>
       </c>
@@ -37724,7 +37727,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="237" ht="15.15" spans="1:50">
+    <row r="237" spans="1:50">
       <c r="A237" s="1">
         <v>46059</v>
       </c>
@@ -37874,7 +37877,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="238" ht="15.15" spans="1:50">
+    <row r="238" spans="1:50">
       <c r="A238" s="1">
         <v>46059</v>
       </c>
@@ -38024,7 +38027,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="239" ht="15.15" spans="1:50">
+    <row r="239" spans="1:50">
       <c r="A239" s="1">
         <v>46059</v>
       </c>
@@ -38174,7 +38177,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="240" ht="15.15" spans="1:50">
+    <row r="240" spans="1:50">
       <c r="A240" s="1">
         <v>46059</v>
       </c>
@@ -42124,7 +42127,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="266" ht="15.15" spans="1:50">
+    <row r="266" spans="1:50">
       <c r="A266" s="1">
         <v>46059</v>
       </c>
@@ -42276,7 +42279,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="267" ht="15.15" spans="1:50">
+    <row r="267" spans="1:50">
       <c r="A267" s="1">
         <v>46059</v>
       </c>
@@ -42428,7 +42431,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="268" ht="15.15" spans="1:50">
+    <row r="268" spans="1:50">
       <c r="A268" s="1">
         <v>46059</v>
       </c>
@@ -42580,7 +42583,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="269" ht="15.15" spans="1:50">
+    <row r="269" spans="1:50">
       <c r="A269" s="1">
         <v>46059</v>
       </c>
@@ -42732,7 +42735,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="270" ht="15.15" spans="1:50">
+    <row r="270" spans="1:50">
       <c r="A270" s="1">
         <v>46059</v>
       </c>
@@ -42884,7 +42887,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="271" ht="15.15" spans="1:50">
+    <row r="271" spans="1:50">
       <c r="A271" s="1">
         <v>46059</v>
       </c>
@@ -43036,7 +43039,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="272" ht="15.15" spans="1:50">
+    <row r="272" spans="1:50">
       <c r="A272" s="1">
         <v>46059</v>
       </c>
@@ -43188,7 +43191,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="273" ht="15.15" spans="1:50">
+    <row r="273" spans="1:50">
       <c r="A273" s="1">
         <v>46059</v>
       </c>
@@ -43340,7 +43343,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="274" ht="15.15" spans="1:50">
+    <row r="274" spans="1:50">
       <c r="A274" s="12" t="s">
         <v>154</v>
       </c>
@@ -43492,7 +43495,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="275" ht="15.15" spans="1:50">
+    <row r="275" spans="1:50">
       <c r="A275" s="12" t="s">
         <v>154</v>
       </c>
@@ -43644,7 +43647,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="276" ht="15.15" spans="1:50">
+    <row r="276" spans="1:50">
       <c r="A276" s="12" t="s">
         <v>154</v>
       </c>
@@ -43796,7 +43799,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="277" ht="15.15" spans="1:50">
+    <row r="277" spans="1:50">
       <c r="A277" s="12" t="s">
         <v>154</v>
       </c>
@@ -43948,7 +43951,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="278" ht="15.15" spans="1:50">
+    <row r="278" spans="1:50">
       <c r="A278" s="12" t="s">
         <v>154</v>
       </c>
@@ -44100,7 +44103,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="279" ht="15.15" spans="1:50">
+    <row r="279" spans="1:50">
       <c r="A279" s="12" t="s">
         <v>154</v>
       </c>
@@ -44252,7 +44255,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="280" ht="15.15" spans="1:50">
+    <row r="280" spans="1:50">
       <c r="A280" s="12" t="s">
         <v>154</v>
       </c>
@@ -44404,7 +44407,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="281" ht="15.15" spans="1:50">
+    <row r="281" spans="1:50">
       <c r="A281" s="12" t="s">
         <v>154</v>
       </c>
@@ -44556,7 +44559,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="282" ht="15.15" spans="1:50">
+    <row r="282" spans="1:50">
       <c r="A282" s="12" t="s">
         <v>154</v>
       </c>
@@ -44708,7 +44711,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="283" ht="15.15" spans="1:50">
+    <row r="283" spans="1:50">
       <c r="A283" s="12" t="s">
         <v>154</v>
       </c>
@@ -45012,7 +45015,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="285" ht="15.15" spans="1:50">
+    <row r="285" spans="1:50">
       <c r="A285" s="12" t="s">
         <v>154</v>
       </c>
@@ -45164,7 +45167,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="286" ht="15.15" spans="1:50">
+    <row r="286" spans="1:50">
       <c r="A286" s="12" t="s">
         <v>154</v>
       </c>
@@ -45316,7 +45319,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="287" ht="15.15" spans="1:50">
+    <row r="287" spans="1:50">
       <c r="A287" s="12" t="s">
         <v>154</v>
       </c>
@@ -45468,7 +45471,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="288" ht="15.15" spans="1:50">
+    <row r="288" spans="1:50">
       <c r="A288" s="12" t="s">
         <v>154</v>
       </c>
@@ -45620,7 +45623,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="289" ht="15.15" spans="1:50">
+    <row r="289" spans="1:50">
       <c r="A289" s="12" t="s">
         <v>154</v>
       </c>
@@ -45772,7 +45775,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="290" ht="15.15" spans="1:50">
+    <row r="290" spans="1:50">
       <c r="A290" s="12" t="s">
         <v>154</v>
       </c>
@@ -45924,7 +45927,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="291" ht="15.15" spans="1:50">
+    <row r="291" spans="1:50">
       <c r="A291" s="12" t="s">
         <v>154</v>
       </c>
@@ -46228,7 +46231,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="293" ht="15.15" spans="1:50">
+    <row r="293" spans="1:50">
       <c r="A293" s="12" t="s">
         <v>154</v>
       </c>
@@ -46532,7 +46535,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="295" ht="15.15" spans="1:50">
+    <row r="295" spans="1:50">
       <c r="A295" s="12" t="s">
         <v>154</v>
       </c>
@@ -46684,7 +46687,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="296" ht="15.15" spans="1:50">
+    <row r="296" spans="1:50">
       <c r="A296" s="12" t="s">
         <v>154</v>
       </c>
@@ -46836,7 +46839,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="297" ht="15.15" spans="1:50">
+    <row r="297" spans="1:50">
       <c r="A297" s="12" t="s">
         <v>154</v>
       </c>
@@ -47748,7 +47751,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="303" ht="15.15" spans="1:50">
+    <row r="303" spans="1:50">
       <c r="A303" s="12">
         <v>46059</v>
       </c>
@@ -47900,7 +47903,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="304" ht="15.15" spans="1:50">
+    <row r="304" spans="1:50">
       <c r="A304" s="12">
         <v>46059</v>
       </c>
@@ -48052,7 +48055,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="305" ht="15.15" spans="1:50">
+    <row r="305" spans="1:50">
       <c r="A305" s="12">
         <v>46059</v>
       </c>
@@ -48204,7 +48207,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="306" ht="15.15" spans="1:50">
+    <row r="306" spans="1:50">
       <c r="A306" s="12">
         <v>46059</v>
       </c>
@@ -48356,7 +48359,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="307" ht="15.15" spans="1:50">
+    <row r="307" spans="1:50">
       <c r="A307" s="12">
         <v>46059</v>
       </c>
@@ -50636,7 +50639,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="322" ht="15.15" spans="1:50">
+    <row r="322" spans="1:50">
       <c r="A322" s="1">
         <v>46148</v>
       </c>
@@ -50788,7 +50791,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="323" ht="15.15" spans="1:50">
+    <row r="323" spans="1:50">
       <c r="A323" s="1">
         <v>46148</v>
       </c>
@@ -50940,7 +50943,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="324" ht="15.15" spans="1:50">
+    <row r="324" spans="1:50">
       <c r="A324" s="1">
         <v>46148</v>
       </c>
@@ -51092,7 +51095,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="325" ht="15.15" spans="1:50">
+    <row r="325" spans="1:50">
       <c r="A325" s="1">
         <v>46148</v>
       </c>
@@ -51244,7 +51247,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="326" ht="15.15" spans="1:50">
+    <row r="326" spans="1:50">
       <c r="A326" s="1">
         <v>46148</v>
       </c>
@@ -51396,7 +51399,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="327" ht="15.15" spans="1:50">
+    <row r="327" spans="1:50">
       <c r="A327" s="1">
         <v>46148</v>
       </c>
@@ -51548,7 +51551,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="328" ht="15.15" spans="1:50">
+    <row r="328" spans="1:50">
       <c r="A328" s="1">
         <v>46148</v>
       </c>
@@ -51700,7 +51703,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="329" ht="15.15" spans="1:50">
+    <row r="329" spans="1:50">
       <c r="A329" s="1">
         <v>46148</v>
       </c>
@@ -51852,7 +51855,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="330" ht="15.15" spans="1:50">
+    <row r="330" spans="1:50">
       <c r="A330" s="1">
         <v>46148</v>
       </c>
@@ -52004,7 +52007,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="331" ht="15.15" spans="1:50">
+    <row r="331" spans="1:50">
       <c r="A331" s="1">
         <v>46240</v>
       </c>
@@ -52156,7 +52159,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="332" ht="15.15" spans="1:50">
+    <row r="332" spans="1:50">
       <c r="A332" s="1">
         <v>46240</v>
       </c>
@@ -52308,7 +52311,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="333" ht="15.15" spans="1:50">
+    <row r="333" spans="1:50">
       <c r="A333" s="1">
         <v>46240</v>
       </c>
@@ -52460,7 +52463,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="334" ht="15.15" spans="1:50">
+    <row r="334" spans="1:50">
       <c r="A334" s="1">
         <v>46240</v>
       </c>
@@ -52612,7 +52615,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="335" ht="15.15" spans="1:50">
+    <row r="335" spans="1:50">
       <c r="A335" s="1">
         <v>46240</v>
       </c>
@@ -52764,7 +52767,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="336" ht="15.15" spans="1:50">
+    <row r="336" spans="1:50">
       <c r="A336" s="1">
         <v>46240</v>
       </c>
@@ -53981,6 +53984,9 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AX343" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/GPS_Formativas_2026.xlsx
+++ b/GPS_Formativas_2026.xlsx
@@ -182,7 +182,7 @@
     <t>Period Tags</t>
   </si>
   <si>
-    <t>18/5/26</t>
+    <t>18/5/2026</t>
   </si>
   <si>
     <t>U19</t>
@@ -260,7 +260,7 @@
     <t>LAT</t>
   </si>
   <si>
-    <t>19/5/26</t>
+    <t>19/5/2026</t>
   </si>
   <si>
     <t>Thiago Amaro</t>
@@ -314,7 +314,7 @@
     <t>Simon Sueiro</t>
   </si>
   <si>
-    <t>20/5/26</t>
+    <t>20/5/2026</t>
   </si>
   <si>
     <t>MD-2</t>
@@ -326,7 +326,7 @@
     <t>Thiago Santurion</t>
   </si>
   <si>
-    <t>21/5/26</t>
+    <t>21/5/2026</t>
   </si>
   <si>
     <t>Juan Manuel Alvarez</t>
@@ -362,7 +362,7 @@
     <t>Rodrigo Rios</t>
   </si>
   <si>
-    <t>22/5/26</t>
+    <t>22/5/2026</t>
   </si>
   <si>
     <t>Tezzio Acosta</t>
@@ -392,16 +392,16 @@
     <t>Alexander Velazquez</t>
   </si>
   <si>
-    <t>25/5/26</t>
+    <t>25/5/2026</t>
   </si>
   <si>
     <t>MC 20</t>
   </si>
   <si>
-    <t>23/5/26</t>
+    <t>23/5/2026</t>
   </si>
   <si>
-    <t>27/5/26</t>
+    <t>27/5/2026</t>
   </si>
   <si>
     <t>U16</t>
@@ -428,7 +428,7 @@
     <t>DEF</t>
   </si>
   <si>
-    <t>28/5/26</t>
+    <t>28/5/2026</t>
   </si>
   <si>
     <t>EXTENSIVA</t>
@@ -440,13 +440,13 @@
     <t>INTRODUCTORIA</t>
   </si>
   <si>
-    <t>26/5/26</t>
+    <t>26/5/2026</t>
   </si>
   <si>
     <t>Matteo Costantini</t>
   </si>
   <si>
-    <t>29/5/26</t>
+    <t>29/5/2026</t>
   </si>
   <si>
     <t>U15</t>
@@ -494,7 +494,7 @@
     <t>Lautaro Satragno</t>
   </si>
   <si>
-    <t>30/5/26</t>
+    <t>30/5/2026</t>
   </si>
   <si>
     <t>ESPEC脥FICO</t>
@@ -32573,7 +32573,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="203" spans="1:50">
+    <row r="203" ht="15.15" spans="1:50">
       <c r="A203" s="1">
         <v>46028</v>
       </c>
@@ -35613,7 +35613,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="223" spans="1:50">
+    <row r="223" ht="15.15" spans="1:50">
       <c r="A223" s="1" t="s">
         <v>138</v>
       </c>
@@ -35765,7 +35765,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="224" spans="1:50">
+    <row r="224" ht="15.15" spans="1:50">
       <c r="A224" s="1" t="s">
         <v>138</v>
       </c>
@@ -35917,7 +35917,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="225" spans="1:50">
+    <row r="225" ht="15.15" spans="1:50">
       <c r="A225" s="1" t="s">
         <v>138</v>
       </c>
@@ -36069,7 +36069,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="226" spans="1:50">
+    <row r="226" ht="15.15" spans="1:50">
       <c r="A226" s="1" t="s">
         <v>138</v>
       </c>
@@ -36221,7 +36221,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="227" spans="1:50">
+    <row r="227" ht="15.15" spans="1:50">
       <c r="A227" s="1" t="s">
         <v>138</v>
       </c>
@@ -36373,7 +36373,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="228" spans="1:50">
+    <row r="228" ht="15.15" spans="1:50">
       <c r="A228" s="1" t="s">
         <v>138</v>
       </c>
@@ -36525,7 +36525,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="229" spans="1:50">
+    <row r="229" ht="15.15" spans="1:50">
       <c r="A229" s="1" t="s">
         <v>138</v>
       </c>
@@ -40303,7 +40303,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="254" spans="1:50">
+    <row r="254" ht="15.15" spans="1:50">
       <c r="A254" s="11">
         <v>46059</v>
       </c>
@@ -40456,7 +40456,7 @@
       </c>
     </row>
     <row r="255" ht="29.55" spans="1:50">
-      <c r="A255" s="11" t="s">
+      <c r="A255" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B255" t="s">
@@ -40608,7 +40608,7 @@
       </c>
     </row>
     <row r="256" ht="29.55" spans="1:50">
-      <c r="A256" s="11" t="s">
+      <c r="A256" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B256" t="s">
@@ -40760,7 +40760,7 @@
       </c>
     </row>
     <row r="257" ht="29.55" spans="1:50">
-      <c r="A257" s="11" t="s">
+      <c r="A257" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B257" t="s">
@@ -40912,7 +40912,7 @@
       </c>
     </row>
     <row r="258" ht="29.55" spans="1:50">
-      <c r="A258" s="11" t="s">
+      <c r="A258" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B258" t="s">
@@ -41064,7 +41064,7 @@
       </c>
     </row>
     <row r="259" ht="29.55" spans="1:50">
-      <c r="A259" s="11" t="s">
+      <c r="A259" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B259" t="s">
@@ -41216,7 +41216,7 @@
       </c>
     </row>
     <row r="260" ht="29.55" spans="1:50">
-      <c r="A260" s="11" t="s">
+      <c r="A260" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B260" t="s">
@@ -41368,7 +41368,7 @@
       </c>
     </row>
     <row r="261" ht="29.55" spans="1:50">
-      <c r="A261" s="11" t="s">
+      <c r="A261" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B261" t="s">
@@ -41520,7 +41520,7 @@
       </c>
     </row>
     <row r="262" ht="29.55" spans="1:50">
-      <c r="A262" s="11" t="s">
+      <c r="A262" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B262" t="s">
@@ -41672,7 +41672,7 @@
       </c>
     </row>
     <row r="263" ht="29.55" spans="1:50">
-      <c r="A263" s="11" t="s">
+      <c r="A263" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B263" t="s">
@@ -41824,7 +41824,7 @@
       </c>
     </row>
     <row r="264" ht="29.55" spans="1:50">
-      <c r="A264" s="11" t="s">
+      <c r="A264" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B264" t="s">
@@ -41975,7 +41975,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="265" spans="1:50">
+    <row r="265" ht="15.15" spans="1:50">
       <c r="A265" s="11">
         <v>46059</v>
       </c>
@@ -43191,7 +43191,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="273" spans="1:50">
+    <row r="273" ht="15.15" spans="1:50">
       <c r="A273" s="1">
         <v>46059</v>
       </c>
@@ -43343,7 +43343,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="274" spans="1:50">
+    <row r="274" ht="15.15" spans="1:50">
       <c r="A274" s="12" t="s">
         <v>154</v>
       </c>
@@ -43495,7 +43495,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="275" spans="1:50">
+    <row r="275" ht="15.15" spans="1:50">
       <c r="A275" s="12" t="s">
         <v>154</v>
       </c>
@@ -43647,7 +43647,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="276" spans="1:50">
+    <row r="276" ht="15.15" spans="1:50">
       <c r="A276" s="12" t="s">
         <v>154</v>
       </c>
@@ -43799,7 +43799,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="277" spans="1:50">
+    <row r="277" ht="15.15" spans="1:50">
       <c r="A277" s="12" t="s">
         <v>154</v>
       </c>
@@ -43951,7 +43951,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="278" spans="1:50">
+    <row r="278" ht="15.15" spans="1:50">
       <c r="A278" s="12" t="s">
         <v>154</v>
       </c>
@@ -44103,7 +44103,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="279" spans="1:50">
+    <row r="279" ht="15.15" spans="1:50">
       <c r="A279" s="12" t="s">
         <v>154</v>
       </c>
@@ -44255,7 +44255,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="280" spans="1:50">
+    <row r="280" ht="15.15" spans="1:50">
       <c r="A280" s="12" t="s">
         <v>154</v>
       </c>
@@ -44407,7 +44407,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="281" spans="1:50">
+    <row r="281" ht="15.15" spans="1:50">
       <c r="A281" s="12" t="s">
         <v>154</v>
       </c>
@@ -44559,7 +44559,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="282" spans="1:50">
+    <row r="282" ht="15.15" spans="1:50">
       <c r="A282" s="12" t="s">
         <v>154</v>
       </c>
@@ -44711,7 +44711,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="283" spans="1:50">
+    <row r="283" ht="15.15" spans="1:50">
       <c r="A283" s="12" t="s">
         <v>154</v>
       </c>
@@ -45015,7 +45015,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="285" spans="1:50">
+    <row r="285" ht="15.15" spans="1:50">
       <c r="A285" s="12" t="s">
         <v>154</v>
       </c>
@@ -45167,7 +45167,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="286" spans="1:50">
+    <row r="286" ht="15.15" spans="1:50">
       <c r="A286" s="12" t="s">
         <v>154</v>
       </c>
@@ -45319,7 +45319,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="287" spans="1:50">
+    <row r="287" ht="15.15" spans="1:50">
       <c r="A287" s="12" t="s">
         <v>154</v>
       </c>
@@ -45471,7 +45471,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="288" spans="1:50">
+    <row r="288" ht="15.15" spans="1:50">
       <c r="A288" s="12" t="s">
         <v>154</v>
       </c>
@@ -45623,7 +45623,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="289" spans="1:50">
+    <row r="289" ht="15.15" spans="1:50">
       <c r="A289" s="12" t="s">
         <v>154</v>
       </c>
@@ -45775,7 +45775,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="290" spans="1:50">
+    <row r="290" ht="15.15" spans="1:50">
       <c r="A290" s="12" t="s">
         <v>154</v>
       </c>
@@ -45927,7 +45927,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="291" spans="1:50">
+    <row r="291" ht="15.15" spans="1:50">
       <c r="A291" s="12" t="s">
         <v>154</v>
       </c>
@@ -46231,7 +46231,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="293" spans="1:50">
+    <row r="293" ht="15.15" spans="1:50">
       <c r="A293" s="12" t="s">
         <v>154</v>
       </c>
@@ -46535,7 +46535,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="295" spans="1:50">
+    <row r="295" ht="15.15" spans="1:50">
       <c r="A295" s="12" t="s">
         <v>154</v>
       </c>
@@ -46687,7 +46687,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="296" spans="1:50">
+    <row r="296" ht="15.15" spans="1:50">
       <c r="A296" s="12" t="s">
         <v>154</v>
       </c>
@@ -46839,7 +46839,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="297" spans="1:50">
+    <row r="297" ht="15.15" spans="1:50">
       <c r="A297" s="12" t="s">
         <v>154</v>
       </c>

--- a/GPS_Formativas_2026.xlsx
+++ b/GPS_Formativas_2026.xlsx
@@ -32725,7 +32725,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="204" spans="1:50">
+    <row r="204" ht="15.15" spans="1:50">
       <c r="A204" s="1">
         <v>46028</v>
       </c>
@@ -32877,7 +32877,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="205" spans="1:50">
+    <row r="205" ht="15.15" spans="1:50">
       <c r="A205" s="1">
         <v>46028</v>
       </c>
@@ -33029,7 +33029,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="206" spans="1:50">
+    <row r="206" ht="15.15" spans="1:50">
       <c r="A206" s="1">
         <v>46028</v>
       </c>
@@ -33181,7 +33181,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="207" spans="1:50">
+    <row r="207" ht="15.15" spans="1:50">
       <c r="A207" s="1">
         <v>46028</v>
       </c>
@@ -33333,7 +33333,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="208" spans="1:50">
+    <row r="208" ht="15.15" spans="1:50">
       <c r="A208" s="1">
         <v>46028</v>
       </c>
@@ -33485,7 +33485,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="209" spans="1:50">
+    <row r="209" ht="15.15" spans="1:50">
       <c r="A209" s="1">
         <v>46028</v>
       </c>
@@ -33637,7 +33637,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="210" spans="1:50">
+    <row r="210" ht="15.15" spans="1:50">
       <c r="A210" s="1">
         <v>46028</v>
       </c>
@@ -33789,7 +33789,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="211" spans="1:50">
+    <row r="211" ht="15.15" spans="1:50">
       <c r="A211" s="1">
         <v>46059</v>
       </c>
@@ -33941,7 +33941,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="212" spans="1:50">
+    <row r="212" ht="15.15" spans="1:50">
       <c r="A212" s="1">
         <v>46059</v>
       </c>
@@ -34093,7 +34093,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="213" spans="1:50">
+    <row r="213" ht="15.15" spans="1:50">
       <c r="A213" s="1">
         <v>46059</v>
       </c>
@@ -34245,7 +34245,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="214" spans="1:50">
+    <row r="214" ht="15.15" spans="1:50">
       <c r="A214" s="1">
         <v>46059</v>
       </c>
@@ -34397,7 +34397,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="215" spans="1:50">
+    <row r="215" ht="15.15" spans="1:50">
       <c r="A215" s="1">
         <v>46059</v>
       </c>
@@ -34549,7 +34549,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="216" spans="1:50">
+    <row r="216" ht="15.15" spans="1:50">
       <c r="A216" s="1">
         <v>46059</v>
       </c>
@@ -34701,7 +34701,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="217" spans="1:50">
+    <row r="217" ht="15.15" spans="1:50">
       <c r="A217" s="1">
         <v>46059</v>
       </c>
@@ -34853,7 +34853,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="218" spans="1:50">
+    <row r="218" ht="15.15" spans="1:50">
       <c r="A218" s="1">
         <v>46059</v>
       </c>
@@ -37577,7 +37577,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="236" spans="1:50">
+    <row r="236" ht="15.15" spans="1:50">
       <c r="A236" s="1">
         <v>46059</v>
       </c>
@@ -37727,7 +37727,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="237" spans="1:50">
+    <row r="237" ht="15.15" spans="1:50">
       <c r="A237" s="1">
         <v>46059</v>
       </c>
@@ -37877,7 +37877,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="238" spans="1:50">
+    <row r="238" ht="15.15" spans="1:50">
       <c r="A238" s="1">
         <v>46059</v>
       </c>
@@ -38027,7 +38027,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="239" spans="1:50">
+    <row r="239" ht="15.15" spans="1:50">
       <c r="A239" s="1">
         <v>46059</v>
       </c>
@@ -38177,7 +38177,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="240" spans="1:50">
+    <row r="240" ht="15.15" spans="1:50">
       <c r="A240" s="1">
         <v>46059</v>
       </c>
@@ -39391,7 +39391,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="248" spans="1:50">
+    <row r="248" ht="15.15" spans="1:50">
       <c r="A248" s="11">
         <v>46059</v>
       </c>
@@ -39543,7 +39543,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="249" spans="1:50">
+    <row r="249" ht="15.15" spans="1:50">
       <c r="A249" s="11">
         <v>46059</v>
       </c>
@@ -39695,7 +39695,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="250" spans="1:50">
+    <row r="250" ht="15.15" spans="1:50">
       <c r="A250" s="11">
         <v>46059</v>
       </c>
@@ -39847,7 +39847,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="251" spans="1:50">
+    <row r="251" ht="15.15" spans="1:50">
       <c r="A251" s="11">
         <v>46059</v>
       </c>
@@ -39999,7 +39999,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="252" spans="1:50">
+    <row r="252" ht="15.15" spans="1:50">
       <c r="A252" s="11">
         <v>46059</v>
       </c>
@@ -40151,7 +40151,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="253" spans="1:50">
+    <row r="253" ht="15.15" spans="1:50">
       <c r="A253" s="11">
         <v>46059</v>
       </c>
@@ -42127,7 +42127,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="266" spans="1:50">
+    <row r="266" ht="15.15" spans="1:50">
       <c r="A266" s="1">
         <v>46059</v>
       </c>
@@ -42279,7 +42279,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="267" spans="1:50">
+    <row r="267" ht="15.15" spans="1:50">
       <c r="A267" s="1">
         <v>46059</v>
       </c>
@@ -42431,7 +42431,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="268" spans="1:50">
+    <row r="268" ht="15.15" spans="1:50">
       <c r="A268" s="1">
         <v>46059</v>
       </c>
@@ -42583,7 +42583,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="269" spans="1:50">
+    <row r="269" ht="15.15" spans="1:50">
       <c r="A269" s="1">
         <v>46059</v>
       </c>
@@ -42735,7 +42735,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="270" spans="1:50">
+    <row r="270" ht="15.15" spans="1:50">
       <c r="A270" s="1">
         <v>46059</v>
       </c>
@@ -42887,7 +42887,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="271" spans="1:50">
+    <row r="271" ht="15.15" spans="1:50">
       <c r="A271" s="1">
         <v>46059</v>
       </c>
@@ -43039,7 +43039,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="272" spans="1:50">
+    <row r="272" ht="15.15" spans="1:50">
       <c r="A272" s="1">
         <v>46059</v>
       </c>
@@ -47751,7 +47751,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="303" spans="1:50">
+    <row r="303" ht="15.15" spans="1:50">
       <c r="A303" s="12">
         <v>46059</v>
       </c>
@@ -47903,7 +47903,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="304" spans="1:50">
+    <row r="304" ht="15.15" spans="1:50">
       <c r="A304" s="12">
         <v>46059</v>
       </c>
@@ -48055,7 +48055,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="305" spans="1:50">
+    <row r="305" ht="15.15" spans="1:50">
       <c r="A305" s="12">
         <v>46059</v>
       </c>
@@ -48207,7 +48207,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="306" spans="1:50">
+    <row r="306" ht="15.15" spans="1:50">
       <c r="A306" s="12">
         <v>46059</v>
       </c>
@@ -48359,7 +48359,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="307" spans="1:50">
+    <row r="307" ht="15.15" spans="1:50">
       <c r="A307" s="12">
         <v>46059</v>
       </c>
@@ -50639,7 +50639,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="322" spans="1:50">
+    <row r="322" ht="15.15" spans="1:50">
       <c r="A322" s="1">
         <v>46148</v>
       </c>
@@ -50791,7 +50791,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="323" spans="1:50">
+    <row r="323" ht="15.15" spans="1:50">
       <c r="A323" s="1">
         <v>46148</v>
       </c>
@@ -50943,7 +50943,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="324" spans="1:50">
+    <row r="324" ht="15.15" spans="1:50">
       <c r="A324" s="1">
         <v>46148</v>
       </c>
@@ -51095,7 +51095,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="325" spans="1:50">
+    <row r="325" ht="15.15" spans="1:50">
       <c r="A325" s="1">
         <v>46148</v>
       </c>
@@ -51247,7 +51247,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="326" spans="1:50">
+    <row r="326" ht="15.15" spans="1:50">
       <c r="A326" s="1">
         <v>46148</v>
       </c>
@@ -51399,7 +51399,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="327" spans="1:50">
+    <row r="327" ht="15.15" spans="1:50">
       <c r="A327" s="1">
         <v>46148</v>
       </c>
@@ -51551,7 +51551,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="328" spans="1:50">
+    <row r="328" ht="15.15" spans="1:50">
       <c r="A328" s="1">
         <v>46148</v>
       </c>
@@ -51703,7 +51703,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="329" spans="1:50">
+    <row r="329" ht="15.15" spans="1:50">
       <c r="A329" s="1">
         <v>46148</v>
       </c>
@@ -51855,7 +51855,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="330" spans="1:50">
+    <row r="330" ht="15.15" spans="1:50">
       <c r="A330" s="1">
         <v>46148</v>
       </c>
@@ -52007,7 +52007,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="331" spans="1:50">
+    <row r="331" ht="15.15" spans="1:50">
       <c r="A331" s="1">
         <v>46240</v>
       </c>
@@ -52159,7 +52159,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="332" spans="1:50">
+    <row r="332" ht="15.15" spans="1:50">
       <c r="A332" s="1">
         <v>46240</v>
       </c>
@@ -52311,7 +52311,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="333" spans="1:50">
+    <row r="333" ht="15.15" spans="1:50">
       <c r="A333" s="1">
         <v>46240</v>
       </c>
@@ -52463,7 +52463,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="334" spans="1:50">
+    <row r="334" ht="15.15" spans="1:50">
       <c r="A334" s="1">
         <v>46240</v>
       </c>
@@ -52615,7 +52615,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="335" spans="1:50">
+    <row r="335" ht="15.15" spans="1:50">
       <c r="A335" s="1">
         <v>46240</v>
       </c>
@@ -52767,7 +52767,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="336" spans="1:50">
+    <row r="336" ht="15.15" spans="1:50">
       <c r="A336" s="1">
         <v>46240</v>
       </c>
